--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.200001</v>
+        <v>34.799999</v>
       </c>
       <c r="H253" t="n">
-        <v>113.3576</v>
+        <v>115.3464</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.009998</v>
+        <v>47.025002</v>
       </c>
       <c r="H504" t="n">
-        <v>129.0243</v>
+        <v>129.0655</v>
       </c>
     </row>
     <row r="505">
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.48931899999999</v>
+        <v>64.489311</v>
       </c>
       <c r="H507" t="n">
-        <v>99.5643</v>
+        <v>99.5642</v>
       </c>
     </row>
     <row r="508">
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.103897</v>
+        <v>65.103905</v>
       </c>
       <c r="H514" t="n">
         <v>100.5131</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H518" t="n">
         <v>101.1632</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.386787</v>
+        <v>66.38678</v>
       </c>
       <c r="H522" t="n">
         <v>102.4937</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.564171</v>
+        <v>65.56416299999999</v>
       </c>
       <c r="H525" t="n">
         <v>101.2237</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.476028</v>
+        <v>65.47603599999999</v>
       </c>
       <c r="H526" t="n">
         <v>101.0876</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>65.926506</v>
+        <v>65.926498</v>
       </c>
       <c r="H528" t="n">
         <v>101.7831</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.485817</v>
+        <v>65.48582500000001</v>
       </c>
       <c r="H529" t="n">
         <v>101.1027</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.210503</v>
+        <v>66.21051</v>
       </c>
       <c r="H530" t="n">
         <v>102.2216</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.386787</v>
+        <v>66.38678</v>
       </c>
       <c r="H531" t="n">
         <v>102.4937</v>
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.308426</v>
+        <v>66.308441</v>
       </c>
       <c r="H532" t="n">
-        <v>102.3727</v>
+        <v>102.3728</v>
       </c>
     </row>
     <row r="533">
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H534" t="n">
         <v>103.0985</v>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.709953</v>
+        <v>66.709946</v>
       </c>
       <c r="H535" t="n">
-        <v>102.9927</v>
+        <v>102.9926</v>
       </c>
     </row>
     <row r="536">
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H537" t="n">
         <v>103.0985</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.943871</v>
+        <v>67.94386299999999</v>
       </c>
       <c r="H546" t="n">
         <v>104.8977</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.15063499999999</v>
+        <v>67.150627</v>
       </c>
       <c r="H548" t="n">
         <v>103.673</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.788292</v>
+        <v>66.788284</v>
       </c>
       <c r="H549" t="n">
         <v>103.1136</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.396568</v>
+        <v>66.396576</v>
       </c>
       <c r="H552" t="n">
         <v>102.5088</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.259468</v>
+        <v>66.25947600000001</v>
       </c>
       <c r="H553" t="n">
         <v>102.2972</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.494499</v>
+        <v>66.494507</v>
       </c>
       <c r="H554" t="n">
         <v>102.66</v>
@@ -21504,10 +21504,10 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.75891900000001</v>
+        <v>66.758911</v>
       </c>
       <c r="H555" t="n">
-        <v>103.0683</v>
+        <v>103.0682</v>
       </c>
     </row>
     <row r="556">
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.375877</v>
+        <v>67.37587000000001</v>
       </c>
       <c r="H556" t="n">
         <v>104.0208</v>
@@ -21618,10 +21618,10 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.620705</v>
+        <v>67.62069700000001</v>
       </c>
       <c r="H558" t="n">
-        <v>104.3988</v>
+        <v>104.3987</v>
       </c>
     </row>
     <row r="559">
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.248558</v>
+        <v>67.248566</v>
       </c>
       <c r="H560" t="n">
         <v>103.8242</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.748009</v>
+        <v>67.748001</v>
       </c>
       <c r="H562" t="n">
         <v>104.5953</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.89490499999999</v>
+        <v>67.894897</v>
       </c>
       <c r="H563" t="n">
         <v>104.8221</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.65986599999999</v>
+        <v>67.659859</v>
       </c>
       <c r="H564" t="n">
         <v>104.4592</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.601105</v>
+        <v>67.601112</v>
       </c>
       <c r="H566" t="n">
         <v>104.3685</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.85573599999999</v>
+        <v>67.855728</v>
       </c>
       <c r="H567" t="n">
         <v>104.7616</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.76759300000001</v>
+        <v>67.76758599999999</v>
       </c>
       <c r="H568" t="n">
         <v>104.6255</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>68.14952099999999</v>
+        <v>68.149513</v>
       </c>
       <c r="H569" t="n">
         <v>105.2152</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H570" t="n">
         <v>104.2778</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>67.61090900000001</v>
+        <v>67.610901</v>
       </c>
       <c r="H571" t="n">
         <v>104.3836</v>
@@ -22150,10 +22150,10 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>67.99722300000001</v>
+        <v>67.997215</v>
       </c>
       <c r="H572" t="n">
-        <v>104.9801</v>
+        <v>104.98</v>
       </c>
     </row>
     <row r="573">
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>68.272987</v>
+        <v>68.27299499999999</v>
       </c>
       <c r="H573" t="n">
         <v>105.4058</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>68.90331999999999</v>
+        <v>68.903328</v>
       </c>
       <c r="H578" t="n">
         <v>106.379</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>69.632149</v>
+        <v>69.632141</v>
       </c>
       <c r="H579" t="n">
         <v>107.5042</v>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.66628300000001</v>
+        <v>70.66629</v>
       </c>
       <c r="H585" t="n">
         <v>109.1008</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>71.69058200000001</v>
+        <v>71.690575</v>
       </c>
       <c r="H588" t="n">
         <v>110.6822</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.45946499999999</v>
+        <v>70.459457</v>
       </c>
       <c r="H590" t="n">
         <v>108.7815</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>70.804169</v>
+        <v>70.804176</v>
       </c>
       <c r="H595" t="n">
         <v>109.3137</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>72.084534</v>
+        <v>72.084541</v>
       </c>
       <c r="H599" t="n">
         <v>111.2904</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>73.28610999999999</v>
+        <v>73.286118</v>
       </c>
       <c r="H601" t="n">
         <v>113.1455</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>72.754272</v>
+        <v>72.754265</v>
       </c>
       <c r="H602" t="n">
         <v>112.3244</v>
@@ -23366,10 +23366,10 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>73.71946</v>
+        <v>73.71946699999999</v>
       </c>
       <c r="H604" t="n">
-        <v>113.8145</v>
+        <v>113.8146</v>
       </c>
     </row>
     <row r="605">
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.53692599999999</v>
+        <v>74.536934</v>
       </c>
       <c r="H606" t="n">
         <v>115.0766</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.241463</v>
+        <v>74.241455</v>
       </c>
       <c r="H608" t="n">
         <v>114.6205</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.30056</v>
+        <v>74.300552</v>
       </c>
       <c r="H609" t="n">
         <v>114.7117</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>75.69910400000001</v>
+        <v>75.699112</v>
       </c>
       <c r="H617" t="n">
         <v>116.8709</v>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>73.768715</v>
+        <v>73.76870700000001</v>
       </c>
       <c r="H620" t="n">
         <v>113.8906</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>73.128525</v>
+        <v>73.12853200000001</v>
       </c>
       <c r="H625" t="n">
         <v>112.9022</v>
@@ -24202,10 +24202,10 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>72.84290300000001</v>
+        <v>72.842911</v>
       </c>
       <c r="H626" t="n">
-        <v>112.4612</v>
+        <v>112.4613</v>
       </c>
     </row>
     <row r="627">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.629997</v>
+        <v>81.33000199999999</v>
       </c>
       <c r="H755" t="n">
-        <v>126.0275</v>
+        <v>125.5644</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>126.480003</v>
+        <v>126.43</v>
       </c>
       <c r="H1006" t="n">
-        <v>118.6158</v>
+        <v>118.5689</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>126.480003</v>
+        <v>126.43</v>
       </c>
       <c r="H1257" t="n">
-        <v>118.6158</v>
+        <v>118.5689</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>126.480003</v>
+        <v>126.43</v>
       </c>
       <c r="H1508" t="n">
-        <v>118.6158</v>
+        <v>118.5689</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>54.284752</v>
+        <v>54.284748</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.645649</v>
+        <v>53.645645</v>
       </c>
       <c r="H1511" t="n">
         <v>98.8227</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>53.57682</v>
+        <v>53.576817</v>
       </c>
       <c r="H1517" t="n">
         <v>98.69589999999999</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.58263</v>
+        <v>55.582626</v>
       </c>
       <c r="H1523" t="n">
         <v>102.3909</v>
@@ -58329,7 +58329,7 @@
         <v>55.562965</v>
       </c>
       <c r="H1524" t="n">
-        <v>102.3546</v>
+        <v>102.3547</v>
       </c>
     </row>
     <row r="1525">
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.680954</v>
+        <v>55.680958</v>
       </c>
       <c r="H1527" t="n">
         <v>102.572</v>
@@ -58481,7 +58481,7 @@
         <v>54.943523</v>
       </c>
       <c r="H1528" t="n">
-        <v>101.2135</v>
+        <v>101.2136</v>
       </c>
     </row>
     <row r="1529">
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.051685</v>
+        <v>55.051682</v>
       </c>
       <c r="H1530" t="n">
         <v>101.4128</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.779278</v>
+        <v>55.779274</v>
       </c>
       <c r="H1532" t="n">
         <v>102.7531</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.779278</v>
+        <v>55.779274</v>
       </c>
       <c r="H1534" t="n">
         <v>102.7531</v>
@@ -58782,10 +58782,10 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.798939</v>
+        <v>55.798943</v>
       </c>
       <c r="H1536" t="n">
-        <v>102.7893</v>
+        <v>102.7894</v>
       </c>
     </row>
     <row r="1537">
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.818611</v>
+        <v>55.818607</v>
       </c>
       <c r="H1542" t="n">
         <v>102.8256</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.690788</v>
+        <v>55.690784</v>
       </c>
       <c r="H1544" t="n">
         <v>102.5901</v>
@@ -59124,10 +59124,10 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.798939</v>
+        <v>55.798943</v>
       </c>
       <c r="H1545" t="n">
-        <v>102.7893</v>
+        <v>102.7894</v>
       </c>
     </row>
     <row r="1546">
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.385986</v>
+        <v>55.385983</v>
       </c>
       <c r="H1546" t="n">
         <v>102.0286</v>
@@ -59203,7 +59203,7 @@
         <v>55.100842</v>
       </c>
       <c r="H1547" t="n">
-        <v>101.5033</v>
+        <v>101.5034</v>
       </c>
     </row>
     <row r="1548">
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.907101</v>
+        <v>55.907104</v>
       </c>
       <c r="H1548" t="n">
         <v>102.9886</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>57.057491</v>
+        <v>57.057487</v>
       </c>
       <c r="H1550" t="n">
         <v>105.1078</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>56.133247</v>
+        <v>56.133244</v>
       </c>
       <c r="H1552" t="n">
         <v>103.4052</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.855034</v>
+        <v>54.85503</v>
       </c>
       <c r="H1554" t="n">
         <v>101.0505</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.002514</v>
+        <v>55.002518</v>
       </c>
       <c r="H1556" t="n">
         <v>101.3222</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.864864</v>
+        <v>54.864861</v>
       </c>
       <c r="H1557" t="n">
         <v>101.0686</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.516705</v>
+        <v>56.516708</v>
       </c>
       <c r="H1567" t="n">
         <v>104.1116</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.703522</v>
+        <v>56.703526</v>
       </c>
       <c r="H1571" t="n">
         <v>104.4557</v>
@@ -61217,7 +61217,7 @@
         <v>59.392048</v>
       </c>
       <c r="H1600" t="n">
-        <v>109.4083</v>
+        <v>109.4084</v>
       </c>
     </row>
     <row r="1601">
@@ -61521,7 +61521,7 @@
         <v>60.723927</v>
       </c>
       <c r="H1608" t="n">
-        <v>111.8618</v>
+        <v>111.8619</v>
       </c>
     </row>
     <row r="1609">
@@ -61635,7 +61635,7 @@
         <v>60.497017</v>
       </c>
       <c r="H1611" t="n">
-        <v>111.4438</v>
+        <v>111.4439</v>
       </c>
     </row>
     <row r="1612">
@@ -62015,7 +62015,7 @@
         <v>61.986752</v>
       </c>
       <c r="H1621" t="n">
-        <v>114.1881</v>
+        <v>114.1882</v>
       </c>
     </row>
     <row r="1622">
@@ -62053,7 +62053,7 @@
         <v>62.026215</v>
       </c>
       <c r="H1622" t="n">
-        <v>114.2608</v>
+        <v>114.2609</v>
       </c>
     </row>
     <row r="1623">
@@ -62585,7 +62585,7 @@
         <v>57.083481</v>
       </c>
       <c r="H1636" t="n">
-        <v>105.1556</v>
+        <v>105.1557</v>
       </c>
     </row>
     <row r="1637">
@@ -63915,7 +63915,7 @@
         <v>60.070175</v>
       </c>
       <c r="H1671" t="n">
-        <v>110.6575</v>
+        <v>110.6576</v>
       </c>
     </row>
     <row r="1672">
@@ -64637,7 +64637,7 @@
         <v>61.860214</v>
       </c>
       <c r="H1690" t="n">
-        <v>113.955</v>
+        <v>113.9551</v>
       </c>
     </row>
     <row r="1691">
@@ -64675,7 +64675,7 @@
         <v>61.533855</v>
       </c>
       <c r="H1691" t="n">
-        <v>113.3538</v>
+        <v>113.3539</v>
       </c>
     </row>
     <row r="1692">
@@ -65321,7 +65321,7 @@
         <v>64.660004</v>
       </c>
       <c r="H1708" t="n">
-        <v>119.1126</v>
+        <v>119.1127</v>
       </c>
     </row>
     <row r="1709">
@@ -65701,7 +65701,7 @@
         <v>64.199997</v>
       </c>
       <c r="H1718" t="n">
-        <v>118.2652</v>
+        <v>118.2653</v>
       </c>
     </row>
     <row r="1719">
@@ -66233,7 +66233,7 @@
         <v>65.550003</v>
       </c>
       <c r="H1732" t="n">
-        <v>120.7521</v>
+        <v>120.7522</v>
       </c>
     </row>
     <row r="1733">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.669998</v>
+        <v>63.580002</v>
       </c>
       <c r="H1760" t="n">
-        <v>117.2889</v>
+        <v>117.1231</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.226524</v>
+        <v>64.22653200000001</v>
       </c>
       <c r="H506" t="n">
         <v>99.1585</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.489311</v>
+        <v>64.48931899999999</v>
       </c>
       <c r="H507" t="n">
-        <v>99.5642</v>
+        <v>99.5643</v>
       </c>
     </row>
     <row r="508">
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.702377</v>
+        <v>64.70238500000001</v>
       </c>
       <c r="H510" t="n">
         <v>99.89319999999999</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>64.810104</v>
+        <v>64.810097</v>
       </c>
       <c r="H513" t="n">
         <v>100.0595</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.103905</v>
+        <v>65.103897</v>
       </c>
       <c r="H514" t="n">
         <v>100.5131</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.525002</v>
+        <v>65.52499400000001</v>
       </c>
       <c r="H518" t="n">
         <v>101.1632</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.23120900000001</v>
+        <v>65.231201</v>
       </c>
       <c r="H524" t="n">
         <v>100.7096</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.47603599999999</v>
+        <v>65.476028</v>
       </c>
       <c r="H526" t="n">
         <v>101.0876</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>65.926498</v>
+        <v>65.926506</v>
       </c>
       <c r="H528" t="n">
         <v>101.7831</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.48582500000001</v>
+        <v>65.485817</v>
       </c>
       <c r="H529" t="n">
         <v>101.1027</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.21051</v>
+        <v>66.210503</v>
       </c>
       <c r="H530" t="n">
         <v>102.2216</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.308441</v>
+        <v>66.30843400000001</v>
       </c>
       <c r="H532" t="n">
         <v>102.3728</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.435745</v>
+        <v>66.435738</v>
       </c>
       <c r="H533" t="n">
         <v>102.5693</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H534" t="n">
         <v>103.0985</v>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.709946</v>
+        <v>66.709953</v>
       </c>
       <c r="H535" t="n">
-        <v>102.9926</v>
+        <v>102.9927</v>
       </c>
     </row>
     <row r="536">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.582634</v>
+        <v>66.58264200000001</v>
       </c>
       <c r="H536" t="n">
         <v>102.7961</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H537" t="n">
         <v>103.0985</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.739334</v>
+        <v>66.73932600000001</v>
       </c>
       <c r="H544" t="n">
         <v>103.038</v>
@@ -21124,10 +21124,10 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>67.317108</v>
+        <v>67.317116</v>
       </c>
       <c r="H545" t="n">
-        <v>103.93</v>
+        <v>103.9301</v>
       </c>
     </row>
     <row r="546">
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.94386299999999</v>
+        <v>67.943871</v>
       </c>
       <c r="H546" t="n">
         <v>104.8977</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.150627</v>
+        <v>67.150642</v>
       </c>
       <c r="H548" t="n">
         <v>103.673</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.788284</v>
+        <v>66.788292</v>
       </c>
       <c r="H549" t="n">
         <v>103.1136</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.12236</v>
+        <v>66.12236799999999</v>
       </c>
       <c r="H550" t="n">
         <v>102.0855</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.396576</v>
+        <v>66.396568</v>
       </c>
       <c r="H552" t="n">
         <v>102.5088</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.494507</v>
+        <v>66.494499</v>
       </c>
       <c r="H554" t="n">
         <v>102.66</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.37587000000001</v>
+        <v>67.375877</v>
       </c>
       <c r="H556" t="n">
         <v>104.0208</v>
@@ -21618,10 +21618,10 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.62069700000001</v>
+        <v>67.620705</v>
       </c>
       <c r="H558" t="n">
-        <v>104.3987</v>
+        <v>104.3988</v>
       </c>
     </row>
     <row r="559">
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.248566</v>
+        <v>67.248558</v>
       </c>
       <c r="H560" t="n">
         <v>103.8242</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.317108</v>
+        <v>67.317116</v>
       </c>
       <c r="H561" t="n">
-        <v>103.93</v>
+        <v>103.9301</v>
       </c>
     </row>
     <row r="562">
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.748001</v>
+        <v>67.748009</v>
       </c>
       <c r="H562" t="n">
         <v>104.5953</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.659859</v>
+        <v>67.65986599999999</v>
       </c>
       <c r="H564" t="n">
         <v>104.4592</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.76758599999999</v>
+        <v>67.76759300000001</v>
       </c>
       <c r="H568" t="n">
         <v>104.6255</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>68.149513</v>
+        <v>68.14952099999999</v>
       </c>
       <c r="H569" t="n">
         <v>105.2152</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.54235799999999</v>
+        <v>67.542351</v>
       </c>
       <c r="H570" t="n">
         <v>104.2778</v>
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>54.284748</v>
+        <v>54.284752</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.068439</v>
+        <v>54.068443</v>
       </c>
       <c r="H1512" t="n">
         <v>99.6015</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>53.999607</v>
+        <v>53.999611</v>
       </c>
       <c r="H1513" t="n">
         <v>99.4747</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.048775</v>
+        <v>54.048771</v>
       </c>
       <c r="H1515" t="n">
         <v>99.56529999999999</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.012352</v>
+        <v>55.012348</v>
       </c>
       <c r="H1521" t="n">
         <v>101.3403</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.582626</v>
+        <v>55.58263</v>
       </c>
       <c r="H1523" t="n">
         <v>102.3909</v>
@@ -58329,7 +58329,7 @@
         <v>55.562965</v>
       </c>
       <c r="H1524" t="n">
-        <v>102.3547</v>
+        <v>102.3546</v>
       </c>
     </row>
     <row r="1525">
@@ -58481,7 +58481,7 @@
         <v>54.943523</v>
       </c>
       <c r="H1528" t="n">
-        <v>101.2136</v>
+        <v>101.2135</v>
       </c>
     </row>
     <row r="1529">
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.25816</v>
+        <v>55.258163</v>
       </c>
       <c r="H1529" t="n">
         <v>101.7932</v>
@@ -58592,10 +58592,10 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.336819</v>
+        <v>55.336815</v>
       </c>
       <c r="H1531" t="n">
-        <v>101.9381</v>
+        <v>101.938</v>
       </c>
     </row>
     <row r="1532">
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1532" t="n">
         <v>102.7531</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1534" t="n">
         <v>102.7531</v>
@@ -58785,7 +58785,7 @@
         <v>55.798943</v>
       </c>
       <c r="H1536" t="n">
-        <v>102.7894</v>
+        <v>102.7893</v>
       </c>
     </row>
     <row r="1537">
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>56.280735</v>
+        <v>56.280731</v>
       </c>
       <c r="H1538" t="n">
         <v>103.6769</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>56.162743</v>
+        <v>56.162739</v>
       </c>
       <c r="H1539" t="n">
         <v>103.4595</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>56.113579</v>
+        <v>56.113583</v>
       </c>
       <c r="H1540" t="n">
         <v>103.369</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>56.054585</v>
+        <v>56.054581</v>
       </c>
       <c r="H1541" t="n">
         <v>103.2603</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>55.848106</v>
+        <v>55.848103</v>
       </c>
       <c r="H1543" t="n">
         <v>102.8799</v>
@@ -59127,7 +59127,7 @@
         <v>55.798943</v>
       </c>
       <c r="H1545" t="n">
-        <v>102.7894</v>
+        <v>102.7893</v>
       </c>
     </row>
     <row r="1546">
@@ -59203,7 +59203,7 @@
         <v>55.100842</v>
       </c>
       <c r="H1547" t="n">
-        <v>101.5034</v>
+        <v>101.5033</v>
       </c>
     </row>
     <row r="1548">
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.907104</v>
+        <v>55.907101</v>
       </c>
       <c r="H1548" t="n">
         <v>102.9886</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>56.634693</v>
+        <v>56.634697</v>
       </c>
       <c r="H1549" t="n">
         <v>104.3289</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.828438</v>
+        <v>55.828442</v>
       </c>
       <c r="H1553" t="n">
         <v>102.8437</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.85503</v>
+        <v>54.855034</v>
       </c>
       <c r="H1554" t="n">
         <v>101.0505</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.864861</v>
+        <v>54.864864</v>
       </c>
       <c r="H1557" t="n">
         <v>101.0686</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>56.054585</v>
+        <v>56.054581</v>
       </c>
       <c r="H1560" t="n">
         <v>103.2603</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1561" t="n">
         <v>103.3327</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.280735</v>
+        <v>56.280731</v>
       </c>
       <c r="H1562" t="n">
         <v>103.6769</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1563" t="n">
         <v>103.3327</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.162743</v>
+        <v>56.162739</v>
       </c>
       <c r="H1564" t="n">
         <v>103.4595</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.516708</v>
+        <v>56.516705</v>
       </c>
       <c r="H1567" t="n">
         <v>104.1116</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.428215</v>
+        <v>56.428219</v>
       </c>
       <c r="H1568" t="n">
         <v>103.9486</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.369221</v>
+        <v>56.369225</v>
       </c>
       <c r="H1569" t="n">
         <v>103.8399</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.703526</v>
+        <v>56.703522</v>
       </c>
       <c r="H1571" t="n">
         <v>104.4557</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.826939</v>
+        <v>56.826942</v>
       </c>
       <c r="H1573" t="n">
         <v>104.6831</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.521103</v>
+        <v>56.521107</v>
       </c>
       <c r="H1575" t="n">
         <v>104.1197</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>57.320232</v>
+        <v>57.320229</v>
       </c>
       <c r="H1577" t="n">
         <v>105.5918</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>57.211712</v>
+        <v>57.211708</v>
       </c>
       <c r="H1578" t="n">
         <v>105.3919</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.760639</v>
+        <v>58.760635</v>
       </c>
       <c r="H1583" t="n">
         <v>108.2452</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.589367</v>
+        <v>59.589363</v>
       </c>
       <c r="H1587" t="n">
         <v>109.7718</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.688019</v>
+        <v>59.688023</v>
       </c>
       <c r="H1588" t="n">
         <v>109.9536</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.707756</v>
+        <v>59.707752</v>
       </c>
       <c r="H1590" t="n">
         <v>109.9899</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>58.829697</v>
+        <v>58.8297</v>
       </c>
       <c r="H1594" t="n">
         <v>108.3724</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.865604</v>
+        <v>59.865608</v>
       </c>
       <c r="H1599" t="n">
         <v>110.2807</v>
@@ -61217,7 +61217,7 @@
         <v>59.392048</v>
       </c>
       <c r="H1600" t="n">
-        <v>109.4084</v>
+        <v>109.4083</v>
       </c>
     </row>
     <row r="1601">
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.723927</v>
+        <v>60.72393</v>
       </c>
       <c r="H1608" t="n">
         <v>111.8619</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.684467</v>
+        <v>60.684464</v>
       </c>
       <c r="H1609" t="n">
         <v>111.7892</v>
@@ -61635,7 +61635,7 @@
         <v>60.497017</v>
       </c>
       <c r="H1611" t="n">
-        <v>111.4439</v>
+        <v>111.4438</v>
       </c>
     </row>
     <row r="1612">
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>61.779564</v>
+        <v>61.779568</v>
       </c>
       <c r="H1617" t="n">
         <v>113.8065</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>61.592117</v>
+        <v>61.592121</v>
       </c>
       <c r="H1619" t="n">
         <v>113.4612</v>
@@ -62015,7 +62015,7 @@
         <v>61.986752</v>
       </c>
       <c r="H1621" t="n">
-        <v>114.1882</v>
+        <v>114.1881</v>
       </c>
     </row>
     <row r="1622">
@@ -62053,7 +62053,7 @@
         <v>62.026215</v>
       </c>
       <c r="H1622" t="n">
-        <v>114.2609</v>
+        <v>114.2608</v>
       </c>
     </row>
     <row r="1623">
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>59.194733</v>
+        <v>59.194729</v>
       </c>
       <c r="H1624" t="n">
         <v>109.0449</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>59.954399</v>
+        <v>59.954395</v>
       </c>
       <c r="H1625" t="n">
         <v>110.4443</v>
@@ -62354,7 +62354,7 @@
         </is>
       </c>
       <c r="G1630" t="n">
-        <v>59.007282</v>
+        <v>59.007286</v>
       </c>
       <c r="H1630" t="n">
         <v>108.6996</v>
@@ -62392,7 +62392,7 @@
         </is>
       </c>
       <c r="G1631" t="n">
-        <v>58.661976</v>
+        <v>58.66198</v>
       </c>
       <c r="H1631" t="n">
         <v>108.0635</v>
@@ -62430,7 +62430,7 @@
         </is>
       </c>
       <c r="G1632" t="n">
-        <v>58.336411</v>
+        <v>58.336407</v>
       </c>
       <c r="H1632" t="n">
         <v>107.4637</v>
@@ -62585,7 +62585,7 @@
         <v>57.083481</v>
       </c>
       <c r="H1636" t="n">
-        <v>105.1557</v>
+        <v>105.1556</v>
       </c>
     </row>
     <row r="1637">
@@ -63915,7 +63915,7 @@
         <v>60.070175</v>
       </c>
       <c r="H1671" t="n">
-        <v>110.6576</v>
+        <v>110.6575</v>
       </c>
     </row>
     <row r="1672">
@@ -64637,7 +64637,7 @@
         <v>61.860214</v>
       </c>
       <c r="H1690" t="n">
-        <v>113.9551</v>
+        <v>113.955</v>
       </c>
     </row>
     <row r="1691">
@@ -64675,7 +64675,7 @@
         <v>61.533855</v>
       </c>
       <c r="H1691" t="n">
-        <v>113.3539</v>
+        <v>113.3538</v>
       </c>
     </row>
     <row r="1692">
@@ -65321,7 +65321,7 @@
         <v>64.660004</v>
       </c>
       <c r="H1708" t="n">
-        <v>119.1127</v>
+        <v>119.1126</v>
       </c>
     </row>
     <row r="1709">
@@ -65701,7 +65701,7 @@
         <v>64.199997</v>
       </c>
       <c r="H1718" t="n">
-        <v>118.2653</v>
+        <v>118.2652</v>
       </c>
     </row>
     <row r="1719">
@@ -66233,7 +66233,7 @@
         <v>65.550003</v>
       </c>
       <c r="H1732" t="n">
-        <v>120.7522</v>
+        <v>120.7521</v>
       </c>
     </row>
     <row r="1733">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.22653200000001</v>
+        <v>64.226524</v>
       </c>
       <c r="H506" t="n">
         <v>99.1585</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.48931899999999</v>
+        <v>64.489311</v>
       </c>
       <c r="H507" t="n">
-        <v>99.5643</v>
+        <v>99.5642</v>
       </c>
     </row>
     <row r="508">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.799999</v>
+        <v>34.73</v>
       </c>
       <c r="H253" t="n">
-        <v>115.3464</v>
+        <v>115.1144</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>46.91</v>
+        <v>46.665001</v>
       </c>
       <c r="H504" t="n">
-        <v>128.7498</v>
+        <v>128.0774</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.771568</v>
+        <v>64.77156100000001</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.226524</v>
+        <v>64.22653200000001</v>
       </c>
       <c r="H506" t="n">
         <v>99.1585</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.489304</v>
+        <v>64.48931899999999</v>
       </c>
       <c r="H507" t="n">
-        <v>99.5642</v>
+        <v>99.5643</v>
       </c>
     </row>
     <row r="508">
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>64.810112</v>
+        <v>64.810104</v>
       </c>
       <c r="H513" t="n">
         <v>100.0595</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.103897</v>
+        <v>65.103905</v>
       </c>
       <c r="H514" t="n">
         <v>100.5131</v>
@@ -19984,10 +19984,10 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.035347</v>
+        <v>65.035355</v>
       </c>
       <c r="H515" t="n">
-        <v>100.4072</v>
+        <v>100.4073</v>
       </c>
     </row>
     <row r="516">
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.025558</v>
+        <v>65.02555099999999</v>
       </c>
       <c r="H516" t="n">
         <v>100.3921</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.485817</v>
+        <v>65.48582500000001</v>
       </c>
       <c r="H529" t="n">
         <v>101.1027</v>
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.30843400000001</v>
+        <v>66.308441</v>
       </c>
       <c r="H532" t="n">
-        <v>102.3727</v>
+        <v>102.3728</v>
       </c>
     </row>
     <row r="533">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.58264200000001</v>
+        <v>66.582634</v>
       </c>
       <c r="H536" t="n">
         <v>102.7961</v>
@@ -20972,10 +20972,10 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.66098</v>
+        <v>66.660988</v>
       </c>
       <c r="H541" t="n">
-        <v>102.917</v>
+        <v>102.9171</v>
       </c>
     </row>
     <row r="542">
@@ -21010,10 +21010,10 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.357399</v>
+        <v>66.35740699999999</v>
       </c>
       <c r="H542" t="n">
-        <v>102.4483</v>
+        <v>102.4484</v>
       </c>
     </row>
     <row r="543">
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.943871</v>
+        <v>67.94386299999999</v>
       </c>
       <c r="H546" t="n">
         <v>104.8977</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.396568</v>
+        <v>66.396576</v>
       </c>
       <c r="H552" t="n">
         <v>102.5088</v>
@@ -21431,7 +21431,7 @@
         <v>66.259468</v>
       </c>
       <c r="H553" t="n">
-        <v>102.2971</v>
+        <v>102.2972</v>
       </c>
     </row>
     <row r="554">
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.748009</v>
+        <v>67.748001</v>
       </c>
       <c r="H562" t="n">
         <v>104.5953</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.89490499999999</v>
+        <v>67.894897</v>
       </c>
       <c r="H563" t="n">
         <v>104.8221</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.659874</v>
+        <v>67.65986599999999</v>
       </c>
       <c r="H564" t="n">
         <v>104.4592</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.66965500000001</v>
+        <v>67.669662</v>
       </c>
       <c r="H565" t="n">
         <v>104.4743</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.601105</v>
+        <v>67.601112</v>
       </c>
       <c r="H566" t="n">
         <v>104.3685</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>67.61090900000001</v>
+        <v>67.610901</v>
       </c>
       <c r="H571" t="n">
         <v>104.3836</v>
@@ -22153,7 +22153,7 @@
         <v>67.99722300000001</v>
       </c>
       <c r="H572" t="n">
-        <v>104.98</v>
+        <v>104.9801</v>
       </c>
     </row>
     <row r="573">
@@ -22267,7 +22267,7 @@
         <v>68.35178399999999</v>
       </c>
       <c r="H575" t="n">
-        <v>105.5274</v>
+        <v>105.5275</v>
       </c>
     </row>
     <row r="576">
@@ -22343,7 +22343,7 @@
         <v>68.686646</v>
       </c>
       <c r="H577" t="n">
-        <v>106.0444</v>
+        <v>106.0445</v>
       </c>
     </row>
     <row r="578">
@@ -22609,7 +22609,7 @@
         <v>70.577652</v>
       </c>
       <c r="H584" t="n">
-        <v>108.9639</v>
+        <v>108.964</v>
       </c>
     </row>
     <row r="585">
@@ -22799,7 +22799,7 @@
         <v>71.119339</v>
       </c>
       <c r="H589" t="n">
-        <v>109.8002</v>
+        <v>109.8003</v>
       </c>
     </row>
     <row r="590">
@@ -22875,7 +22875,7 @@
         <v>70.76477800000001</v>
       </c>
       <c r="H591" t="n">
-        <v>109.2528</v>
+        <v>109.2529</v>
       </c>
     </row>
     <row r="592">
@@ -23141,7 +23141,7 @@
         <v>71.28677399999999</v>
       </c>
       <c r="H598" t="n">
-        <v>110.0587</v>
+        <v>110.0588</v>
       </c>
     </row>
     <row r="599">
@@ -23521,7 +23521,7 @@
         <v>74.241463</v>
       </c>
       <c r="H608" t="n">
-        <v>114.6204</v>
+        <v>114.6205</v>
       </c>
     </row>
     <row r="609">
@@ -23711,7 +23711,7 @@
         <v>75.10817</v>
       </c>
       <c r="H613" t="n">
-        <v>115.9585</v>
+        <v>115.9586</v>
       </c>
     </row>
     <row r="614">
@@ -23749,7 +23749,7 @@
         <v>74.940735</v>
       </c>
       <c r="H614" t="n">
-        <v>115.7</v>
+        <v>115.7001</v>
       </c>
     </row>
     <row r="615">
@@ -24281,7 +24281,7 @@
         <v>73.187622</v>
       </c>
       <c r="H628" t="n">
-        <v>112.9934</v>
+        <v>112.9935</v>
       </c>
     </row>
     <row r="629">
@@ -25383,7 +25383,7 @@
         <v>74.200523</v>
       </c>
       <c r="H657" t="n">
-        <v>114.5572</v>
+        <v>114.5573</v>
       </c>
     </row>
     <row r="658">
@@ -25497,7 +25497,7 @@
         <v>74.368797</v>
       </c>
       <c r="H660" t="n">
-        <v>114.817</v>
+        <v>114.8171</v>
       </c>
     </row>
     <row r="661">
@@ -25953,7 +25953,7 @@
         <v>76.170357</v>
       </c>
       <c r="H672" t="n">
-        <v>117.5984</v>
+        <v>117.5985</v>
       </c>
     </row>
     <row r="673">
@@ -26029,7 +26029,7 @@
         <v>76.96225699999999</v>
       </c>
       <c r="H674" t="n">
-        <v>118.821</v>
+        <v>118.8211</v>
       </c>
     </row>
     <row r="675">
@@ -26067,7 +26067,7 @@
         <v>77.526482</v>
       </c>
       <c r="H675" t="n">
-        <v>119.6921</v>
+        <v>119.6922</v>
       </c>
     </row>
     <row r="676">
@@ -26447,7 +26447,7 @@
         <v>77.02164500000001</v>
       </c>
       <c r="H685" t="n">
-        <v>118.9127</v>
+        <v>118.9128</v>
       </c>
     </row>
     <row r="686">
@@ -26485,7 +26485,7 @@
         <v>76.56630699999999</v>
       </c>
       <c r="H686" t="n">
-        <v>118.2097</v>
+        <v>118.2098</v>
       </c>
     </row>
     <row r="687">
@@ -26523,7 +26523,7 @@
         <v>76.853371</v>
       </c>
       <c r="H687" t="n">
-        <v>118.6529</v>
+        <v>118.653</v>
       </c>
     </row>
     <row r="688">
@@ -27017,7 +27017,7 @@
         <v>78.470001</v>
       </c>
       <c r="H700" t="n">
-        <v>121.1488</v>
+        <v>121.1489</v>
       </c>
     </row>
     <row r="701">
@@ -27549,7 +27549,7 @@
         <v>79.910004</v>
       </c>
       <c r="H714" t="n">
-        <v>123.372</v>
+        <v>123.3721</v>
       </c>
     </row>
     <row r="715">
@@ -27701,7 +27701,7 @@
         <v>80.400002</v>
       </c>
       <c r="H718" t="n">
-        <v>124.1285</v>
+        <v>124.1286</v>
       </c>
     </row>
     <row r="719">
@@ -28385,7 +28385,7 @@
         <v>81.300003</v>
       </c>
       <c r="H736" t="n">
-        <v>125.518</v>
+        <v>125.5181</v>
       </c>
     </row>
     <row r="737">
@@ -28423,7 +28423,7 @@
         <v>81.199997</v>
       </c>
       <c r="H737" t="n">
-        <v>125.3636</v>
+        <v>125.3637</v>
       </c>
     </row>
     <row r="738">
@@ -28575,7 +28575,7 @@
         <v>81.480003</v>
       </c>
       <c r="H741" t="n">
-        <v>125.7959</v>
+        <v>125.796</v>
       </c>
     </row>
     <row r="742">
@@ -28613,7 +28613,7 @@
         <v>81.660004</v>
       </c>
       <c r="H742" t="n">
-        <v>126.0738</v>
+        <v>126.0739</v>
       </c>
     </row>
     <row r="743">
@@ -28651,7 +28651,7 @@
         <v>81.25</v>
       </c>
       <c r="H743" t="n">
-        <v>125.4408</v>
+        <v>125.4409</v>
       </c>
     </row>
     <row r="744">
@@ -28765,7 +28765,7 @@
         <v>81.55999799999999</v>
       </c>
       <c r="H746" t="n">
-        <v>125.9194</v>
+        <v>125.9195</v>
       </c>
     </row>
     <row r="747">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.040001</v>
+        <v>80.900002</v>
       </c>
       <c r="H755" t="n">
-        <v>125.1166</v>
+        <v>124.9005</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>126.18</v>
+        <v>125.739998</v>
       </c>
       <c r="H1006" t="n">
-        <v>118.3344</v>
+        <v>117.9218</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>126.18</v>
+        <v>125.739998</v>
       </c>
       <c r="H1257" t="n">
-        <v>118.3344</v>
+        <v>117.9218</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>126.18</v>
+        <v>125.739998</v>
       </c>
       <c r="H1508" t="n">
-        <v>118.3344</v>
+        <v>117.9218</v>
       </c>
     </row>
     <row r="1509">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.830002</v>
+        <v>62.720001</v>
       </c>
       <c r="H1760" t="n">
-        <v>115.7415</v>
+        <v>115.5389</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.73</v>
+        <v>35.099998</v>
       </c>
       <c r="H253" t="n">
-        <v>115.1144</v>
+        <v>116.3407</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>46.665001</v>
+        <v>46.705002</v>
       </c>
       <c r="H504" t="n">
-        <v>128.0774</v>
+        <v>128.1872</v>
       </c>
     </row>
     <row r="505">
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.22653200000001</v>
+        <v>64.226524</v>
       </c>
       <c r="H506" t="n">
         <v>99.1585</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.48931899999999</v>
+        <v>64.489311</v>
       </c>
       <c r="H507" t="n">
-        <v>99.5643</v>
+        <v>99.5642</v>
       </c>
     </row>
     <row r="508">
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.770927</v>
+        <v>64.77093499999999</v>
       </c>
       <c r="H509" t="n">
         <v>99.999</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.103905</v>
+        <v>65.103897</v>
       </c>
       <c r="H514" t="n">
         <v>100.5131</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.035355</v>
+        <v>65.035347</v>
       </c>
       <c r="H515" t="n">
         <v>100.4073</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.525002</v>
+        <v>65.52499400000001</v>
       </c>
       <c r="H518" t="n">
         <v>101.1632</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.38678</v>
+        <v>66.386787</v>
       </c>
       <c r="H522" t="n">
         <v>102.4937</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.56416299999999</v>
+        <v>65.564171</v>
       </c>
       <c r="H525" t="n">
         <v>101.2237</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.48582500000001</v>
+        <v>65.485817</v>
       </c>
       <c r="H529" t="n">
         <v>101.1027</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.38678</v>
+        <v>66.386787</v>
       </c>
       <c r="H531" t="n">
         <v>102.4937</v>
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.308441</v>
+        <v>66.308426</v>
       </c>
       <c r="H532" t="n">
-        <v>102.3728</v>
+        <v>102.3727</v>
       </c>
     </row>
     <row r="533">
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.709946</v>
+        <v>66.709953</v>
       </c>
       <c r="H535" t="n">
-        <v>102.9926</v>
+        <v>102.9927</v>
       </c>
     </row>
     <row r="536">
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.660988</v>
+        <v>66.66098</v>
       </c>
       <c r="H541" t="n">
         <v>102.9171</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.35740699999999</v>
+        <v>66.357399</v>
       </c>
       <c r="H542" t="n">
         <v>102.4484</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.94386299999999</v>
+        <v>67.943871</v>
       </c>
       <c r="H546" t="n">
         <v>104.8977</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.396576</v>
+        <v>66.396568</v>
       </c>
       <c r="H552" t="n">
         <v>102.5088</v>
@@ -21504,10 +21504,10 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.758911</v>
+        <v>66.75891900000001</v>
       </c>
       <c r="H555" t="n">
-        <v>103.0682</v>
+        <v>103.0683</v>
       </c>
     </row>
     <row r="556">
@@ -21618,10 +21618,10 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.62069700000001</v>
+        <v>67.620705</v>
       </c>
       <c r="H558" t="n">
-        <v>104.3987</v>
+        <v>104.3988</v>
       </c>
     </row>
     <row r="559">
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.748001</v>
+        <v>67.748009</v>
       </c>
       <c r="H562" t="n">
         <v>104.5953</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.894897</v>
+        <v>67.89490499999999</v>
       </c>
       <c r="H563" t="n">
         <v>104.8221</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.601112</v>
+        <v>67.601105</v>
       </c>
       <c r="H566" t="n">
         <v>104.3685</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.855728</v>
+        <v>67.85573599999999</v>
       </c>
       <c r="H567" t="n">
         <v>104.7616</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.76758599999999</v>
+        <v>67.76759300000001</v>
       </c>
       <c r="H568" t="n">
         <v>104.6255</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.54235799999999</v>
+        <v>67.542351</v>
       </c>
       <c r="H570" t="n">
         <v>104.2778</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>67.610901</v>
+        <v>67.61090900000001</v>
       </c>
       <c r="H571" t="n">
         <v>104.3836</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.900002</v>
+        <v>80.910004</v>
       </c>
       <c r="H755" t="n">
-        <v>124.9005</v>
+        <v>124.9159</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>125.739998</v>
+        <v>125.800003</v>
       </c>
       <c r="H1006" t="n">
-        <v>117.9218</v>
+        <v>117.9781</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>125.739998</v>
+        <v>125.800003</v>
       </c>
       <c r="H1257" t="n">
-        <v>117.9218</v>
+        <v>117.9781</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>125.739998</v>
+        <v>125.800003</v>
       </c>
       <c r="H1508" t="n">
-        <v>117.9218</v>
+        <v>117.9781</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>54.284748</v>
+        <v>54.284752</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.068439</v>
+        <v>54.068436</v>
       </c>
       <c r="H1512" t="n">
         <v>99.6015</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>53.576817</v>
+        <v>53.57682</v>
       </c>
       <c r="H1517" t="n">
         <v>98.69589999999999</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.12743</v>
+        <v>54.127434</v>
       </c>
       <c r="H1519" t="n">
         <v>99.7102</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.317154</v>
+        <v>55.31715</v>
       </c>
       <c r="H1522" t="n">
         <v>101.9018</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.582626</v>
+        <v>55.58263</v>
       </c>
       <c r="H1523" t="n">
         <v>102.3909</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.562965</v>
+        <v>55.562962</v>
       </c>
       <c r="H1524" t="n">
-        <v>102.3547</v>
+        <v>102.3546</v>
       </c>
     </row>
     <row r="1525">
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.680958</v>
+        <v>55.680954</v>
       </c>
       <c r="H1527" t="n">
         <v>102.572</v>
@@ -58481,7 +58481,7 @@
         <v>54.943523</v>
       </c>
       <c r="H1528" t="n">
-        <v>101.2136</v>
+        <v>101.2135</v>
       </c>
     </row>
     <row r="1529">
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.051682</v>
+        <v>55.051678</v>
       </c>
       <c r="H1530" t="n">
         <v>101.4128</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.199165</v>
+        <v>55.199162</v>
       </c>
       <c r="H1533" t="n">
         <v>101.6845</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.798943</v>
+        <v>55.798946</v>
       </c>
       <c r="H1536" t="n">
         <v>102.7894</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>56.113579</v>
+        <v>56.113583</v>
       </c>
       <c r="H1540" t="n">
         <v>103.369</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.690784</v>
+        <v>55.690788</v>
       </c>
       <c r="H1544" t="n">
         <v>102.5901</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.798943</v>
+        <v>55.798946</v>
       </c>
       <c r="H1545" t="n">
         <v>102.7894</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.385983</v>
+        <v>55.385986</v>
       </c>
       <c r="H1546" t="n">
         <v>102.0286</v>
@@ -59203,7 +59203,7 @@
         <v>55.100842</v>
       </c>
       <c r="H1547" t="n">
-        <v>101.5034</v>
+        <v>101.5033</v>
       </c>
     </row>
     <row r="1548">
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.907104</v>
+        <v>55.907101</v>
       </c>
       <c r="H1548" t="n">
         <v>102.9886</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>56.634693</v>
+        <v>56.634697</v>
       </c>
       <c r="H1549" t="n">
         <v>104.3289</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>57.057487</v>
+        <v>57.057491</v>
       </c>
       <c r="H1550" t="n">
         <v>105.1078</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.85503</v>
+        <v>54.855034</v>
       </c>
       <c r="H1554" t="n">
         <v>101.0505</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.002518</v>
+        <v>55.002514</v>
       </c>
       <c r="H1556" t="n">
         <v>101.3222</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.864861</v>
+        <v>54.864864</v>
       </c>
       <c r="H1557" t="n">
         <v>101.0686</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>54.933693</v>
+        <v>54.933689</v>
       </c>
       <c r="H1558" t="n">
         <v>101.1954</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.395817</v>
+        <v>55.395813</v>
       </c>
       <c r="H1559" t="n">
         <v>102.0467</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1561" t="n">
         <v>103.3327</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.093914</v>
+        <v>56.09391</v>
       </c>
       <c r="H1563" t="n">
         <v>103.3327</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.428215</v>
+        <v>56.428219</v>
       </c>
       <c r="H1568" t="n">
         <v>103.9486</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.369221</v>
+        <v>56.369225</v>
       </c>
       <c r="H1569" t="n">
         <v>103.8399</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.826939</v>
+        <v>56.826942</v>
       </c>
       <c r="H1573" t="n">
         <v>104.6831</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.521103</v>
+        <v>56.521107</v>
       </c>
       <c r="H1575" t="n">
         <v>104.1197</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>57.320232</v>
+        <v>57.320229</v>
       </c>
       <c r="H1577" t="n">
         <v>105.5918</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>57.211712</v>
+        <v>57.211708</v>
       </c>
       <c r="H1578" t="n">
         <v>105.3919</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.760639</v>
+        <v>58.760635</v>
       </c>
       <c r="H1583" t="n">
         <v>108.2452</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.589367</v>
+        <v>59.589363</v>
       </c>
       <c r="H1587" t="n">
         <v>109.7718</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.688019</v>
+        <v>59.688023</v>
       </c>
       <c r="H1588" t="n">
         <v>109.9536</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.707756</v>
+        <v>59.707752</v>
       </c>
       <c r="H1590" t="n">
         <v>109.9899</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>58.829697</v>
+        <v>58.8297</v>
       </c>
       <c r="H1594" t="n">
         <v>108.3724</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.865604</v>
+        <v>59.865608</v>
       </c>
       <c r="H1599" t="n">
         <v>110.2807</v>
@@ -61217,7 +61217,7 @@
         <v>59.392048</v>
       </c>
       <c r="H1600" t="n">
-        <v>109.4084</v>
+        <v>109.4083</v>
       </c>
     </row>
     <row r="1601">
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.723927</v>
+        <v>60.72393</v>
       </c>
       <c r="H1608" t="n">
         <v>111.8619</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.684467</v>
+        <v>60.684464</v>
       </c>
       <c r="H1609" t="n">
         <v>111.7892</v>
@@ -61635,7 +61635,7 @@
         <v>60.497017</v>
       </c>
       <c r="H1611" t="n">
-        <v>111.4439</v>
+        <v>111.4438</v>
       </c>
     </row>
     <row r="1612">
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>61.779564</v>
+        <v>61.779568</v>
       </c>
       <c r="H1617" t="n">
         <v>113.8065</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>61.592117</v>
+        <v>61.592121</v>
       </c>
       <c r="H1619" t="n">
         <v>113.4612</v>
@@ -62015,7 +62015,7 @@
         <v>61.986752</v>
       </c>
       <c r="H1621" t="n">
-        <v>114.1882</v>
+        <v>114.1881</v>
       </c>
     </row>
     <row r="1622">
@@ -62053,7 +62053,7 @@
         <v>62.026215</v>
       </c>
       <c r="H1622" t="n">
-        <v>114.2609</v>
+        <v>114.2608</v>
       </c>
     </row>
     <row r="1623">
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>59.194733</v>
+        <v>59.194729</v>
       </c>
       <c r="H1624" t="n">
         <v>109.0449</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>59.954399</v>
+        <v>59.954395</v>
       </c>
       <c r="H1625" t="n">
         <v>110.4443</v>
@@ -62354,7 +62354,7 @@
         </is>
       </c>
       <c r="G1630" t="n">
-        <v>59.007282</v>
+        <v>59.007286</v>
       </c>
       <c r="H1630" t="n">
         <v>108.6996</v>
@@ -62392,7 +62392,7 @@
         </is>
       </c>
       <c r="G1631" t="n">
-        <v>58.661976</v>
+        <v>58.66198</v>
       </c>
       <c r="H1631" t="n">
         <v>108.0635</v>
@@ -62430,7 +62430,7 @@
         </is>
       </c>
       <c r="G1632" t="n">
-        <v>58.336411</v>
+        <v>58.336407</v>
       </c>
       <c r="H1632" t="n">
         <v>107.4637</v>
@@ -62585,7 +62585,7 @@
         <v>57.083481</v>
       </c>
       <c r="H1636" t="n">
-        <v>105.1557</v>
+        <v>105.1556</v>
       </c>
     </row>
     <row r="1637">
@@ -63915,7 +63915,7 @@
         <v>60.070175</v>
       </c>
       <c r="H1671" t="n">
-        <v>110.6576</v>
+        <v>110.6575</v>
       </c>
     </row>
     <row r="1672">
@@ -64637,7 +64637,7 @@
         <v>61.860214</v>
       </c>
       <c r="H1690" t="n">
-        <v>113.9551</v>
+        <v>113.955</v>
       </c>
     </row>
     <row r="1691">
@@ -64675,7 +64675,7 @@
         <v>61.533855</v>
       </c>
       <c r="H1691" t="n">
-        <v>113.3539</v>
+        <v>113.3538</v>
       </c>
     </row>
     <row r="1692">
@@ -65321,7 +65321,7 @@
         <v>64.660004</v>
       </c>
       <c r="H1708" t="n">
-        <v>119.1127</v>
+        <v>119.1126</v>
       </c>
     </row>
     <row r="1709">
@@ -65701,7 +65701,7 @@
         <v>64.199997</v>
       </c>
       <c r="H1718" t="n">
-        <v>118.2653</v>
+        <v>118.2652</v>
       </c>
     </row>
     <row r="1719">
@@ -66233,7 +66233,7 @@
         <v>65.550003</v>
       </c>
       <c r="H1732" t="n">
-        <v>120.7522</v>
+        <v>120.7521</v>
       </c>
     </row>
     <row r="1733">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.720001</v>
+        <v>62.740002</v>
       </c>
       <c r="H1760" t="n">
-        <v>115.5389</v>
+        <v>115.5757</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.77156100000001</v>
+        <v>64.771568</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.226524</v>
+        <v>64.226517</v>
       </c>
       <c r="H506" t="n">
         <v>99.1585</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.489311</v>
+        <v>64.489304</v>
       </c>
       <c r="H507" t="n">
         <v>99.5642</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.702377</v>
+        <v>64.70238500000001</v>
       </c>
       <c r="H510" t="n">
         <v>99.89319999999999</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>64.810104</v>
+        <v>64.810097</v>
       </c>
       <c r="H513" t="n">
         <v>100.0595</v>
@@ -19987,7 +19987,7 @@
         <v>65.035347</v>
       </c>
       <c r="H515" t="n">
-        <v>100.4073</v>
+        <v>100.4072</v>
       </c>
     </row>
     <row r="516">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.386787</v>
+        <v>66.38678</v>
       </c>
       <c r="H522" t="n">
         <v>102.4937</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.23120900000001</v>
+        <v>65.231201</v>
       </c>
       <c r="H524" t="n">
         <v>100.7096</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.564171</v>
+        <v>65.56416299999999</v>
       </c>
       <c r="H525" t="n">
         <v>101.2237</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.485817</v>
+        <v>65.48582500000001</v>
       </c>
       <c r="H529" t="n">
         <v>101.1027</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.386787</v>
+        <v>66.38678</v>
       </c>
       <c r="H531" t="n">
         <v>102.4937</v>
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.308426</v>
+        <v>66.308441</v>
       </c>
       <c r="H532" t="n">
-        <v>102.3727</v>
+        <v>102.3728</v>
       </c>
     </row>
     <row r="533">
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H534" t="n">
         <v>103.0985</v>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.709953</v>
+        <v>66.709946</v>
       </c>
       <c r="H535" t="n">
-        <v>102.9927</v>
+        <v>102.9926</v>
       </c>
     </row>
     <row r="536">
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H537" t="n">
         <v>103.0985</v>
@@ -20975,7 +20975,7 @@
         <v>66.66098</v>
       </c>
       <c r="H541" t="n">
-        <v>102.9171</v>
+        <v>102.917</v>
       </c>
     </row>
     <row r="542">
@@ -21013,7 +21013,7 @@
         <v>66.357399</v>
       </c>
       <c r="H542" t="n">
-        <v>102.4484</v>
+        <v>102.4483</v>
       </c>
     </row>
     <row r="543">
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.739334</v>
+        <v>66.73932600000001</v>
       </c>
       <c r="H544" t="n">
         <v>103.038</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.788292</v>
+        <v>66.788284</v>
       </c>
       <c r="H549" t="n">
         <v>103.1136</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.12236</v>
+        <v>66.12236799999999</v>
       </c>
       <c r="H550" t="n">
         <v>102.0855</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.259468</v>
+        <v>66.25947600000001</v>
       </c>
       <c r="H553" t="n">
         <v>102.2972</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.494499</v>
+        <v>66.494507</v>
       </c>
       <c r="H554" t="n">
         <v>102.66</v>
@@ -21507,7 +21507,7 @@
         <v>66.75891900000001</v>
       </c>
       <c r="H555" t="n">
-        <v>103.0683</v>
+        <v>103.0682</v>
       </c>
     </row>
     <row r="556">
@@ -21542,10 +21542,10 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.375877</v>
+        <v>67.37587000000001</v>
       </c>
       <c r="H556" t="n">
-        <v>104.0208</v>
+        <v>104.0207</v>
       </c>
     </row>
     <row r="557">
@@ -21618,10 +21618,10 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.620705</v>
+        <v>67.62069700000001</v>
       </c>
       <c r="H558" t="n">
-        <v>104.3988</v>
+        <v>104.3987</v>
       </c>
     </row>
     <row r="559">
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.248558</v>
+        <v>67.248566</v>
       </c>
       <c r="H560" t="n">
         <v>103.8242</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.65986599999999</v>
+        <v>67.659859</v>
       </c>
       <c r="H564" t="n">
         <v>104.4592</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.601105</v>
+        <v>67.601112</v>
       </c>
       <c r="H566" t="n">
         <v>104.3685</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.85573599999999</v>
+        <v>67.855728</v>
       </c>
       <c r="H567" t="n">
         <v>104.7616</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.76759300000001</v>
+        <v>67.76758599999999</v>
       </c>
       <c r="H568" t="n">
         <v>104.6255</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>68.14952099999999</v>
+        <v>68.149513</v>
       </c>
       <c r="H569" t="n">
         <v>105.2152</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>67.61090900000001</v>
+        <v>67.610901</v>
       </c>
       <c r="H571" t="n">
         <v>104.3836</v>
@@ -22150,10 +22150,10 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>67.99722300000001</v>
+        <v>67.997215</v>
       </c>
       <c r="H572" t="n">
-        <v>104.9801</v>
+        <v>104.98</v>
       </c>
     </row>
     <row r="573">
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>68.272987</v>
+        <v>68.27299499999999</v>
       </c>
       <c r="H573" t="n">
         <v>105.4058</v>
@@ -22267,7 +22267,7 @@
         <v>68.35178399999999</v>
       </c>
       <c r="H575" t="n">
-        <v>105.5275</v>
+        <v>105.5274</v>
       </c>
     </row>
     <row r="576">
@@ -22343,7 +22343,7 @@
         <v>68.686646</v>
       </c>
       <c r="H577" t="n">
-        <v>106.0445</v>
+        <v>106.0444</v>
       </c>
     </row>
     <row r="578">
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>68.90331999999999</v>
+        <v>68.903328</v>
       </c>
       <c r="H578" t="n">
         <v>106.379</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>69.632149</v>
+        <v>69.632141</v>
       </c>
       <c r="H579" t="n">
         <v>107.5042</v>
@@ -22609,7 +22609,7 @@
         <v>70.577652</v>
       </c>
       <c r="H584" t="n">
-        <v>108.964</v>
+        <v>108.9639</v>
       </c>
     </row>
     <row r="585">
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.66628300000001</v>
+        <v>70.66629</v>
       </c>
       <c r="H585" t="n">
         <v>109.1008</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>71.69058200000001</v>
+        <v>71.690575</v>
       </c>
       <c r="H588" t="n">
         <v>110.6822</v>
@@ -22799,7 +22799,7 @@
         <v>71.119339</v>
       </c>
       <c r="H589" t="n">
-        <v>109.8003</v>
+        <v>109.8002</v>
       </c>
     </row>
     <row r="590">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.45946499999999</v>
+        <v>70.459457</v>
       </c>
       <c r="H590" t="n">
         <v>108.7815</v>
@@ -22875,7 +22875,7 @@
         <v>70.76477800000001</v>
       </c>
       <c r="H591" t="n">
-        <v>109.2529</v>
+        <v>109.2528</v>
       </c>
     </row>
     <row r="592">
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>70.804169</v>
+        <v>70.804176</v>
       </c>
       <c r="H595" t="n">
         <v>109.3137</v>
@@ -23141,7 +23141,7 @@
         <v>71.28677399999999</v>
       </c>
       <c r="H598" t="n">
-        <v>110.0588</v>
+        <v>110.0587</v>
       </c>
     </row>
     <row r="599">
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>72.084534</v>
+        <v>72.084541</v>
       </c>
       <c r="H599" t="n">
         <v>111.2904</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>73.28610999999999</v>
+        <v>73.286118</v>
       </c>
       <c r="H601" t="n">
         <v>113.1455</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>72.754272</v>
+        <v>72.754265</v>
       </c>
       <c r="H602" t="n">
         <v>112.3244</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>73.71946</v>
+        <v>73.71946699999999</v>
       </c>
       <c r="H604" t="n">
         <v>113.8145</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.53692599999999</v>
+        <v>74.536934</v>
       </c>
       <c r="H606" t="n">
         <v>115.0766</v>
@@ -23518,10 +23518,10 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.241463</v>
+        <v>74.241455</v>
       </c>
       <c r="H608" t="n">
-        <v>114.6205</v>
+        <v>114.6204</v>
       </c>
     </row>
     <row r="609">
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.30056</v>
+        <v>74.300552</v>
       </c>
       <c r="H609" t="n">
         <v>114.7117</v>
@@ -23711,7 +23711,7 @@
         <v>75.10817</v>
       </c>
       <c r="H613" t="n">
-        <v>115.9586</v>
+        <v>115.9585</v>
       </c>
     </row>
     <row r="614">
@@ -23749,7 +23749,7 @@
         <v>74.940735</v>
       </c>
       <c r="H614" t="n">
-        <v>115.7001</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="615">
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>75.69910400000001</v>
+        <v>75.699112</v>
       </c>
       <c r="H617" t="n">
         <v>116.8709</v>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>73.768715</v>
+        <v>73.76870700000001</v>
       </c>
       <c r="H620" t="n">
         <v>113.8906</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>73.128525</v>
+        <v>73.12853200000001</v>
       </c>
       <c r="H625" t="n">
         <v>112.9022</v>
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>72.84290300000001</v>
+        <v>72.842911</v>
       </c>
       <c r="H626" t="n">
         <v>112.4612</v>
@@ -24281,7 +24281,7 @@
         <v>73.187622</v>
       </c>
       <c r="H628" t="n">
-        <v>112.9935</v>
+        <v>112.9934</v>
       </c>
     </row>
     <row r="629">
@@ -25383,7 +25383,7 @@
         <v>74.200523</v>
       </c>
       <c r="H657" t="n">
-        <v>114.5573</v>
+        <v>114.5572</v>
       </c>
     </row>
     <row r="658">
@@ -25497,7 +25497,7 @@
         <v>74.368797</v>
       </c>
       <c r="H660" t="n">
-        <v>114.8171</v>
+        <v>114.817</v>
       </c>
     </row>
     <row r="661">
@@ -25953,7 +25953,7 @@
         <v>76.170357</v>
       </c>
       <c r="H672" t="n">
-        <v>117.5985</v>
+        <v>117.5984</v>
       </c>
     </row>
     <row r="673">
@@ -26029,7 +26029,7 @@
         <v>76.96225699999999</v>
       </c>
       <c r="H674" t="n">
-        <v>118.8211</v>
+        <v>118.821</v>
       </c>
     </row>
     <row r="675">
@@ -26067,7 +26067,7 @@
         <v>77.526482</v>
       </c>
       <c r="H675" t="n">
-        <v>119.6922</v>
+        <v>119.6921</v>
       </c>
     </row>
     <row r="676">
@@ -26447,7 +26447,7 @@
         <v>77.02164500000001</v>
       </c>
       <c r="H685" t="n">
-        <v>118.9128</v>
+        <v>118.9127</v>
       </c>
     </row>
     <row r="686">
@@ -26485,7 +26485,7 @@
         <v>76.56630699999999</v>
       </c>
       <c r="H686" t="n">
-        <v>118.2098</v>
+        <v>118.2097</v>
       </c>
     </row>
     <row r="687">
@@ -26523,7 +26523,7 @@
         <v>76.853371</v>
       </c>
       <c r="H687" t="n">
-        <v>118.653</v>
+        <v>118.6529</v>
       </c>
     </row>
     <row r="688">
@@ -27017,7 +27017,7 @@
         <v>78.470001</v>
       </c>
       <c r="H700" t="n">
-        <v>121.1489</v>
+        <v>121.1488</v>
       </c>
     </row>
     <row r="701">
@@ -27549,7 +27549,7 @@
         <v>79.910004</v>
       </c>
       <c r="H714" t="n">
-        <v>123.3721</v>
+        <v>123.372</v>
       </c>
     </row>
     <row r="715">
@@ -27701,7 +27701,7 @@
         <v>80.400002</v>
       </c>
       <c r="H718" t="n">
-        <v>124.1286</v>
+        <v>124.1285</v>
       </c>
     </row>
     <row r="719">
@@ -28385,7 +28385,7 @@
         <v>81.300003</v>
       </c>
       <c r="H736" t="n">
-        <v>125.5181</v>
+        <v>125.518</v>
       </c>
     </row>
     <row r="737">
@@ -28423,7 +28423,7 @@
         <v>81.199997</v>
       </c>
       <c r="H737" t="n">
-        <v>125.3637</v>
+        <v>125.3636</v>
       </c>
     </row>
     <row r="738">
@@ -28575,7 +28575,7 @@
         <v>81.480003</v>
       </c>
       <c r="H741" t="n">
-        <v>125.796</v>
+        <v>125.7959</v>
       </c>
     </row>
     <row r="742">
@@ -28613,7 +28613,7 @@
         <v>81.660004</v>
       </c>
       <c r="H742" t="n">
-        <v>126.0739</v>
+        <v>126.0738</v>
       </c>
     </row>
     <row r="743">
@@ -28651,7 +28651,7 @@
         <v>81.25</v>
       </c>
       <c r="H743" t="n">
-        <v>125.4409</v>
+        <v>125.4408</v>
       </c>
     </row>
     <row r="744">
@@ -28765,7 +28765,7 @@
         <v>81.55999799999999</v>
       </c>
       <c r="H746" t="n">
-        <v>125.9195</v>
+        <v>125.9194</v>
       </c>
     </row>
     <row r="747">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.645645</v>
+        <v>53.645649</v>
       </c>
       <c r="H1511" t="n">
         <v>98.8227</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.068436</v>
+        <v>54.068439</v>
       </c>
       <c r="H1512" t="n">
         <v>99.6015</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.127434</v>
+        <v>54.12743</v>
       </c>
       <c r="H1519" t="n">
         <v>99.7102</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.31715</v>
+        <v>55.317154</v>
       </c>
       <c r="H1522" t="n">
         <v>101.9018</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.562962</v>
+        <v>55.562965</v>
       </c>
       <c r="H1524" t="n">
         <v>102.3546</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.051678</v>
+        <v>55.051685</v>
       </c>
       <c r="H1530" t="n">
         <v>101.4128</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1532" t="n">
         <v>102.7531</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.199162</v>
+        <v>55.199165</v>
       </c>
       <c r="H1533" t="n">
         <v>101.6845</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.779274</v>
+        <v>55.779278</v>
       </c>
       <c r="H1534" t="n">
         <v>102.7531</v>
@@ -58782,10 +58782,10 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.798946</v>
+        <v>55.798939</v>
       </c>
       <c r="H1536" t="n">
-        <v>102.7894</v>
+        <v>102.7893</v>
       </c>
     </row>
     <row r="1537">
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>56.113583</v>
+        <v>56.113579</v>
       </c>
       <c r="H1540" t="n">
         <v>103.369</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.818607</v>
+        <v>55.818611</v>
       </c>
       <c r="H1542" t="n">
         <v>102.8256</v>
@@ -59124,10 +59124,10 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.798946</v>
+        <v>55.798939</v>
       </c>
       <c r="H1545" t="n">
-        <v>102.7894</v>
+        <v>102.7893</v>
       </c>
     </row>
     <row r="1546">
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>56.634697</v>
+        <v>56.634693</v>
       </c>
       <c r="H1549" t="n">
         <v>104.3289</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>56.133244</v>
+        <v>56.133247</v>
       </c>
       <c r="H1552" t="n">
         <v>103.4052</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>54.933689</v>
+        <v>54.933693</v>
       </c>
       <c r="H1558" t="n">
         <v>101.1954</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.395813</v>
+        <v>55.395817</v>
       </c>
       <c r="H1559" t="n">
         <v>102.0467</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.09391</v>
+        <v>56.093914</v>
       </c>
       <c r="H1561" t="n">
         <v>103.3327</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.09391</v>
+        <v>56.093914</v>
       </c>
       <c r="H1563" t="n">
         <v>103.3327</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.516708</v>
+        <v>56.516705</v>
       </c>
       <c r="H1567" t="n">
         <v>104.1116</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.428219</v>
+        <v>56.428215</v>
       </c>
       <c r="H1568" t="n">
         <v>103.9486</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.369225</v>
+        <v>56.369221</v>
       </c>
       <c r="H1569" t="n">
         <v>103.8399</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.703526</v>
+        <v>56.703522</v>
       </c>
       <c r="H1571" t="n">
         <v>104.4557</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.826942</v>
+        <v>56.826939</v>
       </c>
       <c r="H1573" t="n">
         <v>104.6831</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.521107</v>
+        <v>56.521103</v>
       </c>
       <c r="H1575" t="n">
         <v>104.1197</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>57.320229</v>
+        <v>57.320232</v>
       </c>
       <c r="H1577" t="n">
         <v>105.5918</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>57.211708</v>
+        <v>57.211712</v>
       </c>
       <c r="H1578" t="n">
         <v>105.3919</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.760635</v>
+        <v>58.760639</v>
       </c>
       <c r="H1583" t="n">
         <v>108.2452</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.589363</v>
+        <v>59.589367</v>
       </c>
       <c r="H1587" t="n">
         <v>109.7718</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.688023</v>
+        <v>59.688019</v>
       </c>
       <c r="H1588" t="n">
         <v>109.9536</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.707752</v>
+        <v>59.707756</v>
       </c>
       <c r="H1590" t="n">
         <v>109.9899</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>58.8297</v>
+        <v>58.829697</v>
       </c>
       <c r="H1594" t="n">
         <v>108.3724</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.865608</v>
+        <v>59.865604</v>
       </c>
       <c r="H1599" t="n">
         <v>110.2807</v>
@@ -61518,10 +61518,10 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.72393</v>
+        <v>60.723927</v>
       </c>
       <c r="H1608" t="n">
-        <v>111.8619</v>
+        <v>111.8618</v>
       </c>
     </row>
     <row r="1609">
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.684464</v>
+        <v>60.684467</v>
       </c>
       <c r="H1609" t="n">
         <v>111.7892</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>61.779568</v>
+        <v>61.779564</v>
       </c>
       <c r="H1617" t="n">
         <v>113.8065</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>61.592121</v>
+        <v>61.592117</v>
       </c>
       <c r="H1619" t="n">
         <v>113.4612</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>59.194729</v>
+        <v>59.194733</v>
       </c>
       <c r="H1624" t="n">
         <v>109.0449</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>59.954395</v>
+        <v>59.954399</v>
       </c>
       <c r="H1625" t="n">
         <v>110.4443</v>
@@ -62354,7 +62354,7 @@
         </is>
       </c>
       <c r="G1630" t="n">
-        <v>59.007286</v>
+        <v>59.007282</v>
       </c>
       <c r="H1630" t="n">
         <v>108.6996</v>
@@ -62392,7 +62392,7 @@
         </is>
       </c>
       <c r="G1631" t="n">
-        <v>58.66198</v>
+        <v>58.661976</v>
       </c>
       <c r="H1631" t="n">
         <v>108.0635</v>
@@ -62430,7 +62430,7 @@
         </is>
       </c>
       <c r="G1632" t="n">
-        <v>58.336407</v>
+        <v>58.336411</v>
       </c>
       <c r="H1632" t="n">
         <v>107.4637</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.099998</v>
+        <v>34.799999</v>
       </c>
       <c r="H253" t="n">
-        <v>116.3407</v>
+        <v>115.3464</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>46.705002</v>
+        <v>47.025002</v>
       </c>
       <c r="H504" t="n">
-        <v>128.1872</v>
+        <v>129.0655</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.771568</v>
+        <v>64.77156100000001</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.226517</v>
+        <v>64.226524</v>
       </c>
       <c r="H506" t="n">
         <v>99.1585</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.489304</v>
+        <v>64.48931899999999</v>
       </c>
       <c r="H507" t="n">
-        <v>99.5642</v>
+        <v>99.5643</v>
       </c>
     </row>
     <row r="508">
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.77093499999999</v>
+        <v>64.770927</v>
       </c>
       <c r="H509" t="n">
         <v>99.999</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.70238500000001</v>
+        <v>64.702377</v>
       </c>
       <c r="H510" t="n">
         <v>99.89319999999999</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>64.810097</v>
+        <v>64.810104</v>
       </c>
       <c r="H513" t="n">
         <v>100.0595</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.103897</v>
+        <v>65.103905</v>
       </c>
       <c r="H514" t="n">
         <v>100.5131</v>
@@ -19984,10 +19984,10 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.035347</v>
+        <v>65.035355</v>
       </c>
       <c r="H515" t="n">
-        <v>100.4072</v>
+        <v>100.4073</v>
       </c>
     </row>
     <row r="516">
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H518" t="n">
         <v>101.1632</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.231201</v>
+        <v>65.23120900000001</v>
       </c>
       <c r="H524" t="n">
         <v>100.7096</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H534" t="n">
         <v>103.0985</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H537" t="n">
         <v>103.0985</v>
@@ -20972,10 +20972,10 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.66098</v>
+        <v>66.660988</v>
       </c>
       <c r="H541" t="n">
-        <v>102.917</v>
+        <v>102.9171</v>
       </c>
     </row>
     <row r="542">
@@ -21010,10 +21010,10 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.357399</v>
+        <v>66.35740699999999</v>
       </c>
       <c r="H542" t="n">
-        <v>102.4483</v>
+        <v>102.4484</v>
       </c>
     </row>
     <row r="543">
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.73932600000001</v>
+        <v>66.739334</v>
       </c>
       <c r="H544" t="n">
         <v>103.038</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.943871</v>
+        <v>67.94386299999999</v>
       </c>
       <c r="H546" t="n">
         <v>104.8977</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.788284</v>
+        <v>66.788292</v>
       </c>
       <c r="H549" t="n">
         <v>103.1136</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.12236799999999</v>
+        <v>66.12236</v>
       </c>
       <c r="H550" t="n">
         <v>102.0855</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.396568</v>
+        <v>66.396576</v>
       </c>
       <c r="H552" t="n">
         <v>102.5088</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.25947600000001</v>
+        <v>66.259468</v>
       </c>
       <c r="H553" t="n">
         <v>102.2972</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.494507</v>
+        <v>66.494499</v>
       </c>
       <c r="H554" t="n">
         <v>102.66</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.75891900000001</v>
+        <v>66.758911</v>
       </c>
       <c r="H555" t="n">
         <v>103.0682</v>
@@ -21542,10 +21542,10 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.37587000000001</v>
+        <v>67.375877</v>
       </c>
       <c r="H556" t="n">
-        <v>104.0207</v>
+        <v>104.0208</v>
       </c>
     </row>
     <row r="557">
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.248566</v>
+        <v>67.248558</v>
       </c>
       <c r="H560" t="n">
         <v>103.8242</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.748009</v>
+        <v>67.748001</v>
       </c>
       <c r="H562" t="n">
         <v>104.5953</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.89490499999999</v>
+        <v>67.894897</v>
       </c>
       <c r="H563" t="n">
         <v>104.8221</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.659859</v>
+        <v>67.65986599999999</v>
       </c>
       <c r="H564" t="n">
         <v>104.4592</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>68.149513</v>
+        <v>68.14952099999999</v>
       </c>
       <c r="H569" t="n">
         <v>105.2152</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H570" t="n">
         <v>104.2778</v>
@@ -22150,10 +22150,10 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>67.997215</v>
+        <v>67.99722300000001</v>
       </c>
       <c r="H572" t="n">
-        <v>104.98</v>
+        <v>104.9801</v>
       </c>
     </row>
     <row r="573">
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>68.27299499999999</v>
+        <v>68.272987</v>
       </c>
       <c r="H573" t="n">
         <v>105.4058</v>
@@ -22267,7 +22267,7 @@
         <v>68.35178399999999</v>
       </c>
       <c r="H575" t="n">
-        <v>105.5274</v>
+        <v>105.5275</v>
       </c>
     </row>
     <row r="576">
@@ -22343,7 +22343,7 @@
         <v>68.686646</v>
       </c>
       <c r="H577" t="n">
-        <v>106.0444</v>
+        <v>106.0445</v>
       </c>
     </row>
     <row r="578">
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>68.903328</v>
+        <v>68.90331999999999</v>
       </c>
       <c r="H578" t="n">
         <v>106.379</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>69.632141</v>
+        <v>69.632149</v>
       </c>
       <c r="H579" t="n">
         <v>107.5042</v>
@@ -22609,7 +22609,7 @@
         <v>70.577652</v>
       </c>
       <c r="H584" t="n">
-        <v>108.9639</v>
+        <v>108.964</v>
       </c>
     </row>
     <row r="585">
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.66629</v>
+        <v>70.66628300000001</v>
       </c>
       <c r="H585" t="n">
         <v>109.1008</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>71.690575</v>
+        <v>71.69058200000001</v>
       </c>
       <c r="H588" t="n">
         <v>110.6822</v>
@@ -22799,7 +22799,7 @@
         <v>71.119339</v>
       </c>
       <c r="H589" t="n">
-        <v>109.8002</v>
+        <v>109.8003</v>
       </c>
     </row>
     <row r="590">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.459457</v>
+        <v>70.45946499999999</v>
       </c>
       <c r="H590" t="n">
         <v>108.7815</v>
@@ -22875,7 +22875,7 @@
         <v>70.76477800000001</v>
       </c>
       <c r="H591" t="n">
-        <v>109.2528</v>
+        <v>109.2529</v>
       </c>
     </row>
     <row r="592">
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>70.804176</v>
+        <v>70.804169</v>
       </c>
       <c r="H595" t="n">
         <v>109.3137</v>
@@ -23141,7 +23141,7 @@
         <v>71.28677399999999</v>
       </c>
       <c r="H598" t="n">
-        <v>110.0587</v>
+        <v>110.0588</v>
       </c>
     </row>
     <row r="599">
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>72.084541</v>
+        <v>72.084534</v>
       </c>
       <c r="H599" t="n">
         <v>111.2904</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>73.286118</v>
+        <v>73.28610999999999</v>
       </c>
       <c r="H601" t="n">
         <v>113.1455</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>72.754265</v>
+        <v>72.754272</v>
       </c>
       <c r="H602" t="n">
         <v>112.3244</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>73.71946699999999</v>
+        <v>73.71946</v>
       </c>
       <c r="H604" t="n">
         <v>113.8145</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.536934</v>
+        <v>74.53692599999999</v>
       </c>
       <c r="H606" t="n">
         <v>115.0766</v>
@@ -23518,10 +23518,10 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.241455</v>
+        <v>74.241463</v>
       </c>
       <c r="H608" t="n">
-        <v>114.6204</v>
+        <v>114.6205</v>
       </c>
     </row>
     <row r="609">
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.300552</v>
+        <v>74.30056</v>
       </c>
       <c r="H609" t="n">
         <v>114.7117</v>
@@ -23711,7 +23711,7 @@
         <v>75.10817</v>
       </c>
       <c r="H613" t="n">
-        <v>115.9585</v>
+        <v>115.9586</v>
       </c>
     </row>
     <row r="614">
@@ -23749,7 +23749,7 @@
         <v>74.940735</v>
       </c>
       <c r="H614" t="n">
-        <v>115.7</v>
+        <v>115.7001</v>
       </c>
     </row>
     <row r="615">
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>75.699112</v>
+        <v>75.69910400000001</v>
       </c>
       <c r="H617" t="n">
         <v>116.8709</v>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>73.76870700000001</v>
+        <v>73.768715</v>
       </c>
       <c r="H620" t="n">
         <v>113.8906</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>73.12853200000001</v>
+        <v>73.128525</v>
       </c>
       <c r="H625" t="n">
         <v>112.9022</v>
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>72.842911</v>
+        <v>72.84290300000001</v>
       </c>
       <c r="H626" t="n">
         <v>112.4612</v>
@@ -24281,7 +24281,7 @@
         <v>73.187622</v>
       </c>
       <c r="H628" t="n">
-        <v>112.9934</v>
+        <v>112.9935</v>
       </c>
     </row>
     <row r="629">
@@ -25383,7 +25383,7 @@
         <v>74.200523</v>
       </c>
       <c r="H657" t="n">
-        <v>114.5572</v>
+        <v>114.5573</v>
       </c>
     </row>
     <row r="658">
@@ -25497,7 +25497,7 @@
         <v>74.368797</v>
       </c>
       <c r="H660" t="n">
-        <v>114.817</v>
+        <v>114.8171</v>
       </c>
     </row>
     <row r="661">
@@ -25953,7 +25953,7 @@
         <v>76.170357</v>
       </c>
       <c r="H672" t="n">
-        <v>117.5984</v>
+        <v>117.5985</v>
       </c>
     </row>
     <row r="673">
@@ -26029,7 +26029,7 @@
         <v>76.96225699999999</v>
       </c>
       <c r="H674" t="n">
-        <v>118.821</v>
+        <v>118.8211</v>
       </c>
     </row>
     <row r="675">
@@ -26067,7 +26067,7 @@
         <v>77.526482</v>
       </c>
       <c r="H675" t="n">
-        <v>119.6921</v>
+        <v>119.6922</v>
       </c>
     </row>
     <row r="676">
@@ -26447,7 +26447,7 @@
         <v>77.02164500000001</v>
       </c>
       <c r="H685" t="n">
-        <v>118.9127</v>
+        <v>118.9128</v>
       </c>
     </row>
     <row r="686">
@@ -26485,7 +26485,7 @@
         <v>76.56630699999999</v>
       </c>
       <c r="H686" t="n">
-        <v>118.2097</v>
+        <v>118.2098</v>
       </c>
     </row>
     <row r="687">
@@ -26523,7 +26523,7 @@
         <v>76.853371</v>
       </c>
       <c r="H687" t="n">
-        <v>118.6529</v>
+        <v>118.653</v>
       </c>
     </row>
     <row r="688">
@@ -27017,7 +27017,7 @@
         <v>78.470001</v>
       </c>
       <c r="H700" t="n">
-        <v>121.1488</v>
+        <v>121.1489</v>
       </c>
     </row>
     <row r="701">
@@ -27549,7 +27549,7 @@
         <v>79.910004</v>
       </c>
       <c r="H714" t="n">
-        <v>123.372</v>
+        <v>123.3721</v>
       </c>
     </row>
     <row r="715">
@@ -27701,7 +27701,7 @@
         <v>80.400002</v>
       </c>
       <c r="H718" t="n">
-        <v>124.1285</v>
+        <v>124.1286</v>
       </c>
     </row>
     <row r="719">
@@ -28385,7 +28385,7 @@
         <v>81.300003</v>
       </c>
       <c r="H736" t="n">
-        <v>125.518</v>
+        <v>125.5181</v>
       </c>
     </row>
     <row r="737">
@@ -28423,7 +28423,7 @@
         <v>81.199997</v>
       </c>
       <c r="H737" t="n">
-        <v>125.3636</v>
+        <v>125.3637</v>
       </c>
     </row>
     <row r="738">
@@ -28575,7 +28575,7 @@
         <v>81.480003</v>
       </c>
       <c r="H741" t="n">
-        <v>125.7959</v>
+        <v>125.796</v>
       </c>
     </row>
     <row r="742">
@@ -28613,7 +28613,7 @@
         <v>81.660004</v>
       </c>
       <c r="H742" t="n">
-        <v>126.0738</v>
+        <v>126.0739</v>
       </c>
     </row>
     <row r="743">
@@ -28651,7 +28651,7 @@
         <v>81.25</v>
       </c>
       <c r="H743" t="n">
-        <v>125.4408</v>
+        <v>125.4409</v>
       </c>
     </row>
     <row r="744">
@@ -28765,7 +28765,7 @@
         <v>81.55999799999999</v>
       </c>
       <c r="H746" t="n">
-        <v>125.9194</v>
+        <v>125.9195</v>
       </c>
     </row>
     <row r="747">
@@ -29075,7 +29075,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.910004</v>
+        <v>81.33000199999999</v>
       </c>
       <c r="H755" t="n">
-        <v>124.9159</v>
+        <v>125.5644</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>125.800003</v>
+        <v>126.43</v>
       </c>
       <c r="H1006" t="n">
-        <v>117.9781</v>
+        <v>118.5689</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>125.800003</v>
+        <v>126.43</v>
       </c>
       <c r="H1257" t="n">
-        <v>117.9781</v>
+        <v>118.5689</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>125.800003</v>
+        <v>126.43</v>
       </c>
       <c r="H1508" t="n">
-        <v>117.9781</v>
+        <v>118.5689</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>54.284752</v>
+        <v>53.776489</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.655476</v>
+        <v>53.153103</v>
       </c>
       <c r="H1510" t="n">
         <v>98.8408</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.645649</v>
+        <v>53.143368</v>
       </c>
       <c r="H1511" t="n">
         <v>98.8227</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.068439</v>
+        <v>53.562199</v>
       </c>
       <c r="H1512" t="n">
         <v>99.6015</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>53.999607</v>
+        <v>53.494015</v>
       </c>
       <c r="H1513" t="n">
         <v>99.4747</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.881622</v>
+        <v>53.377132</v>
       </c>
       <c r="H1514" t="n">
         <v>99.2574</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.048775</v>
+        <v>53.542721</v>
       </c>
       <c r="H1515" t="n">
         <v>99.56529999999999</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>53.930782</v>
+        <v>53.425835</v>
       </c>
       <c r="H1516" t="n">
         <v>99.3479</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>53.57682</v>
+        <v>53.075188</v>
       </c>
       <c r="H1517" t="n">
         <v>98.69589999999999</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.02911</v>
+        <v>53.523239</v>
       </c>
       <c r="H1518" t="n">
         <v>99.5291</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.12743</v>
+        <v>53.62064</v>
       </c>
       <c r="H1519" t="n">
         <v>99.7102</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.353577</v>
+        <v>53.844669</v>
       </c>
       <c r="H1520" t="n">
         <v>100.1268</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.012352</v>
+        <v>54.497272</v>
       </c>
       <c r="H1521" t="n">
         <v>101.3403</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.317154</v>
+        <v>54.799221</v>
       </c>
       <c r="H1522" t="n">
         <v>101.9018</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.58263</v>
+        <v>55.062218</v>
       </c>
       <c r="H1523" t="n">
         <v>102.3909</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.562965</v>
+        <v>55.042732</v>
       </c>
       <c r="H1524" t="n">
         <v>102.3546</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.494137</v>
+        <v>54.974552</v>
       </c>
       <c r="H1525" t="n">
         <v>102.2279</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.926765</v>
+        <v>55.40313</v>
       </c>
       <c r="H1526" t="n">
         <v>103.0248</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.680954</v>
+        <v>55.159618</v>
       </c>
       <c r="H1527" t="n">
         <v>102.572</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.943523</v>
+        <v>54.429092</v>
       </c>
       <c r="H1528" t="n">
         <v>101.2135</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.25816</v>
+        <v>54.740784</v>
       </c>
       <c r="H1529" t="n">
         <v>101.7932</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.051685</v>
+        <v>54.536236</v>
       </c>
       <c r="H1530" t="n">
         <v>101.4128</v>
@@ -58592,10 +58592,10 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.336819</v>
+        <v>54.818703</v>
       </c>
       <c r="H1531" t="n">
-        <v>101.9381</v>
+        <v>101.938</v>
       </c>
     </row>
     <row r="1532">
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.779278</v>
+        <v>55.257019</v>
       </c>
       <c r="H1532" t="n">
         <v>102.7531</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.199165</v>
+        <v>54.682343</v>
       </c>
       <c r="H1533" t="n">
         <v>101.6845</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.779278</v>
+        <v>55.257019</v>
       </c>
       <c r="H1534" t="n">
         <v>102.7531</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.926765</v>
+        <v>55.40313</v>
       </c>
       <c r="H1535" t="n">
         <v>103.0248</v>
@@ -58782,10 +58782,10 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.798939</v>
+        <v>55.276505</v>
       </c>
       <c r="H1536" t="n">
-        <v>102.7893</v>
+        <v>102.7894</v>
       </c>
     </row>
     <row r="1537">
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.995594</v>
+        <v>55.47131</v>
       </c>
       <c r="H1537" t="n">
         <v>103.1516</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>56.280735</v>
+        <v>55.75378</v>
       </c>
       <c r="H1538" t="n">
         <v>103.6769</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>56.162743</v>
+        <v>55.636894</v>
       </c>
       <c r="H1539" t="n">
         <v>103.4595</v>
@@ -58934,10 +58934,10 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>56.113579</v>
+        <v>55.588188</v>
       </c>
       <c r="H1540" t="n">
-        <v>103.369</v>
+        <v>103.3689</v>
       </c>
     </row>
     <row r="1541">
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>56.054585</v>
+        <v>55.529747</v>
       </c>
       <c r="H1541" t="n">
         <v>103.2603</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.818611</v>
+        <v>55.295986</v>
       </c>
       <c r="H1542" t="n">
         <v>102.8256</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>55.848106</v>
+        <v>55.325203</v>
       </c>
       <c r="H1543" t="n">
         <v>102.8799</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.690788</v>
+        <v>55.169357</v>
       </c>
       <c r="H1544" t="n">
         <v>102.5901</v>
@@ -59124,10 +59124,10 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.798939</v>
+        <v>55.276505</v>
       </c>
       <c r="H1545" t="n">
-        <v>102.7893</v>
+        <v>102.7894</v>
       </c>
     </row>
     <row r="1546">
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.385986</v>
+        <v>54.867409</v>
       </c>
       <c r="H1546" t="n">
         <v>102.0286</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.100842</v>
+        <v>54.584934</v>
       </c>
       <c r="H1547" t="n">
         <v>101.5033</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.907101</v>
+        <v>55.383648</v>
       </c>
       <c r="H1548" t="n">
         <v>102.9886</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>56.634693</v>
+        <v>56.104427</v>
       </c>
       <c r="H1549" t="n">
         <v>104.3289</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>57.057491</v>
+        <v>56.523262</v>
       </c>
       <c r="H1550" t="n">
         <v>105.1078</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>56.674026</v>
+        <v>56.143387</v>
       </c>
       <c r="H1551" t="n">
         <v>104.4014</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>56.133247</v>
+        <v>55.607674</v>
       </c>
       <c r="H1552" t="n">
         <v>103.4052</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.828438</v>
+        <v>55.305721</v>
       </c>
       <c r="H1553" t="n">
         <v>102.8437</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.855034</v>
+        <v>54.341431</v>
       </c>
       <c r="H1554" t="n">
         <v>101.0505</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>54.80587</v>
+        <v>54.292728</v>
       </c>
       <c r="H1555" t="n">
         <v>100.96</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.002514</v>
+        <v>54.487534</v>
       </c>
       <c r="H1556" t="n">
         <v>101.3222</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.864864</v>
+        <v>54.351166</v>
       </c>
       <c r="H1557" t="n">
         <v>101.0686</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>54.933693</v>
+        <v>54.419353</v>
       </c>
       <c r="H1558" t="n">
         <v>101.1954</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.395817</v>
+        <v>54.877144</v>
       </c>
       <c r="H1559" t="n">
         <v>102.0467</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>56.054585</v>
+        <v>55.529747</v>
       </c>
       <c r="H1560" t="n">
         <v>103.2603</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.093914</v>
+        <v>55.56871</v>
       </c>
       <c r="H1561" t="n">
         <v>103.3327</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.280735</v>
+        <v>55.75378</v>
       </c>
       <c r="H1562" t="n">
         <v>103.6769</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.093914</v>
+        <v>55.56871</v>
       </c>
       <c r="H1563" t="n">
         <v>103.3327</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.162743</v>
+        <v>55.636894</v>
       </c>
       <c r="H1564" t="n">
         <v>103.4595</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.251232</v>
+        <v>55.724556</v>
       </c>
       <c r="H1565" t="n">
         <v>103.6225</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.487213</v>
+        <v>55.958328</v>
       </c>
       <c r="H1566" t="n">
         <v>104.0572</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.516705</v>
+        <v>55.987549</v>
       </c>
       <c r="H1567" t="n">
         <v>104.1116</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.428215</v>
+        <v>55.899883</v>
       </c>
       <c r="H1568" t="n">
         <v>103.9486</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.369221</v>
+        <v>55.841442</v>
       </c>
       <c r="H1569" t="n">
         <v>103.8399</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.39872</v>
+        <v>55.870659</v>
       </c>
       <c r="H1570" t="n">
         <v>103.8942</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.703522</v>
+        <v>56.172611</v>
       </c>
       <c r="H1571" t="n">
         <v>104.4557</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.379055</v>
+        <v>55.851185</v>
       </c>
       <c r="H1572" t="n">
         <v>103.858</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.826939</v>
+        <v>56.294872</v>
       </c>
       <c r="H1573" t="n">
         <v>104.6831</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.590164</v>
+        <v>56.06031</v>
       </c>
       <c r="H1574" t="n">
         <v>104.2469</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.521103</v>
+        <v>55.991898</v>
       </c>
       <c r="H1575" t="n">
         <v>104.1197</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>57.093319</v>
+        <v>56.558758</v>
       </c>
       <c r="H1576" t="n">
         <v>105.1738</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>57.320232</v>
+        <v>56.783543</v>
       </c>
       <c r="H1577" t="n">
         <v>105.5918</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>57.211712</v>
+        <v>56.676041</v>
       </c>
       <c r="H1578" t="n">
         <v>105.3919</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>57.428753</v>
+        <v>56.891052</v>
       </c>
       <c r="H1579" t="n">
         <v>105.7917</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>57.507683</v>
+        <v>56.969246</v>
       </c>
       <c r="H1580" t="n">
         <v>105.9371</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>57.813522</v>
+        <v>57.272217</v>
       </c>
       <c r="H1581" t="n">
         <v>106.5005</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.237751</v>
+        <v>57.692474</v>
       </c>
       <c r="H1582" t="n">
         <v>107.282</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.760639</v>
+        <v>58.210468</v>
       </c>
       <c r="H1583" t="n">
         <v>108.2452</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.086205</v>
+        <v>58.53299</v>
       </c>
       <c r="H1584" t="n">
         <v>108.8449</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.066475</v>
+        <v>58.513443</v>
       </c>
       <c r="H1585" t="n">
         <v>108.8086</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.948086</v>
+        <v>58.39616</v>
       </c>
       <c r="H1586" t="n">
         <v>108.5905</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.589367</v>
+        <v>59.031437</v>
       </c>
       <c r="H1587" t="n">
         <v>109.7718</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.688019</v>
+        <v>59.129169</v>
       </c>
       <c r="H1588" t="n">
         <v>109.9536</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.628822</v>
+        <v>59.070522</v>
       </c>
       <c r="H1589" t="n">
         <v>109.8445</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.707756</v>
+        <v>59.148712</v>
       </c>
       <c r="H1590" t="n">
         <v>109.9899</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>60.053055</v>
+        <v>59.49078</v>
       </c>
       <c r="H1591" t="n">
         <v>110.626</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>60.06292</v>
+        <v>59.500557</v>
       </c>
       <c r="H1592" t="n">
         <v>110.6442</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>59.26379</v>
+        <v>58.708908</v>
       </c>
       <c r="H1593" t="n">
         <v>109.1721</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>58.829697</v>
+        <v>58.278881</v>
       </c>
       <c r="H1594" t="n">
         <v>108.3724</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>58.809967</v>
+        <v>58.259331</v>
       </c>
       <c r="H1595" t="n">
         <v>108.3361</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.470974</v>
+        <v>58.91415</v>
       </c>
       <c r="H1596" t="n">
         <v>109.5537</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.421646</v>
+        <v>58.86528</v>
       </c>
       <c r="H1597" t="n">
         <v>109.4629</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.510437</v>
+        <v>58.953243</v>
       </c>
       <c r="H1598" t="n">
         <v>109.6264</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.865604</v>
+        <v>59.305092</v>
       </c>
       <c r="H1599" t="n">
         <v>110.2807</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.392048</v>
+        <v>58.835964</v>
       </c>
       <c r="H1600" t="n">
         <v>109.4083</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.273659</v>
+        <v>58.718685</v>
       </c>
       <c r="H1601" t="n">
         <v>109.1903</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.727486</v>
+        <v>59.168262</v>
       </c>
       <c r="H1602" t="n">
         <v>110.0263</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.358894</v>
+        <v>59.793758</v>
       </c>
       <c r="H1603" t="n">
         <v>111.1894</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.339165</v>
+        <v>59.774212</v>
       </c>
       <c r="H1604" t="n">
         <v>111.1531</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>60.368759</v>
+        <v>59.803532</v>
       </c>
       <c r="H1605" t="n">
         <v>111.2076</v>
@@ -61442,10 +61442,10 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>59.806408</v>
+        <v>59.246445</v>
       </c>
       <c r="H1606" t="n">
-        <v>110.1717</v>
+        <v>110.1716</v>
       </c>
     </row>
     <row r="1607">
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.309566</v>
+        <v>59.744892</v>
       </c>
       <c r="H1607" t="n">
         <v>111.0985</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.723927</v>
+        <v>60.155373</v>
       </c>
       <c r="H1608" t="n">
         <v>111.8618</v>
@@ -61556,10 +61556,10 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.684467</v>
+        <v>60.11628</v>
       </c>
       <c r="H1609" t="n">
-        <v>111.7892</v>
+        <v>111.7891</v>
       </c>
     </row>
     <row r="1610">
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.773258</v>
+        <v>60.204239</v>
       </c>
       <c r="H1610" t="n">
         <v>111.9527</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>60.497017</v>
+        <v>59.930584</v>
       </c>
       <c r="H1611" t="n">
         <v>111.4438</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>60.418091</v>
+        <v>59.852402</v>
       </c>
       <c r="H1612" t="n">
         <v>111.2985</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.506886</v>
+        <v>59.940361</v>
       </c>
       <c r="H1613" t="n">
         <v>111.462</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>60.832455</v>
+        <v>60.262882</v>
       </c>
       <c r="H1614" t="n">
         <v>112.0618</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>61.532921</v>
+        <v>60.956799</v>
       </c>
       <c r="H1615" t="n">
         <v>113.3521</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>61.227085</v>
+        <v>60.65382</v>
       </c>
       <c r="H1616" t="n">
         <v>112.7887</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>61.779564</v>
+        <v>61.201126</v>
       </c>
       <c r="H1617" t="n">
         <v>113.8065</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>61.44413</v>
+        <v>60.868835</v>
       </c>
       <c r="H1618" t="n">
         <v>113.1886</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>61.592117</v>
+        <v>61.015434</v>
       </c>
       <c r="H1619" t="n">
         <v>113.4612</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>62.055813</v>
+        <v>61.474785</v>
       </c>
       <c r="H1620" t="n">
         <v>114.3154</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>61.986752</v>
+        <v>61.406372</v>
       </c>
       <c r="H1621" t="n">
         <v>114.1881</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>62.026215</v>
+        <v>61.445465</v>
       </c>
       <c r="H1622" t="n">
         <v>114.2608</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>61.019901</v>
+        <v>60.448574</v>
       </c>
       <c r="H1623" t="n">
         <v>112.4071</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>59.194733</v>
+        <v>58.640495</v>
       </c>
       <c r="H1624" t="n">
         <v>109.0449</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>59.954399</v>
+        <v>59.393051</v>
       </c>
       <c r="H1625" t="n">
         <v>110.4443</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>59.135536</v>
+        <v>58.581856</v>
       </c>
       <c r="H1626" t="n">
         <v>108.9358</v>
@@ -62240,7 +62240,7 @@
         </is>
       </c>
       <c r="G1627" t="n">
-        <v>58.602787</v>
+        <v>58.054089</v>
       </c>
       <c r="H1627" t="n">
         <v>107.9544</v>
@@ -62278,7 +62278,7 @@
         </is>
       </c>
       <c r="G1628" t="n">
-        <v>58.198288</v>
+        <v>57.653385</v>
       </c>
       <c r="H1628" t="n">
         <v>107.2093</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>59.34272</v>
+        <v>58.787102</v>
       </c>
       <c r="H1629" t="n">
         <v>109.3175</v>
@@ -62354,10 +62354,10 @@
         </is>
       </c>
       <c r="G1630" t="n">
-        <v>59.007282</v>
+        <v>58.4548</v>
       </c>
       <c r="H1630" t="n">
-        <v>108.6996</v>
+        <v>108.6995</v>
       </c>
     </row>
     <row r="1631">
@@ -62392,10 +62392,10 @@
         </is>
       </c>
       <c r="G1631" t="n">
-        <v>58.661976</v>
+        <v>58.112728</v>
       </c>
       <c r="H1631" t="n">
-        <v>108.0635</v>
+        <v>108.0634</v>
       </c>
     </row>
     <row r="1632">
@@ -62430,7 +62430,7 @@
         </is>
       </c>
       <c r="G1632" t="n">
-        <v>58.336411</v>
+        <v>57.790211</v>
       </c>
       <c r="H1632" t="n">
         <v>107.4637</v>
@@ -62468,7 +62468,7 @@
         </is>
       </c>
       <c r="G1633" t="n">
-        <v>58.586716</v>
+        <v>58.038174</v>
       </c>
       <c r="H1633" t="n">
         <v>107.9248</v>
@@ -62506,7 +62506,7 @@
         </is>
       </c>
       <c r="G1634" t="n">
-        <v>58.982304</v>
+        <v>58.430054</v>
       </c>
       <c r="H1634" t="n">
         <v>108.6535</v>
@@ -62544,7 +62544,7 @@
         </is>
       </c>
       <c r="G1635" t="n">
-        <v>58.537266</v>
+        <v>57.989185</v>
       </c>
       <c r="H1635" t="n">
         <v>107.8337</v>
@@ -62582,7 +62582,7 @@
         </is>
       </c>
       <c r="G1636" t="n">
-        <v>57.083481</v>
+        <v>56.549011</v>
       </c>
       <c r="H1636" t="n">
         <v>105.1556</v>
@@ -62620,7 +62620,7 @@
         </is>
       </c>
       <c r="G1637" t="n">
-        <v>56.074726</v>
+        <v>55.549702</v>
       </c>
       <c r="H1637" t="n">
         <v>103.2974</v>
@@ -62658,7 +62658,7 @@
         </is>
       </c>
       <c r="G1638" t="n">
-        <v>56.509872</v>
+        <v>55.980774</v>
       </c>
       <c r="H1638" t="n">
         <v>104.099</v>
@@ -62696,7 +62696,7 @@
         </is>
       </c>
       <c r="G1639" t="n">
-        <v>56.687889</v>
+        <v>56.157124</v>
       </c>
       <c r="H1639" t="n">
         <v>104.4269</v>
@@ -62734,7 +62734,7 @@
         </is>
       </c>
       <c r="G1640" t="n">
-        <v>57.647194</v>
+        <v>57.107449</v>
       </c>
       <c r="H1640" t="n">
         <v>106.1941</v>
@@ -62772,7 +62772,7 @@
         </is>
       </c>
       <c r="G1641" t="n">
-        <v>56.935131</v>
+        <v>56.40205</v>
       </c>
       <c r="H1641" t="n">
         <v>104.8824</v>
@@ -62810,7 +62810,7 @@
         </is>
       </c>
       <c r="G1642" t="n">
-        <v>56.420864</v>
+        <v>55.892601</v>
       </c>
       <c r="H1642" t="n">
         <v>103.935</v>
@@ -62848,7 +62848,7 @@
         </is>
       </c>
       <c r="G1643" t="n">
-        <v>57.00436</v>
+        <v>56.470631</v>
       </c>
       <c r="H1643" t="n">
         <v>105.0099</v>
@@ -62886,7 +62886,7 @@
         </is>
       </c>
       <c r="G1644" t="n">
-        <v>57.281269</v>
+        <v>56.744949</v>
       </c>
       <c r="H1644" t="n">
         <v>105.52</v>
@@ -62924,7 +62924,7 @@
         </is>
       </c>
       <c r="G1645" t="n">
-        <v>58.705395</v>
+        <v>58.155739</v>
       </c>
       <c r="H1645" t="n">
         <v>108.1434</v>
@@ -62962,7 +62962,7 @@
         </is>
       </c>
       <c r="G1646" t="n">
-        <v>58.586716</v>
+        <v>58.038174</v>
       </c>
       <c r="H1646" t="n">
         <v>107.9248</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>57.993332</v>
+        <v>57.450344</v>
       </c>
       <c r="H1647" t="n">
         <v>106.8317</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>60.337196</v>
+        <v>59.772263</v>
       </c>
       <c r="H1648" t="n">
         <v>111.1494</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>60.277859</v>
+        <v>59.713482</v>
       </c>
       <c r="H1649" t="n">
         <v>111.0401</v>
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>60.465763</v>
+        <v>59.899628</v>
       </c>
       <c r="H1650" t="n">
         <v>111.3863</v>
@@ -63152,7 +63152,7 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>60.366867</v>
+        <v>59.801655</v>
       </c>
       <c r="H1651" t="n">
         <v>111.2041</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>60.910801</v>
+        <v>60.340496</v>
       </c>
       <c r="H1652" t="n">
         <v>112.2061</v>
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>60.722897</v>
+        <v>60.154354</v>
       </c>
       <c r="H1653" t="n">
         <v>111.86</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>60.693226</v>
+        <v>60.124958</v>
       </c>
       <c r="H1654" t="n">
         <v>111.8053</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>61.662418</v>
+        <v>61.085079</v>
       </c>
       <c r="H1655" t="n">
         <v>113.5907</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>61.138264</v>
+        <v>60.56583</v>
       </c>
       <c r="H1656" t="n">
         <v>112.6251</v>
@@ -63380,7 +63380,7 @@
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>60.64378</v>
+        <v>60.075974</v>
       </c>
       <c r="H1657" t="n">
         <v>111.7142</v>
@@ -63418,7 +63418,7 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>60.485542</v>
+        <v>59.91922</v>
       </c>
       <c r="H1658" t="n">
         <v>111.4227</v>
@@ -63456,7 +63456,7 @@
         </is>
       </c>
       <c r="G1659" t="n">
-        <v>60.515209</v>
+        <v>59.948612</v>
       </c>
       <c r="H1659" t="n">
         <v>111.4774</v>
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>60.18885</v>
+        <v>59.625309</v>
       </c>
       <c r="H1660" t="n">
         <v>110.8762</v>
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>60.040504</v>
+        <v>59.478348</v>
       </c>
       <c r="H1661" t="n">
         <v>110.6029</v>
@@ -63570,7 +63570,7 @@
         </is>
       </c>
       <c r="G1662" t="n">
-        <v>59.813042</v>
+        <v>59.253017</v>
       </c>
       <c r="H1662" t="n">
         <v>110.1839</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="G1663" t="n">
-        <v>59.506458</v>
+        <v>58.949306</v>
       </c>
       <c r="H1663" t="n">
         <v>109.6191</v>
@@ -63646,7 +63646,7 @@
         </is>
       </c>
       <c r="G1664" t="n">
-        <v>60.376755</v>
+        <v>59.811451</v>
       </c>
       <c r="H1664" t="n">
         <v>111.2223</v>
@@ -63684,7 +63684,7 @@
         </is>
       </c>
       <c r="G1665" t="n">
-        <v>59.684475</v>
+        <v>59.125652</v>
       </c>
       <c r="H1665" t="n">
         <v>109.947</v>
@@ -63722,7 +63722,7 @@
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>60.297638</v>
+        <v>59.733078</v>
       </c>
       <c r="H1666" t="n">
         <v>111.0766</v>
@@ -63760,7 +63760,7 @@
         </is>
       </c>
       <c r="G1667" t="n">
-        <v>61.632751</v>
+        <v>61.055683</v>
       </c>
       <c r="H1667" t="n">
         <v>113.536</v>
@@ -63798,7 +63798,7 @@
         </is>
       </c>
       <c r="G1668" t="n">
-        <v>60.900913</v>
+        <v>60.330704</v>
       </c>
       <c r="H1668" t="n">
         <v>112.1879</v>
@@ -63836,7 +63836,7 @@
         </is>
       </c>
       <c r="G1669" t="n">
-        <v>60.623997</v>
+        <v>60.056381</v>
       </c>
       <c r="H1669" t="n">
         <v>111.6778</v>
@@ -63874,7 +63874,7 @@
         </is>
       </c>
       <c r="G1670" t="n">
-        <v>60.703117</v>
+        <v>60.134758</v>
       </c>
       <c r="H1670" t="n">
         <v>111.8235</v>
@@ -63912,7 +63912,7 @@
         </is>
       </c>
       <c r="G1671" t="n">
-        <v>60.070175</v>
+        <v>59.50774</v>
       </c>
       <c r="H1671" t="n">
         <v>110.6575</v>
@@ -63950,7 +63950,7 @@
         </is>
       </c>
       <c r="G1672" t="n">
-        <v>60.59433</v>
+        <v>60.026989</v>
       </c>
       <c r="H1672" t="n">
         <v>111.6231</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.23716</v>
+        <v>60.663799</v>
       </c>
       <c r="H1673" t="n">
         <v>112.8073</v>
@@ -64026,7 +64026,7 @@
         </is>
       </c>
       <c r="G1674" t="n">
-        <v>60.139404</v>
+        <v>59.576324</v>
       </c>
       <c r="H1674" t="n">
         <v>110.7851</v>
@@ -64064,7 +64064,7 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>60.59433</v>
+        <v>60.026989</v>
       </c>
       <c r="H1675" t="n">
         <v>111.6231</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>60.633888</v>
+        <v>60.066177</v>
       </c>
       <c r="H1676" t="n">
         <v>111.696</v>
@@ -64140,10 +64140,10 @@
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.642643</v>
+        <v>61.065487</v>
       </c>
       <c r="H1677" t="n">
-        <v>113.5543</v>
+        <v>113.5542</v>
       </c>
     </row>
     <row r="1678">
@@ -64178,10 +64178,10 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.642643</v>
+        <v>61.065487</v>
       </c>
       <c r="H1678" t="n">
-        <v>113.5543</v>
+        <v>113.5542</v>
       </c>
     </row>
     <row r="1679">
@@ -64216,10 +64216,10 @@
         </is>
       </c>
       <c r="G1679" t="n">
-        <v>62.186577</v>
+        <v>61.604328</v>
       </c>
       <c r="H1679" t="n">
-        <v>114.5563</v>
+        <v>114.5562</v>
       </c>
     </row>
     <row r="1680">
@@ -64254,7 +64254,7 @@
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>63.234882</v>
+        <v>62.642818</v>
       </c>
       <c r="H1680" t="n">
         <v>116.4874</v>
@@ -64292,7 +64292,7 @@
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>62.463486</v>
+        <v>61.878647</v>
       </c>
       <c r="H1681" t="n">
         <v>115.0664</v>
@@ -64330,7 +64330,7 @@
         </is>
       </c>
       <c r="G1682" t="n">
-        <v>62.433819</v>
+        <v>61.849255</v>
       </c>
       <c r="H1682" t="n">
         <v>115.0117</v>
@@ -64368,7 +64368,7 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>62.196465</v>
+        <v>61.61412</v>
       </c>
       <c r="H1683" t="n">
         <v>114.5745</v>
@@ -64406,7 +64406,7 @@
         </is>
       </c>
       <c r="G1684" t="n">
-        <v>62.216244</v>
+        <v>61.633717</v>
       </c>
       <c r="H1684" t="n">
         <v>114.6109</v>
@@ -64444,7 +64444,7 @@
         </is>
       </c>
       <c r="G1685" t="n">
-        <v>61.899773</v>
+        <v>61.32021</v>
       </c>
       <c r="H1685" t="n">
         <v>114.0279</v>
@@ -64482,7 +64482,7 @@
         </is>
       </c>
       <c r="G1686" t="n">
-        <v>62.26569</v>
+        <v>61.682705</v>
       </c>
       <c r="H1686" t="n">
         <v>114.702</v>
@@ -64520,7 +64520,7 @@
         </is>
       </c>
       <c r="G1687" t="n">
-        <v>61.820652</v>
+        <v>61.241829</v>
       </c>
       <c r="H1687" t="n">
         <v>113.8822</v>
@@ -64558,7 +64558,7 @@
         </is>
       </c>
       <c r="G1688" t="n">
-        <v>62.196465</v>
+        <v>61.61412</v>
       </c>
       <c r="H1688" t="n">
         <v>114.5745</v>
@@ -64596,7 +64596,7 @@
         </is>
       </c>
       <c r="G1689" t="n">
-        <v>61.949223</v>
+        <v>61.369194</v>
       </c>
       <c r="H1689" t="n">
         <v>114.119</v>
@@ -64634,7 +64634,7 @@
         </is>
       </c>
       <c r="G1690" t="n">
-        <v>61.860214</v>
+        <v>61.281021</v>
       </c>
       <c r="H1690" t="n">
         <v>113.955</v>
@@ -64672,7 +64672,7 @@
         </is>
       </c>
       <c r="G1691" t="n">
-        <v>61.533855</v>
+        <v>60.957718</v>
       </c>
       <c r="H1691" t="n">
         <v>113.3538</v>
@@ -64710,7 +64710,7 @@
         </is>
       </c>
       <c r="G1692" t="n">
-        <v>61.474514</v>
+        <v>60.898933</v>
       </c>
       <c r="H1692" t="n">
         <v>113.2445</v>
@@ -64748,7 +64748,7 @@
         </is>
       </c>
       <c r="G1693" t="n">
-        <v>61.870106</v>
+        <v>61.290817</v>
       </c>
       <c r="H1693" t="n">
         <v>113.9733</v>
@@ -64786,7 +64786,7 @@
         </is>
       </c>
       <c r="G1694" t="n">
-        <v>63.027203</v>
+        <v>62.437084</v>
       </c>
       <c r="H1694" t="n">
         <v>116.1048</v>
@@ -64824,7 +64824,7 @@
         </is>
       </c>
       <c r="G1695" t="n">
-        <v>63.080002</v>
+        <v>62.489388</v>
       </c>
       <c r="H1695" t="n">
         <v>116.2021</v>
@@ -64862,7 +64862,7 @@
         </is>
       </c>
       <c r="G1696" t="n">
-        <v>63.25</v>
+        <v>62.657795</v>
       </c>
       <c r="H1696" t="n">
         <v>116.5152</v>
@@ -64900,7 +64900,7 @@
         </is>
       </c>
       <c r="G1697" t="n">
-        <v>63.630001</v>
+        <v>63.034237</v>
       </c>
       <c r="H1697" t="n">
         <v>117.2152</v>
@@ -64938,7 +64938,7 @@
         </is>
       </c>
       <c r="G1698" t="n">
-        <v>63.360001</v>
+        <v>62.766766</v>
       </c>
       <c r="H1698" t="n">
         <v>116.7179</v>
@@ -64976,7 +64976,7 @@
         </is>
       </c>
       <c r="G1699" t="n">
-        <v>63.220001</v>
+        <v>62.628075</v>
       </c>
       <c r="H1699" t="n">
         <v>116.46</v>
@@ -65014,7 +65014,7 @@
         </is>
       </c>
       <c r="G1700" t="n">
-        <v>63.630001</v>
+        <v>63.034237</v>
       </c>
       <c r="H1700" t="n">
         <v>117.2152</v>
@@ -65052,7 +65052,7 @@
         </is>
       </c>
       <c r="G1701" t="n">
-        <v>63.18</v>
+        <v>62.588451</v>
       </c>
       <c r="H1701" t="n">
         <v>116.3863</v>
@@ -65090,7 +65090,7 @@
         </is>
       </c>
       <c r="G1702" t="n">
-        <v>63.299999</v>
+        <v>62.707325</v>
       </c>
       <c r="H1702" t="n">
         <v>116.6073</v>
@@ -65128,7 +65128,7 @@
         </is>
       </c>
       <c r="G1703" t="n">
-        <v>63.790001</v>
+        <v>63.192738</v>
       </c>
       <c r="H1703" t="n">
         <v>117.51</v>
@@ -65166,7 +65166,7 @@
         </is>
       </c>
       <c r="G1704" t="n">
-        <v>63.330002</v>
+        <v>62.737045</v>
       </c>
       <c r="H1704" t="n">
         <v>116.6626</v>
@@ -65204,7 +65204,7 @@
         </is>
       </c>
       <c r="G1705" t="n">
-        <v>63.360001</v>
+        <v>62.766766</v>
       </c>
       <c r="H1705" t="n">
         <v>116.7179</v>
@@ -65242,7 +65242,7 @@
         </is>
       </c>
       <c r="G1706" t="n">
-        <v>63.939999</v>
+        <v>63.341331</v>
       </c>
       <c r="H1706" t="n">
         <v>117.7863</v>
@@ -65280,7 +65280,7 @@
         </is>
       </c>
       <c r="G1707" t="n">
-        <v>63.740002</v>
+        <v>63.143208</v>
       </c>
       <c r="H1707" t="n">
         <v>117.4179</v>
@@ -65318,7 +65318,7 @@
         </is>
       </c>
       <c r="G1708" t="n">
-        <v>64.660004</v>
+        <v>64.054596</v>
       </c>
       <c r="H1708" t="n">
         <v>119.1126</v>
@@ -65356,7 +65356,7 @@
         </is>
       </c>
       <c r="G1709" t="n">
-        <v>65.05999799999999</v>
+        <v>64.450844</v>
       </c>
       <c r="H1709" t="n">
         <v>119.8495</v>
@@ -65394,7 +65394,7 @@
         </is>
       </c>
       <c r="G1710" t="n">
-        <v>64.860001</v>
+        <v>64.252724</v>
       </c>
       <c r="H1710" t="n">
         <v>119.4811</v>
@@ -65432,7 +65432,7 @@
         </is>
       </c>
       <c r="G1711" t="n">
-        <v>64.449997</v>
+        <v>63.846558</v>
       </c>
       <c r="H1711" t="n">
         <v>118.7258</v>
@@ -65470,10 +65470,10 @@
         </is>
       </c>
       <c r="G1712" t="n">
-        <v>63.450001</v>
+        <v>62.855923</v>
       </c>
       <c r="H1712" t="n">
-        <v>116.8837</v>
+        <v>116.8836</v>
       </c>
     </row>
     <row r="1713">
@@ -65508,10 +65508,10 @@
         </is>
       </c>
       <c r="G1713" t="n">
-        <v>63.919998</v>
+        <v>63.321518</v>
       </c>
       <c r="H1713" t="n">
-        <v>117.7495</v>
+        <v>117.7494</v>
       </c>
     </row>
     <row r="1714">
@@ -65546,7 +65546,7 @@
         </is>
       </c>
       <c r="G1714" t="n">
-        <v>63.990002</v>
+        <v>63.390869</v>
       </c>
       <c r="H1714" t="n">
         <v>117.8784</v>
@@ -65584,7 +65584,7 @@
         </is>
       </c>
       <c r="G1715" t="n">
-        <v>63.990002</v>
+        <v>63.390869</v>
       </c>
       <c r="H1715" t="n">
         <v>117.8784</v>
@@ -65622,7 +65622,7 @@
         </is>
       </c>
       <c r="G1716" t="n">
-        <v>63.970001</v>
+        <v>63.371056</v>
       </c>
       <c r="H1716" t="n">
         <v>117.8416</v>
@@ -65660,7 +65660,7 @@
         </is>
       </c>
       <c r="G1717" t="n">
-        <v>64.110001</v>
+        <v>63.509743</v>
       </c>
       <c r="H1717" t="n">
         <v>118.0995</v>
@@ -65698,7 +65698,7 @@
         </is>
       </c>
       <c r="G1718" t="n">
-        <v>64.199997</v>
+        <v>63.598896</v>
       </c>
       <c r="H1718" t="n">
         <v>118.2652</v>
@@ -65736,7 +65736,7 @@
         </is>
       </c>
       <c r="G1719" t="n">
-        <v>63.959999</v>
+        <v>63.361145</v>
       </c>
       <c r="H1719" t="n">
         <v>117.8231</v>
@@ -65774,7 +65774,7 @@
         </is>
       </c>
       <c r="G1720" t="n">
-        <v>63.740002</v>
+        <v>63.143208</v>
       </c>
       <c r="H1720" t="n">
         <v>117.4179</v>
@@ -65812,7 +65812,7 @@
         </is>
       </c>
       <c r="G1721" t="n">
-        <v>64.110001</v>
+        <v>63.509743</v>
       </c>
       <c r="H1721" t="n">
         <v>118.0995</v>
@@ -65850,7 +65850,7 @@
         </is>
       </c>
       <c r="G1722" t="n">
-        <v>64.449997</v>
+        <v>63.846558</v>
       </c>
       <c r="H1722" t="n">
         <v>118.7258</v>
@@ -65888,7 +65888,7 @@
         </is>
       </c>
       <c r="G1723" t="n">
-        <v>63.700001</v>
+        <v>63.10358</v>
       </c>
       <c r="H1723" t="n">
         <v>117.3442</v>
@@ -65926,7 +65926,7 @@
         </is>
       </c>
       <c r="G1724" t="n">
-        <v>64.230003</v>
+        <v>63.62862</v>
       </c>
       <c r="H1724" t="n">
         <v>118.3205</v>
@@ -65964,7 +65964,7 @@
         </is>
       </c>
       <c r="G1725" t="n">
-        <v>64.19000200000001</v>
+        <v>63.588997</v>
       </c>
       <c r="H1725" t="n">
         <v>118.2468</v>
@@ -66002,7 +66002,7 @@
         </is>
       </c>
       <c r="G1726" t="n">
-        <v>64.489998</v>
+        <v>63.886181</v>
       </c>
       <c r="H1726" t="n">
         <v>118.7995</v>
@@ -66040,7 +66040,7 @@
         </is>
       </c>
       <c r="G1727" t="n">
-        <v>64.30999799999999</v>
+        <v>63.707867</v>
       </c>
       <c r="H1727" t="n">
         <v>118.4679</v>
@@ -66078,7 +66078,7 @@
         </is>
       </c>
       <c r="G1728" t="n">
-        <v>64.80999799999999</v>
+        <v>64.203186</v>
       </c>
       <c r="H1728" t="n">
         <v>119.389</v>
@@ -66116,7 +66116,7 @@
         </is>
       </c>
       <c r="G1729" t="n">
-        <v>64.730003</v>
+        <v>64.12394</v>
       </c>
       <c r="H1729" t="n">
         <v>119.2416</v>
@@ -66154,7 +66154,7 @@
         </is>
       </c>
       <c r="G1730" t="n">
-        <v>65.050003</v>
+        <v>64.440941</v>
       </c>
       <c r="H1730" t="n">
         <v>119.8311</v>
@@ -66192,7 +66192,7 @@
         </is>
       </c>
       <c r="G1731" t="n">
-        <v>65.56999999999999</v>
+        <v>64.95607</v>
       </c>
       <c r="H1731" t="n">
         <v>120.789</v>
@@ -66230,7 +66230,7 @@
         </is>
       </c>
       <c r="G1732" t="n">
-        <v>65.550003</v>
+        <v>64.93626399999999</v>
       </c>
       <c r="H1732" t="n">
         <v>120.7521</v>
@@ -66268,7 +66268,7 @@
         </is>
       </c>
       <c r="G1733" t="n">
-        <v>65.699997</v>
+        <v>65.08485400000001</v>
       </c>
       <c r="H1733" t="n">
         <v>121.0285</v>
@@ -66306,7 +66306,7 @@
         </is>
       </c>
       <c r="G1734" t="n">
-        <v>65.91999800000001</v>
+        <v>65.302795</v>
       </c>
       <c r="H1734" t="n">
         <v>121.4337</v>
@@ -66344,7 +66344,7 @@
         </is>
       </c>
       <c r="G1735" t="n">
-        <v>65.900002</v>
+        <v>65.282982</v>
       </c>
       <c r="H1735" t="n">
         <v>121.3969</v>
@@ -66382,7 +66382,7 @@
         </is>
       </c>
       <c r="G1736" t="n">
-        <v>65.949997</v>
+        <v>65.33251199999999</v>
       </c>
       <c r="H1736" t="n">
         <v>121.489</v>
@@ -66420,7 +66420,7 @@
         </is>
       </c>
       <c r="G1737" t="n">
-        <v>65.910004</v>
+        <v>65.29289199999999</v>
       </c>
       <c r="H1737" t="n">
         <v>121.4153</v>
@@ -66458,10 +66458,10 @@
         </is>
       </c>
       <c r="G1738" t="n">
-        <v>65.93000000000001</v>
+        <v>65.312698</v>
       </c>
       <c r="H1738" t="n">
-        <v>121.4522</v>
+        <v>121.4521</v>
       </c>
     </row>
     <row r="1739">
@@ -66496,7 +66496,7 @@
         </is>
       </c>
       <c r="G1739" t="n">
-        <v>65.760002</v>
+        <v>65.144295</v>
       </c>
       <c r="H1739" t="n">
         <v>121.139</v>
@@ -66534,7 +66534,7 @@
         </is>
       </c>
       <c r="G1740" t="n">
-        <v>65.629997</v>
+        <v>65.015511</v>
       </c>
       <c r="H1740" t="n">
         <v>120.8995</v>
@@ -66572,7 +66572,7 @@
         </is>
       </c>
       <c r="G1741" t="n">
-        <v>65.160004</v>
+        <v>64.54991099999999</v>
       </c>
       <c r="H1741" t="n">
         <v>120.0337</v>
@@ -66610,7 +66610,7 @@
         </is>
       </c>
       <c r="G1742" t="n">
-        <v>65.110001</v>
+        <v>64.500381</v>
       </c>
       <c r="H1742" t="n">
         <v>119.9416</v>
@@ -66648,7 +66648,7 @@
         </is>
       </c>
       <c r="G1743" t="n">
-        <v>64.989998</v>
+        <v>64.3815</v>
       </c>
       <c r="H1743" t="n">
         <v>119.7205</v>
@@ -66686,7 +66686,7 @@
         </is>
       </c>
       <c r="G1744" t="n">
-        <v>65.480003</v>
+        <v>64.86691999999999</v>
       </c>
       <c r="H1744" t="n">
         <v>120.6232</v>
@@ -66724,7 +66724,7 @@
         </is>
       </c>
       <c r="G1745" t="n">
-        <v>65.43000000000001</v>
+        <v>64.81738300000001</v>
       </c>
       <c r="H1745" t="n">
         <v>120.5311</v>
@@ -66762,7 +66762,7 @@
         </is>
       </c>
       <c r="G1746" t="n">
-        <v>65.68000000000001</v>
+        <v>65.06504099999999</v>
       </c>
       <c r="H1746" t="n">
         <v>120.9916</v>
@@ -66800,7 +66800,7 @@
         </is>
       </c>
       <c r="G1747" t="n">
-        <v>65.629997</v>
+        <v>65.015511</v>
       </c>
       <c r="H1747" t="n">
         <v>120.8995</v>
@@ -66838,7 +66838,7 @@
         </is>
       </c>
       <c r="G1748" t="n">
-        <v>65.209999</v>
+        <v>64.599442</v>
       </c>
       <c r="H1748" t="n">
         <v>120.1258</v>
@@ -66876,7 +66876,7 @@
         </is>
       </c>
       <c r="G1749" t="n">
-        <v>65.510002</v>
+        <v>64.896637</v>
       </c>
       <c r="H1749" t="n">
         <v>120.6785</v>
@@ -66914,7 +66914,7 @@
         </is>
       </c>
       <c r="G1750" t="n">
-        <v>64.970001</v>
+        <v>64.361694</v>
       </c>
       <c r="H1750" t="n">
         <v>119.6837</v>
@@ -66952,7 +66952,7 @@
         </is>
       </c>
       <c r="G1751" t="n">
-        <v>64.779999</v>
+        <v>64.17346999999999</v>
       </c>
       <c r="H1751" t="n">
         <v>119.3337</v>
@@ -66990,7 +66990,7 @@
         </is>
       </c>
       <c r="G1752" t="n">
-        <v>64.529999</v>
+        <v>63.925808</v>
       </c>
       <c r="H1752" t="n">
         <v>118.8732</v>
@@ -67028,7 +67028,7 @@
         </is>
       </c>
       <c r="G1753" t="n">
-        <v>64.980003</v>
+        <v>64.37159699999999</v>
       </c>
       <c r="H1753" t="n">
         <v>119.7021</v>
@@ -67066,7 +67066,7 @@
         </is>
       </c>
       <c r="G1754" t="n">
-        <v>65</v>
+        <v>64.39141100000001</v>
       </c>
       <c r="H1754" t="n">
         <v>119.739</v>
@@ -67104,7 +67104,7 @@
         </is>
       </c>
       <c r="G1755" t="n">
-        <v>64.970001</v>
+        <v>64.361694</v>
       </c>
       <c r="H1755" t="n">
         <v>119.6837</v>
@@ -67142,7 +67142,7 @@
         </is>
       </c>
       <c r="G1756" t="n">
-        <v>64.93000000000001</v>
+        <v>64.322067</v>
       </c>
       <c r="H1756" t="n">
         <v>119.61</v>
@@ -67180,10 +67180,10 @@
         </is>
       </c>
       <c r="G1757" t="n">
-        <v>64.010002</v>
+        <v>63.410679</v>
       </c>
       <c r="H1757" t="n">
-        <v>117.9153</v>
+        <v>117.9152</v>
       </c>
     </row>
     <row r="1758">
@@ -67218,7 +67218,7 @@
         </is>
       </c>
       <c r="G1758" t="n">
-        <v>63.490002</v>
+        <v>62.89555</v>
       </c>
       <c r="H1758" t="n">
         <v>116.9573</v>
@@ -67256,7 +67256,7 @@
         </is>
       </c>
       <c r="G1759" t="n">
-        <v>63.860001</v>
+        <v>63.262085</v>
       </c>
       <c r="H1759" t="n">
         <v>117.6389</v>
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.740002</v>
+        <v>62.984707</v>
       </c>
       <c r="H1760" t="n">
-        <v>115.5757</v>
+        <v>117.1231</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.950001</v>
+        <v>34.924999</v>
       </c>
       <c r="H253" t="n">
-        <v>117.7561</v>
+        <v>117.6718</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.224998</v>
+        <v>47.115002</v>
       </c>
       <c r="H504" t="n">
-        <v>129.9175</v>
+        <v>129.6149</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.22653200000001</v>
+        <v>64.226524</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,10 +19642,10 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.489311</v>
+        <v>64.48931899999999</v>
       </c>
       <c r="H506" t="n">
-        <v>100.4091</v>
+        <v>100.4092</v>
       </c>
     </row>
     <row r="507">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.77093499999999</v>
+        <v>64.770927</v>
       </c>
       <c r="H508" t="n">
         <v>100.8476</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.70238500000001</v>
+        <v>64.702377</v>
       </c>
       <c r="H509" t="n">
         <v>100.7409</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.810097</v>
+        <v>64.810104</v>
       </c>
       <c r="H512" t="n">
         <v>100.9086</v>
@@ -19908,10 +19908,10 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.103897</v>
+        <v>65.103905</v>
       </c>
       <c r="H513" t="n">
-        <v>101.366</v>
+        <v>101.3661</v>
       </c>
     </row>
     <row r="514">
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.035347</v>
+        <v>65.035355</v>
       </c>
       <c r="H514" t="n">
         <v>101.2593</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H517" t="n">
         <v>102.0217</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.231201</v>
+        <v>65.23120900000001</v>
       </c>
       <c r="H523" t="n">
         <v>101.5643</v>
@@ -20405,7 +20405,7 @@
         <v>65.906921</v>
       </c>
       <c r="H526" t="n">
-        <v>102.6163</v>
+        <v>102.6164</v>
       </c>
     </row>
     <row r="527">
@@ -20443,7 +20443,7 @@
         <v>65.926506</v>
       </c>
       <c r="H527" t="n">
-        <v>102.6468</v>
+        <v>102.6469</v>
       </c>
     </row>
     <row r="528">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>65.485817</v>
+        <v>65.48582500000001</v>
       </c>
       <c r="H528" t="n">
         <v>101.9607</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.30843400000001</v>
+        <v>66.308441</v>
       </c>
       <c r="H531" t="n">
         <v>103.2415</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.435738</v>
+        <v>66.435745</v>
       </c>
       <c r="H532" t="n">
         <v>103.4397</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.709953</v>
+        <v>66.709946</v>
       </c>
       <c r="H534" t="n">
         <v>103.8667</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.58264200000001</v>
+        <v>66.582634</v>
       </c>
       <c r="H535" t="n">
         <v>103.6684</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.66098</v>
+        <v>66.660988</v>
       </c>
       <c r="H540" t="n">
         <v>103.7904</v>
@@ -20972,10 +20972,10 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.357399</v>
+        <v>66.35740699999999</v>
       </c>
       <c r="H541" t="n">
-        <v>103.3177</v>
+        <v>103.3178</v>
       </c>
     </row>
     <row r="542">
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.73932600000001</v>
+        <v>66.739334</v>
       </c>
       <c r="H543" t="n">
         <v>103.9124</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>67.317116</v>
+        <v>67.317108</v>
       </c>
       <c r="H544" t="n">
         <v>104.812</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>67.943871</v>
+        <v>67.94386299999999</v>
       </c>
       <c r="H545" t="n">
         <v>105.7879</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.150642</v>
+        <v>67.15063499999999</v>
       </c>
       <c r="H547" t="n">
         <v>104.5528</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.12236799999999</v>
+        <v>66.12236</v>
       </c>
       <c r="H549" t="n">
         <v>102.9518</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.396568</v>
+        <v>66.396576</v>
       </c>
       <c r="H551" t="n">
         <v>103.3787</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.25947600000001</v>
+        <v>66.259468</v>
       </c>
       <c r="H552" t="n">
         <v>103.1653</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.620705</v>
+        <v>67.62069700000001</v>
       </c>
       <c r="H557" t="n">
         <v>105.2847</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.317116</v>
+        <v>67.317108</v>
       </c>
       <c r="H560" t="n">
         <v>104.812</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.748009</v>
+        <v>67.748001</v>
       </c>
       <c r="H561" t="n">
         <v>105.4829</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.76759300000001</v>
+        <v>67.76758599999999</v>
       </c>
       <c r="H567" t="n">
         <v>105.5134</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H569" t="n">
         <v>105.1627</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>67.997215</v>
+        <v>67.99722300000001</v>
       </c>
       <c r="H571" t="n">
         <v>105.8709</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>68.27299499999999</v>
+        <v>68.272987</v>
       </c>
       <c r="H572" t="n">
         <v>106.3003</v>
@@ -22305,7 +22305,7 @@
         <v>68.686646</v>
       </c>
       <c r="H576" t="n">
-        <v>106.9443</v>
+        <v>106.9444</v>
       </c>
     </row>
     <row r="577">
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>68.903328</v>
+        <v>68.90331999999999</v>
       </c>
       <c r="H577" t="n">
         <v>107.2817</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>69.632141</v>
+        <v>69.632149</v>
       </c>
       <c r="H578" t="n">
         <v>108.4165</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.66629</v>
+        <v>70.66628300000001</v>
       </c>
       <c r="H584" t="n">
         <v>110.0266</v>
@@ -22647,7 +22647,7 @@
         <v>71.040543</v>
       </c>
       <c r="H585" t="n">
-        <v>110.6093</v>
+        <v>110.6094</v>
       </c>
     </row>
     <row r="586">
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>71.690575</v>
+        <v>71.69058200000001</v>
       </c>
       <c r="H587" t="n">
-        <v>111.6214</v>
+        <v>111.6215</v>
       </c>
     </row>
     <row r="588">
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>70.459457</v>
+        <v>70.45946499999999</v>
       </c>
       <c r="H589" t="n">
         <v>109.7046</v>
@@ -22875,7 +22875,7 @@
         <v>71.26707500000001</v>
       </c>
       <c r="H591" t="n">
-        <v>110.962</v>
+        <v>110.9621</v>
       </c>
     </row>
     <row r="592">
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>70.804176</v>
+        <v>70.804169</v>
       </c>
       <c r="H594" t="n">
         <v>110.2413</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>72.084541</v>
+        <v>72.084534</v>
       </c>
       <c r="H598" t="n">
         <v>112.2348</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.286118</v>
+        <v>73.28610999999999</v>
       </c>
       <c r="H600" t="n">
         <v>114.1057</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>72.754265</v>
+        <v>72.754272</v>
       </c>
       <c r="H601" t="n">
         <v>113.2776</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>73.71946699999999</v>
+        <v>73.71946</v>
       </c>
       <c r="H603" t="n">
         <v>114.7804</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>74.536934</v>
+        <v>74.53692599999999</v>
       </c>
       <c r="H605" t="n">
         <v>116.0532</v>
@@ -23480,10 +23480,10 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.241455</v>
+        <v>74.241463</v>
       </c>
       <c r="H607" t="n">
-        <v>115.5931</v>
+        <v>115.5932</v>
       </c>
     </row>
     <row r="608">
@@ -23518,10 +23518,10 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.300552</v>
+        <v>74.30056</v>
       </c>
       <c r="H608" t="n">
-        <v>115.6851</v>
+        <v>115.6852</v>
       </c>
     </row>
     <row r="609">
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>75.699112</v>
+        <v>75.69910400000001</v>
       </c>
       <c r="H616" t="n">
         <v>117.8627</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>73.76870700000001</v>
+        <v>73.768715</v>
       </c>
       <c r="H619" t="n">
         <v>114.8571</v>
@@ -23977,7 +23977,7 @@
         <v>74.271011</v>
       </c>
       <c r="H620" t="n">
-        <v>115.6391</v>
+        <v>115.6392</v>
       </c>
     </row>
     <row r="621">
@@ -24053,7 +24053,7 @@
         <v>72.429253</v>
       </c>
       <c r="H622" t="n">
-        <v>112.7715</v>
+        <v>112.7716</v>
       </c>
     </row>
     <row r="623">
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>73.12853200000001</v>
+        <v>73.128525</v>
       </c>
       <c r="H624" t="n">
         <v>113.8603</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>72.842911</v>
+        <v>72.84290300000001</v>
       </c>
       <c r="H625" t="n">
         <v>113.4156</v>
@@ -24775,7 +24775,7 @@
         <v>72.85430100000001</v>
       </c>
       <c r="H641" t="n">
-        <v>113.4333</v>
+        <v>113.4334</v>
       </c>
     </row>
     <row r="642">
@@ -24965,7 +24965,7 @@
         <v>74.24012</v>
       </c>
       <c r="H646" t="n">
-        <v>115.591</v>
+        <v>115.5911</v>
       </c>
     </row>
     <row r="647">
@@ -25193,7 +25193,7 @@
         <v>74.24012</v>
       </c>
       <c r="H652" t="n">
-        <v>115.591</v>
+        <v>115.5911</v>
       </c>
     </row>
     <row r="653">
@@ -25269,7 +25269,7 @@
         <v>74.002548</v>
       </c>
       <c r="H654" t="n">
-        <v>115.2211</v>
+        <v>115.2212</v>
       </c>
     </row>
     <row r="655">
@@ -25383,7 +25383,7 @@
         <v>73.992653</v>
       </c>
       <c r="H657" t="n">
-        <v>115.2057</v>
+        <v>115.2058</v>
       </c>
     </row>
     <row r="658">
@@ -25573,7 +25573,7 @@
         <v>75.051811</v>
       </c>
       <c r="H662" t="n">
-        <v>116.8548</v>
+        <v>116.8549</v>
       </c>
     </row>
     <row r="663">
@@ -25649,7 +25649,7 @@
         <v>75.051811</v>
       </c>
       <c r="H664" t="n">
-        <v>116.8548</v>
+        <v>116.8549</v>
       </c>
     </row>
     <row r="665">
@@ -25687,7 +25687,7 @@
         <v>74.893433</v>
       </c>
       <c r="H665" t="n">
-        <v>116.6082</v>
+        <v>116.6083</v>
       </c>
     </row>
     <row r="666">
@@ -25801,7 +25801,7 @@
         <v>75.467552</v>
       </c>
       <c r="H668" t="n">
-        <v>117.5021</v>
+        <v>117.5022</v>
       </c>
     </row>
     <row r="669">
@@ -26143,7 +26143,7 @@
         <v>76.77417800000001</v>
       </c>
       <c r="H677" t="n">
-        <v>119.5365</v>
+        <v>119.5366</v>
       </c>
     </row>
     <row r="678">
@@ -26219,7 +26219,7 @@
         <v>76.605904</v>
       </c>
       <c r="H679" t="n">
-        <v>119.2745</v>
+        <v>119.2746</v>
       </c>
     </row>
     <row r="680">
@@ -26333,7 +26333,7 @@
         <v>77.338402</v>
       </c>
       <c r="H682" t="n">
-        <v>120.415</v>
+        <v>120.4151</v>
       </c>
     </row>
     <row r="683">
@@ -26409,7 +26409,7 @@
         <v>77.02164500000001</v>
       </c>
       <c r="H684" t="n">
-        <v>119.9218</v>
+        <v>119.9219</v>
       </c>
     </row>
     <row r="685">
@@ -26485,7 +26485,7 @@
         <v>76.853371</v>
       </c>
       <c r="H686" t="n">
-        <v>119.6598</v>
+        <v>119.6599</v>
       </c>
     </row>
     <row r="687">
@@ -27549,7 +27549,7 @@
         <v>79.760002</v>
       </c>
       <c r="H714" t="n">
-        <v>124.1854</v>
+        <v>124.1855</v>
       </c>
     </row>
     <row r="715">
@@ -27625,7 +27625,7 @@
         <v>80.720001</v>
       </c>
       <c r="H716" t="n">
-        <v>125.6801</v>
+        <v>125.6802</v>
       </c>
     </row>
     <row r="717">
@@ -27853,7 +27853,7 @@
         <v>80.389999</v>
       </c>
       <c r="H722" t="n">
-        <v>125.1663</v>
+        <v>125.1664</v>
       </c>
     </row>
     <row r="723">
@@ -27967,7 +27967,7 @@
         <v>81.19000200000001</v>
       </c>
       <c r="H725" t="n">
-        <v>126.4119</v>
+        <v>126.412</v>
       </c>
     </row>
     <row r="726">
@@ -28271,7 +28271,7 @@
         <v>81.75</v>
       </c>
       <c r="H733" t="n">
-        <v>127.2838</v>
+        <v>127.2839</v>
       </c>
     </row>
     <row r="734">
@@ -28309,7 +28309,7 @@
         <v>81.620003</v>
       </c>
       <c r="H734" t="n">
-        <v>127.0814</v>
+        <v>127.0815</v>
       </c>
     </row>
     <row r="735">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.370003</v>
+        <v>81.199997</v>
       </c>
       <c r="H755" t="n">
-        <v>126.6922</v>
+        <v>126.4275</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>126.459999</v>
+        <v>126.300003</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.5726</v>
+        <v>119.4213</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>126.459999</v>
+        <v>126.300003</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.5726</v>
+        <v>119.4213</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>126.459999</v>
+        <v>126.300003</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.5726</v>
+        <v>119.4213</v>
       </c>
     </row>
     <row r="1509">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.150002</v>
+        <v>63.049999</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.8077</v>
+        <v>118.6196</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.924999</v>
+        <v>35.235001</v>
       </c>
       <c r="H253" t="n">
-        <v>117.6718</v>
+        <v>118.7163</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.115002</v>
+        <v>47.195</v>
       </c>
       <c r="H504" t="n">
-        <v>129.6149</v>
+        <v>129.8349</v>
       </c>
     </row>
     <row r="505">
@@ -19642,10 +19642,10 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.48931899999999</v>
+        <v>64.489304</v>
       </c>
       <c r="H506" t="n">
-        <v>100.4092</v>
+        <v>100.4091</v>
       </c>
     </row>
     <row r="507">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.770927</v>
+        <v>64.77093499999999</v>
       </c>
       <c r="H508" t="n">
         <v>100.8476</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.702377</v>
+        <v>64.70238500000001</v>
       </c>
       <c r="H509" t="n">
         <v>100.7409</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.810104</v>
+        <v>64.810097</v>
       </c>
       <c r="H512" t="n">
         <v>100.9086</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.103905</v>
+        <v>65.103897</v>
       </c>
       <c r="H513" t="n">
         <v>101.3661</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.035355</v>
+        <v>65.035347</v>
       </c>
       <c r="H514" t="n">
         <v>101.2593</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.525002</v>
+        <v>65.52499400000001</v>
       </c>
       <c r="H517" t="n">
         <v>102.0217</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.23120900000001</v>
+        <v>65.231201</v>
       </c>
       <c r="H523" t="n">
         <v>101.5643</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H533" t="n">
         <v>103.9734</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H536" t="n">
         <v>103.9734</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.660988</v>
+        <v>66.66098</v>
       </c>
       <c r="H540" t="n">
         <v>103.7904</v>
@@ -20972,10 +20972,10 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.35740699999999</v>
+        <v>66.357399</v>
       </c>
       <c r="H541" t="n">
-        <v>103.3178</v>
+        <v>103.3177</v>
       </c>
     </row>
     <row r="542">
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.739334</v>
+        <v>66.73932600000001</v>
       </c>
       <c r="H543" t="n">
         <v>103.9124</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>67.94386299999999</v>
+        <v>67.943871</v>
       </c>
       <c r="H545" t="n">
         <v>105.7879</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.788292</v>
+        <v>66.788284</v>
       </c>
       <c r="H548" t="n">
         <v>103.9886</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.12236</v>
+        <v>66.12236799999999</v>
       </c>
       <c r="H549" t="n">
         <v>102.9518</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.396576</v>
+        <v>66.396568</v>
       </c>
       <c r="H551" t="n">
         <v>103.3787</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.259468</v>
+        <v>66.25947600000001</v>
       </c>
       <c r="H552" t="n">
         <v>103.1653</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.494499</v>
+        <v>66.494507</v>
       </c>
       <c r="H553" t="n">
         <v>103.5312</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.758911</v>
+        <v>66.75891900000001</v>
       </c>
       <c r="H554" t="n">
         <v>103.9429</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.375877</v>
+        <v>67.37587000000001</v>
       </c>
       <c r="H555" t="n">
         <v>104.9035</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.248558</v>
+        <v>67.248566</v>
       </c>
       <c r="H559" t="n">
         <v>104.7053</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.748001</v>
+        <v>67.748009</v>
       </c>
       <c r="H561" t="n">
         <v>105.4829</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.894897</v>
+        <v>67.89490499999999</v>
       </c>
       <c r="H562" t="n">
         <v>105.7116</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.65986599999999</v>
+        <v>67.659859</v>
       </c>
       <c r="H563" t="n">
         <v>105.3457</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>68.14952099999999</v>
+        <v>68.149513</v>
       </c>
       <c r="H568" t="n">
         <v>106.1081</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.54235799999999</v>
+        <v>67.542351</v>
       </c>
       <c r="H569" t="n">
         <v>105.1627</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>67.99722300000001</v>
+        <v>67.997215</v>
       </c>
       <c r="H571" t="n">
         <v>105.8709</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>68.272987</v>
+        <v>68.27299499999999</v>
       </c>
       <c r="H572" t="n">
         <v>106.3003</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>68.90331999999999</v>
+        <v>68.903328</v>
       </c>
       <c r="H577" t="n">
         <v>107.2817</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>69.632149</v>
+        <v>69.632141</v>
       </c>
       <c r="H578" t="n">
         <v>108.4165</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.66628300000001</v>
+        <v>70.66629</v>
       </c>
       <c r="H584" t="n">
         <v>110.0266</v>
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>71.69058200000001</v>
+        <v>71.690575</v>
       </c>
       <c r="H587" t="n">
-        <v>111.6215</v>
+        <v>111.6214</v>
       </c>
     </row>
     <row r="588">
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>70.45946499999999</v>
+        <v>70.459457</v>
       </c>
       <c r="H589" t="n">
         <v>109.7046</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>70.804169</v>
+        <v>70.804176</v>
       </c>
       <c r="H594" t="n">
         <v>110.2413</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>72.084534</v>
+        <v>72.084541</v>
       </c>
       <c r="H598" t="n">
         <v>112.2348</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.28610999999999</v>
+        <v>73.286118</v>
       </c>
       <c r="H600" t="n">
         <v>114.1057</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>72.754272</v>
+        <v>72.754265</v>
       </c>
       <c r="H601" t="n">
         <v>113.2776</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>73.71946</v>
+        <v>73.71946699999999</v>
       </c>
       <c r="H603" t="n">
         <v>114.7804</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>74.53692599999999</v>
+        <v>74.536934</v>
       </c>
       <c r="H605" t="n">
         <v>116.0532</v>
@@ -23480,10 +23480,10 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.241463</v>
+        <v>74.241455</v>
       </c>
       <c r="H607" t="n">
-        <v>115.5932</v>
+        <v>115.5931</v>
       </c>
     </row>
     <row r="608">
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.30056</v>
+        <v>74.300552</v>
       </c>
       <c r="H608" t="n">
         <v>115.6852</v>
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>75.69910400000001</v>
+        <v>75.699112</v>
       </c>
       <c r="H616" t="n">
         <v>117.8627</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>73.768715</v>
+        <v>73.76870700000001</v>
       </c>
       <c r="H619" t="n">
         <v>114.8571</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>73.128525</v>
+        <v>73.12853200000001</v>
       </c>
       <c r="H624" t="n">
         <v>113.8603</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>72.84290300000001</v>
+        <v>72.842911</v>
       </c>
       <c r="H625" t="n">
         <v>113.4156</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.199997</v>
+        <v>81.279999</v>
       </c>
       <c r="H755" t="n">
-        <v>126.4275</v>
+        <v>126.5521</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>126.300003</v>
+        <v>126.449997</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.4213</v>
+        <v>119.5632</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>126.300003</v>
+        <v>126.449997</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.4213</v>
+        <v>119.5632</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>126.300003</v>
+        <v>126.449997</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.4213</v>
+        <v>119.5632</v>
       </c>
     </row>
     <row r="1509">
@@ -57832,10 +57832,10 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.562195</v>
+        <v>53.562199</v>
       </c>
       <c r="H1511" t="n">
-        <v>100.7696</v>
+        <v>100.7697</v>
       </c>
     </row>
     <row r="1512">
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>53.494011</v>
+        <v>53.494015</v>
       </c>
       <c r="H1512" t="n">
         <v>100.6414</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>53.523239</v>
+        <v>53.523235</v>
       </c>
       <c r="H1517" t="n">
         <v>100.6964</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>53.620644</v>
+        <v>53.62064</v>
       </c>
       <c r="H1518" t="n">
         <v>100.8796</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.497276</v>
+        <v>54.497272</v>
       </c>
       <c r="H1520" t="n">
         <v>102.5289</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.062214</v>
+        <v>55.06221</v>
       </c>
       <c r="H1522" t="n">
         <v>103.5917</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.042728</v>
+        <v>55.042732</v>
       </c>
       <c r="H1523" t="n">
         <v>103.5551</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.159618</v>
+        <v>55.159622</v>
       </c>
       <c r="H1526" t="n">
         <v>103.775</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>54.429092</v>
+        <v>54.429096</v>
       </c>
       <c r="H1527" t="n">
         <v>102.4006</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.74078</v>
+        <v>54.740784</v>
       </c>
       <c r="H1528" t="n">
         <v>102.987</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>54.536232</v>
+        <v>54.536236</v>
       </c>
       <c r="H1529" t="n">
         <v>102.6022</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.257015</v>
+        <v>55.257019</v>
       </c>
       <c r="H1531" t="n">
         <v>103.9582</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1532" t="n">
         <v>102.877</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.257015</v>
+        <v>55.257019</v>
       </c>
       <c r="H1533" t="n">
         <v>103.9582</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1540" t="n">
         <v>104.4713</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1553" t="n">
         <v>102.2357</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.292725</v>
+        <v>54.292721</v>
       </c>
       <c r="H1554" t="n">
         <v>102.144</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1559" t="n">
         <v>104.4713</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>55.987545</v>
+        <v>55.987541</v>
       </c>
       <c r="H1566" t="n">
         <v>105.3326</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.049999</v>
+        <v>63.040001</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.6196</v>
+        <v>118.6008</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,10 +19642,10 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.489304</v>
+        <v>64.48931899999999</v>
       </c>
       <c r="H506" t="n">
-        <v>100.4091</v>
+        <v>100.4092</v>
       </c>
     </row>
     <row r="507">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.77093499999999</v>
+        <v>64.770927</v>
       </c>
       <c r="H508" t="n">
         <v>100.8476</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.70238500000001</v>
+        <v>64.702377</v>
       </c>
       <c r="H509" t="n">
         <v>100.7409</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.810097</v>
+        <v>64.810104</v>
       </c>
       <c r="H512" t="n">
         <v>100.9086</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.103897</v>
+        <v>65.103905</v>
       </c>
       <c r="H513" t="n">
         <v>101.3661</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.035347</v>
+        <v>65.035355</v>
       </c>
       <c r="H514" t="n">
         <v>101.2593</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H517" t="n">
         <v>102.0217</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.231201</v>
+        <v>65.23120900000001</v>
       </c>
       <c r="H523" t="n">
         <v>101.5643</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H533" t="n">
         <v>103.9734</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H536" t="n">
         <v>103.9734</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.66098</v>
+        <v>66.660988</v>
       </c>
       <c r="H540" t="n">
         <v>103.7904</v>
@@ -20972,10 +20972,10 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.357399</v>
+        <v>66.35740699999999</v>
       </c>
       <c r="H541" t="n">
-        <v>103.3177</v>
+        <v>103.3178</v>
       </c>
     </row>
     <row r="542">
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.73932600000001</v>
+        <v>66.739334</v>
       </c>
       <c r="H543" t="n">
         <v>103.9124</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>67.943871</v>
+        <v>67.94386299999999</v>
       </c>
       <c r="H545" t="n">
         <v>105.7879</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.788284</v>
+        <v>66.788292</v>
       </c>
       <c r="H548" t="n">
         <v>103.9886</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.12236799999999</v>
+        <v>66.12236</v>
       </c>
       <c r="H549" t="n">
         <v>102.9518</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.396568</v>
+        <v>66.396576</v>
       </c>
       <c r="H551" t="n">
         <v>103.3787</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.25947600000001</v>
+        <v>66.259468</v>
       </c>
       <c r="H552" t="n">
         <v>103.1653</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.494507</v>
+        <v>66.494499</v>
       </c>
       <c r="H553" t="n">
         <v>103.5312</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.75891900000001</v>
+        <v>66.758911</v>
       </c>
       <c r="H554" t="n">
         <v>103.9429</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.37587000000001</v>
+        <v>67.375877</v>
       </c>
       <c r="H555" t="n">
         <v>104.9035</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.248566</v>
+        <v>67.248558</v>
       </c>
       <c r="H559" t="n">
         <v>104.7053</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.748009</v>
+        <v>67.748001</v>
       </c>
       <c r="H561" t="n">
         <v>105.4829</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.89490499999999</v>
+        <v>67.894897</v>
       </c>
       <c r="H562" t="n">
         <v>105.7116</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.659859</v>
+        <v>67.65986599999999</v>
       </c>
       <c r="H563" t="n">
         <v>105.3457</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>68.149513</v>
+        <v>68.14952099999999</v>
       </c>
       <c r="H568" t="n">
         <v>106.1081</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H569" t="n">
         <v>105.1627</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>67.997215</v>
+        <v>67.99722300000001</v>
       </c>
       <c r="H571" t="n">
         <v>105.8709</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>68.27299499999999</v>
+        <v>68.272987</v>
       </c>
       <c r="H572" t="n">
         <v>106.3003</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>68.903328</v>
+        <v>68.90331999999999</v>
       </c>
       <c r="H577" t="n">
         <v>107.2817</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>69.632141</v>
+        <v>69.632149</v>
       </c>
       <c r="H578" t="n">
         <v>108.4165</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.66629</v>
+        <v>70.66628300000001</v>
       </c>
       <c r="H584" t="n">
         <v>110.0266</v>
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>71.690575</v>
+        <v>71.69058200000001</v>
       </c>
       <c r="H587" t="n">
-        <v>111.6214</v>
+        <v>111.6215</v>
       </c>
     </row>
     <row r="588">
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>70.459457</v>
+        <v>70.45946499999999</v>
       </c>
       <c r="H589" t="n">
         <v>109.7046</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>70.804176</v>
+        <v>70.804169</v>
       </c>
       <c r="H594" t="n">
         <v>110.2413</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>72.084541</v>
+        <v>72.084534</v>
       </c>
       <c r="H598" t="n">
         <v>112.2348</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.286118</v>
+        <v>73.28610999999999</v>
       </c>
       <c r="H600" t="n">
         <v>114.1057</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>72.754265</v>
+        <v>72.754272</v>
       </c>
       <c r="H601" t="n">
         <v>113.2776</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>73.71946699999999</v>
+        <v>73.71946</v>
       </c>
       <c r="H603" t="n">
         <v>114.7804</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>74.536934</v>
+        <v>74.53692599999999</v>
       </c>
       <c r="H605" t="n">
         <v>116.0532</v>
@@ -23480,10 +23480,10 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.241455</v>
+        <v>74.241463</v>
       </c>
       <c r="H607" t="n">
-        <v>115.5931</v>
+        <v>115.5932</v>
       </c>
     </row>
     <row r="608">
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.300552</v>
+        <v>74.30056</v>
       </c>
       <c r="H608" t="n">
         <v>115.6852</v>
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>75.699112</v>
+        <v>75.69910400000001</v>
       </c>
       <c r="H616" t="n">
         <v>117.8627</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>73.76870700000001</v>
+        <v>73.768715</v>
       </c>
       <c r="H619" t="n">
         <v>114.8571</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>73.12853200000001</v>
+        <v>73.128525</v>
       </c>
       <c r="H624" t="n">
         <v>113.8603</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>72.842911</v>
+        <v>72.84290300000001</v>
       </c>
       <c r="H625" t="n">
         <v>113.4156</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.143364</v>
+        <v>53.143368</v>
       </c>
       <c r="H1510" t="n">
         <v>99.9817</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.562199</v>
+        <v>53.562202</v>
       </c>
       <c r="H1511" t="n">
         <v>100.7697</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.542721</v>
+        <v>53.542717</v>
       </c>
       <c r="H1514" t="n">
         <v>100.733</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.425831</v>
+        <v>53.425835</v>
       </c>
       <c r="H1515" t="n">
         <v>100.5131</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>53.075184</v>
+        <v>53.075188</v>
       </c>
       <c r="H1516" t="n">
         <v>99.85339999999999</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>53.523235</v>
+        <v>53.523239</v>
       </c>
       <c r="H1517" t="n">
         <v>100.6964</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>53.62064</v>
+        <v>53.620636</v>
       </c>
       <c r="H1518" t="n">
         <v>100.8796</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.06221</v>
+        <v>55.062218</v>
       </c>
       <c r="H1522" t="n">
         <v>103.5917</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.974548</v>
+        <v>54.974552</v>
       </c>
       <c r="H1524" t="n">
         <v>103.4268</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.159622</v>
+        <v>55.159618</v>
       </c>
       <c r="H1526" t="n">
         <v>103.775</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.740784</v>
+        <v>54.740788</v>
       </c>
       <c r="H1528" t="n">
         <v>102.987</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>54.536236</v>
+        <v>54.53624</v>
       </c>
       <c r="H1529" t="n">
         <v>102.6022</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1537" t="n">
         <v>104.8928</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>55.588196</v>
+        <v>55.588192</v>
       </c>
       <c r="H1539" t="n">
         <v>104.5813</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>54.867413</v>
+        <v>54.867409</v>
       </c>
       <c r="H1545" t="n">
         <v>103.2252</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>56.523266</v>
+        <v>56.523262</v>
       </c>
       <c r="H1549" t="n">
         <v>106.3405</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.60767</v>
+        <v>55.607674</v>
       </c>
       <c r="H1551" t="n">
         <v>104.6179</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1553" t="n">
         <v>102.2357</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.292721</v>
+        <v>54.292725</v>
       </c>
       <c r="H1554" t="n">
         <v>102.144</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>54.35117</v>
+        <v>54.351166</v>
       </c>
       <c r="H1556" t="n">
         <v>102.254</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1557" t="n">
         <v>102.3823</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>54.877144</v>
+        <v>54.877148</v>
       </c>
       <c r="H1558" t="n">
         <v>103.2435</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1560" t="n">
         <v>104.5446</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1561" t="n">
         <v>104.8928</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1562" t="n">
         <v>104.5446</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>55.987541</v>
+        <v>55.987545</v>
       </c>
       <c r="H1566" t="n">
         <v>105.3326</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.172615</v>
+        <v>56.172611</v>
       </c>
       <c r="H1570" t="n">
         <v>105.6808</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1576" t="n">
         <v>106.8302</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>56.676037</v>
+        <v>56.676041</v>
       </c>
       <c r="H1577" t="n">
         <v>106.6279</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1579" t="n">
         <v>107.1795</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1589" t="n">
         <v>111.2799</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1590" t="n">
         <v>111.9234</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1591" t="n">
         <v>111.9418</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>58.259335</v>
+        <v>58.259331</v>
       </c>
       <c r="H1594" t="n">
         <v>109.6066</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.305092</v>
+        <v>59.305088</v>
       </c>
       <c r="H1598" t="n">
         <v>111.5741</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.168262</v>
+        <v>59.168259</v>
       </c>
       <c r="H1601" t="n">
         <v>111.3167</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.793758</v>
+        <v>59.793755</v>
       </c>
       <c r="H1602" t="n">
         <v>112.4934</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>59.803532</v>
+        <v>59.803528</v>
       </c>
       <c r="H1604" t="n">
         <v>112.5118</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>59.246445</v>
+        <v>59.246449</v>
       </c>
       <c r="H1605" t="n">
         <v>111.4638</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>59.744892</v>
+        <v>59.744896</v>
       </c>
       <c r="H1606" t="n">
         <v>112.4015</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.155376</v>
+        <v>60.155373</v>
       </c>
       <c r="H1607" t="n">
         <v>113.1738</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.11628</v>
+        <v>60.116276</v>
       </c>
       <c r="H1608" t="n">
         <v>113.1002</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1609" t="n">
         <v>113.2657</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1612" t="n">
         <v>112.7693</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1613" t="n">
         <v>113.376</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>60.956791</v>
+        <v>60.956795</v>
       </c>
       <c r="H1614" t="n">
         <v>114.6815</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>60.65382</v>
+        <v>60.653816</v>
       </c>
       <c r="H1615" t="n">
         <v>114.1115</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>61.20113</v>
+        <v>61.201126</v>
       </c>
       <c r="H1616" t="n">
         <v>115.1412</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>61.474789</v>
+        <v>61.474785</v>
       </c>
       <c r="H1619" t="n">
         <v>115.6561</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>61.445469</v>
+        <v>61.445465</v>
       </c>
       <c r="H1621" t="n">
         <v>115.6009</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.640491</v>
+        <v>58.640495</v>
       </c>
       <c r="H1623" t="n">
         <v>110.3237</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>58.581856</v>
+        <v>58.581852</v>
       </c>
       <c r="H1625" t="n">
         <v>110.2134</v>
@@ -62278,7 +62278,7 @@
         </is>
       </c>
       <c r="G1628" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1628" t="n">
         <v>110.5996</v>
@@ -62392,7 +62392,7 @@
         </is>
       </c>
       <c r="G1631" t="n">
-        <v>57.790207</v>
+        <v>57.790211</v>
       </c>
       <c r="H1631" t="n">
         <v>108.7241</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.235001</v>
+        <v>35.099998</v>
       </c>
       <c r="H253" t="n">
-        <v>118.7163</v>
+        <v>118.2614</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.195</v>
+        <v>46.705002</v>
       </c>
       <c r="H504" t="n">
-        <v>129.8349</v>
+        <v>128.4869</v>
       </c>
     </row>
     <row r="505">
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.48931899999999</v>
+        <v>64.489311</v>
       </c>
       <c r="H506" t="n">
         <v>100.4092</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.770927</v>
+        <v>64.77093499999999</v>
       </c>
       <c r="H508" t="n">
         <v>100.8476</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.103905</v>
+        <v>65.103897</v>
       </c>
       <c r="H513" t="n">
         <v>101.3661</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.035355</v>
+        <v>65.035347</v>
       </c>
       <c r="H514" t="n">
         <v>101.2593</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.525002</v>
+        <v>65.52499400000001</v>
       </c>
       <c r="H517" t="n">
         <v>102.0217</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>66.38678</v>
+        <v>66.386787</v>
       </c>
       <c r="H521" t="n">
         <v>103.3635</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.56416299999999</v>
+        <v>65.564171</v>
       </c>
       <c r="H524" t="n">
         <v>102.0827</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>65.48582500000001</v>
+        <v>65.485817</v>
       </c>
       <c r="H528" t="n">
         <v>101.9607</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.38678</v>
+        <v>66.386787</v>
       </c>
       <c r="H530" t="n">
         <v>103.3635</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.308441</v>
+        <v>66.308426</v>
       </c>
       <c r="H531" t="n">
         <v>103.2415</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.709946</v>
+        <v>66.709953</v>
       </c>
       <c r="H534" t="n">
         <v>103.8667</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.660988</v>
+        <v>66.66098</v>
       </c>
       <c r="H540" t="n">
         <v>103.7904</v>
@@ -20972,10 +20972,10 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.35740699999999</v>
+        <v>66.357399</v>
       </c>
       <c r="H541" t="n">
-        <v>103.3178</v>
+        <v>103.3177</v>
       </c>
     </row>
     <row r="542">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>67.94386299999999</v>
+        <v>67.943871</v>
       </c>
       <c r="H545" t="n">
         <v>105.7879</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.396576</v>
+        <v>66.396568</v>
       </c>
       <c r="H551" t="n">
         <v>103.3787</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.758911</v>
+        <v>66.75891900000001</v>
       </c>
       <c r="H554" t="n">
         <v>103.9429</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.62069700000001</v>
+        <v>67.620705</v>
       </c>
       <c r="H557" t="n">
         <v>105.2847</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.748001</v>
+        <v>67.748009</v>
       </c>
       <c r="H561" t="n">
         <v>105.4829</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.894897</v>
+        <v>67.89490499999999</v>
       </c>
       <c r="H562" t="n">
         <v>105.7116</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.601112</v>
+        <v>67.601105</v>
       </c>
       <c r="H565" t="n">
         <v>105.2542</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.855728</v>
+        <v>67.85573599999999</v>
       </c>
       <c r="H566" t="n">
         <v>105.6506</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.76758599999999</v>
+        <v>67.76759300000001</v>
       </c>
       <c r="H567" t="n">
         <v>105.5134</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.54235799999999</v>
+        <v>67.542351</v>
       </c>
       <c r="H569" t="n">
         <v>105.1627</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.610901</v>
+        <v>67.61090900000001</v>
       </c>
       <c r="H570" t="n">
         <v>105.2694</v>
@@ -29075,7 +29075,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.279999</v>
+        <v>80.910004</v>
       </c>
       <c r="H755" t="n">
-        <v>126.5521</v>
+        <v>125.976</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>126.449997</v>
+        <v>125.800003</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.5632</v>
+        <v>118.9486</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>126.449997</v>
+        <v>125.800003</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.5632</v>
+        <v>118.9486</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>126.449997</v>
+        <v>125.800003</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.5632</v>
+        <v>118.9486</v>
       </c>
     </row>
     <row r="1509">
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>53.494015</v>
+        <v>53.494011</v>
       </c>
       <c r="H1512" t="n">
         <v>100.6414</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>53.377132</v>
+        <v>53.377136</v>
       </c>
       <c r="H1513" t="n">
         <v>100.4215</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.542717</v>
+        <v>53.542721</v>
       </c>
       <c r="H1514" t="n">
         <v>100.733</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.425835</v>
+        <v>53.425831</v>
       </c>
       <c r="H1515" t="n">
         <v>100.5131</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>53.075188</v>
+        <v>53.075184</v>
       </c>
       <c r="H1516" t="n">
         <v>99.85339999999999</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>53.523239</v>
+        <v>53.523243</v>
       </c>
       <c r="H1517" t="n">
         <v>100.6964</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>53.620636</v>
+        <v>53.62064</v>
       </c>
       <c r="H1518" t="n">
         <v>100.8796</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.062218</v>
+        <v>55.062214</v>
       </c>
       <c r="H1522" t="n">
         <v>103.5917</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.974552</v>
+        <v>54.974545</v>
       </c>
       <c r="H1524" t="n">
         <v>103.4268</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.159618</v>
+        <v>55.159615</v>
       </c>
       <c r="H1526" t="n">
         <v>103.775</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>54.429096</v>
+        <v>54.429092</v>
       </c>
       <c r="H1527" t="n">
         <v>102.4006</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.740788</v>
+        <v>54.740784</v>
       </c>
       <c r="H1528" t="n">
         <v>102.987</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>54.53624</v>
+        <v>54.536232</v>
       </c>
       <c r="H1529" t="n">
         <v>102.6022</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>54.818703</v>
+        <v>54.818707</v>
       </c>
       <c r="H1530" t="n">
         <v>103.1336</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1531" t="n">
         <v>103.9582</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>54.682339</v>
+        <v>54.682335</v>
       </c>
       <c r="H1532" t="n">
         <v>102.877</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1533" t="n">
         <v>103.9582</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1538" t="n">
         <v>104.6729</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1541" t="n">
         <v>104.0315</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>54.867409</v>
+        <v>54.867405</v>
       </c>
       <c r="H1545" t="n">
         <v>103.2252</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.584934</v>
+        <v>54.584938</v>
       </c>
       <c r="H1546" t="n">
         <v>102.6938</v>
@@ -59200,10 +59200,10 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1547" t="n">
-        <v>104.1965</v>
+        <v>104.1964</v>
       </c>
     </row>
     <row r="1548">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>56.143391</v>
+        <v>56.143394</v>
       </c>
       <c r="H1550" t="n">
         <v>105.6258</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1553" t="n">
         <v>102.2357</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1555" t="n">
         <v>102.5105</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.419353</v>
+        <v>54.419346</v>
       </c>
       <c r="H1557" t="n">
         <v>102.3823</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1560" t="n">
         <v>104.5446</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1562" t="n">
         <v>104.5446</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1563" t="n">
         <v>104.6729</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.724556</v>
+        <v>55.72456</v>
       </c>
       <c r="H1564" t="n">
         <v>104.8378</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.958328</v>
+        <v>55.958332</v>
       </c>
       <c r="H1565" t="n">
         <v>105.2776</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1567" t="n">
         <v>105.1677</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>55.870663</v>
+        <v>55.870667</v>
       </c>
       <c r="H1569" t="n">
         <v>105.1127</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1571" t="n">
         <v>105.0761</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1572" t="n">
         <v>105.9108</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1573" t="n">
         <v>105.4695</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1574" t="n">
         <v>105.3408</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1576" t="n">
         <v>106.8302</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1582" t="n">
         <v>109.5147</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1583" t="n">
         <v>110.1215</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1584" t="n">
         <v>110.0847</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1586" t="n">
         <v>111.0592</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1587" t="n">
         <v>111.2431</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1589" t="n">
         <v>111.2799</v>
@@ -61062,10 +61062,10 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1596" t="n">
-        <v>110.7467</v>
+        <v>110.7466</v>
       </c>
     </row>
     <row r="1597">
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1598" t="n">
         <v>111.5741</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.168259</v>
+        <v>59.168262</v>
       </c>
       <c r="H1601" t="n">
         <v>111.3167</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.793755</v>
+        <v>59.793758</v>
       </c>
       <c r="H1602" t="n">
         <v>112.4934</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>59.803528</v>
+        <v>59.803532</v>
       </c>
       <c r="H1604" t="n">
         <v>112.5118</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>59.246449</v>
+        <v>59.246445</v>
       </c>
       <c r="H1605" t="n">
         <v>111.4638</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>59.744896</v>
+        <v>59.744892</v>
       </c>
       <c r="H1606" t="n">
         <v>112.4015</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.116276</v>
+        <v>60.11628</v>
       </c>
       <c r="H1608" t="n">
         <v>113.1002</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1610" t="n">
         <v>112.7509</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>60.956795</v>
+        <v>60.956799</v>
       </c>
       <c r="H1614" t="n">
         <v>114.6815</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>60.653816</v>
+        <v>60.65382</v>
       </c>
       <c r="H1615" t="n">
         <v>114.1115</v>
@@ -61860,10 +61860,10 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1617" t="n">
-        <v>114.516</v>
+        <v>114.5161</v>
       </c>
     </row>
     <row r="1618">
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1618" t="n">
         <v>114.7919</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1624" t="n">
         <v>111.7396</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>58.581852</v>
+        <v>58.581856</v>
       </c>
       <c r="H1625" t="n">
         <v>110.2134</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1626" t="n">
         <v>109.2205</v>
@@ -62240,7 +62240,7 @@
         </is>
       </c>
       <c r="G1627" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1627" t="n">
         <v>108.4666</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1629" t="n">
         <v>109.9744</v>
@@ -62354,7 +62354,7 @@
         </is>
       </c>
       <c r="G1630" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1630" t="n">
         <v>109.3308</v>
@@ -62468,7 +62468,7 @@
         </is>
       </c>
       <c r="G1633" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1633" t="n">
         <v>109.9278</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1652" t="n">
         <v>113.1719</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1654" t="n">
         <v>114.9229</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1656" t="n">
         <v>113.0244</v>
@@ -63418,7 +63418,7 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1658" t="n">
         <v>112.7848</v>
@@ -63456,7 +63456,7 @@
         </is>
       </c>
       <c r="G1659" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1659" t="n">
         <v>112.1765</v>
@@ -63570,7 +63570,7 @@
         </is>
       </c>
       <c r="G1662" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1662" t="n">
         <v>110.9047</v>
@@ -63684,7 +63684,7 @@
         </is>
       </c>
       <c r="G1665" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1665" t="n">
         <v>112.3793</v>
@@ -63722,7 +63722,7 @@
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1666" t="n">
         <v>114.8676</v>
@@ -63798,7 +63798,7 @@
         </is>
       </c>
       <c r="G1668" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1668" t="n">
         <v>112.9875</v>
@@ -63874,10 +63874,10 @@
         </is>
       </c>
       <c r="G1670" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1670" t="n">
-        <v>111.9554</v>
+        <v>111.9553</v>
       </c>
     </row>
     <row r="1671">
@@ -64254,7 +64254,7 @@
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1680" t="n">
         <v>116.4159</v>
@@ -64330,7 +64330,7 @@
         </is>
       </c>
       <c r="G1682" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1682" t="n">
         <v>115.9182</v>
@@ -64444,7 +64444,7 @@
         </is>
       </c>
       <c r="G1685" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1685" t="n">
         <v>116.0472</v>
@@ -64520,7 +64520,7 @@
         </is>
       </c>
       <c r="G1687" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1687" t="n">
         <v>115.9182</v>
@@ -64558,7 +64558,7 @@
         </is>
       </c>
       <c r="G1688" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1688" t="n">
         <v>115.4574</v>
@@ -64710,7 +64710,7 @@
         </is>
       </c>
       <c r="G1692" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1692" t="n">
         <v>115.31</v>
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.040001</v>
+        <v>62.740002</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.6008</v>
+        <v>118.0364</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.34</v>
+        <v>35.380001</v>
       </c>
       <c r="H253" t="n">
-        <v>118.0558</v>
+        <v>118.1894</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.645</v>
+        <v>47.73</v>
       </c>
       <c r="H504" t="n">
-        <v>130</v>
+        <v>130.2319</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.489304</v>
+        <v>64.489311</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.70238500000001</v>
+        <v>64.702377</v>
       </c>
       <c r="H508" t="n">
         <v>100.3304</v>
@@ -19759,7 +19759,7 @@
         <v>64.868858</v>
       </c>
       <c r="H509" t="n">
-        <v>100.5886</v>
+        <v>100.5885</v>
       </c>
     </row>
     <row r="510">
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.810097</v>
+        <v>64.810104</v>
       </c>
       <c r="H511" t="n">
         <v>100.4974</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.38678</v>
+        <v>66.386787</v>
       </c>
       <c r="H520" t="n">
         <v>102.9423</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.231201</v>
+        <v>65.23120900000001</v>
       </c>
       <c r="H522" t="n">
         <v>101.1504</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.56416299999999</v>
+        <v>65.564171</v>
       </c>
       <c r="H523" t="n">
         <v>101.6667</v>
@@ -20329,7 +20329,7 @@
         <v>65.476028</v>
       </c>
       <c r="H524" t="n">
-        <v>101.5301</v>
+        <v>101.53</v>
       </c>
     </row>
     <row r="525">
@@ -20440,10 +20440,10 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.48582500000001</v>
+        <v>65.485817</v>
       </c>
       <c r="H527" t="n">
-        <v>101.5453</v>
+        <v>101.5452</v>
       </c>
     </row>
     <row r="528">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.38678</v>
+        <v>66.386787</v>
       </c>
       <c r="H529" t="n">
         <v>102.9423</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.308441</v>
+        <v>66.308426</v>
       </c>
       <c r="H530" t="n">
         <v>102.8208</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H532" t="n">
         <v>103.5497</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.709946</v>
+        <v>66.709953</v>
       </c>
       <c r="H533" t="n">
         <v>103.4434</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H535" t="n">
         <v>103.5497</v>
@@ -20937,7 +20937,7 @@
         <v>66.357399</v>
       </c>
       <c r="H540" t="n">
-        <v>102.8968</v>
+        <v>102.8967</v>
       </c>
     </row>
     <row r="541">
@@ -20975,7 +20975,7 @@
         <v>65.946091</v>
       </c>
       <c r="H541" t="n">
-        <v>102.259</v>
+        <v>102.2589</v>
       </c>
     </row>
     <row r="542">
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.73932600000001</v>
+        <v>66.739334</v>
       </c>
       <c r="H542" t="n">
         <v>103.489</v>
@@ -21127,7 +21127,7 @@
         <v>67.434631</v>
       </c>
       <c r="H545" t="n">
-        <v>104.5672</v>
+        <v>104.5671</v>
       </c>
     </row>
     <row r="546">
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.788284</v>
+        <v>66.788292</v>
       </c>
       <c r="H547" t="n">
         <v>103.5649</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.12236799999999</v>
+        <v>66.12236</v>
       </c>
       <c r="H548" t="n">
         <v>102.5323</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.25947600000001</v>
+        <v>66.259468</v>
       </c>
       <c r="H551" t="n">
         <v>102.7449</v>
@@ -21390,10 +21390,10 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.494507</v>
+        <v>66.494499</v>
       </c>
       <c r="H552" t="n">
-        <v>103.1094</v>
+        <v>103.1093</v>
       </c>
     </row>
     <row r="553">
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.37587000000001</v>
+        <v>67.375877</v>
       </c>
       <c r="H554" t="n">
         <v>104.476</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.62069700000001</v>
+        <v>67.620705</v>
       </c>
       <c r="H556" t="n">
         <v>104.8557</v>
@@ -21583,7 +21583,7 @@
         <v>67.434631</v>
       </c>
       <c r="H557" t="n">
-        <v>104.5672</v>
+        <v>104.5671</v>
       </c>
     </row>
     <row r="558">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.248566</v>
+        <v>67.248558</v>
       </c>
       <c r="H558" t="n">
         <v>104.2786</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.659859</v>
+        <v>67.65986599999999</v>
       </c>
       <c r="H562" t="n">
         <v>104.9164</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.601112</v>
+        <v>67.601105</v>
       </c>
       <c r="H564" t="n">
         <v>104.8253</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.855728</v>
+        <v>67.85573599999999</v>
       </c>
       <c r="H565" t="n">
         <v>105.2201</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.76758599999999</v>
+        <v>67.76759300000001</v>
       </c>
       <c r="H566" t="n">
         <v>105.0835</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>68.149513</v>
+        <v>68.14952099999999</v>
       </c>
       <c r="H567" t="n">
         <v>105.6757</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.610901</v>
+        <v>67.61090900000001</v>
       </c>
       <c r="H569" t="n">
         <v>104.8405</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.997215</v>
+        <v>67.99722300000001</v>
       </c>
       <c r="H570" t="n">
         <v>105.4395</v>
@@ -22112,10 +22112,10 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.27299499999999</v>
+        <v>68.272987</v>
       </c>
       <c r="H571" t="n">
-        <v>105.8672</v>
+        <v>105.8671</v>
       </c>
     </row>
     <row r="572">
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>68.903328</v>
+        <v>68.90331999999999</v>
       </c>
       <c r="H576" t="n">
         <v>106.8446</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>69.632141</v>
+        <v>69.632149</v>
       </c>
       <c r="H577" t="n">
         <v>107.9747</v>
@@ -22419,7 +22419,7 @@
         <v>69.868523</v>
       </c>
       <c r="H579" t="n">
-        <v>108.3413</v>
+        <v>108.3412</v>
       </c>
     </row>
     <row r="580">
@@ -22457,7 +22457,7 @@
         <v>70.085205</v>
       </c>
       <c r="H580" t="n">
-        <v>108.6773</v>
+        <v>108.6772</v>
       </c>
     </row>
     <row r="581">
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.66629</v>
+        <v>70.66628300000001</v>
       </c>
       <c r="H583" t="n">
         <v>109.5783</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>71.690575</v>
+        <v>71.69058200000001</v>
       </c>
       <c r="H586" t="n">
         <v>111.1666</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.459457</v>
+        <v>70.45946499999999</v>
       </c>
       <c r="H588" t="n">
         <v>109.2576</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>70.804176</v>
+        <v>70.804169</v>
       </c>
       <c r="H593" t="n">
         <v>109.7921</v>
@@ -23065,7 +23065,7 @@
         <v>71.28677399999999</v>
       </c>
       <c r="H596" t="n">
-        <v>110.5405</v>
+        <v>110.5404</v>
       </c>
     </row>
     <row r="597">
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>72.084541</v>
+        <v>72.084534</v>
       </c>
       <c r="H597" t="n">
         <v>111.7775</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.286118</v>
+        <v>73.28610999999999</v>
       </c>
       <c r="H599" t="n">
         <v>113.6407</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>72.754265</v>
+        <v>72.754272</v>
       </c>
       <c r="H600" t="n">
         <v>112.816</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.71946699999999</v>
+        <v>73.71946</v>
       </c>
       <c r="H602" t="n">
         <v>114.3127</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>74.536934</v>
+        <v>74.53692599999999</v>
       </c>
       <c r="H604" t="n">
         <v>115.5803</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.241455</v>
+        <v>74.241463</v>
       </c>
       <c r="H606" t="n">
         <v>115.1221</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.300552</v>
+        <v>74.30056</v>
       </c>
       <c r="H607" t="n">
         <v>115.2138</v>
@@ -23673,7 +23673,7 @@
         <v>74.940735</v>
       </c>
       <c r="H612" t="n">
-        <v>116.2065</v>
+        <v>116.2064</v>
       </c>
     </row>
     <row r="613">
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>75.699112</v>
+        <v>75.69910400000001</v>
       </c>
       <c r="H615" t="n">
         <v>117.3824</v>
@@ -23825,7 +23825,7 @@
         <v>75.580917</v>
       </c>
       <c r="H616" t="n">
-        <v>117.1992</v>
+        <v>117.1991</v>
       </c>
     </row>
     <row r="617">
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>73.76870700000001</v>
+        <v>73.768715</v>
       </c>
       <c r="H618" t="n">
         <v>114.3891</v>
@@ -23939,7 +23939,7 @@
         <v>74.271011</v>
       </c>
       <c r="H619" t="n">
-        <v>115.168</v>
+        <v>115.1679</v>
       </c>
     </row>
     <row r="620">
@@ -23977,7 +23977,7 @@
         <v>73.52248400000001</v>
       </c>
       <c r="H620" t="n">
-        <v>114.0073</v>
+        <v>114.0072</v>
       </c>
     </row>
     <row r="621">
@@ -24088,10 +24088,10 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>73.12853200000001</v>
+        <v>73.128525</v>
       </c>
       <c r="H623" t="n">
-        <v>113.3964</v>
+        <v>113.3963</v>
       </c>
     </row>
     <row r="624">
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>72.842911</v>
+        <v>72.84290300000001</v>
       </c>
       <c r="H624" t="n">
         <v>112.9535</v>
@@ -24243,7 +24243,7 @@
         <v>73.52248400000001</v>
       </c>
       <c r="H627" t="n">
-        <v>114.0073</v>
+        <v>114.0072</v>
       </c>
     </row>
     <row r="628">
@@ -24319,7 +24319,7 @@
         <v>71.91392500000001</v>
       </c>
       <c r="H629" t="n">
-        <v>111.513</v>
+        <v>111.5129</v>
       </c>
     </row>
     <row r="630">
@@ -24357,7 +24357,7 @@
         <v>71.25071699999999</v>
       </c>
       <c r="H630" t="n">
-        <v>110.4846</v>
+        <v>110.4845</v>
       </c>
     </row>
     <row r="631">
@@ -24471,7 +24471,7 @@
         <v>72.557343</v>
       </c>
       <c r="H633" t="n">
-        <v>112.5107</v>
+        <v>112.5106</v>
       </c>
     </row>
     <row r="634">
@@ -24585,7 +24585,7 @@
         <v>72.45835099999999</v>
       </c>
       <c r="H636" t="n">
-        <v>112.3572</v>
+        <v>112.3571</v>
       </c>
     </row>
     <row r="637">
@@ -24927,7 +24927,7 @@
         <v>74.24012</v>
       </c>
       <c r="H645" t="n">
-        <v>115.1201</v>
+        <v>115.12</v>
       </c>
     </row>
     <row r="646">
@@ -24965,7 +24965,7 @@
         <v>73.962952</v>
       </c>
       <c r="H646" t="n">
-        <v>114.6903</v>
+        <v>114.6902</v>
       </c>
     </row>
     <row r="647">
@@ -25003,7 +25003,7 @@
         <v>74.220322</v>
       </c>
       <c r="H647" t="n">
-        <v>115.0894</v>
+        <v>115.0893</v>
       </c>
     </row>
     <row r="648">
@@ -25041,7 +25041,7 @@
         <v>74.824135</v>
       </c>
       <c r="H648" t="n">
-        <v>116.0257</v>
+        <v>116.0256</v>
       </c>
     </row>
     <row r="649">
@@ -25079,7 +25079,7 @@
         <v>74.74494900000001</v>
       </c>
       <c r="H649" t="n">
-        <v>115.9029</v>
+        <v>115.9028</v>
       </c>
     </row>
     <row r="650">
@@ -25155,7 +25155,7 @@
         <v>74.24012</v>
       </c>
       <c r="H651" t="n">
-        <v>115.1201</v>
+        <v>115.12</v>
       </c>
     </row>
     <row r="652">
@@ -25231,7 +25231,7 @@
         <v>74.002548</v>
       </c>
       <c r="H653" t="n">
-        <v>114.7517</v>
+        <v>114.7516</v>
       </c>
     </row>
     <row r="654">
@@ -25269,7 +25269,7 @@
         <v>73.943153</v>
       </c>
       <c r="H654" t="n">
-        <v>114.6596</v>
+        <v>114.6595</v>
       </c>
     </row>
     <row r="655">
@@ -25307,7 +25307,7 @@
         <v>74.200523</v>
       </c>
       <c r="H655" t="n">
-        <v>115.0587</v>
+        <v>115.0586</v>
       </c>
     </row>
     <row r="656">
@@ -25383,7 +25383,7 @@
         <v>74.843941</v>
       </c>
       <c r="H657" t="n">
-        <v>116.0564</v>
+        <v>116.0563</v>
       </c>
     </row>
     <row r="658">
@@ -25459,7 +25459,7 @@
         <v>74.824135</v>
       </c>
       <c r="H659" t="n">
-        <v>116.0257</v>
+        <v>116.0256</v>
       </c>
     </row>
     <row r="660">
@@ -25687,7 +25687,7 @@
         <v>75.42795599999999</v>
       </c>
       <c r="H665" t="n">
-        <v>116.962</v>
+        <v>116.9619</v>
       </c>
     </row>
     <row r="666">
@@ -25763,7 +25763,7 @@
         <v>75.467552</v>
       </c>
       <c r="H667" t="n">
-        <v>117.0234</v>
+        <v>117.0233</v>
       </c>
     </row>
     <row r="668">
@@ -25877,7 +25877,7 @@
         <v>76.170357</v>
       </c>
       <c r="H670" t="n">
-        <v>118.1132</v>
+        <v>118.1131</v>
       </c>
     </row>
     <row r="671">
@@ -26029,7 +26029,7 @@
         <v>77.17012800000001</v>
       </c>
       <c r="H674" t="n">
-        <v>119.6635</v>
+        <v>119.6634</v>
       </c>
     </row>
     <row r="675">
@@ -26257,7 +26257,7 @@
         <v>77.17012800000001</v>
       </c>
       <c r="H680" t="n">
-        <v>119.6635</v>
+        <v>119.6634</v>
       </c>
     </row>
     <row r="681">
@@ -26485,7 +26485,7 @@
         <v>77.15033</v>
       </c>
       <c r="H686" t="n">
-        <v>119.6328</v>
+        <v>119.6327</v>
       </c>
     </row>
     <row r="687">
@@ -26979,7 +26979,7 @@
         <v>78.56999999999999</v>
       </c>
       <c r="H699" t="n">
-        <v>121.8342</v>
+        <v>121.8341</v>
       </c>
     </row>
     <row r="700">
@@ -27017,7 +27017,7 @@
         <v>78.889999</v>
       </c>
       <c r="H700" t="n">
-        <v>122.3304</v>
+        <v>122.3303</v>
       </c>
     </row>
     <row r="701">
@@ -27131,7 +27131,7 @@
         <v>79.970001</v>
       </c>
       <c r="H703" t="n">
-        <v>124.0051</v>
+        <v>124.005</v>
       </c>
     </row>
     <row r="704">
@@ -27321,7 +27321,7 @@
         <v>79.970001</v>
       </c>
       <c r="H708" t="n">
-        <v>124.0051</v>
+        <v>124.005</v>
       </c>
     </row>
     <row r="709">
@@ -27739,7 +27739,7 @@
         <v>81.519997</v>
       </c>
       <c r="H719" t="n">
-        <v>126.4086</v>
+        <v>126.4085</v>
       </c>
     </row>
     <row r="720">
@@ -27891,7 +27891,7 @@
         <v>80.739998</v>
       </c>
       <c r="H723" t="n">
-        <v>125.1991</v>
+        <v>125.199</v>
       </c>
     </row>
     <row r="724">
@@ -27929,7 +27929,7 @@
         <v>81.19000200000001</v>
       </c>
       <c r="H724" t="n">
-        <v>125.8969</v>
+        <v>125.8968</v>
       </c>
     </row>
     <row r="725">
@@ -28423,7 +28423,7 @@
         <v>81.209999</v>
       </c>
       <c r="H737" t="n">
-        <v>125.9279</v>
+        <v>125.9278</v>
       </c>
     </row>
     <row r="738">
@@ -28461,7 +28461,7 @@
         <v>81.209999</v>
       </c>
       <c r="H738" t="n">
-        <v>125.9279</v>
+        <v>125.9278</v>
       </c>
     </row>
     <row r="739">
@@ -28537,7 +28537,7 @@
         <v>81.660004</v>
       </c>
       <c r="H740" t="n">
-        <v>126.6257</v>
+        <v>126.6256</v>
       </c>
     </row>
     <row r="741">
@@ -28613,7 +28613,7 @@
         <v>81.66999800000001</v>
       </c>
       <c r="H742" t="n">
-        <v>126.6412</v>
+        <v>126.6411</v>
       </c>
     </row>
     <row r="743">
@@ -28765,7 +28765,7 @@
         <v>82.290001</v>
       </c>
       <c r="H746" t="n">
-        <v>127.6026</v>
+        <v>127.6025</v>
       </c>
     </row>
     <row r="747">
@@ -28841,7 +28841,7 @@
         <v>81.81999999999999</v>
       </c>
       <c r="H748" t="n">
-        <v>126.8738</v>
+        <v>126.8737</v>
       </c>
     </row>
     <row r="749">
@@ -28917,7 +28917,7 @@
         <v>81.040001</v>
       </c>
       <c r="H750" t="n">
-        <v>125.6643</v>
+        <v>125.6642</v>
       </c>
     </row>
     <row r="751">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.110001</v>
+        <v>80.989998</v>
       </c>
       <c r="H755" t="n">
-        <v>125.7728</v>
+        <v>125.5867</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>127.489998</v>
+        <v>127.220001</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.6378</v>
+        <v>120.3823</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>127.489998</v>
+        <v>127.220001</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.6378</v>
+        <v>120.3823</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>127.489998</v>
+        <v>127.220001</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.6378</v>
+        <v>120.3823</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.562202</v>
+        <v>53.562199</v>
       </c>
       <c r="H1510" t="n">
         <v>100.7881</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>53.542717</v>
+        <v>53.542721</v>
       </c>
       <c r="H1513" t="n">
         <v>100.7515</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>53.620636</v>
+        <v>53.62064</v>
       </c>
       <c r="H1517" t="n">
         <v>100.8981</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1524" t="n">
         <v>104.2522</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>54.429096</v>
+        <v>54.429092</v>
       </c>
       <c r="H1526" t="n">
         <v>102.4194</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>54.740788</v>
+        <v>54.740784</v>
       </c>
       <c r="H1527" t="n">
         <v>103.0059</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.53624</v>
+        <v>54.536236</v>
       </c>
       <c r="H1528" t="n">
         <v>102.621</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.682339</v>
+        <v>54.682343</v>
       </c>
       <c r="H1531" t="n">
         <v>102.8959</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1533" t="n">
         <v>104.2522</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1536" t="n">
         <v>104.912</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.588192</v>
+        <v>55.588188</v>
       </c>
       <c r="H1538" t="n">
         <v>104.6004</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1540" t="n">
         <v>104.0506</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>56.104431</v>
+        <v>56.104427</v>
       </c>
       <c r="H1547" t="n">
         <v>105.5718</v>
@@ -59276,10 +59276,10 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>56.143391</v>
+        <v>56.143387</v>
       </c>
       <c r="H1549" t="n">
-        <v>105.6452</v>
+        <v>105.6451</v>
       </c>
     </row>
     <row r="1550">
@@ -59428,10 +59428,10 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1553" t="n">
-        <v>102.1627</v>
+        <v>102.1628</v>
       </c>
     </row>
     <row r="1554">
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1554" t="n">
         <v>102.5293</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.877148</v>
+        <v>54.877144</v>
       </c>
       <c r="H1557" t="n">
         <v>103.2625</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1560" t="n">
         <v>104.912</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.987545</v>
+        <v>55.987549</v>
       </c>
       <c r="H1565" t="n">
         <v>105.3519</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>55.870663</v>
+        <v>55.870659</v>
       </c>
       <c r="H1568" t="n">
         <v>105.132</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1570" t="n">
         <v>105.0953</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1571" t="n">
         <v>105.9302</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1572" t="n">
         <v>105.4888</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1573" t="n">
         <v>105.3601</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1575" t="n">
         <v>106.8497</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1581" t="n">
         <v>109.5348</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1582" t="n">
         <v>110.1417</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1583" t="n">
         <v>110.1049</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1585" t="n">
         <v>111.0796</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1586" t="n">
         <v>111.2635</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1588" t="n">
         <v>111.3003</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1595" t="n">
         <v>110.7669</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1597" t="n">
         <v>111.5945</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.168259</v>
+        <v>59.168262</v>
       </c>
       <c r="H1600" t="n">
         <v>111.3371</v>
@@ -61252,10 +61252,10 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.793755</v>
+        <v>59.793758</v>
       </c>
       <c r="H1601" t="n">
-        <v>112.514</v>
+        <v>112.5141</v>
       </c>
     </row>
     <row r="1602">
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>59.803528</v>
+        <v>59.803532</v>
       </c>
       <c r="H1603" t="n">
         <v>112.5324</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>59.246449</v>
+        <v>59.246445</v>
       </c>
       <c r="H1604" t="n">
         <v>111.4842</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>59.744896</v>
+        <v>59.744892</v>
       </c>
       <c r="H1605" t="n">
         <v>112.4221</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.116276</v>
+        <v>60.11628</v>
       </c>
       <c r="H1607" t="n">
         <v>113.1209</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1609" t="n">
         <v>112.7715</v>
@@ -61708,10 +61708,10 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.956795</v>
+        <v>60.956799</v>
       </c>
       <c r="H1613" t="n">
-        <v>114.7025</v>
+        <v>114.7026</v>
       </c>
     </row>
     <row r="1614">
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>60.653816</v>
+        <v>60.65382</v>
       </c>
       <c r="H1614" t="n">
         <v>114.1324</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1616" t="n">
         <v>114.537</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1617" t="n">
         <v>114.8129</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1623" t="n">
         <v>111.76</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.581852</v>
+        <v>58.581856</v>
       </c>
       <c r="H1624" t="n">
         <v>110.2336</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1625" t="n">
         <v>109.2405</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1626" t="n">
         <v>108.4865</v>
@@ -62278,7 +62278,7 @@
         </is>
       </c>
       <c r="G1628" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1628" t="n">
         <v>109.9945</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1629" t="n">
         <v>109.3509</v>
@@ -62430,7 +62430,7 @@
         </is>
       </c>
       <c r="G1632" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1632" t="n">
         <v>109.948</v>
@@ -63152,7 +63152,7 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1651" t="n">
         <v>113.1926</v>
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1653" t="n">
         <v>114.9439</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1655" t="n">
         <v>113.0451</v>
@@ -63380,7 +63380,7 @@
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1657" t="n">
         <v>112.8054</v>
@@ -63418,7 +63418,7 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1658" t="n">
         <v>112.1971</v>
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1661" t="n">
         <v>110.925</v>
@@ -63646,7 +63646,7 @@
         </is>
       </c>
       <c r="G1664" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1664" t="n">
         <v>112.3999</v>
@@ -63684,7 +63684,7 @@
         </is>
       </c>
       <c r="G1665" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1665" t="n">
         <v>114.8886</v>
@@ -63760,7 +63760,7 @@
         </is>
       </c>
       <c r="G1667" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1667" t="n">
         <v>113.0082</v>
@@ -63836,7 +63836,7 @@
         </is>
       </c>
       <c r="G1669" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1669" t="n">
         <v>111.9759</v>
@@ -64216,7 +64216,7 @@
         </is>
       </c>
       <c r="G1679" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1679" t="n">
         <v>116.4372</v>
@@ -64292,7 +64292,7 @@
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1681" t="n">
         <v>115.9394</v>
@@ -64406,7 +64406,7 @@
         </is>
       </c>
       <c r="G1684" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1684" t="n">
         <v>116.0685</v>
@@ -64482,7 +64482,7 @@
         </is>
       </c>
       <c r="G1686" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1686" t="n">
         <v>115.9394</v>
@@ -64520,7 +64520,7 @@
         </is>
       </c>
       <c r="G1687" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1687" t="n">
         <v>115.4786</v>
@@ -64672,7 +64672,7 @@
         </is>
       </c>
       <c r="G1691" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1691" t="n">
         <v>115.3311</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.57</v>
+        <v>63.610001</v>
       </c>
       <c r="H1760" t="n">
-        <v>119.6198</v>
+        <v>119.6951</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.380001</v>
+        <v>35.389999</v>
       </c>
       <c r="H253" t="n">
-        <v>118.1894</v>
+        <v>118.2228</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.73</v>
+        <v>47.799999</v>
       </c>
       <c r="H504" t="n">
-        <v>130.2319</v>
+        <v>130.4229</v>
       </c>
     </row>
     <row r="505">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.103897</v>
+        <v>65.103905</v>
       </c>
       <c r="H512" t="n">
         <v>100.953</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H516" t="n">
         <v>101.606</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.386787</v>
+        <v>66.38678</v>
       </c>
       <c r="H520" t="n">
         <v>102.9423</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.564171</v>
+        <v>65.56416299999999</v>
       </c>
       <c r="H523" t="n">
         <v>101.6667</v>
@@ -20326,10 +20326,10 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.476028</v>
+        <v>65.47603599999999</v>
       </c>
       <c r="H524" t="n">
-        <v>101.53</v>
+        <v>101.5301</v>
       </c>
     </row>
     <row r="525">
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.926506</v>
+        <v>65.926498</v>
       </c>
       <c r="H526" t="n">
         <v>102.2286</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.485817</v>
+        <v>65.48582500000001</v>
       </c>
       <c r="H527" t="n">
         <v>101.5452</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.210503</v>
+        <v>66.21051</v>
       </c>
       <c r="H528" t="n">
         <v>102.669</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.386787</v>
+        <v>66.38678</v>
       </c>
       <c r="H529" t="n">
         <v>102.9423</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.308426</v>
+        <v>66.308441</v>
       </c>
       <c r="H530" t="n">
         <v>102.8208</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H532" t="n">
         <v>103.5497</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.709953</v>
+        <v>66.709946</v>
       </c>
       <c r="H533" t="n">
         <v>103.4434</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H535" t="n">
         <v>103.5497</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>67.943871</v>
+        <v>67.94386299999999</v>
       </c>
       <c r="H544" t="n">
         <v>105.3568</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.15063499999999</v>
+        <v>67.150627</v>
       </c>
       <c r="H546" t="n">
         <v>104.1268</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.788292</v>
+        <v>66.788284</v>
       </c>
       <c r="H547" t="n">
         <v>103.5649</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.396568</v>
+        <v>66.396576</v>
       </c>
       <c r="H550" t="n">
         <v>102.9575</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.259468</v>
+        <v>66.25947600000001</v>
       </c>
       <c r="H551" t="n">
         <v>102.7449</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.494499</v>
+        <v>66.494507</v>
       </c>
       <c r="H552" t="n">
         <v>103.1093</v>
@@ -21428,10 +21428,10 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.75891900000001</v>
+        <v>66.758911</v>
       </c>
       <c r="H553" t="n">
-        <v>103.5194</v>
+        <v>103.5193</v>
       </c>
     </row>
     <row r="554">
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.375877</v>
+        <v>67.37587000000001</v>
       </c>
       <c r="H554" t="n">
         <v>104.476</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.620705</v>
+        <v>67.62069700000001</v>
       </c>
       <c r="H556" t="n">
         <v>104.8557</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.248558</v>
+        <v>67.248566</v>
       </c>
       <c r="H558" t="n">
         <v>104.2786</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.748009</v>
+        <v>67.748001</v>
       </c>
       <c r="H560" t="n">
         <v>105.0531</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.89490499999999</v>
+        <v>67.894897</v>
       </c>
       <c r="H561" t="n">
         <v>105.2809</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.65986599999999</v>
+        <v>67.659859</v>
       </c>
       <c r="H562" t="n">
         <v>104.9164</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.601105</v>
+        <v>67.601112</v>
       </c>
       <c r="H564" t="n">
         <v>104.8253</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.85573599999999</v>
+        <v>67.855728</v>
       </c>
       <c r="H565" t="n">
         <v>105.2201</v>
@@ -21922,10 +21922,10 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.76759300000001</v>
+        <v>67.76758599999999</v>
       </c>
       <c r="H566" t="n">
-        <v>105.0835</v>
+        <v>105.0834</v>
       </c>
     </row>
     <row r="567">
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>68.14952099999999</v>
+        <v>68.149513</v>
       </c>
       <c r="H567" t="n">
         <v>105.6757</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H568" t="n">
         <v>104.7342</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.61090900000001</v>
+        <v>67.610901</v>
       </c>
       <c r="H569" t="n">
         <v>104.8405</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.99722300000001</v>
+        <v>67.997215</v>
       </c>
       <c r="H570" t="n">
         <v>105.4395</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.272987</v>
+        <v>68.27299499999999</v>
       </c>
       <c r="H571" t="n">
         <v>105.8671</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>68.90331999999999</v>
+        <v>68.903328</v>
       </c>
       <c r="H576" t="n">
         <v>106.8446</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>69.632149</v>
+        <v>69.632141</v>
       </c>
       <c r="H577" t="n">
         <v>107.9747</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.66628300000001</v>
+        <v>70.66629</v>
       </c>
       <c r="H583" t="n">
         <v>109.5783</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>71.69058200000001</v>
+        <v>71.690575</v>
       </c>
       <c r="H586" t="n">
         <v>111.1666</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.45946499999999</v>
+        <v>70.459457</v>
       </c>
       <c r="H588" t="n">
         <v>109.2576</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>70.804169</v>
+        <v>70.804176</v>
       </c>
       <c r="H593" t="n">
         <v>109.7921</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>72.084534</v>
+        <v>72.084541</v>
       </c>
       <c r="H597" t="n">
         <v>111.7775</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.28610999999999</v>
+        <v>73.286118</v>
       </c>
       <c r="H599" t="n">
         <v>113.6407</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>72.754272</v>
+        <v>72.754265</v>
       </c>
       <c r="H600" t="n">
         <v>112.816</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.71946</v>
+        <v>73.71946699999999</v>
       </c>
       <c r="H602" t="n">
         <v>114.3127</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>74.53692599999999</v>
+        <v>74.536934</v>
       </c>
       <c r="H604" t="n">
         <v>115.5803</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.241463</v>
+        <v>74.241455</v>
       </c>
       <c r="H606" t="n">
         <v>115.1221</v>
@@ -23480,10 +23480,10 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.30056</v>
+        <v>74.300552</v>
       </c>
       <c r="H607" t="n">
-        <v>115.2138</v>
+        <v>115.2137</v>
       </c>
     </row>
     <row r="608">
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>75.69910400000001</v>
+        <v>75.699112</v>
       </c>
       <c r="H615" t="n">
         <v>117.3824</v>
@@ -23898,10 +23898,10 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>73.768715</v>
+        <v>73.76870700000001</v>
       </c>
       <c r="H618" t="n">
-        <v>114.3891</v>
+        <v>114.389</v>
       </c>
     </row>
     <row r="619">
@@ -24088,10 +24088,10 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>73.128525</v>
+        <v>73.12853200000001</v>
       </c>
       <c r="H623" t="n">
-        <v>113.3963</v>
+        <v>113.3964</v>
       </c>
     </row>
     <row r="624">
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>72.84290300000001</v>
+        <v>72.842911</v>
       </c>
       <c r="H624" t="n">
         <v>112.9535</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.989998</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="H755" t="n">
-        <v>125.5867</v>
+        <v>125.7108</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>127.220001</v>
+        <v>127.410004</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.3823</v>
+        <v>120.5621</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>127.220001</v>
+        <v>127.410004</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.3823</v>
+        <v>120.5621</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>127.220001</v>
+        <v>127.410004</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.3823</v>
+        <v>120.5621</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.562199</v>
+        <v>53.562202</v>
       </c>
       <c r="H1510" t="n">
         <v>100.7881</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.494015</v>
+        <v>53.494011</v>
       </c>
       <c r="H1511" t="n">
         <v>100.6598</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.425835</v>
+        <v>53.425831</v>
       </c>
       <c r="H1514" t="n">
         <v>100.5315</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.075188</v>
+        <v>53.075184</v>
       </c>
       <c r="H1515" t="n">
         <v>99.8717</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.799221</v>
+        <v>54.799225</v>
       </c>
       <c r="H1520" t="n">
         <v>103.1158</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.062218</v>
+        <v>55.062214</v>
       </c>
       <c r="H1521" t="n">
         <v>103.6107</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.974552</v>
+        <v>54.974548</v>
       </c>
       <c r="H1523" t="n">
         <v>103.4457</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1524" t="n">
         <v>104.2522</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>54.818703</v>
+        <v>54.818707</v>
       </c>
       <c r="H1529" t="n">
         <v>103.1525</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1530" t="n">
         <v>103.9773</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.682343</v>
+        <v>54.682335</v>
       </c>
       <c r="H1531" t="n">
         <v>102.8959</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1532" t="n">
         <v>103.9773</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1533" t="n">
         <v>104.2522</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1534" t="n">
         <v>104.0139</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1543" t="n">
         <v>104.0139</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1546" t="n">
         <v>104.2155</v>
@@ -59276,10 +59276,10 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>56.143387</v>
+        <v>56.143394</v>
       </c>
       <c r="H1549" t="n">
-        <v>105.6451</v>
+        <v>105.6452</v>
       </c>
     </row>
     <row r="1550">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.607674</v>
+        <v>55.607677</v>
       </c>
       <c r="H1550" t="n">
         <v>104.6371</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1552" t="n">
         <v>102.2544</v>
@@ -59428,10 +59428,10 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1553" t="n">
-        <v>102.1628</v>
+        <v>102.1627</v>
       </c>
     </row>
     <row r="1554">
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.487534</v>
+        <v>54.48753</v>
       </c>
       <c r="H1554" t="n">
         <v>102.5293</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1556" t="n">
         <v>102.401</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>54.877144</v>
+        <v>54.877148</v>
       </c>
       <c r="H1557" t="n">
         <v>103.2625</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.987549</v>
+        <v>55.987541</v>
       </c>
       <c r="H1565" t="n">
         <v>105.3519</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1566" t="n">
         <v>105.1869</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>55.870659</v>
+        <v>55.870663</v>
       </c>
       <c r="H1568" t="n">
         <v>105.132</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1570" t="n">
         <v>105.0953</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.294872</v>
+        <v>56.294876</v>
       </c>
       <c r="H1571" t="n">
         <v>105.9302</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1573" t="n">
         <v>105.3601</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.558758</v>
+        <v>56.558754</v>
       </c>
       <c r="H1574" t="n">
         <v>106.4267</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>56.676041</v>
+        <v>56.676044</v>
       </c>
       <c r="H1576" t="n">
         <v>106.6474</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1578" t="n">
         <v>107.1992</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>57.692474</v>
+        <v>57.692471</v>
       </c>
       <c r="H1580" t="n">
         <v>108.5601</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1581" t="n">
         <v>109.5348</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.53299</v>
+        <v>58.532986</v>
       </c>
       <c r="H1582" t="n">
         <v>110.1417</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1583" t="n">
         <v>110.1049</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.129169</v>
+        <v>59.129166</v>
       </c>
       <c r="H1586" t="n">
         <v>111.2635</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1588" t="n">
         <v>111.3003</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1589" t="n">
         <v>111.9439</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1590" t="n">
         <v>111.9623</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1592" t="n">
         <v>109.6635</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>58.86528</v>
+        <v>58.865284</v>
       </c>
       <c r="H1595" t="n">
         <v>110.7669</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>58.953243</v>
+        <v>58.953247</v>
       </c>
       <c r="H1596" t="n">
         <v>110.9325</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.305092</v>
+        <v>59.305088</v>
       </c>
       <c r="H1597" t="n">
         <v>111.5945</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1608" t="n">
         <v>113.2865</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1611" t="n">
         <v>112.7899</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1612" t="n">
         <v>113.3968</v>
@@ -61708,10 +61708,10 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.956799</v>
+        <v>60.956795</v>
       </c>
       <c r="H1613" t="n">
-        <v>114.7026</v>
+        <v>114.7025</v>
       </c>
     </row>
     <row r="1614">
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1626" t="n">
         <v>108.4865</v>
@@ -62240,7 +62240,7 @@
         </is>
       </c>
       <c r="G1627" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1627" t="n">
         <v>110.6198</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.610001</v>
+        <v>63.59</v>
       </c>
       <c r="H1760" t="n">
-        <v>119.6951</v>
+        <v>119.6575</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.489311</v>
+        <v>64.489304</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.77093499999999</v>
+        <v>64.770927</v>
       </c>
       <c r="H507" t="n">
         <v>100.4367</v>
@@ -19759,7 +19759,7 @@
         <v>64.868858</v>
       </c>
       <c r="H509" t="n">
-        <v>100.5885</v>
+        <v>100.5886</v>
       </c>
     </row>
     <row r="510">
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.810104</v>
+        <v>64.810112</v>
       </c>
       <c r="H511" t="n">
-        <v>100.4974</v>
+        <v>100.4975</v>
       </c>
     </row>
     <row r="512">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.103905</v>
+        <v>65.103897</v>
       </c>
       <c r="H512" t="n">
         <v>100.953</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.02555099999999</v>
+        <v>65.025558</v>
       </c>
       <c r="H514" t="n">
         <v>100.8315</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.47603599999999</v>
+        <v>65.476028</v>
       </c>
       <c r="H524" t="n">
         <v>101.5301</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.926498</v>
+        <v>65.926506</v>
       </c>
       <c r="H526" t="n">
         <v>102.2286</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.48582500000001</v>
+        <v>65.485817</v>
       </c>
       <c r="H527" t="n">
         <v>101.5452</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.21051</v>
+        <v>66.210503</v>
       </c>
       <c r="H528" t="n">
         <v>102.669</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.308441</v>
+        <v>66.30843400000001</v>
       </c>
       <c r="H530" t="n">
         <v>102.8208</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H532" t="n">
         <v>103.5497</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.582634</v>
+        <v>66.58264200000001</v>
       </c>
       <c r="H534" t="n">
         <v>103.246</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H535" t="n">
         <v>103.5497</v>
@@ -20937,7 +20937,7 @@
         <v>66.357399</v>
       </c>
       <c r="H540" t="n">
-        <v>102.8967</v>
+        <v>102.8968</v>
       </c>
     </row>
     <row r="541">
@@ -20975,7 +20975,7 @@
         <v>65.946091</v>
       </c>
       <c r="H541" t="n">
-        <v>102.2589</v>
+        <v>102.259</v>
       </c>
     </row>
     <row r="542">
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>67.94386299999999</v>
+        <v>67.943871</v>
       </c>
       <c r="H544" t="n">
         <v>105.3568</v>
@@ -21127,7 +21127,7 @@
         <v>67.434631</v>
       </c>
       <c r="H545" t="n">
-        <v>104.5671</v>
+        <v>104.5672</v>
       </c>
     </row>
     <row r="546">
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.150627</v>
+        <v>67.15063499999999</v>
       </c>
       <c r="H546" t="n">
         <v>104.1268</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.788284</v>
+        <v>66.788292</v>
       </c>
       <c r="H547" t="n">
         <v>103.5649</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.396576</v>
+        <v>66.396568</v>
       </c>
       <c r="H550" t="n">
         <v>102.9575</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.25947600000001</v>
+        <v>66.259468</v>
       </c>
       <c r="H551" t="n">
         <v>102.7449</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.494507</v>
+        <v>66.494499</v>
       </c>
       <c r="H552" t="n">
         <v>103.1093</v>
@@ -21431,7 +21431,7 @@
         <v>66.758911</v>
       </c>
       <c r="H553" t="n">
-        <v>103.5193</v>
+        <v>103.5194</v>
       </c>
     </row>
     <row r="554">
@@ -21466,10 +21466,10 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.37587000000001</v>
+        <v>67.375877</v>
       </c>
       <c r="H554" t="n">
-        <v>104.476</v>
+        <v>104.4761</v>
       </c>
     </row>
     <row r="555">
@@ -21583,7 +21583,7 @@
         <v>67.434631</v>
       </c>
       <c r="H557" t="n">
-        <v>104.5671</v>
+        <v>104.5672</v>
       </c>
     </row>
     <row r="558">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.248566</v>
+        <v>67.248558</v>
       </c>
       <c r="H558" t="n">
         <v>104.2786</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.748001</v>
+        <v>67.748009</v>
       </c>
       <c r="H560" t="n">
         <v>105.0531</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.894897</v>
+        <v>67.89490499999999</v>
       </c>
       <c r="H561" t="n">
         <v>105.2809</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.659859</v>
+        <v>67.659874</v>
       </c>
       <c r="H562" t="n">
         <v>104.9164</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.669662</v>
+        <v>67.66965500000001</v>
       </c>
       <c r="H563" t="n">
         <v>104.9316</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.601112</v>
+        <v>67.601105</v>
       </c>
       <c r="H564" t="n">
         <v>104.8253</v>
@@ -21925,7 +21925,7 @@
         <v>67.76758599999999</v>
       </c>
       <c r="H566" t="n">
-        <v>105.0834</v>
+        <v>105.0835</v>
       </c>
     </row>
     <row r="567">
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>68.149513</v>
+        <v>68.14952099999999</v>
       </c>
       <c r="H567" t="n">
         <v>105.6757</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.610901</v>
+        <v>67.61090900000001</v>
       </c>
       <c r="H569" t="n">
         <v>104.8405</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>67.997215</v>
+        <v>67.99722300000001</v>
       </c>
       <c r="H570" t="n">
         <v>105.4395</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.27299499999999</v>
+        <v>68.272987</v>
       </c>
       <c r="H571" t="n">
         <v>105.8671</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>68.903328</v>
+        <v>68.90331999999999</v>
       </c>
       <c r="H576" t="n">
         <v>106.8446</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>69.632141</v>
+        <v>69.632149</v>
       </c>
       <c r="H577" t="n">
         <v>107.9747</v>
@@ -22419,7 +22419,7 @@
         <v>69.868523</v>
       </c>
       <c r="H579" t="n">
-        <v>108.3412</v>
+        <v>108.3413</v>
       </c>
     </row>
     <row r="580">
@@ -22457,7 +22457,7 @@
         <v>70.085205</v>
       </c>
       <c r="H580" t="n">
-        <v>108.6772</v>
+        <v>108.6773</v>
       </c>
     </row>
     <row r="581">
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.66629</v>
+        <v>70.66628300000001</v>
       </c>
       <c r="H583" t="n">
         <v>109.5783</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>71.690575</v>
+        <v>71.69058200000001</v>
       </c>
       <c r="H586" t="n">
         <v>111.1666</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.459457</v>
+        <v>70.45946499999999</v>
       </c>
       <c r="H588" t="n">
         <v>109.2576</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>70.804176</v>
+        <v>70.804169</v>
       </c>
       <c r="H593" t="n">
         <v>109.7921</v>
@@ -23065,7 +23065,7 @@
         <v>71.28677399999999</v>
       </c>
       <c r="H596" t="n">
-        <v>110.5404</v>
+        <v>110.5405</v>
       </c>
     </row>
     <row r="597">
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>72.084541</v>
+        <v>72.084534</v>
       </c>
       <c r="H597" t="n">
         <v>111.7775</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.286118</v>
+        <v>73.28610999999999</v>
       </c>
       <c r="H599" t="n">
         <v>113.6407</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>72.754265</v>
+        <v>72.754272</v>
       </c>
       <c r="H600" t="n">
         <v>112.816</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.71946699999999</v>
+        <v>73.71946</v>
       </c>
       <c r="H602" t="n">
         <v>114.3127</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>74.536934</v>
+        <v>74.53692599999999</v>
       </c>
       <c r="H604" t="n">
         <v>115.5803</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.241455</v>
+        <v>74.241463</v>
       </c>
       <c r="H606" t="n">
         <v>115.1221</v>
@@ -23480,10 +23480,10 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.300552</v>
+        <v>74.30056</v>
       </c>
       <c r="H607" t="n">
-        <v>115.2137</v>
+        <v>115.2138</v>
       </c>
     </row>
     <row r="608">
@@ -23673,7 +23673,7 @@
         <v>74.940735</v>
       </c>
       <c r="H612" t="n">
-        <v>116.2064</v>
+        <v>116.2065</v>
       </c>
     </row>
     <row r="613">
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>75.699112</v>
+        <v>75.69910400000001</v>
       </c>
       <c r="H615" t="n">
         <v>117.3824</v>
@@ -23825,7 +23825,7 @@
         <v>75.580917</v>
       </c>
       <c r="H616" t="n">
-        <v>117.1991</v>
+        <v>117.1992</v>
       </c>
     </row>
     <row r="617">
@@ -23898,10 +23898,10 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>73.76870700000001</v>
+        <v>73.768715</v>
       </c>
       <c r="H618" t="n">
-        <v>114.389</v>
+        <v>114.3891</v>
       </c>
     </row>
     <row r="619">
@@ -23939,7 +23939,7 @@
         <v>74.271011</v>
       </c>
       <c r="H619" t="n">
-        <v>115.1679</v>
+        <v>115.168</v>
       </c>
     </row>
     <row r="620">
@@ -23977,7 +23977,7 @@
         <v>73.52248400000001</v>
       </c>
       <c r="H620" t="n">
-        <v>114.0072</v>
+        <v>114.0073</v>
       </c>
     </row>
     <row r="621">
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>73.12853200000001</v>
+        <v>73.128525</v>
       </c>
       <c r="H623" t="n">
         <v>113.3964</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>72.842911</v>
+        <v>72.84290300000001</v>
       </c>
       <c r="H624" t="n">
         <v>112.9535</v>
@@ -24243,7 +24243,7 @@
         <v>73.52248400000001</v>
       </c>
       <c r="H627" t="n">
-        <v>114.0072</v>
+        <v>114.0073</v>
       </c>
     </row>
     <row r="628">
@@ -24319,7 +24319,7 @@
         <v>71.91392500000001</v>
       </c>
       <c r="H629" t="n">
-        <v>111.5129</v>
+        <v>111.513</v>
       </c>
     </row>
     <row r="630">
@@ -24357,7 +24357,7 @@
         <v>71.25071699999999</v>
       </c>
       <c r="H630" t="n">
-        <v>110.4845</v>
+        <v>110.4846</v>
       </c>
     </row>
     <row r="631">
@@ -24471,7 +24471,7 @@
         <v>72.557343</v>
       </c>
       <c r="H633" t="n">
-        <v>112.5106</v>
+        <v>112.5107</v>
       </c>
     </row>
     <row r="634">
@@ -24585,7 +24585,7 @@
         <v>72.45835099999999</v>
       </c>
       <c r="H636" t="n">
-        <v>112.3571</v>
+        <v>112.3572</v>
       </c>
     </row>
     <row r="637">
@@ -24927,7 +24927,7 @@
         <v>74.24012</v>
       </c>
       <c r="H645" t="n">
-        <v>115.12</v>
+        <v>115.1201</v>
       </c>
     </row>
     <row r="646">
@@ -24965,7 +24965,7 @@
         <v>73.962952</v>
       </c>
       <c r="H646" t="n">
-        <v>114.6902</v>
+        <v>114.6903</v>
       </c>
     </row>
     <row r="647">
@@ -25003,7 +25003,7 @@
         <v>74.220322</v>
       </c>
       <c r="H647" t="n">
-        <v>115.0893</v>
+        <v>115.0894</v>
       </c>
     </row>
     <row r="648">
@@ -25041,7 +25041,7 @@
         <v>74.824135</v>
       </c>
       <c r="H648" t="n">
-        <v>116.0256</v>
+        <v>116.0257</v>
       </c>
     </row>
     <row r="649">
@@ -25079,7 +25079,7 @@
         <v>74.74494900000001</v>
       </c>
       <c r="H649" t="n">
-        <v>115.9028</v>
+        <v>115.9029</v>
       </c>
     </row>
     <row r="650">
@@ -25155,7 +25155,7 @@
         <v>74.24012</v>
       </c>
       <c r="H651" t="n">
-        <v>115.12</v>
+        <v>115.1201</v>
       </c>
     </row>
     <row r="652">
@@ -25231,7 +25231,7 @@
         <v>74.002548</v>
       </c>
       <c r="H653" t="n">
-        <v>114.7516</v>
+        <v>114.7517</v>
       </c>
     </row>
     <row r="654">
@@ -25269,7 +25269,7 @@
         <v>73.943153</v>
       </c>
       <c r="H654" t="n">
-        <v>114.6595</v>
+        <v>114.6596</v>
       </c>
     </row>
     <row r="655">
@@ -25307,7 +25307,7 @@
         <v>74.200523</v>
       </c>
       <c r="H655" t="n">
-        <v>115.0586</v>
+        <v>115.0587</v>
       </c>
     </row>
     <row r="656">
@@ -25383,7 +25383,7 @@
         <v>74.843941</v>
       </c>
       <c r="H657" t="n">
-        <v>116.0563</v>
+        <v>116.0564</v>
       </c>
     </row>
     <row r="658">
@@ -25459,7 +25459,7 @@
         <v>74.824135</v>
       </c>
       <c r="H659" t="n">
-        <v>116.0256</v>
+        <v>116.0257</v>
       </c>
     </row>
     <row r="660">
@@ -25687,7 +25687,7 @@
         <v>75.42795599999999</v>
       </c>
       <c r="H665" t="n">
-        <v>116.9619</v>
+        <v>116.962</v>
       </c>
     </row>
     <row r="666">
@@ -25763,7 +25763,7 @@
         <v>75.467552</v>
       </c>
       <c r="H667" t="n">
-        <v>117.0233</v>
+        <v>117.0234</v>
       </c>
     </row>
     <row r="668">
@@ -25877,7 +25877,7 @@
         <v>76.170357</v>
       </c>
       <c r="H670" t="n">
-        <v>118.1131</v>
+        <v>118.1132</v>
       </c>
     </row>
     <row r="671">
@@ -26029,7 +26029,7 @@
         <v>77.17012800000001</v>
       </c>
       <c r="H674" t="n">
-        <v>119.6634</v>
+        <v>119.6635</v>
       </c>
     </row>
     <row r="675">
@@ -26257,7 +26257,7 @@
         <v>77.17012800000001</v>
       </c>
       <c r="H680" t="n">
-        <v>119.6634</v>
+        <v>119.6635</v>
       </c>
     </row>
     <row r="681">
@@ -26485,7 +26485,7 @@
         <v>77.15033</v>
       </c>
       <c r="H686" t="n">
-        <v>119.6327</v>
+        <v>119.6328</v>
       </c>
     </row>
     <row r="687">
@@ -26979,7 +26979,7 @@
         <v>78.56999999999999</v>
       </c>
       <c r="H699" t="n">
-        <v>121.8341</v>
+        <v>121.8342</v>
       </c>
     </row>
     <row r="700">
@@ -27017,7 +27017,7 @@
         <v>78.889999</v>
       </c>
       <c r="H700" t="n">
-        <v>122.3303</v>
+        <v>122.3304</v>
       </c>
     </row>
     <row r="701">
@@ -27131,7 +27131,7 @@
         <v>79.970001</v>
       </c>
       <c r="H703" t="n">
-        <v>124.005</v>
+        <v>124.0051</v>
       </c>
     </row>
     <row r="704">
@@ -27321,7 +27321,7 @@
         <v>79.970001</v>
       </c>
       <c r="H708" t="n">
-        <v>124.005</v>
+        <v>124.0051</v>
       </c>
     </row>
     <row r="709">
@@ -27739,7 +27739,7 @@
         <v>81.519997</v>
       </c>
       <c r="H719" t="n">
-        <v>126.4085</v>
+        <v>126.4086</v>
       </c>
     </row>
     <row r="720">
@@ -27891,7 +27891,7 @@
         <v>80.739998</v>
       </c>
       <c r="H723" t="n">
-        <v>125.199</v>
+        <v>125.1991</v>
       </c>
     </row>
     <row r="724">
@@ -27929,7 +27929,7 @@
         <v>81.19000200000001</v>
       </c>
       <c r="H724" t="n">
-        <v>125.8968</v>
+        <v>125.8969</v>
       </c>
     </row>
     <row r="725">
@@ -28423,7 +28423,7 @@
         <v>81.209999</v>
       </c>
       <c r="H737" t="n">
-        <v>125.9278</v>
+        <v>125.9279</v>
       </c>
     </row>
     <row r="738">
@@ -28461,7 +28461,7 @@
         <v>81.209999</v>
       </c>
       <c r="H738" t="n">
-        <v>125.9278</v>
+        <v>125.9279</v>
       </c>
     </row>
     <row r="739">
@@ -28537,7 +28537,7 @@
         <v>81.660004</v>
       </c>
       <c r="H740" t="n">
-        <v>126.6256</v>
+        <v>126.6257</v>
       </c>
     </row>
     <row r="741">
@@ -28613,7 +28613,7 @@
         <v>81.66999800000001</v>
       </c>
       <c r="H742" t="n">
-        <v>126.6411</v>
+        <v>126.6412</v>
       </c>
     </row>
     <row r="743">
@@ -28765,7 +28765,7 @@
         <v>82.290001</v>
       </c>
       <c r="H746" t="n">
-        <v>127.6025</v>
+        <v>127.6026</v>
       </c>
     </row>
     <row r="747">
@@ -28841,7 +28841,7 @@
         <v>81.81999999999999</v>
       </c>
       <c r="H748" t="n">
-        <v>126.8737</v>
+        <v>126.8738</v>
       </c>
     </row>
     <row r="749">
@@ -28917,7 +28917,7 @@
         <v>81.040001</v>
       </c>
       <c r="H750" t="n">
-        <v>125.6642</v>
+        <v>125.6643</v>
       </c>
     </row>
     <row r="751">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.562202</v>
+        <v>53.562199</v>
       </c>
       <c r="H1510" t="n">
         <v>100.7881</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.494011</v>
+        <v>53.494015</v>
       </c>
       <c r="H1511" t="n">
         <v>100.6598</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.425831</v>
+        <v>53.425835</v>
       </c>
       <c r="H1514" t="n">
         <v>100.5315</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>53.523239</v>
+        <v>53.523235</v>
       </c>
       <c r="H1516" t="n">
         <v>100.7148</v>
@@ -58136,10 +58136,10 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1519" t="n">
-        <v>102.5476</v>
+        <v>102.5477</v>
       </c>
     </row>
     <row r="1520">
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.974548</v>
+        <v>54.974552</v>
       </c>
       <c r="H1523" t="n">
         <v>103.4457</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.159618</v>
+        <v>55.159622</v>
       </c>
       <c r="H1525" t="n">
         <v>103.794</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>54.740784</v>
+        <v>54.74078</v>
       </c>
       <c r="H1527" t="n">
         <v>103.0059</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.536236</v>
+        <v>54.53624</v>
       </c>
       <c r="H1528" t="n">
         <v>102.621</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1530" t="n">
         <v>103.9773</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1531" t="n">
         <v>102.8959</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1532" t="n">
         <v>103.9773</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.169357</v>
+        <v>55.169353</v>
       </c>
       <c r="H1542" t="n">
         <v>103.8123</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1546" t="n">
         <v>104.2155</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1547" t="n">
         <v>105.5718</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1549" t="n">
         <v>105.6452</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.607677</v>
+        <v>55.607674</v>
       </c>
       <c r="H1550" t="n">
         <v>104.6371</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.305721</v>
+        <v>55.305717</v>
       </c>
       <c r="H1551" t="n">
         <v>104.0689</v>
@@ -59428,10 +59428,10 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1553" t="n">
-        <v>102.1627</v>
+        <v>102.1628</v>
       </c>
     </row>
     <row r="1554">
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.958328</v>
+        <v>55.958324</v>
       </c>
       <c r="H1564" t="n">
         <v>105.2969</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.987541</v>
+        <v>55.987545</v>
       </c>
       <c r="H1565" t="n">
         <v>105.3519</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1566" t="n">
         <v>105.1869</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>55.870663</v>
+        <v>55.870659</v>
       </c>
       <c r="H1568" t="n">
         <v>105.132</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.125</v>
+        <v>34.494999</v>
       </c>
       <c r="H253" t="n">
-        <v>114.3206</v>
+        <v>112.2701</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.830002</v>
+        <v>47.790001</v>
       </c>
       <c r="H504" t="n">
-        <v>130.3625</v>
+        <v>130.2535</v>
       </c>
     </row>
     <row r="505">
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.77093499999999</v>
+        <v>64.770927</v>
       </c>
       <c r="H506" t="n">
         <v>100.1666</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.70238500000001</v>
+        <v>64.702377</v>
       </c>
       <c r="H507" t="n">
         <v>100.0606</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.810097</v>
+        <v>64.810112</v>
       </c>
       <c r="H510" t="n">
         <v>100.2272</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.02555099999999</v>
+        <v>65.025558</v>
       </c>
       <c r="H513" t="n">
         <v>100.5604</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H515" t="n">
         <v>101.3327</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.231201</v>
+        <v>65.23120900000001</v>
       </c>
       <c r="H521" t="n">
         <v>100.8784</v>
@@ -20402,10 +20402,10 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.48582500000001</v>
+        <v>65.485817</v>
       </c>
       <c r="H526" t="n">
-        <v>101.2722</v>
+        <v>101.2721</v>
       </c>
     </row>
     <row r="527">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.308441</v>
+        <v>66.30843400000001</v>
       </c>
       <c r="H529" t="n">
         <v>102.5443</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H531" t="n">
-        <v>103.2713</v>
+        <v>103.2712</v>
       </c>
     </row>
     <row r="532">
@@ -20668,10 +20668,10 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.582634</v>
+        <v>66.58264200000001</v>
       </c>
       <c r="H533" t="n">
-        <v>102.9683</v>
+        <v>102.9684</v>
       </c>
     </row>
     <row r="534">
@@ -20706,10 +20706,10 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.778503</v>
+        <v>66.778496</v>
       </c>
       <c r="H534" t="n">
-        <v>103.2713</v>
+        <v>103.2712</v>
       </c>
     </row>
     <row r="535">
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.73932600000001</v>
+        <v>66.739334</v>
       </c>
       <c r="H541" t="n">
         <v>103.2107</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.788284</v>
+        <v>66.788292</v>
       </c>
       <c r="H546" t="n">
         <v>103.2864</v>
@@ -21200,10 +21200,10 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.12236799999999</v>
+        <v>66.12236</v>
       </c>
       <c r="H547" t="n">
-        <v>102.2566</v>
+        <v>102.2565</v>
       </c>
     </row>
     <row r="548">
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.25947600000001</v>
+        <v>66.259468</v>
       </c>
       <c r="H550" t="n">
         <v>102.4686</v>
@@ -21352,10 +21352,10 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.494507</v>
+        <v>66.494499</v>
       </c>
       <c r="H551" t="n">
-        <v>102.8321</v>
+        <v>102.832</v>
       </c>
     </row>
     <row r="552">
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.75891900000001</v>
+        <v>66.758911</v>
       </c>
       <c r="H552" t="n">
         <v>103.241</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.37587000000001</v>
+        <v>67.375877</v>
       </c>
       <c r="H553" t="n">
         <v>104.1951</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.248566</v>
+        <v>67.248558</v>
       </c>
       <c r="H557" t="n">
         <v>103.9982</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.659859</v>
+        <v>67.659874</v>
       </c>
       <c r="H561" t="n">
-        <v>104.6342</v>
+        <v>104.6343</v>
       </c>
     </row>
     <row r="562">
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.669662</v>
+        <v>67.66965500000001</v>
       </c>
       <c r="H562" t="n">
         <v>104.6494</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.601112</v>
+        <v>67.601105</v>
       </c>
       <c r="H563" t="n">
         <v>104.5434</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.149513</v>
+        <v>68.14952099999999</v>
       </c>
       <c r="H566" t="n">
         <v>105.3915</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H567" t="n">
         <v>104.4525</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.610901</v>
+        <v>67.61090900000001</v>
       </c>
       <c r="H568" t="n">
         <v>104.5585</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.997215</v>
+        <v>67.99722300000001</v>
       </c>
       <c r="H569" t="n">
         <v>105.156</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>68.27299499999999</v>
+        <v>68.272987</v>
       </c>
       <c r="H570" t="n">
         <v>105.5824</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>68.903328</v>
+        <v>68.90331999999999</v>
       </c>
       <c r="H575" t="n">
         <v>106.5572</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>69.632141</v>
+        <v>69.632149</v>
       </c>
       <c r="H576" t="n">
         <v>107.6843</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.66629</v>
+        <v>70.66628300000001</v>
       </c>
       <c r="H582" t="n">
         <v>109.2836</v>
@@ -22644,10 +22644,10 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>71.690575</v>
+        <v>71.69058200000001</v>
       </c>
       <c r="H585" t="n">
-        <v>110.8676</v>
+        <v>110.8677</v>
       </c>
     </row>
     <row r="586">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.459457</v>
+        <v>70.45946499999999</v>
       </c>
       <c r="H587" t="n">
         <v>108.9638</v>
@@ -22910,10 +22910,10 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>70.804176</v>
+        <v>70.804169</v>
       </c>
       <c r="H592" t="n">
-        <v>109.4969</v>
+        <v>109.4968</v>
       </c>
     </row>
     <row r="593">
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>72.084541</v>
+        <v>72.084534</v>
       </c>
       <c r="H596" t="n">
         <v>111.4769</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.286118</v>
+        <v>73.28610999999999</v>
       </c>
       <c r="H598" t="n">
         <v>113.3351</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>72.754265</v>
+        <v>72.754272</v>
       </c>
       <c r="H599" t="n">
         <v>112.5126</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>73.71946699999999</v>
+        <v>73.71946</v>
       </c>
       <c r="H601" t="n">
         <v>114.0053</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>74.536934</v>
+        <v>74.53692599999999</v>
       </c>
       <c r="H603" t="n">
         <v>115.2695</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>74.241455</v>
+        <v>74.241463</v>
       </c>
       <c r="H605" t="n">
         <v>114.8125</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.300552</v>
+        <v>74.30056</v>
       </c>
       <c r="H606" t="n">
         <v>114.9039</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>75.699112</v>
+        <v>75.69910400000001</v>
       </c>
       <c r="H614" t="n">
         <v>117.0667</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>73.76870700000001</v>
+        <v>73.768715</v>
       </c>
       <c r="H617" t="n">
         <v>114.0814</v>
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>73.12853200000001</v>
+        <v>73.128525</v>
       </c>
       <c r="H622" t="n">
         <v>113.0914</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>72.842911</v>
+        <v>72.84290300000001</v>
       </c>
       <c r="H623" t="n">
         <v>112.6497</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.66999800000001</v>
+        <v>80.410004</v>
       </c>
       <c r="H755" t="n">
-        <v>124.7541</v>
+        <v>124.352</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>127.410004</v>
+        <v>127</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.2196</v>
+        <v>118.836</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>127.410004</v>
+        <v>127</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.2196</v>
+        <v>118.836</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>127.410004</v>
+        <v>127</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.2196</v>
+        <v>118.836</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.562199</v>
+        <v>53.562202</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.377132</v>
+        <v>53.377136</v>
       </c>
       <c r="H1511" t="n">
         <v>99.6545</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.523239</v>
+        <v>53.523243</v>
       </c>
       <c r="H1515" t="n">
         <v>99.9273</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.497276</v>
+        <v>54.497272</v>
       </c>
       <c r="H1518" t="n">
         <v>101.7458</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.799225</v>
+        <v>54.799221</v>
       </c>
       <c r="H1519" t="n">
         <v>102.3095</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.042728</v>
+        <v>55.042736</v>
       </c>
       <c r="H1521" t="n">
         <v>102.7641</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.974545</v>
+        <v>54.974548</v>
       </c>
       <c r="H1522" t="n">
         <v>102.6368</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1523" t="n">
         <v>103.437</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.159618</v>
+        <v>55.159615</v>
       </c>
       <c r="H1524" t="n">
-        <v>102.9824</v>
+        <v>102.9823</v>
       </c>
     </row>
     <row r="1525">
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>54.74078</v>
+        <v>54.740788</v>
       </c>
       <c r="H1526" t="n">
         <v>102.2004</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>54.536236</v>
+        <v>54.536232</v>
       </c>
       <c r="H1527" t="n">
         <v>101.8185</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.818699</v>
+        <v>54.818707</v>
       </c>
       <c r="H1528" t="n">
         <v>102.3459</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1529" t="n">
         <v>103.1642</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1531" t="n">
         <v>103.1642</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1532" t="n">
         <v>103.437</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1533" t="n">
         <v>103.2006</v>
@@ -58747,7 +58747,7 @@
         <v>55.753777</v>
       </c>
       <c r="H1535" t="n">
-        <v>104.0917</v>
+        <v>104.0916</v>
       </c>
     </row>
     <row r="1536">
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1536" t="n">
         <v>103.8734</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.588196</v>
+        <v>55.588192</v>
       </c>
       <c r="H1537" t="n">
         <v>103.7825</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1538" t="n">
         <v>103.6734</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1542" t="n">
         <v>103.2006</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>54.867413</v>
+        <v>54.867409</v>
       </c>
       <c r="H1543" t="n">
         <v>102.4368</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1545" t="n">
         <v>103.4006</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>56.104431</v>
+        <v>56.104427</v>
       </c>
       <c r="H1546" t="n">
         <v>104.7463</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>56.523266</v>
+        <v>56.523262</v>
       </c>
       <c r="H1547" t="n">
         <v>105.5283</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>56.143391</v>
+        <v>56.143394</v>
       </c>
       <c r="H1548" t="n">
         <v>104.8191</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.60767</v>
+        <v>55.607674</v>
       </c>
       <c r="H1549" t="n">
         <v>103.8189</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.305721</v>
+        <v>55.305717</v>
       </c>
       <c r="H1550" t="n">
         <v>103.2551</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1551" t="n">
         <v>101.4548</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1552" t="n">
         <v>101.3639</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1553" t="n">
         <v>101.7276</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.35117</v>
+        <v>54.351162</v>
       </c>
       <c r="H1554" t="n">
         <v>101.473</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1555" t="n">
         <v>101.6003</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>54.877144</v>
+        <v>54.877148</v>
       </c>
       <c r="H1556" t="n">
         <v>102.455</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1557" t="n">
         <v>103.6734</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1558" t="n">
         <v>103.7461</v>
@@ -59659,7 +59659,7 @@
         <v>55.753777</v>
       </c>
       <c r="H1559" t="n">
-        <v>104.0917</v>
+        <v>104.0916</v>
       </c>
     </row>
     <row r="1560">
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1560" t="n">
         <v>103.7461</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1561" t="n">
         <v>103.8734</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.724556</v>
+        <v>55.72456</v>
       </c>
       <c r="H1562" t="n">
         <v>104.0371</v>
@@ -59811,7 +59811,7 @@
         <v>55.958332</v>
       </c>
       <c r="H1563" t="n">
-        <v>104.4736</v>
+        <v>104.4735</v>
       </c>
     </row>
     <row r="1564">
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1565" t="n">
         <v>104.3644</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>55.870667</v>
+        <v>55.870663</v>
       </c>
       <c r="H1567" t="n">
         <v>104.3099</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.172615</v>
+        <v>56.172611</v>
       </c>
       <c r="H1568" t="n">
         <v>104.8736</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1569" t="n">
         <v>104.2735</v>
@@ -60112,10 +60112,10 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1571" t="n">
-        <v>104.664</v>
+        <v>104.6639</v>
       </c>
     </row>
     <row r="1572">
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1574" t="n">
         <v>106.0142</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1577" t="n">
         <v>106.3609</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1581" t="n">
         <v>109.2804</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1582" t="n">
         <v>109.2439</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.129162</v>
+        <v>59.129169</v>
       </c>
       <c r="H1585" t="n">
         <v>110.3935</v>
@@ -60720,10 +60720,10 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1587" t="n">
-        <v>110.43</v>
+        <v>110.4299</v>
       </c>
     </row>
     <row r="1588">
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1588" t="n">
         <v>111.0686</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1589" t="n">
         <v>111.0868</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1591" t="n">
         <v>108.806</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>58.259335</v>
+        <v>58.259331</v>
       </c>
       <c r="H1592" t="n">
         <v>108.7695</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1594" t="n">
         <v>109.9008</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1596" t="n">
         <v>110.7219</v>
@@ -61179,7 +61179,7 @@
         <v>59.168262</v>
       </c>
       <c r="H1599" t="n">
-        <v>110.4665</v>
+        <v>110.4664</v>
       </c>
     </row>
     <row r="1600">
@@ -61255,7 +61255,7 @@
         <v>59.774212</v>
       </c>
       <c r="H1601" t="n">
-        <v>111.5978</v>
+        <v>111.5977</v>
       </c>
     </row>
     <row r="1602">
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>60.116283</v>
+        <v>60.11628</v>
       </c>
       <c r="H1606" t="n">
         <v>112.2364</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1607" t="n">
         <v>112.4006</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1608" t="n">
         <v>111.8897</v>
@@ -61594,10 +61594,10 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1610" t="n">
-        <v>111.908</v>
+        <v>111.9079</v>
       </c>
     </row>
     <row r="1611">
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1611" t="n">
         <v>112.5101</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>60.956791</v>
+        <v>60.956799</v>
       </c>
       <c r="H1612" t="n">
         <v>113.8056</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1615" t="n">
         <v>113.6414</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>61.474789</v>
+        <v>61.474785</v>
       </c>
       <c r="H1617" t="n">
         <v>114.7727</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>61.445469</v>
+        <v>61.445465</v>
       </c>
       <c r="H1619" t="n">
         <v>114.718</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1624" t="n">
         <v>108.3863</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1625" t="n">
         <v>107.6382</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1626" t="n">
         <v>109.7548</v>
@@ -62392,7 +62392,7 @@
         </is>
       </c>
       <c r="G1631" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1631" t="n">
         <v>109.0882</v>
@@ -62547,7 +62547,7 @@
         <v>55.980774</v>
       </c>
       <c r="H1635" t="n">
-        <v>104.5155</v>
+        <v>104.5154</v>
       </c>
     </row>
     <row r="1636">
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1650" t="n">
         <v>112.3075</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1652" t="n">
         <v>114.0451</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1654" t="n">
         <v>112.1611</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1656" t="n">
         <v>111.9234</v>
@@ -63380,7 +63380,7 @@
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1657" t="n">
         <v>111.3197</v>
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1660" t="n">
         <v>110.0577</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="G1663" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1663" t="n">
         <v>111.521</v>
@@ -63646,10 +63646,10 @@
         </is>
       </c>
       <c r="G1664" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1664" t="n">
-        <v>113.9903</v>
+        <v>113.9902</v>
       </c>
     </row>
     <row r="1665">
@@ -63722,7 +63722,7 @@
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1666" t="n">
         <v>112.1246</v>
@@ -63798,10 +63798,10 @@
         </is>
       </c>
       <c r="G1668" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1668" t="n">
-        <v>111.1003</v>
+        <v>111.1002</v>
       </c>
     </row>
     <row r="1669">
@@ -63991,7 +63991,7 @@
         <v>60.066177</v>
       </c>
       <c r="H1673" t="n">
-        <v>112.1429</v>
+        <v>112.1428</v>
       </c>
     </row>
     <row r="1674">
@@ -64029,7 +64029,7 @@
         <v>61.065487</v>
       </c>
       <c r="H1674" t="n">
-        <v>114.0086</v>
+        <v>114.0085</v>
       </c>
     </row>
     <row r="1675">
@@ -64067,7 +64067,7 @@
         <v>61.065487</v>
       </c>
       <c r="H1675" t="n">
-        <v>114.0086</v>
+        <v>114.0085</v>
       </c>
     </row>
     <row r="1676">
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1678" t="n">
         <v>115.5267</v>
@@ -64254,10 +64254,10 @@
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1680" t="n">
-        <v>115.0329</v>
+        <v>115.0328</v>
       </c>
     </row>
     <row r="1681">
@@ -64368,7 +64368,7 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1683" t="n">
         <v>115.1609</v>
@@ -64444,10 +64444,10 @@
         </is>
       </c>
       <c r="G1685" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1685" t="n">
-        <v>115.0329</v>
+        <v>115.0328</v>
       </c>
     </row>
     <row r="1686">
@@ -64482,7 +64482,7 @@
         </is>
       </c>
       <c r="G1686" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1686" t="n">
         <v>114.5756</v>
@@ -64523,7 +64523,7 @@
         <v>61.281021</v>
       </c>
       <c r="H1687" t="n">
-        <v>114.411</v>
+        <v>114.4109</v>
       </c>
     </row>
     <row r="1688">
@@ -64634,7 +64634,7 @@
         </is>
       </c>
       <c r="G1690" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1690" t="n">
         <v>114.4292</v>
@@ -64713,7 +64713,7 @@
         <v>62.489388</v>
       </c>
       <c r="H1692" t="n">
-        <v>116.667</v>
+        <v>116.6669</v>
       </c>
     </row>
     <row r="1693">
@@ -65891,7 +65891,7 @@
         <v>63.886181</v>
       </c>
       <c r="H1723" t="n">
-        <v>119.2748</v>
+        <v>119.2747</v>
       </c>
     </row>
     <row r="1724">
@@ -66195,7 +66195,7 @@
         <v>65.302795</v>
       </c>
       <c r="H1731" t="n">
-        <v>121.9196</v>
+        <v>121.9195</v>
       </c>
     </row>
     <row r="1732">
@@ -67107,7 +67107,7 @@
         <v>62.89555</v>
       </c>
       <c r="H1755" t="n">
-        <v>117.4253</v>
+        <v>117.4252</v>
       </c>
     </row>
     <row r="1756">
@@ -67221,7 +67221,7 @@
         <v>62.740002</v>
       </c>
       <c r="H1758" t="n">
-        <v>117.1349</v>
+        <v>117.1348</v>
       </c>
     </row>
     <row r="1759">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.099998</v>
+        <v>62.900002</v>
       </c>
       <c r="H1760" t="n">
-        <v>117.807</v>
+        <v>117.4336</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.494999</v>
+        <v>34.605</v>
       </c>
       <c r="H253" t="n">
-        <v>112.2701</v>
+        <v>112.6282</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>47.790001</v>
+        <v>47.695</v>
       </c>
       <c r="H504" t="n">
-        <v>130.2535</v>
+        <v>129.9946</v>
       </c>
     </row>
     <row r="505">
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.770927</v>
+        <v>64.77093499999999</v>
       </c>
       <c r="H506" t="n">
         <v>100.1666</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.702377</v>
+        <v>64.70238500000001</v>
       </c>
       <c r="H507" t="n">
         <v>100.0606</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.810112</v>
+        <v>64.810097</v>
       </c>
       <c r="H510" t="n">
         <v>100.2272</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.025558</v>
+        <v>65.02555099999999</v>
       </c>
       <c r="H513" t="n">
         <v>100.5604</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.525002</v>
+        <v>65.52499400000001</v>
       </c>
       <c r="H515" t="n">
         <v>101.3327</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.23120900000001</v>
+        <v>65.231201</v>
       </c>
       <c r="H521" t="n">
         <v>100.8784</v>
@@ -20402,10 +20402,10 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.485817</v>
+        <v>65.48582500000001</v>
       </c>
       <c r="H526" t="n">
-        <v>101.2721</v>
+        <v>101.2722</v>
       </c>
     </row>
     <row r="527">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.30843400000001</v>
+        <v>66.308441</v>
       </c>
       <c r="H529" t="n">
         <v>102.5443</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H531" t="n">
-        <v>103.2712</v>
+        <v>103.2713</v>
       </c>
     </row>
     <row r="532">
@@ -20668,10 +20668,10 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.58264200000001</v>
+        <v>66.582634</v>
       </c>
       <c r="H533" t="n">
-        <v>102.9684</v>
+        <v>102.9683</v>
       </c>
     </row>
     <row r="534">
@@ -20706,10 +20706,10 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.778496</v>
+        <v>66.778503</v>
       </c>
       <c r="H534" t="n">
-        <v>103.2712</v>
+        <v>103.2713</v>
       </c>
     </row>
     <row r="535">
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.739334</v>
+        <v>66.73932600000001</v>
       </c>
       <c r="H541" t="n">
         <v>103.2107</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.788292</v>
+        <v>66.788284</v>
       </c>
       <c r="H546" t="n">
         <v>103.2864</v>
@@ -21200,10 +21200,10 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.12236</v>
+        <v>66.12236799999999</v>
       </c>
       <c r="H547" t="n">
-        <v>102.2565</v>
+        <v>102.2566</v>
       </c>
     </row>
     <row r="548">
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.259468</v>
+        <v>66.25947600000001</v>
       </c>
       <c r="H550" t="n">
         <v>102.4686</v>
@@ -21352,10 +21352,10 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.494499</v>
+        <v>66.494507</v>
       </c>
       <c r="H551" t="n">
-        <v>102.832</v>
+        <v>102.8321</v>
       </c>
     </row>
     <row r="552">
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.758911</v>
+        <v>66.75891900000001</v>
       </c>
       <c r="H552" t="n">
         <v>103.241</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.375877</v>
+        <v>67.37587000000001</v>
       </c>
       <c r="H553" t="n">
         <v>104.1951</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.248558</v>
+        <v>67.248566</v>
       </c>
       <c r="H557" t="n">
         <v>103.9982</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.659874</v>
+        <v>67.659859</v>
       </c>
       <c r="H561" t="n">
-        <v>104.6343</v>
+        <v>104.6342</v>
       </c>
     </row>
     <row r="562">
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.66965500000001</v>
+        <v>67.669662</v>
       </c>
       <c r="H562" t="n">
         <v>104.6494</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.601105</v>
+        <v>67.601112</v>
       </c>
       <c r="H563" t="n">
         <v>104.5434</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.14952099999999</v>
+        <v>68.149513</v>
       </c>
       <c r="H566" t="n">
         <v>105.3915</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.54235799999999</v>
+        <v>67.542351</v>
       </c>
       <c r="H567" t="n">
         <v>104.4525</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.61090900000001</v>
+        <v>67.610901</v>
       </c>
       <c r="H568" t="n">
         <v>104.5585</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.99722300000001</v>
+        <v>67.997215</v>
       </c>
       <c r="H569" t="n">
         <v>105.156</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>68.272987</v>
+        <v>68.27299499999999</v>
       </c>
       <c r="H570" t="n">
         <v>105.5824</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>68.90331999999999</v>
+        <v>68.903328</v>
       </c>
       <c r="H575" t="n">
         <v>106.5572</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>69.632149</v>
+        <v>69.632141</v>
       </c>
       <c r="H576" t="n">
         <v>107.6843</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.66628300000001</v>
+        <v>70.66629</v>
       </c>
       <c r="H582" t="n">
         <v>109.2836</v>
@@ -22644,10 +22644,10 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>71.69058200000001</v>
+        <v>71.690575</v>
       </c>
       <c r="H585" t="n">
-        <v>110.8677</v>
+        <v>110.8676</v>
       </c>
     </row>
     <row r="586">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.45946499999999</v>
+        <v>70.459457</v>
       </c>
       <c r="H587" t="n">
         <v>108.9638</v>
@@ -22910,10 +22910,10 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>70.804169</v>
+        <v>70.804176</v>
       </c>
       <c r="H592" t="n">
-        <v>109.4968</v>
+        <v>109.4969</v>
       </c>
     </row>
     <row r="593">
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>72.084534</v>
+        <v>72.084541</v>
       </c>
       <c r="H596" t="n">
         <v>111.4769</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.28610999999999</v>
+        <v>73.286118</v>
       </c>
       <c r="H598" t="n">
         <v>113.3351</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>72.754272</v>
+        <v>72.754265</v>
       </c>
       <c r="H599" t="n">
         <v>112.5126</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>73.71946</v>
+        <v>73.71946699999999</v>
       </c>
       <c r="H601" t="n">
         <v>114.0053</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>74.53692599999999</v>
+        <v>74.536934</v>
       </c>
       <c r="H603" t="n">
         <v>115.2695</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>74.241463</v>
+        <v>74.241455</v>
       </c>
       <c r="H605" t="n">
         <v>114.8125</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.30056</v>
+        <v>74.300552</v>
       </c>
       <c r="H606" t="n">
         <v>114.9039</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>75.69910400000001</v>
+        <v>75.699112</v>
       </c>
       <c r="H614" t="n">
         <v>117.0667</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>73.768715</v>
+        <v>73.76870700000001</v>
       </c>
       <c r="H617" t="n">
         <v>114.0814</v>
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>73.128525</v>
+        <v>73.12853200000001</v>
       </c>
       <c r="H622" t="n">
         <v>113.0914</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>72.84290300000001</v>
+        <v>72.842911</v>
       </c>
       <c r="H623" t="n">
         <v>112.6497</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.410004</v>
+        <v>80.5</v>
       </c>
       <c r="H755" t="n">
-        <v>124.352</v>
+        <v>124.4912</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>127</v>
+        <v>127.050003</v>
       </c>
       <c r="H1006" t="n">
-        <v>118.836</v>
+        <v>118.8828</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>127</v>
+        <v>127.050003</v>
       </c>
       <c r="H1257" t="n">
-        <v>118.836</v>
+        <v>118.8828</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>127</v>
+        <v>127.050003</v>
       </c>
       <c r="H1508" t="n">
-        <v>118.836</v>
+        <v>118.8828</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.562202</v>
+        <v>53.562199</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.494011</v>
+        <v>53.494015</v>
       </c>
       <c r="H1510" t="n">
         <v>99.87269999999999</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.377136</v>
+        <v>53.377132</v>
       </c>
       <c r="H1511" t="n">
         <v>99.6545</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.523243</v>
+        <v>53.523239</v>
       </c>
       <c r="H1515" t="n">
         <v>99.9273</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>53.844669</v>
+        <v>53.844673</v>
       </c>
       <c r="H1517" t="n">
         <v>100.5274</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1518" t="n">
         <v>101.7458</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.042736</v>
+        <v>55.042732</v>
       </c>
       <c r="H1521" t="n">
         <v>102.7641</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.974548</v>
+        <v>54.974552</v>
       </c>
       <c r="H1522" t="n">
         <v>102.6368</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.159615</v>
+        <v>55.159618</v>
       </c>
       <c r="H1524" t="n">
-        <v>102.9823</v>
+        <v>102.9824</v>
       </c>
     </row>
     <row r="1525">
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.429092</v>
+        <v>54.429089</v>
       </c>
       <c r="H1525" t="n">
         <v>101.6185</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>54.740788</v>
+        <v>54.740784</v>
       </c>
       <c r="H1526" t="n">
         <v>102.2004</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>54.536232</v>
+        <v>54.536236</v>
       </c>
       <c r="H1527" t="n">
         <v>101.8185</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1528" t="n">
         <v>102.3459</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>54.682339</v>
+        <v>54.682343</v>
       </c>
       <c r="H1530" t="n">
         <v>102.0913</v>
@@ -58744,10 +58744,10 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.753777</v>
+        <v>55.753784</v>
       </c>
       <c r="H1535" t="n">
-        <v>104.0916</v>
+        <v>104.0917</v>
       </c>
     </row>
     <row r="1536">
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.588192</v>
+        <v>55.588188</v>
       </c>
       <c r="H1537" t="n">
         <v>103.7825</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1538" t="n">
         <v>103.6734</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>55.295986</v>
+        <v>55.295982</v>
       </c>
       <c r="H1539" t="n">
         <v>103.237</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1545" t="n">
         <v>103.4006</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1546" t="n">
         <v>104.7463</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1548" t="n">
         <v>104.8191</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.305717</v>
+        <v>55.305721</v>
       </c>
       <c r="H1550" t="n">
         <v>103.2551</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1551" t="n">
         <v>101.4548</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.487534</v>
+        <v>54.48753</v>
       </c>
       <c r="H1553" t="n">
         <v>101.7276</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.351162</v>
+        <v>54.351166</v>
       </c>
       <c r="H1554" t="n">
         <v>101.473</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1557" t="n">
         <v>103.6734</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1558" t="n">
         <v>103.7461</v>
@@ -59656,10 +59656,10 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.753777</v>
+        <v>55.753784</v>
       </c>
       <c r="H1559" t="n">
-        <v>104.0916</v>
+        <v>104.0917</v>
       </c>
     </row>
     <row r="1560">
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1560" t="n">
         <v>103.7461</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.72456</v>
+        <v>55.724556</v>
       </c>
       <c r="H1562" t="n">
         <v>104.0371</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.958332</v>
+        <v>55.958328</v>
       </c>
       <c r="H1563" t="n">
         <v>104.4735</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1565" t="n">
         <v>104.3644</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1566" t="n">
         <v>104.2553</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.294872</v>
+        <v>56.294876</v>
       </c>
       <c r="H1570" t="n">
         <v>105.1019</v>
@@ -60112,10 +60112,10 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1571" t="n">
-        <v>104.6639</v>
+        <v>104.664</v>
       </c>
     </row>
     <row r="1572">
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1574" t="n">
         <v>106.0142</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.53299</v>
+        <v>58.532986</v>
       </c>
       <c r="H1581" t="n">
         <v>109.2804</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.39616</v>
+        <v>58.396156</v>
       </c>
       <c r="H1583" t="n">
         <v>109.0249</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.031437</v>
+        <v>59.031433</v>
       </c>
       <c r="H1584" t="n">
         <v>110.211</v>
@@ -60723,7 +60723,7 @@
         <v>59.148712</v>
       </c>
       <c r="H1587" t="n">
-        <v>110.4299</v>
+        <v>110.43</v>
       </c>
     </row>
     <row r="1588">
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>58.91415</v>
+        <v>58.914154</v>
       </c>
       <c r="H1593" t="n">
         <v>109.992</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>58.86528</v>
+        <v>58.865284</v>
       </c>
       <c r="H1594" t="n">
         <v>109.9008</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.305092</v>
+        <v>59.305088</v>
       </c>
       <c r="H1596" t="n">
         <v>110.7219</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>58.835964</v>
+        <v>58.835968</v>
       </c>
       <c r="H1597" t="n">
         <v>109.8461</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>58.718685</v>
+        <v>58.718681</v>
       </c>
       <c r="H1598" t="n">
         <v>109.6271</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.168262</v>
+        <v>59.168259</v>
       </c>
       <c r="H1599" t="n">
         <v>110.4664</v>
@@ -61255,7 +61255,7 @@
         <v>59.774212</v>
       </c>
       <c r="H1601" t="n">
-        <v>111.5977</v>
+        <v>111.5978</v>
       </c>
     </row>
     <row r="1602">
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>59.246445</v>
+        <v>59.246449</v>
       </c>
       <c r="H1603" t="n">
         <v>110.6124</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>59.852402</v>
+        <v>59.852398</v>
       </c>
       <c r="H1609" t="n">
         <v>111.7437</v>
@@ -61597,7 +61597,7 @@
         <v>59.940361</v>
       </c>
       <c r="H1610" t="n">
-        <v>111.9079</v>
+        <v>111.908</v>
       </c>
     </row>
     <row r="1611">
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>60.956799</v>
+        <v>60.956795</v>
       </c>
       <c r="H1612" t="n">
         <v>113.8056</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>61.406372</v>
+        <v>61.406376</v>
       </c>
       <c r="H1618" t="n">
         <v>114.645</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>59.393051</v>
+        <v>59.393047</v>
       </c>
       <c r="H1622" t="n">
         <v>110.8861</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.581856</v>
+        <v>58.581852</v>
       </c>
       <c r="H1623" t="n">
         <v>109.3716</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1624" t="n">
         <v>108.3863</v>
@@ -62240,7 +62240,7 @@
         </is>
       </c>
       <c r="G1627" t="n">
-        <v>58.4548</v>
+        <v>58.454803</v>
       </c>
       <c r="H1627" t="n">
         <v>109.1344</v>
@@ -62547,7 +62547,7 @@
         <v>55.980774</v>
       </c>
       <c r="H1635" t="n">
-        <v>104.5154</v>
+        <v>104.5155</v>
       </c>
     </row>
     <row r="1636">
@@ -63383,7 +63383,7 @@
         <v>59.625309</v>
       </c>
       <c r="H1657" t="n">
-        <v>111.3197</v>
+        <v>111.3198</v>
       </c>
     </row>
     <row r="1658">
@@ -63801,7 +63801,7 @@
         <v>59.50774</v>
       </c>
       <c r="H1668" t="n">
-        <v>111.1002</v>
+        <v>111.1003</v>
       </c>
     </row>
     <row r="1669">
@@ -63991,7 +63991,7 @@
         <v>60.066177</v>
       </c>
       <c r="H1673" t="n">
-        <v>112.1428</v>
+        <v>112.1429</v>
       </c>
     </row>
     <row r="1674">
@@ -64029,7 +64029,7 @@
         <v>61.065487</v>
       </c>
       <c r="H1674" t="n">
-        <v>114.0085</v>
+        <v>114.0086</v>
       </c>
     </row>
     <row r="1675">
@@ -64067,7 +64067,7 @@
         <v>61.065487</v>
       </c>
       <c r="H1675" t="n">
-        <v>114.0085</v>
+        <v>114.0086</v>
       </c>
     </row>
     <row r="1676">
@@ -64523,7 +64523,7 @@
         <v>61.281021</v>
       </c>
       <c r="H1687" t="n">
-        <v>114.4109</v>
+        <v>114.411</v>
       </c>
     </row>
     <row r="1688">
@@ -64713,7 +64713,7 @@
         <v>62.489388</v>
       </c>
       <c r="H1692" t="n">
-        <v>116.6669</v>
+        <v>116.667</v>
       </c>
     </row>
     <row r="1693">
@@ -65891,7 +65891,7 @@
         <v>63.886181</v>
       </c>
       <c r="H1723" t="n">
-        <v>119.2747</v>
+        <v>119.2748</v>
       </c>
     </row>
     <row r="1724">
@@ -66195,7 +66195,7 @@
         <v>65.302795</v>
       </c>
       <c r="H1731" t="n">
-        <v>121.9195</v>
+        <v>121.9196</v>
       </c>
     </row>
     <row r="1732">
@@ -67107,7 +67107,7 @@
         <v>62.89555</v>
       </c>
       <c r="H1755" t="n">
-        <v>117.4252</v>
+        <v>117.4253</v>
       </c>
     </row>
     <row r="1756">
@@ -67221,7 +67221,7 @@
         <v>62.740002</v>
       </c>
       <c r="H1758" t="n">
-        <v>117.1348</v>
+        <v>117.1349</v>
       </c>
     </row>
     <row r="1759">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.900002</v>
+        <v>62.84</v>
       </c>
       <c r="H1760" t="n">
-        <v>117.4336</v>
+        <v>117.3215</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.70238500000001</v>
+        <v>64.702377</v>
       </c>
       <c r="H507" t="n">
         <v>100.0606</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.810097</v>
+        <v>64.810104</v>
       </c>
       <c r="H510" t="n">
         <v>100.2272</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.103897</v>
+        <v>65.103905</v>
       </c>
       <c r="H511" t="n">
         <v>100.6815</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.52499400000001</v>
+        <v>65.525002</v>
       </c>
       <c r="H515" t="n">
         <v>101.3327</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.231201</v>
+        <v>65.23120900000001</v>
       </c>
       <c r="H521" t="n">
         <v>100.8784</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.476028</v>
+        <v>65.47603599999999</v>
       </c>
       <c r="H523" t="n">
         <v>101.257</v>
@@ -20364,10 +20364,10 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.926506</v>
+        <v>65.926498</v>
       </c>
       <c r="H525" t="n">
-        <v>101.9537</v>
+        <v>101.9536</v>
       </c>
     </row>
     <row r="526">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.210503</v>
+        <v>66.21051</v>
       </c>
       <c r="H527" t="n">
         <v>102.3929</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.73932600000001</v>
+        <v>66.739334</v>
       </c>
       <c r="H541" t="n">
         <v>103.2107</v>
@@ -21048,10 +21048,10 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>67.943871</v>
+        <v>67.94386299999999</v>
       </c>
       <c r="H543" t="n">
-        <v>105.0735</v>
+        <v>105.0734</v>
       </c>
     </row>
     <row r="544">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>67.15063499999999</v>
+        <v>67.150627</v>
       </c>
       <c r="H545" t="n">
         <v>103.8467</v>
@@ -21200,10 +21200,10 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.12236799999999</v>
+        <v>66.12236</v>
       </c>
       <c r="H547" t="n">
-        <v>102.2566</v>
+        <v>102.2565</v>
       </c>
     </row>
     <row r="548">
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.396568</v>
+        <v>66.396576</v>
       </c>
       <c r="H549" t="n">
         <v>102.6806</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.75891900000001</v>
+        <v>66.758911</v>
       </c>
       <c r="H552" t="n">
         <v>103.241</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.748009</v>
+        <v>67.748001</v>
       </c>
       <c r="H559" t="n">
         <v>104.7706</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.89490499999999</v>
+        <v>67.894897</v>
       </c>
       <c r="H560" t="n">
         <v>104.9977</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.542351</v>
+        <v>67.54235799999999</v>
       </c>
       <c r="H567" t="n">
         <v>104.4525</v>
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.562199</v>
+        <v>53.562195</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57949,7 +57949,7 @@
         <v>53.075184</v>
       </c>
       <c r="H1514" t="n">
-        <v>99.0907</v>
+        <v>99.0908</v>
       </c>
     </row>
     <row r="1515">
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>53.844673</v>
+        <v>53.844669</v>
       </c>
       <c r="H1517" t="n">
         <v>100.5274</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.042732</v>
+        <v>55.042728</v>
       </c>
       <c r="H1521" t="n">
         <v>102.7641</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.974552</v>
+        <v>54.974548</v>
       </c>
       <c r="H1522" t="n">
         <v>102.6368</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1523" t="n">
         <v>103.437</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>54.740784</v>
+        <v>54.74078</v>
       </c>
       <c r="H1526" t="n">
         <v>102.2004</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>54.536236</v>
+        <v>54.536232</v>
       </c>
       <c r="H1527" t="n">
         <v>101.8185</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1529" t="n">
         <v>103.1642</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>54.682343</v>
+        <v>54.682335</v>
       </c>
       <c r="H1530" t="n">
         <v>102.0913</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1531" t="n">
         <v>103.1642</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1532" t="n">
         <v>103.437</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.753784</v>
+        <v>55.75378</v>
       </c>
       <c r="H1535" t="n">
         <v>104.0917</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.588188</v>
+        <v>55.588196</v>
       </c>
       <c r="H1537" t="n">
         <v>103.7825</v>
@@ -58975,7 +58975,7 @@
         <v>55.169357</v>
       </c>
       <c r="H1541" t="n">
-        <v>103.0005</v>
+        <v>103.0006</v>
       </c>
     </row>
     <row r="1542">
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>56.143391</v>
+        <v>56.143394</v>
       </c>
       <c r="H1548" t="n">
         <v>104.8191</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.351166</v>
+        <v>54.35117</v>
       </c>
       <c r="H1554" t="n">
         <v>101.473</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1558" t="n">
         <v>103.7461</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.753784</v>
+        <v>55.75378</v>
       </c>
       <c r="H1559" t="n">
         <v>104.0917</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1560" t="n">
         <v>103.7461</v>
@@ -59811,7 +59811,7 @@
         <v>55.958328</v>
       </c>
       <c r="H1563" t="n">
-        <v>104.4735</v>
+        <v>104.4736</v>
       </c>
     </row>
     <row r="1564">
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.987545</v>
+        <v>55.987549</v>
       </c>
       <c r="H1564" t="n">
         <v>104.5281</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1569" t="n">
         <v>104.2735</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1572" t="n">
         <v>104.5362</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1580" t="n">
         <v>108.6783</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1582" t="n">
         <v>109.2439</v>
@@ -60568,10 +60568,10 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.396156</v>
+        <v>58.39616</v>
       </c>
       <c r="H1583" t="n">
-        <v>109.0249</v>
+        <v>109.025</v>
       </c>
     </row>
     <row r="1584">
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.129169</v>
+        <v>59.129166</v>
       </c>
       <c r="H1585" t="n">
         <v>110.3935</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1587" t="n">
         <v>110.43</v>
@@ -60799,7 +60799,7 @@
         <v>59.500557</v>
       </c>
       <c r="H1589" t="n">
-        <v>111.0868</v>
+        <v>111.0869</v>
       </c>
     </row>
     <row r="1590">
@@ -60837,7 +60837,7 @@
         <v>58.708908</v>
       </c>
       <c r="H1590" t="n">
-        <v>109.6088</v>
+        <v>109.6089</v>
       </c>
     </row>
     <row r="1591">
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>58.914154</v>
+        <v>58.91415</v>
       </c>
       <c r="H1593" t="n">
         <v>109.992</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>58.835968</v>
+        <v>58.835964</v>
       </c>
       <c r="H1597" t="n">
         <v>109.8461</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>58.718681</v>
+        <v>58.718685</v>
       </c>
       <c r="H1598" t="n">
         <v>109.6271</v>
@@ -61179,7 +61179,7 @@
         <v>59.168259</v>
       </c>
       <c r="H1599" t="n">
-        <v>110.4664</v>
+        <v>110.4665</v>
       </c>
     </row>
     <row r="1600">
@@ -61214,10 +61214,10 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.793758</v>
+        <v>59.793755</v>
       </c>
       <c r="H1600" t="n">
-        <v>111.6342</v>
+        <v>111.6343</v>
       </c>
     </row>
     <row r="1601">
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.803532</v>
+        <v>59.803528</v>
       </c>
       <c r="H1602" t="n">
         <v>111.6525</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>59.744892</v>
+        <v>59.744896</v>
       </c>
       <c r="H1604" t="n">
         <v>111.543</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>60.11628</v>
+        <v>60.116276</v>
       </c>
       <c r="H1606" t="n">
         <v>112.2364</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1608" t="n">
         <v>111.8897</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>59.852398</v>
+        <v>59.852402</v>
       </c>
       <c r="H1609" t="n">
         <v>111.7437</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.65382</v>
+        <v>60.653816</v>
       </c>
       <c r="H1613" t="n">
         <v>113.24</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1615" t="n">
         <v>113.6414</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>61.015434</v>
+        <v>61.015438</v>
       </c>
       <c r="H1616" t="n">
         <v>113.9151</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>61.406376</v>
+        <v>61.406372</v>
       </c>
       <c r="H1618" t="n">
         <v>114.645</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1625" t="n">
         <v>107.6382</v>
@@ -62278,7 +62278,7 @@
         </is>
       </c>
       <c r="G1628" t="n">
-        <v>58.112728</v>
+        <v>58.112732</v>
       </c>
       <c r="H1628" t="n">
         <v>108.4958</v>
@@ -62319,7 +62319,7 @@
         <v>57.790211</v>
       </c>
       <c r="H1629" t="n">
-        <v>107.8936</v>
+        <v>107.8937</v>
       </c>
     </row>
     <row r="1630">
@@ -62392,7 +62392,7 @@
         </is>
       </c>
       <c r="G1631" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1631" t="n">
         <v>109.0882</v>
@@ -62471,7 +62471,7 @@
         <v>56.549011</v>
       </c>
       <c r="H1633" t="n">
-        <v>105.5763</v>
+        <v>105.5764</v>
       </c>
     </row>
     <row r="1634">
@@ -62509,7 +62509,7 @@
         <v>55.549702</v>
       </c>
       <c r="H1634" t="n">
-        <v>103.7106</v>
+        <v>103.7107</v>
       </c>
     </row>
     <row r="1635">
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1650" t="n">
         <v>112.3075</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1652" t="n">
         <v>114.0451</v>
@@ -63266,10 +63266,10 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1654" t="n">
-        <v>112.1611</v>
+        <v>112.1612</v>
       </c>
     </row>
     <row r="1655">
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1656" t="n">
         <v>111.9234</v>
@@ -63380,7 +63380,7 @@
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1657" t="n">
         <v>111.3198</v>
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1660" t="n">
         <v>110.0577</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="G1663" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1663" t="n">
         <v>111.521</v>
@@ -63646,10 +63646,10 @@
         </is>
       </c>
       <c r="G1664" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1664" t="n">
-        <v>113.9902</v>
+        <v>113.9903</v>
       </c>
     </row>
     <row r="1665">
@@ -63722,7 +63722,7 @@
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1666" t="n">
         <v>112.1246</v>
@@ -63798,7 +63798,7 @@
         </is>
       </c>
       <c r="G1668" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1668" t="n">
         <v>111.1003</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1678" t="n">
         <v>115.5267</v>
@@ -64254,10 +64254,10 @@
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1680" t="n">
-        <v>115.0328</v>
+        <v>115.0329</v>
       </c>
     </row>
     <row r="1681">
@@ -64368,7 +64368,7 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1683" t="n">
         <v>115.1609</v>
@@ -64444,10 +64444,10 @@
         </is>
       </c>
       <c r="G1685" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1685" t="n">
-        <v>115.0328</v>
+        <v>115.0329</v>
       </c>
     </row>
     <row r="1686">
@@ -64482,7 +64482,7 @@
         </is>
       </c>
       <c r="G1686" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1686" t="n">
         <v>114.5756</v>
@@ -64561,7 +64561,7 @@
         <v>60.957718</v>
       </c>
       <c r="H1688" t="n">
-        <v>113.8073</v>
+        <v>113.8074</v>
       </c>
     </row>
     <row r="1689">
@@ -64634,10 +64634,10 @@
         </is>
       </c>
       <c r="G1690" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1690" t="n">
-        <v>114.4292</v>
+        <v>114.4293</v>
       </c>
     </row>
     <row r="1691">
@@ -64979,7 +64979,7 @@
         <v>62.707325</v>
       </c>
       <c r="H1699" t="n">
-        <v>117.0738</v>
+        <v>117.0739</v>
       </c>
     </row>
     <row r="1700">
@@ -65549,7 +65549,7 @@
         <v>63.509743</v>
       </c>
       <c r="H1714" t="n">
-        <v>118.5719</v>
+        <v>118.572</v>
       </c>
     </row>
     <row r="1715">
@@ -65701,7 +65701,7 @@
         <v>63.509743</v>
       </c>
       <c r="H1718" t="n">
-        <v>118.5719</v>
+        <v>118.572</v>
       </c>
     </row>
     <row r="1719">
@@ -65777,7 +65777,7 @@
         <v>63.10358</v>
       </c>
       <c r="H1720" t="n">
-        <v>117.8136</v>
+        <v>117.8137</v>
       </c>
     </row>
     <row r="1721">
@@ -65929,7 +65929,7 @@
         <v>63.707867</v>
       </c>
       <c r="H1724" t="n">
-        <v>118.9418</v>
+        <v>118.9419</v>
       </c>
     </row>
     <row r="1725">
@@ -66005,7 +66005,7 @@
         <v>64.12394</v>
       </c>
       <c r="H1726" t="n">
-        <v>119.7186</v>
+        <v>119.7187</v>
       </c>
     </row>
     <row r="1727">
@@ -66119,7 +66119,7 @@
         <v>64.93626399999999</v>
       </c>
       <c r="H1729" t="n">
-        <v>121.2352</v>
+        <v>121.2353</v>
       </c>
     </row>
     <row r="1730">
@@ -66347,7 +66347,7 @@
         <v>65.312698</v>
       </c>
       <c r="H1735" t="n">
-        <v>121.938</v>
+        <v>121.9381</v>
       </c>
     </row>
     <row r="1736">
@@ -67031,7 +67031,7 @@
         <v>64.322067</v>
       </c>
       <c r="H1753" t="n">
-        <v>120.0885</v>
+        <v>120.0886</v>
       </c>
     </row>
     <row r="1754">
@@ -67259,7 +67259,7 @@
         <v>63.040001</v>
       </c>
       <c r="H1759" t="n">
-        <v>117.6949</v>
+        <v>117.695</v>
       </c>
     </row>
     <row r="1760">
@@ -67297,7 +67297,7 @@
         <v>62.84</v>
       </c>
       <c r="H1760" t="n">
-        <v>117.3215</v>
+        <v>117.3216</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.663208</v>
+        <v>64.303673</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.77093499999999</v>
+        <v>64.410797</v>
       </c>
       <c r="H506" t="n">
         <v>100.1666</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.702377</v>
+        <v>64.342628</v>
       </c>
       <c r="H507" t="n">
         <v>100.0606</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.868858</v>
+        <v>64.508179</v>
       </c>
       <c r="H508" t="n">
         <v>100.318</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.908035</v>
+        <v>64.547134</v>
       </c>
       <c r="H509" t="n">
         <v>100.3786</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.810104</v>
+        <v>64.44976</v>
       </c>
       <c r="H510" t="n">
         <v>100.2272</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.103905</v>
+        <v>64.741913</v>
       </c>
       <c r="H511" t="n">
         <v>100.6815</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.035347</v>
+        <v>64.673744</v>
       </c>
       <c r="H512" t="n">
         <v>100.5755</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.02555099999999</v>
+        <v>64.664001</v>
       </c>
       <c r="H513" t="n">
         <v>100.5604</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.55437499999999</v>
+        <v>65.189888</v>
       </c>
       <c r="H514" t="n">
         <v>101.3782</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.525002</v>
+        <v>65.160675</v>
       </c>
       <c r="H515" t="n">
         <v>101.3327</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.87754099999999</v>
+        <v>65.511246</v>
       </c>
       <c r="H516" t="n">
         <v>101.8779</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>66.02443700000001</v>
+        <v>65.65733299999999</v>
       </c>
       <c r="H517" t="n">
         <v>102.1051</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>66.02443700000001</v>
+        <v>65.65733299999999</v>
       </c>
       <c r="H518" t="n">
         <v>102.1051</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>66.38678</v>
+        <v>66.017662</v>
       </c>
       <c r="H519" t="n">
         <v>102.6655</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.279053</v>
+        <v>65.910538</v>
       </c>
       <c r="H520" t="n">
         <v>102.4989</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.23120900000001</v>
+        <v>64.868515</v>
       </c>
       <c r="H521" t="n">
         <v>100.8784</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.56416299999999</v>
+        <v>65.199623</v>
       </c>
       <c r="H522" t="n">
         <v>101.3933</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.47603599999999</v>
+        <v>65.111977</v>
       </c>
       <c r="H523" t="n">
         <v>101.257</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.906921</v>
+        <v>65.540474</v>
       </c>
       <c r="H524" t="n">
         <v>101.9234</v>
@@ -20364,10 +20364,10 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.926498</v>
+        <v>65.559952</v>
       </c>
       <c r="H525" t="n">
-        <v>101.9536</v>
+        <v>101.9537</v>
       </c>
     </row>
     <row r="526">
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.48582500000001</v>
+        <v>65.121719</v>
       </c>
       <c r="H526" t="n">
         <v>101.2722</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.21051</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H527" t="n">
         <v>102.3929</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.38678</v>
+        <v>66.017662</v>
       </c>
       <c r="H528" t="n">
         <v>102.6655</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.308441</v>
+        <v>65.939758</v>
       </c>
       <c r="H529" t="n">
         <v>102.5443</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.435745</v>
+        <v>66.06635300000001</v>
       </c>
       <c r="H530" t="n">
         <v>102.7412</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.778503</v>
+        <v>66.407196</v>
       </c>
       <c r="H531" t="n">
-        <v>103.2713</v>
+        <v>103.2712</v>
       </c>
     </row>
     <row r="532">
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.709946</v>
+        <v>66.339035</v>
       </c>
       <c r="H532" t="n">
         <v>103.1652</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.582634</v>
+        <v>66.212425</v>
       </c>
       <c r="H533" t="n">
         <v>102.9683</v>
@@ -20706,10 +20706,10 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.778503</v>
+        <v>66.407196</v>
       </c>
       <c r="H534" t="n">
-        <v>103.2713</v>
+        <v>103.2712</v>
       </c>
     </row>
     <row r="535">
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.465126</v>
+        <v>66.095581</v>
       </c>
       <c r="H535" t="n">
         <v>102.7866</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.425949</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H536" t="n">
         <v>102.726</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.465126</v>
+        <v>66.095581</v>
       </c>
       <c r="H537" t="n">
         <v>102.7866</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.66098</v>
+        <v>66.290344</v>
       </c>
       <c r="H538" t="n">
         <v>103.0895</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.357399</v>
+        <v>65.988449</v>
       </c>
       <c r="H539" t="n">
         <v>102.62</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>65.946091</v>
+        <v>65.579414</v>
       </c>
       <c r="H540" t="n">
         <v>101.9839</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.739334</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H541" t="n">
         <v>103.2107</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>67.317108</v>
+        <v>66.942825</v>
       </c>
       <c r="H542" t="n">
         <v>104.1042</v>
@@ -21048,10 +21048,10 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>67.94386299999999</v>
+        <v>67.566093</v>
       </c>
       <c r="H543" t="n">
-        <v>105.0734</v>
+        <v>105.0735</v>
       </c>
     </row>
     <row r="544">
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>67.434631</v>
+        <v>67.059692</v>
       </c>
       <c r="H544" t="n">
         <v>104.2859</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>67.150627</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H545" t="n">
         <v>103.8467</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.788284</v>
+        <v>66.416939</v>
       </c>
       <c r="H546" t="n">
         <v>103.2864</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.12236</v>
+        <v>65.754715</v>
       </c>
       <c r="H547" t="n">
         <v>102.2565</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.08319899999999</v>
+        <v>65.71577499999999</v>
       </c>
       <c r="H548" t="n">
         <v>102.196</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.396576</v>
+        <v>66.027405</v>
       </c>
       <c r="H549" t="n">
         <v>102.6806</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.25947600000001</v>
+        <v>65.89106</v>
       </c>
       <c r="H550" t="n">
         <v>102.4686</v>
@@ -21352,10 +21352,10 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.494507</v>
+        <v>66.124779</v>
       </c>
       <c r="H551" t="n">
-        <v>102.8321</v>
+        <v>102.832</v>
       </c>
     </row>
     <row r="552">
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.758911</v>
+        <v>66.387726</v>
       </c>
       <c r="H552" t="n">
         <v>103.241</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.37587000000001</v>
+        <v>67.001251</v>
       </c>
       <c r="H553" t="n">
         <v>104.1951</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.33669999999999</v>
+        <v>66.96230300000001</v>
       </c>
       <c r="H554" t="n">
         <v>104.1345</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.62069700000001</v>
+        <v>67.24472</v>
       </c>
       <c r="H555" t="n">
         <v>104.5737</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.434631</v>
+        <v>67.059692</v>
       </c>
       <c r="H556" t="n">
         <v>104.2859</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.248566</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H557" t="n">
         <v>103.9982</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.317108</v>
+        <v>66.942825</v>
       </c>
       <c r="H558" t="n">
         <v>104.1042</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.748001</v>
+        <v>67.371315</v>
       </c>
       <c r="H559" t="n">
         <v>104.7706</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.894897</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H560" t="n">
         <v>104.9977</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.659859</v>
+        <v>67.283669</v>
       </c>
       <c r="H561" t="n">
-        <v>104.6342</v>
+        <v>104.6343</v>
       </c>
     </row>
     <row r="562">
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.669662</v>
+        <v>67.29341100000001</v>
       </c>
       <c r="H562" t="n">
         <v>104.6494</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.601112</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H563" t="n">
         <v>104.5434</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.855728</v>
+        <v>67.478447</v>
       </c>
       <c r="H564" t="n">
         <v>104.9372</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.76758599999999</v>
+        <v>67.390793</v>
       </c>
       <c r="H565" t="n">
         <v>104.8008</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.149513</v>
+        <v>67.770599</v>
       </c>
       <c r="H566" t="n">
         <v>105.3915</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.54235799999999</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H567" t="n">
         <v>104.4525</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.610901</v>
+        <v>67.234978</v>
       </c>
       <c r="H568" t="n">
         <v>104.5585</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.997215</v>
+        <v>67.619141</v>
       </c>
       <c r="H569" t="n">
         <v>105.156</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>68.27299499999999</v>
+        <v>67.893379</v>
       </c>
       <c r="H570" t="n">
         <v>105.5824</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.194199</v>
+        <v>67.815033</v>
       </c>
       <c r="H571" t="n">
         <v>105.4606</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>68.35178399999999</v>
+        <v>67.97174099999999</v>
       </c>
       <c r="H572" t="n">
         <v>105.7043</v>
@@ -22188,10 +22188,10 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>68.657104</v>
+        <v>68.275352</v>
       </c>
       <c r="H573" t="n">
-        <v>106.1765</v>
+        <v>106.1764</v>
       </c>
     </row>
     <row r="574">
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>68.686646</v>
+        <v>68.30474100000001</v>
       </c>
       <c r="H574" t="n">
         <v>106.2221</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>68.903328</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H575" t="n">
         <v>106.5572</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>69.632141</v>
+        <v>69.24498699999999</v>
       </c>
       <c r="H576" t="n">
         <v>107.6843</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>70.16398599999999</v>
+        <v>69.773872</v>
       </c>
       <c r="H577" t="n">
         <v>108.5068</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>69.868523</v>
+        <v>69.48004899999999</v>
       </c>
       <c r="H578" t="n">
         <v>108.0499</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.085205</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H579" t="n">
         <v>108.385</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.626892</v>
+        <v>70.2342</v>
       </c>
       <c r="H580" t="n">
         <v>109.2227</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>70.577652</v>
+        <v>70.185226</v>
       </c>
       <c r="H581" t="n">
         <v>109.1465</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.66629</v>
+        <v>70.273376</v>
       </c>
       <c r="H582" t="n">
         <v>109.2836</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>71.040543</v>
+        <v>70.645561</v>
       </c>
       <c r="H583" t="n">
         <v>109.8624</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>71.739822</v>
+        <v>71.340942</v>
       </c>
       <c r="H584" t="n">
         <v>110.9438</v>
@@ -22644,10 +22644,10 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>71.690575</v>
+        <v>71.291977</v>
       </c>
       <c r="H585" t="n">
-        <v>110.8676</v>
+        <v>110.8677</v>
       </c>
     </row>
     <row r="586">
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>71.119339</v>
+        <v>70.723907</v>
       </c>
       <c r="H586" t="n">
         <v>109.9842</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.459457</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H587" t="n">
         <v>108.9638</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.76477800000001</v>
+        <v>70.371315</v>
       </c>
       <c r="H588" t="n">
         <v>109.4359</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>71.26707500000001</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H589" t="n">
         <v>110.2127</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.912514</v>
+        <v>70.518227</v>
       </c>
       <c r="H590" t="n">
         <v>109.6644</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>70.823875</v>
+        <v>70.43008399999999</v>
       </c>
       <c r="H591" t="n">
         <v>109.5273</v>
@@ -22910,10 +22910,10 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>70.804176</v>
+        <v>70.410484</v>
       </c>
       <c r="H592" t="n">
-        <v>109.4969</v>
+        <v>109.4968</v>
       </c>
     </row>
     <row r="593">
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>70.922363</v>
+        <v>70.52803</v>
       </c>
       <c r="H593" t="n">
         <v>109.6796</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>71.07994100000001</v>
+        <v>70.684731</v>
       </c>
       <c r="H594" t="n">
         <v>109.9233</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>71.28677399999999</v>
+        <v>70.890404</v>
       </c>
       <c r="H595" t="n">
         <v>110.2432</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>72.084541</v>
+        <v>71.683746</v>
       </c>
       <c r="H596" t="n">
         <v>111.4769</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>72.78381299999999</v>
+        <v>72.37913500000001</v>
       </c>
       <c r="H597" t="n">
         <v>112.5583</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.286118</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H598" t="n">
         <v>113.3351</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>72.754265</v>
+        <v>72.349754</v>
       </c>
       <c r="H599" t="n">
         <v>112.5126</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.61112199999999</v>
+        <v>73.201836</v>
       </c>
       <c r="H600" t="n">
         <v>113.8377</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>73.71946699999999</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H601" t="n">
         <v>114.0053</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.97554</v>
+        <v>73.564224</v>
       </c>
       <c r="H602" t="n">
         <v>114.4013</v>
@@ -23328,10 +23328,10 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>74.536934</v>
+        <v>74.12249</v>
       </c>
       <c r="H603" t="n">
-        <v>115.2695</v>
+        <v>115.2694</v>
       </c>
     </row>
     <row r="604">
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>74.251312</v>
+        <v>73.838463</v>
       </c>
       <c r="H604" t="n">
         <v>114.8278</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>74.241455</v>
+        <v>73.828667</v>
       </c>
       <c r="H605" t="n">
         <v>114.8125</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.300552</v>
+        <v>73.88743599999999</v>
       </c>
       <c r="H606" t="n">
         <v>114.9039</v>
@@ -23480,10 +23480,10 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.28085299999999</v>
+        <v>73.867851</v>
       </c>
       <c r="H607" t="n">
-        <v>114.8734</v>
+        <v>114.8735</v>
       </c>
     </row>
     <row r="608">
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.911186</v>
+        <v>74.494675</v>
       </c>
       <c r="H608" t="n">
         <v>115.8482</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.911186</v>
+        <v>74.494675</v>
       </c>
       <c r="H609" t="n">
         <v>115.8482</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>75.10817</v>
+        <v>74.69055899999999</v>
       </c>
       <c r="H610" t="n">
         <v>116.1529</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>74.940735</v>
+        <v>74.524055</v>
       </c>
       <c r="H611" t="n">
         <v>115.8939</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>75.14756800000001</v>
+        <v>74.729744</v>
       </c>
       <c r="H612" t="n">
         <v>116.2138</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>75.561218</v>
+        <v>75.141098</v>
       </c>
       <c r="H613" t="n">
         <v>116.8535</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>75.699112</v>
+        <v>75.278206</v>
       </c>
       <c r="H614" t="n">
         <v>117.0667</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>75.580917</v>
+        <v>75.16068300000001</v>
       </c>
       <c r="H615" t="n">
         <v>116.884</v>
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>75.423332</v>
+        <v>75.00398300000001</v>
       </c>
       <c r="H616" t="n">
         <v>116.6403</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>73.76870700000001</v>
+        <v>73.35855100000001</v>
       </c>
       <c r="H617" t="n">
         <v>114.0814</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>74.271011</v>
+        <v>73.85805499999999</v>
       </c>
       <c r="H618" t="n">
         <v>114.8582</v>
@@ -23936,10 +23936,10 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>73.52248400000001</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H619" t="n">
-        <v>113.7006</v>
+        <v>113.7007</v>
       </c>
     </row>
     <row r="620">
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.429253</v>
+        <v>72.026535</v>
       </c>
       <c r="H620" t="n">
         <v>112.01</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>73.492943</v>
+        <v>73.084312</v>
       </c>
       <c r="H621" t="n">
         <v>113.655</v>
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>73.12853200000001</v>
+        <v>72.721931</v>
       </c>
       <c r="H622" t="n">
         <v>113.0914</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>72.842911</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H623" t="n">
         <v>112.6497</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>72.96109800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H624" t="n">
         <v>112.8325</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>73.187622</v>
+        <v>72.780693</v>
       </c>
       <c r="H625" t="n">
         <v>113.1828</v>
@@ -24202,10 +24202,10 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>73.52248400000001</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H626" t="n">
-        <v>113.7006</v>
+        <v>113.7007</v>
       </c>
     </row>
     <row r="627">
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>73.049736</v>
+        <v>72.64357</v>
       </c>
       <c r="H627" t="n">
         <v>112.9696</v>
@@ -24278,10 +24278,10 @@
         </is>
       </c>
       <c r="G628" t="n">
-        <v>71.91392500000001</v>
+        <v>71.514084</v>
       </c>
       <c r="H628" t="n">
-        <v>111.213</v>
+        <v>111.2131</v>
       </c>
     </row>
     <row r="629">
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>71.25071699999999</v>
+        <v>70.854561</v>
       </c>
       <c r="H629" t="n">
         <v>110.1874</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>71.428894</v>
+        <v>71.031746</v>
       </c>
       <c r="H630" t="n">
         <v>110.463</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>71.805038</v>
+        <v>71.4058</v>
       </c>
       <c r="H631" t="n">
         <v>111.0447</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>72.557343</v>
+        <v>72.153915</v>
       </c>
       <c r="H632" t="n">
         <v>112.2081</v>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G633" t="n">
-        <v>72.18119</v>
+        <v>71.779854</v>
       </c>
       <c r="H633" t="n">
         <v>111.6264</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>71.805038</v>
+        <v>71.4058</v>
       </c>
       <c r="H634" t="n">
         <v>111.0447</v>
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>72.45835099999999</v>
+        <v>72.05547300000001</v>
       </c>
       <c r="H635" t="n">
         <v>112.055</v>
@@ -24582,7 +24582,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>72.389061</v>
+        <v>71.986572</v>
       </c>
       <c r="H636" t="n">
         <v>111.9478</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>73.091866</v>
+        <v>72.685463</v>
       </c>
       <c r="H637" t="n">
         <v>113.0347</v>
@@ -24658,7 +24658,7 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.171059</v>
+        <v>72.76422100000001</v>
       </c>
       <c r="H638" t="n">
         <v>113.1572</v>
@@ -24696,7 +24696,7 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>72.85430100000001</v>
+        <v>72.449219</v>
       </c>
       <c r="H639" t="n">
         <v>112.6673</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>74.250015</v>
+        <v>73.837181</v>
       </c>
       <c r="H640" t="n">
         <v>114.8258</v>
@@ -24772,10 +24772,10 @@
         </is>
       </c>
       <c r="G641" t="n">
-        <v>74.358902</v>
+        <v>73.945465</v>
       </c>
       <c r="H641" t="n">
-        <v>114.9941</v>
+        <v>114.9942</v>
       </c>
     </row>
     <row r="642">
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>74.19062</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H642" t="n">
         <v>114.7339</v>
@@ -24848,7 +24848,7 @@
         </is>
       </c>
       <c r="G643" t="n">
-        <v>73.903564</v>
+        <v>73.492653</v>
       </c>
       <c r="H643" t="n">
         <v>114.29</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>74.24012</v>
+        <v>73.827332</v>
       </c>
       <c r="H644" t="n">
         <v>114.8104</v>
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G645" t="n">
-        <v>73.962952</v>
+        <v>73.55171199999999</v>
       </c>
       <c r="H645" t="n">
         <v>114.3818</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>74.220322</v>
+        <v>73.807655</v>
       </c>
       <c r="H646" t="n">
         <v>114.7798</v>
@@ -25000,7 +25000,7 @@
         </is>
       </c>
       <c r="G647" t="n">
-        <v>74.824135</v>
+        <v>74.40810399999999</v>
       </c>
       <c r="H647" t="n">
         <v>115.7136</v>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>74.74494900000001</v>
+        <v>74.32936100000001</v>
       </c>
       <c r="H648" t="n">
         <v>115.5912</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>74.29950700000001</v>
+        <v>73.886391</v>
       </c>
       <c r="H649" t="n">
         <v>114.9023</v>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>74.24012</v>
+        <v>73.827332</v>
       </c>
       <c r="H650" t="n">
         <v>114.8104</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>74.418297</v>
+        <v>74.004524</v>
       </c>
       <c r="H651" t="n">
         <v>115.086</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.002548</v>
+        <v>73.591087</v>
       </c>
       <c r="H652" t="n">
         <v>114.4431</v>
@@ -25228,7 +25228,7 @@
         </is>
       </c>
       <c r="G653" t="n">
-        <v>73.943153</v>
+        <v>73.532028</v>
       </c>
       <c r="H653" t="n">
         <v>114.3512</v>
@@ -25266,7 +25266,7 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>74.200523</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H654" t="n">
         <v>114.7492</v>
@@ -25304,7 +25304,7 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>73.992653</v>
+        <v>73.581245</v>
       </c>
       <c r="H655" t="n">
         <v>114.4277</v>
@@ -25342,7 +25342,7 @@
         </is>
       </c>
       <c r="G656" t="n">
-        <v>74.843941</v>
+        <v>74.427795</v>
       </c>
       <c r="H656" t="n">
         <v>115.7442</v>
@@ -25380,7 +25380,7 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>74.368797</v>
+        <v>73.955299</v>
       </c>
       <c r="H657" t="n">
         <v>115.0094</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>74.824135</v>
+        <v>74.40810399999999</v>
       </c>
       <c r="H658" t="n">
         <v>115.7136</v>
@@ -25456,7 +25456,7 @@
         </is>
       </c>
       <c r="G659" t="n">
-        <v>75.556641</v>
+        <v>75.136543</v>
       </c>
       <c r="H659" t="n">
         <v>116.8464</v>
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>75.051811</v>
+        <v>74.634506</v>
       </c>
       <c r="H660" t="n">
         <v>116.0657</v>
@@ -25532,7 +25532,7 @@
         </is>
       </c>
       <c r="G661" t="n">
-        <v>74.873634</v>
+        <v>74.457329</v>
       </c>
       <c r="H661" t="n">
         <v>115.7902</v>
@@ -25570,7 +25570,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>75.051811</v>
+        <v>74.634506</v>
       </c>
       <c r="H662" t="n">
         <v>116.0657</v>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="G663" t="n">
-        <v>74.893433</v>
+        <v>74.47702</v>
       </c>
       <c r="H663" t="n">
         <v>115.8208</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>75.42795599999999</v>
+        <v>75.008568</v>
       </c>
       <c r="H664" t="n">
         <v>116.6474</v>
@@ -25684,7 +25684,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>76.041679</v>
+        <v>75.618881</v>
       </c>
       <c r="H665" t="n">
         <v>117.5965</v>
@@ -25722,7 +25722,7 @@
         </is>
       </c>
       <c r="G666" t="n">
-        <v>75.467552</v>
+        <v>75.047943</v>
       </c>
       <c r="H666" t="n">
         <v>116.7086</v>
@@ -25760,7 +25760,7 @@
         </is>
       </c>
       <c r="G667" t="n">
-        <v>75.517044</v>
+        <v>75.097168</v>
       </c>
       <c r="H667" t="n">
         <v>116.7852</v>
@@ -25798,7 +25798,7 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>75.814003</v>
+        <v>75.392471</v>
       </c>
       <c r="H668" t="n">
         <v>117.2444</v>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.170357</v>
+        <v>75.746841</v>
       </c>
       <c r="H669" t="n">
         <v>117.7955</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>76.23964700000001</v>
+        <v>75.81574999999999</v>
       </c>
       <c r="H670" t="n">
         <v>117.9027</v>
@@ -25912,7 +25912,7 @@
         </is>
       </c>
       <c r="G671" t="n">
-        <v>76.96225699999999</v>
+        <v>76.53434</v>
       </c>
       <c r="H671" t="n">
         <v>119.0202</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>77.526482</v>
+        <v>77.095421</v>
       </c>
       <c r="H672" t="n">
         <v>119.8927</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="G673" t="n">
-        <v>77.17012800000001</v>
+        <v>76.741051</v>
       </c>
       <c r="H673" t="n">
         <v>119.3416</v>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>77.001846</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H674" t="n">
         <v>119.0814</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.77417800000001</v>
+        <v>76.34730500000001</v>
       </c>
       <c r="H675" t="n">
         <v>118.7293</v>
@@ -26102,7 +26102,7 @@
         </is>
       </c>
       <c r="G676" t="n">
-        <v>76.704887</v>
+        <v>76.278397</v>
       </c>
       <c r="H676" t="n">
         <v>118.6221</v>
@@ -26140,7 +26140,7 @@
         </is>
       </c>
       <c r="G677" t="n">
-        <v>76.605904</v>
+        <v>76.179962</v>
       </c>
       <c r="H677" t="n">
         <v>118.4691</v>
@@ -26178,7 +26178,7 @@
         </is>
       </c>
       <c r="G678" t="n">
-        <v>77.199821</v>
+        <v>76.770584</v>
       </c>
       <c r="H678" t="n">
         <v>119.3876</v>
@@ -26216,7 +26216,7 @@
         </is>
       </c>
       <c r="G679" t="n">
-        <v>77.17012800000001</v>
+        <v>76.741051</v>
       </c>
       <c r="H679" t="n">
         <v>119.3416</v>
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="G680" t="n">
-        <v>77.338402</v>
+        <v>76.908394</v>
       </c>
       <c r="H680" t="n">
         <v>119.6019</v>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G681" t="n">
-        <v>77.348305</v>
+        <v>76.918243</v>
       </c>
       <c r="H681" t="n">
         <v>119.6172</v>
@@ -26330,7 +26330,7 @@
         </is>
       </c>
       <c r="G682" t="n">
-        <v>77.02164500000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H682" t="n">
         <v>119.112</v>
@@ -26368,7 +26368,7 @@
         </is>
       </c>
       <c r="G683" t="n">
-        <v>76.56630699999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H683" t="n">
         <v>118.4078</v>
@@ -26406,7 +26406,7 @@
         </is>
       </c>
       <c r="G684" t="n">
-        <v>76.853371</v>
+        <v>76.426056</v>
       </c>
       <c r="H684" t="n">
         <v>118.8518</v>
@@ -26444,7 +26444,7 @@
         </is>
       </c>
       <c r="G685" t="n">
-        <v>77.15033</v>
+        <v>76.721367</v>
       </c>
       <c r="H685" t="n">
         <v>119.311</v>
@@ -26482,10 +26482,10 @@
         </is>
       </c>
       <c r="G686" t="n">
-        <v>78.298576</v>
+        <v>77.86322800000001</v>
       </c>
       <c r="H686" t="n">
-        <v>121.0867</v>
+        <v>121.0868</v>
       </c>
     </row>
     <row r="687">
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G687" t="n">
-        <v>78.40746300000001</v>
+        <v>77.971512</v>
       </c>
       <c r="H687" t="n">
         <v>121.2551</v>
@@ -26558,7 +26558,7 @@
         </is>
       </c>
       <c r="G688" t="n">
-        <v>78.437157</v>
+        <v>78.00103799999999</v>
       </c>
       <c r="H688" t="n">
         <v>121.3011</v>
@@ -26596,7 +26596,7 @@
         </is>
       </c>
       <c r="G689" t="n">
-        <v>78.79351</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H689" t="n">
         <v>121.8522</v>
@@ -26634,7 +26634,7 @@
         </is>
       </c>
       <c r="G690" t="n">
-        <v>78.58000199999999</v>
+        <v>78.143089</v>
       </c>
       <c r="H690" t="n">
         <v>121.522</v>
@@ -26672,7 +26672,7 @@
         </is>
       </c>
       <c r="G691" t="n">
-        <v>78.349998</v>
+        <v>77.914368</v>
       </c>
       <c r="H691" t="n">
         <v>121.1663</v>
@@ -26710,7 +26710,7 @@
         </is>
       </c>
       <c r="G692" t="n">
-        <v>78.980003</v>
+        <v>78.540863</v>
       </c>
       <c r="H692" t="n">
         <v>122.1406</v>
@@ -26748,7 +26748,7 @@
         </is>
       </c>
       <c r="G693" t="n">
-        <v>78.620003</v>
+        <v>78.182869</v>
       </c>
       <c r="H693" t="n">
         <v>121.5838</v>
@@ -26786,7 +26786,7 @@
         </is>
       </c>
       <c r="G694" t="n">
-        <v>78.839996</v>
+        <v>78.401642</v>
       </c>
       <c r="H694" t="n">
         <v>121.924</v>
@@ -26824,7 +26824,7 @@
         </is>
       </c>
       <c r="G695" t="n">
-        <v>79.120003</v>
+        <v>78.68008399999999</v>
       </c>
       <c r="H695" t="n">
         <v>122.3571</v>
@@ -26862,7 +26862,7 @@
         </is>
       </c>
       <c r="G696" t="n">
-        <v>78.81999999999999</v>
+        <v>78.38175200000001</v>
       </c>
       <c r="H696" t="n">
         <v>121.8931</v>
@@ -26900,7 +26900,7 @@
         </is>
       </c>
       <c r="G697" t="n">
-        <v>78.470001</v>
+        <v>78.033699</v>
       </c>
       <c r="H697" t="n">
         <v>121.3519</v>
@@ -26938,7 +26938,7 @@
         </is>
       </c>
       <c r="G698" t="n">
-        <v>78.56999999999999</v>
+        <v>78.13314099999999</v>
       </c>
       <c r="H698" t="n">
         <v>121.5065</v>
@@ -26976,7 +26976,7 @@
         </is>
       </c>
       <c r="G699" t="n">
-        <v>78.889999</v>
+        <v>78.451363</v>
       </c>
       <c r="H699" t="n">
         <v>122.0014</v>
@@ -27014,7 +27014,7 @@
         </is>
       </c>
       <c r="G700" t="n">
-        <v>79.379997</v>
+        <v>78.938637</v>
       </c>
       <c r="H700" t="n">
         <v>122.7591</v>
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="G701" t="n">
-        <v>79.870003</v>
+        <v>79.42591899999999</v>
       </c>
       <c r="H701" t="n">
         <v>123.5169</v>
@@ -27090,7 +27090,7 @@
         </is>
       </c>
       <c r="G702" t="n">
-        <v>79.970001</v>
+        <v>79.52536000000001</v>
       </c>
       <c r="H702" t="n">
         <v>123.6716</v>
@@ -27128,7 +27128,7 @@
         </is>
       </c>
       <c r="G703" t="n">
-        <v>79.980003</v>
+        <v>79.535309</v>
       </c>
       <c r="H703" t="n">
         <v>123.687</v>
@@ -27166,7 +27166,7 @@
         </is>
       </c>
       <c r="G704" t="n">
-        <v>79.339996</v>
+        <v>78.89885700000001</v>
       </c>
       <c r="H704" t="n">
         <v>122.6973</v>
@@ -27204,7 +27204,7 @@
         </is>
       </c>
       <c r="G705" t="n">
-        <v>79.639999</v>
+        <v>79.19718899999999</v>
       </c>
       <c r="H705" t="n">
         <v>123.1612</v>
@@ -27242,7 +27242,7 @@
         </is>
       </c>
       <c r="G706" t="n">
-        <v>79.849998</v>
+        <v>79.406021</v>
       </c>
       <c r="H706" t="n">
         <v>123.486</v>
@@ -27280,7 +27280,7 @@
         </is>
       </c>
       <c r="G707" t="n">
-        <v>79.970001</v>
+        <v>79.52536000000001</v>
       </c>
       <c r="H707" t="n">
         <v>123.6716</v>
@@ -27318,7 +27318,7 @@
         </is>
       </c>
       <c r="G708" t="n">
-        <v>79.949997</v>
+        <v>79.50547</v>
       </c>
       <c r="H708" t="n">
         <v>123.6406</v>
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="G709" t="n">
-        <v>79.839996</v>
+        <v>79.39608</v>
       </c>
       <c r="H709" t="n">
         <v>123.4705</v>
@@ -27394,7 +27394,7 @@
         </is>
       </c>
       <c r="G710" t="n">
-        <v>80.06999999999999</v>
+        <v>79.624802</v>
       </c>
       <c r="H710" t="n">
         <v>123.8262</v>
@@ -27432,7 +27432,7 @@
         </is>
       </c>
       <c r="G711" t="n">
-        <v>79.910004</v>
+        <v>79.465698</v>
       </c>
       <c r="H711" t="n">
         <v>123.5788</v>
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="G712" t="n">
-        <v>79.760002</v>
+        <v>79.31652800000001</v>
       </c>
       <c r="H712" t="n">
         <v>123.3468</v>
@@ -27508,7 +27508,7 @@
         </is>
       </c>
       <c r="G713" t="n">
-        <v>80.010002</v>
+        <v>79.56514</v>
       </c>
       <c r="H713" t="n">
         <v>123.7334</v>
@@ -27546,7 +27546,7 @@
         </is>
       </c>
       <c r="G714" t="n">
-        <v>80.720001</v>
+        <v>80.271187</v>
       </c>
       <c r="H714" t="n">
         <v>124.8314</v>
@@ -27584,10 +27584,10 @@
         </is>
       </c>
       <c r="G715" t="n">
-        <v>80.400002</v>
+        <v>79.952972</v>
       </c>
       <c r="H715" t="n">
-        <v>124.3365</v>
+        <v>124.3366</v>
       </c>
     </row>
     <row r="716">
@@ -27622,7 +27622,7 @@
         </is>
       </c>
       <c r="G716" t="n">
-        <v>80.970001</v>
+        <v>80.51979799999999</v>
       </c>
       <c r="H716" t="n">
         <v>125.218</v>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="G717" t="n">
-        <v>81.16999800000001</v>
+        <v>80.718681</v>
       </c>
       <c r="H717" t="n">
         <v>125.5273</v>
@@ -27698,7 +27698,7 @@
         </is>
       </c>
       <c r="G718" t="n">
-        <v>81.519997</v>
+        <v>81.066734</v>
       </c>
       <c r="H718" t="n">
         <v>126.0686</v>
@@ -27736,7 +27736,7 @@
         </is>
       </c>
       <c r="G719" t="n">
-        <v>81.139999</v>
+        <v>80.68885</v>
       </c>
       <c r="H719" t="n">
         <v>125.4809</v>
@@ -27774,7 +27774,7 @@
         </is>
       </c>
       <c r="G720" t="n">
-        <v>80.389999</v>
+        <v>79.94302399999999</v>
       </c>
       <c r="H720" t="n">
         <v>124.3211</v>
@@ -27812,7 +27812,7 @@
         </is>
       </c>
       <c r="G721" t="n">
-        <v>80.55999799999999</v>
+        <v>80.112076</v>
       </c>
       <c r="H721" t="n">
         <v>124.584</v>
@@ -27850,7 +27850,7 @@
         </is>
       </c>
       <c r="G722" t="n">
-        <v>80.739998</v>
+        <v>80.291077</v>
       </c>
       <c r="H722" t="n">
         <v>124.8623</v>
@@ -27888,7 +27888,7 @@
         </is>
       </c>
       <c r="G723" t="n">
-        <v>81.19000200000001</v>
+        <v>80.738579</v>
       </c>
       <c r="H723" t="n">
         <v>125.5583</v>
@@ -27926,7 +27926,7 @@
         </is>
       </c>
       <c r="G724" t="n">
-        <v>81.160004</v>
+        <v>80.708748</v>
       </c>
       <c r="H724" t="n">
         <v>125.5119</v>
@@ -27964,7 +27964,7 @@
         </is>
       </c>
       <c r="G725" t="n">
-        <v>81.339996</v>
+        <v>80.88774100000001</v>
       </c>
       <c r="H725" t="n">
         <v>125.7902</v>
@@ -28002,7 +28002,7 @@
         </is>
       </c>
       <c r="G726" t="n">
-        <v>81.459999</v>
+        <v>81.00707199999999</v>
       </c>
       <c r="H726" t="n">
         <v>125.9758</v>
@@ -28040,7 +28040,7 @@
         </is>
       </c>
       <c r="G727" t="n">
-        <v>81.629997</v>
+        <v>81.176125</v>
       </c>
       <c r="H727" t="n">
         <v>126.2387</v>
@@ -28078,7 +28078,7 @@
         </is>
       </c>
       <c r="G728" t="n">
-        <v>81.699997</v>
+        <v>81.245735</v>
       </c>
       <c r="H728" t="n">
         <v>126.347</v>
@@ -28116,7 +28116,7 @@
         </is>
       </c>
       <c r="G729" t="n">
-        <v>81.860001</v>
+        <v>81.404854</v>
       </c>
       <c r="H729" t="n">
         <v>126.5944</v>
@@ -28154,7 +28154,7 @@
         </is>
       </c>
       <c r="G730" t="n">
-        <v>81.94000200000001</v>
+        <v>81.48440600000001</v>
       </c>
       <c r="H730" t="n">
         <v>126.7181</v>
@@ -28192,7 +28192,7 @@
         </is>
       </c>
       <c r="G731" t="n">
-        <v>81.75</v>
+        <v>81.295464</v>
       </c>
       <c r="H731" t="n">
         <v>126.4243</v>
@@ -28230,7 +28230,7 @@
         </is>
       </c>
       <c r="G732" t="n">
-        <v>81.620003</v>
+        <v>81.166191</v>
       </c>
       <c r="H732" t="n">
         <v>126.2233</v>
@@ -28268,7 +28268,7 @@
         </is>
       </c>
       <c r="G733" t="n">
-        <v>81.300003</v>
+        <v>80.84796900000001</v>
       </c>
       <c r="H733" t="n">
         <v>125.7284</v>
@@ -28306,7 +28306,7 @@
         </is>
       </c>
       <c r="G734" t="n">
-        <v>81.199997</v>
+        <v>80.74852</v>
       </c>
       <c r="H734" t="n">
         <v>125.5737</v>
@@ -28344,7 +28344,7 @@
         </is>
       </c>
       <c r="G735" t="n">
-        <v>80.860001</v>
+        <v>80.410408</v>
       </c>
       <c r="H735" t="n">
         <v>125.0479</v>
@@ -28382,7 +28382,7 @@
         </is>
       </c>
       <c r="G736" t="n">
-        <v>81.209999</v>
+        <v>80.758461</v>
       </c>
       <c r="H736" t="n">
         <v>125.5892</v>
@@ -28420,7 +28420,7 @@
         </is>
       </c>
       <c r="G737" t="n">
-        <v>81.209999</v>
+        <v>80.758461</v>
       </c>
       <c r="H737" t="n">
         <v>125.5892</v>
@@ -28458,10 +28458,10 @@
         </is>
       </c>
       <c r="G738" t="n">
-        <v>81.480003</v>
+        <v>81.02697000000001</v>
       </c>
       <c r="H738" t="n">
-        <v>126.0067</v>
+        <v>126.0068</v>
       </c>
     </row>
     <row r="739">
@@ -28496,7 +28496,7 @@
         </is>
       </c>
       <c r="G739" t="n">
-        <v>81.660004</v>
+        <v>81.205963</v>
       </c>
       <c r="H739" t="n">
         <v>126.2851</v>
@@ -28534,7 +28534,7 @@
         </is>
       </c>
       <c r="G740" t="n">
-        <v>81.25</v>
+        <v>80.798241</v>
       </c>
       <c r="H740" t="n">
         <v>125.6511</v>
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="G741" t="n">
-        <v>81.66999800000001</v>
+        <v>81.21590399999999</v>
       </c>
       <c r="H741" t="n">
         <v>126.3006</v>
@@ -28610,7 +28610,7 @@
         </is>
       </c>
       <c r="G742" t="n">
-        <v>81.389999</v>
+        <v>80.937462</v>
       </c>
       <c r="H742" t="n">
         <v>125.8676</v>
@@ -28648,7 +28648,7 @@
         </is>
       </c>
       <c r="G743" t="n">
-        <v>81.55999799999999</v>
+        <v>81.106514</v>
       </c>
       <c r="H743" t="n">
         <v>126.1305</v>
@@ -28686,7 +28686,7 @@
         </is>
       </c>
       <c r="G744" t="n">
-        <v>81.760002</v>
+        <v>81.30540499999999</v>
       </c>
       <c r="H744" t="n">
         <v>126.4398</v>
@@ -28724,7 +28724,7 @@
         </is>
       </c>
       <c r="G745" t="n">
-        <v>82.290001</v>
+        <v>81.832458</v>
       </c>
       <c r="H745" t="n">
         <v>127.2594</v>
@@ -28762,7 +28762,7 @@
         </is>
       </c>
       <c r="G746" t="n">
-        <v>82.110001</v>
+        <v>81.653458</v>
       </c>
       <c r="H746" t="n">
         <v>126.981</v>
@@ -28800,7 +28800,7 @@
         </is>
       </c>
       <c r="G747" t="n">
-        <v>81.81999999999999</v>
+        <v>81.36507400000001</v>
       </c>
       <c r="H747" t="n">
         <v>126.5325</v>
@@ -28838,7 +28838,7 @@
         </is>
       </c>
       <c r="G748" t="n">
-        <v>81.730003</v>
+        <v>81.27557400000001</v>
       </c>
       <c r="H748" t="n">
         <v>126.3934</v>
@@ -28876,7 +28876,7 @@
         </is>
       </c>
       <c r="G749" t="n">
-        <v>81.040001</v>
+        <v>80.589409</v>
       </c>
       <c r="H749" t="n">
         <v>125.3263</v>
@@ -28914,7 +28914,7 @@
         </is>
       </c>
       <c r="G750" t="n">
-        <v>80.639999</v>
+        <v>80.19163500000001</v>
       </c>
       <c r="H750" t="n">
         <v>124.7077</v>
@@ -28952,7 +28952,7 @@
         </is>
       </c>
       <c r="G751" t="n">
-        <v>81.269997</v>
+        <v>80.81813</v>
       </c>
       <c r="H751" t="n">
         <v>125.682</v>
@@ -28990,7 +28990,7 @@
         </is>
       </c>
       <c r="G752" t="n">
-        <v>81.33000199999999</v>
+        <v>80.87779999999999</v>
       </c>
       <c r="H752" t="n">
         <v>125.7748</v>
@@ -29028,7 +29028,7 @@
         </is>
       </c>
       <c r="G753" t="n">
-        <v>80.910004</v>
+        <v>80.46013600000001</v>
       </c>
       <c r="H753" t="n">
         <v>125.1253</v>
@@ -29066,7 +29066,7 @@
         </is>
       </c>
       <c r="G754" t="n">
-        <v>81.279999</v>
+        <v>80.82807200000001</v>
       </c>
       <c r="H754" t="n">
         <v>125.6974</v>
@@ -29107,7 +29107,7 @@
         <v>80.5</v>
       </c>
       <c r="H755" t="n">
-        <v>124.4912</v>
+        <v>125.1873</v>
       </c>
     </row>
     <row r="756">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.562195</v>
+        <v>53.562199</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.494015</v>
+        <v>53.494011</v>
       </c>
       <c r="H1510" t="n">
         <v>99.87269999999999</v>
@@ -57949,7 +57949,7 @@
         <v>53.075184</v>
       </c>
       <c r="H1514" t="n">
-        <v>99.0908</v>
+        <v>99.0907</v>
       </c>
     </row>
     <row r="1515">
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.799221</v>
+        <v>54.799225</v>
       </c>
       <c r="H1519" t="n">
         <v>102.3095</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.974548</v>
+        <v>54.974545</v>
       </c>
       <c r="H1522" t="n">
         <v>102.6368</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.429089</v>
+        <v>54.429092</v>
       </c>
       <c r="H1525" t="n">
         <v>101.6185</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>54.536232</v>
+        <v>54.536236</v>
       </c>
       <c r="H1527" t="n">
         <v>101.8185</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.818703</v>
+        <v>54.818699</v>
       </c>
       <c r="H1528" t="n">
         <v>102.3459</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1530" t="n">
         <v>102.0913</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1533" t="n">
         <v>103.2006</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1535" t="n">
         <v>104.0917</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1536" t="n">
         <v>103.8734</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1539" t="n">
         <v>103.237</v>
@@ -58975,7 +58975,7 @@
         <v>55.169357</v>
       </c>
       <c r="H1541" t="n">
-        <v>103.0006</v>
+        <v>103.0005</v>
       </c>
     </row>
     <row r="1542">
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1542" t="n">
         <v>103.2006</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>54.867409</v>
+        <v>54.867413</v>
       </c>
       <c r="H1543" t="n">
         <v>102.4368</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>56.523262</v>
+        <v>56.523266</v>
       </c>
       <c r="H1547" t="n">
         <v>105.5283</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1548" t="n">
         <v>104.8191</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.607674</v>
+        <v>55.60767</v>
       </c>
       <c r="H1549" t="n">
         <v>103.8189</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1552" t="n">
         <v>101.3639</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1555" t="n">
         <v>101.6003</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>54.877148</v>
+        <v>54.877144</v>
       </c>
       <c r="H1556" t="n">
         <v>102.455</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1558" t="n">
         <v>103.7461</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1559" t="n">
         <v>104.0917</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1560" t="n">
         <v>103.7461</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1561" t="n">
         <v>103.8734</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.958328</v>
+        <v>55.958332</v>
       </c>
       <c r="H1563" t="n">
         <v>104.4736</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.987549</v>
+        <v>55.987545</v>
       </c>
       <c r="H1564" t="n">
         <v>104.5281</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>55.841446</v>
+        <v>55.841442</v>
       </c>
       <c r="H1566" t="n">
         <v>104.2553</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>55.870663</v>
+        <v>55.870667</v>
       </c>
       <c r="H1567" t="n">
         <v>104.3099</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.172611</v>
+        <v>56.172615</v>
       </c>
       <c r="H1568" t="n">
         <v>104.8736</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1570" t="n">
         <v>105.1019</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1572" t="n">
         <v>104.5362</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1577" t="n">
         <v>106.3609</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1580" t="n">
         <v>108.6783</v>
@@ -60571,7 +60571,7 @@
         <v>58.39616</v>
       </c>
       <c r="H1583" t="n">
-        <v>109.025</v>
+        <v>109.0249</v>
       </c>
     </row>
     <row r="1584">
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1584" t="n">
         <v>110.211</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.129166</v>
+        <v>59.129162</v>
       </c>
       <c r="H1585" t="n">
         <v>110.3935</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1588" t="n">
         <v>111.0686</v>
@@ -60796,10 +60796,10 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1589" t="n">
-        <v>111.0869</v>
+        <v>111.0868</v>
       </c>
     </row>
     <row r="1590">
@@ -60837,7 +60837,7 @@
         <v>58.708908</v>
       </c>
       <c r="H1590" t="n">
-        <v>109.6089</v>
+        <v>109.6088</v>
       </c>
     </row>
     <row r="1591">
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1591" t="n">
         <v>108.806</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>58.259331</v>
+        <v>58.259335</v>
       </c>
       <c r="H1592" t="n">
         <v>108.7695</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.168259</v>
+        <v>59.168262</v>
       </c>
       <c r="H1599" t="n">
         <v>110.4665</v>
@@ -61214,10 +61214,10 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.793755</v>
+        <v>59.793758</v>
       </c>
       <c r="H1600" t="n">
-        <v>111.6343</v>
+        <v>111.6342</v>
       </c>
     </row>
     <row r="1601">
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.803528</v>
+        <v>59.803532</v>
       </c>
       <c r="H1602" t="n">
         <v>111.6525</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>59.246449</v>
+        <v>59.246445</v>
       </c>
       <c r="H1603" t="n">
         <v>110.6124</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>59.744896</v>
+        <v>59.744892</v>
       </c>
       <c r="H1604" t="n">
         <v>111.543</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>60.116276</v>
+        <v>60.116283</v>
       </c>
       <c r="H1606" t="n">
         <v>112.2364</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1607" t="n">
         <v>112.4006</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1610" t="n">
         <v>111.908</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1611" t="n">
         <v>112.5101</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>60.956795</v>
+        <v>60.956791</v>
       </c>
       <c r="H1612" t="n">
         <v>113.8056</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.653816</v>
+        <v>60.65382</v>
       </c>
       <c r="H1613" t="n">
         <v>113.24</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1616" t="n">
         <v>113.9151</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>61.474785</v>
+        <v>61.474789</v>
       </c>
       <c r="H1617" t="n">
         <v>114.7727</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>61.445465</v>
+        <v>61.445469</v>
       </c>
       <c r="H1619" t="n">
         <v>114.718</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1622" t="n">
         <v>110.8861</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.581852</v>
+        <v>58.581856</v>
       </c>
       <c r="H1623" t="n">
         <v>109.3716</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1626" t="n">
         <v>109.7548</v>
@@ -62240,7 +62240,7 @@
         </is>
       </c>
       <c r="G1627" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1627" t="n">
         <v>109.1344</v>
@@ -62278,7 +62278,7 @@
         </is>
       </c>
       <c r="G1628" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1628" t="n">
         <v>108.4958</v>
@@ -62319,7 +62319,7 @@
         <v>57.790211</v>
       </c>
       <c r="H1629" t="n">
-        <v>107.8937</v>
+        <v>107.8936</v>
       </c>
     </row>
     <row r="1630">
@@ -62471,7 +62471,7 @@
         <v>56.549011</v>
       </c>
       <c r="H1633" t="n">
-        <v>105.5764</v>
+        <v>105.5763</v>
       </c>
     </row>
     <row r="1634">
@@ -62509,7 +62509,7 @@
         <v>55.549702</v>
       </c>
       <c r="H1634" t="n">
-        <v>103.7107</v>
+        <v>103.7106</v>
       </c>
     </row>
     <row r="1635">
@@ -63269,7 +63269,7 @@
         <v>60.075977</v>
       </c>
       <c r="H1654" t="n">
-        <v>112.1612</v>
+        <v>112.1611</v>
       </c>
     </row>
     <row r="1655">
@@ -63383,7 +63383,7 @@
         <v>59.625305</v>
       </c>
       <c r="H1657" t="n">
-        <v>111.3198</v>
+        <v>111.3197</v>
       </c>
     </row>
     <row r="1658">
@@ -64561,7 +64561,7 @@
         <v>60.957718</v>
       </c>
       <c r="H1688" t="n">
-        <v>113.8074</v>
+        <v>113.8073</v>
       </c>
     </row>
     <row r="1689">
@@ -64637,7 +64637,7 @@
         <v>61.290821</v>
       </c>
       <c r="H1690" t="n">
-        <v>114.4293</v>
+        <v>114.4292</v>
       </c>
     </row>
     <row r="1691">
@@ -64979,7 +64979,7 @@
         <v>62.707325</v>
       </c>
       <c r="H1699" t="n">
-        <v>117.0739</v>
+        <v>117.0738</v>
       </c>
     </row>
     <row r="1700">
@@ -65549,7 +65549,7 @@
         <v>63.509743</v>
       </c>
       <c r="H1714" t="n">
-        <v>118.572</v>
+        <v>118.5719</v>
       </c>
     </row>
     <row r="1715">
@@ -65701,7 +65701,7 @@
         <v>63.509743</v>
       </c>
       <c r="H1718" t="n">
-        <v>118.572</v>
+        <v>118.5719</v>
       </c>
     </row>
     <row r="1719">
@@ -65777,7 +65777,7 @@
         <v>63.10358</v>
       </c>
       <c r="H1720" t="n">
-        <v>117.8137</v>
+        <v>117.8136</v>
       </c>
     </row>
     <row r="1721">
@@ -65929,7 +65929,7 @@
         <v>63.707867</v>
       </c>
       <c r="H1724" t="n">
-        <v>118.9419</v>
+        <v>118.9418</v>
       </c>
     </row>
     <row r="1725">
@@ -66005,7 +66005,7 @@
         <v>64.12394</v>
       </c>
       <c r="H1726" t="n">
-        <v>119.7187</v>
+        <v>119.7186</v>
       </c>
     </row>
     <row r="1727">
@@ -66119,7 +66119,7 @@
         <v>64.93626399999999</v>
       </c>
       <c r="H1729" t="n">
-        <v>121.2353</v>
+        <v>121.2352</v>
       </c>
     </row>
     <row r="1730">
@@ -66347,7 +66347,7 @@
         <v>65.312698</v>
       </c>
       <c r="H1735" t="n">
-        <v>121.9381</v>
+        <v>121.938</v>
       </c>
     </row>
     <row r="1736">
@@ -67031,7 +67031,7 @@
         <v>64.322067</v>
       </c>
       <c r="H1753" t="n">
-        <v>120.0886</v>
+        <v>120.0885</v>
       </c>
     </row>
     <row r="1754">
@@ -67259,7 +67259,7 @@
         <v>63.040001</v>
       </c>
       <c r="H1759" t="n">
-        <v>117.695</v>
+        <v>117.6949</v>
       </c>
     </row>
     <row r="1760">
@@ -67297,7 +67297,7 @@
         <v>62.84</v>
       </c>
       <c r="H1760" t="n">
-        <v>117.3216</v>
+        <v>117.3215</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.939999</v>
+        <v>35.07</v>
       </c>
       <c r="H253" t="n">
-        <v>114.2203</v>
+        <v>114.6453</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.735001</v>
+        <v>48.970001</v>
       </c>
       <c r="H504" t="n">
-        <v>132.7567</v>
+        <v>133.3969</v>
       </c>
     </row>
     <row r="505">
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.50818599999999</v>
+        <v>64.508179</v>
       </c>
       <c r="H506" t="n">
         <v>100.2573</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.547134</v>
+        <v>64.54714199999999</v>
       </c>
       <c r="H507" t="n">
         <v>100.3178</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.449753</v>
+        <v>64.44974499999999</v>
       </c>
       <c r="H508" t="n">
         <v>100.1665</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H513" t="n">
         <v>101.2714</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.657341</v>
+        <v>65.65733299999999</v>
       </c>
       <c r="H515" t="n">
         <v>102.0433</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.657341</v>
+        <v>65.65733299999999</v>
       </c>
       <c r="H516" t="n">
         <v>102.0433</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H518" t="n">
         <v>102.4368</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.19961499999999</v>
+        <v>65.199623</v>
       </c>
       <c r="H520" t="n">
         <v>101.3319</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H521" t="n">
         <v>101.1957</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H524" t="n">
         <v>101.2108</v>
@@ -20364,10 +20364,10 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.842361</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H525" t="n">
-        <v>102.3308</v>
+        <v>102.3309</v>
       </c>
     </row>
     <row r="526">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H527" t="n">
         <v>102.4822</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.06635300000001</v>
+        <v>66.066345</v>
       </c>
       <c r="H528" t="n">
         <v>102.679</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H529" t="n">
         <v>103.2087</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.339035</v>
+        <v>66.339043</v>
       </c>
       <c r="H530" t="n">
         <v>103.1028</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H532" t="n">
         <v>103.2087</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H534" t="n">
         <v>102.6638</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H536" t="n">
         <v>103.0271</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.988449</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H537" t="n">
         <v>102.5579</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>65.754715</v>
+        <v>65.754723</v>
       </c>
       <c r="H545" t="n">
         <v>102.1946</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>65.71577499999999</v>
+        <v>65.715767</v>
       </c>
       <c r="H546" t="n">
         <v>102.1341</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H547" t="n">
         <v>102.6184</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H551" t="n">
         <v>104.132</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>66.96229599999999</v>
+        <v>66.96230300000001</v>
       </c>
       <c r="H552" t="n">
         <v>104.0714</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.24472</v>
+        <v>67.24472799999999</v>
       </c>
       <c r="H553" t="n">
         <v>104.5104</v>
@@ -21618,10 +21618,10 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H558" t="n">
-        <v>104.9342</v>
+        <v>104.9341</v>
       </c>
     </row>
     <row r="559">
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H564" t="n">
         <v>105.3277</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H565" t="n">
         <v>104.3893</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H571" t="n">
         <v>106.1122</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H574" t="n">
         <v>107.6191</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H575" t="n">
         <v>108.4411</v>
@@ -22340,10 +22340,10 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H577" t="n">
-        <v>108.3193</v>
+        <v>108.3194</v>
       </c>
     </row>
     <row r="578">
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H579" t="n">
         <v>109.0804</v>
@@ -22682,10 +22682,10 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H586" t="n">
-        <v>109.3696</v>
+        <v>109.3697</v>
       </c>
     </row>
     <row r="587">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.410492</v>
+        <v>70.4105</v>
       </c>
       <c r="H590" t="n">
         <v>109.4305</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H594" t="n">
         <v>111.4094</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H596" t="n">
         <v>113.2665</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H600" t="n">
         <v>114.332</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H602" t="n">
         <v>114.7582</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H605" t="n">
         <v>114.8039</v>
@@ -23556,10 +23556,10 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H609" t="n">
-        <v>115.8237</v>
+        <v>115.8238</v>
       </c>
     </row>
     <row r="610">
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H614" t="n">
         <v>116.5696</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H615" t="n">
         <v>114.0123</v>
@@ -24050,10 +24050,10 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H622" t="n">
-        <v>112.7641</v>
+        <v>112.7642</v>
       </c>
     </row>
     <row r="623">
@@ -24164,10 +24164,10 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>72.64357800000001</v>
+        <v>72.64357</v>
       </c>
       <c r="H625" t="n">
-        <v>112.9012</v>
+        <v>112.9011</v>
       </c>
     </row>
     <row r="626">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.870003</v>
+        <v>80.910004</v>
       </c>
       <c r="H755" t="n">
-        <v>125.6865</v>
+        <v>125.7487</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>128.179993</v>
+        <v>128.600006</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.582</v>
+        <v>119.9739</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>128.179993</v>
+        <v>128.600006</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.582</v>
+        <v>119.9739</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>128.179993</v>
+        <v>128.600006</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.582</v>
+        <v>119.9739</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.542717</v>
+        <v>53.542721</v>
       </c>
       <c r="H1510" t="n">
         <v>100.3102</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.425835</v>
+        <v>53.425831</v>
       </c>
       <c r="H1511" t="n">
         <v>100.0912</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>53.075188</v>
+        <v>53.075184</v>
       </c>
       <c r="H1512" t="n">
         <v>99.43429999999999</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.620636</v>
+        <v>53.62064</v>
       </c>
       <c r="H1514" t="n">
         <v>100.4562</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.844669</v>
+        <v>53.844673</v>
       </c>
       <c r="H1515" t="n">
         <v>100.8759</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1516" t="n">
         <v>102.0985</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.062218</v>
+        <v>55.062214</v>
       </c>
       <c r="H1518" t="n">
         <v>103.1569</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1521" t="n">
         <v>103.7956</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.429096</v>
+        <v>54.429089</v>
       </c>
       <c r="H1523" t="n">
         <v>101.9708</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.740788</v>
+        <v>54.740784</v>
       </c>
       <c r="H1524" t="n">
-        <v>102.5548</v>
+        <v>102.5547</v>
       </c>
     </row>
     <row r="1525">
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.53624</v>
+        <v>54.536236</v>
       </c>
       <c r="H1525" t="n">
         <v>102.1715</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1527" t="n">
         <v>103.5219</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.682339</v>
+        <v>54.682343</v>
       </c>
       <c r="H1528" t="n">
         <v>102.4453</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1529" t="n">
         <v>103.5219</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1530" t="n">
         <v>103.7956</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.753777</v>
+        <v>55.753784</v>
       </c>
       <c r="H1533" t="n">
         <v>104.4526</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.588192</v>
+        <v>55.588188</v>
       </c>
       <c r="H1535" t="n">
         <v>104.1423</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1536" t="n">
         <v>104.0328</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1550" t="n">
         <v>101.7153</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1553" t="n">
         <v>101.9526</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1555" t="n">
         <v>104.0328</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.753777</v>
+        <v>55.753784</v>
       </c>
       <c r="H1557" t="n">
         <v>104.4526</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1564" t="n">
         <v>104.6168</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1567" t="n">
         <v>104.635</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1570" t="n">
         <v>104.8987</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1578" t="n">
         <v>109.0551</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1580" t="n">
         <v>109.6227</v>
@@ -60492,10 +60492,10 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.39616</v>
+        <v>58.396156</v>
       </c>
       <c r="H1581" t="n">
-        <v>109.403</v>
+        <v>109.4029</v>
       </c>
     </row>
     <row r="1582">
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1583" t="n">
         <v>110.7762</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1585" t="n">
         <v>110.8128</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>58.91415</v>
+        <v>58.914154</v>
       </c>
       <c r="H1591" t="n">
         <v>110.3734</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>58.835964</v>
+        <v>58.835968</v>
       </c>
       <c r="H1595" t="n">
         <v>110.2269</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>58.718685</v>
+        <v>58.718681</v>
       </c>
       <c r="H1596" t="n">
         <v>110.0072</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.793755</v>
+        <v>59.793758</v>
       </c>
       <c r="H1598" t="n">
         <v>112.0213</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.803528</v>
+        <v>59.803532</v>
       </c>
       <c r="H1600" t="n">
         <v>112.0396</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.744896</v>
+        <v>59.744892</v>
       </c>
       <c r="H1602" t="n">
         <v>111.9298</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.116276</v>
+        <v>60.11628</v>
       </c>
       <c r="H1604" t="n">
         <v>112.6255</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1606" t="n">
         <v>112.2776</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>59.852402</v>
+        <v>59.852398</v>
       </c>
       <c r="H1607" t="n">
         <v>112.1312</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>60.653816</v>
+        <v>60.65382</v>
       </c>
       <c r="H1611" t="n">
         <v>113.6326</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1613" t="n">
         <v>114.0354</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1614" t="n">
         <v>114.3101</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>61.406372</v>
+        <v>61.406376</v>
       </c>
       <c r="H1616" t="n">
         <v>115.0425</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1623" t="n">
         <v>108.0114</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1626" t="n">
         <v>108.872</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1629" t="n">
         <v>109.4665</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1648" t="n">
         <v>112.6969</v>
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1650" t="n">
         <v>114.4405</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1652" t="n">
         <v>112.55</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1654" t="n">
         <v>112.3114</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1655" t="n">
         <v>111.7057</v>
@@ -63418,10 +63418,10 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1658" t="n">
-        <v>110.4392</v>
+        <v>110.4393</v>
       </c>
     </row>
     <row r="1659">
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1661" t="n">
         <v>111.9076</v>
@@ -63570,7 +63570,7 @@
         </is>
       </c>
       <c r="G1662" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1662" t="n">
         <v>114.3855</v>
@@ -63646,7 +63646,7 @@
         </is>
       </c>
       <c r="G1664" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1664" t="n">
         <v>112.5133</v>
@@ -63722,7 +63722,7 @@
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1666" t="n">
         <v>111.4855</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1676" t="n">
         <v>115.9273</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1678" t="n">
         <v>115.4317</v>
@@ -64292,7 +64292,7 @@
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1681" t="n">
         <v>115.5602</v>
@@ -64368,7 +64368,7 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1683" t="n">
         <v>115.4317</v>
@@ -64406,7 +64406,7 @@
         </is>
       </c>
       <c r="G1684" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1684" t="n">
         <v>114.9728</v>
@@ -64558,7 +64558,7 @@
         </is>
       </c>
       <c r="G1688" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1688" t="n">
         <v>114.826</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.400002</v>
+        <v>63.509998</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.7775</v>
+        <v>118.9835</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.342636</v>
+        <v>64.342628</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19683,7 +19683,7 @@
         <v>64.54714199999999</v>
       </c>
       <c r="H507" t="n">
-        <v>100.3178</v>
+        <v>100.3179</v>
       </c>
     </row>
     <row r="508">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.44974499999999</v>
+        <v>64.449753</v>
       </c>
       <c r="H508" t="n">
         <v>100.1665</v>
@@ -19759,7 +19759,7 @@
         <v>64.741913</v>
       </c>
       <c r="H509" t="n">
-        <v>100.6205</v>
+        <v>100.6206</v>
       </c>
     </row>
     <row r="510">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.189888</v>
+        <v>65.18988</v>
       </c>
       <c r="H512" t="n">
         <v>101.3168</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.160667</v>
+        <v>65.160675</v>
       </c>
       <c r="H513" t="n">
         <v>101.2714</v>
@@ -19949,7 +19949,7 @@
         <v>65.511253</v>
       </c>
       <c r="H514" t="n">
-        <v>101.8162</v>
+        <v>101.8163</v>
       </c>
     </row>
     <row r="515">
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.121712</v>
+        <v>65.121719</v>
       </c>
       <c r="H524" t="n">
         <v>101.2108</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.339043</v>
+        <v>66.339035</v>
       </c>
       <c r="H530" t="n">
         <v>103.1028</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.212433</v>
+        <v>66.212425</v>
       </c>
       <c r="H531" t="n">
         <v>102.906</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H534" t="n">
         <v>102.6638</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H536" t="n">
         <v>103.0271</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.98844099999999</v>
+        <v>65.988457</v>
       </c>
       <c r="H537" t="n">
         <v>102.5579</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.942825</v>
+        <v>66.94283299999999</v>
       </c>
       <c r="H540" t="n">
         <v>104.0412</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H541" t="n">
         <v>105.0098</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H543" t="n">
         <v>103.7839</v>
@@ -21089,7 +21089,7 @@
         <v>66.416939</v>
       </c>
       <c r="H544" t="n">
-        <v>103.2238</v>
+        <v>103.2239</v>
       </c>
     </row>
     <row r="545">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>65.754723</v>
+        <v>65.754715</v>
       </c>
       <c r="H545" t="n">
         <v>102.1946</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>65.715767</v>
+        <v>65.71577499999999</v>
       </c>
       <c r="H546" t="n">
         <v>102.1341</v>
@@ -21200,10 +21200,10 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027412</v>
       </c>
       <c r="H547" t="n">
-        <v>102.6184</v>
+        <v>102.6185</v>
       </c>
     </row>
     <row r="548">
@@ -21241,7 +21241,7 @@
         <v>65.891068</v>
       </c>
       <c r="H548" t="n">
-        <v>102.4065</v>
+        <v>102.4066</v>
       </c>
     </row>
     <row r="549">
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.124786</v>
+        <v>66.124779</v>
       </c>
       <c r="H549" t="n">
         <v>102.7698</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.24472799999999</v>
+        <v>67.24472</v>
       </c>
       <c r="H553" t="n">
         <v>104.5104</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>66.942825</v>
+        <v>66.94283299999999</v>
       </c>
       <c r="H556" t="n">
         <v>104.0412</v>
@@ -21621,7 +21621,7 @@
         <v>67.51739499999999</v>
       </c>
       <c r="H558" t="n">
-        <v>104.9341</v>
+        <v>104.9342</v>
       </c>
     </row>
     <row r="559">
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.22524300000001</v>
+        <v>67.22525</v>
       </c>
       <c r="H561" t="n">
         <v>104.4801</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.3908</v>
+        <v>67.390793</v>
       </c>
       <c r="H563" t="n">
         <v>104.7374</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H565" t="n">
         <v>104.3893</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H568" t="n">
         <v>105.5185</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H571" t="n">
         <v>106.1122</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>68.30474100000001</v>
+        <v>68.304733</v>
       </c>
       <c r="H572" t="n">
         <v>106.1578</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H573" t="n">
         <v>106.4927</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>69.24498</v>
+        <v>69.24498699999999</v>
       </c>
       <c r="H574" t="n">
         <v>107.6191</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H577" t="n">
         <v>108.3194</v>
@@ -22381,7 +22381,7 @@
         <v>70.2342</v>
       </c>
       <c r="H578" t="n">
-        <v>109.1565</v>
+        <v>109.1566</v>
       </c>
     </row>
     <row r="579">
@@ -22419,7 +22419,7 @@
         <v>70.18523399999999</v>
       </c>
       <c r="H579" t="n">
-        <v>109.0804</v>
+        <v>109.0805</v>
       </c>
     </row>
     <row r="580">
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>71.340942</v>
+        <v>71.340935</v>
       </c>
       <c r="H582" t="n">
         <v>110.8766</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H583" t="n">
         <v>110.8005</v>
@@ -22609,7 +22609,7 @@
         <v>70.723907</v>
       </c>
       <c r="H584" t="n">
-        <v>109.9176</v>
+        <v>109.9177</v>
       </c>
     </row>
     <row r="585">
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H585" t="n">
         <v>108.8978</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H587" t="n">
         <v>110.146</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.51823400000001</v>
+        <v>70.518227</v>
       </c>
       <c r="H588" t="n">
         <v>109.598</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.4105</v>
+        <v>70.410484</v>
       </c>
       <c r="H590" t="n">
         <v>109.4305</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>70.684731</v>
+        <v>70.68472300000001</v>
       </c>
       <c r="H592" t="n">
         <v>109.8568</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H594" t="n">
         <v>111.4094</v>
@@ -23027,7 +23027,7 @@
         <v>72.37912799999999</v>
       </c>
       <c r="H595" t="n">
-        <v>112.4901</v>
+        <v>112.4902</v>
       </c>
     </row>
     <row r="596">
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H597" t="n">
         <v>112.4445</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H599" t="n">
         <v>113.9362</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H600" t="n">
         <v>114.332</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H601" t="n">
         <v>115.1997</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H602" t="n">
         <v>114.7582</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H606" t="n">
         <v>115.7781</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H607" t="n">
         <v>115.7781</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.524055</v>
+        <v>74.524063</v>
       </c>
       <c r="H609" t="n">
         <v>115.8238</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H610" t="n">
         <v>116.1434</v>
@@ -23632,10 +23632,10 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>75.14109000000001</v>
+        <v>75.141098</v>
       </c>
       <c r="H611" t="n">
-        <v>116.7827</v>
+        <v>116.7828</v>
       </c>
     </row>
     <row r="612">
@@ -23670,10 +23670,10 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>75.27821400000001</v>
+        <v>75.278206</v>
       </c>
       <c r="H612" t="n">
-        <v>116.9958</v>
+        <v>116.9959</v>
       </c>
     </row>
     <row r="613">
@@ -23746,10 +23746,10 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>75.003967</v>
+        <v>75.00398300000001</v>
       </c>
       <c r="H614" t="n">
-        <v>116.5696</v>
+        <v>116.5697</v>
       </c>
     </row>
     <row r="615">
@@ -23784,10 +23784,10 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>73.358543</v>
+        <v>73.35855100000001</v>
       </c>
       <c r="H615" t="n">
-        <v>114.0123</v>
+        <v>114.0124</v>
       </c>
     </row>
     <row r="616">
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.721931</v>
+        <v>72.721924</v>
       </c>
       <c r="H620" t="n">
         <v>113.0229</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H621" t="n">
         <v>112.5815</v>
@@ -24167,7 +24167,7 @@
         <v>72.64357</v>
       </c>
       <c r="H625" t="n">
-        <v>112.9011</v>
+        <v>112.9012</v>
       </c>
     </row>
     <row r="626">
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H626" t="n">
         <v>111.1457</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H627" t="n">
         <v>110.1207</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H629" t="n">
         <v>110.9774</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H632" t="n">
         <v>110.9774</v>
@@ -24509,7 +24509,7 @@
         <v>71.986572</v>
       </c>
       <c r="H634" t="n">
-        <v>111.88</v>
+        <v>111.8801</v>
       </c>
     </row>
     <row r="635">
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H635" t="n">
         <v>112.9663</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H637" t="n">
         <v>112.5991</v>
@@ -24696,7 +24696,7 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H639" t="n">
         <v>114.9245</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H640" t="n">
         <v>114.6644</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H642" t="n">
         <v>114.7409</v>
@@ -24886,10 +24886,10 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H644" t="n">
-        <v>114.7103</v>
+        <v>114.7104</v>
       </c>
     </row>
     <row r="645">
@@ -24927,7 +24927,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H645" t="n">
-        <v>115.6435</v>
+        <v>115.6436</v>
       </c>
     </row>
     <row r="646">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H648" t="n">
         <v>114.7409</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H651" t="n">
         <v>114.282</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H652" t="n">
         <v>114.6797</v>
@@ -25266,7 +25266,7 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H654" t="n">
         <v>115.6742</v>
@@ -25345,7 +25345,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H656" t="n">
-        <v>115.6435</v>
+        <v>115.6436</v>
       </c>
     </row>
     <row r="657">
@@ -25380,7 +25380,7 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H657" t="n">
         <v>116.7757</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H658" t="n">
         <v>115.9954</v>
@@ -25459,7 +25459,7 @@
         <v>74.457329</v>
       </c>
       <c r="H659" t="n">
-        <v>115.72</v>
+        <v>115.7201</v>
       </c>
     </row>
     <row r="660">
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H660" t="n">
         <v>115.9954</v>
@@ -25684,7 +25684,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H665" t="n">
         <v>116.7145</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H670" t="n">
         <v>119.8201</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H672" t="n">
         <v>119.0093</v>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H674" t="n">
         <v>118.5503</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H675" t="n">
         <v>118.3973</v>
@@ -26181,7 +26181,7 @@
         <v>76.908394</v>
       </c>
       <c r="H678" t="n">
-        <v>119.5294</v>
+        <v>119.5295</v>
       </c>
     </row>
     <row r="679">
@@ -26219,7 +26219,7 @@
         <v>76.918243</v>
       </c>
       <c r="H679" t="n">
-        <v>119.5447</v>
+        <v>119.5448</v>
       </c>
     </row>
     <row r="680">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="G680" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H680" t="n">
         <v>119.0399</v>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G681" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H681" t="n">
         <v>118.3361</v>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G687" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H687" t="n">
         <v>121.7784</v>
@@ -27055,7 +27055,7 @@
         <v>79.535309</v>
       </c>
       <c r="H701" t="n">
-        <v>123.6121</v>
+        <v>123.6122</v>
       </c>
     </row>
     <row r="702">
@@ -27131,7 +27131,7 @@
         <v>79.19718899999999</v>
       </c>
       <c r="H703" t="n">
-        <v>123.0866</v>
+        <v>123.0867</v>
       </c>
     </row>
     <row r="704">
@@ -27625,7 +27625,7 @@
         <v>81.066734</v>
       </c>
       <c r="H716" t="n">
-        <v>125.9922</v>
+        <v>125.9923</v>
       </c>
     </row>
     <row r="717">
@@ -27663,7 +27663,7 @@
         <v>80.68885</v>
       </c>
       <c r="H717" t="n">
-        <v>125.4049</v>
+        <v>125.405</v>
       </c>
     </row>
     <row r="718">
@@ -27739,7 +27739,7 @@
         <v>80.112076</v>
       </c>
       <c r="H719" t="n">
-        <v>124.5085</v>
+        <v>124.5086</v>
       </c>
     </row>
     <row r="720">
@@ -27777,7 +27777,7 @@
         <v>80.291077</v>
       </c>
       <c r="H720" t="n">
-        <v>124.7867</v>
+        <v>124.7868</v>
       </c>
     </row>
     <row r="721">
@@ -27815,7 +27815,7 @@
         <v>80.738579</v>
       </c>
       <c r="H721" t="n">
-        <v>125.4822</v>
+        <v>125.4823</v>
       </c>
     </row>
     <row r="722">
@@ -28005,7 +28005,7 @@
         <v>81.245735</v>
       </c>
       <c r="H726" t="n">
-        <v>126.2704</v>
+        <v>126.2705</v>
       </c>
     </row>
     <row r="727">
@@ -28043,7 +28043,7 @@
         <v>81.404854</v>
       </c>
       <c r="H727" t="n">
-        <v>126.5177</v>
+        <v>126.5178</v>
       </c>
     </row>
     <row r="728">
@@ -28119,7 +28119,7 @@
         <v>81.295464</v>
       </c>
       <c r="H729" t="n">
-        <v>126.3477</v>
+        <v>126.3478</v>
       </c>
     </row>
     <row r="730">
@@ -28195,7 +28195,7 @@
         <v>80.84796900000001</v>
       </c>
       <c r="H731" t="n">
-        <v>125.6522</v>
+        <v>125.6523</v>
       </c>
     </row>
     <row r="732">
@@ -28309,7 +28309,7 @@
         <v>80.758461</v>
       </c>
       <c r="H734" t="n">
-        <v>125.5131</v>
+        <v>125.5132</v>
       </c>
     </row>
     <row r="735">
@@ -28347,7 +28347,7 @@
         <v>80.758461</v>
       </c>
       <c r="H735" t="n">
-        <v>125.5131</v>
+        <v>125.5132</v>
       </c>
     </row>
     <row r="736">
@@ -28385,7 +28385,7 @@
         <v>81.02697000000001</v>
       </c>
       <c r="H736" t="n">
-        <v>125.9304</v>
+        <v>125.9305</v>
       </c>
     </row>
     <row r="737">
@@ -28423,7 +28423,7 @@
         <v>81.205963</v>
       </c>
       <c r="H737" t="n">
-        <v>126.2086</v>
+        <v>126.2087</v>
       </c>
     </row>
     <row r="738">
@@ -28537,7 +28537,7 @@
         <v>80.937462</v>
       </c>
       <c r="H740" t="n">
-        <v>125.7913</v>
+        <v>125.7914</v>
       </c>
     </row>
     <row r="741">
@@ -29069,7 +29069,7 @@
         <v>80.5</v>
       </c>
       <c r="H754" t="n">
-        <v>125.1114</v>
+        <v>125.1115</v>
       </c>
     </row>
     <row r="755">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.425831</v>
+        <v>53.425835</v>
       </c>
       <c r="H1511" t="n">
         <v>100.0912</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>53.075184</v>
+        <v>53.075188</v>
       </c>
       <c r="H1512" t="n">
         <v>99.43429999999999</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>53.523239</v>
+        <v>53.523243</v>
       </c>
       <c r="H1513" t="n">
         <v>100.2737</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.62064</v>
+        <v>53.620636</v>
       </c>
       <c r="H1514" t="n">
         <v>100.4562</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.497276</v>
+        <v>54.497272</v>
       </c>
       <c r="H1516" t="n">
         <v>102.0985</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.062214</v>
+        <v>55.062218</v>
       </c>
       <c r="H1518" t="n">
         <v>103.1569</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.974552</v>
+        <v>54.974556</v>
       </c>
       <c r="H1520" t="n">
         <v>102.9927</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1521" t="n">
         <v>103.7956</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.159618</v>
+        <v>55.159615</v>
       </c>
       <c r="H1522" t="n">
         <v>103.3394</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.429089</v>
+        <v>54.429092</v>
       </c>
       <c r="H1523" t="n">
         <v>101.9708</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.740784</v>
+        <v>54.740788</v>
       </c>
       <c r="H1524" t="n">
-        <v>102.5547</v>
+        <v>102.5548</v>
       </c>
     </row>
     <row r="1525">
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1527" t="n">
         <v>103.5219</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1529" t="n">
         <v>103.5219</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1530" t="n">
         <v>103.7956</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.753784</v>
+        <v>55.75378</v>
       </c>
       <c r="H1533" t="n">
         <v>104.4526</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1536" t="n">
         <v>104.0328</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.325203</v>
+        <v>55.325207</v>
       </c>
       <c r="H1538" t="n">
         <v>103.6496</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.867409</v>
+        <v>54.867413</v>
       </c>
       <c r="H1541" t="n">
         <v>102.792</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>54.351166</v>
+        <v>54.351162</v>
       </c>
       <c r="H1552" t="n">
         <v>101.8248</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1553" t="n">
         <v>101.9526</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1555" t="n">
         <v>104.0328</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.753784</v>
+        <v>55.75378</v>
       </c>
       <c r="H1557" t="n">
         <v>104.4526</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.841446</v>
+        <v>55.841442</v>
       </c>
       <c r="H1564" t="n">
         <v>104.6168</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1567" t="n">
         <v>104.635</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.54714199999999</v>
+        <v>64.547134</v>
       </c>
       <c r="H507" t="n">
-        <v>100.3179</v>
+        <v>100.3178</v>
       </c>
     </row>
     <row r="508">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.449753</v>
+        <v>64.44976</v>
       </c>
       <c r="H508" t="n">
         <v>100.1665</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.18988</v>
+        <v>65.189888</v>
       </c>
       <c r="H512" t="n">
         <v>101.3168</v>
@@ -19946,10 +19946,10 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.511253</v>
+        <v>65.511246</v>
       </c>
       <c r="H514" t="n">
-        <v>101.8163</v>
+        <v>101.8162</v>
       </c>
     </row>
     <row r="515">
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H519" t="n">
         <v>100.8173</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.939751</v>
+        <v>65.939758</v>
       </c>
       <c r="H527" t="n">
         <v>102.4822</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.066345</v>
+        <v>66.06635300000001</v>
       </c>
       <c r="H528" t="n">
         <v>102.679</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H529" t="n">
         <v>103.2087</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H532" t="n">
         <v>103.2087</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H533" t="n">
         <v>102.7244</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H535" t="n">
         <v>102.7244</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.988457</v>
+        <v>65.988449</v>
       </c>
       <c r="H537" t="n">
         <v>102.5579</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>65.57942199999999</v>
+        <v>65.579414</v>
       </c>
       <c r="H538" t="n">
         <v>101.9222</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.94283299999999</v>
+        <v>66.942825</v>
       </c>
       <c r="H540" t="n">
         <v>104.0412</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H541" t="n">
         <v>105.0098</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H542" t="n">
         <v>104.2228</v>
@@ -21200,10 +21200,10 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.027412</v>
+        <v>66.027405</v>
       </c>
       <c r="H547" t="n">
-        <v>102.6185</v>
+        <v>102.6184</v>
       </c>
     </row>
     <row r="548">
@@ -21238,10 +21238,10 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H548" t="n">
-        <v>102.4066</v>
+        <v>102.4065</v>
       </c>
     </row>
     <row r="549">
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H551" t="n">
         <v>104.132</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H554" t="n">
         <v>104.2228</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>66.94283299999999</v>
+        <v>66.942825</v>
       </c>
       <c r="H556" t="n">
         <v>104.0412</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.371323</v>
+        <v>67.371315</v>
       </c>
       <c r="H557" t="n">
         <v>104.7071</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.22525</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H561" t="n">
         <v>104.4801</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275352</v>
       </c>
       <c r="H571" t="n">
         <v>106.1122</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>68.304733</v>
+        <v>68.30474100000001</v>
       </c>
       <c r="H572" t="n">
         <v>106.1578</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>69.773865</v>
+        <v>69.773872</v>
       </c>
       <c r="H575" t="n">
         <v>108.4411</v>
@@ -22416,10 +22416,10 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.18523399999999</v>
+        <v>70.185226</v>
       </c>
       <c r="H579" t="n">
-        <v>109.0805</v>
+        <v>109.0804</v>
       </c>
     </row>
     <row r="580">
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>70.645554</v>
+        <v>70.645561</v>
       </c>
       <c r="H581" t="n">
         <v>109.7959</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>71.340935</v>
+        <v>71.340942</v>
       </c>
       <c r="H582" t="n">
         <v>110.8766</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>70.371323</v>
+        <v>70.371315</v>
       </c>
       <c r="H586" t="n">
         <v>109.3697</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>70.68472300000001</v>
+        <v>70.684731</v>
       </c>
       <c r="H592" t="n">
         <v>109.8568</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>70.890411</v>
+        <v>70.890404</v>
       </c>
       <c r="H593" t="n">
         <v>110.1764</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H594" t="n">
         <v>111.4094</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>72.37912799999999</v>
+        <v>72.37913500000001</v>
       </c>
       <c r="H595" t="n">
         <v>112.4902</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>73.86784400000001</v>
+        <v>73.867851</v>
       </c>
       <c r="H605" t="n">
         <v>114.8039</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H606" t="n">
         <v>115.7781</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H607" t="n">
         <v>115.7781</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.524063</v>
+        <v>74.524055</v>
       </c>
       <c r="H609" t="n">
         <v>115.8238</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H617" t="n">
         <v>113.6318</v>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.721924</v>
+        <v>72.721931</v>
       </c>
       <c r="H620" t="n">
         <v>113.0229</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H621" t="n">
         <v>112.5815</v>
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>72.55542800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H622" t="n">
         <v>112.7642</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H624" t="n">
         <v>113.6318</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.425835</v>
+        <v>53.425831</v>
       </c>
       <c r="H1511" t="n">
         <v>100.0912</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>53.075188</v>
+        <v>53.075184</v>
       </c>
       <c r="H1512" t="n">
         <v>99.43429999999999</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>53.523243</v>
+        <v>53.523239</v>
       </c>
       <c r="H1513" t="n">
         <v>100.2737</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.620636</v>
+        <v>53.62064</v>
       </c>
       <c r="H1514" t="n">
         <v>100.4562</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.844673</v>
+        <v>53.844669</v>
       </c>
       <c r="H1515" t="n">
         <v>100.8759</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.799221</v>
+        <v>54.799225</v>
       </c>
       <c r="H1517" t="n">
         <v>102.6642</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.062218</v>
+        <v>55.062214</v>
       </c>
       <c r="H1518" t="n">
         <v>103.1569</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>55.042732</v>
+        <v>55.042728</v>
       </c>
       <c r="H1519" t="n">
         <v>103.1204</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.974556</v>
+        <v>54.974545</v>
       </c>
       <c r="H1520" t="n">
         <v>102.9927</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.159615</v>
+        <v>55.159618</v>
       </c>
       <c r="H1522" t="n">
         <v>103.3394</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.740788</v>
+        <v>54.740784</v>
       </c>
       <c r="H1524" t="n">
-        <v>102.5548</v>
+        <v>102.5547</v>
       </c>
     </row>
     <row r="1525">
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.536236</v>
+        <v>54.536232</v>
       </c>
       <c r="H1525" t="n">
         <v>102.1715</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1527" t="n">
         <v>103.5219</v>
@@ -58478,10 +58478,10 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.682343</v>
+        <v>54.682335</v>
       </c>
       <c r="H1528" t="n">
-        <v>102.4453</v>
+        <v>102.4452</v>
       </c>
     </row>
     <row r="1529">
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1529" t="n">
         <v>103.5219</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1533" t="n">
         <v>104.4526</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1534" t="n">
         <v>104.2336</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.588188</v>
+        <v>55.588192</v>
       </c>
       <c r="H1535" t="n">
         <v>104.1423</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1537" t="n">
         <v>103.5949</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.325207</v>
+        <v>55.325203</v>
       </c>
       <c r="H1538" t="n">
         <v>103.6496</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.867413</v>
+        <v>54.867409</v>
       </c>
       <c r="H1541" t="n">
         <v>102.792</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1543" t="n">
         <v>103.7591</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>56.143391</v>
+        <v>56.143394</v>
       </c>
       <c r="H1546" t="n">
         <v>105.1825</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1549" t="n">
         <v>101.8066</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1550" t="n">
         <v>101.7153</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>54.351162</v>
+        <v>54.351166</v>
       </c>
       <c r="H1552" t="n">
         <v>101.8248</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1553" t="n">
         <v>101.9526</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.877148</v>
+        <v>54.877144</v>
       </c>
       <c r="H1554" t="n">
         <v>102.8102</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1557" t="n">
         <v>104.4526</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1559" t="n">
         <v>104.2336</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.958328</v>
+        <v>55.958332</v>
       </c>
       <c r="H1561" t="n">
         <v>104.8358</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1564" t="n">
         <v>104.6168</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.870663</v>
+        <v>55.870667</v>
       </c>
       <c r="H1565" t="n">
         <v>104.6715</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.172611</v>
+        <v>56.172615</v>
       </c>
       <c r="H1566" t="n">
         <v>105.2372</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1569" t="n">
         <v>105.0268</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1570" t="n">
         <v>104.8987</v>
@@ -60112,10 +60112,10 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.558758</v>
+        <v>56.558754</v>
       </c>
       <c r="H1571" t="n">
-        <v>105.9607</v>
+        <v>105.9606</v>
       </c>
     </row>
     <row r="1572">
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1572" t="n">
         <v>106.3818</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.676041</v>
+        <v>56.676044</v>
       </c>
       <c r="H1573" t="n">
         <v>106.1804</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1575" t="n">
         <v>106.7297</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>57.692474</v>
+        <v>57.692471</v>
       </c>
       <c r="H1577" t="n">
         <v>108.0846</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1578" t="n">
         <v>109.0551</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1580" t="n">
         <v>109.6227</v>
@@ -60492,10 +60492,10 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.396156</v>
+        <v>58.39616</v>
       </c>
       <c r="H1581" t="n">
-        <v>109.4029</v>
+        <v>109.403</v>
       </c>
     </row>
     <row r="1582">
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1582" t="n">
         <v>110.5931</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>59.129169</v>
+        <v>59.129166</v>
       </c>
       <c r="H1583" t="n">
         <v>110.7762</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1585" t="n">
         <v>110.8128</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1586" t="n">
         <v>111.4537</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1587" t="n">
         <v>111.472</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1589" t="n">
         <v>109.1832</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>58.914154</v>
+        <v>58.91415</v>
       </c>
       <c r="H1591" t="n">
         <v>110.3734</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>58.953243</v>
+        <v>58.953247</v>
       </c>
       <c r="H1593" t="n">
         <v>110.4466</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>58.835968</v>
+        <v>58.835964</v>
       </c>
       <c r="H1595" t="n">
         <v>110.2269</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>58.718681</v>
+        <v>58.718685</v>
       </c>
       <c r="H1596" t="n">
         <v>110.0072</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.168259</v>
+        <v>59.168262</v>
       </c>
       <c r="H1597" t="n">
         <v>110.8495</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.246449</v>
+        <v>59.246445</v>
       </c>
       <c r="H1601" t="n">
         <v>110.9959</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1605" t="n">
         <v>112.7903</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>59.852398</v>
+        <v>59.852402</v>
       </c>
       <c r="H1607" t="n">
         <v>112.1312</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1608" t="n">
         <v>112.296</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1609" t="n">
         <v>112.9002</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>61.406376</v>
+        <v>61.406372</v>
       </c>
       <c r="H1616" t="n">
         <v>115.0425</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1620" t="n">
         <v>111.2706</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>58.581852</v>
+        <v>58.581856</v>
       </c>
       <c r="H1621" t="n">
         <v>109.7508</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1622" t="n">
         <v>108.7621</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1623" t="n">
         <v>108.0114</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1624" t="n">
         <v>110.1354</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1625" t="n">
         <v>109.5128</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.75</v>
+        <v>35.244999</v>
       </c>
       <c r="H253" t="n">
-        <v>116.8683</v>
+        <v>115.2174</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.93</v>
+        <v>49.220001</v>
       </c>
       <c r="H504" t="n">
-        <v>133.2879</v>
+        <v>134.0779</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.342636</v>
+        <v>64.342628</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.50818599999999</v>
+        <v>64.508179</v>
       </c>
       <c r="H506" t="n">
         <v>100.2573</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.547134</v>
+        <v>64.54715</v>
       </c>
       <c r="H507" t="n">
-        <v>100.3178</v>
+        <v>100.3179</v>
       </c>
     </row>
     <row r="508">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.44974499999999</v>
+        <v>64.44976</v>
       </c>
       <c r="H508" t="n">
         <v>100.1665</v>
@@ -19756,10 +19756,10 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.74191999999999</v>
+        <v>64.741905</v>
       </c>
       <c r="H509" t="n">
-        <v>100.6206</v>
+        <v>100.6205</v>
       </c>
     </row>
     <row r="510">
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.67375199999999</v>
+        <v>64.673744</v>
       </c>
       <c r="H510" t="n">
         <v>100.5146</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.664001</v>
+        <v>64.66400899999999</v>
       </c>
       <c r="H511" t="n">
         <v>100.4995</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.18988</v>
+        <v>65.189888</v>
       </c>
       <c r="H512" t="n">
         <v>101.3168</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H513" t="n">
         <v>101.2714</v>
@@ -19949,7 +19949,7 @@
         <v>65.511253</v>
       </c>
       <c r="H514" t="n">
-        <v>101.8162</v>
+        <v>101.8163</v>
       </c>
     </row>
     <row r="515">
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H517" t="n">
         <v>102.6033</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H519" t="n">
         <v>100.8173</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H521" t="n">
         <v>101.1957</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H524" t="n">
         <v>101.2108</v>
@@ -20364,10 +20364,10 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.842361</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H525" t="n">
-        <v>102.3308</v>
+        <v>102.3309</v>
       </c>
     </row>
     <row r="526">
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H526" t="n">
         <v>102.6033</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H534" t="n">
         <v>102.6638</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H536" t="n">
         <v>103.0271</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H543" t="n">
         <v>103.7839</v>
@@ -21089,7 +21089,7 @@
         <v>66.416939</v>
       </c>
       <c r="H544" t="n">
-        <v>103.2238</v>
+        <v>103.2239</v>
       </c>
     </row>
     <row r="545">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>65.754723</v>
+        <v>65.754715</v>
       </c>
       <c r="H545" t="n">
         <v>102.1946</v>
@@ -21241,7 +21241,7 @@
         <v>65.891068</v>
       </c>
       <c r="H548" t="n">
-        <v>102.4065</v>
+        <v>102.4066</v>
       </c>
     </row>
     <row r="549">
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H551" t="n">
         <v>104.132</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.371323</v>
+        <v>67.37133</v>
       </c>
       <c r="H557" t="n">
         <v>104.7071</v>
@@ -21618,10 +21618,10 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.51739499999999</v>
+        <v>67.51741</v>
       </c>
       <c r="H558" t="n">
-        <v>104.9341</v>
+        <v>104.9342</v>
       </c>
     </row>
     <row r="559">
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.283669</v>
+        <v>67.283676</v>
       </c>
       <c r="H559" t="n">
         <v>104.5709</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.293419</v>
+        <v>67.293404</v>
       </c>
       <c r="H560" t="n">
         <v>104.586</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.3908</v>
+        <v>67.390793</v>
       </c>
       <c r="H563" t="n">
         <v>104.7374</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H564" t="n">
         <v>105.3277</v>
@@ -21922,10 +21922,10 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.23497</v>
+        <v>67.234993</v>
       </c>
       <c r="H566" t="n">
-        <v>104.4952</v>
+        <v>104.4953</v>
       </c>
     </row>
     <row r="567">
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.619141</v>
+        <v>67.619148</v>
       </c>
       <c r="H567" t="n">
         <v>105.0923</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H568" t="n">
         <v>105.5185</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.815033</v>
+        <v>67.81502500000001</v>
       </c>
       <c r="H569" t="n">
         <v>105.3967</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H573" t="n">
         <v>106.4927</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H575" t="n">
         <v>108.4411</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>69.48004899999999</v>
+        <v>69.480057</v>
       </c>
       <c r="H576" t="n">
         <v>107.9845</v>
@@ -22340,10 +22340,10 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H577" t="n">
-        <v>108.3193</v>
+        <v>108.3194</v>
       </c>
     </row>
     <row r="578">
@@ -22381,7 +22381,7 @@
         <v>70.2342</v>
       </c>
       <c r="H578" t="n">
-        <v>109.1565</v>
+        <v>109.1566</v>
       </c>
     </row>
     <row r="579">
@@ -22416,10 +22416,10 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H579" t="n">
-        <v>109.0804</v>
+        <v>109.0805</v>
       </c>
     </row>
     <row r="580">
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.273376</v>
+        <v>70.273369</v>
       </c>
       <c r="H580" t="n">
         <v>109.2174</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H583" t="n">
         <v>110.8005</v>
@@ -22606,10 +22606,10 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.723907</v>
+        <v>70.72391500000001</v>
       </c>
       <c r="H584" t="n">
-        <v>109.9176</v>
+        <v>109.9177</v>
       </c>
     </row>
     <row r="585">
@@ -22682,10 +22682,10 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H586" t="n">
-        <v>109.3696</v>
+        <v>109.3697</v>
       </c>
     </row>
     <row r="587">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H587" t="n">
         <v>110.146</v>
@@ -23027,7 +23027,7 @@
         <v>72.37912799999999</v>
       </c>
       <c r="H595" t="n">
-        <v>112.4901</v>
+        <v>112.4902</v>
       </c>
     </row>
     <row r="596">
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H597" t="n">
         <v>112.4445</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.201836</v>
+        <v>73.201843</v>
       </c>
       <c r="H598" t="n">
         <v>113.7688</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H599" t="n">
         <v>113.9362</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H601" t="n">
         <v>115.1997</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>73.828667</v>
+        <v>73.82867400000001</v>
       </c>
       <c r="H603" t="n">
         <v>114.743</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H605" t="n">
         <v>114.8039</v>
@@ -23556,10 +23556,10 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H609" t="n">
-        <v>115.8237</v>
+        <v>115.8238</v>
       </c>
     </row>
     <row r="610">
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H610" t="n">
         <v>116.1434</v>
@@ -23673,7 +23673,7 @@
         <v>75.27821400000001</v>
       </c>
       <c r="H612" t="n">
-        <v>116.9958</v>
+        <v>116.9959</v>
       </c>
     </row>
     <row r="613">
@@ -23787,7 +23787,7 @@
         <v>73.35855100000001</v>
       </c>
       <c r="H615" t="n">
-        <v>114.0123</v>
+        <v>114.0124</v>
       </c>
     </row>
     <row r="616">
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.721931</v>
+        <v>72.72191599999999</v>
       </c>
       <c r="H620" t="n">
         <v>113.0229</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H621" t="n">
         <v>112.5815</v>
@@ -24050,10 +24050,10 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H622" t="n">
-        <v>112.7641</v>
+        <v>112.7642</v>
       </c>
     </row>
     <row r="623">
@@ -24164,10 +24164,10 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>72.64357800000001</v>
+        <v>72.643562</v>
       </c>
       <c r="H625" t="n">
-        <v>112.9012</v>
+        <v>112.9011</v>
       </c>
     </row>
     <row r="626">
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H626" t="n">
         <v>111.1457</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H627" t="n">
         <v>110.1207</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H629" t="n">
         <v>110.9774</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H632" t="n">
         <v>110.9774</v>
@@ -24509,7 +24509,7 @@
         <v>71.986572</v>
       </c>
       <c r="H634" t="n">
-        <v>111.88</v>
+        <v>111.8801</v>
       </c>
     </row>
     <row r="635">
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H635" t="n">
         <v>112.9663</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H637" t="n">
         <v>112.5991</v>
@@ -24696,7 +24696,7 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H639" t="n">
         <v>114.9245</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H640" t="n">
         <v>114.6644</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H642" t="n">
         <v>114.7409</v>
@@ -24886,10 +24886,10 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H644" t="n">
-        <v>114.7103</v>
+        <v>114.7104</v>
       </c>
     </row>
     <row r="645">
@@ -24927,7 +24927,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H645" t="n">
-        <v>115.6435</v>
+        <v>115.6436</v>
       </c>
     </row>
     <row r="646">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H648" t="n">
         <v>114.7409</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H651" t="n">
         <v>114.282</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H652" t="n">
         <v>114.6797</v>
@@ -25266,7 +25266,7 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H654" t="n">
         <v>115.6742</v>
@@ -25345,7 +25345,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H656" t="n">
-        <v>115.6435</v>
+        <v>115.6436</v>
       </c>
     </row>
     <row r="657">
@@ -25380,7 +25380,7 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H657" t="n">
         <v>116.7757</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H658" t="n">
         <v>115.9954</v>
@@ -25459,7 +25459,7 @@
         <v>74.457329</v>
       </c>
       <c r="H659" t="n">
-        <v>115.72</v>
+        <v>115.7201</v>
       </c>
     </row>
     <row r="660">
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H660" t="n">
         <v>115.9954</v>
@@ -25684,7 +25684,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H665" t="n">
         <v>116.7145</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H670" t="n">
         <v>119.8201</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H672" t="n">
         <v>119.0093</v>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H674" t="n">
         <v>118.5503</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H675" t="n">
         <v>118.3973</v>
@@ -26181,7 +26181,7 @@
         <v>76.908394</v>
       </c>
       <c r="H678" t="n">
-        <v>119.5294</v>
+        <v>119.5295</v>
       </c>
     </row>
     <row r="679">
@@ -26219,7 +26219,7 @@
         <v>76.918243</v>
       </c>
       <c r="H679" t="n">
-        <v>119.5447</v>
+        <v>119.5448</v>
       </c>
     </row>
     <row r="680">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="G680" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H680" t="n">
         <v>119.0399</v>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G681" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H681" t="n">
         <v>118.3361</v>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G687" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H687" t="n">
         <v>121.7784</v>
@@ -27055,7 +27055,7 @@
         <v>79.535309</v>
       </c>
       <c r="H701" t="n">
-        <v>123.6121</v>
+        <v>123.6122</v>
       </c>
     </row>
     <row r="702">
@@ -27131,7 +27131,7 @@
         <v>79.19718899999999</v>
       </c>
       <c r="H703" t="n">
-        <v>123.0866</v>
+        <v>123.0867</v>
       </c>
     </row>
     <row r="704">
@@ -27625,7 +27625,7 @@
         <v>81.066734</v>
       </c>
       <c r="H716" t="n">
-        <v>125.9922</v>
+        <v>125.9923</v>
       </c>
     </row>
     <row r="717">
@@ -27663,7 +27663,7 @@
         <v>80.68885</v>
       </c>
       <c r="H717" t="n">
-        <v>125.4049</v>
+        <v>125.405</v>
       </c>
     </row>
     <row r="718">
@@ -27739,7 +27739,7 @@
         <v>80.112076</v>
       </c>
       <c r="H719" t="n">
-        <v>124.5085</v>
+        <v>124.5086</v>
       </c>
     </row>
     <row r="720">
@@ -27777,7 +27777,7 @@
         <v>80.291077</v>
       </c>
       <c r="H720" t="n">
-        <v>124.7867</v>
+        <v>124.7868</v>
       </c>
     </row>
     <row r="721">
@@ -27815,7 +27815,7 @@
         <v>80.738579</v>
       </c>
       <c r="H721" t="n">
-        <v>125.4822</v>
+        <v>125.4823</v>
       </c>
     </row>
     <row r="722">
@@ -28005,7 +28005,7 @@
         <v>81.245735</v>
       </c>
       <c r="H726" t="n">
-        <v>126.2704</v>
+        <v>126.2705</v>
       </c>
     </row>
     <row r="727">
@@ -28043,7 +28043,7 @@
         <v>81.404854</v>
       </c>
       <c r="H727" t="n">
-        <v>126.5177</v>
+        <v>126.5178</v>
       </c>
     </row>
     <row r="728">
@@ -28119,7 +28119,7 @@
         <v>81.295464</v>
       </c>
       <c r="H729" t="n">
-        <v>126.3477</v>
+        <v>126.3478</v>
       </c>
     </row>
     <row r="730">
@@ -28195,7 +28195,7 @@
         <v>80.84796900000001</v>
       </c>
       <c r="H731" t="n">
-        <v>125.6522</v>
+        <v>125.6523</v>
       </c>
     </row>
     <row r="732">
@@ -28309,7 +28309,7 @@
         <v>80.758461</v>
       </c>
       <c r="H734" t="n">
-        <v>125.5131</v>
+        <v>125.5132</v>
       </c>
     </row>
     <row r="735">
@@ -28347,7 +28347,7 @@
         <v>80.758461</v>
       </c>
       <c r="H735" t="n">
-        <v>125.5131</v>
+        <v>125.5132</v>
       </c>
     </row>
     <row r="736">
@@ -28385,7 +28385,7 @@
         <v>81.02697000000001</v>
       </c>
       <c r="H736" t="n">
-        <v>125.9304</v>
+        <v>125.9305</v>
       </c>
     </row>
     <row r="737">
@@ -28423,7 +28423,7 @@
         <v>81.205963</v>
       </c>
       <c r="H737" t="n">
-        <v>126.2086</v>
+        <v>126.2087</v>
       </c>
     </row>
     <row r="738">
@@ -28537,7 +28537,7 @@
         <v>80.937462</v>
       </c>
       <c r="H740" t="n">
-        <v>125.7913</v>
+        <v>125.7914</v>
       </c>
     </row>
     <row r="741">
@@ -29069,7 +29069,7 @@
         <v>80.5</v>
       </c>
       <c r="H754" t="n">
-        <v>125.1114</v>
+        <v>125.1115</v>
       </c>
     </row>
     <row r="755">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.099998</v>
+        <v>81.040001</v>
       </c>
       <c r="H755" t="n">
-        <v>126.0439</v>
+        <v>125.9507</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>129.279999</v>
+        <v>129.360001</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.6083</v>
+        <v>120.6829</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>129.279999</v>
+        <v>129.360001</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.6083</v>
+        <v>120.6829</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>129.279999</v>
+        <v>129.360001</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.6083</v>
+        <v>120.6829</v>
       </c>
     </row>
     <row r="1509">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.425831</v>
+        <v>53.425835</v>
       </c>
       <c r="H1511" t="n">
         <v>100.0912</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>53.075184</v>
+        <v>53.075188</v>
       </c>
       <c r="H1512" t="n">
         <v>99.43429999999999</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.620644</v>
+        <v>53.62064</v>
       </c>
       <c r="H1514" t="n">
         <v>100.4562</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.497276</v>
+        <v>54.497272</v>
       </c>
       <c r="H1516" t="n">
         <v>102.0985</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.062214</v>
+        <v>55.062218</v>
       </c>
       <c r="H1518" t="n">
         <v>103.1569</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>55.042728</v>
+        <v>55.042732</v>
       </c>
       <c r="H1519" t="n">
         <v>103.1204</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.974548</v>
+        <v>54.974552</v>
       </c>
       <c r="H1520" t="n">
         <v>102.9927</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1521" t="n">
         <v>103.7956</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.74078</v>
+        <v>54.740784</v>
       </c>
       <c r="H1524" t="n">
         <v>102.5547</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.536232</v>
+        <v>54.536236</v>
       </c>
       <c r="H1525" t="n">
         <v>102.1715</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.257015</v>
+        <v>55.257019</v>
       </c>
       <c r="H1527" t="n">
         <v>103.5219</v>
@@ -58478,10 +58478,10 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.682335</v>
+        <v>54.682343</v>
       </c>
       <c r="H1528" t="n">
-        <v>102.4452</v>
+        <v>102.4453</v>
       </c>
     </row>
     <row r="1529">
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.257015</v>
+        <v>55.257019</v>
       </c>
       <c r="H1529" t="n">
         <v>103.5219</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1530" t="n">
         <v>103.7956</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.588196</v>
+        <v>55.588188</v>
       </c>
       <c r="H1535" t="n">
         <v>104.1423</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1536" t="n">
         <v>104.0328</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1537" t="n">
         <v>103.5949</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.867413</v>
+        <v>54.867409</v>
       </c>
       <c r="H1541" t="n">
         <v>102.792</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>56.104431</v>
+        <v>56.104427</v>
       </c>
       <c r="H1544" t="n">
         <v>105.1095</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>56.523266</v>
+        <v>56.523262</v>
       </c>
       <c r="H1545" t="n">
         <v>105.8942</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>56.143391</v>
+        <v>56.143387</v>
       </c>
       <c r="H1546" t="n">
         <v>105.1825</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.60767</v>
+        <v>55.607674</v>
       </c>
       <c r="H1547" t="n">
         <v>104.1788</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1550" t="n">
         <v>101.7153</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1551" t="n">
         <v>102.0803</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>54.35117</v>
+        <v>54.351166</v>
       </c>
       <c r="H1552" t="n">
         <v>101.8248</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1553" t="n">
         <v>101.9526</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1555" t="n">
         <v>104.0328</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1556" t="n">
         <v>104.1058</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1558" t="n">
         <v>104.1058</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.987545</v>
+        <v>55.987549</v>
       </c>
       <c r="H1562" t="n">
         <v>104.8905</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.870663</v>
+        <v>55.870659</v>
       </c>
       <c r="H1565" t="n">
         <v>104.6715</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.172615</v>
+        <v>56.172611</v>
       </c>
       <c r="H1566" t="n">
         <v>105.2372</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1567" t="n">
         <v>104.635</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1568" t="n">
         <v>105.4663</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1569" t="n">
         <v>105.0268</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1570" t="n">
         <v>104.8987</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.676037</v>
+        <v>56.676041</v>
       </c>
       <c r="H1573" t="n">
         <v>106.1804</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1575" t="n">
         <v>106.7297</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1578" t="n">
         <v>109.0551</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1579" t="n">
         <v>109.6593</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1580" t="n">
         <v>109.6227</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1582" t="n">
         <v>110.5931</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1583" t="n">
         <v>110.7762</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1586" t="n">
         <v>111.4537</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1587" t="n">
         <v>111.472</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.259335</v>
+        <v>58.259331</v>
       </c>
       <c r="H1590" t="n">
         <v>109.1466</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1592" t="n">
         <v>110.2818</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.155376</v>
+        <v>60.155373</v>
       </c>
       <c r="H1603" t="n">
         <v>112.6988</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1605" t="n">
         <v>112.7903</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1606" t="n">
         <v>112.2776</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1608" t="n">
         <v>112.296</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1609" t="n">
         <v>112.9002</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.956791</v>
+        <v>60.956799</v>
       </c>
       <c r="H1610" t="n">
         <v>114.2002</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>61.20113</v>
+        <v>61.201126</v>
       </c>
       <c r="H1612" t="n">
         <v>114.658</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1613" t="n">
         <v>114.0354</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1614" t="n">
         <v>114.3101</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>61.474789</v>
+        <v>61.474785</v>
       </c>
       <c r="H1615" t="n">
         <v>115.1706</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>61.445469</v>
+        <v>61.445465</v>
       </c>
       <c r="H1617" t="n">
         <v>115.1157</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.640491</v>
+        <v>58.640495</v>
       </c>
       <c r="H1619" t="n">
         <v>109.8607</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1620" t="n">
         <v>111.2706</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1622" t="n">
         <v>108.7621</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1623" t="n">
         <v>108.0114</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1624" t="n">
         <v>110.1354</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1625" t="n">
         <v>109.5128</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1626" t="n">
         <v>108.872</v>
@@ -62240,7 +62240,7 @@
         </is>
       </c>
       <c r="G1627" t="n">
-        <v>57.790207</v>
+        <v>57.790211</v>
       </c>
       <c r="H1627" t="n">
         <v>108.2677</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1629" t="n">
         <v>109.4665</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1648" t="n">
         <v>112.6969</v>
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1650" t="n">
         <v>114.4405</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1652" t="n">
         <v>112.55</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1654" t="n">
         <v>112.3114</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1655" t="n">
         <v>111.7057</v>
@@ -63418,10 +63418,10 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1658" t="n">
-        <v>110.4392</v>
+        <v>110.4393</v>
       </c>
     </row>
     <row r="1659">
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1661" t="n">
         <v>111.9076</v>
@@ -63570,7 +63570,7 @@
         </is>
       </c>
       <c r="G1662" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1662" t="n">
         <v>114.3855</v>
@@ -63646,7 +63646,7 @@
         </is>
       </c>
       <c r="G1664" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1664" t="n">
         <v>112.5133</v>
@@ -63722,7 +63722,7 @@
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1666" t="n">
         <v>111.4855</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1676" t="n">
         <v>115.9273</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1678" t="n">
         <v>115.4317</v>
@@ -64292,7 +64292,7 @@
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1681" t="n">
         <v>115.5602</v>
@@ -64368,7 +64368,7 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1683" t="n">
         <v>115.4317</v>
@@ -64406,7 +64406,7 @@
         </is>
       </c>
       <c r="G1684" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1684" t="n">
         <v>114.9728</v>
@@ -64558,7 +64558,7 @@
         </is>
       </c>
       <c r="G1688" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1688" t="n">
         <v>114.826</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.779999</v>
+        <v>63.650002</v>
       </c>
       <c r="H1760" t="n">
-        <v>119.4894</v>
+        <v>119.2458</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.244999</v>
+        <v>35.044998</v>
       </c>
       <c r="H253" t="n">
-        <v>115.2174</v>
+        <v>114.5636</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>49.220001</v>
+        <v>49.189999</v>
       </c>
       <c r="H504" t="n">
-        <v>134.0779</v>
+        <v>133.9962</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.342628</v>
+        <v>64.342636</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.54715</v>
+        <v>64.54714199999999</v>
       </c>
       <c r="H507" t="n">
-        <v>100.3179</v>
+        <v>100.3178</v>
       </c>
     </row>
     <row r="508">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.44976</v>
+        <v>64.44974499999999</v>
       </c>
       <c r="H508" t="n">
         <v>100.1665</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.741905</v>
+        <v>64.741913</v>
       </c>
       <c r="H509" t="n">
         <v>100.6205</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.66400899999999</v>
+        <v>64.664001</v>
       </c>
       <c r="H511" t="n">
         <v>100.4995</v>
@@ -19949,7 +19949,7 @@
         <v>65.511253</v>
       </c>
       <c r="H514" t="n">
-        <v>101.8163</v>
+        <v>101.8162</v>
       </c>
     </row>
     <row r="515">
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>66.01767</v>
+        <v>66.017662</v>
       </c>
       <c r="H517" t="n">
         <v>102.6033</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H518" t="n">
         <v>102.4368</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H519" t="n">
         <v>100.8173</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.121712</v>
+        <v>65.121719</v>
       </c>
       <c r="H524" t="n">
         <v>101.2108</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.01767</v>
+        <v>66.017662</v>
       </c>
       <c r="H526" t="n">
         <v>102.6033</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.939751</v>
+        <v>65.939758</v>
       </c>
       <c r="H527" t="n">
         <v>102.4822</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.407196</v>
+        <v>66.407211</v>
       </c>
       <c r="H529" t="n">
         <v>103.2087</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.212433</v>
+        <v>66.212425</v>
       </c>
       <c r="H531" t="n">
         <v>102.906</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.407196</v>
+        <v>66.407211</v>
       </c>
       <c r="H532" t="n">
         <v>103.2087</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H534" t="n">
         <v>102.6638</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.988449</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H537" t="n">
         <v>102.5579</v>
@@ -20934,10 +20934,10 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H540" t="n">
-        <v>104.0412</v>
+        <v>104.0411</v>
       </c>
     </row>
     <row r="541">
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H541" t="n">
         <v>105.0098</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H543" t="n">
         <v>103.7839</v>
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.416939</v>
+        <v>66.41693100000001</v>
       </c>
       <c r="H544" t="n">
-        <v>103.2239</v>
+        <v>103.2238</v>
       </c>
     </row>
     <row r="545">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>65.754715</v>
+        <v>65.754723</v>
       </c>
       <c r="H545" t="n">
         <v>102.1946</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H547" t="n">
         <v>102.6184</v>
@@ -21241,7 +21241,7 @@
         <v>65.891068</v>
       </c>
       <c r="H548" t="n">
-        <v>102.4066</v>
+        <v>102.4065</v>
       </c>
     </row>
     <row r="549">
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.124786</v>
+        <v>66.12479399999999</v>
       </c>
       <c r="H549" t="n">
         <v>102.7698</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.387726</v>
+        <v>66.387733</v>
       </c>
       <c r="H550" t="n">
         <v>103.1784</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H551" t="n">
         <v>104.132</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.87464900000001</v>
+        <v>66.874657</v>
       </c>
       <c r="H555" t="n">
         <v>103.9352</v>
@@ -21542,10 +21542,10 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H556" t="n">
-        <v>104.0412</v>
+        <v>104.0411</v>
       </c>
     </row>
     <row r="557">
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.37133</v>
+        <v>67.371323</v>
       </c>
       <c r="H557" t="n">
         <v>104.7071</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.51741</v>
+        <v>67.517403</v>
       </c>
       <c r="H558" t="n">
         <v>104.9342</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.283676</v>
+        <v>67.283661</v>
       </c>
       <c r="H559" t="n">
         <v>104.5709</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.293404</v>
+        <v>67.29341100000001</v>
       </c>
       <c r="H560" t="n">
         <v>104.586</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H562" t="n">
         <v>104.8736</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.770599</v>
+        <v>67.77059199999999</v>
       </c>
       <c r="H564" t="n">
         <v>105.3277</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H565" t="n">
         <v>104.3893</v>
@@ -21922,10 +21922,10 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.234993</v>
+        <v>67.234978</v>
       </c>
       <c r="H566" t="n">
-        <v>104.4953</v>
+        <v>104.4952</v>
       </c>
     </row>
     <row r="567">
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.619148</v>
+        <v>67.619141</v>
       </c>
       <c r="H567" t="n">
         <v>105.0923</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H568" t="n">
         <v>105.5185</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>67.81502500000001</v>
+        <v>67.815033</v>
       </c>
       <c r="H569" t="n">
         <v>105.3967</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H571" t="n">
         <v>106.1122</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H573" t="n">
         <v>106.4927</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H574" t="n">
         <v>107.6191</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>69.480057</v>
+        <v>69.48004899999999</v>
       </c>
       <c r="H576" t="n">
         <v>107.9845</v>
@@ -22381,7 +22381,7 @@
         <v>70.2342</v>
       </c>
       <c r="H578" t="n">
-        <v>109.1566</v>
+        <v>109.1565</v>
       </c>
     </row>
     <row r="579">
@@ -22419,7 +22419,7 @@
         <v>70.18523399999999</v>
       </c>
       <c r="H579" t="n">
-        <v>109.0805</v>
+        <v>109.0804</v>
       </c>
     </row>
     <row r="580">
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.273369</v>
+        <v>70.273376</v>
       </c>
       <c r="H580" t="n">
         <v>109.2174</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H583" t="n">
         <v>110.8005</v>
@@ -22606,10 +22606,10 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.72391500000001</v>
+        <v>70.723907</v>
       </c>
       <c r="H584" t="n">
-        <v>109.9177</v>
+        <v>109.9176</v>
       </c>
     </row>
     <row r="585">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H587" t="n">
         <v>110.146</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.410492</v>
+        <v>70.4105</v>
       </c>
       <c r="H590" t="n">
         <v>109.4305</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H594" t="n">
         <v>111.4094</v>
@@ -23027,7 +23027,7 @@
         <v>72.37912799999999</v>
       </c>
       <c r="H595" t="n">
-        <v>112.4902</v>
+        <v>112.4901</v>
       </c>
     </row>
     <row r="596">
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H596" t="n">
         <v>113.2665</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H597" t="n">
         <v>112.4445</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.201843</v>
+        <v>73.201836</v>
       </c>
       <c r="H598" t="n">
         <v>113.7688</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H599" t="n">
         <v>113.9362</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H600" t="n">
         <v>114.332</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H601" t="n">
         <v>115.1997</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H602" t="n">
         <v>114.7582</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>73.82867400000001</v>
+        <v>73.828667</v>
       </c>
       <c r="H603" t="n">
         <v>114.743</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H610" t="n">
         <v>116.1434</v>
@@ -23673,7 +23673,7 @@
         <v>75.27821400000001</v>
       </c>
       <c r="H612" t="n">
-        <v>116.9959</v>
+        <v>116.9958</v>
       </c>
     </row>
     <row r="613">
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H614" t="n">
         <v>116.5696</v>
@@ -23784,10 +23784,10 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H615" t="n">
-        <v>114.0124</v>
+        <v>114.0123</v>
       </c>
     </row>
     <row r="616">
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.72191599999999</v>
+        <v>72.721931</v>
       </c>
       <c r="H620" t="n">
         <v>113.0229</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H621" t="n">
         <v>112.5815</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>72.643562</v>
+        <v>72.64357</v>
       </c>
       <c r="H625" t="n">
         <v>112.9011</v>
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H626" t="n">
         <v>111.1457</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H627" t="n">
         <v>110.1207</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H629" t="n">
         <v>110.9774</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H632" t="n">
         <v>110.9774</v>
@@ -24509,7 +24509,7 @@
         <v>71.986572</v>
       </c>
       <c r="H634" t="n">
-        <v>111.8801</v>
+        <v>111.88</v>
       </c>
     </row>
     <row r="635">
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H635" t="n">
         <v>112.9663</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H637" t="n">
         <v>112.5991</v>
@@ -24696,7 +24696,7 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H639" t="n">
         <v>114.9245</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H640" t="n">
         <v>114.6644</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H642" t="n">
         <v>114.7409</v>
@@ -24886,10 +24886,10 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H644" t="n">
-        <v>114.7104</v>
+        <v>114.7103</v>
       </c>
     </row>
     <row r="645">
@@ -24927,7 +24927,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H645" t="n">
-        <v>115.6436</v>
+        <v>115.6435</v>
       </c>
     </row>
     <row r="646">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H648" t="n">
         <v>114.7409</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H651" t="n">
         <v>114.282</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H652" t="n">
         <v>114.6797</v>
@@ -25266,7 +25266,7 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H654" t="n">
         <v>115.6742</v>
@@ -25345,7 +25345,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H656" t="n">
-        <v>115.6436</v>
+        <v>115.6435</v>
       </c>
     </row>
     <row r="657">
@@ -25380,7 +25380,7 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H657" t="n">
         <v>116.7757</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H658" t="n">
         <v>115.9954</v>
@@ -25459,7 +25459,7 @@
         <v>74.457329</v>
       </c>
       <c r="H659" t="n">
-        <v>115.7201</v>
+        <v>115.72</v>
       </c>
     </row>
     <row r="660">
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H660" t="n">
         <v>115.9954</v>
@@ -25684,7 +25684,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H665" t="n">
         <v>116.7145</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H670" t="n">
         <v>119.8201</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H672" t="n">
         <v>119.0093</v>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H674" t="n">
         <v>118.5503</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H675" t="n">
         <v>118.3973</v>
@@ -26181,7 +26181,7 @@
         <v>76.908394</v>
       </c>
       <c r="H678" t="n">
-        <v>119.5295</v>
+        <v>119.5294</v>
       </c>
     </row>
     <row r="679">
@@ -26219,7 +26219,7 @@
         <v>76.918243</v>
       </c>
       <c r="H679" t="n">
-        <v>119.5448</v>
+        <v>119.5447</v>
       </c>
     </row>
     <row r="680">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="G680" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H680" t="n">
         <v>119.0399</v>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G681" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H681" t="n">
         <v>118.3361</v>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G687" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H687" t="n">
         <v>121.7784</v>
@@ -27055,7 +27055,7 @@
         <v>79.535309</v>
       </c>
       <c r="H701" t="n">
-        <v>123.6122</v>
+        <v>123.6121</v>
       </c>
     </row>
     <row r="702">
@@ -27131,7 +27131,7 @@
         <v>79.19718899999999</v>
       </c>
       <c r="H703" t="n">
-        <v>123.0867</v>
+        <v>123.0866</v>
       </c>
     </row>
     <row r="704">
@@ -27625,7 +27625,7 @@
         <v>81.066734</v>
       </c>
       <c r="H716" t="n">
-        <v>125.9923</v>
+        <v>125.9922</v>
       </c>
     </row>
     <row r="717">
@@ -27663,7 +27663,7 @@
         <v>80.68885</v>
       </c>
       <c r="H717" t="n">
-        <v>125.405</v>
+        <v>125.4049</v>
       </c>
     </row>
     <row r="718">
@@ -27739,7 +27739,7 @@
         <v>80.112076</v>
       </c>
       <c r="H719" t="n">
-        <v>124.5086</v>
+        <v>124.5085</v>
       </c>
     </row>
     <row r="720">
@@ -27777,7 +27777,7 @@
         <v>80.291077</v>
       </c>
       <c r="H720" t="n">
-        <v>124.7868</v>
+        <v>124.7867</v>
       </c>
     </row>
     <row r="721">
@@ -27815,7 +27815,7 @@
         <v>80.738579</v>
       </c>
       <c r="H721" t="n">
-        <v>125.4823</v>
+        <v>125.4822</v>
       </c>
     </row>
     <row r="722">
@@ -28005,7 +28005,7 @@
         <v>81.245735</v>
       </c>
       <c r="H726" t="n">
-        <v>126.2705</v>
+        <v>126.2704</v>
       </c>
     </row>
     <row r="727">
@@ -28043,7 +28043,7 @@
         <v>81.404854</v>
       </c>
       <c r="H727" t="n">
-        <v>126.5178</v>
+        <v>126.5177</v>
       </c>
     </row>
     <row r="728">
@@ -28119,7 +28119,7 @@
         <v>81.295464</v>
       </c>
       <c r="H729" t="n">
-        <v>126.3478</v>
+        <v>126.3477</v>
       </c>
     </row>
     <row r="730">
@@ -28195,7 +28195,7 @@
         <v>80.84796900000001</v>
       </c>
       <c r="H731" t="n">
-        <v>125.6523</v>
+        <v>125.6522</v>
       </c>
     </row>
     <row r="732">
@@ -28309,7 +28309,7 @@
         <v>80.758461</v>
       </c>
       <c r="H734" t="n">
-        <v>125.5132</v>
+        <v>125.5131</v>
       </c>
     </row>
     <row r="735">
@@ -28347,7 +28347,7 @@
         <v>80.758461</v>
       </c>
       <c r="H735" t="n">
-        <v>125.5132</v>
+        <v>125.5131</v>
       </c>
     </row>
     <row r="736">
@@ -28385,7 +28385,7 @@
         <v>81.02697000000001</v>
       </c>
       <c r="H736" t="n">
-        <v>125.9305</v>
+        <v>125.9304</v>
       </c>
     </row>
     <row r="737">
@@ -28423,7 +28423,7 @@
         <v>81.205963</v>
       </c>
       <c r="H737" t="n">
-        <v>126.2087</v>
+        <v>126.2086</v>
       </c>
     </row>
     <row r="738">
@@ -28537,7 +28537,7 @@
         <v>80.937462</v>
       </c>
       <c r="H740" t="n">
-        <v>125.7914</v>
+        <v>125.7913</v>
       </c>
     </row>
     <row r="741">
@@ -29069,7 +29069,7 @@
         <v>80.5</v>
       </c>
       <c r="H754" t="n">
-        <v>125.1115</v>
+        <v>125.1114</v>
       </c>
     </row>
     <row r="755">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81.040001</v>
+        <v>80.900002</v>
       </c>
       <c r="H755" t="n">
-        <v>125.9507</v>
+        <v>125.7331</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>129.360001</v>
+        <v>129.380005</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.6829</v>
+        <v>120.7016</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>129.360001</v>
+        <v>129.380005</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.6829</v>
+        <v>120.7016</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>129.360001</v>
+        <v>129.380005</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.6829</v>
+        <v>120.7016</v>
       </c>
     </row>
     <row r="1509">
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>53.075188</v>
+        <v>53.07518</v>
       </c>
       <c r="H1512" t="n">
         <v>99.43429999999999</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.799221</v>
+        <v>54.799225</v>
       </c>
       <c r="H1517" t="n">
         <v>102.6642</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.062218</v>
+        <v>55.06221</v>
       </c>
       <c r="H1518" t="n">
         <v>103.1569</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.974552</v>
+        <v>54.974548</v>
       </c>
       <c r="H1520" t="n">
         <v>102.9927</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.40313</v>
+        <v>55.403122</v>
       </c>
       <c r="H1521" t="n">
         <v>103.7956</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.159618</v>
+        <v>55.159622</v>
       </c>
       <c r="H1522" t="n">
         <v>103.3394</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.740784</v>
+        <v>54.74078</v>
       </c>
       <c r="H1524" t="n">
         <v>102.5547</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>54.818703</v>
+        <v>54.818707</v>
       </c>
       <c r="H1526" t="n">
         <v>102.7007</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1527" t="n">
         <v>103.5219</v>
@@ -58478,10 +58478,10 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.682343</v>
+        <v>54.682335</v>
       </c>
       <c r="H1528" t="n">
-        <v>102.4453</v>
+        <v>102.4452</v>
       </c>
     </row>
     <row r="1529">
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1529" t="n">
         <v>103.5219</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.40313</v>
+        <v>55.403122</v>
       </c>
       <c r="H1530" t="n">
         <v>103.7956</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1531" t="n">
         <v>103.5584</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1536" t="n">
         <v>104.0328</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1540" t="n">
         <v>103.5584</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.867409</v>
+        <v>54.867405</v>
       </c>
       <c r="H1541" t="n">
         <v>102.792</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>54.584934</v>
+        <v>54.584938</v>
       </c>
       <c r="H1542" t="n">
         <v>102.2628</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1543" t="n">
         <v>103.7591</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>56.523262</v>
+        <v>56.523266</v>
       </c>
       <c r="H1545" t="n">
         <v>105.8942</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>56.143387</v>
+        <v>56.143394</v>
       </c>
       <c r="H1546" t="n">
         <v>105.1825</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.305721</v>
+        <v>55.305717</v>
       </c>
       <c r="H1548" t="n">
         <v>103.6131</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1549" t="n">
         <v>101.8066</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>54.487534</v>
+        <v>54.48753</v>
       </c>
       <c r="H1551" t="n">
         <v>102.0803</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1553" t="n">
         <v>101.9526</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.877144</v>
+        <v>54.877151</v>
       </c>
       <c r="H1554" t="n">
         <v>102.8102</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1555" t="n">
         <v>104.0328</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1556" t="n">
         <v>104.1058</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1558" t="n">
         <v>104.1058</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.987549</v>
+        <v>55.987545</v>
       </c>
       <c r="H1562" t="n">
         <v>104.8905</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1563" t="n">
         <v>104.7263</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.870659</v>
+        <v>55.870663</v>
       </c>
       <c r="H1565" t="n">
         <v>104.6715</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1567" t="n">
         <v>104.635</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.294872</v>
+        <v>56.294876</v>
       </c>
       <c r="H1568" t="n">
         <v>105.4663</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1570" t="n">
         <v>104.8987</v>
@@ -60112,10 +60112,10 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.558758</v>
+        <v>56.558754</v>
       </c>
       <c r="H1571" t="n">
-        <v>105.9607</v>
+        <v>105.9606</v>
       </c>
     </row>
     <row r="1572">
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.676041</v>
+        <v>56.676044</v>
       </c>
       <c r="H1573" t="n">
         <v>106.1804</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1575" t="n">
         <v>106.7297</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>57.692474</v>
+        <v>57.692471</v>
       </c>
       <c r="H1577" t="n">
         <v>108.0846</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1578" t="n">
         <v>109.0551</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.53299</v>
+        <v>58.532986</v>
       </c>
       <c r="H1579" t="n">
         <v>109.6593</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1580" t="n">
         <v>109.6227</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>59.129169</v>
+        <v>59.129166</v>
       </c>
       <c r="H1583" t="n">
         <v>110.7762</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1585" t="n">
         <v>110.8128</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1586" t="n">
         <v>111.4537</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1587" t="n">
         <v>111.472</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1589" t="n">
         <v>109.1832</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>58.86528</v>
+        <v>58.865284</v>
       </c>
       <c r="H1592" t="n">
         <v>110.2818</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>58.953243</v>
+        <v>58.953247</v>
       </c>
       <c r="H1593" t="n">
         <v>110.4466</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>59.305092</v>
+        <v>59.305088</v>
       </c>
       <c r="H1594" t="n">
         <v>111.1058</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1605" t="n">
         <v>112.7903</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1608" t="n">
         <v>112.296</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1609" t="n">
         <v>112.9002</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.956799</v>
+        <v>60.956795</v>
       </c>
       <c r="H1610" t="n">
         <v>114.2002</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1623" t="n">
         <v>108.0114</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1624" t="n">
         <v>110.1354</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.650002</v>
+        <v>63.580002</v>
       </c>
       <c r="H1760" t="n">
-        <v>119.2458</v>
+        <v>119.1147</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.342636</v>
+        <v>64.342628</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19683,7 +19683,7 @@
         <v>64.54714199999999</v>
       </c>
       <c r="H507" t="n">
-        <v>100.3178</v>
+        <v>100.3179</v>
       </c>
     </row>
     <row r="508">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.44974499999999</v>
+        <v>64.449753</v>
       </c>
       <c r="H508" t="n">
         <v>100.1665</v>
@@ -19759,7 +19759,7 @@
         <v>64.741913</v>
       </c>
       <c r="H509" t="n">
-        <v>100.6205</v>
+        <v>100.6206</v>
       </c>
     </row>
     <row r="510">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.189888</v>
+        <v>65.18988</v>
       </c>
       <c r="H512" t="n">
         <v>101.3168</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.160667</v>
+        <v>65.160675</v>
       </c>
       <c r="H513" t="n">
         <v>101.2714</v>
@@ -19949,7 +19949,7 @@
         <v>65.511253</v>
       </c>
       <c r="H514" t="n">
-        <v>101.8162</v>
+        <v>101.8163</v>
       </c>
     </row>
     <row r="515">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H527" t="n">
         <v>102.4822</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.06635300000001</v>
+        <v>66.066345</v>
       </c>
       <c r="H528" t="n">
         <v>102.679</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.407211</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H529" t="n">
         <v>103.2087</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.407211</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H532" t="n">
         <v>103.2087</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H534" t="n">
         <v>102.6638</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H536" t="n">
         <v>103.0271</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.98844099999999</v>
+        <v>65.988457</v>
       </c>
       <c r="H537" t="n">
         <v>102.5579</v>
@@ -20934,10 +20934,10 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.942818</v>
+        <v>66.94283299999999</v>
       </c>
       <c r="H540" t="n">
-        <v>104.0411</v>
+        <v>104.0412</v>
       </c>
     </row>
     <row r="541">
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H541" t="n">
         <v>105.0098</v>
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.41693100000001</v>
+        <v>66.416939</v>
       </c>
       <c r="H544" t="n">
-        <v>103.2238</v>
+        <v>103.2239</v>
       </c>
     </row>
     <row r="545">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>65.754723</v>
+        <v>65.754715</v>
       </c>
       <c r="H545" t="n">
         <v>102.1946</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>65.715767</v>
+        <v>65.71577499999999</v>
       </c>
       <c r="H546" t="n">
         <v>102.1341</v>
@@ -21200,10 +21200,10 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027412</v>
       </c>
       <c r="H547" t="n">
-        <v>102.6184</v>
+        <v>102.6185</v>
       </c>
     </row>
     <row r="548">
@@ -21241,7 +21241,7 @@
         <v>65.891068</v>
       </c>
       <c r="H548" t="n">
-        <v>102.4065</v>
+        <v>102.4066</v>
       </c>
     </row>
     <row r="549">
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.12479399999999</v>
+        <v>66.124779</v>
       </c>
       <c r="H549" t="n">
         <v>102.7698</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.387733</v>
+        <v>66.387726</v>
       </c>
       <c r="H550" t="n">
         <v>103.1784</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H551" t="n">
         <v>104.132</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.874657</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H555" t="n">
         <v>103.9352</v>
@@ -21542,10 +21542,10 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>66.942818</v>
+        <v>66.94283299999999</v>
       </c>
       <c r="H556" t="n">
-        <v>104.0411</v>
+        <v>104.0412</v>
       </c>
     </row>
     <row r="557">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H558" t="n">
         <v>104.9342</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.283661</v>
+        <v>67.283669</v>
       </c>
       <c r="H559" t="n">
         <v>104.5709</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.22524300000001</v>
+        <v>67.22525</v>
       </c>
       <c r="H561" t="n">
         <v>104.4801</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H564" t="n">
         <v>105.3277</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H565" t="n">
         <v>104.3893</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H568" t="n">
         <v>105.5185</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H571" t="n">
         <v>106.1122</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>68.30474100000001</v>
+        <v>68.304733</v>
       </c>
       <c r="H572" t="n">
         <v>106.1578</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H573" t="n">
         <v>106.4927</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>69.24498</v>
+        <v>69.24498699999999</v>
       </c>
       <c r="H574" t="n">
         <v>107.6191</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H577" t="n">
         <v>108.3194</v>
@@ -22381,7 +22381,7 @@
         <v>70.2342</v>
       </c>
       <c r="H578" t="n">
-        <v>109.1565</v>
+        <v>109.1566</v>
       </c>
     </row>
     <row r="579">
@@ -22419,7 +22419,7 @@
         <v>70.18523399999999</v>
       </c>
       <c r="H579" t="n">
-        <v>109.0804</v>
+        <v>109.0805</v>
       </c>
     </row>
     <row r="580">
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>71.340942</v>
+        <v>71.340935</v>
       </c>
       <c r="H582" t="n">
         <v>110.8766</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H583" t="n">
         <v>110.8005</v>
@@ -22609,7 +22609,7 @@
         <v>70.723907</v>
       </c>
       <c r="H584" t="n">
-        <v>109.9176</v>
+        <v>109.9177</v>
       </c>
     </row>
     <row r="585">
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H585" t="n">
         <v>108.8978</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H587" t="n">
         <v>110.146</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.51823400000001</v>
+        <v>70.518227</v>
       </c>
       <c r="H588" t="n">
         <v>109.598</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.4105</v>
+        <v>70.410484</v>
       </c>
       <c r="H590" t="n">
         <v>109.4305</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>70.684731</v>
+        <v>70.68472300000001</v>
       </c>
       <c r="H592" t="n">
         <v>109.8568</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H594" t="n">
         <v>111.4094</v>
@@ -23027,7 +23027,7 @@
         <v>72.37912799999999</v>
       </c>
       <c r="H595" t="n">
-        <v>112.4901</v>
+        <v>112.4902</v>
       </c>
     </row>
     <row r="596">
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H597" t="n">
         <v>112.4445</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H599" t="n">
         <v>113.9362</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H600" t="n">
         <v>114.332</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H601" t="n">
         <v>115.1997</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H602" t="n">
         <v>114.7582</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H606" t="n">
         <v>115.7781</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H607" t="n">
         <v>115.7781</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.524055</v>
+        <v>74.524063</v>
       </c>
       <c r="H609" t="n">
         <v>115.8238</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H610" t="n">
         <v>116.1434</v>
@@ -23632,10 +23632,10 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>75.14109000000001</v>
+        <v>75.141098</v>
       </c>
       <c r="H611" t="n">
-        <v>116.7827</v>
+        <v>116.7828</v>
       </c>
     </row>
     <row r="612">
@@ -23670,10 +23670,10 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>75.27821400000001</v>
+        <v>75.278206</v>
       </c>
       <c r="H612" t="n">
-        <v>116.9958</v>
+        <v>116.9959</v>
       </c>
     </row>
     <row r="613">
@@ -23746,10 +23746,10 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>75.003967</v>
+        <v>75.00398300000001</v>
       </c>
       <c r="H614" t="n">
-        <v>116.5696</v>
+        <v>116.5697</v>
       </c>
     </row>
     <row r="615">
@@ -23784,10 +23784,10 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>73.358543</v>
+        <v>73.35855100000001</v>
       </c>
       <c r="H615" t="n">
-        <v>114.0123</v>
+        <v>114.0124</v>
       </c>
     </row>
     <row r="616">
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.721931</v>
+        <v>72.721924</v>
       </c>
       <c r="H620" t="n">
         <v>113.0229</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H621" t="n">
         <v>112.5815</v>
@@ -24167,7 +24167,7 @@
         <v>72.64357</v>
       </c>
       <c r="H625" t="n">
-        <v>112.9011</v>
+        <v>112.9012</v>
       </c>
     </row>
     <row r="626">
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H626" t="n">
         <v>111.1457</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H627" t="n">
         <v>110.1207</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H629" t="n">
         <v>110.9774</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H632" t="n">
         <v>110.9774</v>
@@ -24509,7 +24509,7 @@
         <v>71.986572</v>
       </c>
       <c r="H634" t="n">
-        <v>111.88</v>
+        <v>111.8801</v>
       </c>
     </row>
     <row r="635">
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H635" t="n">
         <v>112.9663</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H637" t="n">
         <v>112.5991</v>
@@ -24696,7 +24696,7 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H639" t="n">
         <v>114.9245</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H640" t="n">
         <v>114.6644</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H642" t="n">
         <v>114.7409</v>
@@ -24886,10 +24886,10 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H644" t="n">
-        <v>114.7103</v>
+        <v>114.7104</v>
       </c>
     </row>
     <row r="645">
@@ -24927,7 +24927,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H645" t="n">
-        <v>115.6435</v>
+        <v>115.6436</v>
       </c>
     </row>
     <row r="646">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H648" t="n">
         <v>114.7409</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H651" t="n">
         <v>114.282</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H652" t="n">
         <v>114.6797</v>
@@ -25266,7 +25266,7 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H654" t="n">
         <v>115.6742</v>
@@ -25345,7 +25345,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H656" t="n">
-        <v>115.6435</v>
+        <v>115.6436</v>
       </c>
     </row>
     <row r="657">
@@ -25380,7 +25380,7 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H657" t="n">
         <v>116.7757</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H658" t="n">
         <v>115.9954</v>
@@ -25459,7 +25459,7 @@
         <v>74.457329</v>
       </c>
       <c r="H659" t="n">
-        <v>115.72</v>
+        <v>115.7201</v>
       </c>
     </row>
     <row r="660">
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H660" t="n">
         <v>115.9954</v>
@@ -25684,7 +25684,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H665" t="n">
         <v>116.7145</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H670" t="n">
         <v>119.8201</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H672" t="n">
         <v>119.0093</v>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H674" t="n">
         <v>118.5503</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H675" t="n">
         <v>118.3973</v>
@@ -26181,7 +26181,7 @@
         <v>76.908394</v>
       </c>
       <c r="H678" t="n">
-        <v>119.5294</v>
+        <v>119.5295</v>
       </c>
     </row>
     <row r="679">
@@ -26219,7 +26219,7 @@
         <v>76.918243</v>
       </c>
       <c r="H679" t="n">
-        <v>119.5447</v>
+        <v>119.5448</v>
       </c>
     </row>
     <row r="680">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="G680" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H680" t="n">
         <v>119.0399</v>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G681" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H681" t="n">
         <v>118.3361</v>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G687" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H687" t="n">
         <v>121.7784</v>
@@ -27055,7 +27055,7 @@
         <v>79.535309</v>
       </c>
       <c r="H701" t="n">
-        <v>123.6121</v>
+        <v>123.6122</v>
       </c>
     </row>
     <row r="702">
@@ -27131,7 +27131,7 @@
         <v>79.19718899999999</v>
       </c>
       <c r="H703" t="n">
-        <v>123.0866</v>
+        <v>123.0867</v>
       </c>
     </row>
     <row r="704">
@@ -27625,7 +27625,7 @@
         <v>81.066734</v>
       </c>
       <c r="H716" t="n">
-        <v>125.9922</v>
+        <v>125.9923</v>
       </c>
     </row>
     <row r="717">
@@ -27663,7 +27663,7 @@
         <v>80.68885</v>
       </c>
       <c r="H717" t="n">
-        <v>125.4049</v>
+        <v>125.405</v>
       </c>
     </row>
     <row r="718">
@@ -27739,7 +27739,7 @@
         <v>80.112076</v>
       </c>
       <c r="H719" t="n">
-        <v>124.5085</v>
+        <v>124.5086</v>
       </c>
     </row>
     <row r="720">
@@ -27777,7 +27777,7 @@
         <v>80.291077</v>
       </c>
       <c r="H720" t="n">
-        <v>124.7867</v>
+        <v>124.7868</v>
       </c>
     </row>
     <row r="721">
@@ -27815,7 +27815,7 @@
         <v>80.738579</v>
       </c>
       <c r="H721" t="n">
-        <v>125.4822</v>
+        <v>125.4823</v>
       </c>
     </row>
     <row r="722">
@@ -28005,7 +28005,7 @@
         <v>81.245735</v>
       </c>
       <c r="H726" t="n">
-        <v>126.2704</v>
+        <v>126.2705</v>
       </c>
     </row>
     <row r="727">
@@ -28043,7 +28043,7 @@
         <v>81.404854</v>
       </c>
       <c r="H727" t="n">
-        <v>126.5177</v>
+        <v>126.5178</v>
       </c>
     </row>
     <row r="728">
@@ -28119,7 +28119,7 @@
         <v>81.295464</v>
       </c>
       <c r="H729" t="n">
-        <v>126.3477</v>
+        <v>126.3478</v>
       </c>
     </row>
     <row r="730">
@@ -28195,7 +28195,7 @@
         <v>80.84796900000001</v>
       </c>
       <c r="H731" t="n">
-        <v>125.6522</v>
+        <v>125.6523</v>
       </c>
     </row>
     <row r="732">
@@ -28309,7 +28309,7 @@
         <v>80.758461</v>
       </c>
       <c r="H734" t="n">
-        <v>125.5131</v>
+        <v>125.5132</v>
       </c>
     </row>
     <row r="735">
@@ -28347,7 +28347,7 @@
         <v>80.758461</v>
       </c>
       <c r="H735" t="n">
-        <v>125.5131</v>
+        <v>125.5132</v>
       </c>
     </row>
     <row r="736">
@@ -28385,7 +28385,7 @@
         <v>81.02697000000001</v>
       </c>
       <c r="H736" t="n">
-        <v>125.9304</v>
+        <v>125.9305</v>
       </c>
     </row>
     <row r="737">
@@ -28423,7 +28423,7 @@
         <v>81.205963</v>
       </c>
       <c r="H737" t="n">
-        <v>126.2086</v>
+        <v>126.2087</v>
       </c>
     </row>
     <row r="738">
@@ -28537,7 +28537,7 @@
         <v>80.937462</v>
       </c>
       <c r="H740" t="n">
-        <v>125.7913</v>
+        <v>125.7914</v>
       </c>
     </row>
     <row r="741">
@@ -29069,7 +29069,7 @@
         <v>80.5</v>
       </c>
       <c r="H754" t="n">
-        <v>125.1114</v>
+        <v>125.1115</v>
       </c>
     </row>
     <row r="755">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.542721</v>
+        <v>53.542717</v>
       </c>
       <c r="H1510" t="n">
         <v>100.3102</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>53.07518</v>
+        <v>53.075188</v>
       </c>
       <c r="H1512" t="n">
         <v>99.43429999999999</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.62064</v>
+        <v>53.620636</v>
       </c>
       <c r="H1514" t="n">
         <v>100.4562</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.799225</v>
+        <v>54.799221</v>
       </c>
       <c r="H1517" t="n">
         <v>102.6642</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.06221</v>
+        <v>55.062218</v>
       </c>
       <c r="H1518" t="n">
         <v>103.1569</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.974548</v>
+        <v>54.974552</v>
       </c>
       <c r="H1520" t="n">
         <v>102.9927</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.403122</v>
+        <v>55.403126</v>
       </c>
       <c r="H1521" t="n">
         <v>103.7956</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.159622</v>
+        <v>55.159618</v>
       </c>
       <c r="H1522" t="n">
         <v>103.3394</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.429092</v>
+        <v>54.429096</v>
       </c>
       <c r="H1523" t="n">
         <v>101.9708</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.74078</v>
+        <v>54.740788</v>
       </c>
       <c r="H1524" t="n">
-        <v>102.5547</v>
+        <v>102.5548</v>
       </c>
     </row>
     <row r="1525">
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.536236</v>
+        <v>54.53624</v>
       </c>
       <c r="H1525" t="n">
         <v>102.1715</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1526" t="n">
         <v>102.7007</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1527" t="n">
         <v>103.5219</v>
@@ -58478,10 +58478,10 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1528" t="n">
-        <v>102.4452</v>
+        <v>102.4453</v>
       </c>
     </row>
     <row r="1529">
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1529" t="n">
         <v>103.5219</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.403122</v>
+        <v>55.403126</v>
       </c>
       <c r="H1530" t="n">
         <v>103.7956</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1531" t="n">
         <v>103.5584</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1533" t="n">
         <v>104.4526</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.588188</v>
+        <v>55.588192</v>
       </c>
       <c r="H1535" t="n">
         <v>104.1423</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1536" t="n">
         <v>104.0328</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.295986</v>
+        <v>55.295982</v>
       </c>
       <c r="H1537" t="n">
         <v>103.5949</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1540" t="n">
         <v>103.5584</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.867405</v>
+        <v>54.867409</v>
       </c>
       <c r="H1541" t="n">
         <v>102.792</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>54.584938</v>
+        <v>54.584934</v>
       </c>
       <c r="H1542" t="n">
         <v>102.2628</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1543" t="n">
         <v>103.7591</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1544" t="n">
         <v>105.1095</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>56.523266</v>
+        <v>56.523262</v>
       </c>
       <c r="H1545" t="n">
         <v>105.8942</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1546" t="n">
         <v>105.1825</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.305717</v>
+        <v>55.305721</v>
       </c>
       <c r="H1548" t="n">
         <v>103.6131</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1549" t="n">
         <v>101.8066</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1550" t="n">
         <v>101.7153</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1553" t="n">
         <v>101.9526</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>54.877151</v>
+        <v>54.877148</v>
       </c>
       <c r="H1554" t="n">
         <v>102.8102</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1555" t="n">
         <v>104.0328</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1556" t="n">
         <v>104.1058</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1557" t="n">
         <v>104.4526</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1558" t="n">
         <v>104.1058</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1563" t="n">
         <v>104.7263</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1569" t="n">
         <v>105.0268</v>
@@ -60112,10 +60112,10 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.558754</v>
+        <v>56.558758</v>
       </c>
       <c r="H1571" t="n">
-        <v>105.9606</v>
+        <v>105.9607</v>
       </c>
     </row>
     <row r="1572">
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1572" t="n">
         <v>106.3818</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.676044</v>
+        <v>56.676041</v>
       </c>
       <c r="H1573" t="n">
         <v>106.1804</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1575" t="n">
         <v>106.7297</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>57.692471</v>
+        <v>57.692474</v>
       </c>
       <c r="H1577" t="n">
         <v>108.0846</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>59.031437</v>
+        <v>59.031433</v>
       </c>
       <c r="H1582" t="n">
         <v>110.5931</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1586" t="n">
         <v>111.4537</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1587" t="n">
         <v>111.472</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1589" t="n">
         <v>109.1832</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>58.953247</v>
+        <v>58.953243</v>
       </c>
       <c r="H1593" t="n">
         <v>110.4466</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.168262</v>
+        <v>59.168259</v>
       </c>
       <c r="H1597" t="n">
         <v>110.8495</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.793758</v>
+        <v>59.793755</v>
       </c>
       <c r="H1598" t="n">
         <v>112.0213</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.803532</v>
+        <v>59.803528</v>
       </c>
       <c r="H1600" t="n">
         <v>112.0396</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.246445</v>
+        <v>59.246449</v>
       </c>
       <c r="H1601" t="n">
         <v>110.9959</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.744892</v>
+        <v>59.744896</v>
       </c>
       <c r="H1602" t="n">
         <v>111.9298</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.11628</v>
+        <v>60.116276</v>
       </c>
       <c r="H1604" t="n">
         <v>112.6255</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1605" t="n">
         <v>112.7903</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1606" t="n">
         <v>112.2776</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1608" t="n">
         <v>112.296</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1609" t="n">
         <v>112.9002</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>60.65382</v>
+        <v>60.653816</v>
       </c>
       <c r="H1611" t="n">
         <v>113.6326</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1613" t="n">
         <v>114.0354</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>61.015434</v>
+        <v>61.015438</v>
       </c>
       <c r="H1614" t="n">
         <v>114.3101</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>59.393051</v>
+        <v>59.393047</v>
       </c>
       <c r="H1620" t="n">
         <v>111.2706</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>58.581856</v>
+        <v>58.581852</v>
       </c>
       <c r="H1621" t="n">
         <v>109.7508</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1622" t="n">
         <v>108.7621</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1624" t="n">
         <v>110.1354</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>58.4548</v>
+        <v>58.454803</v>
       </c>
       <c r="H1625" t="n">
         <v>109.5128</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>58.112728</v>
+        <v>58.112732</v>
       </c>
       <c r="H1626" t="n">
         <v>108.872</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1629" t="n">
         <v>109.4665</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1648" t="n">
         <v>112.6969</v>
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1650" t="n">
         <v>114.4405</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1652" t="n">
         <v>112.55</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1654" t="n">
         <v>112.3114</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1655" t="n">
         <v>111.7057</v>
@@ -63418,10 +63418,10 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1658" t="n">
-        <v>110.4393</v>
+        <v>110.4392</v>
       </c>
     </row>
     <row r="1659">
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1661" t="n">
         <v>111.9076</v>
@@ -63570,7 +63570,7 @@
         </is>
       </c>
       <c r="G1662" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1662" t="n">
         <v>114.3855</v>
@@ -63646,7 +63646,7 @@
         </is>
       </c>
       <c r="G1664" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1664" t="n">
         <v>112.5133</v>
@@ -63722,7 +63722,7 @@
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1666" t="n">
         <v>111.4855</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1676" t="n">
         <v>115.9273</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1678" t="n">
         <v>115.4317</v>
@@ -64292,7 +64292,7 @@
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1681" t="n">
         <v>115.5602</v>
@@ -64368,7 +64368,7 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1683" t="n">
         <v>115.4317</v>
@@ -64406,7 +64406,7 @@
         </is>
       </c>
       <c r="G1684" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1684" t="n">
         <v>114.9728</v>
@@ -64558,7 +64558,7 @@
         </is>
       </c>
       <c r="G1688" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1688" t="n">
         <v>114.826</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.044998</v>
+        <v>35.07</v>
       </c>
       <c r="H253" t="n">
-        <v>114.5636</v>
+        <v>114.6453</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>49.189999</v>
+        <v>48.970001</v>
       </c>
       <c r="H504" t="n">
-        <v>133.9962</v>
+        <v>133.3969</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.342628</v>
+        <v>64.342636</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19683,7 +19683,7 @@
         <v>64.54714199999999</v>
       </c>
       <c r="H507" t="n">
-        <v>100.3179</v>
+        <v>100.3178</v>
       </c>
     </row>
     <row r="508">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.449753</v>
+        <v>64.44974499999999</v>
       </c>
       <c r="H508" t="n">
         <v>100.1665</v>
@@ -19759,7 +19759,7 @@
         <v>64.741913</v>
       </c>
       <c r="H509" t="n">
-        <v>100.6206</v>
+        <v>100.6205</v>
       </c>
     </row>
     <row r="510">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.18988</v>
+        <v>65.189888</v>
       </c>
       <c r="H512" t="n">
         <v>101.3168</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H513" t="n">
         <v>101.2714</v>
@@ -19949,7 +19949,7 @@
         <v>65.511253</v>
       </c>
       <c r="H514" t="n">
-        <v>101.8163</v>
+        <v>101.8162</v>
       </c>
     </row>
     <row r="515">
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H524" t="n">
         <v>101.2108</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.339035</v>
+        <v>66.339043</v>
       </c>
       <c r="H530" t="n">
         <v>103.1028</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H531" t="n">
         <v>102.906</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H534" t="n">
         <v>102.6638</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H536" t="n">
         <v>103.0271</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.988457</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H537" t="n">
         <v>102.5579</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.94283299999999</v>
+        <v>66.942825</v>
       </c>
       <c r="H540" t="n">
         <v>104.0412</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H541" t="n">
         <v>105.0098</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H543" t="n">
         <v>103.7839</v>
@@ -21089,7 +21089,7 @@
         <v>66.416939</v>
       </c>
       <c r="H544" t="n">
-        <v>103.2239</v>
+        <v>103.2238</v>
       </c>
     </row>
     <row r="545">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>65.754715</v>
+        <v>65.754723</v>
       </c>
       <c r="H545" t="n">
         <v>102.1946</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>65.71577499999999</v>
+        <v>65.715767</v>
       </c>
       <c r="H546" t="n">
         <v>102.1341</v>
@@ -21200,10 +21200,10 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.027412</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H547" t="n">
-        <v>102.6185</v>
+        <v>102.6184</v>
       </c>
     </row>
     <row r="548">
@@ -21241,7 +21241,7 @@
         <v>65.891068</v>
       </c>
       <c r="H548" t="n">
-        <v>102.4066</v>
+        <v>102.4065</v>
       </c>
     </row>
     <row r="549">
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.124779</v>
+        <v>66.124786</v>
       </c>
       <c r="H549" t="n">
         <v>102.7698</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.24472</v>
+        <v>67.24472799999999</v>
       </c>
       <c r="H553" t="n">
         <v>104.5104</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>66.94283299999999</v>
+        <v>66.942825</v>
       </c>
       <c r="H556" t="n">
         <v>104.0412</v>
@@ -21621,7 +21621,7 @@
         <v>67.51739499999999</v>
       </c>
       <c r="H558" t="n">
-        <v>104.9342</v>
+        <v>104.9341</v>
       </c>
     </row>
     <row r="559">
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.22525</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H561" t="n">
         <v>104.4801</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H563" t="n">
         <v>104.7374</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H565" t="n">
         <v>104.3893</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H568" t="n">
         <v>105.5185</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H571" t="n">
         <v>106.1122</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>68.304733</v>
+        <v>68.30474100000001</v>
       </c>
       <c r="H572" t="n">
         <v>106.1578</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H573" t="n">
         <v>106.4927</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H574" t="n">
         <v>107.6191</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H577" t="n">
         <v>108.3194</v>
@@ -22381,7 +22381,7 @@
         <v>70.2342</v>
       </c>
       <c r="H578" t="n">
-        <v>109.1566</v>
+        <v>109.1565</v>
       </c>
     </row>
     <row r="579">
@@ -22419,7 +22419,7 @@
         <v>70.18523399999999</v>
       </c>
       <c r="H579" t="n">
-        <v>109.0805</v>
+        <v>109.0804</v>
       </c>
     </row>
     <row r="580">
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>71.340935</v>
+        <v>71.340942</v>
       </c>
       <c r="H582" t="n">
         <v>110.8766</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H583" t="n">
         <v>110.8005</v>
@@ -22609,7 +22609,7 @@
         <v>70.723907</v>
       </c>
       <c r="H584" t="n">
-        <v>109.9177</v>
+        <v>109.9176</v>
       </c>
     </row>
     <row r="585">
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H585" t="n">
         <v>108.8978</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H587" t="n">
         <v>110.146</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.518227</v>
+        <v>70.51823400000001</v>
       </c>
       <c r="H588" t="n">
         <v>109.598</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.410484</v>
+        <v>70.4105</v>
       </c>
       <c r="H590" t="n">
         <v>109.4305</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>70.68472300000001</v>
+        <v>70.684731</v>
       </c>
       <c r="H592" t="n">
         <v>109.8568</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H594" t="n">
         <v>111.4094</v>
@@ -23027,7 +23027,7 @@
         <v>72.37912799999999</v>
       </c>
       <c r="H595" t="n">
-        <v>112.4902</v>
+        <v>112.4901</v>
       </c>
     </row>
     <row r="596">
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H597" t="n">
         <v>112.4445</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H599" t="n">
         <v>113.9362</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H600" t="n">
         <v>114.332</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H601" t="n">
         <v>115.1997</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H602" t="n">
         <v>114.7582</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H606" t="n">
         <v>115.7781</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H607" t="n">
         <v>115.7781</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.524063</v>
+        <v>74.524055</v>
       </c>
       <c r="H609" t="n">
         <v>115.8238</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H610" t="n">
         <v>116.1434</v>
@@ -23632,10 +23632,10 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>75.141098</v>
+        <v>75.14109000000001</v>
       </c>
       <c r="H611" t="n">
-        <v>116.7828</v>
+        <v>116.7827</v>
       </c>
     </row>
     <row r="612">
@@ -23670,10 +23670,10 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>75.278206</v>
+        <v>75.27821400000001</v>
       </c>
       <c r="H612" t="n">
-        <v>116.9959</v>
+        <v>116.9958</v>
       </c>
     </row>
     <row r="613">
@@ -23746,10 +23746,10 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>75.00398300000001</v>
+        <v>75.003967</v>
       </c>
       <c r="H614" t="n">
-        <v>116.5697</v>
+        <v>116.5696</v>
       </c>
     </row>
     <row r="615">
@@ -23784,10 +23784,10 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H615" t="n">
-        <v>114.0124</v>
+        <v>114.0123</v>
       </c>
     </row>
     <row r="616">
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.721924</v>
+        <v>72.721931</v>
       </c>
       <c r="H620" t="n">
         <v>113.0229</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H621" t="n">
         <v>112.5815</v>
@@ -24167,7 +24167,7 @@
         <v>72.64357</v>
       </c>
       <c r="H625" t="n">
-        <v>112.9012</v>
+        <v>112.9011</v>
       </c>
     </row>
     <row r="626">
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H626" t="n">
         <v>111.1457</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H627" t="n">
         <v>110.1207</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H629" t="n">
         <v>110.9774</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H632" t="n">
         <v>110.9774</v>
@@ -24509,7 +24509,7 @@
         <v>71.986572</v>
       </c>
       <c r="H634" t="n">
-        <v>111.8801</v>
+        <v>111.88</v>
       </c>
     </row>
     <row r="635">
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H635" t="n">
         <v>112.9663</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H637" t="n">
         <v>112.5991</v>
@@ -24696,7 +24696,7 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H639" t="n">
         <v>114.9245</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H640" t="n">
         <v>114.6644</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H642" t="n">
         <v>114.7409</v>
@@ -24886,10 +24886,10 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H644" t="n">
-        <v>114.7104</v>
+        <v>114.7103</v>
       </c>
     </row>
     <row r="645">
@@ -24927,7 +24927,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H645" t="n">
-        <v>115.6436</v>
+        <v>115.6435</v>
       </c>
     </row>
     <row r="646">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H648" t="n">
         <v>114.7409</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H651" t="n">
         <v>114.282</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H652" t="n">
         <v>114.6797</v>
@@ -25266,7 +25266,7 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H654" t="n">
         <v>115.6742</v>
@@ -25345,7 +25345,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H656" t="n">
-        <v>115.6436</v>
+        <v>115.6435</v>
       </c>
     </row>
     <row r="657">
@@ -25380,7 +25380,7 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H657" t="n">
         <v>116.7757</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H658" t="n">
         <v>115.9954</v>
@@ -25459,7 +25459,7 @@
         <v>74.457329</v>
       </c>
       <c r="H659" t="n">
-        <v>115.7201</v>
+        <v>115.72</v>
       </c>
     </row>
     <row r="660">
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H660" t="n">
         <v>115.9954</v>
@@ -25684,7 +25684,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H665" t="n">
         <v>116.7145</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H670" t="n">
         <v>119.8201</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H672" t="n">
         <v>119.0093</v>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H674" t="n">
         <v>118.5503</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H675" t="n">
         <v>118.3973</v>
@@ -26181,7 +26181,7 @@
         <v>76.908394</v>
       </c>
       <c r="H678" t="n">
-        <v>119.5295</v>
+        <v>119.5294</v>
       </c>
     </row>
     <row r="679">
@@ -26219,7 +26219,7 @@
         <v>76.918243</v>
       </c>
       <c r="H679" t="n">
-        <v>119.5448</v>
+        <v>119.5447</v>
       </c>
     </row>
     <row r="680">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="G680" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H680" t="n">
         <v>119.0399</v>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G681" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H681" t="n">
         <v>118.3361</v>
@@ -26520,7 +26520,7 @@
         </is>
       </c>
       <c r="G687" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H687" t="n">
         <v>121.7784</v>
@@ -27055,7 +27055,7 @@
         <v>79.535309</v>
       </c>
       <c r="H701" t="n">
-        <v>123.6122</v>
+        <v>123.6121</v>
       </c>
     </row>
     <row r="702">
@@ -27131,7 +27131,7 @@
         <v>79.19718899999999</v>
       </c>
       <c r="H703" t="n">
-        <v>123.0867</v>
+        <v>123.0866</v>
       </c>
     </row>
     <row r="704">
@@ -27625,7 +27625,7 @@
         <v>81.066734</v>
       </c>
       <c r="H716" t="n">
-        <v>125.9923</v>
+        <v>125.9922</v>
       </c>
     </row>
     <row r="717">
@@ -27663,7 +27663,7 @@
         <v>80.68885</v>
       </c>
       <c r="H717" t="n">
-        <v>125.405</v>
+        <v>125.4049</v>
       </c>
     </row>
     <row r="718">
@@ -27739,7 +27739,7 @@
         <v>80.112076</v>
       </c>
       <c r="H719" t="n">
-        <v>124.5086</v>
+        <v>124.5085</v>
       </c>
     </row>
     <row r="720">
@@ -27777,7 +27777,7 @@
         <v>80.291077</v>
       </c>
       <c r="H720" t="n">
-        <v>124.7868</v>
+        <v>124.7867</v>
       </c>
     </row>
     <row r="721">
@@ -27815,7 +27815,7 @@
         <v>80.738579</v>
       </c>
       <c r="H721" t="n">
-        <v>125.4823</v>
+        <v>125.4822</v>
       </c>
     </row>
     <row r="722">
@@ -28005,7 +28005,7 @@
         <v>81.245735</v>
       </c>
       <c r="H726" t="n">
-        <v>126.2705</v>
+        <v>126.2704</v>
       </c>
     </row>
     <row r="727">
@@ -28043,7 +28043,7 @@
         <v>81.404854</v>
       </c>
       <c r="H727" t="n">
-        <v>126.5178</v>
+        <v>126.5177</v>
       </c>
     </row>
     <row r="728">
@@ -28119,7 +28119,7 @@
         <v>81.295464</v>
       </c>
       <c r="H729" t="n">
-        <v>126.3478</v>
+        <v>126.3477</v>
       </c>
     </row>
     <row r="730">
@@ -28195,7 +28195,7 @@
         <v>80.84796900000001</v>
       </c>
       <c r="H731" t="n">
-        <v>125.6523</v>
+        <v>125.6522</v>
       </c>
     </row>
     <row r="732">
@@ -28309,7 +28309,7 @@
         <v>80.758461</v>
       </c>
       <c r="H734" t="n">
-        <v>125.5132</v>
+        <v>125.5131</v>
       </c>
     </row>
     <row r="735">
@@ -28347,7 +28347,7 @@
         <v>80.758461</v>
       </c>
       <c r="H735" t="n">
-        <v>125.5132</v>
+        <v>125.5131</v>
       </c>
     </row>
     <row r="736">
@@ -28385,7 +28385,7 @@
         <v>81.02697000000001</v>
       </c>
       <c r="H736" t="n">
-        <v>125.9305</v>
+        <v>125.9304</v>
       </c>
     </row>
     <row r="737">
@@ -28423,7 +28423,7 @@
         <v>81.205963</v>
       </c>
       <c r="H737" t="n">
-        <v>126.2087</v>
+        <v>126.2086</v>
       </c>
     </row>
     <row r="738">
@@ -28537,7 +28537,7 @@
         <v>80.937462</v>
       </c>
       <c r="H740" t="n">
-        <v>125.7914</v>
+        <v>125.7913</v>
       </c>
     </row>
     <row r="741">
@@ -29069,13 +29069,13 @@
         <v>80.5</v>
       </c>
       <c r="H754" t="n">
-        <v>125.1115</v>
+        <v>125.1114</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.900002</v>
+        <v>80.910004</v>
       </c>
       <c r="H755" t="n">
-        <v>125.7331</v>
+        <v>125.7487</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>129.380005</v>
+        <v>128.600006</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.7016</v>
+        <v>119.9739</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>129.380005</v>
+        <v>128.600006</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.7016</v>
+        <v>119.9739</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>129.380005</v>
+        <v>128.600006</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.7016</v>
+        <v>119.9739</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.542717</v>
+        <v>53.542721</v>
       </c>
       <c r="H1510" t="n">
         <v>100.3102</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>53.523239</v>
+        <v>53.523243</v>
       </c>
       <c r="H1513" t="n">
         <v>100.2737</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>53.844669</v>
+        <v>53.844673</v>
       </c>
       <c r="H1515" t="n">
         <v>100.8759</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.974552</v>
+        <v>54.974556</v>
       </c>
       <c r="H1520" t="n">
         <v>102.9927</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.159618</v>
+        <v>55.159615</v>
       </c>
       <c r="H1522" t="n">
         <v>103.3394</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.429096</v>
+        <v>54.429092</v>
       </c>
       <c r="H1523" t="n">
         <v>101.9708</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.53624</v>
+        <v>54.536236</v>
       </c>
       <c r="H1525" t="n">
         <v>102.1715</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.682339</v>
+        <v>54.682343</v>
       </c>
       <c r="H1528" t="n">
         <v>102.4453</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1533" t="n">
         <v>104.4526</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.588192</v>
+        <v>55.588188</v>
       </c>
       <c r="H1535" t="n">
         <v>104.1423</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.325203</v>
+        <v>55.325207</v>
       </c>
       <c r="H1538" t="n">
         <v>103.6496</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.867409</v>
+        <v>54.867413</v>
       </c>
       <c r="H1541" t="n">
         <v>102.792</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1550" t="n">
         <v>101.7153</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>54.351166</v>
+        <v>54.351162</v>
       </c>
       <c r="H1552" t="n">
         <v>101.8248</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1557" t="n">
         <v>104.4526</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1570" t="n">
         <v>104.8987</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1578" t="n">
         <v>109.0551</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1580" t="n">
         <v>109.6227</v>
@@ -60492,10 +60492,10 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.39616</v>
+        <v>58.396156</v>
       </c>
       <c r="H1581" t="n">
-        <v>109.403</v>
+        <v>109.4029</v>
       </c>
     </row>
     <row r="1582">
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1583" t="n">
         <v>110.7762</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1585" t="n">
         <v>110.8128</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>58.91415</v>
+        <v>58.914154</v>
       </c>
       <c r="H1591" t="n">
         <v>110.3734</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>58.835964</v>
+        <v>58.835968</v>
       </c>
       <c r="H1595" t="n">
         <v>110.2269</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>58.718685</v>
+        <v>58.718681</v>
       </c>
       <c r="H1596" t="n">
         <v>110.0072</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.793755</v>
+        <v>59.793758</v>
       </c>
       <c r="H1598" t="n">
         <v>112.0213</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.803528</v>
+        <v>59.803532</v>
       </c>
       <c r="H1600" t="n">
         <v>112.0396</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.744896</v>
+        <v>59.744892</v>
       </c>
       <c r="H1602" t="n">
         <v>111.9298</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.116276</v>
+        <v>60.11628</v>
       </c>
       <c r="H1604" t="n">
         <v>112.6255</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1606" t="n">
         <v>112.2776</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>59.852402</v>
+        <v>59.852398</v>
       </c>
       <c r="H1607" t="n">
         <v>112.1312</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>60.653816</v>
+        <v>60.65382</v>
       </c>
       <c r="H1611" t="n">
         <v>113.6326</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1613" t="n">
         <v>114.0354</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1614" t="n">
         <v>114.3101</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>61.406372</v>
+        <v>61.406376</v>
       </c>
       <c r="H1616" t="n">
         <v>115.0425</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1623" t="n">
         <v>108.0114</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1626" t="n">
         <v>108.872</v>
@@ -62316,7 +62316,7 @@
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1629" t="n">
         <v>109.4665</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1648" t="n">
         <v>112.6969</v>
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1650" t="n">
         <v>114.4405</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1652" t="n">
         <v>112.55</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1654" t="n">
         <v>112.3114</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1655" t="n">
         <v>111.7057</v>
@@ -63418,10 +63418,10 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1658" t="n">
-        <v>110.4392</v>
+        <v>110.4393</v>
       </c>
     </row>
     <row r="1659">
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1661" t="n">
         <v>111.9076</v>
@@ -63570,7 +63570,7 @@
         </is>
       </c>
       <c r="G1662" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1662" t="n">
         <v>114.3855</v>
@@ -63646,7 +63646,7 @@
         </is>
       </c>
       <c r="G1664" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1664" t="n">
         <v>112.5133</v>
@@ -63722,7 +63722,7 @@
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1666" t="n">
         <v>111.4855</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1676" t="n">
         <v>115.9273</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1678" t="n">
         <v>115.4317</v>
@@ -64292,7 +64292,7 @@
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1681" t="n">
         <v>115.5602</v>
@@ -64368,7 +64368,7 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1683" t="n">
         <v>115.4317</v>
@@ -64406,7 +64406,7 @@
         </is>
       </c>
       <c r="G1684" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1684" t="n">
         <v>114.9728</v>
@@ -64558,7 +64558,7 @@
         </is>
       </c>
       <c r="G1688" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1688" t="n">
         <v>114.826</v>
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.580002</v>
+        <v>63.509998</v>
       </c>
       <c r="H1760" t="n">
-        <v>119.1147</v>
+        <v>118.9835</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.630001</v>
+        <v>35.345001</v>
       </c>
       <c r="H253" t="n">
-        <v>115.8699</v>
+        <v>114.9431</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.990002</v>
+        <v>48.77</v>
       </c>
       <c r="H504" t="n">
-        <v>132.7462</v>
+        <v>132.1501</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.50818599999999</v>
+        <v>64.508179</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.547134</v>
+        <v>64.54714199999999</v>
       </c>
       <c r="H506" t="n">
         <v>100.0604</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.44974499999999</v>
+        <v>64.449753</v>
       </c>
       <c r="H507" t="n">
         <v>99.90940000000001</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.67375199999999</v>
+        <v>64.673744</v>
       </c>
       <c r="H509" t="n">
         <v>100.2567</v>
@@ -19797,7 +19797,7 @@
         <v>64.664001</v>
       </c>
       <c r="H510" t="n">
-        <v>100.2415</v>
+        <v>100.2416</v>
       </c>
     </row>
     <row r="511">
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.18988</v>
+        <v>65.189888</v>
       </c>
       <c r="H511" t="n">
         <v>101.0568</v>
@@ -19911,7 +19911,7 @@
         <v>65.511253</v>
       </c>
       <c r="H513" t="n">
-        <v>101.5549</v>
+        <v>101.555</v>
       </c>
     </row>
     <row r="514">
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H517" t="n">
         <v>102.1739</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H518" t="n">
         <v>100.5586</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.111969</v>
+        <v>65.11198400000001</v>
       </c>
       <c r="H520" t="n">
         <v>100.936</v>
@@ -20215,7 +20215,7 @@
         <v>65.540474</v>
       </c>
       <c r="H521" t="n">
-        <v>101.6002</v>
+        <v>101.6003</v>
       </c>
     </row>
     <row r="522">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.559952</v>
+        <v>65.559944</v>
       </c>
       <c r="H522" t="n">
         <v>101.6304</v>
@@ -20326,10 +20326,10 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.842361</v>
+        <v>65.842377</v>
       </c>
       <c r="H524" t="n">
-        <v>102.0682</v>
+        <v>102.0683</v>
       </c>
     </row>
     <row r="525">
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.939751</v>
+        <v>65.939758</v>
       </c>
       <c r="H526" t="n">
         <v>102.2192</v>
@@ -20478,10 +20478,10 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.407196</v>
+        <v>66.407211</v>
       </c>
       <c r="H528" t="n">
-        <v>102.9438</v>
+        <v>102.9439</v>
       </c>
     </row>
     <row r="529">
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.212433</v>
+        <v>66.212425</v>
       </c>
       <c r="H530" t="n">
         <v>102.6419</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.407196</v>
+        <v>66.407211</v>
       </c>
       <c r="H531" t="n">
-        <v>102.9438</v>
+        <v>102.9439</v>
       </c>
     </row>
     <row r="532">
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H535" t="n">
         <v>102.7627</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>65.988449</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H536" t="n">
         <v>102.2947</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368256</v>
       </c>
       <c r="H538" t="n">
         <v>102.8835</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H539" t="n">
         <v>103.7742</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.77726699999999</v>
+        <v>66.77726</v>
       </c>
       <c r="H542" t="n">
         <v>103.5175</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.416939</v>
+        <v>66.41693100000001</v>
       </c>
       <c r="H543" t="n">
         <v>102.9589</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>65.754723</v>
+        <v>65.754715</v>
       </c>
       <c r="H544" t="n">
         <v>101.9324</v>
@@ -21238,10 +21238,10 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.124786</v>
+        <v>66.12479399999999</v>
       </c>
       <c r="H548" t="n">
-        <v>102.506</v>
+        <v>102.5061</v>
       </c>
     </row>
     <row r="549">
@@ -21279,7 +21279,7 @@
         <v>66.387726</v>
       </c>
       <c r="H549" t="n">
-        <v>102.9136</v>
+        <v>102.9137</v>
       </c>
     </row>
     <row r="550">
@@ -21355,7 +21355,7 @@
         <v>66.96230300000001</v>
       </c>
       <c r="H551" t="n">
-        <v>103.8043</v>
+        <v>103.8044</v>
       </c>
     </row>
     <row r="552">
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.87464900000001</v>
+        <v>66.874657</v>
       </c>
       <c r="H554" t="n">
         <v>103.6685</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H555" t="n">
         <v>103.7742</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.371323</v>
+        <v>67.371315</v>
       </c>
       <c r="H556" t="n">
         <v>104.4384</v>
@@ -21583,7 +21583,7 @@
         <v>67.51739499999999</v>
       </c>
       <c r="H557" t="n">
-        <v>104.6648</v>
+        <v>104.6649</v>
       </c>
     </row>
     <row r="558">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.283669</v>
+        <v>67.283661</v>
       </c>
       <c r="H558" t="n">
         <v>104.3025</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.293419</v>
+        <v>67.29341100000001</v>
       </c>
       <c r="H559" t="n">
         <v>104.3176</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H561" t="n">
         <v>104.6045</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.3908</v>
+        <v>67.390793</v>
       </c>
       <c r="H562" t="n">
         <v>104.4686</v>
@@ -21884,10 +21884,10 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.23497</v>
+        <v>67.234978</v>
       </c>
       <c r="H565" t="n">
-        <v>104.227</v>
+        <v>104.2271</v>
       </c>
     </row>
     <row r="566">
@@ -22001,7 +22001,7 @@
         <v>67.815033</v>
       </c>
       <c r="H568" t="n">
-        <v>105.1262</v>
+        <v>105.1263</v>
       </c>
     </row>
     <row r="569">
@@ -22074,10 +22074,10 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H570" t="n">
-        <v>105.8398</v>
+        <v>105.8399</v>
       </c>
     </row>
     <row r="571">
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H573" t="n">
         <v>107.3429</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H574" t="n">
         <v>108.1628</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H576" t="n">
         <v>108.0414</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H578" t="n">
         <v>108.8005</v>
@@ -22419,7 +22419,7 @@
         <v>70.273376</v>
       </c>
       <c r="H579" t="n">
-        <v>108.9371</v>
+        <v>108.9372</v>
       </c>
     </row>
     <row r="580">
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H585" t="n">
         <v>109.089</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>70.410492</v>
+        <v>70.4105</v>
       </c>
       <c r="H589" t="n">
         <v>109.1497</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H593" t="n">
         <v>111.1235</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H595" t="n">
         <v>112.9758</v>
@@ -23141,7 +23141,7 @@
         <v>73.309578</v>
       </c>
       <c r="H598" t="n">
-        <v>113.6438</v>
+        <v>113.6439</v>
       </c>
     </row>
     <row r="599">
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H599" t="n">
         <v>114.0386</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H601" t="n">
         <v>114.4637</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H604" t="n">
         <v>114.5093</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H608" t="n">
         <v>115.5265</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H613" t="n">
         <v>116.2705</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H614" t="n">
         <v>113.7198</v>
@@ -24012,10 +24012,10 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H621" t="n">
-        <v>112.4747</v>
+        <v>112.4748</v>
       </c>
     </row>
     <row r="622">
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>72.64357800000001</v>
+        <v>72.64357</v>
       </c>
       <c r="H624" t="n">
         <v>112.6114</v>
@@ -24319,7 +24319,7 @@
         <v>72.153915</v>
       </c>
       <c r="H629" t="n">
-        <v>111.8523</v>
+        <v>111.8524</v>
       </c>
     </row>
     <row r="630">
@@ -24737,7 +24737,7 @@
         <v>73.492653</v>
       </c>
       <c r="H640" t="n">
-        <v>113.9276</v>
+        <v>113.9277</v>
       </c>
     </row>
     <row r="641">
@@ -24851,7 +24851,7 @@
         <v>73.807648</v>
       </c>
       <c r="H643" t="n">
-        <v>114.4159</v>
+        <v>114.416</v>
       </c>
     </row>
     <row r="644">
@@ -25383,7 +25383,7 @@
         <v>74.634514</v>
       </c>
       <c r="H657" t="n">
-        <v>115.6977</v>
+        <v>115.6978</v>
       </c>
     </row>
     <row r="658">
@@ -25459,7 +25459,7 @@
         <v>74.634514</v>
       </c>
       <c r="H659" t="n">
-        <v>115.6977</v>
+        <v>115.6978</v>
       </c>
     </row>
     <row r="660">
@@ -26485,7 +26485,7 @@
         <v>78.355408</v>
       </c>
       <c r="H686" t="n">
-        <v>121.4658</v>
+        <v>121.4659</v>
       </c>
     </row>
     <row r="687">
@@ -26561,7 +26561,7 @@
         <v>77.914368</v>
       </c>
       <c r="H688" t="n">
-        <v>120.7821</v>
+        <v>120.7822</v>
       </c>
     </row>
     <row r="689">
@@ -26713,7 +26713,7 @@
         <v>78.68008399999999</v>
       </c>
       <c r="H692" t="n">
-        <v>121.9691</v>
+        <v>121.9692</v>
       </c>
     </row>
     <row r="693">
@@ -27283,7 +27283,7 @@
         <v>79.624802</v>
       </c>
       <c r="H707" t="n">
-        <v>123.4336</v>
+        <v>123.4337</v>
       </c>
     </row>
     <row r="708">
@@ -27663,7 +27663,7 @@
         <v>79.94302399999999</v>
       </c>
       <c r="H717" t="n">
-        <v>123.9269</v>
+        <v>123.927</v>
       </c>
     </row>
     <row r="718">
@@ -27853,7 +27853,7 @@
         <v>80.88774100000001</v>
       </c>
       <c r="H722" t="n">
-        <v>125.3914</v>
+        <v>125.3915</v>
       </c>
     </row>
     <row r="723">
@@ -28385,7 +28385,7 @@
         <v>81.205963</v>
       </c>
       <c r="H736" t="n">
-        <v>125.8847</v>
+        <v>125.8848</v>
       </c>
     </row>
     <row r="737">
@@ -28651,7 +28651,7 @@
         <v>81.653458</v>
       </c>
       <c r="H743" t="n">
-        <v>126.5784</v>
+        <v>126.5785</v>
       </c>
     </row>
     <row r="744">
@@ -28803,7 +28803,7 @@
         <v>80.19163500000001</v>
       </c>
       <c r="H747" t="n">
-        <v>124.3123</v>
+        <v>124.3124</v>
       </c>
     </row>
     <row r="748">
@@ -28955,7 +28955,7 @@
         <v>80.82807200000001</v>
       </c>
       <c r="H751" t="n">
-        <v>125.2989</v>
+        <v>125.299</v>
       </c>
     </row>
     <row r="752">
@@ -29069,7 +29069,7 @@
         <v>80.910004</v>
       </c>
       <c r="H754" t="n">
-        <v>125.4259</v>
+        <v>125.426</v>
       </c>
     </row>
     <row r="755">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.839996</v>
+        <v>80.900002</v>
       </c>
       <c r="H755" t="n">
-        <v>125.3174</v>
+        <v>125.4105</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>129.479996</v>
+        <v>129.100006</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.6935</v>
+        <v>120.3393</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>129.479996</v>
+        <v>129.100006</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.6935</v>
+        <v>120.3393</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>129.479996</v>
+        <v>129.100006</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.6935</v>
+        <v>120.3393</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.542717</v>
+        <v>53.542721</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.425835</v>
+        <v>53.425831</v>
       </c>
       <c r="H1510" t="n">
         <v>99.7817</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.075188</v>
+        <v>53.075184</v>
       </c>
       <c r="H1511" t="n">
         <v>99.1268</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>53.620636</v>
+        <v>53.62064</v>
       </c>
       <c r="H1513" t="n">
         <v>100.1455</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.844669</v>
+        <v>53.844673</v>
       </c>
       <c r="H1514" t="n">
         <v>100.5639</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1515" t="n">
         <v>101.7828</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.062218</v>
+        <v>55.062214</v>
       </c>
       <c r="H1517" t="n">
         <v>102.8379</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1520" t="n">
         <v>103.4746</v>
@@ -58250,10 +58250,10 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.429096</v>
+        <v>54.429089</v>
       </c>
       <c r="H1522" t="n">
-        <v>101.6555</v>
+        <v>101.6554</v>
       </c>
     </row>
     <row r="1523">
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.740788</v>
+        <v>54.740784</v>
       </c>
       <c r="H1523" t="n">
         <v>102.2376</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.53624</v>
+        <v>54.536236</v>
       </c>
       <c r="H1524" t="n">
         <v>101.8556</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1526" t="n">
         <v>103.2017</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>54.682339</v>
+        <v>54.682343</v>
       </c>
       <c r="H1527" t="n">
         <v>102.1284</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1528" t="n">
         <v>103.2017</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1529" t="n">
         <v>103.4746</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.753777</v>
+        <v>55.753784</v>
       </c>
       <c r="H1532" t="n">
         <v>104.1295</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.588192</v>
+        <v>55.588188</v>
       </c>
       <c r="H1534" t="n">
         <v>103.8203</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1535" t="n">
         <v>103.7111</v>
@@ -59165,7 +59165,7 @@
         <v>55.607674</v>
       </c>
       <c r="H1546" t="n">
-        <v>103.8567</v>
+        <v>103.8566</v>
       </c>
     </row>
     <row r="1547">
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1549" t="n">
         <v>101.4008</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1552" t="n">
         <v>101.6373</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1554" t="n">
         <v>103.7111</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.753777</v>
+        <v>55.753784</v>
       </c>
       <c r="H1556" t="n">
         <v>104.1295</v>
@@ -59659,7 +59659,7 @@
         <v>55.724556</v>
       </c>
       <c r="H1559" t="n">
-        <v>104.075</v>
+        <v>104.0749</v>
       </c>
     </row>
     <row r="1560">
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1563" t="n">
         <v>104.2933</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1566" t="n">
         <v>104.3114</v>
@@ -60036,10 +60036,10 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1569" t="n">
-        <v>104.5743</v>
+        <v>104.5742</v>
       </c>
     </row>
     <row r="1570">
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1577" t="n">
         <v>108.7178</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1579" t="n">
         <v>109.2837</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.39616</v>
+        <v>58.396156</v>
       </c>
       <c r="H1580" t="n">
         <v>109.0646</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1582" t="n">
         <v>110.4336</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1584" t="n">
         <v>110.4701</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.91415</v>
+        <v>58.914154</v>
       </c>
       <c r="H1590" t="n">
         <v>110.0321</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>58.835964</v>
+        <v>58.835968</v>
       </c>
       <c r="H1594" t="n">
         <v>109.886</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>58.718685</v>
+        <v>58.718681</v>
       </c>
       <c r="H1595" t="n">
         <v>109.667</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.793755</v>
+        <v>59.793758</v>
       </c>
       <c r="H1597" t="n">
         <v>111.6749</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.803528</v>
+        <v>59.803532</v>
       </c>
       <c r="H1599" t="n">
         <v>111.6931</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.744896</v>
+        <v>59.744892</v>
       </c>
       <c r="H1601" t="n">
         <v>111.5836</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.116276</v>
+        <v>60.11628</v>
       </c>
       <c r="H1603" t="n">
         <v>112.2772</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1605" t="n">
         <v>111.9304</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>59.852402</v>
+        <v>59.852398</v>
       </c>
       <c r="H1606" t="n">
         <v>111.7844</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.653816</v>
+        <v>60.65382</v>
       </c>
       <c r="H1610" t="n">
         <v>113.2812</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1612" t="n">
         <v>113.6827</v>
@@ -61708,10 +61708,10 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1613" t="n">
-        <v>113.9566</v>
+        <v>113.9565</v>
       </c>
     </row>
     <row r="1614">
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>61.406372</v>
+        <v>61.406376</v>
       </c>
       <c r="H1615" t="n">
         <v>114.6867</v>
@@ -61901,7 +61901,7 @@
         <v>58.640495</v>
       </c>
       <c r="H1618" t="n">
-        <v>109.521</v>
+        <v>109.5209</v>
       </c>
     </row>
     <row r="1619">
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1622" t="n">
         <v>107.6774</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1625" t="n">
         <v>108.5353</v>
@@ -62278,7 +62278,7 @@
         </is>
       </c>
       <c r="G1628" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1628" t="n">
         <v>109.1279</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1647" t="n">
         <v>112.3483</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1649" t="n">
         <v>114.0866</v>
@@ -63152,10 +63152,10 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1651" t="n">
-        <v>112.202</v>
+        <v>112.2019</v>
       </c>
     </row>
     <row r="1652">
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1653" t="n">
         <v>111.9641</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1654" t="n">
         <v>111.3603</v>
@@ -63380,7 +63380,7 @@
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1657" t="n">
         <v>110.0977</v>
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1660" t="n">
         <v>111.5615</v>
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1661" t="n">
         <v>114.0317</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="G1663" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1663" t="n">
         <v>112.1654</v>
@@ -63684,7 +63684,7 @@
         </is>
       </c>
       <c r="G1665" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1665" t="n">
         <v>111.1407</v>
@@ -63877,7 +63877,7 @@
         <v>60.066177</v>
       </c>
       <c r="H1670" t="n">
-        <v>112.1837</v>
+        <v>112.1836</v>
       </c>
     </row>
     <row r="1671">
@@ -64064,7 +64064,7 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1675" t="n">
         <v>115.5687</v>
@@ -64105,7 +64105,7 @@
         <v>61.849255</v>
       </c>
       <c r="H1676" t="n">
-        <v>115.5139</v>
+        <v>115.5138</v>
       </c>
     </row>
     <row r="1677">
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1677" t="n">
         <v>115.0747</v>
@@ -64254,7 +64254,7 @@
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1680" t="n">
         <v>115.2028</v>
@@ -64330,7 +64330,7 @@
         </is>
       </c>
       <c r="G1682" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1682" t="n">
         <v>115.0747</v>
@@ -64368,10 +64368,10 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1683" t="n">
-        <v>114.6173</v>
+        <v>114.6172</v>
       </c>
     </row>
     <row r="1684">
@@ -64447,7 +64447,7 @@
         <v>60.957718</v>
       </c>
       <c r="H1685" t="n">
-        <v>113.8488</v>
+        <v>113.8487</v>
       </c>
     </row>
     <row r="1686">
@@ -64520,7 +64520,7 @@
         </is>
       </c>
       <c r="G1687" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1687" t="n">
         <v>114.4709</v>
@@ -64713,7 +64713,7 @@
         <v>62.766766</v>
       </c>
       <c r="H1692" t="n">
-        <v>117.2275</v>
+        <v>117.2274</v>
       </c>
     </row>
     <row r="1693">
@@ -64979,7 +64979,7 @@
         <v>62.766766</v>
       </c>
       <c r="H1699" t="n">
-        <v>117.2275</v>
+        <v>117.2274</v>
       </c>
     </row>
     <row r="1700">
@@ -65017,7 +65017,7 @@
         <v>63.341331</v>
       </c>
       <c r="H1700" t="n">
-        <v>118.3006</v>
+        <v>118.3005</v>
       </c>
     </row>
     <row r="1701">
@@ -65131,7 +65131,7 @@
         <v>64.450844</v>
       </c>
       <c r="H1703" t="n">
-        <v>120.3728</v>
+        <v>120.3727</v>
       </c>
     </row>
     <row r="1704">
@@ -65283,7 +65283,7 @@
         <v>63.321518</v>
       </c>
       <c r="H1707" t="n">
-        <v>118.2636</v>
+        <v>118.2635</v>
       </c>
     </row>
     <row r="1708">
@@ -65777,7 +65777,7 @@
         <v>63.886181</v>
       </c>
       <c r="H1720" t="n">
-        <v>119.3182</v>
+        <v>119.3181</v>
       </c>
     </row>
     <row r="1721">
@@ -65967,7 +65967,7 @@
         <v>64.95607</v>
       </c>
       <c r="H1725" t="n">
-        <v>121.3164</v>
+        <v>121.3163</v>
       </c>
     </row>
     <row r="1726">
@@ -66689,7 +66689,7 @@
         <v>64.361694</v>
       </c>
       <c r="H1744" t="n">
-        <v>120.2063</v>
+        <v>120.2062</v>
       </c>
     </row>
     <row r="1745">
@@ -66841,7 +66841,7 @@
         <v>64.39141100000001</v>
       </c>
       <c r="H1748" t="n">
-        <v>120.2618</v>
+        <v>120.2617</v>
       </c>
     </row>
     <row r="1749">
@@ -66879,7 +66879,7 @@
         <v>64.361694</v>
       </c>
       <c r="H1749" t="n">
-        <v>120.2063</v>
+        <v>120.2062</v>
       </c>
     </row>
     <row r="1750">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.27</v>
+        <v>63.290001</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.1673</v>
+        <v>118.2047</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.345001</v>
+        <v>35.98</v>
       </c>
       <c r="H253" t="n">
-        <v>114.9431</v>
+        <v>117.0081</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.77</v>
+        <v>48.865002</v>
       </c>
       <c r="H504" t="n">
-        <v>132.1501</v>
+        <v>132.4075</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.508179</v>
+        <v>64.50818599999999</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.54714199999999</v>
+        <v>64.547134</v>
       </c>
       <c r="H506" t="n">
         <v>100.0604</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.449753</v>
+        <v>64.44974499999999</v>
       </c>
       <c r="H507" t="n">
         <v>99.90940000000001</v>
@@ -19759,7 +19759,7 @@
         <v>64.673744</v>
       </c>
       <c r="H509" t="n">
-        <v>100.2567</v>
+        <v>100.2566</v>
       </c>
     </row>
     <row r="510">
@@ -19797,7 +19797,7 @@
         <v>64.664001</v>
       </c>
       <c r="H510" t="n">
-        <v>100.2416</v>
+        <v>100.2415</v>
       </c>
     </row>
     <row r="511">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H512" t="n">
         <v>101.0115</v>
@@ -19911,7 +19911,7 @@
         <v>65.511253</v>
       </c>
       <c r="H513" t="n">
-        <v>101.555</v>
+        <v>101.5549</v>
       </c>
     </row>
     <row r="514">
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.11198400000001</v>
+        <v>65.111969</v>
       </c>
       <c r="H520" t="n">
         <v>100.936</v>
@@ -20215,7 +20215,7 @@
         <v>65.540474</v>
       </c>
       <c r="H521" t="n">
-        <v>101.6003</v>
+        <v>101.6002</v>
       </c>
     </row>
     <row r="522">
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.559944</v>
+        <v>65.559952</v>
       </c>
       <c r="H522" t="n">
         <v>101.6304</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H523" t="n">
         <v>100.9511</v>
@@ -20326,10 +20326,10 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.842377</v>
+        <v>65.842361</v>
       </c>
       <c r="H524" t="n">
-        <v>102.0683</v>
+        <v>102.0682</v>
       </c>
     </row>
     <row r="525">
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H526" t="n">
         <v>102.2192</v>
@@ -20478,10 +20478,10 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.407211</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H528" t="n">
-        <v>102.9439</v>
+        <v>102.9438</v>
       </c>
     </row>
     <row r="529">
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H530" t="n">
         <v>102.6419</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.407211</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H531" t="n">
-        <v>102.9439</v>
+        <v>102.9438</v>
       </c>
     </row>
     <row r="532">
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H535" t="n">
         <v>102.7627</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H538" t="n">
         <v>102.8835</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H539" t="n">
         <v>103.7742</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H541" t="n">
         <v>103.9553</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.77726</v>
+        <v>66.777275</v>
       </c>
       <c r="H542" t="n">
         <v>103.5175</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.41693100000001</v>
+        <v>66.416939</v>
       </c>
       <c r="H543" t="n">
         <v>102.9589</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H546" t="n">
         <v>102.3551</v>
@@ -21238,10 +21238,10 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.12479399999999</v>
+        <v>66.124786</v>
       </c>
       <c r="H548" t="n">
-        <v>102.5061</v>
+        <v>102.506</v>
       </c>
     </row>
     <row r="549">
@@ -21279,7 +21279,7 @@
         <v>66.387726</v>
       </c>
       <c r="H549" t="n">
-        <v>102.9137</v>
+        <v>102.9136</v>
       </c>
     </row>
     <row r="550">
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H550" t="n">
         <v>103.8647</v>
@@ -21355,7 +21355,7 @@
         <v>66.96230300000001</v>
       </c>
       <c r="H551" t="n">
-        <v>103.8044</v>
+        <v>103.8043</v>
       </c>
     </row>
     <row r="552">
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H553" t="n">
         <v>103.9553</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.874657</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H554" t="n">
         <v>103.6685</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H555" t="n">
         <v>103.7742</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H556" t="n">
         <v>104.4384</v>
@@ -21583,7 +21583,7 @@
         <v>67.51739499999999</v>
       </c>
       <c r="H557" t="n">
-        <v>104.6649</v>
+        <v>104.6648</v>
       </c>
     </row>
     <row r="558">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.283661</v>
+        <v>67.283676</v>
       </c>
       <c r="H558" t="n">
         <v>104.3025</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.22524300000001</v>
+        <v>67.22525</v>
       </c>
       <c r="H560" t="n">
         <v>104.212</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.478447</v>
+        <v>67.47843899999999</v>
       </c>
       <c r="H561" t="n">
         <v>104.6045</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H562" t="n">
         <v>104.4686</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H563" t="n">
         <v>105.0574</v>
@@ -21884,10 +21884,10 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.234978</v>
+        <v>67.23497</v>
       </c>
       <c r="H565" t="n">
-        <v>104.2271</v>
+        <v>104.227</v>
       </c>
     </row>
     <row r="566">
@@ -22001,7 +22001,7 @@
         <v>67.815033</v>
       </c>
       <c r="H568" t="n">
-        <v>105.1263</v>
+        <v>105.1262</v>
       </c>
     </row>
     <row r="569">
@@ -22419,7 +22419,7 @@
         <v>70.273376</v>
       </c>
       <c r="H579" t="n">
-        <v>108.9372</v>
+        <v>108.9371</v>
       </c>
     </row>
     <row r="580">
@@ -23141,7 +23141,7 @@
         <v>73.309578</v>
       </c>
       <c r="H598" t="n">
-        <v>113.6439</v>
+        <v>113.6438</v>
       </c>
     </row>
     <row r="599">
@@ -23749,7 +23749,7 @@
         <v>73.358543</v>
       </c>
       <c r="H614" t="n">
-        <v>113.7198</v>
+        <v>113.7197</v>
       </c>
     </row>
     <row r="615">
@@ -24319,7 +24319,7 @@
         <v>72.153915</v>
       </c>
       <c r="H629" t="n">
-        <v>111.8524</v>
+        <v>111.8523</v>
       </c>
     </row>
     <row r="630">
@@ -24737,7 +24737,7 @@
         <v>73.492653</v>
       </c>
       <c r="H640" t="n">
-        <v>113.9277</v>
+        <v>113.9276</v>
       </c>
     </row>
     <row r="641">
@@ -24851,7 +24851,7 @@
         <v>73.807648</v>
       </c>
       <c r="H643" t="n">
-        <v>114.416</v>
+        <v>114.4159</v>
       </c>
     </row>
     <row r="644">
@@ -25383,7 +25383,7 @@
         <v>74.634514</v>
       </c>
       <c r="H657" t="n">
-        <v>115.6978</v>
+        <v>115.6977</v>
       </c>
     </row>
     <row r="658">
@@ -25459,7 +25459,7 @@
         <v>74.634514</v>
       </c>
       <c r="H659" t="n">
-        <v>115.6978</v>
+        <v>115.6977</v>
       </c>
     </row>
     <row r="660">
@@ -26485,7 +26485,7 @@
         <v>78.355408</v>
       </c>
       <c r="H686" t="n">
-        <v>121.4659</v>
+        <v>121.4658</v>
       </c>
     </row>
     <row r="687">
@@ -26561,7 +26561,7 @@
         <v>77.914368</v>
       </c>
       <c r="H688" t="n">
-        <v>120.7822</v>
+        <v>120.7821</v>
       </c>
     </row>
     <row r="689">
@@ -26713,7 +26713,7 @@
         <v>78.68008399999999</v>
       </c>
       <c r="H692" t="n">
-        <v>121.9692</v>
+        <v>121.9691</v>
       </c>
     </row>
     <row r="693">
@@ -27283,7 +27283,7 @@
         <v>79.624802</v>
       </c>
       <c r="H707" t="n">
-        <v>123.4337</v>
+        <v>123.4336</v>
       </c>
     </row>
     <row r="708">
@@ -27663,7 +27663,7 @@
         <v>79.94302399999999</v>
       </c>
       <c r="H717" t="n">
-        <v>123.927</v>
+        <v>123.9269</v>
       </c>
     </row>
     <row r="718">
@@ -27853,7 +27853,7 @@
         <v>80.88774100000001</v>
       </c>
       <c r="H722" t="n">
-        <v>125.3915</v>
+        <v>125.3914</v>
       </c>
     </row>
     <row r="723">
@@ -28385,7 +28385,7 @@
         <v>81.205963</v>
       </c>
       <c r="H736" t="n">
-        <v>125.8848</v>
+        <v>125.8847</v>
       </c>
     </row>
     <row r="737">
@@ -28651,7 +28651,7 @@
         <v>81.653458</v>
       </c>
       <c r="H743" t="n">
-        <v>126.5785</v>
+        <v>126.5784</v>
       </c>
     </row>
     <row r="744">
@@ -28803,7 +28803,7 @@
         <v>80.19163500000001</v>
       </c>
       <c r="H747" t="n">
-        <v>124.3124</v>
+        <v>124.3123</v>
       </c>
     </row>
     <row r="748">
@@ -28955,7 +28955,7 @@
         <v>80.82807200000001</v>
       </c>
       <c r="H751" t="n">
-        <v>125.299</v>
+        <v>125.2989</v>
       </c>
     </row>
     <row r="752">
@@ -29069,7 +29069,7 @@
         <v>80.910004</v>
       </c>
       <c r="H754" t="n">
-        <v>125.426</v>
+        <v>125.4259</v>
       </c>
     </row>
     <row r="755">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.900002</v>
+        <v>80.760002</v>
       </c>
       <c r="H755" t="n">
-        <v>125.4105</v>
+        <v>125.1934</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>129.100006</v>
+        <v>129.119995</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.3393</v>
+        <v>120.3579</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>129.100006</v>
+        <v>129.119995</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.3393</v>
+        <v>120.3579</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>129.100006</v>
+        <v>129.119995</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.3393</v>
+        <v>120.3579</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.542721</v>
+        <v>53.542717</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.075184</v>
+        <v>53.07518</v>
       </c>
       <c r="H1511" t="n">
         <v>99.1268</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>53.844673</v>
+        <v>53.844669</v>
       </c>
       <c r="H1514" t="n">
         <v>100.5639</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.497276</v>
+        <v>54.497272</v>
       </c>
       <c r="H1515" t="n">
         <v>101.7828</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.799221</v>
+        <v>54.799225</v>
       </c>
       <c r="H1516" t="n">
         <v>102.3467</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.974552</v>
+        <v>54.974548</v>
       </c>
       <c r="H1519" t="n">
         <v>102.6742</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1520" t="n">
         <v>103.4746</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.159618</v>
+        <v>55.159622</v>
       </c>
       <c r="H1521" t="n">
         <v>103.0198</v>
@@ -58250,10 +58250,10 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.429089</v>
+        <v>54.429092</v>
       </c>
       <c r="H1522" t="n">
-        <v>101.6554</v>
+        <v>101.6555</v>
       </c>
     </row>
     <row r="1523">
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.818703</v>
+        <v>54.818699</v>
       </c>
       <c r="H1525" t="n">
         <v>102.3831</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1526" t="n">
         <v>103.2017</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>54.682343</v>
+        <v>54.682339</v>
       </c>
       <c r="H1527" t="n">
         <v>102.1284</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1528" t="n">
         <v>103.2017</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1529" t="n">
         <v>103.4746</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1530" t="n">
         <v>103.2381</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.753784</v>
+        <v>55.753777</v>
       </c>
       <c r="H1532" t="n">
         <v>104.1295</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1533" t="n">
         <v>103.9112</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.588188</v>
+        <v>55.588196</v>
       </c>
       <c r="H1534" t="n">
         <v>103.8203</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1535" t="n">
         <v>103.7111</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.325203</v>
+        <v>55.325199</v>
       </c>
       <c r="H1537" t="n">
         <v>103.3291</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.169357</v>
+        <v>55.169353</v>
       </c>
       <c r="H1538" t="n">
         <v>103.038</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1539" t="n">
         <v>103.2381</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.607674</v>
+        <v>55.60767</v>
       </c>
       <c r="H1546" t="n">
         <v>103.8566</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.305721</v>
+        <v>55.305725</v>
       </c>
       <c r="H1547" t="n">
         <v>103.2927</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1549" t="n">
         <v>101.4008</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1550" t="n">
         <v>101.7646</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>54.351166</v>
+        <v>54.35117</v>
       </c>
       <c r="H1551" t="n">
         <v>101.5099</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1552" t="n">
         <v>101.6373</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1554" t="n">
         <v>103.7111</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1555" t="n">
         <v>103.7839</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.753784</v>
+        <v>55.753777</v>
       </c>
       <c r="H1556" t="n">
         <v>104.1295</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1557" t="n">
         <v>103.7839</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1558" t="n">
         <v>103.9112</v>
@@ -59659,7 +59659,7 @@
         <v>55.724556</v>
       </c>
       <c r="H1559" t="n">
-        <v>104.0749</v>
+        <v>104.075</v>
       </c>
     </row>
     <row r="1560">
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.987545</v>
+        <v>55.987541</v>
       </c>
       <c r="H1561" t="n">
         <v>104.5661</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.841446</v>
+        <v>55.841442</v>
       </c>
       <c r="H1563" t="n">
         <v>104.2933</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1566" t="n">
         <v>104.3114</v>
@@ -60036,10 +60036,10 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1569" t="n">
-        <v>104.5742</v>
+        <v>104.5743</v>
       </c>
     </row>
     <row r="1570">
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1571" t="n">
         <v>106.0528</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.676041</v>
+        <v>56.676037</v>
       </c>
       <c r="H1572" t="n">
         <v>105.852</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1574" t="n">
         <v>106.3996</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1577" t="n">
         <v>108.7178</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1579" t="n">
         <v>109.2837</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.396156</v>
+        <v>58.39616</v>
       </c>
       <c r="H1580" t="n">
         <v>109.0646</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>59.129169</v>
+        <v>59.129166</v>
       </c>
       <c r="H1582" t="n">
         <v>110.4336</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1585" t="n">
         <v>111.109</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1586" t="n">
         <v>111.1273</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>58.259331</v>
+        <v>58.259335</v>
       </c>
       <c r="H1589" t="n">
         <v>108.8091</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.914154</v>
+        <v>58.91415</v>
       </c>
       <c r="H1590" t="n">
         <v>110.0321</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1593" t="n">
         <v>110.7622</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>58.835968</v>
+        <v>58.835964</v>
       </c>
       <c r="H1594" t="n">
         <v>109.886</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>58.718681</v>
+        <v>58.718685</v>
       </c>
       <c r="H1595" t="n">
         <v>109.667</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.168259</v>
+        <v>59.168262</v>
       </c>
       <c r="H1596" t="n">
         <v>110.5066</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.246449</v>
+        <v>59.246445</v>
       </c>
       <c r="H1600" t="n">
         <v>110.6527</v>
@@ -61290,10 +61290,10 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>60.155373</v>
+        <v>60.155376</v>
       </c>
       <c r="H1602" t="n">
-        <v>112.3502</v>
+        <v>112.3503</v>
       </c>
     </row>
     <row r="1603">
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1604" t="n">
         <v>112.4415</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1605" t="n">
         <v>111.9304</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>59.852398</v>
+        <v>59.852402</v>
       </c>
       <c r="H1606" t="n">
         <v>111.7844</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1607" t="n">
         <v>111.9487</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1608" t="n">
         <v>112.551</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.956795</v>
+        <v>60.956791</v>
       </c>
       <c r="H1609" t="n">
         <v>113.847</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.201126</v>
+        <v>61.20113</v>
       </c>
       <c r="H1611" t="n">
         <v>114.3034</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1612" t="n">
         <v>113.6827</v>
@@ -61708,10 +61708,10 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>61.015434</v>
+        <v>61.015438</v>
       </c>
       <c r="H1613" t="n">
-        <v>113.9565</v>
+        <v>113.9566</v>
       </c>
     </row>
     <row r="1614">
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>61.474785</v>
+        <v>61.474789</v>
       </c>
       <c r="H1614" t="n">
         <v>114.8145</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>61.406376</v>
+        <v>61.406372</v>
       </c>
       <c r="H1615" t="n">
         <v>114.6867</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>61.445465</v>
+        <v>61.445469</v>
       </c>
       <c r="H1616" t="n">
         <v>114.7597</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.640495</v>
+        <v>58.640491</v>
       </c>
       <c r="H1618" t="n">
         <v>109.5209</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>58.581852</v>
+        <v>58.581856</v>
       </c>
       <c r="H1620" t="n">
         <v>109.4114</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1622" t="n">
         <v>107.6774</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1623" t="n">
         <v>109.7948</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>58.112728</v>
+        <v>58.112732</v>
       </c>
       <c r="H1625" t="n">
         <v>108.5353</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>57.790211</v>
+        <v>57.790207</v>
       </c>
       <c r="H1626" t="n">
         <v>107.9329</v>
@@ -62278,7 +62278,7 @@
         </is>
       </c>
       <c r="G1628" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1628" t="n">
         <v>109.1279</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1647" t="n">
         <v>112.3483</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1649" t="n">
         <v>114.0866</v>
@@ -63152,10 +63152,10 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1651" t="n">
-        <v>112.2019</v>
+        <v>112.202</v>
       </c>
     </row>
     <row r="1652">
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1653" t="n">
         <v>111.9641</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1654" t="n">
         <v>111.3603</v>
@@ -63380,7 +63380,7 @@
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1657" t="n">
         <v>110.0977</v>
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1660" t="n">
         <v>111.5615</v>
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1661" t="n">
         <v>114.0317</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="G1663" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1663" t="n">
         <v>112.1654</v>
@@ -63684,7 +63684,7 @@
         </is>
       </c>
       <c r="G1665" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1665" t="n">
         <v>111.1407</v>
@@ -63877,7 +63877,7 @@
         <v>60.066177</v>
       </c>
       <c r="H1670" t="n">
-        <v>112.1836</v>
+        <v>112.1837</v>
       </c>
     </row>
     <row r="1671">
@@ -64064,7 +64064,7 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1675" t="n">
         <v>115.5687</v>
@@ -64105,7 +64105,7 @@
         <v>61.849255</v>
       </c>
       <c r="H1676" t="n">
-        <v>115.5138</v>
+        <v>115.5139</v>
       </c>
     </row>
     <row r="1677">
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1677" t="n">
         <v>115.0747</v>
@@ -64254,7 +64254,7 @@
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1680" t="n">
         <v>115.2028</v>
@@ -64330,7 +64330,7 @@
         </is>
       </c>
       <c r="G1682" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1682" t="n">
         <v>115.0747</v>
@@ -64368,10 +64368,10 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1683" t="n">
-        <v>114.6172</v>
+        <v>114.6173</v>
       </c>
     </row>
     <row r="1684">
@@ -64447,7 +64447,7 @@
         <v>60.957718</v>
       </c>
       <c r="H1685" t="n">
-        <v>113.8487</v>
+        <v>113.8488</v>
       </c>
     </row>
     <row r="1686">
@@ -64520,7 +64520,7 @@
         </is>
       </c>
       <c r="G1687" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1687" t="n">
         <v>114.4709</v>
@@ -64713,7 +64713,7 @@
         <v>62.766766</v>
       </c>
       <c r="H1692" t="n">
-        <v>117.2274</v>
+        <v>117.2275</v>
       </c>
     </row>
     <row r="1693">
@@ -64979,7 +64979,7 @@
         <v>62.766766</v>
       </c>
       <c r="H1699" t="n">
-        <v>117.2274</v>
+        <v>117.2275</v>
       </c>
     </row>
     <row r="1700">
@@ -65017,7 +65017,7 @@
         <v>63.341331</v>
       </c>
       <c r="H1700" t="n">
-        <v>118.3005</v>
+        <v>118.3006</v>
       </c>
     </row>
     <row r="1701">
@@ -65131,7 +65131,7 @@
         <v>64.450844</v>
       </c>
       <c r="H1703" t="n">
-        <v>120.3727</v>
+        <v>120.3728</v>
       </c>
     </row>
     <row r="1704">
@@ -65283,7 +65283,7 @@
         <v>63.321518</v>
       </c>
       <c r="H1707" t="n">
-        <v>118.2635</v>
+        <v>118.2636</v>
       </c>
     </row>
     <row r="1708">
@@ -65777,7 +65777,7 @@
         <v>63.886181</v>
       </c>
       <c r="H1720" t="n">
-        <v>119.3181</v>
+        <v>119.3182</v>
       </c>
     </row>
     <row r="1721">
@@ -65967,7 +65967,7 @@
         <v>64.95607</v>
       </c>
       <c r="H1725" t="n">
-        <v>121.3163</v>
+        <v>121.3164</v>
       </c>
     </row>
     <row r="1726">
@@ -66689,7 +66689,7 @@
         <v>64.361694</v>
       </c>
       <c r="H1744" t="n">
-        <v>120.2062</v>
+        <v>120.2063</v>
       </c>
     </row>
     <row r="1745">
@@ -66841,7 +66841,7 @@
         <v>64.39141100000001</v>
       </c>
       <c r="H1748" t="n">
-        <v>120.2617</v>
+        <v>120.2618</v>
       </c>
     </row>
     <row r="1749">
@@ -66879,7 +66879,7 @@
         <v>64.361694</v>
       </c>
       <c r="H1749" t="n">
-        <v>120.2062</v>
+        <v>120.2063</v>
       </c>
     </row>
     <row r="1750">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.290001</v>
+        <v>63.360001</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.2047</v>
+        <v>118.3354</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.547134</v>
+        <v>64.54714199999999</v>
       </c>
       <c r="H506" t="n">
         <v>100.0604</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.44974499999999</v>
+        <v>64.449753</v>
       </c>
       <c r="H507" t="n">
         <v>99.90940000000001</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.74191999999999</v>
+        <v>64.741913</v>
       </c>
       <c r="H508" t="n">
         <v>100.3623</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.189888</v>
+        <v>65.18988</v>
       </c>
       <c r="H511" t="n">
         <v>101.0568</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.160667</v>
+        <v>65.160675</v>
       </c>
       <c r="H512" t="n">
         <v>101.0115</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H518" t="n">
         <v>100.5586</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H520" t="n">
         <v>100.936</v>
@@ -20212,10 +20212,10 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.540474</v>
+        <v>65.540482</v>
       </c>
       <c r="H521" t="n">
-        <v>101.6002</v>
+        <v>101.6003</v>
       </c>
     </row>
     <row r="522">
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.121712</v>
+        <v>65.121719</v>
       </c>
       <c r="H523" t="n">
         <v>100.9511</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.842361</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H524" t="n">
         <v>102.0682</v>
@@ -20440,10 +20440,10 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.06635300000001</v>
+        <v>66.066345</v>
       </c>
       <c r="H527" t="n">
-        <v>102.4155</v>
+        <v>102.4154</v>
       </c>
     </row>
     <row r="528">
@@ -20478,10 +20478,10 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407211</v>
       </c>
       <c r="H528" t="n">
-        <v>102.9438</v>
+        <v>102.9439</v>
       </c>
     </row>
     <row r="529">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.339035</v>
+        <v>66.339043</v>
       </c>
       <c r="H529" t="n">
         <v>102.8382</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407211</v>
       </c>
       <c r="H531" t="n">
-        <v>102.9438</v>
+        <v>102.9439</v>
       </c>
     </row>
     <row r="532">
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H533" t="n">
         <v>102.4004</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>65.98844099999999</v>
+        <v>65.988449</v>
       </c>
       <c r="H536" t="n">
         <v>102.2947</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H542" t="n">
         <v>103.5175</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027405</v>
       </c>
       <c r="H546" t="n">
         <v>102.3551</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.124786</v>
+        <v>66.124779</v>
       </c>
       <c r="H548" t="n">
         <v>102.506</v>
@@ -21276,10 +21276,10 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.387726</v>
+        <v>66.387733</v>
       </c>
       <c r="H549" t="n">
-        <v>102.9136</v>
+        <v>102.9137</v>
       </c>
     </row>
     <row r="550">
@@ -21352,10 +21352,10 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.96230300000001</v>
+        <v>66.962311</v>
       </c>
       <c r="H551" t="n">
-        <v>103.8043</v>
+        <v>103.8044</v>
       </c>
     </row>
     <row r="552">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.283676</v>
+        <v>67.283669</v>
       </c>
       <c r="H558" t="n">
         <v>104.3025</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H561" t="n">
         <v>104.6045</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H564" t="n">
         <v>104.1214</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.23497</v>
+        <v>67.234978</v>
       </c>
       <c r="H565" t="n">
         <v>104.227</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H567" t="n">
         <v>105.2477</v>
@@ -22074,10 +22074,10 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H570" t="n">
-        <v>105.8399</v>
+        <v>105.8398</v>
       </c>
     </row>
     <row r="571">
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.30474100000001</v>
+        <v>68.304733</v>
       </c>
       <c r="H571" t="n">
         <v>105.8854</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H572" t="n">
         <v>106.2194</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>69.24498</v>
+        <v>69.24498699999999</v>
       </c>
       <c r="H573" t="n">
         <v>107.3429</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H576" t="n">
         <v>108.0414</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>71.340942</v>
+        <v>71.340935</v>
       </c>
       <c r="H581" t="n">
         <v>110.5921</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H582" t="n">
         <v>110.5162</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H584" t="n">
         <v>108.6183</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H586" t="n">
         <v>109.8633</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.51823400000001</v>
+        <v>70.518227</v>
       </c>
       <c r="H587" t="n">
         <v>109.3167</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>70.4105</v>
+        <v>70.410484</v>
       </c>
       <c r="H589" t="n">
         <v>109.1497</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>70.684731</v>
+        <v>70.68472300000001</v>
       </c>
       <c r="H591" t="n">
         <v>109.5748</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H593" t="n">
         <v>111.1235</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H596" t="n">
         <v>112.1559</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H598" t="n">
         <v>113.6438</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H599" t="n">
         <v>114.0386</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H600" t="n">
         <v>114.904</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H601" t="n">
         <v>114.4637</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H605" t="n">
         <v>115.481</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H606" t="n">
         <v>115.481</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.524055</v>
+        <v>74.524063</v>
       </c>
       <c r="H608" t="n">
         <v>115.5265</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H609" t="n">
         <v>115.8454</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>75.14109000000001</v>
+        <v>75.141098</v>
       </c>
       <c r="H610" t="n">
         <v>116.483</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>75.27821400000001</v>
+        <v>75.278206</v>
       </c>
       <c r="H611" t="n">
         <v>116.6956</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>75.003967</v>
+        <v>75.00398300000001</v>
       </c>
       <c r="H613" t="n">
         <v>116.2705</v>
@@ -23746,10 +23746,10 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>73.358543</v>
+        <v>73.35855100000001</v>
       </c>
       <c r="H614" t="n">
-        <v>113.7197</v>
+        <v>113.7198</v>
       </c>
     </row>
     <row r="615">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>72.721931</v>
+        <v>72.721924</v>
       </c>
       <c r="H619" t="n">
         <v>112.7329</v>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H620" t="n">
         <v>112.2926</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H625" t="n">
         <v>110.8605</v>
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H626" t="n">
         <v>109.8381</v>
@@ -24278,7 +24278,7 @@
         </is>
       </c>
       <c r="G628" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H628" t="n">
         <v>110.6926</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H631" t="n">
         <v>110.6926</v>
@@ -24506,10 +24506,10 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H634" t="n">
-        <v>112.6764</v>
+        <v>112.6763</v>
       </c>
     </row>
     <row r="635">
@@ -24582,7 +24582,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H636" t="n">
         <v>112.3101</v>
@@ -24658,7 +24658,7 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H638" t="n">
         <v>114.6296</v>
@@ -24696,10 +24696,10 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H639" t="n">
-        <v>114.3702</v>
+        <v>114.3701</v>
       </c>
     </row>
     <row r="640">
@@ -24772,7 +24772,7 @@
         </is>
       </c>
       <c r="G641" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H641" t="n">
         <v>114.4465</v>
@@ -24848,10 +24848,10 @@
         </is>
       </c>
       <c r="G643" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H643" t="n">
-        <v>114.4159</v>
+        <v>114.416</v>
       </c>
     </row>
     <row r="644">
@@ -25000,7 +25000,7 @@
         </is>
       </c>
       <c r="G647" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H647" t="n">
         <v>114.4465</v>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H650" t="n">
         <v>113.9887</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H651" t="n">
         <v>114.3854</v>
@@ -25228,7 +25228,7 @@
         </is>
       </c>
       <c r="G653" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H653" t="n">
         <v>115.3773</v>
@@ -25342,7 +25342,7 @@
         </is>
       </c>
       <c r="G656" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H656" t="n">
         <v>116.476</v>
@@ -25380,7 +25380,7 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H657" t="n">
         <v>115.6977</v>
@@ -25456,7 +25456,7 @@
         </is>
       </c>
       <c r="G659" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H659" t="n">
         <v>115.6977</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H664" t="n">
         <v>116.4149</v>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H669" t="n">
         <v>119.5126</v>
@@ -25912,7 +25912,7 @@
         </is>
       </c>
       <c r="G671" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H671" t="n">
         <v>118.7039</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="G673" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H673" t="n">
         <v>118.2461</v>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H674" t="n">
         <v>118.0935</v>
@@ -26216,7 +26216,7 @@
         </is>
       </c>
       <c r="G679" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H679" t="n">
         <v>118.7344</v>
@@ -26254,10 +26254,10 @@
         </is>
       </c>
       <c r="G680" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H680" t="n">
-        <v>118.0325</v>
+        <v>118.0324</v>
       </c>
     </row>
     <row r="681">
@@ -26482,7 +26482,7 @@
         </is>
       </c>
       <c r="G686" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H686" t="n">
         <v>121.4658</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.07518</v>
+        <v>53.075184</v>
       </c>
       <c r="H1511" t="n">
         <v>99.1268</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>53.523239</v>
+        <v>53.523235</v>
       </c>
       <c r="H1512" t="n">
         <v>99.9636</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1515" t="n">
         <v>101.7828</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.799225</v>
+        <v>54.799221</v>
       </c>
       <c r="H1516" t="n">
         <v>102.3467</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1520" t="n">
         <v>103.4746</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.159622</v>
+        <v>55.159618</v>
       </c>
       <c r="H1521" t="n">
         <v>103.0198</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.536236</v>
+        <v>54.53624</v>
       </c>
       <c r="H1524" t="n">
         <v>101.8556</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.818699</v>
+        <v>54.818703</v>
       </c>
       <c r="H1525" t="n">
         <v>102.3831</v>
@@ -58402,10 +58402,10 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1526" t="n">
-        <v>103.2017</v>
+        <v>103.2018</v>
       </c>
     </row>
     <row r="1527">
@@ -58478,10 +58478,10 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1528" t="n">
-        <v>103.2017</v>
+        <v>103.2018</v>
       </c>
     </row>
     <row r="1529">
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1529" t="n">
         <v>103.4746</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1530" t="n">
         <v>103.2381</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1532" t="n">
         <v>104.1295</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1533" t="n">
         <v>103.9112</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.588196</v>
+        <v>55.588192</v>
       </c>
       <c r="H1534" t="n">
         <v>103.8203</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1535" t="n">
         <v>103.7111</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.169353</v>
+        <v>55.169357</v>
       </c>
       <c r="H1538" t="n">
         <v>103.038</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1539" t="n">
         <v>103.2381</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.867409</v>
+        <v>54.867405</v>
       </c>
       <c r="H1540" t="n">
         <v>102.4741</v>
@@ -59162,10 +59162,10 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.60767</v>
+        <v>55.607674</v>
       </c>
       <c r="H1546" t="n">
-        <v>103.8566</v>
+        <v>103.8567</v>
       </c>
     </row>
     <row r="1547">
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.305725</v>
+        <v>55.305721</v>
       </c>
       <c r="H1547" t="n">
         <v>103.2927</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.487534</v>
+        <v>54.48753</v>
       </c>
       <c r="H1550" t="n">
         <v>101.7646</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1552" t="n">
         <v>101.6373</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1554" t="n">
         <v>103.7111</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1555" t="n">
         <v>103.7839</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1556" t="n">
         <v>104.1295</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1557" t="n">
         <v>103.7839</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1558" t="n">
         <v>103.9112</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.987541</v>
+        <v>55.987545</v>
       </c>
       <c r="H1561" t="n">
         <v>104.5661</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1563" t="n">
         <v>104.2933</v>
@@ -59922,10 +59922,10 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1566" t="n">
-        <v>104.3114</v>
+        <v>104.3115</v>
       </c>
     </row>
     <row r="1567">
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1571" t="n">
         <v>106.0528</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.676037</v>
+        <v>56.676041</v>
       </c>
       <c r="H1572" t="n">
         <v>105.852</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1574" t="n">
         <v>106.3996</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1584" t="n">
         <v>110.4701</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1585" t="n">
         <v>111.109</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1586" t="n">
         <v>111.1273</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>58.259335</v>
+        <v>58.259331</v>
       </c>
       <c r="H1589" t="n">
         <v>108.8091</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>59.305092</v>
+        <v>59.305088</v>
       </c>
       <c r="H1593" t="n">
         <v>110.7622</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.168262</v>
+        <v>59.168259</v>
       </c>
       <c r="H1596" t="n">
         <v>110.5066</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.793758</v>
+        <v>59.793755</v>
       </c>
       <c r="H1597" t="n">
         <v>111.6749</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.803532</v>
+        <v>59.803528</v>
       </c>
       <c r="H1599" t="n">
         <v>111.6931</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.246445</v>
+        <v>59.246449</v>
       </c>
       <c r="H1600" t="n">
         <v>110.6527</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.744892</v>
+        <v>59.744896</v>
       </c>
       <c r="H1601" t="n">
         <v>111.5836</v>
@@ -61290,10 +61290,10 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>60.155376</v>
+        <v>60.155373</v>
       </c>
       <c r="H1602" t="n">
-        <v>112.3503</v>
+        <v>112.3502</v>
       </c>
     </row>
     <row r="1603">
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.11628</v>
+        <v>60.116276</v>
       </c>
       <c r="H1603" t="n">
         <v>112.2772</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1604" t="n">
         <v>112.4415</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1607" t="n">
         <v>111.9487</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1608" t="n">
         <v>112.551</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.956791</v>
+        <v>60.956795</v>
       </c>
       <c r="H1609" t="n">
         <v>113.847</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.65382</v>
+        <v>60.653816</v>
       </c>
       <c r="H1610" t="n">
         <v>113.2812</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.20113</v>
+        <v>61.201126</v>
       </c>
       <c r="H1611" t="n">
         <v>114.3034</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>61.474789</v>
+        <v>61.474785</v>
       </c>
       <c r="H1614" t="n">
         <v>114.8145</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>61.445469</v>
+        <v>61.445465</v>
       </c>
       <c r="H1616" t="n">
         <v>114.7597</v>
@@ -61898,10 +61898,10 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.640491</v>
+        <v>58.640495</v>
       </c>
       <c r="H1618" t="n">
-        <v>109.5209</v>
+        <v>109.521</v>
       </c>
     </row>
     <row r="1619">
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>58.581856</v>
+        <v>58.581852</v>
       </c>
       <c r="H1620" t="n">
         <v>109.4114</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1623" t="n">
         <v>109.7948</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>57.790207</v>
+        <v>57.790211</v>
       </c>
       <c r="H1626" t="n">
         <v>107.9329</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.98</v>
+        <v>35.044998</v>
       </c>
       <c r="H253" t="n">
-        <v>117.0081</v>
+        <v>113.9675</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.865002</v>
+        <v>49.189999</v>
       </c>
       <c r="H504" t="n">
-        <v>132.4075</v>
+        <v>133.2882</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.50818599999999</v>
+        <v>64.508179</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.54714199999999</v>
+        <v>64.54715</v>
       </c>
       <c r="H506" t="n">
         <v>100.0604</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.449753</v>
+        <v>64.44976</v>
       </c>
       <c r="H507" t="n">
         <v>99.90940000000001</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.741913</v>
+        <v>64.741905</v>
       </c>
       <c r="H508" t="n">
         <v>100.3623</v>
@@ -19759,7 +19759,7 @@
         <v>64.673744</v>
       </c>
       <c r="H509" t="n">
-        <v>100.2566</v>
+        <v>100.2567</v>
       </c>
     </row>
     <row r="510">
@@ -19794,10 +19794,10 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>64.664001</v>
+        <v>64.66400899999999</v>
       </c>
       <c r="H510" t="n">
-        <v>100.2415</v>
+        <v>100.2416</v>
       </c>
     </row>
     <row r="511">
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.18988</v>
+        <v>65.189888</v>
       </c>
       <c r="H511" t="n">
         <v>101.0568</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H512" t="n">
         <v>101.0115</v>
@@ -19911,7 +19911,7 @@
         <v>65.511253</v>
       </c>
       <c r="H513" t="n">
-        <v>101.5549</v>
+        <v>101.555</v>
       </c>
     </row>
     <row r="514">
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H516" t="n">
         <v>102.34</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.910538</v>
+        <v>65.91052999999999</v>
       </c>
       <c r="H517" t="n">
         <v>102.1739</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H518" t="n">
         <v>100.5586</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.540482</v>
+        <v>65.540474</v>
       </c>
       <c r="H521" t="n">
         <v>101.6003</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H523" t="n">
         <v>100.9511</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H525" t="n">
         <v>102.34</v>
@@ -20440,10 +20440,10 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.066345</v>
+        <v>66.06635300000001</v>
       </c>
       <c r="H527" t="n">
-        <v>102.4154</v>
+        <v>102.4155</v>
       </c>
     </row>
     <row r="528">
@@ -20478,10 +20478,10 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.407211</v>
+        <v>66.407196</v>
       </c>
       <c r="H528" t="n">
-        <v>102.9439</v>
+        <v>102.9438</v>
       </c>
     </row>
     <row r="529">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.339043</v>
+        <v>66.339035</v>
       </c>
       <c r="H529" t="n">
         <v>102.8382</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.407211</v>
+        <v>66.407196</v>
       </c>
       <c r="H531" t="n">
-        <v>102.9439</v>
+        <v>102.9438</v>
       </c>
     </row>
     <row r="532">
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H535" t="n">
         <v>102.7627</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H541" t="n">
         <v>103.9553</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H542" t="n">
         <v>103.5175</v>
@@ -21238,10 +21238,10 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.124779</v>
+        <v>66.124786</v>
       </c>
       <c r="H548" t="n">
-        <v>102.506</v>
+        <v>102.5061</v>
       </c>
     </row>
     <row r="549">
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.387733</v>
+        <v>66.387726</v>
       </c>
       <c r="H549" t="n">
         <v>102.9137</v>
@@ -21317,7 +21317,7 @@
         <v>67.001259</v>
       </c>
       <c r="H550" t="n">
-        <v>103.8647</v>
+        <v>103.8648</v>
       </c>
     </row>
     <row r="551">
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.962311</v>
+        <v>66.96230300000001</v>
       </c>
       <c r="H551" t="n">
         <v>103.8044</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H553" t="n">
         <v>103.9553</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.371323</v>
+        <v>67.37133</v>
       </c>
       <c r="H556" t="n">
         <v>104.4384</v>
@@ -21580,10 +21580,10 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.51739499999999</v>
+        <v>67.51741</v>
       </c>
       <c r="H557" t="n">
-        <v>104.6648</v>
+        <v>104.6649</v>
       </c>
     </row>
     <row r="558">
@@ -21618,10 +21618,10 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.283669</v>
+        <v>67.283676</v>
       </c>
       <c r="H558" t="n">
-        <v>104.3025</v>
+        <v>104.3026</v>
       </c>
     </row>
     <row r="559">
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.29341100000001</v>
+        <v>67.293404</v>
       </c>
       <c r="H559" t="n">
         <v>104.3176</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.22525</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H560" t="n">
         <v>104.212</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.478447</v>
+        <v>67.47843899999999</v>
       </c>
       <c r="H561" t="n">
         <v>104.6045</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.3908</v>
+        <v>67.390793</v>
       </c>
       <c r="H562" t="n">
         <v>104.4686</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H564" t="n">
         <v>104.1214</v>
@@ -21884,10 +21884,10 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.234978</v>
+        <v>67.234993</v>
       </c>
       <c r="H565" t="n">
-        <v>104.227</v>
+        <v>104.2271</v>
       </c>
     </row>
     <row r="566">
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.619141</v>
+        <v>67.619148</v>
       </c>
       <c r="H566" t="n">
         <v>104.8226</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>67.815033</v>
+        <v>67.81502500000001</v>
       </c>
       <c r="H568" t="n">
         <v>105.1262</v>
@@ -22077,7 +22077,7 @@
         <v>68.27536000000001</v>
       </c>
       <c r="H570" t="n">
-        <v>105.8398</v>
+        <v>105.8399</v>
       </c>
     </row>
     <row r="571">
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.304733</v>
+        <v>68.30474100000001</v>
       </c>
       <c r="H571" t="n">
         <v>105.8854</v>
@@ -22191,7 +22191,7 @@
         <v>69.24498699999999</v>
       </c>
       <c r="H573" t="n">
-        <v>107.3429</v>
+        <v>107.343</v>
       </c>
     </row>
     <row r="574">
@@ -22264,10 +22264,10 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>69.48004899999999</v>
+        <v>69.480057</v>
       </c>
       <c r="H575" t="n">
-        <v>107.7073</v>
+        <v>107.7074</v>
       </c>
     </row>
     <row r="576">
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H576" t="n">
         <v>108.0414</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.273376</v>
+        <v>70.273369</v>
       </c>
       <c r="H579" t="n">
         <v>108.9371</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>71.340935</v>
+        <v>71.340942</v>
       </c>
       <c r="H581" t="n">
         <v>110.5921</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.723907</v>
+        <v>70.72391500000001</v>
       </c>
       <c r="H583" t="n">
         <v>109.6356</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H584" t="n">
         <v>108.6183</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.518227</v>
+        <v>70.51823400000001</v>
       </c>
       <c r="H587" t="n">
         <v>109.3167</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>70.410484</v>
+        <v>70.410492</v>
       </c>
       <c r="H589" t="n">
         <v>109.1497</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>70.68472300000001</v>
+        <v>70.684731</v>
       </c>
       <c r="H591" t="n">
         <v>109.5748</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>72.87863900000001</v>
+        <v>72.878632</v>
       </c>
       <c r="H595" t="n">
         <v>112.9758</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.201836</v>
+        <v>73.201843</v>
       </c>
       <c r="H597" t="n">
         <v>113.4768</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.828667</v>
+        <v>73.82867400000001</v>
       </c>
       <c r="H602" t="n">
         <v>114.4485</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H605" t="n">
         <v>115.481</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H606" t="n">
         <v>115.481</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.524063</v>
+        <v>74.524055</v>
       </c>
       <c r="H608" t="n">
         <v>115.5265</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>75.141098</v>
+        <v>75.14109000000001</v>
       </c>
       <c r="H610" t="n">
         <v>116.483</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>75.278206</v>
+        <v>75.27821400000001</v>
       </c>
       <c r="H611" t="n">
         <v>116.6956</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>75.00398300000001</v>
+        <v>75.003975</v>
       </c>
       <c r="H613" t="n">
         <v>116.2705</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>72.721924</v>
+        <v>72.72191599999999</v>
       </c>
       <c r="H619" t="n">
         <v>112.7329</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>72.64357</v>
+        <v>72.643562</v>
       </c>
       <c r="H624" t="n">
         <v>112.6114</v>
@@ -24319,7 +24319,7 @@
         <v>72.153915</v>
       </c>
       <c r="H629" t="n">
-        <v>111.8523</v>
+        <v>111.8524</v>
       </c>
     </row>
     <row r="630">
@@ -24509,7 +24509,7 @@
         <v>72.685463</v>
       </c>
       <c r="H634" t="n">
-        <v>112.6763</v>
+        <v>112.6764</v>
       </c>
     </row>
     <row r="635">
@@ -24699,7 +24699,7 @@
         <v>73.77810700000001</v>
       </c>
       <c r="H639" t="n">
-        <v>114.3701</v>
+        <v>114.3702</v>
       </c>
     </row>
     <row r="640">
@@ -24737,7 +24737,7 @@
         <v>73.492653</v>
       </c>
       <c r="H640" t="n">
-        <v>113.9276</v>
+        <v>113.9277</v>
       </c>
     </row>
     <row r="641">
@@ -25649,7 +25649,7 @@
         <v>75.097168</v>
       </c>
       <c r="H664" t="n">
-        <v>116.4149</v>
+        <v>116.415</v>
       </c>
     </row>
     <row r="665">
@@ -26257,7 +26257,7 @@
         <v>76.140587</v>
       </c>
       <c r="H680" t="n">
-        <v>118.0324</v>
+        <v>118.0325</v>
       </c>
     </row>
     <row r="681">
@@ -26485,7 +26485,7 @@
         <v>78.35541499999999</v>
       </c>
       <c r="H686" t="n">
-        <v>121.4658</v>
+        <v>121.4659</v>
       </c>
     </row>
     <row r="687">
@@ -26561,7 +26561,7 @@
         <v>77.914368</v>
       </c>
       <c r="H688" t="n">
-        <v>120.7821</v>
+        <v>120.7822</v>
       </c>
     </row>
     <row r="689">
@@ -26713,7 +26713,7 @@
         <v>78.68008399999999</v>
       </c>
       <c r="H692" t="n">
-        <v>121.9691</v>
+        <v>121.9692</v>
       </c>
     </row>
     <row r="693">
@@ -27283,7 +27283,7 @@
         <v>79.624802</v>
       </c>
       <c r="H707" t="n">
-        <v>123.4336</v>
+        <v>123.4337</v>
       </c>
     </row>
     <row r="708">
@@ -27663,7 +27663,7 @@
         <v>79.94302399999999</v>
       </c>
       <c r="H717" t="n">
-        <v>123.9269</v>
+        <v>123.927</v>
       </c>
     </row>
     <row r="718">
@@ -27853,7 +27853,7 @@
         <v>80.88774100000001</v>
       </c>
       <c r="H722" t="n">
-        <v>125.3914</v>
+        <v>125.3915</v>
       </c>
     </row>
     <row r="723">
@@ -28385,7 +28385,7 @@
         <v>81.205963</v>
       </c>
       <c r="H736" t="n">
-        <v>125.8847</v>
+        <v>125.8848</v>
       </c>
     </row>
     <row r="737">
@@ -28651,7 +28651,7 @@
         <v>81.653458</v>
       </c>
       <c r="H743" t="n">
-        <v>126.5784</v>
+        <v>126.5785</v>
       </c>
     </row>
     <row r="744">
@@ -28803,7 +28803,7 @@
         <v>80.19163500000001</v>
       </c>
       <c r="H747" t="n">
-        <v>124.3123</v>
+        <v>124.3124</v>
       </c>
     </row>
     <row r="748">
@@ -28955,7 +28955,7 @@
         <v>80.82807200000001</v>
       </c>
       <c r="H751" t="n">
-        <v>125.2989</v>
+        <v>125.299</v>
       </c>
     </row>
     <row r="752">
@@ -29069,13 +29069,13 @@
         <v>80.910004</v>
       </c>
       <c r="H754" t="n">
-        <v>125.4259</v>
+        <v>125.426</v>
       </c>
     </row>
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.760002</v>
+        <v>80.900002</v>
       </c>
       <c r="H755" t="n">
-        <v>125.1934</v>
+        <v>125.4105</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>129.119995</v>
+        <v>129.380005</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.3579</v>
+        <v>120.6003</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>129.119995</v>
+        <v>129.380005</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.3579</v>
+        <v>120.6003</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>129.119995</v>
+        <v>129.380005</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.3579</v>
+        <v>120.6003</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.542717</v>
+        <v>53.542721</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.425831</v>
+        <v>53.425835</v>
       </c>
       <c r="H1510" t="n">
         <v>99.7817</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.799221</v>
+        <v>54.799225</v>
       </c>
       <c r="H1516" t="n">
         <v>102.3467</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.974548</v>
+        <v>54.974552</v>
       </c>
       <c r="H1519" t="n">
         <v>102.6742</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1520" t="n">
         <v>103.4746</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.159618</v>
+        <v>55.159622</v>
       </c>
       <c r="H1521" t="n">
         <v>103.0198</v>
@@ -58253,7 +58253,7 @@
         <v>54.429092</v>
       </c>
       <c r="H1522" t="n">
-        <v>101.6555</v>
+        <v>101.6554</v>
       </c>
     </row>
     <row r="1523">
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.740784</v>
+        <v>54.74078</v>
       </c>
       <c r="H1523" t="n">
         <v>102.2376</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.818703</v>
+        <v>54.818707</v>
       </c>
       <c r="H1525" t="n">
         <v>102.3831</v>
@@ -58402,10 +58402,10 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1526" t="n">
-        <v>103.2018</v>
+        <v>103.2017</v>
       </c>
     </row>
     <row r="1527">
@@ -58478,10 +58478,10 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1528" t="n">
-        <v>103.2018</v>
+        <v>103.2017</v>
       </c>
     </row>
     <row r="1529">
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1529" t="n">
         <v>103.4746</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1530" t="n">
         <v>103.2381</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.588192</v>
+        <v>55.588188</v>
       </c>
       <c r="H1534" t="n">
         <v>103.8203</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1535" t="n">
         <v>103.7111</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1536" t="n">
         <v>103.2745</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.325199</v>
+        <v>55.325203</v>
       </c>
       <c r="H1537" t="n">
         <v>103.3291</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.169357</v>
+        <v>55.169353</v>
       </c>
       <c r="H1538" t="n">
         <v>103.038</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1539" t="n">
         <v>103.2381</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.867405</v>
+        <v>54.867409</v>
       </c>
       <c r="H1540" t="n">
         <v>102.4741</v>
@@ -59165,7 +59165,7 @@
         <v>55.607674</v>
       </c>
       <c r="H1546" t="n">
-        <v>103.8567</v>
+        <v>103.8566</v>
       </c>
     </row>
     <row r="1547">
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.305721</v>
+        <v>55.305717</v>
       </c>
       <c r="H1547" t="n">
         <v>103.2927</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1548" t="n">
         <v>101.4917</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1549" t="n">
         <v>101.4008</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>54.35117</v>
+        <v>54.351166</v>
       </c>
       <c r="H1551" t="n">
         <v>101.5099</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1554" t="n">
         <v>103.7111</v>
@@ -59659,7 +59659,7 @@
         <v>55.724556</v>
       </c>
       <c r="H1559" t="n">
-        <v>104.075</v>
+        <v>104.0749</v>
       </c>
     </row>
     <row r="1560">
@@ -59694,10 +59694,10 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.958328</v>
+        <v>55.958324</v>
       </c>
       <c r="H1560" t="n">
-        <v>104.5116</v>
+        <v>104.5115</v>
       </c>
     </row>
     <row r="1561">
@@ -59808,10 +59808,10 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.841446</v>
+        <v>55.841442</v>
       </c>
       <c r="H1563" t="n">
-        <v>104.2933</v>
+        <v>104.2932</v>
       </c>
     </row>
     <row r="1564">
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.870663</v>
+        <v>55.870659</v>
       </c>
       <c r="H1564" t="n">
         <v>104.3478</v>
@@ -59922,10 +59922,10 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1566" t="n">
-        <v>104.3115</v>
+        <v>104.3114</v>
       </c>
     </row>
     <row r="1567">
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1568" t="n">
         <v>104.702</v>
@@ -60074,10 +60074,10 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.558758</v>
+        <v>56.558754</v>
       </c>
       <c r="H1570" t="n">
-        <v>105.633</v>
+        <v>105.6329</v>
       </c>
     </row>
     <row r="1571">
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1571" t="n">
         <v>106.0528</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.676041</v>
+        <v>56.676044</v>
       </c>
       <c r="H1572" t="n">
         <v>105.852</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1574" t="n">
         <v>106.3996</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>57.692474</v>
+        <v>57.692471</v>
       </c>
       <c r="H1576" t="n">
         <v>107.7504</v>
@@ -60419,7 +60419,7 @@
         <v>58.513439</v>
       </c>
       <c r="H1579" t="n">
-        <v>109.2837</v>
+        <v>109.2836</v>
       </c>
     </row>
     <row r="1580">
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1581" t="n">
         <v>110.2511</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1585" t="n">
         <v>111.109</v>
@@ -60682,10 +60682,10 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1586" t="n">
-        <v>111.1273</v>
+        <v>111.1272</v>
       </c>
     </row>
     <row r="1587">
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1588" t="n">
         <v>108.8456</v>
@@ -60837,7 +60837,7 @@
         <v>58.91415</v>
       </c>
       <c r="H1590" t="n">
-        <v>110.0321</v>
+        <v>110.032</v>
       </c>
     </row>
     <row r="1591">
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>58.953243</v>
+        <v>58.953247</v>
       </c>
       <c r="H1592" t="n">
         <v>110.1051</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.168259</v>
+        <v>59.168262</v>
       </c>
       <c r="H1596" t="n">
         <v>110.5066</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.793755</v>
+        <v>59.793758</v>
       </c>
       <c r="H1597" t="n">
         <v>111.6749</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.803528</v>
+        <v>59.803532</v>
       </c>
       <c r="H1599" t="n">
         <v>111.6931</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.246449</v>
+        <v>59.246445</v>
       </c>
       <c r="H1600" t="n">
         <v>110.6527</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.744896</v>
+        <v>59.744892</v>
       </c>
       <c r="H1601" t="n">
         <v>111.5836</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.116276</v>
+        <v>60.11628</v>
       </c>
       <c r="H1603" t="n">
         <v>112.2772</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1604" t="n">
         <v>112.4415</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1605" t="n">
         <v>111.9304</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1607" t="n">
         <v>111.9487</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1608" t="n">
         <v>112.551</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.653816</v>
+        <v>60.65382</v>
       </c>
       <c r="H1610" t="n">
         <v>113.2812</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1612" t="n">
         <v>113.6827</v>
@@ -61708,10 +61708,10 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1613" t="n">
-        <v>113.9566</v>
+        <v>113.9565</v>
       </c>
     </row>
     <row r="1614">
@@ -61901,7 +61901,7 @@
         <v>58.640495</v>
       </c>
       <c r="H1618" t="n">
-        <v>109.521</v>
+        <v>109.5209</v>
       </c>
     </row>
     <row r="1619">
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1619" t="n">
         <v>110.9265</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>58.581852</v>
+        <v>58.581856</v>
       </c>
       <c r="H1620" t="n">
         <v>109.4114</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1621" t="n">
         <v>108.4257</v>
@@ -62053,7 +62053,7 @@
         <v>57.653381</v>
       </c>
       <c r="H1622" t="n">
-        <v>107.6774</v>
+        <v>107.6773</v>
       </c>
     </row>
     <row r="1623">
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1623" t="n">
         <v>109.7948</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1624" t="n">
         <v>109.1741</v>
@@ -62164,7 +62164,7 @@
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1625" t="n">
         <v>108.5353</v>
@@ -62278,7 +62278,7 @@
         </is>
       </c>
       <c r="G1628" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1628" t="n">
         <v>109.1279</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1647" t="n">
         <v>112.3483</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1649" t="n">
         <v>114.0866</v>
@@ -63152,10 +63152,10 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1651" t="n">
-        <v>112.202</v>
+        <v>112.2019</v>
       </c>
     </row>
     <row r="1652">
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1653" t="n">
         <v>111.9641</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1654" t="n">
         <v>111.3603</v>
@@ -63380,7 +63380,7 @@
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1657" t="n">
         <v>110.0977</v>
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1660" t="n">
         <v>111.5615</v>
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1661" t="n">
         <v>114.0317</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="G1663" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1663" t="n">
         <v>112.1654</v>
@@ -63684,7 +63684,7 @@
         </is>
       </c>
       <c r="G1665" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1665" t="n">
         <v>111.1407</v>
@@ -63877,7 +63877,7 @@
         <v>60.066177</v>
       </c>
       <c r="H1670" t="n">
-        <v>112.1837</v>
+        <v>112.1836</v>
       </c>
     </row>
     <row r="1671">
@@ -64064,7 +64064,7 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1675" t="n">
         <v>115.5687</v>
@@ -64105,7 +64105,7 @@
         <v>61.849255</v>
       </c>
       <c r="H1676" t="n">
-        <v>115.5139</v>
+        <v>115.5138</v>
       </c>
     </row>
     <row r="1677">
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1677" t="n">
         <v>115.0747</v>
@@ -64254,7 +64254,7 @@
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1680" t="n">
         <v>115.2028</v>
@@ -64330,7 +64330,7 @@
         </is>
       </c>
       <c r="G1682" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1682" t="n">
         <v>115.0747</v>
@@ -64368,10 +64368,10 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1683" t="n">
-        <v>114.6173</v>
+        <v>114.6172</v>
       </c>
     </row>
     <row r="1684">
@@ -64447,7 +64447,7 @@
         <v>60.957718</v>
       </c>
       <c r="H1685" t="n">
-        <v>113.8488</v>
+        <v>113.8487</v>
       </c>
     </row>
     <row r="1686">
@@ -64520,7 +64520,7 @@
         </is>
       </c>
       <c r="G1687" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1687" t="n">
         <v>114.4709</v>
@@ -64713,7 +64713,7 @@
         <v>62.766766</v>
       </c>
       <c r="H1692" t="n">
-        <v>117.2275</v>
+        <v>117.2274</v>
       </c>
     </row>
     <row r="1693">
@@ -64979,7 +64979,7 @@
         <v>62.766766</v>
       </c>
       <c r="H1699" t="n">
-        <v>117.2275</v>
+        <v>117.2274</v>
       </c>
     </row>
     <row r="1700">
@@ -65017,7 +65017,7 @@
         <v>63.341331</v>
       </c>
       <c r="H1700" t="n">
-        <v>118.3006</v>
+        <v>118.3005</v>
       </c>
     </row>
     <row r="1701">
@@ -65131,7 +65131,7 @@
         <v>64.450844</v>
       </c>
       <c r="H1703" t="n">
-        <v>120.3728</v>
+        <v>120.3727</v>
       </c>
     </row>
     <row r="1704">
@@ -65283,7 +65283,7 @@
         <v>63.321518</v>
       </c>
       <c r="H1707" t="n">
-        <v>118.2636</v>
+        <v>118.2635</v>
       </c>
     </row>
     <row r="1708">
@@ -65777,7 +65777,7 @@
         <v>63.886181</v>
       </c>
       <c r="H1720" t="n">
-        <v>119.3182</v>
+        <v>119.3181</v>
       </c>
     </row>
     <row r="1721">
@@ -65967,7 +65967,7 @@
         <v>64.95607</v>
       </c>
       <c r="H1725" t="n">
-        <v>121.3164</v>
+        <v>121.3163</v>
       </c>
     </row>
     <row r="1726">
@@ -66689,7 +66689,7 @@
         <v>64.361694</v>
       </c>
       <c r="H1744" t="n">
-        <v>120.2063</v>
+        <v>120.2062</v>
       </c>
     </row>
     <row r="1745">
@@ -66841,7 +66841,7 @@
         <v>64.39141100000001</v>
       </c>
       <c r="H1748" t="n">
-        <v>120.2618</v>
+        <v>120.2617</v>
       </c>
     </row>
     <row r="1749">
@@ -66879,7 +66879,7 @@
         <v>64.361694</v>
       </c>
       <c r="H1749" t="n">
-        <v>120.2063</v>
+        <v>120.2062</v>
       </c>
     </row>
     <row r="1750">
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.360001</v>
+        <v>63.580002</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.3354</v>
+        <v>118.7463</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.700001</v>
+        <v>35.775002</v>
       </c>
       <c r="H253" t="n">
-        <v>117.5309</v>
+        <v>117.7778</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.59</v>
+        <v>48.455002</v>
       </c>
       <c r="H504" t="n">
-        <v>131.8589</v>
+        <v>131.4925</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.54714199999999</v>
+        <v>64.54715</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.74191999999999</v>
+        <v>64.741913</v>
       </c>
       <c r="H507" t="n">
-        <v>100.3018</v>
+        <v>100.3017</v>
       </c>
     </row>
     <row r="508">
@@ -19721,7 +19721,7 @@
         <v>64.67375199999999</v>
       </c>
       <c r="H508" t="n">
-        <v>100.1962</v>
+        <v>100.1961</v>
       </c>
     </row>
     <row r="509">
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H511" t="n">
         <v>100.9505</v>
@@ -19873,7 +19873,7 @@
         <v>65.511253</v>
       </c>
       <c r="H512" t="n">
-        <v>101.4937</v>
+        <v>101.4936</v>
       </c>
     </row>
     <row r="513">
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.910538</v>
+        <v>65.91052999999999</v>
       </c>
       <c r="H516" t="n">
         <v>102.1122</v>
@@ -20101,7 +20101,7 @@
         <v>65.199623</v>
       </c>
       <c r="H518" t="n">
-        <v>101.0109</v>
+        <v>101.0108</v>
       </c>
     </row>
     <row r="519">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H527" t="n">
         <v>102.8817</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H530" t="n">
         <v>102.8817</v>
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H532" t="n">
-        <v>102.3386</v>
+        <v>102.3385</v>
       </c>
     </row>
     <row r="533">
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>65.988449</v>
+        <v>65.988457</v>
       </c>
       <c r="H535" t="n">
         <v>102.233</v>
@@ -20820,10 +20820,10 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H537" t="n">
-        <v>102.8214</v>
+        <v>102.8213</v>
       </c>
     </row>
     <row r="538">
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H538" t="n">
         <v>103.7115</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H541" t="n">
         <v>103.455</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>66.027405</v>
+        <v>66.027412</v>
       </c>
       <c r="H545" t="n">
         <v>102.2933</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>65.89106</v>
+        <v>65.891068</v>
       </c>
       <c r="H546" t="n">
         <v>102.0821</v>
@@ -21279,7 +21279,7 @@
         <v>67.001259</v>
       </c>
       <c r="H549" t="n">
-        <v>103.8021</v>
+        <v>103.802</v>
       </c>
     </row>
     <row r="550">
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H554" t="n">
         <v>103.7115</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H555" t="n">
         <v>104.3754</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.51739499999999</v>
+        <v>67.517403</v>
       </c>
       <c r="H556" t="n">
         <v>104.6017</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.22524300000001</v>
+        <v>67.22525</v>
       </c>
       <c r="H559" t="n">
         <v>104.1491</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.478447</v>
+        <v>67.47843899999999</v>
       </c>
       <c r="H560" t="n">
         <v>104.5413</v>
@@ -21773,7 +21773,7 @@
         <v>67.770599</v>
       </c>
       <c r="H562" t="n">
-        <v>104.994</v>
+        <v>104.9939</v>
       </c>
     </row>
     <row r="563">
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.234978</v>
+        <v>67.23498499999999</v>
       </c>
       <c r="H564" t="n">
         <v>104.1641</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.815033</v>
+        <v>67.81502500000001</v>
       </c>
       <c r="H567" t="n">
         <v>105.0628</v>
@@ -22036,10 +22036,10 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H569" t="n">
-        <v>105.776</v>
+        <v>105.7759</v>
       </c>
     </row>
     <row r="570">
@@ -22153,7 +22153,7 @@
         <v>69.24498699999999</v>
       </c>
       <c r="H572" t="n">
-        <v>107.2782</v>
+        <v>107.2781</v>
       </c>
     </row>
     <row r="573">
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>69.48004899999999</v>
+        <v>69.480057</v>
       </c>
       <c r="H574" t="n">
         <v>107.6423</v>
@@ -22267,7 +22267,7 @@
         <v>69.695526</v>
       </c>
       <c r="H575" t="n">
-        <v>107.9762</v>
+        <v>107.9761</v>
       </c>
     </row>
     <row r="576">
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.723907</v>
+        <v>70.72391500000001</v>
       </c>
       <c r="H582" t="n">
         <v>109.5694</v>
@@ -22568,10 +22568,10 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H583" t="n">
-        <v>108.5528</v>
+        <v>108.5527</v>
       </c>
     </row>
     <row r="584">
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H585" t="n">
         <v>109.797</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>73.201836</v>
+        <v>73.201843</v>
       </c>
       <c r="H596" t="n">
         <v>113.4083</v>
@@ -23138,10 +23138,10 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H598" t="n">
-        <v>113.9698</v>
+        <v>113.9697</v>
       </c>
     </row>
     <row r="599">
@@ -23179,7 +23179,7 @@
         <v>74.12249</v>
       </c>
       <c r="H599" t="n">
-        <v>114.8347</v>
+        <v>114.8346</v>
       </c>
     </row>
     <row r="600">
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H600" t="n">
         <v>114.3946</v>
@@ -23255,7 +23255,7 @@
         <v>73.82867400000001</v>
       </c>
       <c r="H601" t="n">
-        <v>114.3795</v>
+        <v>114.3794</v>
       </c>
     </row>
     <row r="602">
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.887444</v>
+        <v>73.88743599999999</v>
       </c>
       <c r="H602" t="n">
         <v>114.4705</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H608" t="n">
         <v>115.7754</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>75.003967</v>
+        <v>75.003975</v>
       </c>
       <c r="H612" t="n">
         <v>116.2003</v>
@@ -23863,7 +23863,7 @@
         <v>73.084312</v>
       </c>
       <c r="H617" t="n">
-        <v>113.2263</v>
+        <v>113.2262</v>
       </c>
     </row>
     <row r="618">
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>72.721924</v>
+        <v>72.72191599999999</v>
       </c>
       <c r="H618" t="n">
         <v>112.6648</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>72.64357</v>
+        <v>72.643562</v>
       </c>
       <c r="H623" t="n">
         <v>112.5434</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H624" t="n">
         <v>110.7936</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H625" t="n">
         <v>109.7718</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H627" t="n">
         <v>110.6258</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H630" t="n">
         <v>110.6258</v>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G633" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H633" t="n">
         <v>112.6083</v>
@@ -24509,7 +24509,7 @@
         <v>72.76422100000001</v>
       </c>
       <c r="H634" t="n">
-        <v>112.7304</v>
+        <v>112.7303</v>
       </c>
     </row>
     <row r="635">
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H635" t="n">
         <v>112.2423</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H637" t="n">
         <v>114.5604</v>
@@ -24658,7 +24658,7 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H638" t="n">
         <v>114.3011</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H640" t="n">
         <v>114.3774</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H642" t="n">
         <v>114.3469</v>
@@ -24889,7 +24889,7 @@
         <v>74.32936100000001</v>
       </c>
       <c r="H644" t="n">
-        <v>115.1552</v>
+        <v>115.1551</v>
       </c>
     </row>
     <row r="645">
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H646" t="n">
         <v>114.3774</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H649" t="n">
         <v>113.9199</v>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H650" t="n">
         <v>114.3164</v>
@@ -25190,10 +25190,10 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H652" t="n">
-        <v>115.3077</v>
+        <v>115.3076</v>
       </c>
     </row>
     <row r="653">
@@ -25304,7 +25304,7 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H655" t="n">
         <v>116.4057</v>
@@ -25342,7 +25342,7 @@
         </is>
       </c>
       <c r="G656" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H656" t="n">
         <v>115.6279</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H658" t="n">
         <v>115.6279</v>
@@ -25535,7 +25535,7 @@
         <v>75.618881</v>
       </c>
       <c r="H661" t="n">
-        <v>117.153</v>
+        <v>117.1529</v>
       </c>
     </row>
     <row r="662">
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="G663" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H663" t="n">
         <v>116.3447</v>
@@ -25725,7 +25725,7 @@
         <v>75.81574999999999</v>
       </c>
       <c r="H666" t="n">
-        <v>117.458</v>
+        <v>117.4579</v>
       </c>
     </row>
     <row r="667">
@@ -25798,7 +25798,7 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H668" t="n">
         <v>119.4405</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H670" t="n">
         <v>118.6322</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H672" t="n">
         <v>118.1747</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="G673" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H673" t="n">
         <v>118.0222</v>
@@ -26178,7 +26178,7 @@
         </is>
       </c>
       <c r="G678" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H678" t="n">
         <v>118.6627</v>
@@ -26216,7 +26216,7 @@
         </is>
       </c>
       <c r="G679" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H679" t="n">
         <v>117.9612</v>
@@ -26444,7 +26444,7 @@
         </is>
       </c>
       <c r="G685" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H685" t="n">
         <v>121.3925</v>
@@ -26637,7 +26637,7 @@
         <v>78.401642</v>
       </c>
       <c r="H690" t="n">
-        <v>121.4642</v>
+        <v>121.4641</v>
       </c>
     </row>
     <row r="691">
@@ -27055,7 +27055,7 @@
         <v>79.19718899999999</v>
       </c>
       <c r="H701" t="n">
-        <v>122.6967</v>
+        <v>122.6966</v>
       </c>
     </row>
     <row r="702">
@@ -27283,7 +27283,7 @@
         <v>79.465698</v>
       </c>
       <c r="H707" t="n">
-        <v>123.1127</v>
+        <v>123.1126</v>
       </c>
     </row>
     <row r="708">
@@ -27397,7 +27397,7 @@
         <v>80.271187</v>
       </c>
       <c r="H710" t="n">
-        <v>124.3606</v>
+        <v>124.3605</v>
       </c>
     </row>
     <row r="711">
@@ -27435,7 +27435,7 @@
         <v>79.952972</v>
       </c>
       <c r="H711" t="n">
-        <v>123.8676</v>
+        <v>123.8675</v>
       </c>
     </row>
     <row r="712">
@@ -27625,7 +27625,7 @@
         <v>79.94302399999999</v>
       </c>
       <c r="H716" t="n">
-        <v>123.8522</v>
+        <v>123.8521</v>
       </c>
     </row>
     <row r="717">
@@ -27663,7 +27663,7 @@
         <v>80.112076</v>
       </c>
       <c r="H717" t="n">
-        <v>124.1141</v>
+        <v>124.114</v>
       </c>
     </row>
     <row r="718">
@@ -27777,7 +27777,7 @@
         <v>80.708748</v>
       </c>
       <c r="H720" t="n">
-        <v>125.0385</v>
+        <v>125.0384</v>
       </c>
     </row>
     <row r="721">
@@ -27815,7 +27815,7 @@
         <v>80.88774100000001</v>
       </c>
       <c r="H721" t="n">
-        <v>125.3158</v>
+        <v>125.3157</v>
       </c>
     </row>
     <row r="722">
@@ -28309,7 +28309,7 @@
         <v>81.02697000000001</v>
       </c>
       <c r="H734" t="n">
-        <v>125.5315</v>
+        <v>125.5314</v>
       </c>
     </row>
     <row r="735">
@@ -28841,7 +28841,7 @@
         <v>80.87779999999999</v>
       </c>
       <c r="H748" t="n">
-        <v>125.3004</v>
+        <v>125.3003</v>
       </c>
     </row>
     <row r="749">
@@ -29069,7 +29069,7 @@
         <v>80.900002</v>
       </c>
       <c r="H754" t="n">
-        <v>125.3348</v>
+        <v>125.3347</v>
       </c>
     </row>
     <row r="755">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.650002</v>
+        <v>80.589996</v>
       </c>
       <c r="H755" t="n">
-        <v>124.9474</v>
+        <v>124.8545</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>128.460007</v>
+        <v>128.490005</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.9664</v>
+        <v>119.9944</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>128.460007</v>
+        <v>128.490005</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.9664</v>
+        <v>119.9944</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>128.460007</v>
+        <v>128.490005</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.9664</v>
+        <v>119.9944</v>
       </c>
     </row>
     <row r="1509">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.523239</v>
+        <v>53.523243</v>
       </c>
       <c r="H1511" t="n">
         <v>100.1823</v>
@@ -57984,10 +57984,10 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.799225</v>
+        <v>54.799221</v>
       </c>
       <c r="H1515" t="n">
-        <v>102.5707</v>
+        <v>102.5706</v>
       </c>
     </row>
     <row r="1516">
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.042732</v>
+        <v>55.042736</v>
       </c>
       <c r="H1517" t="n">
         <v>103.0264</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1519" t="n">
         <v>103.701</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.159618</v>
+        <v>55.159615</v>
       </c>
       <c r="H1520" t="n">
         <v>103.2452</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.740784</v>
+        <v>54.740788</v>
       </c>
       <c r="H1522" t="n">
         <v>102.4613</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.536236</v>
+        <v>54.536232</v>
       </c>
       <c r="H1523" t="n">
         <v>102.0784</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1526" t="n">
         <v>102.3519</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1528" t="n">
         <v>103.701</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1529" t="n">
         <v>103.464</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1531" t="n">
         <v>104.3573</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.588188</v>
+        <v>55.588192</v>
       </c>
       <c r="H1533" t="n">
         <v>104.0474</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1538" t="n">
         <v>103.464</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.607677</v>
+        <v>55.607674</v>
       </c>
       <c r="H1545" t="n">
         <v>104.0839</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.305721</v>
+        <v>55.305717</v>
       </c>
       <c r="H1546" t="n">
         <v>103.5187</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1548" t="n">
         <v>101.6226</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1549" t="n">
         <v>101.9872</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.351166</v>
+        <v>54.351162</v>
       </c>
       <c r="H1550" t="n">
         <v>101.732</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1554" t="n">
         <v>104.0109</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1555" t="n">
         <v>104.3573</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1556" t="n">
         <v>104.0109</v>
@@ -59618,10 +59618,10 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.724556</v>
+        <v>55.72456</v>
       </c>
       <c r="H1558" t="n">
-        <v>104.3026</v>
+        <v>104.3027</v>
       </c>
     </row>
     <row r="1559">
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.958328</v>
+        <v>55.958332</v>
       </c>
       <c r="H1559" t="n">
         <v>104.7402</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.987541</v>
+        <v>55.987545</v>
       </c>
       <c r="H1560" t="n">
         <v>104.7949</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1565" t="n">
         <v>104.5397</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1566" t="n">
         <v>105.3701</v>
@@ -59998,10 +59998,10 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1568" t="n">
-        <v>104.8031</v>
+        <v>104.803</v>
       </c>
     </row>
     <row r="1569">
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.558754</v>
+        <v>56.558758</v>
       </c>
       <c r="H1569" t="n">
         <v>105.8641</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>56.676044</v>
+        <v>56.676041</v>
       </c>
       <c r="H1571" t="n">
         <v>106.0836</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1573" t="n">
         <v>106.6324</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>57.692471</v>
+        <v>57.692474</v>
       </c>
       <c r="H1575" t="n">
         <v>107.9861</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1576" t="n">
         <v>108.9557</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1577" t="n">
         <v>109.5593</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1578" t="n">
         <v>109.5228</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1581" t="n">
         <v>110.6752</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1583" t="n">
         <v>110.7118</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1584" t="n">
         <v>111.3521</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1585" t="n">
         <v>111.3704</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1587" t="n">
         <v>109.0837</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1590" t="n">
         <v>110.1813</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>58.953247</v>
+        <v>58.953243</v>
       </c>
       <c r="H1591" t="n">
         <v>110.346</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1592" t="n">
         <v>111.0045</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1603" t="n">
         <v>112.6875</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1606" t="n">
         <v>112.1936</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1607" t="n">
         <v>112.7973</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.956795</v>
+        <v>60.956799</v>
       </c>
       <c r="H1608" t="n">
         <v>114.0961</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1621" t="n">
         <v>107.9129</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1622" t="n">
         <v>110.035</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.240002</v>
+        <v>63.09</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.3697</v>
+        <v>118.0889</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.775002</v>
+        <v>36.014999</v>
       </c>
       <c r="H253" t="n">
-        <v>117.7778</v>
+        <v>118.5679</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.455002</v>
+        <v>48.369999</v>
       </c>
       <c r="H504" t="n">
-        <v>131.4925</v>
+        <v>131.2619</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.54715</v>
+        <v>64.547134</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.449753</v>
+        <v>64.44974499999999</v>
       </c>
       <c r="H506" t="n">
         <v>99.84910000000001</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.741913</v>
+        <v>64.74191999999999</v>
       </c>
       <c r="H507" t="n">
-        <v>100.3017</v>
+        <v>100.3018</v>
       </c>
     </row>
     <row r="508">
@@ -19718,10 +19718,10 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.67375199999999</v>
+        <v>64.673744</v>
       </c>
       <c r="H508" t="n">
-        <v>100.1961</v>
+        <v>100.1962</v>
       </c>
     </row>
     <row r="509">
@@ -19759,7 +19759,7 @@
         <v>64.664001</v>
       </c>
       <c r="H509" t="n">
-        <v>100.181</v>
+        <v>100.1811</v>
       </c>
     </row>
     <row r="510">
@@ -19873,7 +19873,7 @@
         <v>65.511253</v>
       </c>
       <c r="H512" t="n">
-        <v>101.4936</v>
+        <v>101.4937</v>
       </c>
     </row>
     <row r="513">
@@ -20022,10 +20022,10 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H516" t="n">
-        <v>102.1122</v>
+        <v>102.1123</v>
       </c>
     </row>
     <row r="517">
@@ -20101,7 +20101,7 @@
         <v>65.199623</v>
       </c>
       <c r="H518" t="n">
-        <v>101.0108</v>
+        <v>101.0109</v>
       </c>
     </row>
     <row r="519">
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.111977</v>
+        <v>65.111969</v>
       </c>
       <c r="H519" t="n">
         <v>100.8751</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H522" t="n">
         <v>100.8902</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.84236900000001</v>
+        <v>65.842361</v>
       </c>
       <c r="H523" t="n">
         <v>102.0066</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H525" t="n">
         <v>102.1575</v>
@@ -20405,7 +20405,7 @@
         <v>66.06635300000001</v>
       </c>
       <c r="H526" t="n">
-        <v>102.3536</v>
+        <v>102.3537</v>
       </c>
     </row>
     <row r="527">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H527" t="n">
         <v>102.8817</v>
@@ -20516,10 +20516,10 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H529" t="n">
-        <v>102.5799</v>
+        <v>102.58</v>
       </c>
     </row>
     <row r="530">
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H530" t="n">
         <v>102.8817</v>
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H532" t="n">
-        <v>102.3385</v>
+        <v>102.3386</v>
       </c>
     </row>
     <row r="533">
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>65.988457</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H535" t="n">
         <v>102.233</v>
@@ -20823,7 +20823,7 @@
         <v>66.36824799999999</v>
       </c>
       <c r="H537" t="n">
-        <v>102.8213</v>
+        <v>102.8214</v>
       </c>
     </row>
     <row r="538">
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H540" t="n">
         <v>103.8926</v>
@@ -20975,7 +20975,7 @@
         <v>66.777275</v>
       </c>
       <c r="H541" t="n">
-        <v>103.455</v>
+        <v>103.4551</v>
       </c>
     </row>
     <row r="542">
@@ -21051,7 +21051,7 @@
         <v>65.754715</v>
       </c>
       <c r="H543" t="n">
-        <v>101.8708</v>
+        <v>101.8709</v>
       </c>
     </row>
     <row r="544">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>66.027412</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H545" t="n">
         <v>102.2933</v>
@@ -21279,7 +21279,7 @@
         <v>67.001259</v>
       </c>
       <c r="H549" t="n">
-        <v>103.802</v>
+        <v>103.8021</v>
       </c>
     </row>
     <row r="550">
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H552" t="n">
         <v>103.8926</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H556" t="n">
         <v>104.6017</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.283669</v>
+        <v>67.283676</v>
       </c>
       <c r="H557" t="n">
         <v>104.2396</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H561" t="n">
-        <v>104.4055</v>
+        <v>104.4056</v>
       </c>
     </row>
     <row r="562">
@@ -21773,7 +21773,7 @@
         <v>67.770599</v>
       </c>
       <c r="H562" t="n">
-        <v>104.9939</v>
+        <v>104.994</v>
       </c>
     </row>
     <row r="563">
@@ -21811,7 +21811,7 @@
         <v>67.16681699999999</v>
       </c>
       <c r="H563" t="n">
-        <v>104.0585</v>
+        <v>104.0586</v>
       </c>
     </row>
     <row r="564">
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.23498499999999</v>
+        <v>67.23497</v>
       </c>
       <c r="H564" t="n">
         <v>104.1641</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.619148</v>
+        <v>67.619141</v>
       </c>
       <c r="H565" t="n">
         <v>104.7593</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H566" t="n">
         <v>105.1842</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.81502500000001</v>
+        <v>67.815033</v>
       </c>
       <c r="H567" t="n">
         <v>105.0628</v>
@@ -22036,10 +22036,10 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H569" t="n">
-        <v>105.7759</v>
+        <v>105.776</v>
       </c>
     </row>
     <row r="570">
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H571" t="n">
         <v>106.1553</v>
@@ -22150,10 +22150,10 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H572" t="n">
-        <v>107.2781</v>
+        <v>107.2782</v>
       </c>
     </row>
     <row r="573">
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>69.480057</v>
+        <v>69.48004899999999</v>
       </c>
       <c r="H574" t="n">
         <v>107.6423</v>
@@ -22267,7 +22267,7 @@
         <v>69.695526</v>
       </c>
       <c r="H575" t="n">
-        <v>107.9761</v>
+        <v>107.9762</v>
       </c>
     </row>
     <row r="576">
@@ -22343,7 +22343,7 @@
         <v>70.18523399999999</v>
       </c>
       <c r="H577" t="n">
-        <v>108.7348</v>
+        <v>108.7349</v>
       </c>
     </row>
     <row r="578">
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.273369</v>
+        <v>70.273376</v>
       </c>
       <c r="H578" t="n">
         <v>108.8714</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H581" t="n">
         <v>110.4495</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.72391500000001</v>
+        <v>70.723907</v>
       </c>
       <c r="H582" t="n">
         <v>109.5694</v>
@@ -22571,7 +22571,7 @@
         <v>70.067696</v>
       </c>
       <c r="H583" t="n">
-        <v>108.5527</v>
+        <v>108.5528</v>
       </c>
     </row>
     <row r="584">
@@ -22609,7 +22609,7 @@
         <v>70.371323</v>
       </c>
       <c r="H584" t="n">
-        <v>109.0231</v>
+        <v>109.0232</v>
       </c>
     </row>
     <row r="585">
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H585" t="n">
         <v>109.797</v>
@@ -22685,7 +22685,7 @@
         <v>70.51823400000001</v>
       </c>
       <c r="H586" t="n">
-        <v>109.2507</v>
+        <v>109.2508</v>
       </c>
     </row>
     <row r="587">
@@ -22758,10 +22758,10 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.410492</v>
+        <v>70.4105</v>
       </c>
       <c r="H588" t="n">
-        <v>109.0838</v>
+        <v>109.0839</v>
       </c>
     </row>
     <row r="589">
@@ -22875,7 +22875,7 @@
         <v>70.890411</v>
       </c>
       <c r="H591" t="n">
-        <v>109.8273</v>
+        <v>109.8274</v>
       </c>
     </row>
     <row r="592">
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H592" t="n">
         <v>111.0564</v>
@@ -22951,7 +22951,7 @@
         <v>72.37912799999999</v>
       </c>
       <c r="H593" t="n">
-        <v>112.1337</v>
+        <v>112.1338</v>
       </c>
     </row>
     <row r="594">
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H594" t="n">
         <v>112.9076</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H595" t="n">
         <v>112.0882</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>73.201843</v>
+        <v>73.201836</v>
       </c>
       <c r="H596" t="n">
         <v>113.4083</v>
@@ -23100,10 +23100,10 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H597" t="n">
-        <v>113.5752</v>
+        <v>113.5753</v>
       </c>
     </row>
     <row r="598">
@@ -23138,10 +23138,10 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H598" t="n">
-        <v>113.9697</v>
+        <v>113.9698</v>
       </c>
     </row>
     <row r="599">
@@ -23176,10 +23176,10 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H599" t="n">
-        <v>114.8346</v>
+        <v>114.8347</v>
       </c>
     </row>
     <row r="600">
@@ -23214,10 +23214,10 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H600" t="n">
-        <v>114.3946</v>
+        <v>114.3947</v>
       </c>
     </row>
     <row r="601">
@@ -23252,10 +23252,10 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>73.82867400000001</v>
+        <v>73.828667</v>
       </c>
       <c r="H601" t="n">
-        <v>114.3794</v>
+        <v>114.3795</v>
       </c>
     </row>
     <row r="602">
@@ -23331,7 +23331,7 @@
         <v>73.86784400000001</v>
       </c>
       <c r="H603" t="n">
-        <v>114.4401</v>
+        <v>114.4402</v>
       </c>
     </row>
     <row r="604">
@@ -23445,7 +23445,7 @@
         <v>74.69055899999999</v>
       </c>
       <c r="H606" t="n">
-        <v>115.7147</v>
+        <v>115.7148</v>
       </c>
     </row>
     <row r="607">
@@ -23518,10 +23518,10 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H608" t="n">
-        <v>115.7754</v>
+        <v>115.7755</v>
       </c>
     </row>
     <row r="609">
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H612" t="n">
         <v>116.2003</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H613" t="n">
         <v>113.6511</v>
@@ -23863,7 +23863,7 @@
         <v>73.084312</v>
       </c>
       <c r="H617" t="n">
-        <v>113.2262</v>
+        <v>113.2263</v>
       </c>
     </row>
     <row r="618">
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>72.72191599999999</v>
+        <v>72.721931</v>
       </c>
       <c r="H618" t="n">
         <v>112.6648</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H619" t="n">
         <v>112.2248</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>72.643562</v>
+        <v>72.64357</v>
       </c>
       <c r="H623" t="n">
         <v>112.5434</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H624" t="n">
         <v>110.7936</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H625" t="n">
         <v>109.7718</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H627" t="n">
         <v>110.6258</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H630" t="n">
         <v>110.6258</v>
@@ -24468,10 +24468,10 @@
         </is>
       </c>
       <c r="G633" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H633" t="n">
-        <v>112.6083</v>
+        <v>112.6084</v>
       </c>
     </row>
     <row r="634">
@@ -24509,7 +24509,7 @@
         <v>72.76422100000001</v>
       </c>
       <c r="H634" t="n">
-        <v>112.7303</v>
+        <v>112.7304</v>
       </c>
     </row>
     <row r="635">
@@ -24544,10 +24544,10 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H635" t="n">
-        <v>112.2423</v>
+        <v>112.2424</v>
       </c>
     </row>
     <row r="636">
@@ -24585,7 +24585,7 @@
         <v>73.837181</v>
       </c>
       <c r="H636" t="n">
-        <v>114.3926</v>
+        <v>114.3927</v>
       </c>
     </row>
     <row r="637">
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H637" t="n">
         <v>114.5604</v>
@@ -24658,7 +24658,7 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H638" t="n">
         <v>114.3011</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H640" t="n">
         <v>114.3774</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H642" t="n">
         <v>114.3469</v>
@@ -24851,7 +24851,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H643" t="n">
-        <v>115.2771</v>
+        <v>115.2772</v>
       </c>
     </row>
     <row r="644">
@@ -24889,7 +24889,7 @@
         <v>74.32936100000001</v>
       </c>
       <c r="H644" t="n">
-        <v>115.1551</v>
+        <v>115.1552</v>
       </c>
     </row>
     <row r="645">
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H646" t="n">
         <v>114.3774</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H649" t="n">
         <v>113.9199</v>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H650" t="n">
         <v>114.3164</v>
@@ -25190,10 +25190,10 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H652" t="n">
-        <v>115.3076</v>
+        <v>115.3077</v>
       </c>
     </row>
     <row r="653">
@@ -25231,7 +25231,7 @@
         <v>73.955299</v>
       </c>
       <c r="H653" t="n">
-        <v>114.5756</v>
+        <v>114.5757</v>
       </c>
     </row>
     <row r="654">
@@ -25269,7 +25269,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H654" t="n">
-        <v>115.2771</v>
+        <v>115.2772</v>
       </c>
     </row>
     <row r="655">
@@ -25304,7 +25304,7 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H655" t="n">
         <v>116.4057</v>
@@ -25342,7 +25342,7 @@
         </is>
       </c>
       <c r="G656" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H656" t="n">
         <v>115.6279</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H658" t="n">
         <v>115.6279</v>
@@ -25535,7 +25535,7 @@
         <v>75.618881</v>
       </c>
       <c r="H661" t="n">
-        <v>117.1529</v>
+        <v>117.153</v>
       </c>
     </row>
     <row r="662">
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="G663" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H663" t="n">
         <v>116.3447</v>
@@ -25725,7 +25725,7 @@
         <v>75.81574999999999</v>
       </c>
       <c r="H666" t="n">
-        <v>117.4579</v>
+        <v>117.458</v>
       </c>
     </row>
     <row r="667">
@@ -25798,7 +25798,7 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H668" t="n">
         <v>119.4405</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H670" t="n">
         <v>118.6322</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H672" t="n">
         <v>118.1747</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="G673" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H673" t="n">
         <v>118.0222</v>
@@ -26178,7 +26178,7 @@
         </is>
       </c>
       <c r="G678" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H678" t="n">
         <v>118.6627</v>
@@ -26216,7 +26216,7 @@
         </is>
       </c>
       <c r="G679" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H679" t="n">
         <v>117.9612</v>
@@ -26444,7 +26444,7 @@
         </is>
       </c>
       <c r="G685" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H685" t="n">
         <v>121.3925</v>
@@ -26523,7 +26523,7 @@
         <v>77.914368</v>
       </c>
       <c r="H687" t="n">
-        <v>120.7092</v>
+        <v>120.7093</v>
       </c>
     </row>
     <row r="688">
@@ -26561,7 +26561,7 @@
         <v>78.540863</v>
       </c>
       <c r="H688" t="n">
-        <v>121.6798</v>
+        <v>121.6799</v>
       </c>
     </row>
     <row r="689">
@@ -26637,7 +26637,7 @@
         <v>78.401642</v>
       </c>
       <c r="H690" t="n">
-        <v>121.4641</v>
+        <v>121.4642</v>
       </c>
     </row>
     <row r="691">
@@ -26713,7 +26713,7 @@
         <v>78.38175200000001</v>
       </c>
       <c r="H692" t="n">
-        <v>121.4333</v>
+        <v>121.4334</v>
       </c>
     </row>
     <row r="693">
@@ -27055,7 +27055,7 @@
         <v>79.19718899999999</v>
       </c>
       <c r="H701" t="n">
-        <v>122.6966</v>
+        <v>122.6967</v>
       </c>
     </row>
     <row r="702">
@@ -27245,7 +27245,7 @@
         <v>79.624802</v>
       </c>
       <c r="H706" t="n">
-        <v>123.3591</v>
+        <v>123.3592</v>
       </c>
     </row>
     <row r="707">
@@ -27283,7 +27283,7 @@
         <v>79.465698</v>
       </c>
       <c r="H707" t="n">
-        <v>123.1126</v>
+        <v>123.1127</v>
       </c>
     </row>
     <row r="708">
@@ -27321,7 +27321,7 @@
         <v>79.31652800000001</v>
       </c>
       <c r="H708" t="n">
-        <v>122.8815</v>
+        <v>122.8816</v>
       </c>
     </row>
     <row r="709">
@@ -27397,7 +27397,7 @@
         <v>80.271187</v>
       </c>
       <c r="H710" t="n">
-        <v>124.3605</v>
+        <v>124.3606</v>
       </c>
     </row>
     <row r="711">
@@ -27435,7 +27435,7 @@
         <v>79.952972</v>
       </c>
       <c r="H711" t="n">
-        <v>123.8675</v>
+        <v>123.8676</v>
       </c>
     </row>
     <row r="712">
@@ -27511,7 +27511,7 @@
         <v>80.718681</v>
       </c>
       <c r="H713" t="n">
-        <v>125.0538</v>
+        <v>125.0539</v>
       </c>
     </row>
     <row r="714">
@@ -27625,7 +27625,7 @@
         <v>79.94302399999999</v>
       </c>
       <c r="H716" t="n">
-        <v>123.8521</v>
+        <v>123.8522</v>
       </c>
     </row>
     <row r="717">
@@ -27663,7 +27663,7 @@
         <v>80.112076</v>
       </c>
       <c r="H717" t="n">
-        <v>124.114</v>
+        <v>124.1141</v>
       </c>
     </row>
     <row r="718">
@@ -27777,7 +27777,7 @@
         <v>80.708748</v>
       </c>
       <c r="H720" t="n">
-        <v>125.0384</v>
+        <v>125.0385</v>
       </c>
     </row>
     <row r="721">
@@ -27815,7 +27815,7 @@
         <v>80.88774100000001</v>
       </c>
       <c r="H721" t="n">
-        <v>125.3157</v>
+        <v>125.3158</v>
       </c>
     </row>
     <row r="722">
@@ -27891,7 +27891,7 @@
         <v>81.176125</v>
       </c>
       <c r="H723" t="n">
-        <v>125.7625</v>
+        <v>125.7626</v>
       </c>
     </row>
     <row r="724">
@@ -28005,7 +28005,7 @@
         <v>81.48440600000001</v>
       </c>
       <c r="H726" t="n">
-        <v>126.2401</v>
+        <v>126.2402</v>
       </c>
     </row>
     <row r="727">
@@ -28081,7 +28081,7 @@
         <v>81.166191</v>
       </c>
       <c r="H728" t="n">
-        <v>125.7471</v>
+        <v>125.7472</v>
       </c>
     </row>
     <row r="729">
@@ -28119,7 +28119,7 @@
         <v>80.84796900000001</v>
       </c>
       <c r="H729" t="n">
-        <v>125.2541</v>
+        <v>125.2542</v>
       </c>
     </row>
     <row r="730">
@@ -28195,7 +28195,7 @@
         <v>80.410408</v>
       </c>
       <c r="H731" t="n">
-        <v>124.5762</v>
+        <v>124.5763</v>
       </c>
     </row>
     <row r="732">
@@ -28309,7 +28309,7 @@
         <v>81.02697000000001</v>
       </c>
       <c r="H734" t="n">
-        <v>125.5314</v>
+        <v>125.5315</v>
       </c>
     </row>
     <row r="735">
@@ -28613,7 +28613,7 @@
         <v>81.653458</v>
       </c>
       <c r="H742" t="n">
-        <v>126.502</v>
+        <v>126.5021</v>
       </c>
     </row>
     <row r="743">
@@ -28841,7 +28841,7 @@
         <v>80.87779999999999</v>
       </c>
       <c r="H748" t="n">
-        <v>125.3003</v>
+        <v>125.3004</v>
       </c>
     </row>
     <row r="749">
@@ -28993,7 +28993,7 @@
         <v>80.5</v>
       </c>
       <c r="H752" t="n">
-        <v>124.715</v>
+        <v>124.7151</v>
       </c>
     </row>
     <row r="753">
@@ -29031,7 +29031,7 @@
         <v>80.910004</v>
       </c>
       <c r="H753" t="n">
-        <v>125.3502</v>
+        <v>125.3503</v>
       </c>
     </row>
     <row r="754">
@@ -29069,7 +29069,7 @@
         <v>80.900002</v>
       </c>
       <c r="H754" t="n">
-        <v>125.3347</v>
+        <v>125.3348</v>
       </c>
     </row>
     <row r="755">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.589996</v>
+        <v>80.239998</v>
       </c>
       <c r="H755" t="n">
-        <v>124.8545</v>
+        <v>124.3123</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>128.490005</v>
+        <v>128.380005</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.9944</v>
+        <v>119.8917</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>128.490005</v>
+        <v>128.380005</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.9944</v>
+        <v>119.8917</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>128.490005</v>
+        <v>128.380005</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.9944</v>
+        <v>119.8917</v>
       </c>
     </row>
     <row r="1509">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>53.523243</v>
+        <v>53.523239</v>
       </c>
       <c r="H1511" t="n">
         <v>100.1823</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1514" t="n">
         <v>102.0055</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.062214</v>
+        <v>55.06221</v>
       </c>
       <c r="H1516" t="n">
         <v>103.0629</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.042736</v>
+        <v>55.042732</v>
       </c>
       <c r="H1517" t="n">
         <v>103.0264</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.974548</v>
+        <v>54.974545</v>
       </c>
       <c r="H1518" t="n">
         <v>102.8988</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.159615</v>
+        <v>55.159618</v>
       </c>
       <c r="H1520" t="n">
         <v>103.2452</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.740788</v>
+        <v>54.74078</v>
       </c>
       <c r="H1522" t="n">
         <v>102.4613</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.536232</v>
+        <v>54.536236</v>
       </c>
       <c r="H1523" t="n">
         <v>102.0784</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1524" t="n">
         <v>102.6071</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1531" t="n">
         <v>104.3573</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1534" t="n">
         <v>103.938</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.295986</v>
+        <v>55.295982</v>
       </c>
       <c r="H1535" t="n">
         <v>103.5005</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>54.867409</v>
+        <v>54.867405</v>
       </c>
       <c r="H1539" t="n">
         <v>102.6983</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.584934</v>
+        <v>54.584938</v>
       </c>
       <c r="H1540" t="n">
         <v>102.1696</v>
@@ -58972,10 +58972,10 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1541" t="n">
-        <v>103.6645</v>
+        <v>103.6646</v>
       </c>
     </row>
     <row r="1542">
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>56.104427</v>
+        <v>56.104435</v>
       </c>
       <c r="H1542" t="n">
         <v>105.0137</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1544" t="n">
         <v>105.0866</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.305717</v>
+        <v>55.305725</v>
       </c>
       <c r="H1546" t="n">
         <v>103.5187</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1547" t="n">
         <v>101.7138</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1548" t="n">
         <v>101.6226</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.487534</v>
+        <v>54.48753</v>
       </c>
       <c r="H1549" t="n">
         <v>101.9872</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.351162</v>
+        <v>54.35117</v>
       </c>
       <c r="H1550" t="n">
         <v>101.732</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>54.41935</v>
+        <v>54.419346</v>
       </c>
       <c r="H1551" t="n">
         <v>101.8596</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1553" t="n">
         <v>103.938</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1555" t="n">
         <v>104.3573</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1561" t="n">
         <v>104.6308</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.870663</v>
+        <v>55.870667</v>
       </c>
       <c r="H1563" t="n">
         <v>104.5761</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.294872</v>
+        <v>56.294876</v>
       </c>
       <c r="H1566" t="n">
         <v>105.3701</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1567" t="n">
         <v>104.9311</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1570" t="n">
         <v>106.2848</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>58.53299</v>
+        <v>58.532986</v>
       </c>
       <c r="H1577" t="n">
         <v>109.5593</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.39616</v>
+        <v>58.396156</v>
       </c>
       <c r="H1579" t="n">
         <v>109.3032</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>59.031437</v>
+        <v>59.031433</v>
       </c>
       <c r="H1580" t="n">
         <v>110.4923</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>58.91415</v>
+        <v>58.914154</v>
       </c>
       <c r="H1589" t="n">
         <v>110.2728</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.86528</v>
+        <v>58.865284</v>
       </c>
       <c r="H1590" t="n">
         <v>110.1813</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.305092</v>
+        <v>59.305088</v>
       </c>
       <c r="H1592" t="n">
         <v>111.0045</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>58.835964</v>
+        <v>58.835968</v>
       </c>
       <c r="H1593" t="n">
         <v>110.1264</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>58.718685</v>
+        <v>58.718681</v>
       </c>
       <c r="H1594" t="n">
         <v>109.9069</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.168262</v>
+        <v>59.168259</v>
       </c>
       <c r="H1595" t="n">
         <v>110.7484</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.246445</v>
+        <v>59.246449</v>
       </c>
       <c r="H1599" t="n">
         <v>110.8948</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>59.852402</v>
+        <v>59.852398</v>
       </c>
       <c r="H1605" t="n">
         <v>112.029</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.956799</v>
+        <v>60.956795</v>
       </c>
       <c r="H1608" t="n">
         <v>114.0961</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>61.406372</v>
+        <v>61.406376</v>
       </c>
       <c r="H1614" t="n">
         <v>114.9376</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>59.393051</v>
+        <v>59.393047</v>
       </c>
       <c r="H1618" t="n">
         <v>111.1692</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.581856</v>
+        <v>58.581852</v>
       </c>
       <c r="H1619" t="n">
         <v>109.6508</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1620" t="n">
         <v>108.663</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.4548</v>
+        <v>58.454803</v>
       </c>
       <c r="H1623" t="n">
         <v>109.413</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.09</v>
+        <v>62.98</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.0889</v>
+        <v>117.8831</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.547134</v>
+        <v>64.54714199999999</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.44974499999999</v>
+        <v>64.449753</v>
       </c>
       <c r="H506" t="n">
         <v>99.84910000000001</v>
@@ -19721,7 +19721,7 @@
         <v>64.673744</v>
       </c>
       <c r="H508" t="n">
-        <v>100.1962</v>
+        <v>100.1961</v>
       </c>
     </row>
     <row r="509">
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.664001</v>
+        <v>64.66400899999999</v>
       </c>
       <c r="H509" t="n">
         <v>100.1811</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.160667</v>
+        <v>65.160675</v>
       </c>
       <c r="H511" t="n">
         <v>100.9505</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H515" t="n">
         <v>102.2782</v>
@@ -20022,10 +20022,10 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.910538</v>
+        <v>65.91052999999999</v>
       </c>
       <c r="H516" t="n">
-        <v>102.1123</v>
+        <v>102.1122</v>
       </c>
     </row>
     <row r="517">
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H519" t="n">
         <v>100.8751</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.559952</v>
+        <v>65.559944</v>
       </c>
       <c r="H521" t="n">
         <v>101.5691</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.121712</v>
+        <v>65.121719</v>
       </c>
       <c r="H522" t="n">
         <v>100.8902</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H524" t="n">
         <v>102.2782</v>
@@ -20405,7 +20405,7 @@
         <v>66.06635300000001</v>
       </c>
       <c r="H526" t="n">
-        <v>102.3537</v>
+        <v>102.3536</v>
       </c>
     </row>
     <row r="527">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.339035</v>
+        <v>66.339027</v>
       </c>
       <c r="H528" t="n">
         <v>102.7761</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H531" t="n">
         <v>102.3989</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H533" t="n">
         <v>102.3989</v>
@@ -20747,7 +20747,7 @@
         <v>65.98844099999999</v>
       </c>
       <c r="H535" t="n">
-        <v>102.233</v>
+        <v>102.2329</v>
       </c>
     </row>
     <row r="536">
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368263</v>
       </c>
       <c r="H537" t="n">
         <v>102.8214</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H538" t="n">
         <v>103.7115</v>
@@ -20972,10 +20972,10 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H541" t="n">
-        <v>103.4551</v>
+        <v>103.455</v>
       </c>
     </row>
     <row r="542">
@@ -21048,10 +21048,10 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>65.754715</v>
+        <v>65.754707</v>
       </c>
       <c r="H543" t="n">
-        <v>101.8709</v>
+        <v>101.8708</v>
       </c>
     </row>
     <row r="544">
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027405</v>
       </c>
       <c r="H545" t="n">
         <v>102.2933</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H546" t="n">
         <v>102.0821</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H554" t="n">
         <v>103.7115</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.51739499999999</v>
+        <v>67.517403</v>
       </c>
       <c r="H556" t="n">
         <v>104.6017</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.283676</v>
+        <v>67.283669</v>
       </c>
       <c r="H557" t="n">
         <v>104.2396</v>
@@ -21656,10 +21656,10 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.22525</v>
+        <v>67.225235</v>
       </c>
       <c r="H559" t="n">
-        <v>104.1491</v>
+        <v>104.149</v>
       </c>
     </row>
     <row r="560">
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H560" t="n">
         <v>104.5413</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.3908</v>
+        <v>67.390793</v>
       </c>
       <c r="H561" t="n">
-        <v>104.4056</v>
+        <v>104.4055</v>
       </c>
     </row>
     <row r="562">
@@ -21770,10 +21770,10 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.770599</v>
+        <v>67.77059199999999</v>
       </c>
       <c r="H562" t="n">
-        <v>104.994</v>
+        <v>104.9939</v>
       </c>
     </row>
     <row r="563">
@@ -21811,7 +21811,7 @@
         <v>67.16681699999999</v>
       </c>
       <c r="H563" t="n">
-        <v>104.0586</v>
+        <v>104.0585</v>
       </c>
     </row>
     <row r="564">
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.23497</v>
+        <v>67.234978</v>
       </c>
       <c r="H564" t="n">
         <v>104.1641</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.619141</v>
+        <v>67.619148</v>
       </c>
       <c r="H565" t="n">
         <v>104.7593</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H566" t="n">
         <v>105.1842</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.815033</v>
+        <v>67.81502500000001</v>
       </c>
       <c r="H567" t="n">
         <v>105.0628</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H569" t="n">
         <v>105.776</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H571" t="n">
         <v>106.1553</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>69.24498</v>
+        <v>69.24498699999999</v>
       </c>
       <c r="H572" t="n">
         <v>107.2782</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>69.48004899999999</v>
+        <v>69.480057</v>
       </c>
       <c r="H574" t="n">
         <v>107.6423</v>
@@ -22343,7 +22343,7 @@
         <v>70.18523399999999</v>
       </c>
       <c r="H577" t="n">
-        <v>108.7349</v>
+        <v>108.7348</v>
       </c>
     </row>
     <row r="578">
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.273376</v>
+        <v>70.273369</v>
       </c>
       <c r="H578" t="n">
         <v>108.8714</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H581" t="n">
         <v>110.4495</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.723907</v>
+        <v>70.72391500000001</v>
       </c>
       <c r="H582" t="n">
         <v>109.5694</v>
@@ -22571,7 +22571,7 @@
         <v>70.067696</v>
       </c>
       <c r="H583" t="n">
-        <v>108.5528</v>
+        <v>108.5527</v>
       </c>
     </row>
     <row r="584">
@@ -22609,7 +22609,7 @@
         <v>70.371323</v>
       </c>
       <c r="H584" t="n">
-        <v>109.0232</v>
+        <v>109.0231</v>
       </c>
     </row>
     <row r="585">
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H585" t="n">
         <v>109.797</v>
@@ -22685,7 +22685,7 @@
         <v>70.51823400000001</v>
       </c>
       <c r="H586" t="n">
-        <v>109.2508</v>
+        <v>109.2507</v>
       </c>
     </row>
     <row r="587">
@@ -22758,10 +22758,10 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.4105</v>
+        <v>70.410492</v>
       </c>
       <c r="H588" t="n">
-        <v>109.0839</v>
+        <v>109.0838</v>
       </c>
     </row>
     <row r="589">
@@ -22875,7 +22875,7 @@
         <v>70.890411</v>
       </c>
       <c r="H591" t="n">
-        <v>109.8274</v>
+        <v>109.8273</v>
       </c>
     </row>
     <row r="592">
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H592" t="n">
         <v>111.0564</v>
@@ -22951,7 +22951,7 @@
         <v>72.37912799999999</v>
       </c>
       <c r="H593" t="n">
-        <v>112.1338</v>
+        <v>112.1337</v>
       </c>
     </row>
     <row r="594">
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>72.87863900000001</v>
+        <v>72.878632</v>
       </c>
       <c r="H594" t="n">
         <v>112.9076</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H595" t="n">
         <v>112.0882</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>73.201836</v>
+        <v>73.201843</v>
       </c>
       <c r="H596" t="n">
         <v>113.4083</v>
@@ -23100,10 +23100,10 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H597" t="n">
-        <v>113.5753</v>
+        <v>113.5752</v>
       </c>
     </row>
     <row r="598">
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H598" t="n">
         <v>113.9698</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H599" t="n">
         <v>114.8347</v>
@@ -23214,10 +23214,10 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H600" t="n">
-        <v>114.3947</v>
+        <v>114.3946</v>
       </c>
     </row>
     <row r="601">
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>73.828667</v>
+        <v>73.82867400000001</v>
       </c>
       <c r="H601" t="n">
         <v>114.3795</v>
@@ -23331,7 +23331,7 @@
         <v>73.86784400000001</v>
       </c>
       <c r="H603" t="n">
-        <v>114.4402</v>
+        <v>114.4401</v>
       </c>
     </row>
     <row r="604">
@@ -23445,7 +23445,7 @@
         <v>74.69055899999999</v>
       </c>
       <c r="H606" t="n">
-        <v>115.7148</v>
+        <v>115.7147</v>
       </c>
     </row>
     <row r="607">
@@ -23518,10 +23518,10 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H608" t="n">
-        <v>115.7755</v>
+        <v>115.7754</v>
       </c>
     </row>
     <row r="609">
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>75.003967</v>
+        <v>75.003975</v>
       </c>
       <c r="H612" t="n">
         <v>116.2003</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>73.358543</v>
+        <v>73.35855100000001</v>
       </c>
       <c r="H613" t="n">
         <v>113.6511</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>72.721931</v>
+        <v>72.72191599999999</v>
       </c>
       <c r="H618" t="n">
         <v>112.6648</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H619" t="n">
         <v>112.2248</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>72.64357</v>
+        <v>72.643562</v>
       </c>
       <c r="H623" t="n">
         <v>112.5434</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H624" t="n">
         <v>110.7936</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H625" t="n">
         <v>109.7718</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H627" t="n">
         <v>110.6258</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H630" t="n">
         <v>110.6258</v>
@@ -24468,10 +24468,10 @@
         </is>
       </c>
       <c r="G633" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H633" t="n">
-        <v>112.6084</v>
+        <v>112.6083</v>
       </c>
     </row>
     <row r="634">
@@ -24544,10 +24544,10 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H635" t="n">
-        <v>112.2424</v>
+        <v>112.2423</v>
       </c>
     </row>
     <row r="636">
@@ -24585,7 +24585,7 @@
         <v>73.837181</v>
       </c>
       <c r="H636" t="n">
-        <v>114.3927</v>
+        <v>114.3926</v>
       </c>
     </row>
     <row r="637">
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H637" t="n">
         <v>114.5604</v>
@@ -24658,7 +24658,7 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H638" t="n">
         <v>114.3011</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H640" t="n">
         <v>114.3774</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H642" t="n">
         <v>114.3469</v>
@@ -24851,7 +24851,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H643" t="n">
-        <v>115.2772</v>
+        <v>115.2771</v>
       </c>
     </row>
     <row r="644">
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H646" t="n">
         <v>114.3774</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H649" t="n">
         <v>113.9199</v>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H650" t="n">
         <v>114.3164</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H652" t="n">
         <v>115.3077</v>
@@ -25231,7 +25231,7 @@
         <v>73.955299</v>
       </c>
       <c r="H653" t="n">
-        <v>114.5757</v>
+        <v>114.5756</v>
       </c>
     </row>
     <row r="654">
@@ -25269,7 +25269,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H654" t="n">
-        <v>115.2772</v>
+        <v>115.2771</v>
       </c>
     </row>
     <row r="655">
@@ -25304,7 +25304,7 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H655" t="n">
         <v>116.4057</v>
@@ -25342,7 +25342,7 @@
         </is>
       </c>
       <c r="G656" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H656" t="n">
         <v>115.6279</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H658" t="n">
         <v>115.6279</v>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="G663" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H663" t="n">
         <v>116.3447</v>
@@ -25798,7 +25798,7 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H668" t="n">
         <v>119.4405</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H670" t="n">
         <v>118.6322</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H672" t="n">
         <v>118.1747</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="G673" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H673" t="n">
         <v>118.0222</v>
@@ -26178,7 +26178,7 @@
         </is>
       </c>
       <c r="G678" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H678" t="n">
         <v>118.6627</v>
@@ -26216,7 +26216,7 @@
         </is>
       </c>
       <c r="G679" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H679" t="n">
         <v>117.9612</v>
@@ -26444,7 +26444,7 @@
         </is>
       </c>
       <c r="G685" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H685" t="n">
         <v>121.3925</v>
@@ -26523,7 +26523,7 @@
         <v>77.914368</v>
       </c>
       <c r="H687" t="n">
-        <v>120.7093</v>
+        <v>120.7092</v>
       </c>
     </row>
     <row r="688">
@@ -26561,7 +26561,7 @@
         <v>78.540863</v>
       </c>
       <c r="H688" t="n">
-        <v>121.6799</v>
+        <v>121.6798</v>
       </c>
     </row>
     <row r="689">
@@ -26713,7 +26713,7 @@
         <v>78.38175200000001</v>
       </c>
       <c r="H692" t="n">
-        <v>121.4334</v>
+        <v>121.4333</v>
       </c>
     </row>
     <row r="693">
@@ -27245,7 +27245,7 @@
         <v>79.624802</v>
       </c>
       <c r="H706" t="n">
-        <v>123.3592</v>
+        <v>123.3591</v>
       </c>
     </row>
     <row r="707">
@@ -27321,7 +27321,7 @@
         <v>79.31652800000001</v>
       </c>
       <c r="H708" t="n">
-        <v>122.8816</v>
+        <v>122.8815</v>
       </c>
     </row>
     <row r="709">
@@ -27511,7 +27511,7 @@
         <v>80.718681</v>
       </c>
       <c r="H713" t="n">
-        <v>125.0539</v>
+        <v>125.0538</v>
       </c>
     </row>
     <row r="714">
@@ -27891,7 +27891,7 @@
         <v>81.176125</v>
       </c>
       <c r="H723" t="n">
-        <v>125.7626</v>
+        <v>125.7625</v>
       </c>
     </row>
     <row r="724">
@@ -28005,7 +28005,7 @@
         <v>81.48440600000001</v>
       </c>
       <c r="H726" t="n">
-        <v>126.2402</v>
+        <v>126.2401</v>
       </c>
     </row>
     <row r="727">
@@ -28081,7 +28081,7 @@
         <v>81.166191</v>
       </c>
       <c r="H728" t="n">
-        <v>125.7472</v>
+        <v>125.7471</v>
       </c>
     </row>
     <row r="729">
@@ -28119,7 +28119,7 @@
         <v>80.84796900000001</v>
       </c>
       <c r="H729" t="n">
-        <v>125.2542</v>
+        <v>125.2541</v>
       </c>
     </row>
     <row r="730">
@@ -28195,7 +28195,7 @@
         <v>80.410408</v>
       </c>
       <c r="H731" t="n">
-        <v>124.5763</v>
+        <v>124.5762</v>
       </c>
     </row>
     <row r="732">
@@ -28613,7 +28613,7 @@
         <v>81.653458</v>
       </c>
       <c r="H742" t="n">
-        <v>126.5021</v>
+        <v>126.502</v>
       </c>
     </row>
     <row r="743">
@@ -28993,7 +28993,7 @@
         <v>80.5</v>
       </c>
       <c r="H752" t="n">
-        <v>124.7151</v>
+        <v>124.715</v>
       </c>
     </row>
     <row r="753">
@@ -29031,7 +29031,7 @@
         <v>80.910004</v>
       </c>
       <c r="H753" t="n">
-        <v>125.3503</v>
+        <v>125.3502</v>
       </c>
     </row>
     <row r="754">
@@ -29107,7 +29107,7 @@
         <v>80.239998</v>
       </c>
       <c r="H755" t="n">
-        <v>124.3123</v>
+        <v>124.3122</v>
       </c>
     </row>
     <row r="756">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.425831</v>
+        <v>53.425835</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.075184</v>
+        <v>53.075188</v>
       </c>
       <c r="H1510" t="n">
         <v>99.3437</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>53.62064</v>
+        <v>53.620636</v>
       </c>
       <c r="H1512" t="n">
         <v>100.3646</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.497276</v>
+        <v>54.497272</v>
       </c>
       <c r="H1514" t="n">
         <v>102.0055</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.06221</v>
+        <v>55.062218</v>
       </c>
       <c r="H1516" t="n">
         <v>103.0629</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.974545</v>
+        <v>54.974552</v>
       </c>
       <c r="H1518" t="n">
         <v>102.8988</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1519" t="n">
         <v>103.701</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.429092</v>
+        <v>54.429096</v>
       </c>
       <c r="H1521" t="n">
         <v>101.8779</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.74078</v>
+        <v>54.740788</v>
       </c>
       <c r="H1522" t="n">
         <v>102.4613</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.536236</v>
+        <v>54.53624</v>
       </c>
       <c r="H1523" t="n">
         <v>102.0784</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1525" t="n">
         <v>103.4275</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1527" t="n">
         <v>103.4275</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1528" t="n">
         <v>103.701</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1531" t="n">
         <v>104.3573</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1534" t="n">
         <v>103.938</v>
@@ -58785,7 +58785,7 @@
         <v>55.325203</v>
       </c>
       <c r="H1536" t="n">
-        <v>103.5552</v>
+        <v>103.5551</v>
       </c>
     </row>
     <row r="1537">
@@ -58823,7 +58823,7 @@
         <v>55.169357</v>
       </c>
       <c r="H1537" t="n">
-        <v>103.2635</v>
+        <v>103.2634</v>
       </c>
     </row>
     <row r="1538">
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>54.867405</v>
+        <v>54.867409</v>
       </c>
       <c r="H1539" t="n">
         <v>102.6983</v>
@@ -58934,10 +58934,10 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.584938</v>
+        <v>54.584934</v>
       </c>
       <c r="H1540" t="n">
-        <v>102.1696</v>
+        <v>102.1695</v>
       </c>
     </row>
     <row r="1541">
@@ -58975,7 +58975,7 @@
         <v>55.383648</v>
       </c>
       <c r="H1541" t="n">
-        <v>103.6646</v>
+        <v>103.6645</v>
       </c>
     </row>
     <row r="1542">
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>56.104435</v>
+        <v>56.104431</v>
       </c>
       <c r="H1542" t="n">
         <v>105.0137</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.305725</v>
+        <v>55.305721</v>
       </c>
       <c r="H1546" t="n">
         <v>103.5187</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.35117</v>
+        <v>54.351166</v>
       </c>
       <c r="H1550" t="n">
         <v>101.732</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>54.419346</v>
+        <v>54.419353</v>
       </c>
       <c r="H1551" t="n">
         <v>101.8596</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1553" t="n">
         <v>103.938</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1554" t="n">
         <v>104.0109</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1555" t="n">
         <v>104.3573</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1556" t="n">
         <v>104.0109</v>
@@ -59618,10 +59618,10 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.72456</v>
+        <v>55.724556</v>
       </c>
       <c r="H1558" t="n">
-        <v>104.3027</v>
+        <v>104.3026</v>
       </c>
     </row>
     <row r="1559">
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.958332</v>
+        <v>55.958328</v>
       </c>
       <c r="H1559" t="n">
         <v>104.7402</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.870667</v>
+        <v>55.870663</v>
       </c>
       <c r="H1563" t="n">
         <v>104.5761</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1565" t="n">
         <v>104.5397</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1568" t="n">
         <v>104.803</v>
@@ -60302,10 +60302,10 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1576" t="n">
-        <v>108.9557</v>
+        <v>108.9556</v>
       </c>
     </row>
     <row r="1577">
@@ -60378,10 +60378,10 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1578" t="n">
-        <v>109.5228</v>
+        <v>109.5227</v>
       </c>
     </row>
     <row r="1579">
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.396156</v>
+        <v>58.39616</v>
       </c>
       <c r="H1579" t="n">
         <v>109.3032</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>59.129169</v>
+        <v>59.129166</v>
       </c>
       <c r="H1581" t="n">
         <v>110.6752</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1583" t="n">
         <v>110.7118</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>58.914154</v>
+        <v>58.91415</v>
       </c>
       <c r="H1589" t="n">
         <v>110.2728</v>
@@ -60875,7 +60875,7 @@
         <v>58.953243</v>
       </c>
       <c r="H1591" t="n">
-        <v>110.346</v>
+        <v>110.3459</v>
       </c>
     </row>
     <row r="1592">
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>58.835968</v>
+        <v>58.835964</v>
       </c>
       <c r="H1593" t="n">
         <v>110.1264</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>58.718681</v>
+        <v>58.718685</v>
       </c>
       <c r="H1594" t="n">
         <v>109.9069</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.793758</v>
+        <v>59.793755</v>
       </c>
       <c r="H1596" t="n">
         <v>111.9192</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.803532</v>
+        <v>59.803528</v>
       </c>
       <c r="H1598" t="n">
         <v>111.9375</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.744892</v>
+        <v>59.744896</v>
       </c>
       <c r="H1600" t="n">
         <v>111.8277</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>60.11628</v>
+        <v>60.116276</v>
       </c>
       <c r="H1602" t="n">
         <v>112.5229</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1604" t="n">
         <v>112.1753</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>59.852398</v>
+        <v>59.852402</v>
       </c>
       <c r="H1605" t="n">
         <v>112.029</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.65382</v>
+        <v>60.653816</v>
       </c>
       <c r="H1609" t="n">
         <v>113.529</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1611" t="n">
         <v>113.9315</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>61.015434</v>
+        <v>61.015438</v>
       </c>
       <c r="H1612" t="n">
         <v>114.2059</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>61.406376</v>
+        <v>61.406372</v>
       </c>
       <c r="H1614" t="n">
         <v>114.9376</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1621" t="n">
         <v>107.9129</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.112728</v>
+        <v>58.112732</v>
       </c>
       <c r="H1624" t="n">
         <v>108.7727</v>
@@ -62240,7 +62240,7 @@
         </is>
       </c>
       <c r="G1627" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1627" t="n">
         <v>109.3667</v>
@@ -62775,7 +62775,7 @@
         <v>59.772263</v>
       </c>
       <c r="H1641" t="n">
-        <v>111.879</v>
+        <v>111.8789</v>
       </c>
     </row>
     <row r="1642">
@@ -62851,7 +62851,7 @@
         <v>59.899628</v>
       </c>
       <c r="H1643" t="n">
-        <v>112.1174</v>
+        <v>112.1173</v>
       </c>
     </row>
     <row r="1644">
@@ -62927,7 +62927,7 @@
         <v>60.340496</v>
       </c>
       <c r="H1645" t="n">
-        <v>112.9426</v>
+        <v>112.9425</v>
       </c>
     </row>
     <row r="1646">
@@ -62962,7 +62962,7 @@
         </is>
       </c>
       <c r="G1646" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1646" t="n">
         <v>112.5941</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1648" t="n">
         <v>114.3362</v>
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1650" t="n">
         <v>112.4474</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1652" t="n">
         <v>112.209</v>
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1653" t="n">
         <v>111.6039</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1656" t="n">
         <v>110.3386</v>
@@ -63456,7 +63456,7 @@
         </is>
       </c>
       <c r="G1659" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1659" t="n">
         <v>111.8056</v>
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1660" t="n">
         <v>114.2812</v>
@@ -63570,10 +63570,10 @@
         </is>
       </c>
       <c r="G1662" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1662" t="n">
-        <v>112.4108</v>
+        <v>112.4107</v>
       </c>
     </row>
     <row r="1663">
@@ -63646,7 +63646,7 @@
         </is>
       </c>
       <c r="G1664" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1664" t="n">
         <v>111.3838</v>
@@ -63877,7 +63877,7 @@
         <v>61.065487</v>
       </c>
       <c r="H1670" t="n">
-        <v>114.2996</v>
+        <v>114.2995</v>
       </c>
     </row>
     <row r="1671">
@@ -63915,7 +63915,7 @@
         <v>61.065487</v>
       </c>
       <c r="H1671" t="n">
-        <v>114.2996</v>
+        <v>114.2995</v>
       </c>
     </row>
     <row r="1672">
@@ -64026,7 +64026,7 @@
         </is>
       </c>
       <c r="G1674" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1674" t="n">
         <v>115.8216</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1676" t="n">
         <v>115.3265</v>
@@ -64216,7 +64216,7 @@
         </is>
       </c>
       <c r="G1679" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1679" t="n">
         <v>115.4548</v>
@@ -64292,7 +64292,7 @@
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1681" t="n">
         <v>115.3265</v>
@@ -64330,7 +64330,7 @@
         </is>
       </c>
       <c r="G1682" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1682" t="n">
         <v>114.868</v>
@@ -64482,7 +64482,7 @@
         </is>
       </c>
       <c r="G1686" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1686" t="n">
         <v>114.7213</v>
@@ -65815,7 +65815,7 @@
         <v>64.203186</v>
       </c>
       <c r="H1721" t="n">
-        <v>120.1726</v>
+        <v>120.1725</v>
       </c>
     </row>
     <row r="1722">
@@ -66043,7 +66043,7 @@
         <v>65.302795</v>
       </c>
       <c r="H1727" t="n">
-        <v>122.2308</v>
+        <v>122.2307</v>
       </c>
     </row>
     <row r="1728">
@@ -67297,7 +67297,7 @@
         <v>62.98</v>
       </c>
       <c r="H1760" t="n">
-        <v>117.8831</v>
+        <v>117.883</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>36.014999</v>
+        <v>35.98</v>
       </c>
       <c r="H253" t="n">
-        <v>118.5679</v>
+        <v>118.4527</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.369999</v>
+        <v>48.865002</v>
       </c>
       <c r="H504" t="n">
-        <v>131.2619</v>
+        <v>132.6052</v>
       </c>
     </row>
     <row r="505">
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.74191999999999</v>
+        <v>64.741913</v>
       </c>
       <c r="H507" t="n">
-        <v>100.3018</v>
+        <v>100.3017</v>
       </c>
     </row>
     <row r="508">
@@ -19756,10 +19756,10 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.66400899999999</v>
+        <v>64.664001</v>
       </c>
       <c r="H509" t="n">
-        <v>100.1811</v>
+        <v>100.181</v>
       </c>
     </row>
     <row r="510">
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H511" t="n">
         <v>100.9505</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H516" t="n">
         <v>102.1122</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.199623</v>
+        <v>65.199631</v>
       </c>
       <c r="H518" t="n">
         <v>101.0109</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.559944</v>
+        <v>65.559952</v>
       </c>
       <c r="H521" t="n">
         <v>101.5691</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H522" t="n">
         <v>100.8902</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>65.842361</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H523" t="n">
         <v>102.0066</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.939751</v>
+        <v>65.93974300000001</v>
       </c>
       <c r="H525" t="n">
         <v>102.1575</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.339027</v>
+        <v>66.339043</v>
       </c>
       <c r="H528" t="n">
         <v>102.7761</v>
@@ -20516,10 +20516,10 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.212433</v>
+        <v>66.212425</v>
       </c>
       <c r="H529" t="n">
-        <v>102.58</v>
+        <v>102.5799</v>
       </c>
     </row>
     <row r="530">
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.095581</v>
+        <v>66.095573</v>
       </c>
       <c r="H531" t="n">
         <v>102.3989</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.095581</v>
+        <v>66.095573</v>
       </c>
       <c r="H533" t="n">
         <v>102.3989</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H534" t="n">
         <v>102.7007</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.368263</v>
+        <v>66.368256</v>
       </c>
       <c r="H537" t="n">
         <v>102.8214</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H539" t="n">
         <v>104.6771</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H540" t="n">
         <v>103.8926</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>65.754707</v>
+        <v>65.754715</v>
       </c>
       <c r="H543" t="n">
         <v>101.8708</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H545" t="n">
         <v>102.2933</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.387726</v>
+        <v>66.387733</v>
       </c>
       <c r="H548" t="n">
         <v>102.8515</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.24472</v>
+        <v>67.24472799999999</v>
       </c>
       <c r="H551" t="n">
         <v>104.1792</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H552" t="n">
         <v>103.8926</v>
@@ -21694,10 +21694,10 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.478447</v>
+        <v>67.478455</v>
       </c>
       <c r="H560" t="n">
-        <v>104.5413</v>
+        <v>104.5414</v>
       </c>
     </row>
     <row r="561">
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H561" t="n">
-        <v>104.4055</v>
+        <v>104.4056</v>
       </c>
     </row>
     <row r="562">
@@ -21770,10 +21770,10 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H562" t="n">
-        <v>104.9939</v>
+        <v>104.994</v>
       </c>
     </row>
     <row r="563">
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H563" t="n">
         <v>104.0585</v>
@@ -21846,10 +21846,10 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.234978</v>
+        <v>67.23498499999999</v>
       </c>
       <c r="H564" t="n">
-        <v>104.1641</v>
+        <v>104.1642</v>
       </c>
     </row>
     <row r="565">
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>67.81502500000001</v>
+        <v>67.815033</v>
       </c>
       <c r="H567" t="n">
         <v>105.0628</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H569" t="n">
         <v>105.776</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>69.480057</v>
+        <v>69.48004899999999</v>
       </c>
       <c r="H574" t="n">
         <v>107.6423</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.72391500000001</v>
+        <v>70.723907</v>
       </c>
       <c r="H582" t="n">
         <v>109.5694</v>
@@ -22568,10 +22568,10 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H583" t="n">
-        <v>108.5527</v>
+        <v>108.5528</v>
       </c>
     </row>
     <row r="584">
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H585" t="n">
         <v>109.797</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>73.201843</v>
+        <v>73.201836</v>
       </c>
       <c r="H596" t="n">
         <v>113.4083</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H598" t="n">
         <v>113.9698</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H600" t="n">
         <v>114.3946</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.88743599999999</v>
+        <v>73.887444</v>
       </c>
       <c r="H602" t="n">
         <v>114.4705</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H608" t="n">
         <v>115.7754</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H612" t="n">
         <v>116.2003</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>72.72191599999999</v>
+        <v>72.721924</v>
       </c>
       <c r="H618" t="n">
         <v>112.6648</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>72.643562</v>
+        <v>72.64357</v>
       </c>
       <c r="H623" t="n">
         <v>112.5434</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H624" t="n">
         <v>110.7936</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H625" t="n">
         <v>109.7718</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H627" t="n">
         <v>110.6258</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H630" t="n">
         <v>110.6258</v>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G633" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H633" t="n">
         <v>112.6083</v>
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H635" t="n">
         <v>112.2423</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H637" t="n">
         <v>114.5604</v>
@@ -24658,7 +24658,7 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H638" t="n">
         <v>114.3011</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H640" t="n">
         <v>114.3774</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H642" t="n">
         <v>114.3469</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H646" t="n">
         <v>114.3774</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H649" t="n">
         <v>113.9199</v>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H650" t="n">
         <v>114.3164</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H652" t="n">
         <v>115.3077</v>
@@ -25304,7 +25304,7 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H655" t="n">
         <v>116.4057</v>
@@ -25342,7 +25342,7 @@
         </is>
       </c>
       <c r="G656" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H656" t="n">
         <v>115.6279</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H658" t="n">
         <v>115.6279</v>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="G663" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H663" t="n">
         <v>116.3447</v>
@@ -25798,7 +25798,7 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H668" t="n">
         <v>119.4405</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H670" t="n">
         <v>118.6322</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H672" t="n">
         <v>118.1747</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="G673" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H673" t="n">
         <v>118.0222</v>
@@ -26178,7 +26178,7 @@
         </is>
       </c>
       <c r="G678" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H678" t="n">
         <v>118.6627</v>
@@ -26216,7 +26216,7 @@
         </is>
       </c>
       <c r="G679" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H679" t="n">
         <v>117.9612</v>
@@ -26444,7 +26444,7 @@
         </is>
       </c>
       <c r="G685" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H685" t="n">
         <v>121.3925</v>
@@ -29075,7 +29075,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.239998</v>
+        <v>80.760002</v>
       </c>
       <c r="H755" t="n">
-        <v>124.3122</v>
+        <v>125.1179</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>128.380005</v>
+        <v>129.119995</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.8917</v>
+        <v>120.5827</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>128.380005</v>
+        <v>129.119995</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.8917</v>
+        <v>120.5827</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>128.380005</v>
+        <v>129.119995</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.8917</v>
+        <v>120.5827</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.425835</v>
+        <v>53.425831</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.075188</v>
+        <v>53.075184</v>
       </c>
       <c r="H1510" t="n">
         <v>99.3437</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>53.620636</v>
+        <v>53.62064</v>
       </c>
       <c r="H1512" t="n">
         <v>100.3646</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1514" t="n">
         <v>102.0055</v>
@@ -57984,10 +57984,10 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.799221</v>
+        <v>54.799225</v>
       </c>
       <c r="H1515" t="n">
-        <v>102.5706</v>
+        <v>102.5707</v>
       </c>
     </row>
     <row r="1516">
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.062218</v>
+        <v>55.062214</v>
       </c>
       <c r="H1516" t="n">
         <v>103.0629</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.042732</v>
+        <v>55.042728</v>
       </c>
       <c r="H1517" t="n">
         <v>103.0264</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.974552</v>
+        <v>54.974545</v>
       </c>
       <c r="H1518" t="n">
         <v>102.8988</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.429096</v>
+        <v>54.429092</v>
       </c>
       <c r="H1521" t="n">
         <v>101.8779</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.740788</v>
+        <v>54.74078</v>
       </c>
       <c r="H1522" t="n">
         <v>102.4613</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.53624</v>
+        <v>54.536236</v>
       </c>
       <c r="H1523" t="n">
         <v>102.0784</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>54.818703</v>
+        <v>54.818699</v>
       </c>
       <c r="H1524" t="n">
         <v>102.6071</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1529" t="n">
         <v>103.464</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1532" t="n">
         <v>104.1386</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.588192</v>
+        <v>55.588196</v>
       </c>
       <c r="H1533" t="n">
         <v>104.0474</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1534" t="n">
         <v>103.938</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1535" t="n">
         <v>103.5005</v>
@@ -58785,7 +58785,7 @@
         <v>55.325203</v>
       </c>
       <c r="H1536" t="n">
-        <v>103.5551</v>
+        <v>103.5552</v>
       </c>
     </row>
     <row r="1537">
@@ -58823,7 +58823,7 @@
         <v>55.169357</v>
       </c>
       <c r="H1537" t="n">
-        <v>103.2634</v>
+        <v>103.2635</v>
       </c>
     </row>
     <row r="1538">
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1538" t="n">
         <v>103.464</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>54.867409</v>
+        <v>54.867413</v>
       </c>
       <c r="H1539" t="n">
         <v>102.6983</v>
@@ -58937,7 +58937,7 @@
         <v>54.584934</v>
       </c>
       <c r="H1540" t="n">
-        <v>102.1695</v>
+        <v>102.1696</v>
       </c>
     </row>
     <row r="1541">
@@ -58975,7 +58975,7 @@
         <v>55.383648</v>
       </c>
       <c r="H1541" t="n">
-        <v>103.6645</v>
+        <v>103.6646</v>
       </c>
     </row>
     <row r="1542">
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>56.523262</v>
+        <v>56.523266</v>
       </c>
       <c r="H1543" t="n">
         <v>105.7976</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.607674</v>
+        <v>55.60767</v>
       </c>
       <c r="H1545" t="n">
         <v>104.0839</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.351166</v>
+        <v>54.35117</v>
       </c>
       <c r="H1550" t="n">
         <v>101.732</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>54.877148</v>
+        <v>54.877144</v>
       </c>
       <c r="H1552" t="n">
         <v>102.7165</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1553" t="n">
         <v>103.938</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1557" t="n">
         <v>104.1386</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.958328</v>
+        <v>55.958332</v>
       </c>
       <c r="H1559" t="n">
         <v>104.7402</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.870663</v>
+        <v>55.870667</v>
       </c>
       <c r="H1563" t="n">
         <v>104.5761</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.172611</v>
+        <v>56.172615</v>
       </c>
       <c r="H1564" t="n">
         <v>105.1413</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1566" t="n">
         <v>105.3701</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1568" t="n">
         <v>104.803</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1573" t="n">
         <v>106.6324</v>
@@ -60302,10 +60302,10 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1576" t="n">
-        <v>108.9556</v>
+        <v>108.9557</v>
       </c>
     </row>
     <row r="1577">
@@ -60381,7 +60381,7 @@
         <v>58.513439</v>
       </c>
       <c r="H1578" t="n">
-        <v>109.5227</v>
+        <v>109.5228</v>
       </c>
     </row>
     <row r="1579">
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1580" t="n">
         <v>110.4923</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>59.129166</v>
+        <v>59.129162</v>
       </c>
       <c r="H1581" t="n">
         <v>110.6752</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1584" t="n">
         <v>111.3521</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1585" t="n">
         <v>111.3704</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1587" t="n">
         <v>109.0837</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>58.259331</v>
+        <v>58.259335</v>
       </c>
       <c r="H1588" t="n">
         <v>109.0471</v>
@@ -60875,7 +60875,7 @@
         <v>58.953243</v>
       </c>
       <c r="H1591" t="n">
-        <v>110.3459</v>
+        <v>110.346</v>
       </c>
     </row>
     <row r="1592">
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.168259</v>
+        <v>59.168262</v>
       </c>
       <c r="H1595" t="n">
         <v>110.7484</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.793755</v>
+        <v>59.793758</v>
       </c>
       <c r="H1596" t="n">
         <v>111.9192</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.803528</v>
+        <v>59.803532</v>
       </c>
       <c r="H1598" t="n">
         <v>111.9375</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.246449</v>
+        <v>59.246445</v>
       </c>
       <c r="H1599" t="n">
         <v>110.8948</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.744896</v>
+        <v>59.744892</v>
       </c>
       <c r="H1600" t="n">
         <v>111.8277</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>60.116276</v>
+        <v>60.116283</v>
       </c>
       <c r="H1602" t="n">
         <v>112.5229</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1603" t="n">
         <v>112.6875</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1606" t="n">
         <v>112.1936</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1607" t="n">
         <v>112.7973</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.956795</v>
+        <v>60.956791</v>
       </c>
       <c r="H1608" t="n">
         <v>114.0961</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>60.653816</v>
+        <v>60.65382</v>
       </c>
       <c r="H1609" t="n">
         <v>113.529</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1612" t="n">
         <v>114.2059</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>61.474785</v>
+        <v>61.474789</v>
       </c>
       <c r="H1613" t="n">
         <v>115.0657</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>61.445465</v>
+        <v>61.445469</v>
       </c>
       <c r="H1615" t="n">
         <v>115.0108</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1618" t="n">
         <v>111.1692</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.581852</v>
+        <v>58.581856</v>
       </c>
       <c r="H1619" t="n">
         <v>109.6508</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1622" t="n">
         <v>110.035</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1623" t="n">
         <v>109.413</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1624" t="n">
         <v>108.7727</v>
@@ -62775,7 +62775,7 @@
         <v>59.772263</v>
       </c>
       <c r="H1641" t="n">
-        <v>111.8789</v>
+        <v>111.879</v>
       </c>
     </row>
     <row r="1642">
@@ -62851,7 +62851,7 @@
         <v>59.899628</v>
       </c>
       <c r="H1643" t="n">
-        <v>112.1173</v>
+        <v>112.1174</v>
       </c>
     </row>
     <row r="1644">
@@ -62927,7 +62927,7 @@
         <v>60.340496</v>
       </c>
       <c r="H1645" t="n">
-        <v>112.9425</v>
+        <v>112.9426</v>
       </c>
     </row>
     <row r="1646">
@@ -63573,7 +63573,7 @@
         <v>60.056377</v>
       </c>
       <c r="H1662" t="n">
-        <v>112.4107</v>
+        <v>112.4108</v>
       </c>
     </row>
     <row r="1663">
@@ -63877,7 +63877,7 @@
         <v>61.065487</v>
       </c>
       <c r="H1670" t="n">
-        <v>114.2995</v>
+        <v>114.2996</v>
       </c>
     </row>
     <row r="1671">
@@ -63915,7 +63915,7 @@
         <v>61.065487</v>
       </c>
       <c r="H1671" t="n">
-        <v>114.2995</v>
+        <v>114.2996</v>
       </c>
     </row>
     <row r="1672">
@@ -65815,7 +65815,7 @@
         <v>64.203186</v>
       </c>
       <c r="H1721" t="n">
-        <v>120.1725</v>
+        <v>120.1726</v>
       </c>
     </row>
     <row r="1722">
@@ -66043,7 +66043,7 @@
         <v>65.302795</v>
       </c>
       <c r="H1727" t="n">
-        <v>122.2307</v>
+        <v>122.2308</v>
       </c>
     </row>
     <row r="1728">
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.98</v>
+        <v>63.360001</v>
       </c>
       <c r="H1760" t="n">
-        <v>117.883</v>
+        <v>118.5943</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.720001</v>
+        <v>35.349998</v>
       </c>
       <c r="H253" t="n">
-        <v>119.0468</v>
+        <v>117.8137</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.740002</v>
+        <v>48.700001</v>
       </c>
       <c r="H504" t="n">
-        <v>132.4817</v>
+        <v>132.3729</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.44974499999999</v>
+        <v>64.449753</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.673744</v>
+        <v>64.67375199999999</v>
       </c>
       <c r="H507" t="n">
         <v>100.3476</v>
@@ -19984,10 +19984,10 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.910538</v>
+        <v>65.91052999999999</v>
       </c>
       <c r="H515" t="n">
-        <v>102.2666</v>
+        <v>102.2665</v>
       </c>
     </row>
     <row r="516">
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H516" t="n">
         <v>100.6497</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.121712</v>
+        <v>65.121719</v>
       </c>
       <c r="H521" t="n">
         <v>101.0426</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.939751</v>
+        <v>65.939758</v>
       </c>
       <c r="H524" t="n">
         <v>102.3119</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.066345</v>
+        <v>66.06635300000001</v>
       </c>
       <c r="H525" t="n">
         <v>102.5083</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H526" t="n">
         <v>103.0372</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.339043</v>
+        <v>66.339035</v>
       </c>
       <c r="H527" t="n">
         <v>102.9314</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.212433</v>
+        <v>66.212425</v>
       </c>
       <c r="H528" t="n">
         <v>102.735</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H529" t="n">
         <v>103.0372</v>
@@ -20557,7 +20557,7 @@
         <v>66.095573</v>
       </c>
       <c r="H530" t="n">
-        <v>102.5537</v>
+        <v>102.5536</v>
       </c>
     </row>
     <row r="531">
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H531" t="n">
         <v>102.4932</v>
@@ -20633,7 +20633,7 @@
         <v>66.095573</v>
       </c>
       <c r="H532" t="n">
-        <v>102.5537</v>
+        <v>102.5536</v>
       </c>
     </row>
     <row r="533">
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H533" t="n">
         <v>102.8559</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>65.98844099999999</v>
+        <v>65.988457</v>
       </c>
       <c r="H534" t="n">
         <v>102.3874</v>
@@ -20823,7 +20823,7 @@
         <v>66.942825</v>
       </c>
       <c r="H537" t="n">
-        <v>103.8683</v>
+        <v>103.8682</v>
       </c>
     </row>
     <row r="538">
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H538" t="n">
         <v>104.8353</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>65.754723</v>
+        <v>65.754715</v>
       </c>
       <c r="H542" t="n">
         <v>102.0248</v>
@@ -21051,7 +21051,7 @@
         <v>65.715767</v>
       </c>
       <c r="H543" t="n">
-        <v>101.9644</v>
+        <v>101.9643</v>
       </c>
     </row>
     <row r="544">
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027412</v>
       </c>
       <c r="H544" t="n">
         <v>102.4479</v>
@@ -21127,7 +21127,7 @@
         <v>65.891068</v>
       </c>
       <c r="H545" t="n">
-        <v>102.2364</v>
+        <v>102.2363</v>
       </c>
     </row>
     <row r="546">
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.24472799999999</v>
+        <v>67.24472</v>
       </c>
       <c r="H550" t="n">
         <v>104.3367</v>
@@ -21431,7 +21431,7 @@
         <v>66.942825</v>
       </c>
       <c r="H553" t="n">
-        <v>103.8683</v>
+        <v>103.8682</v>
       </c>
     </row>
     <row r="554">
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.51739499999999</v>
+        <v>67.517403</v>
       </c>
       <c r="H555" t="n">
         <v>104.7598</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.22524300000001</v>
+        <v>67.22525</v>
       </c>
       <c r="H558" t="n">
         <v>104.3065</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.478447</v>
+        <v>67.47843899999999</v>
       </c>
       <c r="H559" t="n">
         <v>104.6993</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.3908</v>
+        <v>67.390793</v>
       </c>
       <c r="H560" t="n">
         <v>104.5633</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H562" t="n">
         <v>104.2158</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.234978</v>
+        <v>67.23498499999999</v>
       </c>
       <c r="H563" t="n">
         <v>104.3216</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.619141</v>
+        <v>67.619148</v>
       </c>
       <c r="H564" t="n">
         <v>104.9176</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H565" t="n">
         <v>105.3431</v>
@@ -21922,10 +21922,10 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.815033</v>
+        <v>67.81502500000001</v>
       </c>
       <c r="H566" t="n">
-        <v>105.2216</v>
+        <v>105.2215</v>
       </c>
     </row>
     <row r="567">
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H568" t="n">
         <v>105.9358</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H570" t="n">
         <v>106.3157</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>69.24498</v>
+        <v>69.24498699999999</v>
       </c>
       <c r="H571" t="n">
         <v>107.4403</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>69.48004899999999</v>
+        <v>69.480057</v>
       </c>
       <c r="H573" t="n">
         <v>107.805</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>70.273376</v>
+        <v>70.273369</v>
       </c>
       <c r="H577" t="n">
         <v>109.0359</v>
@@ -22419,7 +22419,7 @@
         <v>71.340942</v>
       </c>
       <c r="H579" t="n">
-        <v>110.6924</v>
+        <v>110.6923</v>
       </c>
     </row>
     <row r="580">
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H580" t="n">
         <v>110.6164</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>70.723907</v>
+        <v>70.72391500000001</v>
       </c>
       <c r="H581" t="n">
         <v>109.735</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H584" t="n">
         <v>109.9629</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.4105</v>
+        <v>70.410492</v>
       </c>
       <c r="H587" t="n">
         <v>109.2487</v>
@@ -22872,10 +22872,10 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H591" t="n">
-        <v>111.2243</v>
+        <v>111.2242</v>
       </c>
     </row>
     <row r="592">
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>72.87863900000001</v>
+        <v>72.878632</v>
       </c>
       <c r="H593" t="n">
         <v>113.0782</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H594" t="n">
         <v>112.2576</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.201836</v>
+        <v>73.201843</v>
       </c>
       <c r="H595" t="n">
         <v>113.5797</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H596" t="n">
         <v>113.7469</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H597" t="n">
         <v>114.142</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H598" t="n">
         <v>115.0082</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H599" t="n">
         <v>114.5675</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.828667</v>
+        <v>73.82867400000001</v>
       </c>
       <c r="H600" t="n">
         <v>114.5523</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H607" t="n">
         <v>115.9504</v>
@@ -23521,7 +23521,7 @@
         <v>75.14109000000001</v>
       </c>
       <c r="H608" t="n">
-        <v>116.5887</v>
+        <v>116.5886</v>
       </c>
     </row>
     <row r="609">
@@ -23597,7 +23597,7 @@
         <v>75.16068300000001</v>
       </c>
       <c r="H610" t="n">
-        <v>116.6191</v>
+        <v>116.619</v>
       </c>
     </row>
     <row r="611">
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>75.003967</v>
+        <v>75.003975</v>
       </c>
       <c r="H611" t="n">
         <v>116.3759</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>73.358543</v>
+        <v>73.35855100000001</v>
       </c>
       <c r="H612" t="n">
         <v>113.8229</v>
@@ -23749,7 +23749,7 @@
         <v>73.113693</v>
       </c>
       <c r="H614" t="n">
-        <v>113.443</v>
+        <v>113.4429</v>
       </c>
     </row>
     <row r="615">
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>72.721931</v>
+        <v>72.72191599999999</v>
       </c>
       <c r="H617" t="n">
         <v>112.8351</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H618" t="n">
         <v>112.3944</v>
@@ -24015,7 +24015,7 @@
         <v>73.113693</v>
       </c>
       <c r="H621" t="n">
-        <v>113.443</v>
+        <v>113.4429</v>
       </c>
     </row>
     <row r="622">
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>72.64357</v>
+        <v>72.643562</v>
       </c>
       <c r="H622" t="n">
         <v>112.7135</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H623" t="n">
         <v>110.961</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H624" t="n">
         <v>109.9377</v>
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H626" t="n">
         <v>110.793</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H629" t="n">
         <v>110.793</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H632" t="n">
         <v>112.7785</v>
@@ -24506,10 +24506,10 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H634" t="n">
-        <v>112.412</v>
+        <v>112.4119</v>
       </c>
     </row>
     <row r="635">
@@ -24582,7 +24582,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H636" t="n">
         <v>114.7335</v>
@@ -24620,10 +24620,10 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H637" t="n">
-        <v>114.4739</v>
+        <v>114.4738</v>
       </c>
     </row>
     <row r="638">
@@ -24696,7 +24696,7 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H639" t="n">
         <v>114.5502</v>
@@ -24772,7 +24772,7 @@
         </is>
       </c>
       <c r="G641" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H641" t="n">
         <v>114.5197</v>
@@ -24813,7 +24813,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H642" t="n">
-        <v>115.4514</v>
+        <v>115.4513</v>
       </c>
     </row>
     <row r="643">
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G645" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H645" t="n">
         <v>114.5502</v>
@@ -24965,7 +24965,7 @@
         <v>74.004524</v>
       </c>
       <c r="H646" t="n">
-        <v>114.8252</v>
+        <v>114.8251</v>
       </c>
     </row>
     <row r="647">
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H648" t="n">
         <v>114.092</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H649" t="n">
         <v>114.4891</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H651" t="n">
         <v>115.4819</v>
@@ -25231,7 +25231,7 @@
         <v>74.40810399999999</v>
       </c>
       <c r="H653" t="n">
-        <v>115.4514</v>
+        <v>115.4513</v>
       </c>
     </row>
     <row r="654">
@@ -25266,7 +25266,7 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H654" t="n">
         <v>116.5816</v>
@@ -25304,10 +25304,10 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H655" t="n">
-        <v>115.8027</v>
+        <v>115.8026</v>
       </c>
     </row>
     <row r="656">
@@ -25380,10 +25380,10 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H657" t="n">
-        <v>115.8027</v>
+        <v>115.8026</v>
       </c>
     </row>
     <row r="658">
@@ -25570,7 +25570,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H662" t="n">
         <v>116.5205</v>
@@ -25687,7 +25687,7 @@
         <v>75.81574999999999</v>
       </c>
       <c r="H665" t="n">
-        <v>117.6355</v>
+        <v>117.6354</v>
       </c>
     </row>
     <row r="666">
@@ -25760,7 +25760,7 @@
         </is>
       </c>
       <c r="G667" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H667" t="n">
         <v>119.621</v>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H669" t="n">
         <v>118.8115</v>
@@ -25912,7 +25912,7 @@
         </is>
       </c>
       <c r="G671" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H671" t="n">
         <v>118.3533</v>
@@ -25950,10 +25950,10 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H672" t="n">
-        <v>118.2006</v>
+        <v>118.2005</v>
       </c>
     </row>
     <row r="673">
@@ -26140,10 +26140,10 @@
         </is>
       </c>
       <c r="G677" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H677" t="n">
-        <v>118.8421</v>
+        <v>118.842</v>
       </c>
     </row>
     <row r="678">
@@ -26178,7 +26178,7 @@
         </is>
       </c>
       <c r="G678" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H678" t="n">
         <v>118.1395</v>
@@ -26406,7 +26406,7 @@
         </is>
       </c>
       <c r="G684" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H684" t="n">
         <v>121.576</v>
@@ -26485,7 +26485,7 @@
         <v>77.914368</v>
       </c>
       <c r="H686" t="n">
-        <v>120.8917</v>
+        <v>120.8916</v>
       </c>
     </row>
     <row r="687">
@@ -26675,7 +26675,7 @@
         <v>78.38175200000001</v>
       </c>
       <c r="H691" t="n">
-        <v>121.6169</v>
+        <v>121.6168</v>
       </c>
     </row>
     <row r="692">
@@ -26789,7 +26789,7 @@
         <v>78.451363</v>
       </c>
       <c r="H694" t="n">
-        <v>121.7249</v>
+        <v>121.7248</v>
       </c>
     </row>
     <row r="695">
@@ -27397,7 +27397,7 @@
         <v>79.952972</v>
       </c>
       <c r="H710" t="n">
-        <v>124.0548</v>
+        <v>124.0547</v>
       </c>
     </row>
     <row r="711">
@@ -27511,7 +27511,7 @@
         <v>81.066734</v>
       </c>
       <c r="H713" t="n">
-        <v>125.7829</v>
+        <v>125.7828</v>
       </c>
     </row>
     <row r="714">
@@ -27663,7 +27663,7 @@
         <v>80.291077</v>
       </c>
       <c r="H717" t="n">
-        <v>124.5794</v>
+        <v>124.5793</v>
       </c>
     </row>
     <row r="718">
@@ -28005,7 +28005,7 @@
         <v>81.295464</v>
       </c>
       <c r="H726" t="n">
-        <v>126.1378</v>
+        <v>126.1377</v>
       </c>
     </row>
     <row r="727">
@@ -28271,7 +28271,7 @@
         <v>81.02697000000001</v>
       </c>
       <c r="H733" t="n">
-        <v>125.7212</v>
+        <v>125.7211</v>
       </c>
     </row>
     <row r="734">
@@ -28537,7 +28537,7 @@
         <v>81.832458</v>
       </c>
       <c r="H740" t="n">
-        <v>126.971</v>
+        <v>126.9709</v>
       </c>
     </row>
     <row r="741">
@@ -28727,7 +28727,7 @@
         <v>80.19163500000001</v>
       </c>
       <c r="H745" t="n">
-        <v>124.4251</v>
+        <v>124.425</v>
       </c>
     </row>
     <row r="746">
@@ -28879,7 +28879,7 @@
         <v>80.82807200000001</v>
       </c>
       <c r="H749" t="n">
-        <v>125.4126</v>
+        <v>125.4125</v>
       </c>
     </row>
     <row r="750">
@@ -29031,7 +29031,7 @@
         <v>80.900002</v>
       </c>
       <c r="H753" t="n">
-        <v>125.5242</v>
+        <v>125.5241</v>
       </c>
     </row>
     <row r="754">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.519997</v>
+        <v>80.370003</v>
       </c>
       <c r="H755" t="n">
-        <v>124.9345</v>
+        <v>124.7018</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>129.050003</v>
+        <v>128.919998</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.6413</v>
+        <v>120.5198</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>129.050003</v>
+        <v>128.919998</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.6413</v>
+        <v>120.5198</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>129.050003</v>
+        <v>128.919998</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.6413</v>
+        <v>120.5198</v>
       </c>
     </row>
     <row r="1509">
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.042728</v>
+        <v>55.042732</v>
       </c>
       <c r="H1516" t="n">
         <v>103.7071</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.974545</v>
+        <v>54.974548</v>
       </c>
       <c r="H1517" t="n">
         <v>103.5786</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.536232</v>
+        <v>54.536236</v>
       </c>
       <c r="H1522" t="n">
         <v>102.7528</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.818703</v>
+        <v>54.818707</v>
       </c>
       <c r="H1523" t="n">
         <v>103.285</v>
@@ -58478,10 +58478,10 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1528" t="n">
-        <v>104.1476</v>
+        <v>104.1475</v>
       </c>
     </row>
     <row r="1529">
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1530" t="n">
         <v>105.0468</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1531" t="n">
         <v>104.8266</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.588192</v>
+        <v>55.588188</v>
       </c>
       <c r="H1532" t="n">
         <v>104.7348</v>
@@ -58820,10 +58820,10 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1537" t="n">
-        <v>104.1476</v>
+        <v>104.1475</v>
       </c>
     </row>
     <row r="1538">
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>56.104431</v>
+        <v>56.104427</v>
       </c>
       <c r="H1541" t="n">
         <v>105.7075</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.607674</v>
+        <v>55.607677</v>
       </c>
       <c r="H1544" t="n">
         <v>104.7715</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>54.877144</v>
+        <v>54.877148</v>
       </c>
       <c r="H1551" t="n">
         <v>103.3951</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1554" t="n">
         <v>105.0468</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1556" t="n">
         <v>104.8266</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.958332</v>
+        <v>55.958328</v>
       </c>
       <c r="H1558" t="n">
         <v>105.4322</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.987545</v>
+        <v>55.987541</v>
       </c>
       <c r="H1559" t="n">
         <v>105.4872</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1560" t="n">
         <v>105.3221</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.841446</v>
+        <v>55.841442</v>
       </c>
       <c r="H1561" t="n">
         <v>105.212</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.870667</v>
+        <v>55.870663</v>
       </c>
       <c r="H1562" t="n">
         <v>105.267</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.172615</v>
+        <v>56.172611</v>
       </c>
       <c r="H1563" t="n">
         <v>105.8359</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.380001</v>
+        <v>63.209999</v>
       </c>
       <c r="H1760" t="n">
-        <v>119.4155</v>
+        <v>119.0952</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.349998</v>
+        <v>35.34</v>
       </c>
       <c r="H253" t="n">
-        <v>117.8137</v>
+        <v>117.7804</v>
       </c>
     </row>
     <row r="254">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.449753</v>
+        <v>64.44976</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19680,10 +19680,10 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.67375199999999</v>
+        <v>64.673737</v>
       </c>
       <c r="H507" t="n">
-        <v>100.3476</v>
+        <v>100.3475</v>
       </c>
     </row>
     <row r="508">
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>65.160667</v>
+        <v>65.160675</v>
       </c>
       <c r="H510" t="n">
         <v>101.1031</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.65733299999999</v>
+        <v>65.657341</v>
       </c>
       <c r="H512" t="n">
         <v>101.8737</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.65733299999999</v>
+        <v>65.657341</v>
       </c>
       <c r="H513" t="n">
         <v>101.8737</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H515" t="n">
         <v>102.2665</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H516" t="n">
         <v>100.6497</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.199623</v>
+        <v>65.19961499999999</v>
       </c>
       <c r="H517" t="n">
         <v>101.1635</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.111977</v>
+        <v>65.111969</v>
       </c>
       <c r="H518" t="n">
         <v>101.0275</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.540474</v>
+        <v>65.540482</v>
       </c>
       <c r="H519" t="n">
         <v>101.6924</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H526" t="n">
         <v>103.0372</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H528" t="n">
         <v>102.735</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H529" t="n">
         <v>103.0372</v>
@@ -20668,10 +20668,10 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H533" t="n">
-        <v>102.8559</v>
+        <v>102.8558</v>
       </c>
     </row>
     <row r="534">
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>65.988457</v>
+        <v>65.988449</v>
       </c>
       <c r="H534" t="n">
         <v>102.3874</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>65.57942199999999</v>
+        <v>65.579414</v>
       </c>
       <c r="H535" t="n">
         <v>101.7528</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368256</v>
       </c>
       <c r="H536" t="n">
         <v>102.9767</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H537" t="n">
         <v>103.8682</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H538" t="n">
         <v>104.8353</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H539" t="n">
         <v>104.0496</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.416939</v>
+        <v>66.416946</v>
       </c>
       <c r="H541" t="n">
         <v>103.0523</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.027412</v>
+        <v>66.027405</v>
       </c>
       <c r="H544" t="n">
         <v>102.4479</v>
@@ -21203,7 +21203,7 @@
         <v>66.387726</v>
       </c>
       <c r="H547" t="n">
-        <v>103.007</v>
+        <v>103.0069</v>
       </c>
     </row>
     <row r="548">
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H548" t="n">
         <v>103.9589</v>
@@ -21317,7 +21317,7 @@
         <v>67.24472</v>
       </c>
       <c r="H550" t="n">
-        <v>104.3367</v>
+        <v>104.3366</v>
       </c>
     </row>
     <row r="551">
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H551" t="n">
         <v>104.0496</v>
@@ -21393,7 +21393,7 @@
         <v>66.87464900000001</v>
       </c>
       <c r="H552" t="n">
-        <v>103.7625</v>
+        <v>103.7624</v>
       </c>
     </row>
     <row r="553">
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H553" t="n">
         <v>103.8682</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.371323</v>
+        <v>67.371315</v>
       </c>
       <c r="H554" t="n">
         <v>104.5331</v>
@@ -21507,7 +21507,7 @@
         <v>67.517403</v>
       </c>
       <c r="H555" t="n">
-        <v>104.7598</v>
+        <v>104.7597</v>
       </c>
     </row>
     <row r="556">
@@ -21618,10 +21618,10 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.22525</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H558" t="n">
-        <v>104.3065</v>
+        <v>104.3064</v>
       </c>
     </row>
     <row r="559">
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H559" t="n">
         <v>104.6993</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H560" t="n">
         <v>104.5633</v>
@@ -21808,10 +21808,10 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.23498499999999</v>
+        <v>67.234978</v>
       </c>
       <c r="H563" t="n">
-        <v>104.3216</v>
+        <v>104.3215</v>
       </c>
     </row>
     <row r="564">
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.619148</v>
+        <v>67.619141</v>
       </c>
       <c r="H564" t="n">
         <v>104.9176</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>67.81502500000001</v>
+        <v>67.815033</v>
       </c>
       <c r="H566" t="n">
         <v>105.2215</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275352</v>
       </c>
       <c r="H568" t="n">
         <v>105.9358</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>69.773865</v>
+        <v>69.773872</v>
       </c>
       <c r="H572" t="n">
         <v>108.2609</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>69.480057</v>
+        <v>69.48004899999999</v>
       </c>
       <c r="H573" t="n">
         <v>107.805</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H574" t="n">
         <v>108.1393</v>
@@ -22302,10 +22302,10 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.18523399999999</v>
+        <v>70.185226</v>
       </c>
       <c r="H576" t="n">
-        <v>108.8992</v>
+        <v>108.8991</v>
       </c>
     </row>
     <row r="577">
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>70.273369</v>
+        <v>70.273376</v>
       </c>
       <c r="H577" t="n">
         <v>109.0359</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.645554</v>
+        <v>70.645561</v>
       </c>
       <c r="H578" t="n">
         <v>109.6134</v>
@@ -22492,10 +22492,10 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>70.72391500000001</v>
+        <v>70.723907</v>
       </c>
       <c r="H581" t="n">
-        <v>109.735</v>
+        <v>109.7349</v>
       </c>
     </row>
     <row r="582">
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H582" t="n">
         <v>108.7168</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.371323</v>
+        <v>70.371315</v>
       </c>
       <c r="H583" t="n">
         <v>109.1879</v>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.51823400000001</v>
+        <v>70.518227</v>
       </c>
       <c r="H585" t="n">
         <v>109.4158</v>
@@ -22685,7 +22685,7 @@
         <v>70.43008399999999</v>
       </c>
       <c r="H586" t="n">
-        <v>109.2791</v>
+        <v>109.279</v>
       </c>
     </row>
     <row r="587">
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.410492</v>
+        <v>70.410484</v>
       </c>
       <c r="H587" t="n">
-        <v>109.2487</v>
+        <v>109.2486</v>
       </c>
     </row>
     <row r="588">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.890411</v>
+        <v>70.890404</v>
       </c>
       <c r="H590" t="n">
         <v>109.9933</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H591" t="n">
         <v>111.2242</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>72.37912799999999</v>
+        <v>72.37913500000001</v>
       </c>
       <c r="H592" t="n">
         <v>112.3032</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H593" t="n">
         <v>113.0782</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.201843</v>
+        <v>73.201836</v>
       </c>
       <c r="H595" t="n">
         <v>113.5797</v>
@@ -23065,7 +23065,7 @@
         <v>73.30956999999999</v>
       </c>
       <c r="H596" t="n">
-        <v>113.7469</v>
+        <v>113.7468</v>
       </c>
     </row>
     <row r="597">
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.82867400000001</v>
+        <v>73.828667</v>
       </c>
       <c r="H600" t="n">
         <v>114.5523</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.86784400000001</v>
+        <v>73.867851</v>
       </c>
       <c r="H602" t="n">
         <v>114.6131</v>
@@ -23445,7 +23445,7 @@
         <v>74.524055</v>
       </c>
       <c r="H606" t="n">
-        <v>115.6313</v>
+        <v>115.6312</v>
       </c>
     </row>
     <row r="607">
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>75.14109000000001</v>
+        <v>75.141098</v>
       </c>
       <c r="H608" t="n">
         <v>116.5886</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>75.27821400000001</v>
+        <v>75.278206</v>
       </c>
       <c r="H609" t="n">
         <v>116.8014</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>75.003975</v>
+        <v>75.00398300000001</v>
       </c>
       <c r="H611" t="n">
         <v>116.3759</v>
@@ -23673,7 +23673,7 @@
         <v>73.35855100000001</v>
       </c>
       <c r="H612" t="n">
-        <v>113.8229</v>
+        <v>113.8228</v>
       </c>
     </row>
     <row r="613">
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H614" t="n">
         <v>113.4429</v>
@@ -23825,7 +23825,7 @@
         <v>73.084312</v>
       </c>
       <c r="H616" t="n">
-        <v>113.3974</v>
+        <v>113.3973</v>
       </c>
     </row>
     <row r="617">
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>72.72191599999999</v>
+        <v>72.721931</v>
       </c>
       <c r="H617" t="n">
         <v>112.8351</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H618" t="n">
         <v>112.3944</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>72.55542800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H619" t="n">
         <v>112.5767</v>
@@ -23977,7 +23977,7 @@
         <v>72.780693</v>
       </c>
       <c r="H620" t="n">
-        <v>112.9263</v>
+        <v>112.9262</v>
       </c>
     </row>
     <row r="621">
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H621" t="n">
         <v>113.4429</v>
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>72.643562</v>
+        <v>72.64357</v>
       </c>
       <c r="H622" t="n">
         <v>112.7135</v>
@@ -24243,7 +24243,7 @@
         <v>72.153915</v>
       </c>
       <c r="H627" t="n">
-        <v>111.9538</v>
+        <v>111.9537</v>
       </c>
     </row>
     <row r="628">
@@ -24281,7 +24281,7 @@
         <v>71.779854</v>
       </c>
       <c r="H628" t="n">
-        <v>111.3734</v>
+        <v>111.3733</v>
       </c>
     </row>
     <row r="629">
@@ -24889,7 +24889,7 @@
         <v>73.886391</v>
       </c>
       <c r="H644" t="n">
-        <v>114.6419</v>
+        <v>114.6418</v>
       </c>
     </row>
     <row r="645">
@@ -25003,7 +25003,7 @@
         <v>73.591087</v>
       </c>
       <c r="H647" t="n">
-        <v>114.1837</v>
+        <v>114.1836</v>
       </c>
     </row>
     <row r="648">
@@ -25991,7 +25991,7 @@
         <v>76.770584</v>
       </c>
       <c r="H673" t="n">
-        <v>119.117</v>
+        <v>119.1169</v>
       </c>
     </row>
     <row r="674">
@@ -26181,7 +26181,7 @@
         <v>76.140587</v>
       </c>
       <c r="H678" t="n">
-        <v>118.1395</v>
+        <v>118.1394</v>
       </c>
     </row>
     <row r="679">
@@ -26561,7 +26561,7 @@
         <v>78.182869</v>
       </c>
       <c r="H688" t="n">
-        <v>121.3083</v>
+        <v>121.3082</v>
       </c>
     </row>
     <row r="689">
@@ -26865,7 +26865,7 @@
         <v>79.42591899999999</v>
       </c>
       <c r="H696" t="n">
-        <v>123.237</v>
+        <v>123.2369</v>
       </c>
     </row>
     <row r="697">
@@ -26903,7 +26903,7 @@
         <v>79.52536000000001</v>
       </c>
       <c r="H697" t="n">
-        <v>123.3913</v>
+        <v>123.3912</v>
       </c>
     </row>
     <row r="698">
@@ -27093,7 +27093,7 @@
         <v>79.52536000000001</v>
       </c>
       <c r="H702" t="n">
-        <v>123.3913</v>
+        <v>123.3912</v>
       </c>
     </row>
     <row r="703">
@@ -27207,7 +27207,7 @@
         <v>79.624802</v>
       </c>
       <c r="H705" t="n">
-        <v>123.5456</v>
+        <v>123.5455</v>
       </c>
     </row>
     <row r="706">
@@ -28043,7 +28043,7 @@
         <v>81.166191</v>
       </c>
       <c r="H727" t="n">
-        <v>125.9372</v>
+        <v>125.9371</v>
       </c>
     </row>
     <row r="728">
@@ -28347,7 +28347,7 @@
         <v>80.798241</v>
       </c>
       <c r="H735" t="n">
-        <v>125.3663</v>
+        <v>125.3662</v>
       </c>
     </row>
     <row r="736">
@@ -28613,7 +28613,7 @@
         <v>81.36507400000001</v>
       </c>
       <c r="H742" t="n">
-        <v>126.2458</v>
+        <v>126.2457</v>
       </c>
     </row>
     <row r="743">
@@ -28841,7 +28841,7 @@
         <v>80.46013600000001</v>
       </c>
       <c r="H748" t="n">
-        <v>124.8417</v>
+        <v>124.8416</v>
       </c>
     </row>
     <row r="749">
@@ -28993,7 +28993,7 @@
         <v>80.910004</v>
       </c>
       <c r="H752" t="n">
-        <v>125.5397</v>
+        <v>125.5396</v>
       </c>
     </row>
     <row r="753">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.370003</v>
+        <v>80.540001</v>
       </c>
       <c r="H755" t="n">
-        <v>124.7018</v>
+        <v>124.9656</v>
       </c>
     </row>
     <row r="756">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.523239</v>
+        <v>53.523235</v>
       </c>
       <c r="H1510" t="n">
         <v>100.8442</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1513" t="n">
         <v>102.6794</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.799225</v>
+        <v>54.799221</v>
       </c>
       <c r="H1514" t="n">
         <v>103.2483</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1518" t="n">
         <v>104.3861</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.536236</v>
+        <v>54.53624</v>
       </c>
       <c r="H1522" t="n">
         <v>102.7528</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1523" t="n">
         <v>103.285</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1525" t="n">
         <v>103.0281</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1527" t="n">
         <v>104.3861</v>
@@ -58478,10 +58478,10 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1528" t="n">
-        <v>104.1475</v>
+        <v>104.1476</v>
       </c>
     </row>
     <row r="1529">
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.588188</v>
+        <v>55.588192</v>
       </c>
       <c r="H1532" t="n">
         <v>104.7348</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1533" t="n">
         <v>104.6247</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.295986</v>
+        <v>55.295982</v>
       </c>
       <c r="H1534" t="n">
         <v>104.1843</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.325203</v>
+        <v>55.325199</v>
       </c>
       <c r="H1535" t="n">
         <v>104.2393</v>
@@ -58820,10 +58820,10 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1537" t="n">
-        <v>104.1475</v>
+        <v>104.1476</v>
       </c>
     </row>
     <row r="1538">
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>54.867409</v>
+        <v>54.867405</v>
       </c>
       <c r="H1538" t="n">
         <v>103.3768</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1540" t="n">
         <v>104.3494</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1541" t="n">
         <v>105.7075</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1543" t="n">
         <v>105.7809</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.607677</v>
+        <v>55.607674</v>
       </c>
       <c r="H1544" t="n">
         <v>104.7715</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1546" t="n">
         <v>102.3858</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.351166</v>
+        <v>54.35117</v>
       </c>
       <c r="H1549" t="n">
         <v>102.4041</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1552" t="n">
         <v>104.6247</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.987541</v>
+        <v>55.987545</v>
       </c>
       <c r="H1559" t="n">
         <v>105.4872</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1560" t="n">
         <v>105.3221</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1561" t="n">
         <v>105.212</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1564" t="n">
         <v>105.2303</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1566" t="n">
         <v>105.6243</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.558754</v>
+        <v>56.558758</v>
       </c>
       <c r="H1568" t="n">
         <v>106.5635</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1569" t="n">
         <v>106.987</v>
@@ -60074,10 +60074,10 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.676044</v>
+        <v>56.676041</v>
       </c>
       <c r="H1570" t="n">
-        <v>106.7845</v>
+        <v>106.7844</v>
       </c>
     </row>
     <row r="1571">
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1572" t="n">
         <v>107.3369</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>57.692471</v>
+        <v>57.692474</v>
       </c>
       <c r="H1574" t="n">
         <v>108.6995</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>59.031437</v>
+        <v>59.031433</v>
       </c>
       <c r="H1579" t="n">
         <v>111.2223</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1583" t="n">
         <v>112.0878</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1584" t="n">
         <v>112.1062</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1586" t="n">
         <v>109.8044</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.953247</v>
+        <v>58.953243</v>
       </c>
       <c r="H1590" t="n">
         <v>111.075</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>59.168262</v>
+        <v>59.168259</v>
       </c>
       <c r="H1594" t="n">
         <v>111.4801</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.793758</v>
+        <v>59.793755</v>
       </c>
       <c r="H1595" t="n">
         <v>112.6586</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.803532</v>
+        <v>59.803528</v>
       </c>
       <c r="H1597" t="n">
         <v>112.677</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.246445</v>
+        <v>59.246449</v>
       </c>
       <c r="H1598" t="n">
         <v>111.6274</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.744892</v>
+        <v>59.744896</v>
       </c>
       <c r="H1599" t="n">
         <v>112.5665</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>60.11628</v>
+        <v>60.116276</v>
       </c>
       <c r="H1601" t="n">
         <v>113.2663</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1602" t="n">
         <v>113.432</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1603" t="n">
         <v>112.9164</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1605" t="n">
         <v>112.9348</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1606" t="n">
         <v>113.5425</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.65382</v>
+        <v>60.653816</v>
       </c>
       <c r="H1608" t="n">
         <v>114.2791</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1610" t="n">
         <v>114.6842</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.015434</v>
+        <v>61.015438</v>
       </c>
       <c r="H1611" t="n">
         <v>114.9604</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>59.393051</v>
+        <v>59.393047</v>
       </c>
       <c r="H1617" t="n">
         <v>111.9036</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.581856</v>
+        <v>58.581852</v>
       </c>
       <c r="H1618" t="n">
         <v>110.3752</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1619" t="n">
         <v>109.3809</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1621" t="n">
         <v>110.7619</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>58.4548</v>
+        <v>58.454803</v>
       </c>
       <c r="H1622" t="n">
         <v>110.1358</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.112728</v>
+        <v>58.112732</v>
       </c>
       <c r="H1623" t="n">
         <v>109.4913</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1626" t="n">
         <v>110.0892</v>
@@ -62924,7 +62924,7 @@
         </is>
       </c>
       <c r="G1645" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1645" t="n">
         <v>113.338</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1647" t="n">
         <v>115.0916</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1649" t="n">
         <v>113.1903</v>
@@ -63152,7 +63152,7 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1651" t="n">
         <v>112.9504</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1652" t="n">
         <v>112.3412</v>
@@ -63304,10 +63304,10 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1655" t="n">
-        <v>111.0676</v>
+        <v>111.0675</v>
       </c>
     </row>
     <row r="1656">
@@ -63418,7 +63418,7 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1658" t="n">
         <v>112.5443</v>
@@ -63456,7 +63456,7 @@
         </is>
       </c>
       <c r="G1659" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1659" t="n">
         <v>115.0362</v>
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1661" t="n">
         <v>113.1534</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="G1663" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1663" t="n">
         <v>112.1197</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1673" t="n">
         <v>116.5868</v>
@@ -64064,7 +64064,7 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1675" t="n">
         <v>116.0884</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1678" t="n">
         <v>116.2176</v>
@@ -64254,7 +64254,7 @@
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1680" t="n">
         <v>116.0884</v>
@@ -64292,7 +64292,7 @@
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1681" t="n">
         <v>115.6269</v>
@@ -64444,7 +64444,7 @@
         </is>
       </c>
       <c r="G1685" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1685" t="n">
         <v>115.4792</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.209999</v>
+        <v>63.23</v>
       </c>
       <c r="H1760" t="n">
-        <v>119.0952</v>
+        <v>119.1329</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.44976</v>
+        <v>64.449753</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.741913</v>
+        <v>64.74191999999999</v>
       </c>
       <c r="H506" t="n">
         <v>100.4533</v>
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.673737</v>
+        <v>64.673744</v>
       </c>
       <c r="H507" t="n">
         <v>100.3475</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.511253</v>
+        <v>65.511246</v>
       </c>
       <c r="H511" t="n">
         <v>101.647</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.657341</v>
+        <v>65.65733299999999</v>
       </c>
       <c r="H512" t="n">
         <v>101.8737</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.657341</v>
+        <v>65.65733299999999</v>
       </c>
       <c r="H513" t="n">
         <v>101.8737</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.19961499999999</v>
+        <v>65.199623</v>
       </c>
       <c r="H517" t="n">
         <v>101.1635</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H518" t="n">
         <v>101.0275</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.540482</v>
+        <v>65.540474</v>
       </c>
       <c r="H519" t="n">
         <v>101.6924</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H524" t="n">
         <v>102.3119</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H531" t="n">
         <v>102.4932</v>
@@ -20668,10 +20668,10 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H533" t="n">
-        <v>102.8558</v>
+        <v>102.8559</v>
       </c>
     </row>
     <row r="534">
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H538" t="n">
         <v>104.8353</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H540" t="n">
         <v>103.6114</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.416946</v>
+        <v>66.416939</v>
       </c>
       <c r="H541" t="n">
         <v>103.0523</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H545" t="n">
         <v>102.2363</v>
@@ -21203,7 +21203,7 @@
         <v>66.387726</v>
       </c>
       <c r="H547" t="n">
-        <v>103.0069</v>
+        <v>103.007</v>
       </c>
     </row>
     <row r="548">
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H548" t="n">
         <v>103.9589</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.96230300000001</v>
+        <v>66.962311</v>
       </c>
       <c r="H549" t="n">
         <v>103.8985</v>
@@ -21317,7 +21317,7 @@
         <v>67.24472</v>
       </c>
       <c r="H550" t="n">
-        <v>104.3366</v>
+        <v>104.3367</v>
       </c>
     </row>
     <row r="551">
@@ -21393,7 +21393,7 @@
         <v>66.87464900000001</v>
       </c>
       <c r="H552" t="n">
-        <v>103.7624</v>
+        <v>103.7625</v>
       </c>
     </row>
     <row r="553">
@@ -21507,7 +21507,7 @@
         <v>67.517403</v>
       </c>
       <c r="H555" t="n">
-        <v>104.7597</v>
+        <v>104.7598</v>
       </c>
     </row>
     <row r="556">
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.770599</v>
+        <v>67.77059199999999</v>
       </c>
       <c r="H561" t="n">
         <v>105.1526</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H562" t="n">
         <v>104.2158</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.234978</v>
+        <v>67.23497</v>
       </c>
       <c r="H563" t="n">
         <v>104.3215</v>
@@ -21925,7 +21925,7 @@
         <v>67.815033</v>
       </c>
       <c r="H566" t="n">
-        <v>105.2215</v>
+        <v>105.2216</v>
       </c>
     </row>
     <row r="567">
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>68.275352</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H568" t="n">
         <v>105.9358</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>68.30474100000001</v>
+        <v>68.304733</v>
       </c>
       <c r="H569" t="n">
         <v>105.9814</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H572" t="n">
         <v>108.2609</v>
@@ -22302,10 +22302,10 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H576" t="n">
-        <v>108.8991</v>
+        <v>108.8992</v>
       </c>
     </row>
     <row r="577">
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.645561</v>
+        <v>70.645554</v>
       </c>
       <c r="H578" t="n">
         <v>109.6134</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>71.340942</v>
+        <v>71.340935</v>
       </c>
       <c r="H579" t="n">
         <v>110.6923</v>
@@ -22495,7 +22495,7 @@
         <v>70.723907</v>
       </c>
       <c r="H581" t="n">
-        <v>109.7349</v>
+        <v>109.735</v>
       </c>
     </row>
     <row r="582">
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H583" t="n">
         <v>109.1879</v>
@@ -22685,7 +22685,7 @@
         <v>70.43008399999999</v>
       </c>
       <c r="H586" t="n">
-        <v>109.279</v>
+        <v>109.2791</v>
       </c>
     </row>
     <row r="587">
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>70.684731</v>
+        <v>70.68472300000001</v>
       </c>
       <c r="H589" t="n">
         <v>109.6742</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.890404</v>
+        <v>70.890411</v>
       </c>
       <c r="H590" t="n">
         <v>109.9933</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H591" t="n">
         <v>111.2242</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>72.37913500000001</v>
+        <v>72.37912799999999</v>
       </c>
       <c r="H592" t="n">
         <v>112.3032</v>
@@ -23065,7 +23065,7 @@
         <v>73.30956999999999</v>
       </c>
       <c r="H596" t="n">
-        <v>113.7468</v>
+        <v>113.7469</v>
       </c>
     </row>
     <row r="597">
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H602" t="n">
         <v>114.6131</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H603" t="n">
         <v>115.5857</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H604" t="n">
         <v>115.5857</v>
@@ -23442,10 +23442,10 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.524055</v>
+        <v>74.524063</v>
       </c>
       <c r="H606" t="n">
-        <v>115.6312</v>
+        <v>115.6313</v>
       </c>
     </row>
     <row r="607">
@@ -23521,7 +23521,7 @@
         <v>75.141098</v>
       </c>
       <c r="H608" t="n">
-        <v>116.5886</v>
+        <v>116.5887</v>
       </c>
     </row>
     <row r="609">
@@ -23673,7 +23673,7 @@
         <v>73.35855100000001</v>
       </c>
       <c r="H612" t="n">
-        <v>113.8228</v>
+        <v>113.8229</v>
       </c>
     </row>
     <row r="613">
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>73.11370100000001</v>
+        <v>73.113693</v>
       </c>
       <c r="H614" t="n">
         <v>113.4429</v>
@@ -23825,7 +23825,7 @@
         <v>73.084312</v>
       </c>
       <c r="H616" t="n">
-        <v>113.3973</v>
+        <v>113.3974</v>
       </c>
     </row>
     <row r="617">
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>72.721931</v>
+        <v>72.721924</v>
       </c>
       <c r="H617" t="n">
         <v>112.8351</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H618" t="n">
         <v>112.3944</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H619" t="n">
         <v>112.5767</v>
@@ -23977,7 +23977,7 @@
         <v>72.780693</v>
       </c>
       <c r="H620" t="n">
-        <v>112.9262</v>
+        <v>112.9263</v>
       </c>
     </row>
     <row r="621">
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>73.11370100000001</v>
+        <v>73.113693</v>
       </c>
       <c r="H621" t="n">
         <v>113.4429</v>
@@ -24243,7 +24243,7 @@
         <v>72.153915</v>
       </c>
       <c r="H627" t="n">
-        <v>111.9537</v>
+        <v>111.9538</v>
       </c>
     </row>
     <row r="628">
@@ -24281,7 +24281,7 @@
         <v>71.779854</v>
       </c>
       <c r="H628" t="n">
-        <v>111.3733</v>
+        <v>111.3734</v>
       </c>
     </row>
     <row r="629">
@@ -24889,7 +24889,7 @@
         <v>73.886391</v>
       </c>
       <c r="H644" t="n">
-        <v>114.6418</v>
+        <v>114.6419</v>
       </c>
     </row>
     <row r="645">
@@ -25003,7 +25003,7 @@
         <v>73.591087</v>
       </c>
       <c r="H647" t="n">
-        <v>114.1836</v>
+        <v>114.1837</v>
       </c>
     </row>
     <row r="648">
@@ -25991,7 +25991,7 @@
         <v>76.770584</v>
       </c>
       <c r="H673" t="n">
-        <v>119.1169</v>
+        <v>119.117</v>
       </c>
     </row>
     <row r="674">
@@ -26181,7 +26181,7 @@
         <v>76.140587</v>
       </c>
       <c r="H678" t="n">
-        <v>118.1394</v>
+        <v>118.1395</v>
       </c>
     </row>
     <row r="679">
@@ -26561,7 +26561,7 @@
         <v>78.182869</v>
       </c>
       <c r="H688" t="n">
-        <v>121.3082</v>
+        <v>121.3083</v>
       </c>
     </row>
     <row r="689">
@@ -26865,7 +26865,7 @@
         <v>79.42591899999999</v>
       </c>
       <c r="H696" t="n">
-        <v>123.2369</v>
+        <v>123.237</v>
       </c>
     </row>
     <row r="697">
@@ -26903,7 +26903,7 @@
         <v>79.52536000000001</v>
       </c>
       <c r="H697" t="n">
-        <v>123.3912</v>
+        <v>123.3913</v>
       </c>
     </row>
     <row r="698">
@@ -27093,7 +27093,7 @@
         <v>79.52536000000001</v>
       </c>
       <c r="H702" t="n">
-        <v>123.3912</v>
+        <v>123.3913</v>
       </c>
     </row>
     <row r="703">
@@ -27207,7 +27207,7 @@
         <v>79.624802</v>
       </c>
       <c r="H705" t="n">
-        <v>123.5455</v>
+        <v>123.5456</v>
       </c>
     </row>
     <row r="706">
@@ -28043,7 +28043,7 @@
         <v>81.166191</v>
       </c>
       <c r="H727" t="n">
-        <v>125.9371</v>
+        <v>125.9372</v>
       </c>
     </row>
     <row r="728">
@@ -28347,7 +28347,7 @@
         <v>80.798241</v>
       </c>
       <c r="H735" t="n">
-        <v>125.3662</v>
+        <v>125.3663</v>
       </c>
     </row>
     <row r="736">
@@ -28613,7 +28613,7 @@
         <v>81.36507400000001</v>
       </c>
       <c r="H742" t="n">
-        <v>126.2457</v>
+        <v>126.2458</v>
       </c>
     </row>
     <row r="743">
@@ -28841,7 +28841,7 @@
         <v>80.46013600000001</v>
       </c>
       <c r="H748" t="n">
-        <v>124.8416</v>
+        <v>124.8417</v>
       </c>
     </row>
     <row r="749">
@@ -28993,7 +28993,7 @@
         <v>80.910004</v>
       </c>
       <c r="H752" t="n">
-        <v>125.5396</v>
+        <v>125.5397</v>
       </c>
     </row>
     <row r="753">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.523235</v>
+        <v>53.523239</v>
       </c>
       <c r="H1510" t="n">
         <v>100.8442</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.497276</v>
+        <v>54.497272</v>
       </c>
       <c r="H1513" t="n">
         <v>102.6794</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.799221</v>
+        <v>54.799225</v>
       </c>
       <c r="H1514" t="n">
         <v>103.2483</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.042732</v>
+        <v>55.042728</v>
       </c>
       <c r="H1516" t="n">
         <v>103.7071</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.974548</v>
+        <v>54.974545</v>
       </c>
       <c r="H1517" t="n">
         <v>103.5786</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1518" t="n">
         <v>104.3861</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.53624</v>
+        <v>54.536232</v>
       </c>
       <c r="H1522" t="n">
         <v>102.7528</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.682339</v>
+        <v>54.682335</v>
       </c>
       <c r="H1525" t="n">
         <v>103.0281</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1527" t="n">
         <v>104.3861</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1530" t="n">
         <v>105.0468</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1531" t="n">
         <v>104.8266</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1533" t="n">
         <v>104.6247</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1534" t="n">
         <v>104.1843</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.325199</v>
+        <v>55.325203</v>
       </c>
       <c r="H1535" t="n">
         <v>104.2393</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>54.867405</v>
+        <v>54.867409</v>
       </c>
       <c r="H1538" t="n">
         <v>103.3768</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1540" t="n">
         <v>104.3494</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>56.143391</v>
+        <v>56.143394</v>
       </c>
       <c r="H1543" t="n">
         <v>105.7809</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1546" t="n">
         <v>102.3858</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.35117</v>
+        <v>54.351166</v>
       </c>
       <c r="H1549" t="n">
         <v>102.4041</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>54.877148</v>
+        <v>54.877144</v>
       </c>
       <c r="H1551" t="n">
         <v>103.3951</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1552" t="n">
         <v>104.6247</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1554" t="n">
         <v>105.0468</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1556" t="n">
         <v>104.8266</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.958328</v>
+        <v>55.958332</v>
       </c>
       <c r="H1558" t="n">
         <v>105.4322</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.870663</v>
+        <v>55.870667</v>
       </c>
       <c r="H1562" t="n">
         <v>105.267</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.172611</v>
+        <v>56.172615</v>
       </c>
       <c r="H1563" t="n">
         <v>105.8359</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1564" t="n">
         <v>105.2303</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1566" t="n">
         <v>105.6243</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.558758</v>
+        <v>56.558754</v>
       </c>
       <c r="H1568" t="n">
         <v>106.5635</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1569" t="n">
         <v>106.987</v>
@@ -60074,10 +60074,10 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.676041</v>
+        <v>56.676044</v>
       </c>
       <c r="H1570" t="n">
-        <v>106.7844</v>
+        <v>106.7845</v>
       </c>
     </row>
     <row r="1571">
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1572" t="n">
         <v>107.3369</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>57.692474</v>
+        <v>57.692471</v>
       </c>
       <c r="H1574" t="n">
         <v>108.6995</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1579" t="n">
         <v>111.2223</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1583" t="n">
         <v>112.0878</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1584" t="n">
         <v>112.1062</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1586" t="n">
         <v>109.8044</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.953243</v>
+        <v>58.953247</v>
       </c>
       <c r="H1590" t="n">
         <v>111.075</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>59.168259</v>
+        <v>59.168262</v>
       </c>
       <c r="H1594" t="n">
         <v>111.4801</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.793755</v>
+        <v>59.793758</v>
       </c>
       <c r="H1595" t="n">
         <v>112.6586</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.803528</v>
+        <v>59.803532</v>
       </c>
       <c r="H1597" t="n">
         <v>112.677</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.246449</v>
+        <v>59.246445</v>
       </c>
       <c r="H1598" t="n">
         <v>111.6274</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.744896</v>
+        <v>59.744892</v>
       </c>
       <c r="H1599" t="n">
         <v>112.5665</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>60.116276</v>
+        <v>60.11628</v>
       </c>
       <c r="H1601" t="n">
         <v>113.2663</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1602" t="n">
         <v>113.432</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1603" t="n">
         <v>112.9164</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1605" t="n">
         <v>112.9348</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1606" t="n">
         <v>113.5425</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.653816</v>
+        <v>60.65382</v>
       </c>
       <c r="H1608" t="n">
         <v>114.2791</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1610" t="n">
         <v>114.6842</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1611" t="n">
         <v>114.9604</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1617" t="n">
         <v>111.9036</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.581852</v>
+        <v>58.581856</v>
       </c>
       <c r="H1618" t="n">
         <v>110.3752</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1619" t="n">
         <v>109.3809</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1621" t="n">
         <v>110.7619</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1622" t="n">
         <v>110.1358</v>
@@ -62088,7 +62088,7 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1623" t="n">
         <v>109.4913</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1626" t="n">
         <v>110.0892</v>
@@ -62924,7 +62924,7 @@
         </is>
       </c>
       <c r="G1645" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1645" t="n">
         <v>113.338</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1647" t="n">
         <v>115.0916</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1649" t="n">
         <v>113.1903</v>
@@ -63152,7 +63152,7 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1651" t="n">
         <v>112.9504</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1652" t="n">
         <v>112.3412</v>
@@ -63304,10 +63304,10 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1655" t="n">
-        <v>111.0675</v>
+        <v>111.0676</v>
       </c>
     </row>
     <row r="1656">
@@ -63418,7 +63418,7 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1658" t="n">
         <v>112.5443</v>
@@ -63456,7 +63456,7 @@
         </is>
       </c>
       <c r="G1659" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1659" t="n">
         <v>115.0362</v>
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1661" t="n">
         <v>113.1534</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="G1663" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1663" t="n">
         <v>112.1197</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1673" t="n">
         <v>116.5868</v>
@@ -64064,7 +64064,7 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1675" t="n">
         <v>116.0884</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1678" t="n">
         <v>116.2176</v>
@@ -64254,7 +64254,7 @@
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1680" t="n">
         <v>116.0884</v>
@@ -64292,7 +64292,7 @@
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1681" t="n">
         <v>115.6269</v>
@@ -64444,7 +64444,7 @@
         </is>
       </c>
       <c r="G1685" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1685" t="n">
         <v>115.4792</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.34</v>
+        <v>36.014999</v>
       </c>
       <c r="H253" t="n">
-        <v>117.7804</v>
+        <v>120.03</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.700001</v>
+        <v>48.369999</v>
       </c>
       <c r="H504" t="n">
-        <v>132.3729</v>
+        <v>131.4759</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.449753</v>
+        <v>64.44976</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.74191999999999</v>
+        <v>64.741913</v>
       </c>
       <c r="H506" t="n">
         <v>100.4533</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H516" t="n">
         <v>100.6497</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.540474</v>
+        <v>65.540482</v>
       </c>
       <c r="H519" t="n">
         <v>101.6924</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.939751</v>
+        <v>65.939758</v>
       </c>
       <c r="H524" t="n">
         <v>102.3119</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H530" t="n">
         <v>102.5536</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H531" t="n">
         <v>102.4932</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H532" t="n">
         <v>102.5536</v>
@@ -20671,7 +20671,7 @@
         <v>66.290344</v>
       </c>
       <c r="H533" t="n">
-        <v>102.8559</v>
+        <v>102.8558</v>
       </c>
     </row>
     <row r="534">
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>65.988449</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H534" t="n">
         <v>102.3874</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H536" t="n">
         <v>102.9767</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H538" t="n">
         <v>104.8353</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>67.059692</v>
+        <v>67.05970000000001</v>
       </c>
       <c r="H539" t="n">
         <v>104.0496</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H544" t="n">
         <v>102.4479</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.124786</v>
+        <v>66.124779</v>
       </c>
       <c r="H546" t="n">
         <v>102.599</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.387726</v>
+        <v>66.387733</v>
       </c>
       <c r="H547" t="n">
         <v>103.007</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H548" t="n">
         <v>103.9589</v>
@@ -21317,7 +21317,7 @@
         <v>67.24472</v>
       </c>
       <c r="H550" t="n">
-        <v>104.3367</v>
+        <v>104.3366</v>
       </c>
     </row>
     <row r="551">
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.059692</v>
+        <v>67.05970000000001</v>
       </c>
       <c r="H551" t="n">
         <v>104.0496</v>
@@ -21393,7 +21393,7 @@
         <v>66.87464900000001</v>
       </c>
       <c r="H552" t="n">
-        <v>103.7625</v>
+        <v>103.7624</v>
       </c>
     </row>
     <row r="553">
@@ -21504,10 +21504,10 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H555" t="n">
-        <v>104.7598</v>
+        <v>104.7597</v>
       </c>
     </row>
     <row r="556">
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H561" t="n">
         <v>105.1526</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.23497</v>
+        <v>67.234978</v>
       </c>
       <c r="H563" t="n">
         <v>104.3215</v>
@@ -21925,7 +21925,7 @@
         <v>67.815033</v>
       </c>
       <c r="H566" t="n">
-        <v>105.2216</v>
+        <v>105.2215</v>
       </c>
     </row>
     <row r="567">
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275352</v>
       </c>
       <c r="H568" t="n">
         <v>105.9358</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>68.304733</v>
+        <v>68.30474100000001</v>
       </c>
       <c r="H569" t="n">
         <v>105.9814</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>69.773865</v>
+        <v>69.773872</v>
       </c>
       <c r="H572" t="n">
         <v>108.2609</v>
@@ -22302,10 +22302,10 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.18523399999999</v>
+        <v>70.185226</v>
       </c>
       <c r="H576" t="n">
-        <v>108.8992</v>
+        <v>108.8991</v>
       </c>
     </row>
     <row r="577">
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.645554</v>
+        <v>70.645561</v>
       </c>
       <c r="H578" t="n">
         <v>109.6134</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>71.340935</v>
+        <v>71.340942</v>
       </c>
       <c r="H579" t="n">
         <v>110.6923</v>
@@ -22495,7 +22495,7 @@
         <v>70.723907</v>
       </c>
       <c r="H581" t="n">
-        <v>109.735</v>
+        <v>109.7349</v>
       </c>
     </row>
     <row r="582">
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.371323</v>
+        <v>70.371315</v>
       </c>
       <c r="H583" t="n">
         <v>109.1879</v>
@@ -22685,7 +22685,7 @@
         <v>70.43008399999999</v>
       </c>
       <c r="H586" t="n">
-        <v>109.2791</v>
+        <v>109.279</v>
       </c>
     </row>
     <row r="587">
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>70.68472300000001</v>
+        <v>70.684731</v>
       </c>
       <c r="H589" t="n">
         <v>109.6742</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>70.890411</v>
+        <v>70.890404</v>
       </c>
       <c r="H590" t="n">
         <v>109.9933</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H591" t="n">
         <v>111.2242</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>72.37912799999999</v>
+        <v>72.37913500000001</v>
       </c>
       <c r="H592" t="n">
         <v>112.3032</v>
@@ -23065,7 +23065,7 @@
         <v>73.30956999999999</v>
       </c>
       <c r="H596" t="n">
-        <v>113.7469</v>
+        <v>113.7468</v>
       </c>
     </row>
     <row r="597">
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>73.86784400000001</v>
+        <v>73.867851</v>
       </c>
       <c r="H602" t="n">
         <v>114.6131</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H603" t="n">
         <v>115.5857</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H604" t="n">
         <v>115.5857</v>
@@ -23442,10 +23442,10 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>74.524063</v>
+        <v>74.524055</v>
       </c>
       <c r="H606" t="n">
-        <v>115.6313</v>
+        <v>115.6312</v>
       </c>
     </row>
     <row r="607">
@@ -23521,7 +23521,7 @@
         <v>75.141098</v>
       </c>
       <c r="H608" t="n">
-        <v>116.5887</v>
+        <v>116.5886</v>
       </c>
     </row>
     <row r="609">
@@ -23673,7 +23673,7 @@
         <v>73.35855100000001</v>
       </c>
       <c r="H612" t="n">
-        <v>113.8229</v>
+        <v>113.8228</v>
       </c>
     </row>
     <row r="613">
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H614" t="n">
         <v>113.4429</v>
@@ -23825,7 +23825,7 @@
         <v>73.084312</v>
       </c>
       <c r="H616" t="n">
-        <v>113.3974</v>
+        <v>113.3973</v>
       </c>
     </row>
     <row r="617">
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>72.721924</v>
+        <v>72.721931</v>
       </c>
       <c r="H617" t="n">
         <v>112.8351</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H618" t="n">
         <v>112.3944</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>72.55542800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H619" t="n">
         <v>112.5767</v>
@@ -23977,7 +23977,7 @@
         <v>72.780693</v>
       </c>
       <c r="H620" t="n">
-        <v>112.9263</v>
+        <v>112.9262</v>
       </c>
     </row>
     <row r="621">
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H621" t="n">
         <v>113.4429</v>
@@ -24243,7 +24243,7 @@
         <v>72.153915</v>
       </c>
       <c r="H627" t="n">
-        <v>111.9538</v>
+        <v>111.9537</v>
       </c>
     </row>
     <row r="628">
@@ -24281,7 +24281,7 @@
         <v>71.779854</v>
       </c>
       <c r="H628" t="n">
-        <v>111.3734</v>
+        <v>111.3733</v>
       </c>
     </row>
     <row r="629">
@@ -24889,7 +24889,7 @@
         <v>73.886391</v>
       </c>
       <c r="H644" t="n">
-        <v>114.6419</v>
+        <v>114.6418</v>
       </c>
     </row>
     <row r="645">
@@ -25003,7 +25003,7 @@
         <v>73.591087</v>
       </c>
       <c r="H647" t="n">
-        <v>114.1837</v>
+        <v>114.1836</v>
       </c>
     </row>
     <row r="648">
@@ -25991,7 +25991,7 @@
         <v>76.770584</v>
       </c>
       <c r="H673" t="n">
-        <v>119.117</v>
+        <v>119.1169</v>
       </c>
     </row>
     <row r="674">
@@ -26181,7 +26181,7 @@
         <v>76.140587</v>
       </c>
       <c r="H678" t="n">
-        <v>118.1395</v>
+        <v>118.1394</v>
       </c>
     </row>
     <row r="679">
@@ -26561,7 +26561,7 @@
         <v>78.182869</v>
       </c>
       <c r="H688" t="n">
-        <v>121.3083</v>
+        <v>121.3082</v>
       </c>
     </row>
     <row r="689">
@@ -26865,7 +26865,7 @@
         <v>79.42591899999999</v>
       </c>
       <c r="H696" t="n">
-        <v>123.237</v>
+        <v>123.2369</v>
       </c>
     </row>
     <row r="697">
@@ -26903,7 +26903,7 @@
         <v>79.52536000000001</v>
       </c>
       <c r="H697" t="n">
-        <v>123.3913</v>
+        <v>123.3912</v>
       </c>
     </row>
     <row r="698">
@@ -27093,7 +27093,7 @@
         <v>79.52536000000001</v>
       </c>
       <c r="H702" t="n">
-        <v>123.3913</v>
+        <v>123.3912</v>
       </c>
     </row>
     <row r="703">
@@ -27207,7 +27207,7 @@
         <v>79.624802</v>
       </c>
       <c r="H705" t="n">
-        <v>123.5456</v>
+        <v>123.5455</v>
       </c>
     </row>
     <row r="706">
@@ -28043,7 +28043,7 @@
         <v>81.166191</v>
       </c>
       <c r="H727" t="n">
-        <v>125.9372</v>
+        <v>125.9371</v>
       </c>
     </row>
     <row r="728">
@@ -28347,7 +28347,7 @@
         <v>80.798241</v>
       </c>
       <c r="H735" t="n">
-        <v>125.3663</v>
+        <v>125.3662</v>
       </c>
     </row>
     <row r="736">
@@ -28613,7 +28613,7 @@
         <v>81.36507400000001</v>
       </c>
       <c r="H742" t="n">
-        <v>126.2458</v>
+        <v>126.2457</v>
       </c>
     </row>
     <row r="743">
@@ -28841,7 +28841,7 @@
         <v>80.46013600000001</v>
       </c>
       <c r="H748" t="n">
-        <v>124.8417</v>
+        <v>124.8416</v>
       </c>
     </row>
     <row r="749">
@@ -28993,7 +28993,7 @@
         <v>80.910004</v>
       </c>
       <c r="H752" t="n">
-        <v>125.5397</v>
+        <v>125.5396</v>
       </c>
     </row>
     <row r="753">
@@ -29075,7 +29075,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.540001</v>
+        <v>80.239998</v>
       </c>
       <c r="H755" t="n">
-        <v>124.9656</v>
+        <v>124.5001</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>128.919998</v>
+        <v>128.380005</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.5198</v>
+        <v>120.015</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>128.919998</v>
+        <v>128.380005</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.5198</v>
+        <v>120.015</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>128.919998</v>
+        <v>128.380005</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.5198</v>
+        <v>120.015</v>
       </c>
     </row>
     <row r="1509">
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1513" t="n">
         <v>102.6794</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.740784</v>
+        <v>54.74078</v>
       </c>
       <c r="H1521" t="n">
         <v>103.1382</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.536232</v>
+        <v>54.536236</v>
       </c>
       <c r="H1522" t="n">
         <v>102.7528</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.818703</v>
+        <v>54.818699</v>
       </c>
       <c r="H1523" t="n">
         <v>103.285</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1524" t="n">
         <v>104.1108</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1525" t="n">
         <v>103.0281</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1526" t="n">
         <v>104.1108</v>
@@ -58478,10 +58478,10 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1528" t="n">
-        <v>104.1476</v>
+        <v>104.1475</v>
       </c>
     </row>
     <row r="1529">
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.588192</v>
+        <v>55.588196</v>
       </c>
       <c r="H1532" t="n">
         <v>104.7348</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1533" t="n">
         <v>104.6247</v>
@@ -58820,10 +58820,10 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1537" t="n">
-        <v>104.1476</v>
+        <v>104.1475</v>
       </c>
     </row>
     <row r="1538">
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>54.867409</v>
+        <v>54.867413</v>
       </c>
       <c r="H1538" t="n">
         <v>103.3768</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1540" t="n">
         <v>104.3494</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>56.523262</v>
+        <v>56.523266</v>
       </c>
       <c r="H1542" t="n">
         <v>106.4966</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1543" t="n">
         <v>105.7809</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.607674</v>
+        <v>55.60767</v>
       </c>
       <c r="H1544" t="n">
         <v>104.7715</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1546" t="n">
         <v>102.3858</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.351166</v>
+        <v>54.35117</v>
       </c>
       <c r="H1549" t="n">
         <v>102.4041</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1550" t="n">
         <v>102.5326</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1552" t="n">
         <v>104.6247</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.841446</v>
+        <v>55.841442</v>
       </c>
       <c r="H1561" t="n">
         <v>105.212</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1565" t="n">
         <v>106.0663</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1566" t="n">
         <v>105.6243</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1567" t="n">
         <v>105.4954</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.558754</v>
+        <v>56.558758</v>
       </c>
       <c r="H1568" t="n">
         <v>106.5635</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1569" t="n">
         <v>106.987</v>
@@ -60074,10 +60074,10 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.676044</v>
+        <v>56.676041</v>
       </c>
       <c r="H1570" t="n">
-        <v>106.7845</v>
+        <v>106.7844</v>
       </c>
     </row>
     <row r="1571">
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>57.692471</v>
+        <v>57.692474</v>
       </c>
       <c r="H1574" t="n">
         <v>108.6995</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1575" t="n">
         <v>109.6755</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>59.129166</v>
+        <v>59.129162</v>
       </c>
       <c r="H1580" t="n">
         <v>111.4064</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>58.259331</v>
+        <v>58.259335</v>
       </c>
       <c r="H1587" t="n">
         <v>109.7676</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.953247</v>
+        <v>58.953243</v>
       </c>
       <c r="H1590" t="n">
         <v>111.075</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>60.11628</v>
+        <v>60.116283</v>
       </c>
       <c r="H1601" t="n">
         <v>113.2663</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1603" t="n">
         <v>112.9164</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.956795</v>
+        <v>60.956791</v>
       </c>
       <c r="H1607" t="n">
         <v>114.8499</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1610" t="n">
         <v>114.6842</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>61.474785</v>
+        <v>61.474789</v>
       </c>
       <c r="H1612" t="n">
         <v>115.8259</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>61.445465</v>
+        <v>61.445469</v>
       </c>
       <c r="H1614" t="n">
         <v>115.7706</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1619" t="n">
         <v>109.3809</v>
@@ -62202,7 +62202,7 @@
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1626" t="n">
         <v>110.0892</v>
@@ -62924,7 +62924,7 @@
         </is>
       </c>
       <c r="G1645" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1645" t="n">
         <v>113.338</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1647" t="n">
         <v>115.0916</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1649" t="n">
         <v>113.1903</v>
@@ -63152,7 +63152,7 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1651" t="n">
         <v>112.9504</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1652" t="n">
         <v>112.3412</v>
@@ -63304,10 +63304,10 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1655" t="n">
-        <v>111.0676</v>
+        <v>111.0675</v>
       </c>
     </row>
     <row r="1656">
@@ -63418,7 +63418,7 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1658" t="n">
         <v>112.5443</v>
@@ -63456,7 +63456,7 @@
         </is>
       </c>
       <c r="G1659" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1659" t="n">
         <v>115.0362</v>
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1661" t="n">
         <v>113.1534</v>
@@ -63608,7 +63608,7 @@
         </is>
       </c>
       <c r="G1663" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1663" t="n">
         <v>112.1197</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1673" t="n">
         <v>116.5868</v>
@@ -64064,7 +64064,7 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1675" t="n">
         <v>116.0884</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1678" t="n">
         <v>116.2176</v>
@@ -64254,7 +64254,7 @@
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1680" t="n">
         <v>116.0884</v>
@@ -64292,7 +64292,7 @@
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1681" t="n">
         <v>115.6269</v>
@@ -64444,7 +64444,7 @@
         </is>
       </c>
       <c r="G1685" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1685" t="n">
         <v>115.4792</v>
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.23</v>
+        <v>62.98</v>
       </c>
       <c r="H1760" t="n">
-        <v>119.1329</v>
+        <v>118.6619</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.205002</v>
+        <v>34.555</v>
       </c>
       <c r="H253" t="n">
-        <v>113.2616</v>
+        <v>114.4205</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.049999</v>
+        <v>48.130001</v>
       </c>
       <c r="H504" t="n">
-        <v>130.6772</v>
+        <v>130.8948</v>
       </c>
     </row>
     <row r="505">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.44000200000001</v>
+        <v>80.349998</v>
       </c>
       <c r="H755" t="n">
-        <v>124.3781</v>
+        <v>124.239</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>128.619995</v>
+        <v>128.570007</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.7914</v>
+        <v>119.7448</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>128.619995</v>
+        <v>128.570007</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.7914</v>
+        <v>119.7448</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>128.619995</v>
+        <v>128.570007</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.7914</v>
+        <v>119.7448</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.844669</v>
+        <v>53.844673</v>
       </c>
       <c r="H1510" t="n">
         <v>100.4178</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>55.06221</v>
+        <v>55.062214</v>
       </c>
       <c r="H1513" t="n">
         <v>102.6885</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>55.042736</v>
+        <v>55.042732</v>
       </c>
       <c r="H1514" t="n">
         <v>102.6521</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.974548</v>
+        <v>54.974552</v>
       </c>
       <c r="H1515" t="n">
         <v>102.525</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.403133</v>
+        <v>55.40313</v>
       </c>
       <c r="H1516" t="n">
         <v>103.3243</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.429092</v>
+        <v>54.429089</v>
       </c>
       <c r="H1518" t="n">
         <v>101.5077</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.403133</v>
+        <v>55.40313</v>
       </c>
       <c r="H1525" t="n">
         <v>103.3243</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.75378</v>
+        <v>55.753784</v>
       </c>
       <c r="H1528" t="n">
         <v>103.9782</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.636898</v>
+        <v>55.636894</v>
       </c>
       <c r="H1529" t="n">
         <v>103.7602</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.588192</v>
+        <v>55.588188</v>
       </c>
       <c r="H1530" t="n">
         <v>103.6694</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1551" t="n">
         <v>103.6331</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.75378</v>
+        <v>55.753784</v>
       </c>
       <c r="H1552" t="n">
         <v>103.9782</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1553" t="n">
         <v>103.6331</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.636898</v>
+        <v>55.636894</v>
       </c>
       <c r="H1554" t="n">
         <v>103.7602</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.72456</v>
+        <v>55.724556</v>
       </c>
       <c r="H1555" t="n">
         <v>103.9237</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.958332</v>
+        <v>55.958328</v>
       </c>
       <c r="H1556" t="n">
         <v>104.3597</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1559" t="n">
         <v>104.1417</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.299999</v>
+        <v>63.200001</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.0516</v>
+        <v>117.8651</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>64.67375199999999</v>
+        <v>64.673744</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.160667</v>
+        <v>65.160675</v>
       </c>
       <c r="H508" t="n">
         <v>100.7529</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>65.511253</v>
+        <v>65.511246</v>
       </c>
       <c r="H509" t="n">
         <v>101.295</v>
@@ -19908,10 +19908,10 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H513" t="n">
-        <v>101.9123</v>
+        <v>101.9124</v>
       </c>
     </row>
     <row r="514">
@@ -19949,7 +19949,7 @@
         <v>64.868515</v>
       </c>
       <c r="H514" t="n">
-        <v>100.3011</v>
+        <v>100.3012</v>
       </c>
     </row>
     <row r="515">
@@ -20063,7 +20063,7 @@
         <v>65.540474</v>
       </c>
       <c r="H517" t="n">
-        <v>101.3401</v>
+        <v>101.3402</v>
       </c>
     </row>
     <row r="518">
@@ -20177,7 +20177,7 @@
         <v>65.84236900000001</v>
       </c>
       <c r="H520" t="n">
-        <v>101.8069</v>
+        <v>101.807</v>
       </c>
     </row>
     <row r="521">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H528" t="n">
         <v>102.1985</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H530" t="n">
         <v>102.1985</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>65.988457</v>
+        <v>65.988449</v>
       </c>
       <c r="H532" t="n">
         <v>102.0328</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>65.57942199999999</v>
+        <v>65.579414</v>
       </c>
       <c r="H533" t="n">
         <v>101.4004</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H536" t="n">
         <v>104.4722</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H537" t="n">
         <v>103.6892</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H538" t="n">
         <v>103.2525</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>65.715767</v>
+        <v>65.71577499999999</v>
       </c>
       <c r="H541" t="n">
         <v>101.6112</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.027412</v>
+        <v>66.027405</v>
       </c>
       <c r="H542" t="n">
         <v>102.0931</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H543" t="n">
         <v>101.8822</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.124786</v>
+        <v>66.124779</v>
       </c>
       <c r="H544" t="n">
         <v>102.2436</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H546" t="n">
         <v>103.5988</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H549" t="n">
         <v>103.6892</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.371323</v>
+        <v>67.371315</v>
       </c>
       <c r="H552" t="n">
         <v>104.171</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H553" t="n">
         <v>104.3969</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.22525</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H556" t="n">
         <v>103.9452</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H557" t="n">
         <v>104.3367</v>
@@ -21621,7 +21621,7 @@
         <v>67.390793</v>
       </c>
       <c r="H558" t="n">
-        <v>104.2011</v>
+        <v>104.2012</v>
       </c>
     </row>
     <row r="559">
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.23498499999999</v>
+        <v>67.234978</v>
       </c>
       <c r="H561" t="n">
         <v>103.9602</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.619148</v>
+        <v>67.619141</v>
       </c>
       <c r="H562" t="n">
         <v>104.5542</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.81502500000001</v>
+        <v>67.815033</v>
       </c>
       <c r="H564" t="n">
         <v>104.8571</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275352</v>
       </c>
       <c r="H566" t="n">
         <v>105.5689</v>
@@ -22039,7 +22039,7 @@
         <v>69.24498699999999</v>
       </c>
       <c r="H569" t="n">
-        <v>107.0681</v>
+        <v>107.0682</v>
       </c>
     </row>
     <row r="570">
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>69.773865</v>
+        <v>69.773872</v>
       </c>
       <c r="H570" t="n">
         <v>107.8859</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>69.480057</v>
+        <v>69.48004899999999</v>
       </c>
       <c r="H571" t="n">
         <v>107.4316</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H572" t="n">
         <v>107.7648</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>70.18523399999999</v>
+        <v>70.185226</v>
       </c>
       <c r="H574" t="n">
         <v>108.522</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>70.273369</v>
+        <v>70.273376</v>
       </c>
       <c r="H575" t="n">
         <v>108.6583</v>
@@ -22302,10 +22302,10 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.645554</v>
+        <v>70.645561</v>
       </c>
       <c r="H576" t="n">
-        <v>109.2337</v>
+        <v>109.2338</v>
       </c>
     </row>
     <row r="577">
@@ -22381,7 +22381,7 @@
         <v>71.291977</v>
       </c>
       <c r="H578" t="n">
-        <v>110.2332</v>
+        <v>110.2333</v>
       </c>
     </row>
     <row r="579">
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.72391500000001</v>
+        <v>70.723907</v>
       </c>
       <c r="H579" t="n">
         <v>109.3549</v>
@@ -22454,10 +22454,10 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H580" t="n">
-        <v>108.3402</v>
+        <v>108.3403</v>
       </c>
     </row>
     <row r="581">
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>70.371323</v>
+        <v>70.371315</v>
       </c>
       <c r="H581" t="n">
         <v>108.8097</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.51823400000001</v>
+        <v>70.518227</v>
       </c>
       <c r="H583" t="n">
         <v>109.0369</v>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.410492</v>
+        <v>70.410484</v>
       </c>
       <c r="H585" t="n">
         <v>108.8703</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.890411</v>
+        <v>70.890404</v>
       </c>
       <c r="H588" t="n">
         <v>109.6123</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H589" t="n">
         <v>110.839</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>72.37912799999999</v>
+        <v>72.37913500000001</v>
       </c>
       <c r="H590" t="n">
         <v>111.9142</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H591" t="n">
         <v>112.6866</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.201843</v>
+        <v>73.201836</v>
       </c>
       <c r="H593" t="n">
         <v>113.1863</v>
@@ -23027,7 +23027,7 @@
         <v>73.564224</v>
       </c>
       <c r="H595" t="n">
-        <v>113.7466</v>
+        <v>113.7467</v>
       </c>
     </row>
     <row r="596">
@@ -23065,7 +23065,7 @@
         <v>74.12249</v>
       </c>
       <c r="H596" t="n">
-        <v>114.6098</v>
+        <v>114.6099</v>
       </c>
     </row>
     <row r="597">
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.82867400000001</v>
+        <v>73.828667</v>
       </c>
       <c r="H598" t="n">
         <v>114.1555</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.86784400000001</v>
+        <v>73.867851</v>
       </c>
       <c r="H600" t="n">
         <v>114.2161</v>
@@ -23442,10 +23442,10 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>75.14109000000001</v>
+        <v>75.141098</v>
       </c>
       <c r="H606" t="n">
-        <v>116.1848</v>
+        <v>116.1849</v>
       </c>
     </row>
     <row r="607">
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>75.27821400000001</v>
+        <v>75.278206</v>
       </c>
       <c r="H607" t="n">
         <v>116.3969</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>75.003975</v>
+        <v>75.00398300000001</v>
       </c>
       <c r="H609" t="n">
         <v>115.9728</v>
@@ -23670,10 +23670,10 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H612" t="n">
-        <v>113.05</v>
+        <v>113.0501</v>
       </c>
     </row>
     <row r="613">
@@ -23711,7 +23711,7 @@
         <v>72.026535</v>
       </c>
       <c r="H613" t="n">
-        <v>111.369</v>
+        <v>111.3691</v>
       </c>
     </row>
     <row r="614">
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>72.72191599999999</v>
+        <v>72.721931</v>
       </c>
       <c r="H615" t="n">
         <v>112.4443</v>
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H616" t="n">
         <v>112.0051</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>72.55542800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H617" t="n">
         <v>112.1868</v>
@@ -23936,10 +23936,10 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H619" t="n">
-        <v>113.05</v>
+        <v>113.0501</v>
       </c>
     </row>
     <row r="620">
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.643562</v>
+        <v>72.64357</v>
       </c>
       <c r="H620" t="n">
         <v>112.3231</v>
@@ -24129,7 +24129,7 @@
         <v>71.4058</v>
       </c>
       <c r="H624" t="n">
-        <v>110.4092</v>
+        <v>110.4093</v>
       </c>
     </row>
     <row r="625">
@@ -24243,7 +24243,7 @@
         <v>71.4058</v>
       </c>
       <c r="H627" t="n">
-        <v>110.4092</v>
+        <v>110.4093</v>
       </c>
     </row>
     <row r="628">
@@ -24319,7 +24319,7 @@
         <v>71.986572</v>
       </c>
       <c r="H629" t="n">
-        <v>111.3072</v>
+        <v>111.3073</v>
       </c>
     </row>
     <row r="630">
@@ -24699,7 +24699,7 @@
         <v>73.807655</v>
       </c>
       <c r="H639" t="n">
-        <v>114.123</v>
+        <v>114.1231</v>
       </c>
     </row>
     <row r="640">
@@ -24889,7 +24889,7 @@
         <v>74.004524</v>
       </c>
       <c r="H644" t="n">
-        <v>114.4274</v>
+        <v>114.4275</v>
       </c>
     </row>
     <row r="645">
@@ -25231,7 +25231,7 @@
         <v>74.634506</v>
       </c>
       <c r="H653" t="n">
-        <v>115.4015</v>
+        <v>115.4016</v>
       </c>
     </row>
     <row r="654">
@@ -25307,7 +25307,7 @@
         <v>74.634506</v>
       </c>
       <c r="H655" t="n">
-        <v>115.4015</v>
+        <v>115.4016</v>
       </c>
     </row>
     <row r="656">
@@ -26295,7 +26295,7 @@
         <v>78.00103799999999</v>
       </c>
       <c r="H681" t="n">
-        <v>120.6069</v>
+        <v>120.607</v>
       </c>
     </row>
     <row r="682">
@@ -26409,7 +26409,7 @@
         <v>77.914368</v>
       </c>
       <c r="H684" t="n">
-        <v>120.4729</v>
+        <v>120.473</v>
       </c>
     </row>
     <row r="685">
@@ -26447,7 +26447,7 @@
         <v>78.540863</v>
       </c>
       <c r="H685" t="n">
-        <v>121.4416</v>
+        <v>121.4417</v>
       </c>
     </row>
     <row r="686">
@@ -26637,7 +26637,7 @@
         <v>78.033699</v>
       </c>
       <c r="H690" t="n">
-        <v>120.6574</v>
+        <v>120.6575</v>
       </c>
     </row>
     <row r="691">
@@ -26713,7 +26713,7 @@
         <v>78.451363</v>
       </c>
       <c r="H692" t="n">
-        <v>121.3032</v>
+        <v>121.3033</v>
       </c>
     </row>
     <row r="693">
@@ -27131,7 +27131,7 @@
         <v>79.624802</v>
       </c>
       <c r="H703" t="n">
-        <v>123.1176</v>
+        <v>123.1177</v>
       </c>
     </row>
     <row r="704">
@@ -27169,7 +27169,7 @@
         <v>79.465698</v>
       </c>
       <c r="H704" t="n">
-        <v>122.8716</v>
+        <v>122.8717</v>
       </c>
     </row>
     <row r="705">
@@ -27739,7 +27739,7 @@
         <v>81.00707199999999</v>
       </c>
       <c r="H719" t="n">
-        <v>125.2549</v>
+        <v>125.255</v>
       </c>
     </row>
     <row r="720">
@@ -27777,7 +27777,7 @@
         <v>81.176125</v>
       </c>
       <c r="H720" t="n">
-        <v>125.5163</v>
+        <v>125.5164</v>
       </c>
     </row>
     <row r="721">
@@ -28005,7 +28005,7 @@
         <v>80.84796900000001</v>
       </c>
       <c r="H726" t="n">
-        <v>125.0089</v>
+        <v>125.009</v>
       </c>
     </row>
     <row r="727">
@@ -28119,7 +28119,7 @@
         <v>80.758461</v>
       </c>
       <c r="H729" t="n">
-        <v>124.8705</v>
+        <v>124.8706</v>
       </c>
     </row>
     <row r="730">
@@ -28157,7 +28157,7 @@
         <v>80.758461</v>
       </c>
       <c r="H730" t="n">
-        <v>124.8705</v>
+        <v>124.8706</v>
       </c>
     </row>
     <row r="731">
@@ -28271,7 +28271,7 @@
         <v>80.798241</v>
       </c>
       <c r="H733" t="n">
-        <v>124.932</v>
+        <v>124.9321</v>
       </c>
     </row>
     <row r="734">
@@ -28309,7 +28309,7 @@
         <v>81.21590399999999</v>
       </c>
       <c r="H734" t="n">
-        <v>125.5778</v>
+        <v>125.5779</v>
       </c>
     </row>
     <row r="735">
@@ -28613,7 +28613,7 @@
         <v>80.589409</v>
       </c>
       <c r="H742" t="n">
-        <v>124.6091</v>
+        <v>124.6092</v>
       </c>
     </row>
     <row r="743">
@@ -28841,7 +28841,7 @@
         <v>81.06999999999999</v>
       </c>
       <c r="H748" t="n">
-        <v>125.3522</v>
+        <v>125.3523</v>
       </c>
     </row>
     <row r="749">
@@ -29069,7 +29069,7 @@
         <v>80.540001</v>
       </c>
       <c r="H754" t="n">
-        <v>124.5327</v>
+        <v>124.5328</v>
       </c>
     </row>
     <row r="755">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.62064</v>
+        <v>53.620636</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.497276</v>
+        <v>54.497272</v>
       </c>
       <c r="H1511" t="n">
         <v>101.6349</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>55.062214</v>
+        <v>55.062218</v>
       </c>
       <c r="H1513" t="n">
         <v>102.6885</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.974552</v>
+        <v>54.974556</v>
       </c>
       <c r="H1515" t="n">
         <v>102.525</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1516" t="n">
         <v>103.3243</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.159618</v>
+        <v>55.159615</v>
       </c>
       <c r="H1517" t="n">
         <v>102.8701</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.429089</v>
+        <v>54.429092</v>
       </c>
       <c r="H1518" t="n">
         <v>101.5077</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.740784</v>
+        <v>54.740788</v>
       </c>
       <c r="H1519" t="n">
         <v>102.089</v>
@@ -58177,7 +58177,7 @@
         <v>54.536236</v>
       </c>
       <c r="H1520" t="n">
-        <v>101.7075</v>
+        <v>101.7076</v>
       </c>
     </row>
     <row r="1521">
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1522" t="n">
         <v>103.0518</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1524" t="n">
         <v>103.0518</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1525" t="n">
         <v>103.3243</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.753784</v>
+        <v>55.75378</v>
       </c>
       <c r="H1528" t="n">
         <v>103.9782</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1531" t="n">
         <v>103.5604</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.325203</v>
+        <v>55.325207</v>
       </c>
       <c r="H1533" t="n">
         <v>103.1789</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>54.867409</v>
+        <v>54.867413</v>
       </c>
       <c r="H1536" t="n">
         <v>102.3252</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.351166</v>
+        <v>54.351162</v>
       </c>
       <c r="H1547" t="n">
         <v>101.3624</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1548" t="n">
         <v>101.4896</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1550" t="n">
         <v>103.5604</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.753784</v>
+        <v>55.75378</v>
       </c>
       <c r="H1552" t="n">
         <v>103.9782</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.841446</v>
+        <v>55.841442</v>
       </c>
       <c r="H1559" t="n">
         <v>104.1417</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1562" t="n">
         <v>104.1599</v>
@@ -60647,7 +60647,7 @@
         <v>58.259331</v>
       </c>
       <c r="H1585" t="n">
-        <v>108.6509</v>
+        <v>108.651</v>
       </c>
     </row>
     <row r="1586">
@@ -60837,7 +60837,7 @@
         <v>58.835968</v>
       </c>
       <c r="H1590" t="n">
-        <v>109.7263</v>
+        <v>109.7264</v>
       </c>
     </row>
     <row r="1591">
@@ -61103,7 +61103,7 @@
         <v>59.744892</v>
       </c>
       <c r="H1597" t="n">
-        <v>111.4214</v>
+        <v>111.4215</v>
       </c>
     </row>
     <row r="1598">
@@ -61521,7 +61521,7 @@
         <v>60.868835</v>
       </c>
       <c r="H1608" t="n">
-        <v>113.5175</v>
+        <v>113.5176</v>
       </c>
     </row>
     <row r="1609">
@@ -61559,7 +61559,7 @@
         <v>61.015434</v>
       </c>
       <c r="H1609" t="n">
-        <v>113.7909</v>
+        <v>113.791</v>
       </c>
     </row>
     <row r="1610">
@@ -62547,7 +62547,7 @@
         <v>58.155739</v>
       </c>
       <c r="H1635" t="n">
-        <v>108.4577</v>
+        <v>108.4578</v>
       </c>
     </row>
     <row r="1636">
@@ -63573,7 +63573,7 @@
         <v>60.026989</v>
       </c>
       <c r="H1662" t="n">
-        <v>111.9475</v>
+        <v>111.9476</v>
       </c>
     </row>
     <row r="1663">
@@ -63687,7 +63687,7 @@
         <v>60.026989</v>
       </c>
       <c r="H1665" t="n">
-        <v>111.9475</v>
+        <v>111.9476</v>
       </c>
     </row>
     <row r="1666">
@@ -63877,7 +63877,7 @@
         <v>62.642818</v>
       </c>
       <c r="H1670" t="n">
-        <v>116.8259</v>
+        <v>116.826</v>
       </c>
     </row>
     <row r="1671">
@@ -64599,7 +64599,7 @@
         <v>62.628075</v>
       </c>
       <c r="H1689" t="n">
-        <v>116.7984</v>
+        <v>116.7985</v>
       </c>
     </row>
     <row r="1690">
@@ -64713,7 +64713,7 @@
         <v>62.707325</v>
       </c>
       <c r="H1692" t="n">
-        <v>116.9462</v>
+        <v>116.9463</v>
       </c>
     </row>
     <row r="1693">
@@ -64903,7 +64903,7 @@
         <v>63.143208</v>
       </c>
       <c r="H1697" t="n">
-        <v>117.7591</v>
+        <v>117.7592</v>
       </c>
     </row>
     <row r="1698">
@@ -64941,7 +64941,7 @@
         <v>64.054596</v>
       </c>
       <c r="H1698" t="n">
-        <v>119.4588</v>
+        <v>119.4589</v>
       </c>
     </row>
     <row r="1699">
@@ -65017,7 +65017,7 @@
         <v>64.252724</v>
       </c>
       <c r="H1700" t="n">
-        <v>119.8283</v>
+        <v>119.8284</v>
       </c>
     </row>
     <row r="1701">
@@ -65397,7 +65397,7 @@
         <v>63.143208</v>
       </c>
       <c r="H1710" t="n">
-        <v>117.7591</v>
+        <v>117.7592</v>
       </c>
     </row>
     <row r="1711">
@@ -65511,7 +65511,7 @@
         <v>63.10358</v>
       </c>
       <c r="H1713" t="n">
-        <v>117.6852</v>
+        <v>117.6853</v>
       </c>
     </row>
     <row r="1714">
@@ -66081,7 +66081,7 @@
         <v>65.312698</v>
       </c>
       <c r="H1728" t="n">
-        <v>121.8051</v>
+        <v>121.8052</v>
       </c>
     </row>
     <row r="1729">
@@ -66879,7 +66879,7 @@
         <v>63.262085</v>
       </c>
       <c r="H1749" t="n">
-        <v>117.9808</v>
+        <v>117.9809</v>
       </c>
     </row>
     <row r="1750">
@@ -66917,7 +66917,7 @@
         <v>62.984707</v>
       </c>
       <c r="H1750" t="n">
-        <v>117.4635</v>
+        <v>117.4636</v>
       </c>
     </row>
     <row r="1751">
@@ -67145,7 +67145,7 @@
         <v>63.580002</v>
       </c>
       <c r="H1756" t="n">
-        <v>118.5737</v>
+        <v>118.5738</v>
       </c>
     </row>
     <row r="1757">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H508" t="n">
         <v>100.7529</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>65.511246</v>
+        <v>65.511253</v>
       </c>
       <c r="H509" t="n">
         <v>101.295</v>
@@ -19946,10 +19946,10 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H514" t="n">
-        <v>100.3012</v>
+        <v>100.3011</v>
       </c>
     </row>
     <row r="515">
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H519" t="n">
         <v>100.6927</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H522" t="n">
         <v>101.9575</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.06635300000001</v>
+        <v>66.066345</v>
       </c>
       <c r="H523" t="n">
         <v>102.1533</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H524" t="n">
         <v>102.6803</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.339035</v>
+        <v>66.339043</v>
       </c>
       <c r="H525" t="n">
         <v>102.5749</v>
@@ -20402,10 +20402,10 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H526" t="n">
-        <v>102.3791</v>
+        <v>102.3792</v>
       </c>
     </row>
     <row r="527">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H527" t="n">
         <v>102.6803</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.095581</v>
+        <v>66.095573</v>
       </c>
       <c r="H528" t="n">
         <v>102.1985</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H529" t="n">
         <v>102.1382</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.095581</v>
+        <v>66.095573</v>
       </c>
       <c r="H530" t="n">
         <v>102.1985</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H531" t="n">
         <v>102.4996</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>65.988449</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H532" t="n">
         <v>102.0328</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>65.579414</v>
+        <v>65.57942199999999</v>
       </c>
       <c r="H533" t="n">
         <v>101.4004</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H537" t="n">
         <v>103.6892</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H538" t="n">
         <v>103.2525</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>65.754715</v>
+        <v>65.754723</v>
       </c>
       <c r="H540" t="n">
         <v>101.6714</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>65.71577499999999</v>
+        <v>65.715767</v>
       </c>
       <c r="H541" t="n">
         <v>101.6112</v>
@@ -21010,10 +21010,10 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H542" t="n">
-        <v>102.0931</v>
+        <v>102.093</v>
       </c>
     </row>
     <row r="543">
@@ -21048,10 +21048,10 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>65.89106</v>
+        <v>65.891068</v>
       </c>
       <c r="H543" t="n">
-        <v>101.8822</v>
+        <v>101.8823</v>
       </c>
     </row>
     <row r="544">
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.124779</v>
+        <v>66.124786</v>
       </c>
       <c r="H544" t="n">
         <v>102.2436</v>
@@ -21162,10 +21162,10 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H546" t="n">
-        <v>103.5988</v>
+        <v>103.5989</v>
       </c>
     </row>
     <row r="547">
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.24472</v>
+        <v>67.24472799999999</v>
       </c>
       <c r="H548" t="n">
         <v>103.9753</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H549" t="n">
         <v>103.6892</v>
@@ -21390,10 +21390,10 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H552" t="n">
-        <v>104.171</v>
+        <v>104.1711</v>
       </c>
     </row>
     <row r="553">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H558" t="n">
         <v>104.2012</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H560" t="n">
         <v>103.8548</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H563" t="n">
         <v>104.9783</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.275352</v>
+        <v>68.275368</v>
       </c>
       <c r="H566" t="n">
         <v>105.5689</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H568" t="n">
         <v>105.9475</v>
@@ -22036,10 +22036,10 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H569" t="n">
-        <v>107.0682</v>
+        <v>107.0681</v>
       </c>
     </row>
     <row r="570">
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H570" t="n">
         <v>107.8859</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H572" t="n">
         <v>107.7648</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H574" t="n">
         <v>108.522</v>
@@ -22302,10 +22302,10 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.645561</v>
+        <v>70.645554</v>
       </c>
       <c r="H576" t="n">
-        <v>109.2338</v>
+        <v>109.2337</v>
       </c>
     </row>
     <row r="577">
@@ -22378,10 +22378,10 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H578" t="n">
-        <v>110.2333</v>
+        <v>110.2332</v>
       </c>
     </row>
     <row r="579">
@@ -22454,10 +22454,10 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H580" t="n">
-        <v>108.3403</v>
+        <v>108.3402</v>
       </c>
     </row>
     <row r="581">
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H581" t="n">
         <v>108.8097</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H582" t="n">
         <v>109.5821</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.518227</v>
+        <v>70.51823400000001</v>
       </c>
       <c r="H583" t="n">
         <v>109.0369</v>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.410484</v>
+        <v>70.4105</v>
       </c>
       <c r="H585" t="n">
         <v>108.8703</v>
@@ -22758,10 +22758,10 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>70.890404</v>
+        <v>70.890411</v>
       </c>
       <c r="H588" t="n">
-        <v>109.6123</v>
+        <v>109.6124</v>
       </c>
     </row>
     <row r="589">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>72.37913500000001</v>
+        <v>72.37912799999999</v>
       </c>
       <c r="H590" t="n">
         <v>111.9142</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H592" t="n">
         <v>111.8688</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H594" t="n">
         <v>113.3529</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H595" t="n">
         <v>113.7467</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H596" t="n">
         <v>114.6099</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H597" t="n">
         <v>114.1707</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H600" t="n">
         <v>114.2161</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H605" t="n">
         <v>115.5488</v>
@@ -23442,10 +23442,10 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>75.141098</v>
+        <v>75.14109000000001</v>
       </c>
       <c r="H606" t="n">
-        <v>116.1849</v>
+        <v>116.1848</v>
       </c>
     </row>
     <row r="607">
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>75.278206</v>
+        <v>75.27821400000001</v>
       </c>
       <c r="H607" t="n">
         <v>116.3969</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>75.00398300000001</v>
+        <v>75.003967</v>
       </c>
       <c r="H609" t="n">
         <v>115.9728</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H610" t="n">
         <v>113.4286</v>
@@ -23670,10 +23670,10 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>73.11370100000001</v>
+        <v>73.113693</v>
       </c>
       <c r="H612" t="n">
-        <v>113.0501</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="613">
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H617" t="n">
         <v>112.1868</v>
@@ -23936,10 +23936,10 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>73.11370100000001</v>
+        <v>73.113693</v>
       </c>
       <c r="H619" t="n">
-        <v>113.0501</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="620">
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H621" t="n">
         <v>110.5767</v>
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H622" t="n">
         <v>109.5569</v>
@@ -24126,10 +24126,10 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H624" t="n">
-        <v>110.4093</v>
+        <v>110.4092</v>
       </c>
     </row>
     <row r="625">
@@ -24240,10 +24240,10 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H627" t="n">
-        <v>110.4093</v>
+        <v>110.4092</v>
       </c>
     </row>
     <row r="628">
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H630" t="n">
         <v>112.3879</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H632" t="n">
         <v>112.0226</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H634" t="n">
         <v>114.3361</v>
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H635" t="n">
         <v>114.0774</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H637" t="n">
         <v>114.1535</v>
@@ -24696,10 +24696,10 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H639" t="n">
-        <v>114.1231</v>
+        <v>114.123</v>
       </c>
     </row>
     <row r="640">
@@ -24848,7 +24848,7 @@
         </is>
       </c>
       <c r="G643" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H643" t="n">
         <v>114.1535</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H646" t="n">
         <v>113.6969</v>
@@ -25000,7 +25000,7 @@
         </is>
       </c>
       <c r="G647" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H647" t="n">
         <v>114.0926</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H649" t="n">
         <v>115.0819</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H652" t="n">
         <v>116.1778</v>
@@ -25228,7 +25228,7 @@
         </is>
       </c>
       <c r="G653" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H653" t="n">
         <v>115.4016</v>
@@ -25304,7 +25304,7 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H655" t="n">
         <v>115.4016</v>
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H660" t="n">
         <v>116.1169</v>
@@ -25684,7 +25684,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H665" t="n">
         <v>119.2067</v>
@@ -25760,7 +25760,7 @@
         </is>
       </c>
       <c r="G667" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H667" t="n">
         <v>118.4</v>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H669" t="n">
         <v>117.9434</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H670" t="n">
         <v>117.7912</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H675" t="n">
         <v>118.4304</v>
@@ -26102,7 +26102,7 @@
         </is>
       </c>
       <c r="G676" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H676" t="n">
         <v>117.7303</v>
@@ -26330,7 +26330,7 @@
         </is>
       </c>
       <c r="G682" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H682" t="n">
         <v>121.1549</v>
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>53.620636</v>
+        <v>53.62064</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>53.844673</v>
+        <v>53.844669</v>
       </c>
       <c r="H1510" t="n">
         <v>100.4178</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>55.062218</v>
+        <v>55.06221</v>
       </c>
       <c r="H1513" t="n">
         <v>102.6885</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.974556</v>
+        <v>54.974548</v>
       </c>
       <c r="H1515" t="n">
         <v>102.525</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.159615</v>
+        <v>55.159622</v>
       </c>
       <c r="H1517" t="n">
         <v>102.8701</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.429092</v>
+        <v>54.429096</v>
       </c>
       <c r="H1518" t="n">
         <v>101.5077</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.740788</v>
+        <v>54.740784</v>
       </c>
       <c r="H1519" t="n">
         <v>102.089</v>
@@ -58177,7 +58177,7 @@
         <v>54.536236</v>
       </c>
       <c r="H1520" t="n">
-        <v>101.7076</v>
+        <v>101.7075</v>
       </c>
     </row>
     <row r="1521">
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.682343</v>
+        <v>54.682339</v>
       </c>
       <c r="H1523" t="n">
         <v>101.98</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.588188</v>
+        <v>55.588196</v>
       </c>
       <c r="H1530" t="n">
         <v>103.6694</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.325207</v>
+        <v>55.325203</v>
       </c>
       <c r="H1533" t="n">
         <v>103.1789</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>56.523262</v>
+        <v>56.523266</v>
       </c>
       <c r="H1540" t="n">
         <v>105.4133</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.607674</v>
+        <v>55.60767</v>
       </c>
       <c r="H1542" t="n">
         <v>103.7057</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1544" t="n">
         <v>101.3442</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>54.292728</v>
+        <v>54.292721</v>
       </c>
       <c r="H1545" t="n">
         <v>101.2534</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.351162</v>
+        <v>54.35117</v>
       </c>
       <c r="H1547" t="n">
         <v>101.3624</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1548" t="n">
         <v>101.4896</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>54.877148</v>
+        <v>54.877144</v>
       </c>
       <c r="H1549" t="n">
         <v>102.3433</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1551" t="n">
         <v>103.6331</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1553" t="n">
         <v>103.6331</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.987545</v>
+        <v>55.987541</v>
       </c>
       <c r="H1557" t="n">
         <v>104.4142</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.172611</v>
+        <v>56.172615</v>
       </c>
       <c r="H1561" t="n">
         <v>104.7593</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1565" t="n">
         <v>104.4223</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1567" t="n">
         <v>105.8987</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.676041</v>
+        <v>56.676037</v>
       </c>
       <c r="H1568" t="n">
         <v>105.6982</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1570" t="n">
         <v>106.245</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1573" t="n">
         <v>108.5598</v>
@@ -60264,10 +60264,10 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1575" t="n">
-        <v>109.1249</v>
+        <v>109.1248</v>
       </c>
     </row>
     <row r="1576">
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>58.396156</v>
+        <v>58.39616</v>
       </c>
       <c r="H1576" t="n">
         <v>108.9061</v>
@@ -60378,10 +60378,10 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>59.129169</v>
+        <v>59.129166</v>
       </c>
       <c r="H1578" t="n">
-        <v>110.2732</v>
+        <v>110.2731</v>
       </c>
     </row>
     <row r="1579">
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1581" t="n">
         <v>110.9475</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1582" t="n">
         <v>110.9658</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>58.259331</v>
+        <v>58.259335</v>
       </c>
       <c r="H1585" t="n">
         <v>108.651</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.914154</v>
+        <v>58.91415</v>
       </c>
       <c r="H1586" t="n">
         <v>109.8722</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1589" t="n">
         <v>110.6012</v>
@@ -60834,10 +60834,10 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.835968</v>
+        <v>58.835964</v>
       </c>
       <c r="H1590" t="n">
-        <v>109.7264</v>
+        <v>109.7263</v>
       </c>
     </row>
     <row r="1591">
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>58.718681</v>
+        <v>58.718685</v>
       </c>
       <c r="H1591" t="n">
         <v>109.5076</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.168259</v>
+        <v>59.168262</v>
       </c>
       <c r="H1592" t="n">
         <v>110.3461</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.246449</v>
+        <v>59.246445</v>
       </c>
       <c r="H1596" t="n">
         <v>110.4919</v>
@@ -61103,7 +61103,7 @@
         <v>59.744892</v>
       </c>
       <c r="H1597" t="n">
-        <v>111.4215</v>
+        <v>111.4214</v>
       </c>
     </row>
     <row r="1598">
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>60.155373</v>
+        <v>60.155376</v>
       </c>
       <c r="H1598" t="n">
         <v>112.187</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1600" t="n">
         <v>112.2781</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1601" t="n">
         <v>111.7678</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.852398</v>
+        <v>59.852402</v>
       </c>
       <c r="H1602" t="n">
         <v>111.6219</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1603" t="n">
         <v>111.786</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1604" t="n">
         <v>112.3875</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>60.956795</v>
+        <v>60.956791</v>
       </c>
       <c r="H1605" t="n">
         <v>113.6816</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>61.201126</v>
+        <v>61.20113</v>
       </c>
       <c r="H1607" t="n">
         <v>114.1373</v>
@@ -61518,10 +61518,10 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1608" t="n">
-        <v>113.5176</v>
+        <v>113.5175</v>
       </c>
     </row>
     <row r="1609">
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>61.015434</v>
+        <v>61.015438</v>
       </c>
       <c r="H1609" t="n">
         <v>113.791</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>61.474785</v>
+        <v>61.474789</v>
       </c>
       <c r="H1610" t="n">
         <v>114.6476</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.406376</v>
+        <v>61.406372</v>
       </c>
       <c r="H1611" t="n">
         <v>114.52</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>61.445465</v>
+        <v>61.445469</v>
       </c>
       <c r="H1612" t="n">
         <v>114.5929</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>58.640495</v>
+        <v>58.640491</v>
       </c>
       <c r="H1614" t="n">
         <v>109.3618</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>58.581852</v>
+        <v>58.581856</v>
       </c>
       <c r="H1616" t="n">
         <v>109.2524</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1618" t="n">
         <v>107.5209</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1619" t="n">
         <v>109.6352</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>58.112728</v>
+        <v>58.112732</v>
       </c>
       <c r="H1621" t="n">
         <v>108.3775</v>
@@ -62050,10 +62050,10 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>57.790211</v>
+        <v>57.790207</v>
       </c>
       <c r="H1622" t="n">
-        <v>107.7761</v>
+        <v>107.776</v>
       </c>
     </row>
     <row r="1623">
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1624" t="n">
         <v>108.9693</v>
@@ -62547,7 +62547,7 @@
         <v>58.155739</v>
       </c>
       <c r="H1635" t="n">
-        <v>108.4578</v>
+        <v>108.4577</v>
       </c>
     </row>
     <row r="1636">
@@ -62848,7 +62848,7 @@
         </is>
       </c>
       <c r="G1643" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1643" t="n">
         <v>112.1851</v>
@@ -62924,7 +62924,7 @@
         </is>
       </c>
       <c r="G1645" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1645" t="n">
         <v>113.9208</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1647" t="n">
         <v>112.0389</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1649" t="n">
         <v>111.8014</v>
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1650" t="n">
         <v>111.1984</v>
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1653" t="n">
         <v>109.9377</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1656" t="n">
         <v>111.3994</v>
@@ -63380,7 +63380,7 @@
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1657" t="n">
         <v>113.866</v>
@@ -63456,7 +63456,7 @@
         </is>
       </c>
       <c r="G1659" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1659" t="n">
         <v>112.0024</v>
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1661" t="n">
         <v>110.9792</v>
@@ -63573,7 +63573,7 @@
         <v>60.026989</v>
       </c>
       <c r="H1662" t="n">
-        <v>111.9476</v>
+        <v>111.9475</v>
       </c>
     </row>
     <row r="1663">
@@ -63687,7 +63687,7 @@
         <v>60.026989</v>
       </c>
       <c r="H1665" t="n">
-        <v>111.9476</v>
+        <v>111.9475</v>
       </c>
     </row>
     <row r="1666">
@@ -63877,7 +63877,7 @@
         <v>62.642818</v>
       </c>
       <c r="H1670" t="n">
-        <v>116.826</v>
+        <v>116.8259</v>
       </c>
     </row>
     <row r="1671">
@@ -63912,7 +63912,7 @@
         </is>
       </c>
       <c r="G1671" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1671" t="n">
         <v>115.4008</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1673" t="n">
         <v>114.9075</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1676" t="n">
         <v>115.0354</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1678" t="n">
         <v>114.9075</v>
@@ -64216,7 +64216,7 @@
         </is>
       </c>
       <c r="G1679" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1679" t="n">
         <v>114.4507</v>
@@ -64368,7 +64368,7 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1683" t="n">
         <v>114.3045</v>
@@ -64599,7 +64599,7 @@
         <v>62.628075</v>
       </c>
       <c r="H1689" t="n">
-        <v>116.7985</v>
+        <v>116.7984</v>
       </c>
     </row>
     <row r="1690">
@@ -64713,7 +64713,7 @@
         <v>62.707325</v>
       </c>
       <c r="H1692" t="n">
-        <v>116.9463</v>
+        <v>116.9462</v>
       </c>
     </row>
     <row r="1693">
@@ -64903,7 +64903,7 @@
         <v>63.143208</v>
       </c>
       <c r="H1697" t="n">
-        <v>117.7592</v>
+        <v>117.7591</v>
       </c>
     </row>
     <row r="1698">
@@ -64941,7 +64941,7 @@
         <v>64.054596</v>
       </c>
       <c r="H1698" t="n">
-        <v>119.4589</v>
+        <v>119.4588</v>
       </c>
     </row>
     <row r="1699">
@@ -65017,7 +65017,7 @@
         <v>64.252724</v>
       </c>
       <c r="H1700" t="n">
-        <v>119.8284</v>
+        <v>119.8283</v>
       </c>
     </row>
     <row r="1701">
@@ -65397,7 +65397,7 @@
         <v>63.143208</v>
       </c>
       <c r="H1710" t="n">
-        <v>117.7592</v>
+        <v>117.7591</v>
       </c>
     </row>
     <row r="1711">
@@ -65511,7 +65511,7 @@
         <v>63.10358</v>
       </c>
       <c r="H1713" t="n">
-        <v>117.6853</v>
+        <v>117.6852</v>
       </c>
     </row>
     <row r="1714">
@@ -66081,7 +66081,7 @@
         <v>65.312698</v>
       </c>
       <c r="H1728" t="n">
-        <v>121.8052</v>
+        <v>121.8051</v>
       </c>
     </row>
     <row r="1729">
@@ -66879,7 +66879,7 @@
         <v>63.262085</v>
       </c>
       <c r="H1749" t="n">
-        <v>117.9809</v>
+        <v>117.9808</v>
       </c>
     </row>
     <row r="1750">
@@ -66917,7 +66917,7 @@
         <v>62.984707</v>
       </c>
       <c r="H1750" t="n">
-        <v>117.4636</v>
+        <v>117.4635</v>
       </c>
     </row>
     <row r="1751">
@@ -67145,7 +67145,7 @@
         <v>63.580002</v>
       </c>
       <c r="H1756" t="n">
-        <v>118.5738</v>
+        <v>118.5737</v>
       </c>
     </row>
     <row r="1757">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.384998</v>
+        <v>34.535</v>
       </c>
       <c r="H253" t="n">
-        <v>113.8576</v>
+        <v>114.3543</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.455002</v>
+        <v>48.580002</v>
       </c>
       <c r="H504" t="n">
-        <v>131.7786</v>
+        <v>132.1186</v>
       </c>
     </row>
     <row r="505">
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.19961499999999</v>
+        <v>65.199623</v>
       </c>
       <c r="H515" t="n">
         <v>100.8131</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.111977</v>
+        <v>65.11198400000001</v>
       </c>
       <c r="H516" t="n">
         <v>100.6776</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.84236900000001</v>
+        <v>65.842377</v>
       </c>
       <c r="H520" t="n">
         <v>101.807</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407211</v>
       </c>
       <c r="H524" t="n">
         <v>102.6803</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407211</v>
       </c>
       <c r="H527" t="n">
         <v>102.6803</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H529" t="n">
         <v>102.1382</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H531" t="n">
         <v>102.4996</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.77726699999999</v>
+        <v>66.77726</v>
       </c>
       <c r="H538" t="n">
         <v>103.2525</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.416939</v>
+        <v>66.41693100000001</v>
       </c>
       <c r="H539" t="n">
         <v>102.6954</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.027412</v>
+        <v>66.027405</v>
       </c>
       <c r="H542" t="n">
         <v>102.0931</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.124786</v>
+        <v>66.12479399999999</v>
       </c>
       <c r="H544" t="n">
         <v>102.2436</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>66.38771800000001</v>
+        <v>66.387726</v>
       </c>
       <c r="H545" t="n">
         <v>102.6502</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.770599</v>
+        <v>67.77059199999999</v>
       </c>
       <c r="H559" t="n">
         <v>104.7884</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H566" t="n">
         <v>105.5689</v>
@@ -22036,10 +22036,10 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H569" t="n">
-        <v>107.0682</v>
+        <v>107.0681</v>
       </c>
     </row>
     <row r="570">
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H570" t="n">
         <v>107.8859</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H572" t="n">
         <v>107.7648</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H574" t="n">
         <v>108.522</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H581" t="n">
         <v>108.8097</v>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.410492</v>
+        <v>70.4105</v>
       </c>
       <c r="H585" t="n">
         <v>108.8703</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H589" t="n">
         <v>110.839</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H591" t="n">
         <v>112.6866</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H595" t="n">
         <v>113.7467</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H597" t="n">
         <v>114.1707</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H600" t="n">
         <v>114.2161</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H604" t="n">
         <v>115.2308</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H609" t="n">
         <v>115.9728</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H610" t="n">
         <v>113.4286</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H617" t="n">
         <v>112.1868</v>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.64357800000001</v>
+        <v>72.64357</v>
       </c>
       <c r="H620" t="n">
         <v>112.3231</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.31999999999999</v>
+        <v>80.19000200000001</v>
       </c>
       <c r="H755" t="n">
-        <v>124.1926</v>
+        <v>123.9916</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>128.869995</v>
+        <v>128.690002</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.0242</v>
+        <v>119.8566</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>128.869995</v>
+        <v>128.690002</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.0242</v>
+        <v>119.8566</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>128.869995</v>
+        <v>128.690002</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.0242</v>
+        <v>119.8566</v>
       </c>
     </row>
     <row r="1509">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1511" t="n">
         <v>101.6349</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.799225</v>
+        <v>54.799221</v>
       </c>
       <c r="H1512" t="n">
         <v>102.198</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1516" t="n">
         <v>103.3243</v>
@@ -58174,10 +58174,10 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.536236</v>
+        <v>54.53624</v>
       </c>
       <c r="H1520" t="n">
-        <v>101.7075</v>
+        <v>101.7076</v>
       </c>
     </row>
     <row r="1521">
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1521" t="n">
         <v>102.2343</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1523" t="n">
         <v>101.98</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1525" t="n">
         <v>103.3243</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1526" t="n">
         <v>103.0881</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.588188</v>
+        <v>55.588192</v>
       </c>
       <c r="H1530" t="n">
         <v>103.6694</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1531" t="n">
         <v>103.5604</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.295986</v>
+        <v>55.295982</v>
       </c>
       <c r="H1532" t="n">
         <v>103.1244</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.325203</v>
+        <v>55.325199</v>
       </c>
       <c r="H1533" t="n">
         <v>103.1789</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1535" t="n">
         <v>103.0881</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>54.867409</v>
+        <v>54.867405</v>
       </c>
       <c r="H1536" t="n">
         <v>102.3252</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1538" t="n">
         <v>103.2879</v>
@@ -58896,10 +58896,10 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1539" t="n">
-        <v>104.6321</v>
+        <v>104.6322</v>
       </c>
     </row>
     <row r="1540">
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1541" t="n">
         <v>104.7048</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.607677</v>
+        <v>55.607674</v>
       </c>
       <c r="H1542" t="n">
         <v>103.7057</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1544" t="n">
         <v>101.3442</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.351166</v>
+        <v>54.35117</v>
       </c>
       <c r="H1547" t="n">
         <v>101.3624</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1550" t="n">
         <v>103.5604</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.987541</v>
+        <v>55.987545</v>
       </c>
       <c r="H1557" t="n">
         <v>104.4142</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1558" t="n">
         <v>104.2507</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1559" t="n">
         <v>104.1417</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1562" t="n">
         <v>104.1599</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1564" t="n">
         <v>104.5499</v>
@@ -59922,10 +59922,10 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.558754</v>
+        <v>56.558758</v>
       </c>
       <c r="H1566" t="n">
-        <v>105.4794</v>
+        <v>105.4795</v>
       </c>
     </row>
     <row r="1567">
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1567" t="n">
         <v>105.8987</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.676044</v>
+        <v>56.676041</v>
       </c>
       <c r="H1568" t="n">
         <v>105.6982</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1570" t="n">
         <v>106.245</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>57.692471</v>
+        <v>57.692474</v>
       </c>
       <c r="H1572" t="n">
         <v>107.5938</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.031437</v>
+        <v>59.031433</v>
       </c>
       <c r="H1577" t="n">
         <v>110.0909</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1581" t="n">
         <v>110.9475</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1582" t="n">
         <v>110.9658</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1584" t="n">
         <v>108.6874</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>58.953247</v>
+        <v>58.953243</v>
       </c>
       <c r="H1588" t="n">
         <v>109.9451</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.168262</v>
+        <v>59.168259</v>
       </c>
       <c r="H1592" t="n">
         <v>110.3461</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>59.793758</v>
+        <v>59.793755</v>
       </c>
       <c r="H1593" t="n">
         <v>111.5126</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.803532</v>
+        <v>59.803528</v>
       </c>
       <c r="H1595" t="n">
         <v>111.5308</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.246445</v>
+        <v>59.246449</v>
       </c>
       <c r="H1596" t="n">
         <v>110.4919</v>
@@ -61100,10 +61100,10 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.744892</v>
+        <v>59.744896</v>
       </c>
       <c r="H1597" t="n">
-        <v>111.4214</v>
+        <v>111.4215</v>
       </c>
     </row>
     <row r="1598">
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.11628</v>
+        <v>60.116276</v>
       </c>
       <c r="H1599" t="n">
         <v>112.1141</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1600" t="n">
         <v>112.2781</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1601" t="n">
         <v>111.7678</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1603" t="n">
         <v>111.786</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1604" t="n">
         <v>112.3875</v>
@@ -61442,10 +61442,10 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>60.65382</v>
+        <v>60.653816</v>
       </c>
       <c r="H1606" t="n">
-        <v>113.1166</v>
+        <v>113.1165</v>
       </c>
     </row>
     <row r="1607">
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1608" t="n">
         <v>113.5175</v>
@@ -61556,10 +61556,10 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>61.015434</v>
+        <v>61.015438</v>
       </c>
       <c r="H1609" t="n">
-        <v>113.7909</v>
+        <v>113.791</v>
       </c>
     </row>
     <row r="1610">
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>59.393051</v>
+        <v>59.393047</v>
       </c>
       <c r="H1615" t="n">
         <v>110.7653</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>58.581856</v>
+        <v>58.581852</v>
       </c>
       <c r="H1616" t="n">
         <v>109.2524</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1617" t="n">
         <v>108.2682</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1619" t="n">
         <v>109.6352</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>58.4548</v>
+        <v>58.454803</v>
       </c>
       <c r="H1620" t="n">
         <v>109.0155</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>58.112728</v>
+        <v>58.112732</v>
       </c>
       <c r="H1621" t="n">
         <v>108.3775</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1624" t="n">
         <v>108.9693</v>
@@ -62848,7 +62848,7 @@
         </is>
       </c>
       <c r="G1643" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1643" t="n">
         <v>112.1851</v>
@@ -62924,7 +62924,7 @@
         </is>
       </c>
       <c r="G1645" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1645" t="n">
         <v>113.9208</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1647" t="n">
         <v>112.0389</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1649" t="n">
         <v>111.8014</v>
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1650" t="n">
         <v>111.1984</v>
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1653" t="n">
         <v>109.9377</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1656" t="n">
         <v>111.3994</v>
@@ -63380,7 +63380,7 @@
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1657" t="n">
         <v>113.866</v>
@@ -63456,7 +63456,7 @@
         </is>
       </c>
       <c r="G1659" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1659" t="n">
         <v>112.0024</v>
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1661" t="n">
         <v>110.9792</v>
@@ -63912,7 +63912,7 @@
         </is>
       </c>
       <c r="G1671" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1671" t="n">
         <v>115.4008</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1673" t="n">
         <v>114.9075</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1676" t="n">
         <v>115.0354</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1678" t="n">
         <v>114.9075</v>
@@ -64216,7 +64216,7 @@
         </is>
       </c>
       <c r="G1679" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1679" t="n">
         <v>114.4507</v>
@@ -64368,7 +64368,7 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1683" t="n">
         <v>114.3045</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.400002</v>
+        <v>63.139999</v>
       </c>
       <c r="H1760" t="n">
-        <v>118.2381</v>
+        <v>117.7532</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.664001</v>
+        <v>64.66400899999999</v>
       </c>
       <c r="H506" t="n">
         <v>99.9849</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H508" t="n">
         <v>100.7529</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H512" t="n">
         <v>102.078</v>
@@ -19908,10 +19908,10 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.910538</v>
+        <v>65.91052999999999</v>
       </c>
       <c r="H513" t="n">
-        <v>101.9124</v>
+        <v>101.9123</v>
       </c>
     </row>
     <row r="514">
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.11198400000001</v>
+        <v>65.111977</v>
       </c>
       <c r="H516" t="n">
         <v>100.6776</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.559944</v>
+        <v>65.559952</v>
       </c>
       <c r="H518" t="n">
         <v>101.3703</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H519" t="n">
         <v>100.6927</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.842377</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H520" t="n">
         <v>101.807</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H521" t="n">
         <v>102.078</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H522" t="n">
         <v>101.9575</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.407211</v>
+        <v>66.407196</v>
       </c>
       <c r="H524" t="n">
         <v>102.6803</v>
@@ -20402,10 +20402,10 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H526" t="n">
-        <v>102.3791</v>
+        <v>102.3792</v>
       </c>
     </row>
     <row r="527">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.407211</v>
+        <v>66.407196</v>
       </c>
       <c r="H527" t="n">
         <v>102.6803</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H529" t="n">
         <v>102.1382</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>65.98844099999999</v>
+        <v>65.988449</v>
       </c>
       <c r="H532" t="n">
         <v>102.0328</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H534" t="n">
         <v>102.6201</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H535" t="n">
         <v>103.5085</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.77726</v>
+        <v>66.777275</v>
       </c>
       <c r="H538" t="n">
         <v>103.2525</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.41693100000001</v>
+        <v>66.416939</v>
       </c>
       <c r="H539" t="n">
         <v>102.6954</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.12479399999999</v>
+        <v>66.124786</v>
       </c>
       <c r="H544" t="n">
         <v>102.2436</v>
@@ -21162,10 +21162,10 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H546" t="n">
-        <v>103.5988</v>
+        <v>103.5989</v>
       </c>
     </row>
     <row r="547">
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.874657</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H550" t="n">
         <v>103.4031</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H551" t="n">
         <v>103.5085</v>
@@ -21390,10 +21390,10 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.371315</v>
+        <v>67.37133</v>
       </c>
       <c r="H552" t="n">
-        <v>104.171</v>
+        <v>104.1711</v>
       </c>
     </row>
     <row r="553">
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.51739499999999</v>
+        <v>67.51741</v>
       </c>
       <c r="H553" t="n">
         <v>104.3969</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.283661</v>
+        <v>67.283676</v>
       </c>
       <c r="H554" t="n">
         <v>104.0355</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.29341100000001</v>
+        <v>67.293404</v>
       </c>
       <c r="H555" t="n">
         <v>104.0506</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.478447</v>
+        <v>67.47843899999999</v>
       </c>
       <c r="H557" t="n">
         <v>104.3367</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H559" t="n">
         <v>104.7884</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.234978</v>
+        <v>67.234993</v>
       </c>
       <c r="H561" t="n">
-        <v>103.9602</v>
+        <v>103.9603</v>
       </c>
     </row>
     <row r="562">
@@ -21770,10 +21770,10 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.619141</v>
+        <v>67.619148</v>
       </c>
       <c r="H562" t="n">
-        <v>104.5542</v>
+        <v>104.5543</v>
       </c>
     </row>
     <row r="563">
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H563" t="n">
         <v>104.9783</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.815033</v>
+        <v>67.81502500000001</v>
       </c>
       <c r="H564" t="n">
         <v>104.8571</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H566" t="n">
         <v>105.5689</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H568" t="n">
         <v>105.9475</v>
@@ -22036,10 +22036,10 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>69.24498</v>
+        <v>69.24498699999999</v>
       </c>
       <c r="H569" t="n">
-        <v>107.0681</v>
+        <v>107.0682</v>
       </c>
     </row>
     <row r="570">
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>69.48004899999999</v>
+        <v>69.480057</v>
       </c>
       <c r="H571" t="n">
         <v>107.4316</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>70.273376</v>
+        <v>70.273369</v>
       </c>
       <c r="H575" t="n">
         <v>108.6583</v>
@@ -22378,10 +22378,10 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H578" t="n">
-        <v>110.2332</v>
+        <v>110.2333</v>
       </c>
     </row>
     <row r="579">
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.723907</v>
+        <v>70.72391500000001</v>
       </c>
       <c r="H579" t="n">
         <v>109.3549</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H582" t="n">
         <v>109.5821</v>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.4105</v>
+        <v>70.410492</v>
       </c>
       <c r="H585" t="n">
         <v>108.8703</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H589" t="n">
         <v>110.839</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>72.87863900000001</v>
+        <v>72.878632</v>
       </c>
       <c r="H591" t="n">
         <v>112.6866</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H592" t="n">
         <v>111.8688</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.201836</v>
+        <v>73.201843</v>
       </c>
       <c r="H593" t="n">
         <v>113.1863</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H594" t="n">
         <v>113.3529</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H595" t="n">
         <v>113.7467</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H596" t="n">
         <v>114.6099</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H597" t="n">
         <v>114.1707</v>
@@ -23138,10 +23138,10 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.828667</v>
+        <v>73.82867400000001</v>
       </c>
       <c r="H598" t="n">
-        <v>114.1555</v>
+        <v>114.1556</v>
       </c>
     </row>
     <row r="599">
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H605" t="n">
         <v>115.5488</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>75.003967</v>
+        <v>75.003975</v>
       </c>
       <c r="H609" t="n">
         <v>115.9728</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>73.358543</v>
+        <v>73.35855100000001</v>
       </c>
       <c r="H610" t="n">
         <v>113.4286</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>72.721931</v>
+        <v>72.72191599999999</v>
       </c>
       <c r="H615" t="n">
         <v>112.4443</v>
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H616" t="n">
         <v>112.0051</v>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.64357</v>
+        <v>72.643562</v>
       </c>
       <c r="H620" t="n">
         <v>112.3231</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H621" t="n">
         <v>110.5767</v>
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H622" t="n">
         <v>109.5569</v>
@@ -24126,10 +24126,10 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H624" t="n">
-        <v>110.4092</v>
+        <v>110.4093</v>
       </c>
     </row>
     <row r="625">
@@ -24240,10 +24240,10 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H627" t="n">
-        <v>110.4092</v>
+        <v>110.4093</v>
       </c>
     </row>
     <row r="628">
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H630" t="n">
         <v>112.3879</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H632" t="n">
         <v>112.0226</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H634" t="n">
         <v>114.3361</v>
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H635" t="n">
         <v>114.0774</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H637" t="n">
         <v>114.1535</v>
@@ -24696,10 +24696,10 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H639" t="n">
-        <v>114.123</v>
+        <v>114.1231</v>
       </c>
     </row>
     <row r="640">
@@ -24848,7 +24848,7 @@
         </is>
       </c>
       <c r="G643" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H643" t="n">
         <v>114.1535</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H646" t="n">
         <v>113.6969</v>
@@ -25000,7 +25000,7 @@
         </is>
       </c>
       <c r="G647" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H647" t="n">
         <v>114.0926</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H649" t="n">
         <v>115.0819</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H652" t="n">
         <v>116.1778</v>
@@ -25228,7 +25228,7 @@
         </is>
       </c>
       <c r="G653" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H653" t="n">
         <v>115.4016</v>
@@ -25304,7 +25304,7 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H655" t="n">
         <v>115.4016</v>
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H660" t="n">
         <v>116.1169</v>
@@ -25684,7 +25684,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H665" t="n">
         <v>119.2067</v>
@@ -25760,7 +25760,7 @@
         </is>
       </c>
       <c r="G667" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H667" t="n">
         <v>118.4</v>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H669" t="n">
         <v>117.9434</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H670" t="n">
         <v>117.7912</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H675" t="n">
         <v>118.4304</v>
@@ -26102,7 +26102,7 @@
         </is>
       </c>
       <c r="G676" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H676" t="n">
         <v>117.7303</v>
@@ -26330,7 +26330,7 @@
         </is>
       </c>
       <c r="G682" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H682" t="n">
         <v>121.1549</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>55.062214</v>
+        <v>55.06221</v>
       </c>
       <c r="H1513" t="n">
         <v>102.6885</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.974548</v>
+        <v>54.974545</v>
       </c>
       <c r="H1515" t="n">
         <v>102.525</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.740784</v>
+        <v>54.74078</v>
       </c>
       <c r="H1519" t="n">
         <v>102.089</v>
@@ -58174,10 +58174,10 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.53624</v>
+        <v>54.536236</v>
       </c>
       <c r="H1520" t="n">
-        <v>101.7076</v>
+        <v>101.7075</v>
       </c>
     </row>
     <row r="1521">
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.325199</v>
+        <v>55.325203</v>
       </c>
       <c r="H1533" t="n">
         <v>103.1789</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>54.584934</v>
+        <v>54.584938</v>
       </c>
       <c r="H1537" t="n">
         <v>101.7984</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>56.104431</v>
+        <v>56.104435</v>
       </c>
       <c r="H1539" t="n">
         <v>104.6322</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>55.305721</v>
+        <v>55.305725</v>
       </c>
       <c r="H1543" t="n">
         <v>103.1426</v>
@@ -59238,10 +59238,10 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>54.41935</v>
+        <v>54.419346</v>
       </c>
       <c r="H1548" t="n">
-        <v>101.4896</v>
+        <v>101.4895</v>
       </c>
     </row>
     <row r="1549">
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1551" t="n">
         <v>103.6331</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1553" t="n">
         <v>103.6331</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.724556</v>
+        <v>55.72456</v>
       </c>
       <c r="H1555" t="n">
         <v>103.9237</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.958328</v>
+        <v>55.958332</v>
       </c>
       <c r="H1556" t="n">
         <v>104.3597</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.841446</v>
+        <v>55.841442</v>
       </c>
       <c r="H1559" t="n">
         <v>104.1417</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.870663</v>
+        <v>55.870667</v>
       </c>
       <c r="H1560" t="n">
         <v>104.1962</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1565" t="n">
         <v>104.4223</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1573" t="n">
         <v>108.5598</v>
@@ -60264,10 +60264,10 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1575" t="n">
-        <v>109.1248</v>
+        <v>109.1249</v>
       </c>
     </row>
     <row r="1576">
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>58.39616</v>
+        <v>58.396156</v>
       </c>
       <c r="H1576" t="n">
         <v>108.9061</v>
@@ -60378,10 +60378,10 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1578" t="n">
-        <v>110.2731</v>
+        <v>110.2732</v>
       </c>
     </row>
     <row r="1579">
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1580" t="n">
         <v>110.3096</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.91415</v>
+        <v>58.914154</v>
       </c>
       <c r="H1586" t="n">
         <v>109.8722</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.835964</v>
+        <v>58.835968</v>
       </c>
       <c r="H1590" t="n">
         <v>109.7263</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>58.718685</v>
+        <v>58.718681</v>
       </c>
       <c r="H1591" t="n">
         <v>109.5076</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>59.793755</v>
+        <v>59.793758</v>
       </c>
       <c r="H1593" t="n">
         <v>111.5126</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.803528</v>
+        <v>59.803532</v>
       </c>
       <c r="H1595" t="n">
         <v>111.5308</v>
@@ -61100,10 +61100,10 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.744896</v>
+        <v>59.744892</v>
       </c>
       <c r="H1597" t="n">
-        <v>111.4215</v>
+        <v>111.4214</v>
       </c>
     </row>
     <row r="1598">
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.116276</v>
+        <v>60.11628</v>
       </c>
       <c r="H1599" t="n">
         <v>112.1141</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1601" t="n">
         <v>111.7678</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.852402</v>
+        <v>59.852398</v>
       </c>
       <c r="H1602" t="n">
         <v>111.6219</v>
@@ -61442,10 +61442,10 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>60.653816</v>
+        <v>60.65382</v>
       </c>
       <c r="H1606" t="n">
-        <v>113.1165</v>
+        <v>113.1166</v>
       </c>
     </row>
     <row r="1607">
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1608" t="n">
         <v>113.5175</v>
@@ -61556,10 +61556,10 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1609" t="n">
-        <v>113.791</v>
+        <v>113.7909</v>
       </c>
     </row>
     <row r="1610">
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.406372</v>
+        <v>61.406376</v>
       </c>
       <c r="H1611" t="n">
         <v>114.52</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1618" t="n">
         <v>107.5209</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1621" t="n">
         <v>108.3775</v>
@@ -62126,7 +62126,7 @@
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1624" t="n">
         <v>108.9693</v>
@@ -62848,7 +62848,7 @@
         </is>
       </c>
       <c r="G1643" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1643" t="n">
         <v>112.1851</v>
@@ -62924,7 +62924,7 @@
         </is>
       </c>
       <c r="G1645" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1645" t="n">
         <v>113.9208</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1647" t="n">
         <v>112.0389</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1649" t="n">
         <v>111.8014</v>
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1650" t="n">
         <v>111.1984</v>
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1653" t="n">
         <v>109.9377</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1656" t="n">
         <v>111.3994</v>
@@ -63380,7 +63380,7 @@
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1657" t="n">
         <v>113.866</v>
@@ -63456,7 +63456,7 @@
         </is>
       </c>
       <c r="G1659" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1659" t="n">
         <v>112.0024</v>
@@ -63532,7 +63532,7 @@
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1661" t="n">
         <v>110.9792</v>
@@ -63912,7 +63912,7 @@
         </is>
       </c>
       <c r="G1671" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1671" t="n">
         <v>115.4008</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1673" t="n">
         <v>114.9075</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1676" t="n">
         <v>115.0354</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1678" t="n">
         <v>114.9075</v>
@@ -64216,7 +64216,7 @@
         </is>
       </c>
       <c r="G1679" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1679" t="n">
         <v>114.4507</v>
@@ -64368,7 +64368,7 @@
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1683" t="n">
         <v>114.3045</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.66400899999999</v>
+        <v>64.664001</v>
       </c>
       <c r="H506" t="n">
         <v>99.9849</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.160667</v>
+        <v>65.160675</v>
       </c>
       <c r="H508" t="n">
         <v>100.7529</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>66.01767</v>
+        <v>66.017662</v>
       </c>
       <c r="H512" t="n">
         <v>102.078</v>
@@ -19908,10 +19908,10 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H513" t="n">
-        <v>101.9123</v>
+        <v>101.9124</v>
       </c>
     </row>
     <row r="514">
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.111977</v>
+        <v>65.11198400000001</v>
       </c>
       <c r="H516" t="n">
         <v>100.6776</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.559952</v>
+        <v>65.559944</v>
       </c>
       <c r="H518" t="n">
         <v>101.3703</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.121712</v>
+        <v>65.121719</v>
       </c>
       <c r="H519" t="n">
         <v>100.6927</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.84236900000001</v>
+        <v>65.842377</v>
       </c>
       <c r="H520" t="n">
         <v>101.807</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>66.01767</v>
+        <v>66.017662</v>
       </c>
       <c r="H521" t="n">
         <v>102.078</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.939751</v>
+        <v>65.939758</v>
       </c>
       <c r="H522" t="n">
         <v>101.9575</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.407196</v>
+        <v>66.407211</v>
       </c>
       <c r="H524" t="n">
         <v>102.6803</v>
@@ -20402,10 +20402,10 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.212433</v>
+        <v>66.212425</v>
       </c>
       <c r="H526" t="n">
-        <v>102.3792</v>
+        <v>102.3791</v>
       </c>
     </row>
     <row r="527">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.407196</v>
+        <v>66.407211</v>
       </c>
       <c r="H527" t="n">
         <v>102.6803</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H529" t="n">
         <v>102.1382</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>65.988449</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H532" t="n">
         <v>102.0328</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368256</v>
       </c>
       <c r="H534" t="n">
         <v>102.6201</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H535" t="n">
         <v>103.5085</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.777275</v>
+        <v>66.77726</v>
       </c>
       <c r="H538" t="n">
         <v>103.2525</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.416939</v>
+        <v>66.41693100000001</v>
       </c>
       <c r="H539" t="n">
         <v>102.6954</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.124786</v>
+        <v>66.12479399999999</v>
       </c>
       <c r="H544" t="n">
         <v>102.2436</v>
@@ -21162,10 +21162,10 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H546" t="n">
-        <v>103.5989</v>
+        <v>103.5988</v>
       </c>
     </row>
     <row r="547">
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.87464900000001</v>
+        <v>66.874657</v>
       </c>
       <c r="H550" t="n">
         <v>103.4031</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H551" t="n">
         <v>103.5085</v>
@@ -21390,10 +21390,10 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.37133</v>
+        <v>67.371315</v>
       </c>
       <c r="H552" t="n">
-        <v>104.1711</v>
+        <v>104.171</v>
       </c>
     </row>
     <row r="553">
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.51741</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H553" t="n">
         <v>104.3969</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.283676</v>
+        <v>67.283661</v>
       </c>
       <c r="H554" t="n">
         <v>104.0355</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.293404</v>
+        <v>67.29341100000001</v>
       </c>
       <c r="H555" t="n">
         <v>104.0506</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H557" t="n">
         <v>104.3367</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.770599</v>
+        <v>67.77059199999999</v>
       </c>
       <c r="H559" t="n">
         <v>104.7884</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.234993</v>
+        <v>67.234978</v>
       </c>
       <c r="H561" t="n">
-        <v>103.9603</v>
+        <v>103.9602</v>
       </c>
     </row>
     <row r="562">
@@ -21770,10 +21770,10 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.619148</v>
+        <v>67.619141</v>
       </c>
       <c r="H562" t="n">
-        <v>104.5543</v>
+        <v>104.5542</v>
       </c>
     </row>
     <row r="563">
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H563" t="n">
         <v>104.9783</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>67.81502500000001</v>
+        <v>67.815033</v>
       </c>
       <c r="H564" t="n">
         <v>104.8571</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H566" t="n">
         <v>105.5689</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H568" t="n">
         <v>105.9475</v>
@@ -22036,10 +22036,10 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H569" t="n">
-        <v>107.0682</v>
+        <v>107.0681</v>
       </c>
     </row>
     <row r="570">
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>69.480057</v>
+        <v>69.48004899999999</v>
       </c>
       <c r="H571" t="n">
         <v>107.4316</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>70.273369</v>
+        <v>70.273376</v>
       </c>
       <c r="H575" t="n">
         <v>108.6583</v>
@@ -22378,10 +22378,10 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H578" t="n">
-        <v>110.2333</v>
+        <v>110.2332</v>
       </c>
     </row>
     <row r="579">
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.72391500000001</v>
+        <v>70.723907</v>
       </c>
       <c r="H579" t="n">
         <v>109.3549</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H582" t="n">
         <v>109.5821</v>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.410492</v>
+        <v>70.4105</v>
       </c>
       <c r="H585" t="n">
         <v>108.8703</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H589" t="n">
         <v>110.839</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H591" t="n">
         <v>112.6866</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H592" t="n">
         <v>111.8688</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.201843</v>
+        <v>73.201836</v>
       </c>
       <c r="H593" t="n">
         <v>113.1863</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H594" t="n">
         <v>113.3529</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H595" t="n">
         <v>113.7467</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H596" t="n">
         <v>114.6099</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H597" t="n">
         <v>114.1707</v>
@@ -23138,10 +23138,10 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.82867400000001</v>
+        <v>73.828667</v>
       </c>
       <c r="H598" t="n">
-        <v>114.1556</v>
+        <v>114.1555</v>
       </c>
     </row>
     <row r="599">
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H605" t="n">
         <v>115.5488</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H609" t="n">
         <v>115.9728</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H610" t="n">
         <v>113.4286</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>72.72191599999999</v>
+        <v>72.721931</v>
       </c>
       <c r="H615" t="n">
         <v>112.4443</v>
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H616" t="n">
         <v>112.0051</v>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>72.643562</v>
+        <v>72.64357</v>
       </c>
       <c r="H620" t="n">
         <v>112.3231</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H621" t="n">
         <v>110.5767</v>
@@ -24050,7 +24050,7 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H622" t="n">
         <v>109.5569</v>
@@ -24126,10 +24126,10 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H624" t="n">
-        <v>110.4093</v>
+        <v>110.4092</v>
       </c>
     </row>
     <row r="625">
@@ -24240,10 +24240,10 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H627" t="n">
-        <v>110.4093</v>
+        <v>110.4092</v>
       </c>
     </row>
     <row r="628">
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H630" t="n">
         <v>112.3879</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H632" t="n">
         <v>112.0226</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H634" t="n">
         <v>114.3361</v>
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G635" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H635" t="n">
         <v>114.0774</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H637" t="n">
         <v>114.1535</v>
@@ -24696,10 +24696,10 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H639" t="n">
-        <v>114.1231</v>
+        <v>114.123</v>
       </c>
     </row>
     <row r="640">
@@ -24848,7 +24848,7 @@
         </is>
       </c>
       <c r="G643" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H643" t="n">
         <v>114.1535</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H646" t="n">
         <v>113.6969</v>
@@ -25000,7 +25000,7 @@
         </is>
       </c>
       <c r="G647" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H647" t="n">
         <v>114.0926</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H649" t="n">
         <v>115.0819</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H652" t="n">
         <v>116.1778</v>
@@ -25228,7 +25228,7 @@
         </is>
       </c>
       <c r="G653" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H653" t="n">
         <v>115.4016</v>
@@ -25304,7 +25304,7 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H655" t="n">
         <v>115.4016</v>
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H660" t="n">
         <v>116.1169</v>
@@ -25684,7 +25684,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H665" t="n">
         <v>119.2067</v>
@@ -25760,7 +25760,7 @@
         </is>
       </c>
       <c r="G667" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H667" t="n">
         <v>118.4</v>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H669" t="n">
         <v>117.9434</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H670" t="n">
         <v>117.7912</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H675" t="n">
         <v>118.4304</v>
@@ -26102,7 +26102,7 @@
         </is>
       </c>
       <c r="G676" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H676" t="n">
         <v>117.7303</v>
@@ -26330,7 +26330,7 @@
         </is>
       </c>
       <c r="G682" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H682" t="n">
         <v>121.1549</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.497276</v>
+        <v>54.497272</v>
       </c>
       <c r="H1511" t="n">
         <v>101.6349</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>55.06221</v>
+        <v>55.062214</v>
       </c>
       <c r="H1513" t="n">
         <v>102.6885</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>55.042732</v>
+        <v>55.042736</v>
       </c>
       <c r="H1514" t="n">
         <v>102.6521</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.974545</v>
+        <v>54.974548</v>
       </c>
       <c r="H1515" t="n">
         <v>102.525</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.159618</v>
+        <v>55.159615</v>
       </c>
       <c r="H1517" t="n">
         <v>102.8701</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.74078</v>
+        <v>54.740788</v>
       </c>
       <c r="H1519" t="n">
         <v>102.089</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.536236</v>
+        <v>54.536232</v>
       </c>
       <c r="H1520" t="n">
         <v>101.7075</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.818703</v>
+        <v>54.818707</v>
       </c>
       <c r="H1521" t="n">
         <v>102.2343</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1528" t="n">
         <v>103.9782</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1531" t="n">
         <v>103.5604</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1532" t="n">
         <v>103.1244</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>54.867405</v>
+        <v>54.867409</v>
       </c>
       <c r="H1536" t="n">
         <v>102.3252</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>54.584938</v>
+        <v>54.584934</v>
       </c>
       <c r="H1537" t="n">
         <v>101.7984</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1538" t="n">
         <v>103.2879</v>
@@ -58896,10 +58896,10 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>56.104435</v>
+        <v>56.104427</v>
       </c>
       <c r="H1539" t="n">
-        <v>104.6322</v>
+        <v>104.6321</v>
       </c>
     </row>
     <row r="1540">
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>56.143391</v>
+        <v>56.143394</v>
       </c>
       <c r="H1541" t="n">
         <v>104.7048</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>55.305725</v>
+        <v>55.305717</v>
       </c>
       <c r="H1543" t="n">
         <v>103.1426</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1544" t="n">
         <v>101.3442</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1545" t="n">
         <v>101.2534</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1546" t="n">
         <v>101.6167</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.35117</v>
+        <v>54.351162</v>
       </c>
       <c r="H1547" t="n">
         <v>101.3624</v>
@@ -59238,10 +59238,10 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>54.419346</v>
+        <v>54.41935</v>
       </c>
       <c r="H1548" t="n">
-        <v>101.4895</v>
+        <v>101.4896</v>
       </c>
     </row>
     <row r="1549">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1550" t="n">
         <v>103.5604</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1552" t="n">
         <v>103.9782</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1558" t="n">
         <v>104.2507</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.870667</v>
+        <v>55.870663</v>
       </c>
       <c r="H1560" t="n">
         <v>104.1962</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1563" t="n">
         <v>104.9873</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1564" t="n">
         <v>104.5499</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1567" t="n">
         <v>105.8987</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1574" t="n">
         <v>109.1613</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>58.396156</v>
+        <v>58.39616</v>
       </c>
       <c r="H1576" t="n">
         <v>108.9061</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1577" t="n">
         <v>110.0909</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.914154</v>
+        <v>58.91415</v>
       </c>
       <c r="H1586" t="n">
         <v>109.8722</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1587" t="n">
         <v>109.781</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1589" t="n">
         <v>110.6012</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.835968</v>
+        <v>58.835964</v>
       </c>
       <c r="H1590" t="n">
         <v>109.7263</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>58.718681</v>
+        <v>58.718685</v>
       </c>
       <c r="H1591" t="n">
         <v>109.5076</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.168259</v>
+        <v>59.168262</v>
       </c>
       <c r="H1592" t="n">
         <v>110.3461</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.246449</v>
+        <v>59.246445</v>
       </c>
       <c r="H1596" t="n">
         <v>110.4919</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.852398</v>
+        <v>59.852402</v>
       </c>
       <c r="H1602" t="n">
         <v>111.6219</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>60.956795</v>
+        <v>60.956799</v>
       </c>
       <c r="H1605" t="n">
         <v>113.6816</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.406376</v>
+        <v>61.406372</v>
       </c>
       <c r="H1611" t="n">
         <v>114.52</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1615" t="n">
         <v>110.7653</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>58.581852</v>
+        <v>58.581856</v>
       </c>
       <c r="H1616" t="n">
         <v>109.2524</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1617" t="n">
         <v>108.2682</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1620" t="n">
         <v>109.0155</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.535</v>
+        <v>34.555</v>
       </c>
       <c r="H253" t="n">
-        <v>114.3543</v>
+        <v>114.4205</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.580002</v>
+        <v>48.130001</v>
       </c>
       <c r="H504" t="n">
-        <v>132.1186</v>
+        <v>130.8948</v>
       </c>
     </row>
     <row r="505">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H508" t="n">
         <v>100.7529</v>
@@ -19946,10 +19946,10 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H514" t="n">
-        <v>100.3012</v>
+        <v>100.3011</v>
       </c>
     </row>
     <row r="515">
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.11198400000001</v>
+        <v>65.111977</v>
       </c>
       <c r="H516" t="n">
         <v>100.6776</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.559944</v>
+        <v>65.559952</v>
       </c>
       <c r="H518" t="n">
         <v>101.3703</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H519" t="n">
         <v>100.6927</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.842377</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H520" t="n">
         <v>101.807</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H522" t="n">
         <v>101.9575</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.06635300000001</v>
+        <v>66.066345</v>
       </c>
       <c r="H523" t="n">
         <v>102.1533</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.407211</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H524" t="n">
         <v>102.6803</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.339035</v>
+        <v>66.339043</v>
       </c>
       <c r="H525" t="n">
         <v>102.5749</v>
@@ -20402,10 +20402,10 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H526" t="n">
-        <v>102.3791</v>
+        <v>102.3792</v>
       </c>
     </row>
     <row r="527">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.407211</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H527" t="n">
         <v>102.6803</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H534" t="n">
         <v>102.6201</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H535" t="n">
         <v>103.5085</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H536" t="n">
         <v>104.4722</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.77726</v>
+        <v>66.777275</v>
       </c>
       <c r="H538" t="n">
         <v>103.2525</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.41693100000001</v>
+        <v>66.416939</v>
       </c>
       <c r="H539" t="n">
         <v>102.6954</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>65.754715</v>
+        <v>65.754723</v>
       </c>
       <c r="H540" t="n">
         <v>101.6714</v>
@@ -21010,10 +21010,10 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H542" t="n">
-        <v>102.0931</v>
+        <v>102.093</v>
       </c>
     </row>
     <row r="543">
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.12479399999999</v>
+        <v>66.124786</v>
       </c>
       <c r="H544" t="n">
         <v>102.2436</v>
@@ -21162,10 +21162,10 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H546" t="n">
-        <v>103.5988</v>
+        <v>103.5989</v>
       </c>
     </row>
     <row r="547">
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.24472</v>
+        <v>67.24472799999999</v>
       </c>
       <c r="H548" t="n">
         <v>103.9753</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.874657</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H550" t="n">
         <v>103.4031</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H551" t="n">
         <v>103.5085</v>
@@ -21390,10 +21390,10 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H552" t="n">
-        <v>104.171</v>
+        <v>104.1711</v>
       </c>
     </row>
     <row r="553">
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.283661</v>
+        <v>67.283669</v>
       </c>
       <c r="H554" t="n">
         <v>104.0355</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H558" t="n">
         <v>104.2012</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H559" t="n">
         <v>104.7884</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H560" t="n">
         <v>103.8548</v>
@@ -29075,7 +29075,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.19000200000001</v>
+        <v>80.349998</v>
       </c>
       <c r="H755" t="n">
-        <v>123.9916</v>
+        <v>124.239</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>128.690002</v>
+        <v>128.570007</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.8566</v>
+        <v>119.7448</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>128.690002</v>
+        <v>128.570007</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.8566</v>
+        <v>119.7448</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>128.690002</v>
+        <v>128.570007</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.8566</v>
+        <v>119.7448</v>
       </c>
     </row>
     <row r="1509">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1511" t="n">
         <v>101.6349</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>55.062214</v>
+        <v>55.06221</v>
       </c>
       <c r="H1513" t="n">
         <v>102.6885</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>55.042736</v>
+        <v>55.042732</v>
       </c>
       <c r="H1514" t="n">
         <v>102.6521</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.974548</v>
+        <v>54.974545</v>
       </c>
       <c r="H1515" t="n">
         <v>102.525</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.159615</v>
+        <v>55.159618</v>
       </c>
       <c r="H1517" t="n">
         <v>102.8701</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.740788</v>
+        <v>54.74078</v>
       </c>
       <c r="H1519" t="n">
         <v>102.089</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.536232</v>
+        <v>54.536236</v>
       </c>
       <c r="H1520" t="n">
         <v>101.7075</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1521" t="n">
         <v>102.2343</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1528" t="n">
         <v>103.9782</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1531" t="n">
         <v>103.5604</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.295986</v>
+        <v>55.295982</v>
       </c>
       <c r="H1532" t="n">
         <v>103.1244</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>54.867409</v>
+        <v>54.867405</v>
       </c>
       <c r="H1536" t="n">
         <v>102.3252</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>54.584934</v>
+        <v>54.584938</v>
       </c>
       <c r="H1537" t="n">
         <v>101.7984</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1538" t="n">
         <v>103.2879</v>
@@ -58896,10 +58896,10 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>56.104427</v>
+        <v>56.104435</v>
       </c>
       <c r="H1539" t="n">
-        <v>104.6321</v>
+        <v>104.6322</v>
       </c>
     </row>
     <row r="1540">
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1541" t="n">
         <v>104.7048</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>55.305717</v>
+        <v>55.305725</v>
       </c>
       <c r="H1543" t="n">
         <v>103.1426</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1544" t="n">
         <v>101.3442</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1545" t="n">
         <v>101.2534</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.487534</v>
+        <v>54.48753</v>
       </c>
       <c r="H1546" t="n">
         <v>101.6167</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.351162</v>
+        <v>54.35117</v>
       </c>
       <c r="H1547" t="n">
         <v>101.3624</v>
@@ -59238,10 +59238,10 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>54.41935</v>
+        <v>54.419346</v>
       </c>
       <c r="H1548" t="n">
-        <v>101.4896</v>
+        <v>101.4895</v>
       </c>
     </row>
     <row r="1549">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1550" t="n">
         <v>103.5604</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1552" t="n">
         <v>103.9782</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1558" t="n">
         <v>104.2507</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.870663</v>
+        <v>55.870667</v>
       </c>
       <c r="H1560" t="n">
         <v>104.1962</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.294872</v>
+        <v>56.294876</v>
       </c>
       <c r="H1563" t="n">
         <v>104.9873</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1564" t="n">
         <v>104.5499</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1567" t="n">
         <v>105.8987</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>58.53299</v>
+        <v>58.532986</v>
       </c>
       <c r="H1574" t="n">
         <v>109.1613</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>58.39616</v>
+        <v>58.396156</v>
       </c>
       <c r="H1576" t="n">
         <v>108.9061</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.031437</v>
+        <v>59.031433</v>
       </c>
       <c r="H1577" t="n">
         <v>110.0909</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.91415</v>
+        <v>58.914154</v>
       </c>
       <c r="H1586" t="n">
         <v>109.8722</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>58.86528</v>
+        <v>58.865284</v>
       </c>
       <c r="H1587" t="n">
         <v>109.781</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.305092</v>
+        <v>59.305088</v>
       </c>
       <c r="H1589" t="n">
         <v>110.6012</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>58.835964</v>
+        <v>58.835968</v>
       </c>
       <c r="H1590" t="n">
         <v>109.7263</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>58.718685</v>
+        <v>58.718681</v>
       </c>
       <c r="H1591" t="n">
         <v>109.5076</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.168262</v>
+        <v>59.168259</v>
       </c>
       <c r="H1592" t="n">
         <v>110.3461</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.246445</v>
+        <v>59.246449</v>
       </c>
       <c r="H1596" t="n">
         <v>110.4919</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.852402</v>
+        <v>59.852398</v>
       </c>
       <c r="H1602" t="n">
         <v>111.6219</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>60.956799</v>
+        <v>60.956795</v>
       </c>
       <c r="H1605" t="n">
         <v>113.6816</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.406372</v>
+        <v>61.406376</v>
       </c>
       <c r="H1611" t="n">
         <v>114.52</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>59.393051</v>
+        <v>59.393047</v>
       </c>
       <c r="H1615" t="n">
         <v>110.7653</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>58.581856</v>
+        <v>58.581852</v>
       </c>
       <c r="H1616" t="n">
         <v>109.2524</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1617" t="n">
         <v>108.2682</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>58.4548</v>
+        <v>58.454803</v>
       </c>
       <c r="H1620" t="n">
         <v>109.0155</v>
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.139999</v>
+        <v>63.200001</v>
       </c>
       <c r="H1760" t="n">
-        <v>117.7532</v>
+        <v>117.8651</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>34.75</v>
+        <v>35.48</v>
       </c>
       <c r="H253" t="n">
-        <v>117.9365</v>
+        <v>120.414</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.43</v>
+        <v>48.279999</v>
       </c>
       <c r="H504" t="n">
-        <v>131.5675</v>
+        <v>131.16</v>
       </c>
     </row>
     <row r="505">
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>65.160667</v>
+        <v>65.160675</v>
       </c>
       <c r="H507" t="n">
         <v>100.7681</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.511253</v>
+        <v>65.511246</v>
       </c>
       <c r="H508" t="n">
         <v>101.3102</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.121712</v>
+        <v>65.121719</v>
       </c>
       <c r="H518" t="n">
         <v>100.7078</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.066345</v>
+        <v>66.06635300000001</v>
       </c>
       <c r="H522" t="n">
         <v>102.1687</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.339043</v>
+        <v>66.339035</v>
       </c>
       <c r="H524" t="n">
         <v>102.5904</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H530" t="n">
         <v>102.5151</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>65.98844099999999</v>
+        <v>65.988449</v>
       </c>
       <c r="H531" t="n">
         <v>102.0482</v>
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>65.57942199999999</v>
+        <v>65.579414</v>
       </c>
       <c r="H532" t="n">
-        <v>101.4157</v>
+        <v>101.4156</v>
       </c>
     </row>
     <row r="533">
@@ -20668,10 +20668,10 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368256</v>
       </c>
       <c r="H533" t="n">
-        <v>102.6355</v>
+        <v>102.6356</v>
       </c>
     </row>
     <row r="534">
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H534" t="n">
         <v>103.5241</v>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H535" t="n">
-        <v>104.488</v>
+        <v>104.4879</v>
       </c>
     </row>
     <row r="536">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H536" t="n">
         <v>103.7048</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H537" t="n">
         <v>103.2681</v>
@@ -20896,10 +20896,10 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>65.754723</v>
+        <v>65.754715</v>
       </c>
       <c r="H539" t="n">
-        <v>101.6868</v>
+        <v>101.6867</v>
       </c>
     </row>
     <row r="540">
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027405</v>
       </c>
       <c r="H541" t="n">
         <v>102.1084</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H542" t="n">
         <v>101.8976</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.96230300000001</v>
+        <v>66.962311</v>
       </c>
       <c r="H546" t="n">
         <v>103.5542</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.24472799999999</v>
+        <v>67.24472</v>
       </c>
       <c r="H547" t="n">
         <v>103.991</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H548" t="n">
         <v>103.7048</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H550" t="n">
         <v>103.5241</v>
@@ -21352,10 +21352,10 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.371323</v>
+        <v>67.371315</v>
       </c>
       <c r="H551" t="n">
-        <v>104.1868</v>
+        <v>104.1867</v>
       </c>
     </row>
     <row r="552">
@@ -21390,10 +21390,10 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.51739499999999</v>
+        <v>67.517403</v>
       </c>
       <c r="H552" t="n">
-        <v>104.4126</v>
+        <v>104.4127</v>
       </c>
     </row>
     <row r="553">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.770599</v>
+        <v>67.77059199999999</v>
       </c>
       <c r="H558" t="n">
         <v>104.8042</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.234978</v>
+        <v>67.23497</v>
       </c>
       <c r="H560" t="n">
         <v>103.9759</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H562" t="n">
         <v>104.9941</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H565" t="n">
         <v>105.5848</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.30474100000001</v>
+        <v>68.304733</v>
       </c>
       <c r="H566" t="n">
         <v>105.6302</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H567" t="n">
         <v>105.9635</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>69.24498</v>
+        <v>69.24498699999999</v>
       </c>
       <c r="H568" t="n">
         <v>107.0843</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H571" t="n">
         <v>107.781</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>71.340942</v>
+        <v>71.340935</v>
       </c>
       <c r="H576" t="n">
         <v>110.3256</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H577" t="n">
         <v>110.2499</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H579" t="n">
         <v>108.3566</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H581" t="n">
         <v>109.5986</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.51823400000001</v>
+        <v>70.518227</v>
       </c>
       <c r="H582" t="n">
         <v>109.0533</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.4105</v>
+        <v>70.410484</v>
       </c>
       <c r="H584" t="n">
         <v>108.8867</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>70.684731</v>
+        <v>70.68472300000001</v>
       </c>
       <c r="H586" t="n">
         <v>109.3108</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H588" t="n">
         <v>110.8557</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H591" t="n">
         <v>111.8857</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H593" t="n">
         <v>113.37</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H594" t="n">
         <v>113.7638</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H595" t="n">
         <v>114.6271</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H596" t="n">
         <v>114.1879</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H600" t="n">
         <v>115.2027</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H601" t="n">
         <v>115.2027</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>74.524055</v>
+        <v>74.524063</v>
       </c>
       <c r="H603" t="n">
         <v>115.2481</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H604" t="n">
         <v>115.5662</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>75.14109000000001</v>
+        <v>75.141098</v>
       </c>
       <c r="H605" t="n">
         <v>116.2024</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>75.27821400000001</v>
+        <v>75.278206</v>
       </c>
       <c r="H606" t="n">
         <v>116.4144</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>75.003967</v>
+        <v>75.00398300000001</v>
       </c>
       <c r="H608" t="n">
         <v>115.9903</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>73.358543</v>
+        <v>73.35855100000001</v>
       </c>
       <c r="H609" t="n">
         <v>113.4457</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>72.721931</v>
+        <v>72.721924</v>
       </c>
       <c r="H614" t="n">
         <v>112.4612</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H615" t="n">
         <v>112.022</v>
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H620" t="n">
         <v>110.5933</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H621" t="n">
         <v>109.5734</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H623" t="n">
         <v>110.4259</v>
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H626" t="n">
         <v>110.4259</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H629" t="n">
         <v>112.4048</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H631" t="n">
         <v>112.0395</v>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G633" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H633" t="n">
         <v>114.3534</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H634" t="n">
         <v>114.0946</v>
@@ -24582,7 +24582,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H636" t="n">
         <v>114.1707</v>
@@ -24658,10 +24658,10 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H638" t="n">
-        <v>114.1402</v>
+        <v>114.1403</v>
       </c>
     </row>
     <row r="639">
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H642" t="n">
         <v>114.1707</v>
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G645" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H645" t="n">
         <v>113.714</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H646" t="n">
         <v>114.1098</v>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H648" t="n">
         <v>115.0993</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H651" t="n">
         <v>116.1953</v>
@@ -25190,10 +25190,10 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H652" t="n">
-        <v>115.419</v>
+        <v>115.4189</v>
       </c>
     </row>
     <row r="653">
@@ -25266,10 +25266,10 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H654" t="n">
-        <v>115.419</v>
+        <v>115.4189</v>
       </c>
     </row>
     <row r="655">
@@ -25456,7 +25456,7 @@
         </is>
       </c>
       <c r="G659" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H659" t="n">
         <v>116.1344</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H664" t="n">
         <v>119.2246</v>
@@ -25722,7 +25722,7 @@
         </is>
       </c>
       <c r="G666" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H666" t="n">
         <v>118.4178</v>
@@ -25798,10 +25798,10 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H668" t="n">
-        <v>117.9612</v>
+        <v>117.9611</v>
       </c>
     </row>
     <row r="669">
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H669" t="n">
         <v>117.8089</v>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H674" t="n">
         <v>118.4483</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H675" t="n">
         <v>117.748</v>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G681" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H681" t="n">
         <v>121.1732</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.339996</v>
+        <v>80.099998</v>
       </c>
       <c r="H755" t="n">
-        <v>124.2422</v>
+        <v>123.8711</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>128.899994</v>
+        <v>129.139999</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.2089</v>
+        <v>120.4327</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>128.899994</v>
+        <v>129.139999</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.2089</v>
+        <v>120.4327</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>128.899994</v>
+        <v>129.139999</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.2089</v>
+        <v>120.4327</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.497272</v>
+        <v>54.497269</v>
       </c>
       <c r="H1510" t="n">
         <v>101.212</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.799221</v>
+        <v>54.799225</v>
       </c>
       <c r="H1511" t="n">
         <v>101.7728</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>55.062214</v>
+        <v>55.062218</v>
       </c>
       <c r="H1512" t="n">
         <v>102.2612</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>55.042736</v>
+        <v>55.042732</v>
       </c>
       <c r="H1513" t="n">
         <v>102.225</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.974548</v>
+        <v>54.974552</v>
       </c>
       <c r="H1514" t="n">
         <v>102.0984</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1515" t="n">
         <v>102.8944</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.159615</v>
+        <v>55.159622</v>
       </c>
       <c r="H1516" t="n">
         <v>102.4421</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.536232</v>
+        <v>54.536236</v>
       </c>
       <c r="H1519" t="n">
         <v>101.2844</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.818707</v>
+        <v>54.818699</v>
       </c>
       <c r="H1520" t="n">
         <v>101.809</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1524" t="n">
         <v>102.8944</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1525" t="n">
         <v>102.6592</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1527" t="n">
         <v>103.5456</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1528" t="n">
         <v>103.3285</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.169357</v>
+        <v>55.169353</v>
       </c>
       <c r="H1533" t="n">
         <v>102.4602</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1534" t="n">
         <v>102.6592</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1537" t="n">
         <v>102.8582</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1538" t="n">
         <v>104.1968</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1540" t="n">
         <v>104.2692</v>
@@ -59010,10 +59010,10 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.305717</v>
+        <v>55.305721</v>
       </c>
       <c r="H1542" t="n">
-        <v>102.7134</v>
+        <v>102.7135</v>
       </c>
     </row>
     <row r="1543">
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1543" t="n">
         <v>100.9226</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1544" t="n">
         <v>100.8321</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.351162</v>
+        <v>54.35117</v>
       </c>
       <c r="H1546" t="n">
         <v>100.9407</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1547" t="n">
         <v>101.0673</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1550" t="n">
         <v>103.2019</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1551" t="n">
         <v>103.5456</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1552" t="n">
         <v>103.2019</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1553" t="n">
         <v>103.3285</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.72456</v>
+        <v>55.724556</v>
       </c>
       <c r="H1554" t="n">
         <v>103.4913</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.958332</v>
+        <v>55.958324</v>
       </c>
       <c r="H1555" t="n">
         <v>103.9255</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.987545</v>
+        <v>55.987541</v>
       </c>
       <c r="H1556" t="n">
         <v>103.9797</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1557" t="n">
         <v>103.8169</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1558" t="n">
         <v>103.7084</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>56.172611</v>
+        <v>56.172607</v>
       </c>
       <c r="H1560" t="n">
         <v>104.3234</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.851185</v>
+        <v>55.851177</v>
       </c>
       <c r="H1561" t="n">
         <v>103.7265</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.294872</v>
+        <v>56.294876</v>
       </c>
       <c r="H1562" t="n">
         <v>104.5505</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1563" t="n">
         <v>104.1149</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1564" t="n">
         <v>103.9878</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.676041</v>
+        <v>56.676037</v>
       </c>
       <c r="H1567" t="n">
         <v>105.2584</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1569" t="n">
         <v>105.8029</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1572" t="n">
         <v>108.1081</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>58.53299</v>
+        <v>58.532986</v>
       </c>
       <c r="H1573" t="n">
         <v>108.7071</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1574" t="n">
         <v>108.6708</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>59.031437</v>
+        <v>59.031433</v>
       </c>
       <c r="H1576" t="n">
         <v>109.6328</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.129169</v>
+        <v>59.129166</v>
       </c>
       <c r="H1577" t="n">
         <v>109.8143</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1580" t="n">
         <v>110.4859</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1581" t="n">
         <v>110.5041</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>58.259331</v>
+        <v>58.259335</v>
       </c>
       <c r="H1584" t="n">
         <v>108.1989</v>
@@ -60682,10 +60682,10 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.86528</v>
+        <v>58.865284</v>
       </c>
       <c r="H1586" t="n">
-        <v>109.3242</v>
+        <v>109.3243</v>
       </c>
     </row>
     <row r="1587">
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>60.155373</v>
+        <v>60.155376</v>
       </c>
       <c r="H1597" t="n">
         <v>111.7202</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1599" t="n">
         <v>111.811</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1600" t="n">
         <v>111.3027</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1602" t="n">
         <v>111.3209</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1603" t="n">
         <v>111.9199</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.956799</v>
+        <v>60.956791</v>
       </c>
       <c r="H1604" t="n">
         <v>113.2086</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>61.201126</v>
+        <v>61.20113</v>
       </c>
       <c r="H1606" t="n">
         <v>113.6624</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1607" t="n">
         <v>113.0452</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>61.015434</v>
+        <v>61.015438</v>
       </c>
       <c r="H1608" t="n">
         <v>113.3175</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>61.474785</v>
+        <v>61.474789</v>
       </c>
       <c r="H1609" t="n">
         <v>114.1706</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.445465</v>
+        <v>61.445469</v>
       </c>
       <c r="H1611" t="n">
         <v>114.1162</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>58.640495</v>
+        <v>58.640491</v>
       </c>
       <c r="H1613" t="n">
         <v>108.9068</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>59.393051</v>
+        <v>59.393047</v>
       </c>
       <c r="H1614" t="n">
         <v>110.3044</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1616" t="n">
         <v>107.8177</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1617" t="n">
         <v>107.0735</v>
@@ -61898,10 +61898,10 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1618" t="n">
-        <v>109.1791</v>
+        <v>109.179</v>
       </c>
     </row>
     <row r="1619">
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.4548</v>
+        <v>58.454803</v>
       </c>
       <c r="H1619" t="n">
         <v>108.5619</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>58.112728</v>
+        <v>58.112732</v>
       </c>
       <c r="H1620" t="n">
         <v>107.9266</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>57.790211</v>
+        <v>57.790207</v>
       </c>
       <c r="H1621" t="n">
         <v>107.3276</v>
@@ -62088,10 +62088,10 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1623" t="n">
-        <v>108.5159</v>
+        <v>108.516</v>
       </c>
     </row>
     <row r="1624">
@@ -62810,7 +62810,7 @@
         </is>
       </c>
       <c r="G1642" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1642" t="n">
         <v>111.7183</v>
@@ -62886,7 +62886,7 @@
         </is>
       </c>
       <c r="G1644" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1644" t="n">
         <v>113.4468</v>
@@ -62962,7 +62962,7 @@
         </is>
       </c>
       <c r="G1646" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1646" t="n">
         <v>111.5727</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1648" t="n">
         <v>111.3362</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1649" t="n">
         <v>110.7358</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1652" t="n">
         <v>109.4803</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1655" t="n">
         <v>110.9359</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1656" t="n">
         <v>113.3923</v>
@@ -63418,10 +63418,10 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1658" t="n">
-        <v>111.5364</v>
+        <v>111.5363</v>
       </c>
     </row>
     <row r="1659">
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1660" t="n">
         <v>110.5174</v>
@@ -63874,10 +63874,10 @@
         </is>
       </c>
       <c r="G1670" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1670" t="n">
-        <v>114.9207</v>
+        <v>114.9206</v>
       </c>
     </row>
     <row r="1671">
@@ -63950,7 +63950,7 @@
         </is>
       </c>
       <c r="G1672" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1672" t="n">
         <v>114.4294</v>
@@ -64064,10 +64064,10 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1675" t="n">
-        <v>114.5568</v>
+        <v>114.5567</v>
       </c>
     </row>
     <row r="1676">
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1677" t="n">
         <v>114.4294</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1678" t="n">
         <v>113.9745</v>
@@ -64330,7 +64330,7 @@
         </is>
       </c>
       <c r="G1682" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1682" t="n">
         <v>113.8289</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.099998</v>
+        <v>62.869999</v>
       </c>
       <c r="H1760" t="n">
-        <v>117.1889</v>
+        <v>116.7618</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.511246</v>
+        <v>65.511253</v>
       </c>
       <c r="H508" t="n">
         <v>101.3102</v>
@@ -19756,10 +19756,10 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>65.65733299999999</v>
+        <v>65.657341</v>
       </c>
       <c r="H509" t="n">
-        <v>101.5361</v>
+        <v>101.5362</v>
       </c>
     </row>
     <row r="510">
@@ -19794,10 +19794,10 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>65.65733299999999</v>
+        <v>65.657341</v>
       </c>
       <c r="H510" t="n">
-        <v>101.5361</v>
+        <v>101.5362</v>
       </c>
     </row>
     <row r="511">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.910538</v>
+        <v>65.91052999999999</v>
       </c>
       <c r="H512" t="n">
         <v>101.9277</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.199623</v>
+        <v>65.19961499999999</v>
       </c>
       <c r="H514" t="n">
         <v>100.8283</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.111977</v>
+        <v>65.111969</v>
       </c>
       <c r="H515" t="n">
         <v>100.6928</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.84236900000001</v>
+        <v>65.842361</v>
       </c>
       <c r="H519" t="n">
         <v>101.8223</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>65.939751</v>
+        <v>65.939758</v>
       </c>
       <c r="H521" t="n">
         <v>101.9729</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H523" t="n">
         <v>102.6958</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H526" t="n">
         <v>102.6958</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H528" t="n">
         <v>102.1536</v>
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>65.579414</v>
+        <v>65.57942199999999</v>
       </c>
       <c r="H532" t="n">
-        <v>101.4156</v>
+        <v>101.4157</v>
       </c>
     </row>
     <row r="533">
@@ -20668,10 +20668,10 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H533" t="n">
-        <v>102.6356</v>
+        <v>102.6355</v>
       </c>
     </row>
     <row r="534">
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H534" t="n">
         <v>103.5241</v>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H535" t="n">
-        <v>104.4879</v>
+        <v>104.488</v>
       </c>
     </row>
     <row r="536">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H536" t="n">
         <v>103.7048</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H537" t="n">
         <v>103.2681</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>65.715767</v>
+        <v>65.71577499999999</v>
       </c>
       <c r="H540" t="n">
         <v>101.6265</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>65.89106</v>
+        <v>65.891068</v>
       </c>
       <c r="H542" t="n">
         <v>101.8976</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H545" t="n">
         <v>103.6145</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.962311</v>
+        <v>66.96229599999999</v>
       </c>
       <c r="H546" t="n">
         <v>103.5542</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H548" t="n">
         <v>103.7048</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H550" t="n">
         <v>103.5241</v>
@@ -21352,10 +21352,10 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H551" t="n">
-        <v>104.1867</v>
+        <v>104.1868</v>
       </c>
     </row>
     <row r="552">
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H559" t="n">
         <v>103.8705</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.23497</v>
+        <v>67.234978</v>
       </c>
       <c r="H560" t="n">
         <v>103.9759</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H562" t="n">
         <v>104.9941</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.304733</v>
+        <v>68.30474100000001</v>
       </c>
       <c r="H566" t="n">
         <v>105.6302</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H567" t="n">
         <v>105.9635</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>69.773865</v>
+        <v>69.773872</v>
       </c>
       <c r="H569" t="n">
         <v>107.9022</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>70.18523399999999</v>
+        <v>70.185226</v>
       </c>
       <c r="H573" t="n">
         <v>108.5383</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>71.340935</v>
+        <v>71.340942</v>
       </c>
       <c r="H576" t="n">
         <v>110.3256</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H577" t="n">
         <v>110.2499</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H579" t="n">
         <v>108.3566</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.371323</v>
+        <v>70.371315</v>
       </c>
       <c r="H580" t="n">
         <v>108.8261</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H581" t="n">
         <v>109.5986</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.518227</v>
+        <v>70.51823400000001</v>
       </c>
       <c r="H582" t="n">
         <v>109.0533</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.410484</v>
+        <v>70.410492</v>
       </c>
       <c r="H584" t="n">
         <v>108.8867</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>70.68472300000001</v>
+        <v>70.684731</v>
       </c>
       <c r="H586" t="n">
         <v>109.3108</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>72.87863900000001</v>
+        <v>72.878632</v>
       </c>
       <c r="H590" t="n">
         <v>112.7036</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H591" t="n">
         <v>111.8857</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H593" t="n">
         <v>113.37</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H595" t="n">
         <v>114.6271</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>73.86784400000001</v>
+        <v>73.867851</v>
       </c>
       <c r="H599" t="n">
         <v>114.2333</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H600" t="n">
         <v>115.2027</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H601" t="n">
         <v>115.2027</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>74.524063</v>
+        <v>74.52404799999999</v>
       </c>
       <c r="H603" t="n">
         <v>115.2481</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H604" t="n">
         <v>115.5662</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>75.141098</v>
+        <v>75.14109000000001</v>
       </c>
       <c r="H605" t="n">
         <v>116.2024</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>75.278206</v>
+        <v>75.27821400000001</v>
       </c>
       <c r="H606" t="n">
         <v>116.4144</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>75.00398300000001</v>
+        <v>75.003975</v>
       </c>
       <c r="H608" t="n">
         <v>115.9903</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>72.721924</v>
+        <v>72.721931</v>
       </c>
       <c r="H614" t="n">
         <v>112.4612</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H615" t="n">
         <v>112.022</v>
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>72.55542800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H616" t="n">
         <v>112.2037</v>
@@ -23936,10 +23936,10 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>72.64357</v>
+        <v>72.64357800000001</v>
       </c>
       <c r="H619" t="n">
-        <v>112.34</v>
+        <v>112.3401</v>
       </c>
     </row>
     <row r="620">
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H620" t="n">
         <v>110.5933</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H621" t="n">
         <v>109.5734</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H623" t="n">
         <v>110.4259</v>
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H626" t="n">
         <v>110.4259</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H629" t="n">
         <v>112.4048</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H631" t="n">
         <v>112.0395</v>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G633" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H633" t="n">
         <v>114.3534</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H634" t="n">
         <v>114.0946</v>
@@ -24582,7 +24582,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H636" t="n">
         <v>114.1707</v>
@@ -24658,10 +24658,10 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H638" t="n">
-        <v>114.1403</v>
+        <v>114.1402</v>
       </c>
     </row>
     <row r="639">
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H642" t="n">
         <v>114.1707</v>
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G645" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H645" t="n">
         <v>113.714</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H646" t="n">
         <v>114.1098</v>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H648" t="n">
         <v>115.0993</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H651" t="n">
         <v>116.1953</v>
@@ -25190,10 +25190,10 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H652" t="n">
-        <v>115.4189</v>
+        <v>115.419</v>
       </c>
     </row>
     <row r="653">
@@ -25266,10 +25266,10 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H654" t="n">
-        <v>115.4189</v>
+        <v>115.419</v>
       </c>
     </row>
     <row r="655">
@@ -25456,7 +25456,7 @@
         </is>
       </c>
       <c r="G659" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H659" t="n">
         <v>116.1344</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H664" t="n">
         <v>119.2246</v>
@@ -25722,7 +25722,7 @@
         </is>
       </c>
       <c r="G666" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H666" t="n">
         <v>118.4178</v>
@@ -25798,10 +25798,10 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H668" t="n">
-        <v>117.9611</v>
+        <v>117.9612</v>
       </c>
     </row>
     <row r="669">
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H669" t="n">
         <v>117.8089</v>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H674" t="n">
         <v>118.4483</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H675" t="n">
         <v>117.748</v>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G681" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H681" t="n">
         <v>121.1732</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.497269</v>
+        <v>54.497272</v>
       </c>
       <c r="H1510" t="n">
         <v>101.212</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.799225</v>
+        <v>54.799221</v>
       </c>
       <c r="H1511" t="n">
         <v>101.7728</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>55.062218</v>
+        <v>55.062214</v>
       </c>
       <c r="H1512" t="n">
         <v>102.2612</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>55.042732</v>
+        <v>55.042736</v>
       </c>
       <c r="H1513" t="n">
         <v>102.225</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.974552</v>
+        <v>54.974548</v>
       </c>
       <c r="H1514" t="n">
         <v>102.0984</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1515" t="n">
         <v>102.8944</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.159622</v>
+        <v>55.159615</v>
       </c>
       <c r="H1516" t="n">
         <v>102.4421</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.536236</v>
+        <v>54.536232</v>
       </c>
       <c r="H1519" t="n">
         <v>101.2844</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.818699</v>
+        <v>54.818707</v>
       </c>
       <c r="H1520" t="n">
         <v>101.809</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1524" t="n">
         <v>102.8944</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1525" t="n">
         <v>102.6592</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1527" t="n">
         <v>103.5456</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1528" t="n">
         <v>103.3285</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.169353</v>
+        <v>55.169357</v>
       </c>
       <c r="H1533" t="n">
         <v>102.4602</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1534" t="n">
         <v>102.6592</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1537" t="n">
         <v>102.8582</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>56.104431</v>
+        <v>56.104427</v>
       </c>
       <c r="H1538" t="n">
         <v>104.1968</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>56.143391</v>
+        <v>56.143394</v>
       </c>
       <c r="H1540" t="n">
         <v>104.2692</v>
@@ -59010,10 +59010,10 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.305721</v>
+        <v>55.305717</v>
       </c>
       <c r="H1542" t="n">
-        <v>102.7135</v>
+        <v>102.7134</v>
       </c>
     </row>
     <row r="1543">
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1543" t="n">
         <v>100.9226</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1544" t="n">
         <v>100.8321</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.35117</v>
+        <v>54.351162</v>
       </c>
       <c r="H1546" t="n">
         <v>100.9407</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1547" t="n">
         <v>101.0673</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1550" t="n">
         <v>103.2019</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1551" t="n">
         <v>103.5456</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1552" t="n">
         <v>103.2019</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1553" t="n">
         <v>103.3285</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.724556</v>
+        <v>55.72456</v>
       </c>
       <c r="H1554" t="n">
         <v>103.4913</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.958324</v>
+        <v>55.958332</v>
       </c>
       <c r="H1555" t="n">
         <v>103.9255</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.987541</v>
+        <v>55.987545</v>
       </c>
       <c r="H1556" t="n">
         <v>103.9797</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1557" t="n">
         <v>103.8169</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.841446</v>
+        <v>55.841442</v>
       </c>
       <c r="H1558" t="n">
         <v>103.7084</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>56.172607</v>
+        <v>56.172611</v>
       </c>
       <c r="H1560" t="n">
         <v>104.3234</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.851177</v>
+        <v>55.851185</v>
       </c>
       <c r="H1561" t="n">
         <v>103.7265</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1562" t="n">
         <v>104.5505</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1563" t="n">
         <v>104.1149</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1564" t="n">
         <v>103.9878</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.676037</v>
+        <v>56.676041</v>
       </c>
       <c r="H1567" t="n">
         <v>105.2584</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1569" t="n">
         <v>105.8029</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1572" t="n">
         <v>108.1081</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1573" t="n">
         <v>108.7071</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1574" t="n">
         <v>108.6708</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1576" t="n">
         <v>109.6328</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1577" t="n">
         <v>109.8143</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1580" t="n">
         <v>110.4859</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1581" t="n">
         <v>110.5041</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>58.259335</v>
+        <v>58.259331</v>
       </c>
       <c r="H1584" t="n">
         <v>108.1989</v>
@@ -60682,10 +60682,10 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1586" t="n">
-        <v>109.3243</v>
+        <v>109.3242</v>
       </c>
     </row>
     <row r="1587">
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>60.155376</v>
+        <v>60.155373</v>
       </c>
       <c r="H1597" t="n">
         <v>111.7202</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1599" t="n">
         <v>111.811</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1600" t="n">
         <v>111.3027</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1602" t="n">
         <v>111.3209</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1603" t="n">
         <v>111.9199</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.956791</v>
+        <v>60.956799</v>
       </c>
       <c r="H1604" t="n">
         <v>113.2086</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>61.20113</v>
+        <v>61.201126</v>
       </c>
       <c r="H1606" t="n">
         <v>113.6624</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1607" t="n">
         <v>113.0452</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1608" t="n">
         <v>113.3175</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>61.474789</v>
+        <v>61.474785</v>
       </c>
       <c r="H1609" t="n">
         <v>114.1706</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.445469</v>
+        <v>61.445465</v>
       </c>
       <c r="H1611" t="n">
         <v>114.1162</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>58.640491</v>
+        <v>58.640495</v>
       </c>
       <c r="H1613" t="n">
         <v>108.9068</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1614" t="n">
         <v>110.3044</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1616" t="n">
         <v>107.8177</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1617" t="n">
         <v>107.0735</v>
@@ -61898,10 +61898,10 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1618" t="n">
-        <v>109.179</v>
+        <v>109.1791</v>
       </c>
     </row>
     <row r="1619">
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1619" t="n">
         <v>108.5619</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1620" t="n">
         <v>107.9266</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>57.790207</v>
+        <v>57.790211</v>
       </c>
       <c r="H1621" t="n">
         <v>107.3276</v>
@@ -62088,10 +62088,10 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1623" t="n">
-        <v>108.516</v>
+        <v>108.5159</v>
       </c>
     </row>
     <row r="1624">
@@ -62810,7 +62810,7 @@
         </is>
       </c>
       <c r="G1642" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1642" t="n">
         <v>111.7183</v>
@@ -62886,7 +62886,7 @@
         </is>
       </c>
       <c r="G1644" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1644" t="n">
         <v>113.4468</v>
@@ -62962,7 +62962,7 @@
         </is>
       </c>
       <c r="G1646" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1646" t="n">
         <v>111.5727</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1648" t="n">
         <v>111.3362</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1649" t="n">
         <v>110.7358</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1652" t="n">
         <v>109.4803</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1655" t="n">
         <v>110.9359</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1656" t="n">
         <v>113.3923</v>
@@ -63418,10 +63418,10 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1658" t="n">
-        <v>111.5363</v>
+        <v>111.5364</v>
       </c>
     </row>
     <row r="1659">
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1660" t="n">
         <v>110.5174</v>
@@ -63874,10 +63874,10 @@
         </is>
       </c>
       <c r="G1670" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1670" t="n">
-        <v>114.9206</v>
+        <v>114.9207</v>
       </c>
     </row>
     <row r="1671">
@@ -63950,7 +63950,7 @@
         </is>
       </c>
       <c r="G1672" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1672" t="n">
         <v>114.4294</v>
@@ -64064,10 +64064,10 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1675" t="n">
-        <v>114.5567</v>
+        <v>114.5568</v>
       </c>
     </row>
     <row r="1676">
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1677" t="n">
         <v>114.4294</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1678" t="n">
         <v>113.9745</v>
@@ -64330,7 +64330,7 @@
         </is>
       </c>
       <c r="G1682" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1682" t="n">
         <v>113.8289</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.511253</v>
+        <v>65.511246</v>
       </c>
       <c r="H508" t="n">
         <v>101.3102</v>
@@ -19756,10 +19756,10 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>65.657341</v>
+        <v>65.65733299999999</v>
       </c>
       <c r="H509" t="n">
-        <v>101.5362</v>
+        <v>101.5361</v>
       </c>
     </row>
     <row r="510">
@@ -19794,10 +19794,10 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>65.657341</v>
+        <v>65.65733299999999</v>
       </c>
       <c r="H510" t="n">
-        <v>101.5362</v>
+        <v>101.5361</v>
       </c>
     </row>
     <row r="511">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H512" t="n">
         <v>101.9277</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H513" t="n">
         <v>100.3163</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.19961499999999</v>
+        <v>65.199623</v>
       </c>
       <c r="H514" t="n">
         <v>100.8283</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H515" t="n">
         <v>100.6928</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.842361</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H519" t="n">
         <v>101.8223</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.212433</v>
+        <v>66.212425</v>
       </c>
       <c r="H525" t="n">
         <v>102.3946</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H527" t="n">
         <v>102.2139</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H529" t="n">
         <v>102.2139</v>
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>65.57942199999999</v>
+        <v>65.579414</v>
       </c>
       <c r="H532" t="n">
-        <v>101.4157</v>
+        <v>101.4156</v>
       </c>
     </row>
     <row r="533">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H536" t="n">
         <v>103.7048</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H537" t="n">
         <v>103.2681</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H542" t="n">
         <v>101.8976</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.124786</v>
+        <v>66.124779</v>
       </c>
       <c r="H543" t="n">
         <v>102.259</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.96229599999999</v>
+        <v>66.96230300000001</v>
       </c>
       <c r="H546" t="n">
         <v>103.5542</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H548" t="n">
         <v>103.7048</v>
@@ -21352,10 +21352,10 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.371323</v>
+        <v>67.371315</v>
       </c>
       <c r="H551" t="n">
-        <v>104.1868</v>
+        <v>104.1867</v>
       </c>
     </row>
     <row r="552">
@@ -21390,10 +21390,10 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H552" t="n">
-        <v>104.4127</v>
+        <v>104.4126</v>
       </c>
     </row>
     <row r="553">
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.3908</v>
+        <v>67.390793</v>
       </c>
       <c r="H557" t="n">
         <v>104.2169</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H558" t="n">
         <v>104.8042</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H562" t="n">
         <v>104.9941</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275352</v>
       </c>
       <c r="H565" t="n">
         <v>105.5848</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H567" t="n">
         <v>105.9635</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>70.645554</v>
+        <v>70.645561</v>
       </c>
       <c r="H575" t="n">
         <v>109.2502</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H577" t="n">
         <v>110.2499</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H579" t="n">
         <v>108.3566</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H581" t="n">
         <v>109.5986</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.51823400000001</v>
+        <v>70.518227</v>
       </c>
       <c r="H582" t="n">
         <v>109.0533</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.410492</v>
+        <v>70.410484</v>
       </c>
       <c r="H584" t="n">
         <v>108.8867</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.890411</v>
+        <v>70.890404</v>
       </c>
       <c r="H587" t="n">
         <v>109.6289</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H588" t="n">
         <v>110.8557</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>72.37912799999999</v>
+        <v>72.37913500000001</v>
       </c>
       <c r="H589" t="n">
         <v>111.9311</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H590" t="n">
         <v>112.7036</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H591" t="n">
         <v>111.8857</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H593" t="n">
         <v>113.37</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H595" t="n">
         <v>114.6271</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H603" t="n">
         <v>115.2481</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H604" t="n">
         <v>115.5662</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>75.14109000000001</v>
+        <v>75.141098</v>
       </c>
       <c r="H605" t="n">
         <v>116.2024</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>75.27821400000001</v>
+        <v>75.278206</v>
       </c>
       <c r="H606" t="n">
         <v>116.4144</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>75.003975</v>
+        <v>75.00398300000001</v>
       </c>
       <c r="H608" t="n">
         <v>115.9903</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H611" t="n">
         <v>113.0671</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H618" t="n">
         <v>113.0671</v>
@@ -23936,10 +23936,10 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>72.64357800000001</v>
+        <v>72.64357</v>
       </c>
       <c r="H619" t="n">
-        <v>112.3401</v>
+        <v>112.34</v>
       </c>
     </row>
     <row r="620">
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H620" t="n">
         <v>110.5933</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H621" t="n">
         <v>109.5734</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H623" t="n">
         <v>110.4259</v>
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H626" t="n">
         <v>110.4259</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H629" t="n">
         <v>112.4048</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H631" t="n">
         <v>112.0395</v>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G633" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H633" t="n">
         <v>114.3534</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H634" t="n">
         <v>114.0946</v>
@@ -24582,7 +24582,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H636" t="n">
         <v>114.1707</v>
@@ -24658,10 +24658,10 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H638" t="n">
-        <v>114.1402</v>
+        <v>114.1403</v>
       </c>
     </row>
     <row r="639">
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H642" t="n">
         <v>114.1707</v>
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G645" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H645" t="n">
         <v>113.714</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H646" t="n">
         <v>114.1098</v>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H648" t="n">
         <v>115.0993</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H651" t="n">
         <v>116.1953</v>
@@ -25190,10 +25190,10 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H652" t="n">
-        <v>115.419</v>
+        <v>115.4189</v>
       </c>
     </row>
     <row r="653">
@@ -25266,10 +25266,10 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H654" t="n">
-        <v>115.419</v>
+        <v>115.4189</v>
       </c>
     </row>
     <row r="655">
@@ -25456,7 +25456,7 @@
         </is>
       </c>
       <c r="G659" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H659" t="n">
         <v>116.1344</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H664" t="n">
         <v>119.2246</v>
@@ -25722,7 +25722,7 @@
         </is>
       </c>
       <c r="G666" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H666" t="n">
         <v>118.4178</v>
@@ -25798,10 +25798,10 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H668" t="n">
-        <v>117.9612</v>
+        <v>117.9611</v>
       </c>
     </row>
     <row r="669">
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H669" t="n">
         <v>117.8089</v>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H674" t="n">
         <v>118.4483</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H675" t="n">
         <v>117.748</v>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G681" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H681" t="n">
         <v>121.1732</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.497272</v>
+        <v>54.497276</v>
       </c>
       <c r="H1510" t="n">
         <v>101.212</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.799221</v>
+        <v>54.799225</v>
       </c>
       <c r="H1511" t="n">
         <v>101.7728</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>55.042736</v>
+        <v>55.042732</v>
       </c>
       <c r="H1513" t="n">
         <v>102.225</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1515" t="n">
         <v>102.8944</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.159615</v>
+        <v>55.159618</v>
       </c>
       <c r="H1516" t="n">
         <v>102.4421</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.740788</v>
+        <v>54.74078</v>
       </c>
       <c r="H1518" t="n">
         <v>101.6643</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.536232</v>
+        <v>54.53624</v>
       </c>
       <c r="H1519" t="n">
         <v>101.2844</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1520" t="n">
         <v>101.809</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1521" t="n">
         <v>102.623</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1523" t="n">
         <v>102.623</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1524" t="n">
         <v>102.8944</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.276505</v>
+        <v>55.276497</v>
       </c>
       <c r="H1525" t="n">
         <v>102.6592</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1527" t="n">
         <v>103.5456</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1530" t="n">
         <v>103.1295</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.276505</v>
+        <v>55.276497</v>
       </c>
       <c r="H1534" t="n">
         <v>102.6592</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>54.867409</v>
+        <v>54.867413</v>
       </c>
       <c r="H1535" t="n">
         <v>101.8994</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1537" t="n">
         <v>102.8582</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>56.523262</v>
+        <v>56.523266</v>
       </c>
       <c r="H1539" t="n">
         <v>104.9747</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1540" t="n">
         <v>104.2692</v>
@@ -59010,10 +59010,10 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.305717</v>
+        <v>55.305721</v>
       </c>
       <c r="H1542" t="n">
-        <v>102.7134</v>
+        <v>102.7135</v>
       </c>
     </row>
     <row r="1543">
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1543" t="n">
         <v>100.9226</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1544" t="n">
         <v>100.8321</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>54.487534</v>
+        <v>54.48753</v>
       </c>
       <c r="H1545" t="n">
         <v>101.1939</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.351162</v>
+        <v>54.35117</v>
       </c>
       <c r="H1546" t="n">
         <v>100.9407</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1547" t="n">
         <v>101.0673</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1549" t="n">
         <v>103.1295</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1550" t="n">
         <v>103.2019</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1551" t="n">
         <v>103.5456</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1552" t="n">
         <v>103.2019</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.72456</v>
+        <v>55.724556</v>
       </c>
       <c r="H1554" t="n">
         <v>103.4913</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.958332</v>
+        <v>55.958328</v>
       </c>
       <c r="H1555" t="n">
         <v>103.9255</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.987545</v>
+        <v>55.987541</v>
       </c>
       <c r="H1556" t="n">
         <v>103.9797</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.841442</v>
+        <v>55.841438</v>
       </c>
       <c r="H1558" t="n">
         <v>103.7084</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1561" t="n">
         <v>103.7265</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1563" t="n">
         <v>104.1149</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1566" t="n">
         <v>105.4581</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1569" t="n">
         <v>105.8029</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>58.53299</v>
+        <v>58.532986</v>
       </c>
       <c r="H1573" t="n">
         <v>108.7071</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1574" t="n">
         <v>108.6708</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.129169</v>
+        <v>59.129162</v>
       </c>
       <c r="H1577" t="n">
         <v>109.8143</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1579" t="n">
         <v>109.8506</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1580" t="n">
         <v>110.4859</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1581" t="n">
         <v>110.5041</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1583" t="n">
         <v>108.2352</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>58.259331</v>
+        <v>58.259335</v>
       </c>
       <c r="H1584" t="n">
         <v>108.1989</v>
@@ -60682,10 +60682,10 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.86528</v>
+        <v>58.865284</v>
       </c>
       <c r="H1586" t="n">
-        <v>109.3242</v>
+        <v>109.3243</v>
       </c>
     </row>
     <row r="1587">
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.305092</v>
+        <v>59.305088</v>
       </c>
       <c r="H1588" t="n">
         <v>110.1411</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>60.11628</v>
+        <v>60.116283</v>
       </c>
       <c r="H1598" t="n">
         <v>111.6476</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1599" t="n">
         <v>111.811</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1600" t="n">
         <v>111.3027</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1602" t="n">
         <v>111.3209</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1603" t="n">
         <v>111.9199</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.956799</v>
+        <v>60.956791</v>
       </c>
       <c r="H1604" t="n">
         <v>113.2086</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1607" t="n">
         <v>113.0452</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>61.474785</v>
+        <v>61.474789</v>
       </c>
       <c r="H1609" t="n">
         <v>114.1706</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.445465</v>
+        <v>61.445469</v>
       </c>
       <c r="H1611" t="n">
         <v>114.1162</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1616" t="n">
         <v>107.8177</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1617" t="n">
         <v>107.0735</v>
@@ -61898,10 +61898,10 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1618" t="n">
-        <v>109.1791</v>
+        <v>109.179</v>
       </c>
     </row>
     <row r="1619">
@@ -62088,10 +62088,10 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1623" t="n">
-        <v>108.5159</v>
+        <v>108.516</v>
       </c>
     </row>
     <row r="1624">
@@ -62810,7 +62810,7 @@
         </is>
       </c>
       <c r="G1642" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1642" t="n">
         <v>111.7183</v>
@@ -62886,7 +62886,7 @@
         </is>
       </c>
       <c r="G1644" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1644" t="n">
         <v>113.4468</v>
@@ -62962,7 +62962,7 @@
         </is>
       </c>
       <c r="G1646" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1646" t="n">
         <v>111.5727</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1648" t="n">
         <v>111.3362</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1649" t="n">
         <v>110.7358</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1652" t="n">
         <v>109.4803</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1655" t="n">
         <v>110.9359</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1656" t="n">
         <v>113.3923</v>
@@ -63418,10 +63418,10 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1658" t="n">
-        <v>111.5364</v>
+        <v>111.5363</v>
       </c>
     </row>
     <row r="1659">
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1660" t="n">
         <v>110.5174</v>
@@ -63874,10 +63874,10 @@
         </is>
       </c>
       <c r="G1670" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1670" t="n">
-        <v>114.9207</v>
+        <v>114.9206</v>
       </c>
     </row>
     <row r="1671">
@@ -63950,7 +63950,7 @@
         </is>
       </c>
       <c r="G1672" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1672" t="n">
         <v>114.4294</v>
@@ -64064,10 +64064,10 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1675" t="n">
-        <v>114.5568</v>
+        <v>114.5567</v>
       </c>
     </row>
     <row r="1676">
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1677" t="n">
         <v>114.4294</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1678" t="n">
         <v>113.9745</v>
@@ -64330,7 +64330,7 @@
         </is>
       </c>
       <c r="G1682" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1682" t="n">
         <v>113.8289</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.48</v>
+        <v>34.535</v>
       </c>
       <c r="H253" t="n">
-        <v>120.414</v>
+        <v>117.2069</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.279999</v>
+        <v>48.580002</v>
       </c>
       <c r="H504" t="n">
-        <v>131.16</v>
+        <v>131.975</v>
       </c>
     </row>
     <row r="505">
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H507" t="n">
         <v>100.7681</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.511246</v>
+        <v>65.511253</v>
       </c>
       <c r="H508" t="n">
         <v>101.3102</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H513" t="n">
         <v>100.3163</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.199623</v>
+        <v>65.19961499999999</v>
       </c>
       <c r="H514" t="n">
         <v>100.8283</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.111977</v>
+        <v>65.111969</v>
       </c>
       <c r="H515" t="n">
         <v>100.6928</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.84236900000001</v>
+        <v>65.842361</v>
       </c>
       <c r="H519" t="n">
         <v>101.8223</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H523" t="n">
         <v>102.6958</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H526" t="n">
         <v>102.6958</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.095581</v>
+        <v>66.095573</v>
       </c>
       <c r="H527" t="n">
         <v>102.2139</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.095581</v>
+        <v>66.095573</v>
       </c>
       <c r="H529" t="n">
         <v>102.2139</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>65.988449</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H531" t="n">
         <v>102.0482</v>
@@ -20630,10 +20630,10 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>65.579414</v>
+        <v>65.57942199999999</v>
       </c>
       <c r="H532" t="n">
-        <v>101.4156</v>
+        <v>101.4157</v>
       </c>
     </row>
     <row r="533">
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H534" t="n">
         <v>103.5241</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H536" t="n">
         <v>103.7048</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H537" t="n">
         <v>103.2681</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>65.71577499999999</v>
+        <v>65.715767</v>
       </c>
       <c r="H540" t="n">
         <v>101.6265</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>65.89106</v>
+        <v>65.891068</v>
       </c>
       <c r="H542" t="n">
         <v>101.8976</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.124779</v>
+        <v>66.124786</v>
       </c>
       <c r="H543" t="n">
         <v>102.259</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H548" t="n">
         <v>103.7048</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.87464900000001</v>
+        <v>66.874657</v>
       </c>
       <c r="H549" t="n">
         <v>103.4187</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H550" t="n">
         <v>103.5241</v>
@@ -21352,10 +21352,10 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H551" t="n">
-        <v>104.1867</v>
+        <v>104.1868</v>
       </c>
     </row>
     <row r="552">
@@ -21390,10 +21390,10 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.51739499999999</v>
+        <v>67.517403</v>
       </c>
       <c r="H552" t="n">
-        <v>104.4126</v>
+        <v>104.4127</v>
       </c>
     </row>
     <row r="553">
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.283669</v>
+        <v>67.283661</v>
       </c>
       <c r="H553" t="n">
         <v>104.0512</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H559" t="n">
         <v>103.8705</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H562" t="n">
         <v>104.9941</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>68.275352</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H565" t="n">
         <v>105.5848</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H567" t="n">
         <v>105.9635</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>70.645561</v>
+        <v>70.645554</v>
       </c>
       <c r="H575" t="n">
         <v>109.2502</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H577" t="n">
         <v>110.2499</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H579" t="n">
         <v>108.3566</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H581" t="n">
         <v>109.5986</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.518227</v>
+        <v>70.51823400000001</v>
       </c>
       <c r="H582" t="n">
         <v>109.0533</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>70.410484</v>
+        <v>70.410492</v>
       </c>
       <c r="H584" t="n">
         <v>108.8867</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>70.890404</v>
+        <v>70.890411</v>
       </c>
       <c r="H587" t="n">
         <v>109.6289</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H588" t="n">
         <v>110.8557</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>72.37913500000001</v>
+        <v>72.37912799999999</v>
       </c>
       <c r="H589" t="n">
         <v>111.9311</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>72.87863900000001</v>
+        <v>72.878632</v>
       </c>
       <c r="H590" t="n">
         <v>112.7036</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H591" t="n">
         <v>111.8857</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H593" t="n">
         <v>113.37</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H595" t="n">
         <v>114.6271</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>74.524055</v>
+        <v>74.52404799999999</v>
       </c>
       <c r="H603" t="n">
         <v>115.2481</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H604" t="n">
         <v>115.5662</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>75.141098</v>
+        <v>75.14109000000001</v>
       </c>
       <c r="H605" t="n">
         <v>116.2024</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>75.278206</v>
+        <v>75.27821400000001</v>
       </c>
       <c r="H606" t="n">
         <v>116.4144</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>75.00398300000001</v>
+        <v>75.003975</v>
       </c>
       <c r="H608" t="n">
         <v>115.9903</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>73.11370100000001</v>
+        <v>73.113693</v>
       </c>
       <c r="H611" t="n">
         <v>113.0671</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>73.11370100000001</v>
+        <v>73.113693</v>
       </c>
       <c r="H618" t="n">
         <v>113.0671</v>
@@ -23936,10 +23936,10 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>72.64357</v>
+        <v>72.64357800000001</v>
       </c>
       <c r="H619" t="n">
-        <v>112.34</v>
+        <v>112.3401</v>
       </c>
     </row>
     <row r="620">
@@ -23974,7 +23974,7 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H620" t="n">
         <v>110.5933</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H621" t="n">
         <v>109.5734</v>
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H623" t="n">
         <v>110.4259</v>
@@ -24202,7 +24202,7 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H626" t="n">
         <v>110.4259</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H629" t="n">
         <v>112.4048</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H631" t="n">
         <v>112.0395</v>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G633" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H633" t="n">
         <v>114.3534</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H634" t="n">
         <v>114.0946</v>
@@ -24582,7 +24582,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H636" t="n">
         <v>114.1707</v>
@@ -24658,10 +24658,10 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H638" t="n">
-        <v>114.1403</v>
+        <v>114.1402</v>
       </c>
     </row>
     <row r="639">
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H642" t="n">
         <v>114.1707</v>
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G645" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H645" t="n">
         <v>113.714</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H646" t="n">
         <v>114.1098</v>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H648" t="n">
         <v>115.0993</v>
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="G651" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H651" t="n">
         <v>116.1953</v>
@@ -25190,10 +25190,10 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H652" t="n">
-        <v>115.4189</v>
+        <v>115.419</v>
       </c>
     </row>
     <row r="653">
@@ -25266,10 +25266,10 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H654" t="n">
-        <v>115.4189</v>
+        <v>115.419</v>
       </c>
     </row>
     <row r="655">
@@ -25456,7 +25456,7 @@
         </is>
       </c>
       <c r="G659" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H659" t="n">
         <v>116.1344</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H664" t="n">
         <v>119.2246</v>
@@ -25722,7 +25722,7 @@
         </is>
       </c>
       <c r="G666" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H666" t="n">
         <v>118.4178</v>
@@ -25798,10 +25798,10 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H668" t="n">
-        <v>117.9611</v>
+        <v>117.9612</v>
       </c>
     </row>
     <row r="669">
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H669" t="n">
         <v>117.8089</v>
@@ -26026,7 +26026,7 @@
         </is>
       </c>
       <c r="G674" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H674" t="n">
         <v>118.4483</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H675" t="n">
         <v>117.748</v>
@@ -26292,7 +26292,7 @@
         </is>
       </c>
       <c r="G681" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H681" t="n">
         <v>121.1732</v>
@@ -29075,7 +29075,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.099998</v>
+        <v>80.19000200000001</v>
       </c>
       <c r="H755" t="n">
-        <v>123.8711</v>
+        <v>124.0103</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>129.139999</v>
+        <v>128.690002</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.4327</v>
+        <v>120.0131</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>129.139999</v>
+        <v>128.690002</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.4327</v>
+        <v>120.0131</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>129.139999</v>
+        <v>128.690002</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.4327</v>
+        <v>120.0131</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.497276</v>
+        <v>54.497272</v>
       </c>
       <c r="H1510" t="n">
         <v>101.212</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.799225</v>
+        <v>54.799221</v>
       </c>
       <c r="H1511" t="n">
         <v>101.7728</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.974548</v>
+        <v>54.974545</v>
       </c>
       <c r="H1514" t="n">
         <v>102.0984</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.159618</v>
+        <v>55.159615</v>
       </c>
       <c r="H1516" t="n">
         <v>102.4421</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.74078</v>
+        <v>54.740784</v>
       </c>
       <c r="H1518" t="n">
         <v>101.6643</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.53624</v>
+        <v>54.536232</v>
       </c>
       <c r="H1519" t="n">
         <v>101.2844</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.818703</v>
+        <v>54.818707</v>
       </c>
       <c r="H1520" t="n">
         <v>101.809</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1521" t="n">
         <v>102.623</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>54.682339</v>
+        <v>54.682335</v>
       </c>
       <c r="H1522" t="n">
         <v>101.5557</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1523" t="n">
         <v>102.623</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.276497</v>
+        <v>55.276505</v>
       </c>
       <c r="H1525" t="n">
         <v>102.6592</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1527" t="n">
         <v>103.5456</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1528" t="n">
         <v>103.3285</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1530" t="n">
         <v>103.1295</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>55.276497</v>
+        <v>55.276505</v>
       </c>
       <c r="H1534" t="n">
         <v>102.6592</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>54.867413</v>
+        <v>54.867405</v>
       </c>
       <c r="H1535" t="n">
         <v>101.8994</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>54.584934</v>
+        <v>54.584938</v>
       </c>
       <c r="H1536" t="n">
         <v>101.3748</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1537" t="n">
         <v>102.8582</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1538" t="n">
         <v>104.1968</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>56.523266</v>
+        <v>56.523262</v>
       </c>
       <c r="H1539" t="n">
         <v>104.9747</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>56.143391</v>
+        <v>56.143394</v>
       </c>
       <c r="H1540" t="n">
         <v>104.2692</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1543" t="n">
         <v>100.9226</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1545" t="n">
         <v>101.1939</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.35117</v>
+        <v>54.351166</v>
       </c>
       <c r="H1546" t="n">
         <v>100.9407</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.419353</v>
+        <v>54.419346</v>
       </c>
       <c r="H1547" t="n">
         <v>101.0673</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1549" t="n">
         <v>103.1295</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1550" t="n">
         <v>103.2019</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1551" t="n">
         <v>103.5456</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1552" t="n">
         <v>103.2019</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1553" t="n">
         <v>103.3285</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.724556</v>
+        <v>55.72456</v>
       </c>
       <c r="H1554" t="n">
         <v>103.4913</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.958328</v>
+        <v>55.958332</v>
       </c>
       <c r="H1555" t="n">
         <v>103.9255</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.987541</v>
+        <v>55.987545</v>
       </c>
       <c r="H1556" t="n">
         <v>103.9797</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.841438</v>
+        <v>55.841442</v>
       </c>
       <c r="H1558" t="n">
         <v>103.7084</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.870663</v>
+        <v>55.870667</v>
       </c>
       <c r="H1559" t="n">
         <v>103.7627</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1561" t="n">
         <v>103.7265</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1563" t="n">
         <v>104.1149</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1566" t="n">
         <v>105.4581</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1569" t="n">
         <v>105.8029</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1573" t="n">
         <v>108.7071</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1574" t="n">
         <v>108.6708</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.129162</v>
+        <v>59.129169</v>
       </c>
       <c r="H1577" t="n">
         <v>109.8143</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1579" t="n">
         <v>109.8506</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1580" t="n">
         <v>110.4859</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1581" t="n">
         <v>110.5041</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1583" t="n">
         <v>108.2352</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>58.259335</v>
+        <v>58.259331</v>
       </c>
       <c r="H1584" t="n">
         <v>108.1989</v>
@@ -60682,10 +60682,10 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1586" t="n">
-        <v>109.3243</v>
+        <v>109.3242</v>
       </c>
     </row>
     <row r="1587">
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1588" t="n">
         <v>110.1411</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>60.116283</v>
+        <v>60.11628</v>
       </c>
       <c r="H1598" t="n">
         <v>111.6476</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1599" t="n">
         <v>111.811</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1600" t="n">
         <v>111.3027</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1602" t="n">
         <v>111.3209</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1603" t="n">
         <v>111.9199</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>60.956791</v>
+        <v>60.956799</v>
       </c>
       <c r="H1604" t="n">
         <v>113.2086</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1607" t="n">
         <v>113.0452</v>
@@ -61556,7 +61556,7 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>61.474789</v>
+        <v>61.474785</v>
       </c>
       <c r="H1609" t="n">
         <v>114.1706</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>61.445469</v>
+        <v>61.445465</v>
       </c>
       <c r="H1611" t="n">
         <v>114.1162</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1616" t="n">
         <v>107.8177</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1617" t="n">
         <v>107.0735</v>
@@ -61898,10 +61898,10 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1618" t="n">
-        <v>109.179</v>
+        <v>109.1791</v>
       </c>
     </row>
     <row r="1619">
@@ -62088,10 +62088,10 @@
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1623" t="n">
-        <v>108.516</v>
+        <v>108.5159</v>
       </c>
     </row>
     <row r="1624">
@@ -62810,7 +62810,7 @@
         </is>
       </c>
       <c r="G1642" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1642" t="n">
         <v>111.7183</v>
@@ -62886,7 +62886,7 @@
         </is>
       </c>
       <c r="G1644" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1644" t="n">
         <v>113.4468</v>
@@ -62962,7 +62962,7 @@
         </is>
       </c>
       <c r="G1646" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1646" t="n">
         <v>111.5727</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1648" t="n">
         <v>111.3362</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1649" t="n">
         <v>110.7358</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1652" t="n">
         <v>109.4803</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1655" t="n">
         <v>110.9359</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1656" t="n">
         <v>113.3923</v>
@@ -63418,10 +63418,10 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1658" t="n">
-        <v>111.5363</v>
+        <v>111.5364</v>
       </c>
     </row>
     <row r="1659">
@@ -63494,7 +63494,7 @@
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1660" t="n">
         <v>110.5174</v>
@@ -63874,10 +63874,10 @@
         </is>
       </c>
       <c r="G1670" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1670" t="n">
-        <v>114.9206</v>
+        <v>114.9207</v>
       </c>
     </row>
     <row r="1671">
@@ -63950,7 +63950,7 @@
         </is>
       </c>
       <c r="G1672" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1672" t="n">
         <v>114.4294</v>
@@ -64064,10 +64064,10 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1675" t="n">
-        <v>114.5567</v>
+        <v>114.5568</v>
       </c>
     </row>
     <row r="1676">
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1677" t="n">
         <v>114.4294</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1678" t="n">
         <v>113.9745</v>
@@ -64330,7 +64330,7 @@
         </is>
       </c>
       <c r="G1682" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1682" t="n">
         <v>113.8289</v>
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.869999</v>
+        <v>63.139999</v>
       </c>
       <c r="H1760" t="n">
-        <v>116.7618</v>
+        <v>117.2632</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>36.009998</v>
+        <v>35.880001</v>
       </c>
       <c r="H253" t="n">
-        <v>122.6916</v>
+        <v>122.2487</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.43</v>
+        <v>48.369999</v>
       </c>
       <c r="H504" t="n">
-        <v>130.3809</v>
+        <v>130.2194</v>
       </c>
     </row>
     <row r="505">
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>65.160667</v>
+        <v>65.160675</v>
       </c>
       <c r="H506" t="n">
         <v>99.9552</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>66.01767</v>
+        <v>66.017662</v>
       </c>
       <c r="H510" t="n">
         <v>101.2698</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.199631</v>
+        <v>65.199623</v>
       </c>
       <c r="H513" t="n">
         <v>100.0149</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.111977</v>
+        <v>65.11198400000001</v>
       </c>
       <c r="H514" t="n">
         <v>99.8805</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.559952</v>
+        <v>65.559944</v>
       </c>
       <c r="H516" t="n">
         <v>100.5677</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.121712</v>
+        <v>65.121719</v>
       </c>
       <c r="H517" t="n">
         <v>99.8954</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.84236900000001</v>
+        <v>65.842377</v>
       </c>
       <c r="H518" t="n">
         <v>101.0009</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>66.01767</v>
+        <v>66.017662</v>
       </c>
       <c r="H519" t="n">
         <v>101.2698</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.93974300000001</v>
+        <v>65.939758</v>
       </c>
       <c r="H520" t="n">
         <v>101.1503</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407211</v>
       </c>
       <c r="H522" t="n">
         <v>101.8673</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.339043</v>
+        <v>66.339035</v>
       </c>
       <c r="H523" t="n">
         <v>101.7628</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407211</v>
       </c>
       <c r="H525" t="n">
         <v>101.8673</v>
@@ -20706,10 +20706,10 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H534" t="n">
-        <v>103.6451</v>
+        <v>103.645</v>
       </c>
     </row>
     <row r="535">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.77726699999999</v>
+        <v>66.77726</v>
       </c>
       <c r="H536" t="n">
         <v>102.435</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.416939</v>
+        <v>66.41693100000001</v>
       </c>
       <c r="H537" t="n">
         <v>101.8823</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027405</v>
       </c>
       <c r="H540" t="n">
         <v>101.2847</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>65.89106</v>
+        <v>65.891068</v>
       </c>
       <c r="H541" t="n">
         <v>101.0756</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.124786</v>
+        <v>66.12479399999999</v>
       </c>
       <c r="H542" t="n">
         <v>101.4341</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.387733</v>
+        <v>66.387726</v>
       </c>
       <c r="H543" t="n">
         <v>101.8375</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H544" t="n">
         <v>102.7786</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.24472799999999</v>
+        <v>67.24472</v>
       </c>
       <c r="H546" t="n">
         <v>103.1521</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.87464900000001</v>
+        <v>66.874657</v>
       </c>
       <c r="H548" t="n">
         <v>102.5844</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.371323</v>
+        <v>67.371315</v>
       </c>
       <c r="H550" t="n">
         <v>103.3463</v>
@@ -21352,10 +21352,10 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H551" t="n">
-        <v>103.5704</v>
+        <v>103.5703</v>
       </c>
     </row>
     <row r="552">
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.283669</v>
+        <v>67.283661</v>
       </c>
       <c r="H552" t="n">
         <v>103.2118</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.225235</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H554" t="n">
         <v>103.1222</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.478455</v>
+        <v>67.478447</v>
       </c>
       <c r="H555" t="n">
         <v>103.5106</v>
@@ -21542,10 +21542,10 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.3908</v>
+        <v>67.390793</v>
       </c>
       <c r="H556" t="n">
-        <v>103.3762</v>
+        <v>103.3761</v>
       </c>
     </row>
     <row r="557">
@@ -21580,10 +21580,10 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.770599</v>
+        <v>67.77059199999999</v>
       </c>
       <c r="H557" t="n">
-        <v>103.9588</v>
+        <v>103.9587</v>
       </c>
     </row>
     <row r="558">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H558" t="n">
         <v>103.0326</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.23498499999999</v>
+        <v>67.234978</v>
       </c>
       <c r="H559" t="n">
         <v>103.1371</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.619148</v>
+        <v>67.619141</v>
       </c>
       <c r="H560" t="n">
         <v>103.7264</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H561" t="n">
         <v>104.1471</v>
@@ -21922,10 +21922,10 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H566" t="n">
-        <v>105.1086</v>
+        <v>105.1087</v>
       </c>
     </row>
     <row r="567">
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H567" t="n">
         <v>106.2204</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>70.273369</v>
+        <v>70.273376</v>
       </c>
       <c r="H573" t="n">
         <v>107.798</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H576" t="n">
         <v>109.3605</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H578" t="n">
         <v>107.4825</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.410492</v>
+        <v>70.4105</v>
       </c>
       <c r="H583" t="n">
         <v>108.0083</v>
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H587" t="n">
-        <v>109.9614</v>
+        <v>109.9615</v>
       </c>
     </row>
     <row r="588">
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H589" t="n">
         <v>111.7944</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H590" t="n">
         <v>110.9831</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H592" t="n">
         <v>112.4554</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H594" t="n">
         <v>113.7024</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>73.82867400000001</v>
+        <v>73.828667</v>
       </c>
       <c r="H596" t="n">
         <v>113.2517</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.887444</v>
+        <v>73.88743599999999</v>
       </c>
       <c r="H597" t="n">
         <v>113.3419</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H608" t="n">
         <v>112.5306</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>72.721924</v>
+        <v>72.721931</v>
       </c>
       <c r="H613" t="n">
         <v>111.554</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H614" t="n">
         <v>111.1183</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>79.470001</v>
+        <v>79.699997</v>
       </c>
       <c r="H755" t="n">
-        <v>121.9054</v>
+        <v>122.2582</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>128.529999</v>
+        <v>128.809998</v>
       </c>
       <c r="H1006" t="n">
-        <v>118.9652</v>
+        <v>119.2244</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>128.529999</v>
+        <v>128.809998</v>
       </c>
       <c r="H1257" t="n">
-        <v>118.9652</v>
+        <v>119.2244</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>128.529999</v>
+        <v>128.809998</v>
       </c>
       <c r="H1508" t="n">
-        <v>118.9652</v>
+        <v>119.2244</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.799225</v>
+        <v>54.799221</v>
       </c>
       <c r="H1510" t="n">
         <v>100.5541</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>55.062214</v>
+        <v>55.062218</v>
       </c>
       <c r="H1511" t="n">
         <v>101.0366</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.974548</v>
+        <v>54.974552</v>
       </c>
       <c r="H1513" t="n">
         <v>100.8758</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1514" t="n">
         <v>101.6622</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>55.159622</v>
+        <v>55.159618</v>
       </c>
       <c r="H1515" t="n">
         <v>101.2154</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.818699</v>
+        <v>54.818703</v>
       </c>
       <c r="H1519" t="n">
         <v>100.5898</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.682339</v>
+        <v>54.682343</v>
       </c>
       <c r="H1521" t="n">
         <v>100.3396</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1523" t="n">
         <v>101.6622</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1524" t="n">
-        <v>101.4298</v>
+        <v>101.4299</v>
       </c>
     </row>
     <row r="1525">
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1526" t="n">
         <v>102.3056</v>
@@ -58440,10 +58440,10 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1527" t="n">
-        <v>102.0911</v>
+        <v>102.0912</v>
       </c>
     </row>
     <row r="1528">
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.588196</v>
+        <v>55.588188</v>
       </c>
       <c r="H1528" t="n">
         <v>102.0018</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1530" t="n">
         <v>101.4656</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.325199</v>
+        <v>55.325203</v>
       </c>
       <c r="H1531" t="n">
         <v>101.5192</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.169353</v>
+        <v>55.169357</v>
       </c>
       <c r="H1532" t="n">
         <v>101.2332</v>
@@ -58668,10 +58668,10 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1533" t="n">
-        <v>101.4298</v>
+        <v>101.4299</v>
       </c>
     </row>
     <row r="1534">
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>56.104431</v>
+        <v>56.104427</v>
       </c>
       <c r="H1537" t="n">
         <v>102.9491</v>
@@ -58896,10 +58896,10 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>56.143391</v>
+        <v>56.143387</v>
       </c>
       <c r="H1539" t="n">
-        <v>103.0206</v>
+        <v>103.0205</v>
       </c>
     </row>
     <row r="1540">
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.60767</v>
+        <v>55.607674</v>
       </c>
       <c r="H1540" t="n">
         <v>102.0375</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>55.305725</v>
+        <v>55.305721</v>
       </c>
       <c r="H1541" t="n">
         <v>101.4835</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1543" t="n">
         <v>99.6247</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>54.35117</v>
+        <v>54.351166</v>
       </c>
       <c r="H1545" t="n">
         <v>99.7319</v>
@@ -59200,10 +59200,10 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.877148</v>
+        <v>54.877144</v>
       </c>
       <c r="H1547" t="n">
-        <v>100.6971</v>
+        <v>100.697</v>
       </c>
     </row>
     <row r="1548">
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1549" t="n">
         <v>101.966</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1550" t="n">
         <v>102.3056</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1551" t="n">
         <v>101.966</v>
@@ -59390,10 +59390,10 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1552" t="n">
-        <v>102.0911</v>
+        <v>102.0912</v>
       </c>
     </row>
     <row r="1553">
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.987541</v>
+        <v>55.987549</v>
       </c>
       <c r="H1555" t="n">
         <v>102.7346</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.870663</v>
+        <v>55.870659</v>
       </c>
       <c r="H1558" t="n">
         <v>102.5201</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1560" t="n">
         <v>102.4844</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1561" t="n">
         <v>103.2985</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1562" t="n">
         <v>102.8681</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1563" t="n">
         <v>102.7426</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.676037</v>
+        <v>56.676041</v>
       </c>
       <c r="H1566" t="n">
         <v>103.9979</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1568" t="n">
         <v>104.536</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1571" t="n">
         <v>106.8135</v>
@@ -60150,10 +60150,10 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1572" t="n">
-        <v>107.4053</v>
+        <v>107.4054</v>
       </c>
     </row>
     <row r="1573">
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1573" t="n">
         <v>107.3695</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1575" t="n">
         <v>108.32</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1576" t="n">
         <v>108.4993</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1579" t="n">
         <v>109.1629</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1580" t="n">
         <v>109.1808</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.259335</v>
+        <v>58.259331</v>
       </c>
       <c r="H1583" t="n">
         <v>106.9032</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1585" t="n">
         <v>108.0151</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>60.155376</v>
+        <v>60.155373</v>
       </c>
       <c r="H1596" t="n">
         <v>110.3824</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1598" t="n">
         <v>110.472</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1599" t="n">
         <v>109.9699</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1601" t="n">
         <v>109.9878</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1602" t="n">
         <v>110.5796</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.956791</v>
+        <v>60.956799</v>
       </c>
       <c r="H1603" t="n">
         <v>111.8529</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>61.20113</v>
+        <v>61.201126</v>
       </c>
       <c r="H1605" t="n">
         <v>112.3013</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1606" t="n">
         <v>111.6915</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1607" t="n">
         <v>111.9605</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>61.474789</v>
+        <v>61.474785</v>
       </c>
       <c r="H1608" t="n">
         <v>112.8034</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>61.445469</v>
+        <v>61.445465</v>
       </c>
       <c r="H1610" t="n">
         <v>112.7496</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>58.640491</v>
+        <v>58.640495</v>
       </c>
       <c r="H1612" t="n">
         <v>107.6026</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1613" t="n">
         <v>108.9835</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1615" t="n">
         <v>106.5266</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1616" t="n">
         <v>105.7913</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1617" t="n">
         <v>107.8716</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1618" t="n">
         <v>107.2619</v>
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1619" t="n">
         <v>106.6342</v>
@@ -61974,7 +61974,7 @@
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>57.790207</v>
+        <v>57.790211</v>
       </c>
       <c r="H1620" t="n">
         <v>106.0424</v>
@@ -62050,7 +62050,7 @@
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1622" t="n">
         <v>107.2165</v>
@@ -62772,7 +62772,7 @@
         </is>
       </c>
       <c r="G1641" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1641" t="n">
         <v>110.3805</v>
@@ -62848,7 +62848,7 @@
         </is>
       </c>
       <c r="G1643" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1643" t="n">
         <v>112.0883</v>
@@ -62924,7 +62924,7 @@
         </is>
       </c>
       <c r="G1645" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1645" t="n">
         <v>110.2367</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1647" t="n">
         <v>110.003</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1648" t="n">
         <v>109.4097</v>
@@ -63152,7 +63152,7 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1651" t="n">
         <v>108.1693</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1654" t="n">
         <v>109.6075</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1655" t="n">
         <v>112.0344</v>
@@ -63380,7 +63380,7 @@
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1657" t="n">
         <v>110.2007</v>
@@ -63456,7 +63456,7 @@
         </is>
       </c>
       <c r="G1659" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1659" t="n">
         <v>109.194</v>
@@ -63836,7 +63836,7 @@
         </is>
       </c>
       <c r="G1669" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1669" t="n">
         <v>113.5445</v>
@@ -63912,7 +63912,7 @@
         </is>
       </c>
       <c r="G1671" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1671" t="n">
         <v>113.0591</v>
@@ -64026,7 +64026,7 @@
         </is>
       </c>
       <c r="G1674" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1674" t="n">
         <v>113.1849</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1676" t="n">
         <v>113.0591</v>
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1677" t="n">
         <v>112.6097</v>
@@ -64292,10 +64292,10 @@
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1681" t="n">
-        <v>112.4659</v>
+        <v>112.4658</v>
       </c>
     </row>
     <row r="1682">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.139999</v>
+        <v>62.07</v>
       </c>
       <c r="H1760" t="n">
-        <v>114.0241</v>
+        <v>113.8956</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>65.189888</v>
+        <v>65.18988</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.910538</v>
+        <v>65.91052999999999</v>
       </c>
       <c r="H511" t="n">
         <v>101.1055</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H512" t="n">
         <v>99.50700000000001</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.11198400000001</v>
+        <v>65.111969</v>
       </c>
       <c r="H514" t="n">
         <v>99.8805</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.559944</v>
+        <v>65.559952</v>
       </c>
       <c r="H516" t="n">
         <v>100.5677</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.842377</v>
+        <v>65.842361</v>
       </c>
       <c r="H518" t="n">
         <v>101.0009</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H520" t="n">
         <v>101.1503</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.407211</v>
+        <v>66.407196</v>
       </c>
       <c r="H522" t="n">
         <v>101.8673</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H524" t="n">
         <v>101.5686</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.407211</v>
+        <v>66.407196</v>
       </c>
       <c r="H525" t="n">
         <v>101.8673</v>
@@ -20443,7 +20443,7 @@
         <v>66.056618</v>
       </c>
       <c r="H527" t="n">
-        <v>101.3295</v>
+        <v>101.3296</v>
       </c>
     </row>
     <row r="528">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H529" t="n">
         <v>101.6881</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>65.98844099999999</v>
+        <v>65.988449</v>
       </c>
       <c r="H530" t="n">
         <v>101.225</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H532" t="n">
         <v>101.8076</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H533" t="n">
         <v>102.689</v>
@@ -20709,7 +20709,7 @@
         <v>67.566086</v>
       </c>
       <c r="H534" t="n">
-        <v>103.645</v>
+        <v>103.6451</v>
       </c>
     </row>
     <row r="535">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.77726</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H536" t="n">
         <v>102.435</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.41693100000001</v>
+        <v>66.416939</v>
       </c>
       <c r="H537" t="n">
         <v>101.8823</v>
@@ -20858,10 +20858,10 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>65.754715</v>
+        <v>65.754723</v>
       </c>
       <c r="H538" t="n">
-        <v>100.8664</v>
+        <v>100.8665</v>
       </c>
     </row>
     <row r="539">
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.12479399999999</v>
+        <v>66.124786</v>
       </c>
       <c r="H542" t="n">
         <v>101.4341</v>
@@ -21127,7 +21127,7 @@
         <v>66.96230300000001</v>
       </c>
       <c r="H545" t="n">
-        <v>102.7188</v>
+        <v>102.7189</v>
       </c>
     </row>
     <row r="546">
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.874657</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H548" t="n">
         <v>102.5844</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H549" t="n">
         <v>102.689</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H550" t="n">
         <v>103.3463</v>
@@ -21355,7 +21355,7 @@
         <v>67.51739499999999</v>
       </c>
       <c r="H551" t="n">
-        <v>103.5703</v>
+        <v>103.5704</v>
       </c>
     </row>
     <row r="552">
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.283661</v>
+        <v>67.283669</v>
       </c>
       <c r="H552" t="n">
         <v>103.2118</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.29341100000001</v>
+        <v>67.293419</v>
       </c>
       <c r="H553" t="n">
         <v>103.2268</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.478447</v>
+        <v>67.47843899999999</v>
       </c>
       <c r="H555" t="n">
         <v>103.5106</v>
@@ -21542,10 +21542,10 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H556" t="n">
-        <v>103.3761</v>
+        <v>103.3762</v>
       </c>
     </row>
     <row r="557">
@@ -21583,7 +21583,7 @@
         <v>67.77059199999999</v>
       </c>
       <c r="H557" t="n">
-        <v>103.9587</v>
+        <v>103.9588</v>
       </c>
     </row>
     <row r="558">
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.234978</v>
+        <v>67.23497</v>
       </c>
       <c r="H559" t="n">
         <v>103.1371</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H564" t="n">
         <v>104.7331</v>
@@ -21960,10 +21960,10 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>69.24498</v>
+        <v>69.24498699999999</v>
       </c>
       <c r="H567" t="n">
-        <v>106.2204</v>
+        <v>106.2205</v>
       </c>
     </row>
     <row r="568">
@@ -21998,10 +21998,10 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>69.773865</v>
+        <v>69.773872</v>
       </c>
       <c r="H568" t="n">
-        <v>107.0317</v>
+        <v>107.0318</v>
       </c>
     </row>
     <row r="569">
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H570" t="n">
         <v>106.9116</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>70.18523399999999</v>
+        <v>70.185226</v>
       </c>
       <c r="H572" t="n">
         <v>107.6628</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.371323</v>
+        <v>70.371315</v>
       </c>
       <c r="H579" t="n">
         <v>107.9482</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>70.4105</v>
+        <v>70.410492</v>
       </c>
       <c r="H583" t="n">
         <v>108.0083</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H587" t="n">
         <v>109.9615</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>72.87863900000001</v>
+        <v>72.878632</v>
       </c>
       <c r="H589" t="n">
         <v>111.7944</v>
@@ -22913,7 +22913,7 @@
         <v>73.309578</v>
       </c>
       <c r="H592" t="n">
-        <v>112.4554</v>
+        <v>112.4555</v>
       </c>
     </row>
     <row r="593">
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H593" t="n">
         <v>112.8461</v>
@@ -22989,7 +22989,7 @@
         <v>74.12249799999999</v>
       </c>
       <c r="H594" t="n">
-        <v>113.7024</v>
+        <v>113.7025</v>
       </c>
     </row>
     <row r="595">
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H595" t="n">
         <v>113.2668</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.86784400000001</v>
+        <v>73.867851</v>
       </c>
       <c r="H598" t="n">
         <v>113.3118</v>
@@ -23255,7 +23255,7 @@
         <v>74.69055899999999</v>
       </c>
       <c r="H601" t="n">
-        <v>114.5738</v>
+        <v>114.5739</v>
       </c>
     </row>
     <row r="602">
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>74.524055</v>
+        <v>74.52404799999999</v>
       </c>
       <c r="H602" t="n">
         <v>114.3184</v>
@@ -23331,7 +23331,7 @@
         <v>74.729736</v>
       </c>
       <c r="H603" t="n">
-        <v>114.6339</v>
+        <v>114.634</v>
       </c>
     </row>
     <row r="604">
@@ -23369,7 +23369,7 @@
         <v>75.14109000000001</v>
       </c>
       <c r="H604" t="n">
-        <v>115.2649</v>
+        <v>115.265</v>
       </c>
     </row>
     <row r="605">
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>75.003967</v>
+        <v>75.003975</v>
       </c>
       <c r="H607" t="n">
         <v>115.0546</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>73.358543</v>
+        <v>73.35855100000001</v>
       </c>
       <c r="H608" t="n">
         <v>112.5306</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>72.55542800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H615" t="n">
         <v>111.2986</v>
@@ -23825,7 +23825,7 @@
         <v>72.780693</v>
       </c>
       <c r="H616" t="n">
-        <v>111.6441</v>
+        <v>111.6442</v>
       </c>
     </row>
     <row r="617">
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>72.64357</v>
+        <v>72.64357800000001</v>
       </c>
       <c r="H618" t="n">
         <v>111.4338</v>
@@ -26257,7 +26257,7 @@
         <v>78.355408</v>
       </c>
       <c r="H680" t="n">
-        <v>120.1956</v>
+        <v>120.1957</v>
       </c>
     </row>
     <row r="681">
@@ -26637,7 +26637,7 @@
         <v>78.451363</v>
       </c>
       <c r="H690" t="n">
-        <v>120.3428</v>
+        <v>120.3429</v>
       </c>
     </row>
     <row r="691">
@@ -27473,7 +27473,7 @@
         <v>80.112076</v>
       </c>
       <c r="H712" t="n">
-        <v>122.8903</v>
+        <v>122.8904</v>
       </c>
     </row>
     <row r="713">
@@ -27663,7 +27663,7 @@
         <v>81.00707199999999</v>
       </c>
       <c r="H717" t="n">
-        <v>124.2632</v>
+        <v>124.2633</v>
       </c>
     </row>
     <row r="718">
@@ -27777,7 +27777,7 @@
         <v>81.404854</v>
       </c>
       <c r="H720" t="n">
-        <v>124.8734</v>
+        <v>124.8735</v>
       </c>
     </row>
     <row r="721">
@@ -28157,7 +28157,7 @@
         <v>81.205963</v>
       </c>
       <c r="H730" t="n">
-        <v>124.5683</v>
+        <v>124.5684</v>
       </c>
     </row>
     <row r="731">
@@ -28651,7 +28651,7 @@
         <v>80.87779999999999</v>
       </c>
       <c r="H743" t="n">
-        <v>124.0649</v>
+        <v>124.065</v>
       </c>
     </row>
     <row r="744">
@@ -28841,7 +28841,7 @@
         <v>80.910004</v>
       </c>
       <c r="H748" t="n">
-        <v>124.1143</v>
+        <v>124.1144</v>
       </c>
     </row>
     <row r="749">
@@ -28917,7 +28917,7 @@
         <v>80.760002</v>
       </c>
       <c r="H750" t="n">
-        <v>123.8842</v>
+        <v>123.8843</v>
       </c>
     </row>
     <row r="751">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.799221</v>
+        <v>54.799225</v>
       </c>
       <c r="H1510" t="n">
         <v>100.5541</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>55.062218</v>
+        <v>55.06221</v>
       </c>
       <c r="H1511" t="n">
         <v>101.0366</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.974552</v>
+        <v>54.974548</v>
       </c>
       <c r="H1513" t="n">
         <v>100.8758</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>55.40313</v>
+        <v>55.403122</v>
       </c>
       <c r="H1514" t="n">
         <v>101.6622</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>55.159618</v>
+        <v>55.159622</v>
       </c>
       <c r="H1515" t="n">
         <v>101.2154</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.740784</v>
+        <v>54.74078</v>
       </c>
       <c r="H1517" t="n">
         <v>100.4468</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.818703</v>
+        <v>54.818707</v>
       </c>
       <c r="H1519" t="n">
         <v>100.5898</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1520" t="n">
         <v>101.3941</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>54.682343</v>
+        <v>54.682335</v>
       </c>
       <c r="H1521" t="n">
         <v>100.3396</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1522" t="n">
         <v>101.3941</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.40313</v>
+        <v>55.403122</v>
       </c>
       <c r="H1523" t="n">
         <v>101.6622</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1524" t="n">
-        <v>101.4299</v>
+        <v>101.4298</v>
       </c>
     </row>
     <row r="1525">
@@ -58516,10 +58516,10 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1529" t="n">
-        <v>101.8945</v>
+        <v>101.8946</v>
       </c>
     </row>
     <row r="1530">
@@ -58668,10 +58668,10 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1533" t="n">
-        <v>101.4299</v>
+        <v>101.4298</v>
       </c>
     </row>
     <row r="1534">
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>54.867409</v>
+        <v>54.867405</v>
       </c>
       <c r="H1534" t="n">
         <v>100.6792</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>54.584934</v>
+        <v>54.584938</v>
       </c>
       <c r="H1535" t="n">
         <v>100.1609</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1536" t="n">
         <v>101.6265</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>56.523262</v>
+        <v>56.523266</v>
       </c>
       <c r="H1538" t="n">
         <v>103.7176</v>
@@ -58896,10 +58896,10 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>56.143387</v>
+        <v>56.143394</v>
       </c>
       <c r="H1539" t="n">
-        <v>103.0205</v>
+        <v>103.0206</v>
       </c>
     </row>
     <row r="1540">
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>55.305721</v>
+        <v>55.305717</v>
       </c>
       <c r="H1541" t="n">
         <v>101.4835</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1542" t="n">
         <v>99.714</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.487534</v>
+        <v>54.48753</v>
       </c>
       <c r="H1544" t="n">
         <v>99.9821</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1546" t="n">
         <v>99.857</v>
@@ -59200,10 +59200,10 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.877144</v>
+        <v>54.877151</v>
       </c>
       <c r="H1547" t="n">
-        <v>100.697</v>
+        <v>100.6971</v>
       </c>
     </row>
     <row r="1548">
@@ -59238,10 +59238,10 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1548" t="n">
-        <v>101.8945</v>
+        <v>101.8946</v>
       </c>
     </row>
     <row r="1549">
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1549" t="n">
         <v>101.966</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1551" t="n">
         <v>101.966</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.987549</v>
+        <v>55.987545</v>
       </c>
       <c r="H1555" t="n">
         <v>102.7346</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1556" t="n">
         <v>102.5737</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.870659</v>
+        <v>55.870663</v>
       </c>
       <c r="H1558" t="n">
         <v>102.5201</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1560" t="n">
         <v>102.4844</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.294872</v>
+        <v>56.294876</v>
       </c>
       <c r="H1561" t="n">
         <v>103.2985</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1563" t="n">
         <v>102.7426</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.558758</v>
+        <v>56.558754</v>
       </c>
       <c r="H1564" t="n">
         <v>103.7827</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>56.676041</v>
+        <v>56.676044</v>
       </c>
       <c r="H1566" t="n">
         <v>103.9979</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1568" t="n">
         <v>104.536</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>57.692474</v>
+        <v>57.692471</v>
       </c>
       <c r="H1570" t="n">
         <v>105.863</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1571" t="n">
         <v>106.8135</v>
@@ -60150,10 +60150,10 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>58.53299</v>
+        <v>58.532986</v>
       </c>
       <c r="H1572" t="n">
-        <v>107.4054</v>
+        <v>107.4053</v>
       </c>
     </row>
     <row r="1573">
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1573" t="n">
         <v>107.3695</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>59.129169</v>
+        <v>59.129166</v>
       </c>
       <c r="H1576" t="n">
         <v>108.4993</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1578" t="n">
         <v>108.5352</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1579" t="n">
         <v>109.1629</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1580" t="n">
         <v>109.1808</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1582" t="n">
         <v>106.9391</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>58.86528</v>
+        <v>58.865284</v>
       </c>
       <c r="H1585" t="n">
         <v>108.0151</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.953243</v>
+        <v>58.953247</v>
       </c>
       <c r="H1586" t="n">
         <v>108.1765</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.305092</v>
+        <v>59.305088</v>
       </c>
       <c r="H1587" t="n">
         <v>108.8221</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1598" t="n">
         <v>110.472</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1601" t="n">
         <v>109.9878</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1602" t="n">
         <v>110.5796</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.956799</v>
+        <v>60.956795</v>
       </c>
       <c r="H1603" t="n">
         <v>111.8529</v>
@@ -61822,7 +61822,7 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1616" t="n">
         <v>105.7913</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1617" t="n">
         <v>107.8716</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>65.18988</v>
+        <v>65.189888</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H511" t="n">
         <v>101.1055</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H512" t="n">
         <v>99.50700000000001</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H514" t="n">
         <v>99.8805</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H517" t="n">
         <v>99.8954</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.842361</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H518" t="n">
         <v>101.0009</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H522" t="n">
         <v>101.8673</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H525" t="n">
         <v>101.8673</v>
@@ -20443,7 +20443,7 @@
         <v>66.056618</v>
       </c>
       <c r="H527" t="n">
-        <v>101.3296</v>
+        <v>101.3295</v>
       </c>
     </row>
     <row r="528">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H529" t="n">
         <v>101.6881</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>65.988449</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H530" t="n">
         <v>101.225</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368256</v>
       </c>
       <c r="H532" t="n">
         <v>101.8076</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H533" t="n">
         <v>102.689</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H534" t="n">
         <v>103.6451</v>
@@ -20858,10 +20858,10 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>65.754723</v>
+        <v>65.754715</v>
       </c>
       <c r="H538" t="n">
-        <v>100.8665</v>
+        <v>100.8664</v>
       </c>
     </row>
     <row r="539">
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H540" t="n">
         <v>101.2847</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H541" t="n">
         <v>101.0756</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H544" t="n">
         <v>102.7786</v>
@@ -21127,7 +21127,7 @@
         <v>66.96230300000001</v>
       </c>
       <c r="H545" t="n">
-        <v>102.7189</v>
+        <v>102.7188</v>
       </c>
     </row>
     <row r="546">
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H549" t="n">
         <v>102.689</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.51739499999999</v>
+        <v>67.517403</v>
       </c>
       <c r="H551" t="n">
         <v>103.5704</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.283669</v>
+        <v>67.283676</v>
       </c>
       <c r="H552" t="n">
         <v>103.2118</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.293419</v>
+        <v>67.293404</v>
       </c>
       <c r="H553" t="n">
         <v>103.2268</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.22524300000001</v>
+        <v>67.225235</v>
       </c>
       <c r="H554" t="n">
         <v>103.1222</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H555" t="n">
         <v>103.5106</v>
@@ -21542,10 +21542,10 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.3908</v>
+        <v>67.390793</v>
       </c>
       <c r="H556" t="n">
-        <v>103.3762</v>
+        <v>103.3761</v>
       </c>
     </row>
     <row r="557">
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H557" t="n">
         <v>103.9588</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.23497</v>
+        <v>67.23498499999999</v>
       </c>
       <c r="H559" t="n">
         <v>103.1371</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.619141</v>
+        <v>67.619148</v>
       </c>
       <c r="H560" t="n">
         <v>103.7264</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H561" t="n">
         <v>104.1471</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H564" t="n">
         <v>104.7331</v>
@@ -21922,10 +21922,10 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H566" t="n">
-        <v>105.1087</v>
+        <v>105.1086</v>
       </c>
     </row>
     <row r="567">
@@ -21963,7 +21963,7 @@
         <v>69.24498699999999</v>
       </c>
       <c r="H567" t="n">
-        <v>106.2205</v>
+        <v>106.2204</v>
       </c>
     </row>
     <row r="568">
@@ -21998,10 +21998,10 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H568" t="n">
-        <v>107.0318</v>
+        <v>107.0317</v>
       </c>
     </row>
     <row r="569">
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H570" t="n">
         <v>106.9116</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H572" t="n">
         <v>107.6628</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>70.273376</v>
+        <v>70.273369</v>
       </c>
       <c r="H573" t="n">
         <v>107.798</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H576" t="n">
         <v>109.3605</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H578" t="n">
         <v>107.4825</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H579" t="n">
         <v>107.9482</v>
@@ -22723,7 +22723,7 @@
         <v>71.683739</v>
       </c>
       <c r="H587" t="n">
-        <v>109.9615</v>
+        <v>109.9614</v>
       </c>
     </row>
     <row r="588">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H590" t="n">
         <v>110.9831</v>
@@ -22910,10 +22910,10 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H592" t="n">
-        <v>112.4555</v>
+        <v>112.4554</v>
       </c>
     </row>
     <row r="593">
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H593" t="n">
         <v>112.8461</v>
@@ -22986,10 +22986,10 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H594" t="n">
-        <v>113.7025</v>
+        <v>113.7024</v>
       </c>
     </row>
     <row r="595">
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H595" t="n">
         <v>113.2668</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>73.828667</v>
+        <v>73.82867400000001</v>
       </c>
       <c r="H596" t="n">
         <v>113.2517</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.88743599999999</v>
+        <v>73.887444</v>
       </c>
       <c r="H597" t="n">
         <v>113.3419</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H598" t="n">
         <v>113.3118</v>
@@ -23255,7 +23255,7 @@
         <v>74.69055899999999</v>
       </c>
       <c r="H601" t="n">
-        <v>114.5739</v>
+        <v>114.5738</v>
       </c>
     </row>
     <row r="602">
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H602" t="n">
         <v>114.3184</v>
@@ -23331,7 +23331,7 @@
         <v>74.729736</v>
       </c>
       <c r="H603" t="n">
-        <v>114.634</v>
+        <v>114.6339</v>
       </c>
     </row>
     <row r="604">
@@ -23369,7 +23369,7 @@
         <v>75.14109000000001</v>
       </c>
       <c r="H604" t="n">
-        <v>115.265</v>
+        <v>115.2649</v>
       </c>
     </row>
     <row r="605">
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H607" t="n">
         <v>115.0546</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>72.721931</v>
+        <v>72.721924</v>
       </c>
       <c r="H613" t="n">
         <v>111.554</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H614" t="n">
         <v>111.1183</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H615" t="n">
         <v>111.2986</v>
@@ -23825,7 +23825,7 @@
         <v>72.780693</v>
       </c>
       <c r="H616" t="n">
-        <v>111.6442</v>
+        <v>111.6441</v>
       </c>
     </row>
     <row r="617">
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>72.64357800000001</v>
+        <v>72.64357</v>
       </c>
       <c r="H618" t="n">
         <v>111.4338</v>
@@ -26257,7 +26257,7 @@
         <v>78.355408</v>
       </c>
       <c r="H680" t="n">
-        <v>120.1957</v>
+        <v>120.1956</v>
       </c>
     </row>
     <row r="681">
@@ -26637,7 +26637,7 @@
         <v>78.451363</v>
       </c>
       <c r="H690" t="n">
-        <v>120.3429</v>
+        <v>120.3428</v>
       </c>
     </row>
     <row r="691">
@@ -27473,7 +27473,7 @@
         <v>80.112076</v>
       </c>
       <c r="H712" t="n">
-        <v>122.8904</v>
+        <v>122.8903</v>
       </c>
     </row>
     <row r="713">
@@ -27663,7 +27663,7 @@
         <v>81.00707199999999</v>
       </c>
       <c r="H717" t="n">
-        <v>124.2633</v>
+        <v>124.2632</v>
       </c>
     </row>
     <row r="718">
@@ -27777,7 +27777,7 @@
         <v>81.404854</v>
       </c>
       <c r="H720" t="n">
-        <v>124.8735</v>
+        <v>124.8734</v>
       </c>
     </row>
     <row r="721">
@@ -28157,7 +28157,7 @@
         <v>81.205963</v>
       </c>
       <c r="H730" t="n">
-        <v>124.5684</v>
+        <v>124.5683</v>
       </c>
     </row>
     <row r="731">
@@ -28651,7 +28651,7 @@
         <v>80.87779999999999</v>
       </c>
       <c r="H743" t="n">
-        <v>124.065</v>
+        <v>124.0649</v>
       </c>
     </row>
     <row r="744">
@@ -28841,7 +28841,7 @@
         <v>80.910004</v>
       </c>
       <c r="H748" t="n">
-        <v>124.1144</v>
+        <v>124.1143</v>
       </c>
     </row>
     <row r="749">
@@ -28917,7 +28917,7 @@
         <v>80.760002</v>
       </c>
       <c r="H750" t="n">
-        <v>123.8843</v>
+        <v>123.8842</v>
       </c>
     </row>
     <row r="751">
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>55.06221</v>
+        <v>55.062214</v>
       </c>
       <c r="H1511" t="n">
         <v>101.0366</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>55.403122</v>
+        <v>55.403126</v>
       </c>
       <c r="H1514" t="n">
         <v>101.6622</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>55.159622</v>
+        <v>55.159618</v>
       </c>
       <c r="H1515" t="n">
         <v>101.2154</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.74078</v>
+        <v>54.740784</v>
       </c>
       <c r="H1517" t="n">
         <v>100.4468</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.403122</v>
+        <v>55.403126</v>
       </c>
       <c r="H1523" t="n">
         <v>101.6622</v>
@@ -58516,10 +58516,10 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1529" t="n">
-        <v>101.8946</v>
+        <v>101.8945</v>
       </c>
     </row>
     <row r="1530">
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>54.867405</v>
+        <v>54.867409</v>
       </c>
       <c r="H1534" t="n">
         <v>100.6792</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>54.584938</v>
+        <v>54.584934</v>
       </c>
       <c r="H1535" t="n">
         <v>100.1609</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>56.523266</v>
+        <v>56.523262</v>
       </c>
       <c r="H1538" t="n">
         <v>103.7176</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.607674</v>
+        <v>55.607677</v>
       </c>
       <c r="H1540" t="n">
         <v>102.0375</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>55.305717</v>
+        <v>55.305721</v>
       </c>
       <c r="H1541" t="n">
         <v>101.4835</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1543" t="n">
         <v>99.6247</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.877151</v>
+        <v>54.877148</v>
       </c>
       <c r="H1547" t="n">
         <v>100.6971</v>
@@ -59238,10 +59238,10 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1548" t="n">
-        <v>101.8946</v>
+        <v>101.8945</v>
       </c>
     </row>
     <row r="1549">
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1549" t="n">
         <v>101.966</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1551" t="n">
         <v>101.966</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.987545</v>
+        <v>55.987541</v>
       </c>
       <c r="H1555" t="n">
         <v>102.7346</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>35.880001</v>
+        <v>35.48</v>
       </c>
       <c r="H253" t="n">
-        <v>122.2487</v>
+        <v>120.8859</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.369999</v>
+        <v>48.279999</v>
       </c>
       <c r="H504" t="n">
-        <v>130.2194</v>
+        <v>129.9771</v>
       </c>
     </row>
     <row r="505">
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H506" t="n">
         <v>99.9552</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H512" t="n">
         <v>99.50700000000001</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.199623</v>
+        <v>65.19961499999999</v>
       </c>
       <c r="H513" t="n">
         <v>100.0149</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.111977</v>
+        <v>65.111969</v>
       </c>
       <c r="H514" t="n">
         <v>99.8805</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.121712</v>
+        <v>65.121719</v>
       </c>
       <c r="H517" t="n">
         <v>99.8954</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>65.84236900000001</v>
+        <v>65.842361</v>
       </c>
       <c r="H518" t="n">
         <v>101.0009</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>65.939751</v>
+        <v>65.939758</v>
       </c>
       <c r="H520" t="n">
         <v>101.1503</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.212433</v>
+        <v>66.212425</v>
       </c>
       <c r="H524" t="n">
         <v>101.5686</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H527" t="n">
         <v>101.3295</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H529" t="n">
         <v>101.6881</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H532" t="n">
         <v>101.8076</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H536" t="n">
         <v>102.435</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027405</v>
       </c>
       <c r="H540" t="n">
         <v>101.2847</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>65.89106</v>
+        <v>65.891068</v>
       </c>
       <c r="H541" t="n">
         <v>101.0756</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H544" t="n">
         <v>102.7786</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.87464900000001</v>
+        <v>66.874657</v>
       </c>
       <c r="H548" t="n">
         <v>102.5844</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.283676</v>
+        <v>67.283661</v>
       </c>
       <c r="H552" t="n">
         <v>103.2118</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.293404</v>
+        <v>67.29341100000001</v>
       </c>
       <c r="H553" t="n">
         <v>103.2268</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.225235</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H554" t="n">
         <v>103.1222</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H558" t="n">
         <v>103.0326</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.23498499999999</v>
+        <v>67.234978</v>
       </c>
       <c r="H559" t="n">
         <v>103.1371</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.619148</v>
+        <v>67.619141</v>
       </c>
       <c r="H560" t="n">
         <v>103.7264</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H561" t="n">
         <v>104.1471</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H564" t="n">
         <v>104.7331</v>
@@ -21922,10 +21922,10 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H566" t="n">
-        <v>105.1086</v>
+        <v>105.1087</v>
       </c>
     </row>
     <row r="567">
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>69.773865</v>
+        <v>69.773872</v>
       </c>
       <c r="H568" t="n">
         <v>107.0317</v>
@@ -22074,10 +22074,10 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H570" t="n">
-        <v>106.9116</v>
+        <v>106.9115</v>
       </c>
     </row>
     <row r="571">
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>70.18523399999999</v>
+        <v>70.185226</v>
       </c>
       <c r="H572" t="n">
         <v>107.6628</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>70.273369</v>
+        <v>70.273376</v>
       </c>
       <c r="H573" t="n">
         <v>107.798</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H576" t="n">
         <v>109.3605</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H578" t="n">
         <v>107.4825</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.371323</v>
+        <v>70.371315</v>
       </c>
       <c r="H579" t="n">
         <v>107.9482</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H590" t="n">
         <v>110.9831</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H592" t="n">
         <v>112.4554</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H593" t="n">
         <v>112.8461</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H594" t="n">
         <v>113.7024</v>
@@ -23024,10 +23024,10 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H595" t="n">
-        <v>113.2668</v>
+        <v>113.2667</v>
       </c>
     </row>
     <row r="596">
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>73.82867400000001</v>
+        <v>73.828667</v>
       </c>
       <c r="H596" t="n">
         <v>113.2517</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.887444</v>
+        <v>73.88743599999999</v>
       </c>
       <c r="H597" t="n">
         <v>113.3419</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>73.86784400000001</v>
+        <v>73.867851</v>
       </c>
       <c r="H598" t="n">
         <v>113.3118</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>74.524055</v>
+        <v>74.52404799999999</v>
       </c>
       <c r="H602" t="n">
         <v>114.3184</v>
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>75.003967</v>
+        <v>75.003975</v>
       </c>
       <c r="H607" t="n">
         <v>115.0546</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>72.721924</v>
+        <v>72.721931</v>
       </c>
       <c r="H613" t="n">
         <v>111.554</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H614" t="n">
         <v>111.1183</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>72.55542800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H615" t="n">
         <v>111.2986</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>72.64357</v>
+        <v>72.64357800000001</v>
       </c>
       <c r="H618" t="n">
         <v>111.4338</v>
@@ -29075,7 +29075,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>79.699997</v>
+        <v>80.099998</v>
       </c>
       <c r="H755" t="n">
-        <v>122.2582</v>
+        <v>122.8718</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>128.809998</v>
+        <v>129.139999</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.2244</v>
+        <v>119.5298</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>128.809998</v>
+        <v>129.139999</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.2244</v>
+        <v>119.5298</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>128.809998</v>
+        <v>129.139999</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.2244</v>
+        <v>119.5298</v>
       </c>
     </row>
     <row r="1509">
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>55.042732</v>
+        <v>55.042728</v>
       </c>
       <c r="H1512" t="n">
         <v>101.0009</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.974548</v>
+        <v>54.974545</v>
       </c>
       <c r="H1513" t="n">
         <v>100.8758</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.536236</v>
+        <v>54.536232</v>
       </c>
       <c r="H1518" t="n">
         <v>100.0715</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1519" t="n">
         <v>100.5898</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1524" t="n">
-        <v>101.4298</v>
+        <v>101.4299</v>
       </c>
     </row>
     <row r="1525">
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1526" t="n">
         <v>102.3056</v>
@@ -58440,10 +58440,10 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1527" t="n">
-        <v>102.0912</v>
+        <v>102.0911</v>
       </c>
     </row>
     <row r="1528">
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.588188</v>
+        <v>55.588192</v>
       </c>
       <c r="H1528" t="n">
         <v>102.0018</v>
@@ -58668,10 +58668,10 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1533" t="n">
-        <v>101.4298</v>
+        <v>101.4299</v>
       </c>
     </row>
     <row r="1534">
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1537" t="n">
         <v>102.9491</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.607677</v>
+        <v>55.607674</v>
       </c>
       <c r="H1540" t="n">
         <v>102.0375</v>
@@ -59200,10 +59200,10 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>54.877148</v>
+        <v>54.877144</v>
       </c>
       <c r="H1547" t="n">
-        <v>100.6971</v>
+        <v>100.697</v>
       </c>
     </row>
     <row r="1548">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1550" t="n">
         <v>102.3056</v>
@@ -59390,10 +59390,10 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1552" t="n">
-        <v>102.0912</v>
+        <v>102.0911</v>
       </c>
     </row>
     <row r="1553">
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.958328</v>
+        <v>55.958332</v>
       </c>
       <c r="H1554" t="n">
         <v>102.681</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.987541</v>
+        <v>55.987545</v>
       </c>
       <c r="H1555" t="n">
         <v>102.7346</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1556" t="n">
         <v>102.5737</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1557" t="n">
         <v>102.4665</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.870663</v>
+        <v>55.870667</v>
       </c>
       <c r="H1558" t="n">
         <v>102.5201</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>56.172611</v>
+        <v>56.172615</v>
       </c>
       <c r="H1559" t="n">
         <v>103.0742</v>
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.07</v>
+        <v>62.869999</v>
       </c>
       <c r="H1760" t="n">
-        <v>113.8956</v>
+        <v>115.3636</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>36.470001</v>
+        <v>36.23</v>
       </c>
       <c r="H253" t="n">
-        <v>123.753</v>
+        <v>122.9386</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>49.195</v>
+        <v>49.125</v>
       </c>
       <c r="H504" t="n">
-        <v>131.6254</v>
+        <v>131.4381</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>65.160675</v>
+        <v>65.160667</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>65.511246</v>
+        <v>65.511253</v>
       </c>
       <c r="H506" t="n">
         <v>100.538</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H509" t="n">
         <v>101.3152</v>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.868515</v>
+        <v>64.868523</v>
       </c>
       <c r="H511" t="n">
-        <v>99.55159999999999</v>
+        <v>99.5517</v>
       </c>
     </row>
     <row r="512">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.199623</v>
+        <v>65.199631</v>
       </c>
       <c r="H512" t="n">
         <v>100.0598</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.111977</v>
+        <v>65.111969</v>
       </c>
       <c r="H513" t="n">
         <v>99.92529999999999</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.540482</v>
+        <v>65.540474</v>
       </c>
       <c r="H514" t="n">
         <v>100.5829</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H516" t="n">
         <v>99.9402</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.84236900000001</v>
+        <v>65.842361</v>
       </c>
       <c r="H517" t="n">
         <v>101.0462</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H518" t="n">
         <v>101.3152</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.939758</v>
+        <v>65.93974300000001</v>
       </c>
       <c r="H519" t="n">
         <v>101.1956</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.06635300000001</v>
+        <v>66.06636</v>
       </c>
       <c r="H520" t="n">
         <v>101.3899</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.212433</v>
+        <v>66.212425</v>
       </c>
       <c r="H523" t="n">
         <v>101.6141</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.095581</v>
+        <v>66.095573</v>
       </c>
       <c r="H525" t="n">
         <v>101.4348</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H526" t="n">
         <v>101.375</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.095581</v>
+        <v>66.095573</v>
       </c>
       <c r="H527" t="n">
         <v>101.4348</v>
@@ -20519,7 +20519,7 @@
         <v>65.98844099999999</v>
       </c>
       <c r="H529" t="n">
-        <v>101.2703</v>
+        <v>101.2704</v>
       </c>
     </row>
     <row r="530">
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>65.579414</v>
+        <v>65.57942199999999</v>
       </c>
       <c r="H530" t="n">
         <v>100.6426</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368256</v>
       </c>
       <c r="H531" t="n">
         <v>101.8532</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H533" t="n">
         <v>103.6915</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>67.05970000000001</v>
+        <v>67.059692</v>
       </c>
       <c r="H534" t="n">
         <v>102.9144</v>
@@ -20785,7 +20785,7 @@
         <v>66.416939</v>
       </c>
       <c r="H536" t="n">
-        <v>101.9279</v>
+        <v>101.928</v>
       </c>
     </row>
     <row r="537">
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.754715</v>
+        <v>65.754707</v>
       </c>
       <c r="H537" t="n">
         <v>100.9117</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.124779</v>
+        <v>66.124786</v>
       </c>
       <c r="H541" t="n">
         <v>101.4796</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H543" t="n">
         <v>102.8247</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.962311</v>
+        <v>66.96230300000001</v>
       </c>
       <c r="H544" t="n">
         <v>102.7649</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.05970000000001</v>
+        <v>67.059692</v>
       </c>
       <c r="H546" t="n">
         <v>102.9144</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H549" t="n">
         <v>103.3926</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.51739499999999</v>
+        <v>67.517403</v>
       </c>
       <c r="H550" t="n">
         <v>103.6168</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.283669</v>
+        <v>67.283676</v>
       </c>
       <c r="H551" t="n">
         <v>103.2581</v>
@@ -21393,7 +21393,7 @@
         <v>67.29341100000001</v>
       </c>
       <c r="H552" t="n">
-        <v>103.273</v>
+        <v>103.2731</v>
       </c>
     </row>
     <row r="553">
@@ -21580,10 +21580,10 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H557" t="n">
-        <v>103.0787</v>
+        <v>103.0788</v>
       </c>
     </row>
     <row r="558">
@@ -21656,10 +21656,10 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.619141</v>
+        <v>67.619148</v>
       </c>
       <c r="H559" t="n">
-        <v>103.7729</v>
+        <v>103.773</v>
       </c>
     </row>
     <row r="560">
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>68.275352</v>
+        <v>68.275368</v>
       </c>
       <c r="H563" t="n">
         <v>104.78</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H567" t="n">
         <v>107.0797</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H569" t="n">
         <v>106.9595</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H571" t="n">
         <v>107.711</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>70.273376</v>
+        <v>70.273369</v>
       </c>
       <c r="H572" t="n">
         <v>107.8463</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>70.645561</v>
+        <v>70.645554</v>
       </c>
       <c r="H573" t="n">
         <v>108.4175</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H578" t="n">
         <v>107.9966</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H579" t="n">
         <v>108.7632</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.518227</v>
+        <v>70.51823400000001</v>
       </c>
       <c r="H580" t="n">
         <v>108.2221</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.410484</v>
+        <v>70.410492</v>
       </c>
       <c r="H582" t="n">
         <v>108.0567</v>
@@ -22644,10 +22644,10 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>70.890404</v>
+        <v>70.890411</v>
       </c>
       <c r="H585" t="n">
-        <v>108.7932</v>
+        <v>108.7933</v>
       </c>
     </row>
     <row r="586">
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H586" t="n">
         <v>110.0107</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>72.37913500000001</v>
+        <v>72.37912799999999</v>
       </c>
       <c r="H587" t="n">
         <v>111.0779</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>72.87863900000001</v>
+        <v>72.878632</v>
       </c>
       <c r="H588" t="n">
         <v>111.8445</v>
@@ -22799,7 +22799,7 @@
         <v>72.349754</v>
       </c>
       <c r="H589" t="n">
-        <v>111.0328</v>
+        <v>111.0329</v>
       </c>
     </row>
     <row r="590">
@@ -22875,7 +22875,7 @@
         <v>73.30956999999999</v>
       </c>
       <c r="H591" t="n">
-        <v>112.5058</v>
+        <v>112.5059</v>
       </c>
     </row>
     <row r="592">
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H592" t="n">
         <v>112.8967</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H594" t="n">
         <v>113.3175</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.828667</v>
+        <v>73.82867400000001</v>
       </c>
       <c r="H595" t="n">
         <v>113.3025</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>73.88743599999999</v>
+        <v>73.887444</v>
       </c>
       <c r="H596" t="n">
         <v>113.3927</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H597" t="n">
         <v>113.3626</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H602" t="n">
         <v>114.6853</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>75.141098</v>
+        <v>75.14109000000001</v>
       </c>
       <c r="H603" t="n">
         <v>115.3166</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>75.278206</v>
+        <v>75.27821400000001</v>
       </c>
       <c r="H604" t="n">
         <v>115.5271</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>75.00398300000001</v>
+        <v>75.003967</v>
       </c>
       <c r="H606" t="n">
         <v>115.1062</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>73.11370100000001</v>
+        <v>73.113693</v>
       </c>
       <c r="H609" t="n">
         <v>112.2053</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>72.721931</v>
+        <v>72.721924</v>
       </c>
       <c r="H612" t="n">
         <v>111.604</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H613" t="n">
         <v>111.1681</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H614" t="n">
         <v>111.3485</v>
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>73.11370100000001</v>
+        <v>73.113693</v>
       </c>
       <c r="H616" t="n">
         <v>112.2053</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H618" t="n">
         <v>109.7504</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H619" t="n">
         <v>108.7382</v>
@@ -23977,7 +23977,7 @@
         <v>71.031746</v>
       </c>
       <c r="H620" t="n">
-        <v>109.0101</v>
+        <v>109.0102</v>
       </c>
     </row>
     <row r="621">
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H621" t="n">
         <v>109.5842</v>
@@ -24091,7 +24091,7 @@
         <v>71.779854</v>
       </c>
       <c r="H623" t="n">
-        <v>110.1582</v>
+        <v>110.1583</v>
       </c>
     </row>
     <row r="624">
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H624" t="n">
         <v>109.5842</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H627" t="n">
         <v>111.5481</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H629" t="n">
         <v>111.1855</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H631" t="n">
         <v>113.4817</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H632" t="n">
         <v>113.2249</v>
@@ -24506,10 +24506,10 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H634" t="n">
-        <v>113.3004</v>
+        <v>113.3005</v>
       </c>
     </row>
     <row r="635">
@@ -24582,7 +24582,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H636" t="n">
         <v>113.2702</v>
@@ -24734,10 +24734,10 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H640" t="n">
-        <v>113.3004</v>
+        <v>113.3005</v>
       </c>
     </row>
     <row r="641">
@@ -24848,7 +24848,7 @@
         </is>
       </c>
       <c r="G643" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H643" t="n">
         <v>112.8472</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H644" t="n">
         <v>113.24</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H646" t="n">
         <v>114.222</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H649" t="n">
         <v>115.3096</v>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H650" t="n">
         <v>114.5392</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H652" t="n">
         <v>114.5392</v>
@@ -25269,7 +25269,7 @@
         <v>75.008568</v>
       </c>
       <c r="H654" t="n">
-        <v>115.1132</v>
+        <v>115.1133</v>
       </c>
     </row>
     <row r="655">
@@ -25380,7 +25380,7 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H657" t="n">
         <v>115.2492</v>
@@ -25570,7 +25570,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H662" t="n">
         <v>118.3159</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H664" t="n">
         <v>117.5152</v>
@@ -25722,7 +25722,7 @@
         </is>
       </c>
       <c r="G666" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H666" t="n">
         <v>117.062</v>
@@ -25760,10 +25760,10 @@
         </is>
       </c>
       <c r="G667" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H667" t="n">
-        <v>116.9109</v>
+        <v>116.911</v>
       </c>
     </row>
     <row r="668">
@@ -25877,7 +25877,7 @@
         <v>76.908394</v>
       </c>
       <c r="H670" t="n">
-        <v>118.0288</v>
+        <v>118.0289</v>
       </c>
     </row>
     <row r="671">
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H672" t="n">
         <v>117.5454</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="G673" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H673" t="n">
         <v>116.8505</v>
@@ -26216,7 +26216,7 @@
         </is>
       </c>
       <c r="G679" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H679" t="n">
         <v>120.2495</v>
@@ -26333,7 +26333,7 @@
         <v>78.540863</v>
       </c>
       <c r="H682" t="n">
-        <v>120.5341</v>
+        <v>120.5342</v>
       </c>
     </row>
     <row r="683">
@@ -26371,7 +26371,7 @@
         <v>78.182869</v>
       </c>
       <c r="H683" t="n">
-        <v>119.9847</v>
+        <v>119.9848</v>
       </c>
     </row>
     <row r="684">
@@ -26789,7 +26789,7 @@
         <v>78.89885700000001</v>
       </c>
       <c r="H694" t="n">
-        <v>121.0835</v>
+        <v>121.0836</v>
       </c>
     </row>
     <row r="695">
@@ -27435,7 +27435,7 @@
         <v>80.112076</v>
       </c>
       <c r="H711" t="n">
-        <v>122.9454</v>
+        <v>122.9455</v>
       </c>
     </row>
     <row r="712">
@@ -27473,7 +27473,7 @@
         <v>80.291077</v>
       </c>
       <c r="H712" t="n">
-        <v>123.2201</v>
+        <v>123.2202</v>
       </c>
     </row>
     <row r="713">
@@ -27815,7 +27815,7 @@
         <v>81.295464</v>
       </c>
       <c r="H721" t="n">
-        <v>124.7615</v>
+        <v>124.7616</v>
       </c>
     </row>
     <row r="722">
@@ -28195,7 +28195,7 @@
         <v>81.21590399999999</v>
       </c>
       <c r="H731" t="n">
-        <v>124.6394</v>
+        <v>124.6395</v>
       </c>
     </row>
     <row r="732">
@@ -28385,7 +28385,7 @@
         <v>81.653458</v>
       </c>
       <c r="H736" t="n">
-        <v>125.3109</v>
+        <v>125.311</v>
       </c>
     </row>
     <row r="737">
@@ -28841,7 +28841,7 @@
         <v>80.900002</v>
       </c>
       <c r="H748" t="n">
-        <v>124.1546</v>
+        <v>124.1547</v>
       </c>
     </row>
     <row r="749">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.349998</v>
+        <v>80.199997</v>
       </c>
       <c r="H755" t="n">
-        <v>123.3106</v>
+        <v>123.0804</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>130.419998</v>
+        <v>130.039993</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.3025</v>
+        <v>119.952</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>130.419998</v>
+        <v>130.039993</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.3025</v>
+        <v>119.952</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>130.419998</v>
+        <v>130.039993</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.3025</v>
+        <v>119.952</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>54.799225</v>
+        <v>54.799221</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>55.06221</v>
+        <v>55.062214</v>
       </c>
       <c r="H1510" t="n">
         <v>100.4799</v>
@@ -57870,10 +57870,10 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.974548</v>
+        <v>54.974552</v>
       </c>
       <c r="H1512" t="n">
-        <v>100.3199</v>
+        <v>100.32</v>
       </c>
     </row>
     <row r="1513">
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>55.403122</v>
+        <v>55.40313</v>
       </c>
       <c r="H1513" t="n">
         <v>101.102</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>55.159622</v>
+        <v>55.159618</v>
       </c>
       <c r="H1514" t="n">
         <v>100.6577</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.429092</v>
+        <v>54.429089</v>
       </c>
       <c r="H1515" t="n">
         <v>99.3246</v>
@@ -58022,10 +58022,10 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.74078</v>
+        <v>54.740784</v>
       </c>
       <c r="H1516" t="n">
-        <v>99.8933</v>
+        <v>99.8934</v>
       </c>
     </row>
     <row r="1517">
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1518" t="n">
         <v>100.0356</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.682335</v>
+        <v>54.682343</v>
       </c>
       <c r="H1520" t="n">
         <v>99.7867</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.403122</v>
+        <v>55.40313</v>
       </c>
       <c r="H1522" t="n">
         <v>101.102</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1523" t="n">
         <v>100.871</v>
@@ -58329,7 +58329,7 @@
         <v>55.47131</v>
       </c>
       <c r="H1524" t="n">
-        <v>101.2264</v>
+        <v>101.2265</v>
       </c>
     </row>
     <row r="1525">
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.75378</v>
+        <v>55.753784</v>
       </c>
       <c r="H1525" t="n">
         <v>101.7419</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.295986</v>
+        <v>55.295982</v>
       </c>
       <c r="H1529" t="n">
         <v>100.9065</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1532" t="n">
         <v>100.871</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>54.867405</v>
+        <v>54.867409</v>
       </c>
       <c r="H1533" t="n">
         <v>100.1244</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>54.584938</v>
+        <v>54.584934</v>
       </c>
       <c r="H1534" t="n">
         <v>99.60899999999999</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1535" t="n">
         <v>101.0665</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1536" t="n">
         <v>102.3818</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>56.523266</v>
+        <v>56.523262</v>
       </c>
       <c r="H1537" t="n">
         <v>103.1461</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1538" t="n">
         <v>102.4529</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>55.305717</v>
+        <v>55.305721</v>
       </c>
       <c r="H1540" t="n">
         <v>100.9243</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1541" t="n">
         <v>99.16459999999999</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>54.877151</v>
+        <v>54.877148</v>
       </c>
       <c r="H1546" t="n">
         <v>100.1422</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1548" t="n">
         <v>101.4042</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.75378</v>
+        <v>55.753784</v>
       </c>
       <c r="H1549" t="n">
         <v>101.7419</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1550" t="n">
         <v>101.4042</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1555" t="n">
         <v>102.0085</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1556" t="n">
         <v>101.9019</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1559" t="n">
         <v>101.9197</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1561" t="n">
         <v>102.3013</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1562" t="n">
         <v>102.1764</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.558754</v>
+        <v>56.558758</v>
       </c>
       <c r="H1563" t="n">
         <v>103.2109</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1564" t="n">
         <v>103.6211</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.676044</v>
+        <v>56.676041</v>
       </c>
       <c r="H1565" t="n">
         <v>103.4249</v>
@@ -59960,10 +59960,10 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1567" t="n">
-        <v>103.9599</v>
+        <v>103.96</v>
       </c>
     </row>
     <row r="1568">
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>57.692471</v>
+        <v>57.692474</v>
       </c>
       <c r="H1569" t="n">
         <v>105.2797</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1570" t="n">
         <v>106.225</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1572" t="n">
         <v>106.7779</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>58.39616</v>
+        <v>58.396156</v>
       </c>
       <c r="H1573" t="n">
         <v>106.5638</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>59.031437</v>
+        <v>59.031433</v>
       </c>
       <c r="H1574" t="n">
         <v>107.7231</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1575" t="n">
         <v>107.9015</v>
@@ -60305,7 +60305,7 @@
         <v>59.070522</v>
       </c>
       <c r="H1576" t="n">
-        <v>107.7944</v>
+        <v>107.7945</v>
       </c>
     </row>
     <row r="1577">
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1577" t="n">
         <v>107.9371</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1578" t="n">
         <v>108.5614</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1579" t="n">
         <v>108.5792</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1581" t="n">
         <v>106.3498</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.91415</v>
+        <v>58.914154</v>
       </c>
       <c r="H1583" t="n">
         <v>107.5091</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>58.953247</v>
+        <v>58.953243</v>
       </c>
       <c r="H1585" t="n">
         <v>107.5804</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>58.835964</v>
+        <v>58.835968</v>
       </c>
       <c r="H1587" t="n">
         <v>107.3664</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>58.718685</v>
+        <v>58.718681</v>
       </c>
       <c r="H1588" t="n">
         <v>107.1524</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.168262</v>
+        <v>59.168259</v>
       </c>
       <c r="H1589" t="n">
         <v>107.9728</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>59.246445</v>
+        <v>59.246449</v>
       </c>
       <c r="H1593" t="n">
         <v>108.1155</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1597" t="n">
         <v>109.8633</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.852402</v>
+        <v>59.852398</v>
       </c>
       <c r="H1599" t="n">
         <v>109.2213</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1600" t="n">
         <v>109.3818</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1601" t="n">
         <v>109.9703</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>61.406372</v>
+        <v>61.406376</v>
       </c>
       <c r="H1608" t="n">
         <v>112.057</v>
@@ -61559,7 +61559,7 @@
         <v>61.445465</v>
       </c>
       <c r="H1609" t="n">
-        <v>112.1283</v>
+        <v>112.1284</v>
       </c>
     </row>
     <row r="1610">
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>59.393051</v>
+        <v>59.393047</v>
       </c>
       <c r="H1612" t="n">
         <v>108.383</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>58.581856</v>
+        <v>58.581852</v>
       </c>
       <c r="H1613" t="n">
         <v>106.9027</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1614" t="n">
         <v>105.9396</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1615" t="n">
         <v>105.2084</v>
@@ -61822,10 +61822,10 @@
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1616" t="n">
-        <v>107.2772</v>
+        <v>107.2773</v>
       </c>
     </row>
     <row r="1617">
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>58.4548</v>
+        <v>58.454803</v>
       </c>
       <c r="H1617" t="n">
         <v>106.6709</v>
@@ -62243,7 +62243,7 @@
         <v>57.107449</v>
       </c>
       <c r="H1627" t="n">
-        <v>104.2121</v>
+        <v>104.2122</v>
       </c>
     </row>
     <row r="1628">
@@ -62585,7 +62585,7 @@
         <v>59.713482</v>
       </c>
       <c r="H1636" t="n">
-        <v>108.9677</v>
+        <v>108.9678</v>
       </c>
     </row>
     <row r="1637">
@@ -63003,7 +63003,7 @@
         <v>59.625309</v>
       </c>
       <c r="H1647" t="n">
-        <v>108.8068</v>
+        <v>108.8069</v>
       </c>
     </row>
     <row r="1648">
@@ -63117,7 +63117,7 @@
         <v>58.949306</v>
       </c>
       <c r="H1650" t="n">
-        <v>107.5732</v>
+        <v>107.5733</v>
       </c>
     </row>
     <row r="1651">
@@ -63649,7 +63649,7 @@
         <v>61.065487</v>
       </c>
       <c r="H1664" t="n">
-        <v>111.4349</v>
+        <v>111.435</v>
       </c>
     </row>
     <row r="1665">
@@ -63687,7 +63687,7 @@
         <v>61.065487</v>
       </c>
       <c r="H1665" t="n">
-        <v>111.4349</v>
+        <v>111.435</v>
       </c>
     </row>
     <row r="1666">
@@ -63725,7 +63725,7 @@
         <v>61.604328</v>
       </c>
       <c r="H1666" t="n">
-        <v>112.4182</v>
+        <v>112.4183</v>
       </c>
     </row>
     <row r="1667">
@@ -64029,7 +64029,7 @@
         <v>61.241829</v>
       </c>
       <c r="H1674" t="n">
-        <v>111.7567</v>
+        <v>111.7568</v>
       </c>
     </row>
     <row r="1675">
@@ -64599,7 +64599,7 @@
         <v>62.707325</v>
       </c>
       <c r="H1689" t="n">
-        <v>114.431</v>
+        <v>114.4311</v>
       </c>
     </row>
     <row r="1690">
@@ -64637,7 +64637,7 @@
         <v>63.192738</v>
       </c>
       <c r="H1690" t="n">
-        <v>115.3168</v>
+        <v>115.3169</v>
       </c>
     </row>
     <row r="1691">
@@ -65017,7 +65017,7 @@
         <v>63.321518</v>
       </c>
       <c r="H1700" t="n">
-        <v>115.5518</v>
+        <v>115.5519</v>
       </c>
     </row>
     <row r="1701">
@@ -65131,7 +65131,7 @@
         <v>63.371056</v>
       </c>
       <c r="H1703" t="n">
-        <v>115.6422</v>
+        <v>115.6423</v>
       </c>
     </row>
     <row r="1704">
@@ -65397,7 +65397,7 @@
         <v>63.10358</v>
       </c>
       <c r="H1710" t="n">
-        <v>115.1541</v>
+        <v>115.1542</v>
       </c>
     </row>
     <row r="1711">
@@ -65625,7 +65625,7 @@
         <v>64.12394</v>
       </c>
       <c r="H1716" t="n">
-        <v>117.0161</v>
+        <v>117.0162</v>
       </c>
     </row>
     <row r="1717">
@@ -65967,7 +65967,7 @@
         <v>65.312698</v>
       </c>
       <c r="H1725" t="n">
-        <v>119.1854</v>
+        <v>119.1855</v>
       </c>
     </row>
     <row r="1726">
@@ -67031,7 +67031,7 @@
         <v>63.580002</v>
       </c>
       <c r="H1753" t="n">
-        <v>116.0235</v>
+        <v>116.0236</v>
       </c>
     </row>
     <row r="1754">
@@ -67145,7 +67145,7 @@
         <v>63.23</v>
       </c>
       <c r="H1756" t="n">
-        <v>115.3848</v>
+        <v>115.3849</v>
       </c>
     </row>
     <row r="1757">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.619999</v>
+        <v>62.549999</v>
       </c>
       <c r="H1760" t="n">
-        <v>114.2717</v>
+        <v>114.144</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>66.01767</v>
+        <v>66.017662</v>
       </c>
       <c r="H509" t="n">
         <v>101.3152</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>65.910538</v>
+        <v>65.91052999999999</v>
       </c>
       <c r="H510" t="n">
         <v>101.1508</v>
@@ -19832,10 +19832,10 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.868523</v>
+        <v>64.868515</v>
       </c>
       <c r="H511" t="n">
-        <v>99.5517</v>
+        <v>99.55159999999999</v>
       </c>
     </row>
     <row r="512">
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.199631</v>
+        <v>65.199623</v>
       </c>
       <c r="H512" t="n">
         <v>100.0598</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H513" t="n">
         <v>99.92529999999999</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.121712</v>
+        <v>65.121719</v>
       </c>
       <c r="H516" t="n">
         <v>99.9402</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.842361</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H517" t="n">
         <v>101.0462</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>66.01767</v>
+        <v>66.017662</v>
       </c>
       <c r="H518" t="n">
         <v>101.3152</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.93974300000001</v>
+        <v>65.939758</v>
       </c>
       <c r="H519" t="n">
         <v>101.1956</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.06636</v>
+        <v>66.06635300000001</v>
       </c>
       <c r="H520" t="n">
         <v>101.3899</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H521" t="n">
         <v>101.913</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H524" t="n">
         <v>101.913</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H526" t="n">
         <v>101.375</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.98844099999999</v>
+        <v>65.988457</v>
       </c>
       <c r="H529" t="n">
         <v>101.2704</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H531" t="n">
         <v>101.8532</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H532" t="n">
         <v>102.735</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H534" t="n">
         <v>102.9144</v>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H535" t="n">
-        <v>102.4809</v>
+        <v>102.481</v>
       </c>
     </row>
     <row r="536">
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.754707</v>
+        <v>65.754715</v>
       </c>
       <c r="H537" t="n">
         <v>100.9117</v>
@@ -20896,10 +20896,10 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027412</v>
       </c>
       <c r="H539" t="n">
-        <v>101.3301</v>
+        <v>101.3302</v>
       </c>
     </row>
     <row r="540">
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>65.89106</v>
+        <v>65.891068</v>
       </c>
       <c r="H540" t="n">
         <v>101.1209</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>66.387733</v>
+        <v>66.387726</v>
       </c>
       <c r="H542" t="n">
         <v>101.8831</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H546" t="n">
         <v>102.9144</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H548" t="n">
         <v>102.735</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.283676</v>
+        <v>67.283669</v>
       </c>
       <c r="H551" t="n">
         <v>103.2581</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.22524300000001</v>
+        <v>67.22525</v>
       </c>
       <c r="H553" t="n">
         <v>103.1684</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.478447</v>
+        <v>67.47843899999999</v>
       </c>
       <c r="H554" t="n">
         <v>103.557</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.3908</v>
+        <v>67.390793</v>
       </c>
       <c r="H555" t="n">
         <v>103.4225</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.234978</v>
+        <v>67.23498499999999</v>
       </c>
       <c r="H558" t="n">
         <v>103.1834</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.815033</v>
+        <v>67.81502500000001</v>
       </c>
       <c r="H561" t="n">
         <v>104.0736</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H563" t="n">
         <v>104.78</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>69.48004899999999</v>
+        <v>69.480057</v>
       </c>
       <c r="H568" t="n">
         <v>106.6288</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.723907</v>
+        <v>70.72391500000001</v>
       </c>
       <c r="H576" t="n">
         <v>108.5377</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H577" t="n">
         <v>107.5307</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H579" t="n">
         <v>108.7632</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>73.201836</v>
+        <v>73.201843</v>
       </c>
       <c r="H590" t="n">
         <v>112.3405</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H592" t="n">
         <v>112.8967</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H594" t="n">
         <v>113.3175</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>73.887444</v>
+        <v>73.88743599999999</v>
       </c>
       <c r="H596" t="n">
         <v>113.3927</v>
@@ -23290,10 +23290,10 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H602" t="n">
-        <v>114.6853</v>
+        <v>114.6854</v>
       </c>
     </row>
     <row r="603">
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>75.003967</v>
+        <v>75.003975</v>
       </c>
       <c r="H606" t="n">
         <v>115.1062</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>72.721924</v>
+        <v>72.72191599999999</v>
       </c>
       <c r="H612" t="n">
         <v>111.604</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>72.64357</v>
+        <v>72.643562</v>
       </c>
       <c r="H617" t="n">
         <v>111.4838</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H618" t="n">
         <v>109.7504</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H619" t="n">
         <v>108.7382</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H621" t="n">
         <v>109.5842</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H624" t="n">
         <v>109.5842</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H627" t="n">
         <v>111.5481</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H629" t="n">
         <v>111.1855</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H631" t="n">
         <v>113.4817</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H632" t="n">
         <v>113.2249</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H634" t="n">
         <v>113.3005</v>
@@ -24582,10 +24582,10 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H636" t="n">
-        <v>113.2702</v>
+        <v>113.2703</v>
       </c>
     </row>
     <row r="637">
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H640" t="n">
         <v>113.3005</v>
@@ -24848,10 +24848,10 @@
         </is>
       </c>
       <c r="G643" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H643" t="n">
-        <v>112.8472</v>
+        <v>112.8473</v>
       </c>
     </row>
     <row r="644">
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H644" t="n">
         <v>113.24</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H646" t="n">
         <v>114.222</v>
@@ -25076,10 +25076,10 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H649" t="n">
-        <v>115.3096</v>
+        <v>115.3097</v>
       </c>
     </row>
     <row r="650">
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H650" t="n">
         <v>114.5392</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H652" t="n">
         <v>114.5392</v>
@@ -25380,7 +25380,7 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H657" t="n">
         <v>115.2492</v>
@@ -25570,7 +25570,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H662" t="n">
         <v>118.3159</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H664" t="n">
         <v>117.5152</v>
@@ -25722,7 +25722,7 @@
         </is>
       </c>
       <c r="G666" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H666" t="n">
         <v>117.062</v>
@@ -25760,7 +25760,7 @@
         </is>
       </c>
       <c r="G667" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H667" t="n">
         <v>116.911</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H672" t="n">
         <v>117.5454</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="G673" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H673" t="n">
         <v>116.8505</v>
@@ -26216,10 +26216,10 @@
         </is>
       </c>
       <c r="G679" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H679" t="n">
-        <v>120.2495</v>
+        <v>120.2496</v>
       </c>
     </row>
     <row r="680">
@@ -57870,10 +57870,10 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.974552</v>
+        <v>54.974548</v>
       </c>
       <c r="H1512" t="n">
-        <v>100.32</v>
+        <v>100.3199</v>
       </c>
     </row>
     <row r="1513">
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.429089</v>
+        <v>54.429092</v>
       </c>
       <c r="H1515" t="n">
         <v>99.3246</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.536236</v>
+        <v>54.53624</v>
       </c>
       <c r="H1517" t="n">
         <v>99.5201</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.682343</v>
+        <v>54.682339</v>
       </c>
       <c r="H1520" t="n">
         <v>99.7867</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.753784</v>
+        <v>55.75378</v>
       </c>
       <c r="H1525" t="n">
         <v>101.7419</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.588188</v>
+        <v>55.588192</v>
       </c>
       <c r="H1527" t="n">
         <v>101.4397</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.325203</v>
+        <v>55.325199</v>
       </c>
       <c r="H1530" t="n">
         <v>100.9598</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>54.867409</v>
+        <v>54.867405</v>
       </c>
       <c r="H1533" t="n">
         <v>100.1244</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1542" t="n">
         <v>99.0757</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.351166</v>
+        <v>54.35117</v>
       </c>
       <c r="H1544" t="n">
         <v>99.1824</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.753784</v>
+        <v>55.75378</v>
       </c>
       <c r="H1549" t="n">
         <v>101.7419</v>
@@ -59770,10 +59770,10 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1562" t="n">
-        <v>102.1764</v>
+        <v>102.1765</v>
       </c>
     </row>
     <row r="1563">
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1570" t="n">
         <v>106.225</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1572" t="n">
         <v>106.7779</v>
@@ -60188,10 +60188,10 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>58.396156</v>
+        <v>58.39616</v>
       </c>
       <c r="H1573" t="n">
-        <v>106.5638</v>
+        <v>106.5639</v>
       </c>
     </row>
     <row r="1574">
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>59.129169</v>
+        <v>59.129166</v>
       </c>
       <c r="H1575" t="n">
         <v>107.9015</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1577" t="n">
         <v>107.9371</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.914154</v>
+        <v>58.91415</v>
       </c>
       <c r="H1583" t="n">
         <v>107.5091</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>58.835968</v>
+        <v>58.835964</v>
       </c>
       <c r="H1587" t="n">
         <v>107.3664</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>58.718681</v>
+        <v>58.718685</v>
       </c>
       <c r="H1588" t="n">
         <v>107.1524</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.793758</v>
+        <v>59.793755</v>
       </c>
       <c r="H1590" t="n">
         <v>109.1142</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.803532</v>
+        <v>59.803528</v>
       </c>
       <c r="H1592" t="n">
         <v>109.1321</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>59.744892</v>
+        <v>59.744896</v>
       </c>
       <c r="H1594" t="n">
         <v>109.0251</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>60.11628</v>
+        <v>60.116276</v>
       </c>
       <c r="H1596" t="n">
         <v>109.7028</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1598" t="n">
         <v>109.3639</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>59.852398</v>
+        <v>59.852402</v>
       </c>
       <c r="H1599" t="n">
         <v>109.2213</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.65382</v>
+        <v>60.653816</v>
       </c>
       <c r="H1603" t="n">
         <v>110.6837</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1605" t="n">
         <v>111.0761</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>61.015434</v>
+        <v>61.015438</v>
       </c>
       <c r="H1606" t="n">
         <v>111.3436</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>61.406376</v>
+        <v>61.406372</v>
       </c>
       <c r="H1608" t="n">
         <v>112.057</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1615" t="n">
         <v>105.2084</v>
@@ -61898,7 +61898,7 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.112728</v>
+        <v>58.112732</v>
       </c>
       <c r="H1618" t="n">
         <v>106.0466</v>
@@ -62012,7 +62012,7 @@
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1621" t="n">
         <v>106.6257</v>
@@ -62734,7 +62734,7 @@
         </is>
       </c>
       <c r="G1640" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1640" t="n">
         <v>109.7723</v>
@@ -62810,7 +62810,7 @@
         </is>
       </c>
       <c r="G1642" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1642" t="n">
         <v>111.4707</v>
@@ -62886,10 +62886,10 @@
         </is>
       </c>
       <c r="G1644" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1644" t="n">
-        <v>109.6292</v>
+        <v>109.6293</v>
       </c>
     </row>
     <row r="1645">
@@ -62962,7 +62962,7 @@
         </is>
       </c>
       <c r="G1646" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1646" t="n">
         <v>109.3968</v>
@@ -63000,10 +63000,10 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1647" t="n">
-        <v>108.8069</v>
+        <v>108.8068</v>
       </c>
     </row>
     <row r="1648">
@@ -63114,10 +63114,10 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1650" t="n">
-        <v>107.5733</v>
+        <v>107.5732</v>
       </c>
     </row>
     <row r="1651">
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1653" t="n">
         <v>109.0035</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1654" t="n">
         <v>111.4171</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1656" t="n">
         <v>109.5935</v>
@@ -63418,7 +63418,7 @@
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1658" t="n">
         <v>108.5923</v>
@@ -63798,7 +63798,7 @@
         </is>
       </c>
       <c r="G1668" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1668" t="n">
         <v>112.9188</v>
@@ -63874,7 +63874,7 @@
         </is>
       </c>
       <c r="G1670" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1670" t="n">
         <v>112.4361</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1673" t="n">
         <v>112.5613</v>
@@ -64064,7 +64064,7 @@
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1675" t="n">
         <v>112.4361</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1676" t="n">
         <v>111.9892</v>
@@ -64254,10 +64254,10 @@
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1680" t="n">
-        <v>111.8461</v>
+        <v>111.8462</v>
       </c>
     </row>
     <row r="1681">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H510" t="n">
         <v>101.1508</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H511" t="n">
         <v>99.55159999999999</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.199623</v>
+        <v>65.19961499999999</v>
       </c>
       <c r="H512" t="n">
         <v>100.0598</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.111977</v>
+        <v>65.111969</v>
       </c>
       <c r="H513" t="n">
         <v>99.92529999999999</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.84236900000001</v>
+        <v>65.842361</v>
       </c>
       <c r="H517" t="n">
         <v>101.0462</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H521" t="n">
         <v>101.913</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H524" t="n">
         <v>101.913</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>65.988457</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H529" t="n">
         <v>101.2704</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H532" t="n">
         <v>102.735</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H533" t="n">
         <v>103.6915</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.027412</v>
+        <v>66.027405</v>
       </c>
       <c r="H539" t="n">
         <v>101.3302</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H543" t="n">
         <v>102.8247</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.87464900000001</v>
+        <v>66.874657</v>
       </c>
       <c r="H547" t="n">
         <v>102.6304</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H548" t="n">
         <v>102.735</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.283669</v>
+        <v>67.283661</v>
       </c>
       <c r="H551" t="n">
         <v>103.2581</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.22525</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H553" t="n">
         <v>103.1684</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H554" t="n">
         <v>103.557</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H557" t="n">
         <v>103.0788</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.23498499999999</v>
+        <v>67.234978</v>
       </c>
       <c r="H558" t="n">
         <v>103.1834</v>
@@ -21656,10 +21656,10 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.619148</v>
+        <v>67.619141</v>
       </c>
       <c r="H559" t="n">
-        <v>103.773</v>
+        <v>103.7729</v>
       </c>
     </row>
     <row r="560">
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H560" t="n">
         <v>104.1938</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.81502500000001</v>
+        <v>67.815033</v>
       </c>
       <c r="H561" t="n">
         <v>104.0736</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H565" t="n">
         <v>105.1558</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>69.773865</v>
+        <v>69.773872</v>
       </c>
       <c r="H567" t="n">
         <v>107.0797</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>69.480057</v>
+        <v>69.48004899999999</v>
       </c>
       <c r="H568" t="n">
         <v>106.6288</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H569" t="n">
         <v>106.9595</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>70.18523399999999</v>
+        <v>70.185226</v>
       </c>
       <c r="H571" t="n">
         <v>107.711</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>70.273369</v>
+        <v>70.273376</v>
       </c>
       <c r="H572" t="n">
         <v>107.8463</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H575" t="n">
         <v>109.4095</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.72391500000001</v>
+        <v>70.723907</v>
       </c>
       <c r="H576" t="n">
         <v>108.5377</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.371323</v>
+        <v>70.371315</v>
       </c>
       <c r="H578" t="n">
         <v>107.9966</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H579" t="n">
         <v>108.7632</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H589" t="n">
         <v>111.0329</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>73.201843</v>
+        <v>73.201836</v>
       </c>
       <c r="H590" t="n">
         <v>112.3405</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H591" t="n">
         <v>112.5059</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H593" t="n">
         <v>113.7534</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.82867400000001</v>
+        <v>73.828667</v>
       </c>
       <c r="H595" t="n">
         <v>113.3025</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.86784400000001</v>
+        <v>73.867851</v>
       </c>
       <c r="H597" t="n">
         <v>113.3626</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>74.524055</v>
+        <v>74.52404799999999</v>
       </c>
       <c r="H601" t="n">
         <v>114.3697</v>
@@ -23290,10 +23290,10 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H602" t="n">
-        <v>114.6854</v>
+        <v>114.6853</v>
       </c>
     </row>
     <row r="603">
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>72.72191599999999</v>
+        <v>72.721931</v>
       </c>
       <c r="H612" t="n">
         <v>111.604</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H613" t="n">
         <v>111.1681</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>72.55542800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H614" t="n">
         <v>111.3485</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>72.643562</v>
+        <v>72.64357800000001</v>
       </c>
       <c r="H617" t="n">
         <v>111.4838</v>
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H618" t="n">
         <v>109.7504</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H619" t="n">
         <v>108.7382</v>
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H621" t="n">
         <v>109.5842</v>
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H624" t="n">
         <v>109.5842</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H627" t="n">
         <v>111.5481</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H629" t="n">
         <v>111.1855</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H631" t="n">
         <v>113.4817</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H632" t="n">
         <v>113.2249</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H634" t="n">
         <v>113.3005</v>
@@ -24582,10 +24582,10 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H636" t="n">
-        <v>113.2703</v>
+        <v>113.2702</v>
       </c>
     </row>
     <row r="637">
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H640" t="n">
         <v>113.3005</v>
@@ -24848,10 +24848,10 @@
         </is>
       </c>
       <c r="G643" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H643" t="n">
-        <v>112.8473</v>
+        <v>112.8472</v>
       </c>
     </row>
     <row r="644">
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H644" t="n">
         <v>113.24</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H646" t="n">
         <v>114.222</v>
@@ -25076,10 +25076,10 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H649" t="n">
-        <v>115.3097</v>
+        <v>115.3096</v>
       </c>
     </row>
     <row r="650">
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H650" t="n">
         <v>114.5392</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H652" t="n">
         <v>114.5392</v>
@@ -25380,7 +25380,7 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H657" t="n">
         <v>115.2492</v>
@@ -25570,7 +25570,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H662" t="n">
         <v>118.3159</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H664" t="n">
         <v>117.5152</v>
@@ -25722,7 +25722,7 @@
         </is>
       </c>
       <c r="G666" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H666" t="n">
         <v>117.062</v>
@@ -25760,7 +25760,7 @@
         </is>
       </c>
       <c r="G667" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H667" t="n">
         <v>116.911</v>
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H672" t="n">
         <v>117.5454</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="G673" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H673" t="n">
         <v>116.8505</v>
@@ -26216,10 +26216,10 @@
         </is>
       </c>
       <c r="G679" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H679" t="n">
-        <v>120.2496</v>
+        <v>120.2495</v>
       </c>
     </row>
     <row r="680">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>55.062214</v>
+        <v>55.06221</v>
       </c>
       <c r="H1510" t="n">
         <v>100.4799</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1513" t="n">
         <v>101.102</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.53624</v>
+        <v>54.536236</v>
       </c>
       <c r="H1517" t="n">
         <v>99.5201</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1522" t="n">
         <v>101.102</v>
@@ -58440,10 +58440,10 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.588192</v>
+        <v>55.588196</v>
       </c>
       <c r="H1527" t="n">
-        <v>101.4397</v>
+        <v>101.4398</v>
       </c>
     </row>
     <row r="1528">
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1528" t="n">
         <v>101.3331</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.325199</v>
+        <v>55.325203</v>
       </c>
       <c r="H1530" t="n">
         <v>100.9598</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>54.867405</v>
+        <v>54.867409</v>
       </c>
       <c r="H1533" t="n">
         <v>100.1244</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>56.143391</v>
+        <v>56.143394</v>
       </c>
       <c r="H1538" t="n">
         <v>102.4529</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1541" t="n">
         <v>99.16459999999999</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1547" t="n">
         <v>101.3331</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1548" t="n">
         <v>101.4042</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1550" t="n">
         <v>101.4042</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1559" t="n">
         <v>101.9197</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>36.23</v>
+        <v>35.880001</v>
       </c>
       <c r="H253" t="n">
-        <v>122.9386</v>
+        <v>121.7509</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>49.125</v>
+        <v>48.369999</v>
       </c>
       <c r="H504" t="n">
-        <v>131.4381</v>
+        <v>129.4181</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>65.160667</v>
+        <v>65.160675</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H509" t="n">
         <v>101.3152</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>65.910538</v>
+        <v>65.91052999999999</v>
       </c>
       <c r="H510" t="n">
         <v>101.1508</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H511" t="n">
         <v>99.55159999999999</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.19961499999999</v>
+        <v>65.199623</v>
       </c>
       <c r="H512" t="n">
         <v>100.0598</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H513" t="n">
         <v>99.92529999999999</v>
@@ -19984,10 +19984,10 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.559952</v>
+        <v>65.559944</v>
       </c>
       <c r="H515" t="n">
-        <v>100.6128</v>
+        <v>100.6127</v>
       </c>
     </row>
     <row r="516">
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>66.017662</v>
+        <v>66.01767</v>
       </c>
       <c r="H518" t="n">
         <v>101.3152</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H519" t="n">
         <v>101.1956</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.339035</v>
+        <v>66.339027</v>
       </c>
       <c r="H522" t="n">
         <v>101.8084</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H523" t="n">
         <v>101.6141</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H525" t="n">
         <v>101.4348</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H526" t="n">
         <v>101.375</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H527" t="n">
         <v>101.4348</v>
@@ -20519,7 +20519,7 @@
         <v>65.98844099999999</v>
       </c>
       <c r="H529" t="n">
-        <v>101.2704</v>
+        <v>101.2703</v>
       </c>
     </row>
     <row r="530">
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368263</v>
       </c>
       <c r="H531" t="n">
         <v>101.8532</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H533" t="n">
         <v>103.6915</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H534" t="n">
         <v>102.9144</v>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H535" t="n">
-        <v>102.481</v>
+        <v>102.4809</v>
       </c>
     </row>
     <row r="536">
@@ -20785,7 +20785,7 @@
         <v>66.416939</v>
       </c>
       <c r="H536" t="n">
-        <v>101.928</v>
+        <v>101.9279</v>
       </c>
     </row>
     <row r="537">
@@ -20820,10 +20820,10 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.754715</v>
+        <v>65.754707</v>
       </c>
       <c r="H537" t="n">
-        <v>100.9117</v>
+        <v>100.9116</v>
       </c>
     </row>
     <row r="538">
@@ -20899,7 +20899,7 @@
         <v>66.027405</v>
       </c>
       <c r="H539" t="n">
-        <v>101.3302</v>
+        <v>101.3301</v>
       </c>
     </row>
     <row r="540">
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H540" t="n">
         <v>101.1209</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H543" t="n">
         <v>102.8247</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H546" t="n">
         <v>102.9144</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>66.874657</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H547" t="n">
         <v>102.6304</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.283661</v>
+        <v>67.283669</v>
       </c>
       <c r="H551" t="n">
         <v>103.2581</v>
@@ -21393,7 +21393,7 @@
         <v>67.29341100000001</v>
       </c>
       <c r="H552" t="n">
-        <v>103.2731</v>
+        <v>103.273</v>
       </c>
     </row>
     <row r="553">
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.22524300000001</v>
+        <v>67.225235</v>
       </c>
       <c r="H553" t="n">
         <v>103.1684</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.770599</v>
+        <v>67.77059199999999</v>
       </c>
       <c r="H556" t="n">
         <v>104.0054</v>
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H557" t="n">
         <v>103.0788</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.619141</v>
+        <v>67.619148</v>
       </c>
       <c r="H559" t="n">
         <v>103.7729</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H560" t="n">
         <v>104.1938</v>
@@ -21732,10 +21732,10 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>67.815033</v>
+        <v>67.81502500000001</v>
       </c>
       <c r="H561" t="n">
-        <v>104.0736</v>
+        <v>104.0735</v>
       </c>
     </row>
     <row r="562">
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H565" t="n">
         <v>105.1558</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H567" t="n">
         <v>107.0797</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>69.48004899999999</v>
+        <v>69.480057</v>
       </c>
       <c r="H568" t="n">
         <v>106.6288</v>
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H569" t="n">
         <v>106.9595</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H571" t="n">
         <v>107.711</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>70.273376</v>
+        <v>70.273369</v>
       </c>
       <c r="H572" t="n">
         <v>107.8463</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H575" t="n">
         <v>109.4095</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.723907</v>
+        <v>70.72391500000001</v>
       </c>
       <c r="H576" t="n">
         <v>108.5377</v>
@@ -22343,7 +22343,7 @@
         <v>70.067696</v>
       </c>
       <c r="H577" t="n">
-        <v>107.5307</v>
+        <v>107.5306</v>
       </c>
     </row>
     <row r="578">
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H578" t="n">
         <v>107.9966</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H579" t="n">
         <v>108.7632</v>
@@ -22647,7 +22647,7 @@
         <v>70.890411</v>
       </c>
       <c r="H585" t="n">
-        <v>108.7933</v>
+        <v>108.7932</v>
       </c>
     </row>
     <row r="586">
@@ -22796,10 +22796,10 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H589" t="n">
-        <v>111.0329</v>
+        <v>111.0328</v>
       </c>
     </row>
     <row r="590">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>73.201836</v>
+        <v>73.201843</v>
       </c>
       <c r="H590" t="n">
         <v>112.3405</v>
@@ -22872,10 +22872,10 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H591" t="n">
-        <v>112.5059</v>
+        <v>112.5058</v>
       </c>
     </row>
     <row r="592">
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H593" t="n">
         <v>113.7534</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.828667</v>
+        <v>73.82867400000001</v>
       </c>
       <c r="H595" t="n">
         <v>113.3025</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H597" t="n">
         <v>113.3626</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H601" t="n">
         <v>114.3697</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H602" t="n">
         <v>114.6853</v>
@@ -23559,7 +23559,7 @@
         <v>73.113693</v>
       </c>
       <c r="H609" t="n">
-        <v>112.2053</v>
+        <v>112.2052</v>
       </c>
     </row>
     <row r="610">
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>72.721931</v>
+        <v>72.72191599999999</v>
       </c>
       <c r="H612" t="n">
         <v>111.604</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H613" t="n">
         <v>111.1681</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H614" t="n">
         <v>111.3485</v>
@@ -23825,7 +23825,7 @@
         <v>73.113693</v>
       </c>
       <c r="H616" t="n">
-        <v>112.2053</v>
+        <v>112.2052</v>
       </c>
     </row>
     <row r="617">
@@ -23860,10 +23860,10 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>72.64357800000001</v>
+        <v>72.643562</v>
       </c>
       <c r="H617" t="n">
-        <v>111.4838</v>
+        <v>111.4837</v>
       </c>
     </row>
     <row r="618">
@@ -23898,7 +23898,7 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H618" t="n">
         <v>109.7504</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H619" t="n">
         <v>108.7382</v>
@@ -23977,7 +23977,7 @@
         <v>71.031746</v>
       </c>
       <c r="H620" t="n">
-        <v>109.0102</v>
+        <v>109.0101</v>
       </c>
     </row>
     <row r="621">
@@ -24012,7 +24012,7 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H621" t="n">
         <v>109.5842</v>
@@ -24091,7 +24091,7 @@
         <v>71.779854</v>
       </c>
       <c r="H623" t="n">
-        <v>110.1583</v>
+        <v>110.1582</v>
       </c>
     </row>
     <row r="624">
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H624" t="n">
         <v>109.5842</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H627" t="n">
         <v>111.5481</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H629" t="n">
         <v>111.1855</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H631" t="n">
         <v>113.4817</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H632" t="n">
         <v>113.2249</v>
@@ -24506,10 +24506,10 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H634" t="n">
-        <v>113.3005</v>
+        <v>113.3004</v>
       </c>
     </row>
     <row r="635">
@@ -24582,7 +24582,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H636" t="n">
         <v>113.2702</v>
@@ -24734,10 +24734,10 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H640" t="n">
-        <v>113.3005</v>
+        <v>113.3004</v>
       </c>
     </row>
     <row r="641">
@@ -24848,7 +24848,7 @@
         </is>
       </c>
       <c r="G643" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H643" t="n">
         <v>112.8472</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H644" t="n">
         <v>113.24</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H646" t="n">
         <v>114.222</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H649" t="n">
         <v>115.3096</v>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H650" t="n">
         <v>114.5392</v>
@@ -25190,7 +25190,7 @@
         </is>
       </c>
       <c r="G652" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H652" t="n">
         <v>114.5392</v>
@@ -25269,7 +25269,7 @@
         <v>75.008568</v>
       </c>
       <c r="H654" t="n">
-        <v>115.1133</v>
+        <v>115.1132</v>
       </c>
     </row>
     <row r="655">
@@ -25380,7 +25380,7 @@
         </is>
       </c>
       <c r="G657" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H657" t="n">
         <v>115.2492</v>
@@ -25570,7 +25570,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H662" t="n">
         <v>118.3159</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H664" t="n">
         <v>117.5152</v>
@@ -25722,7 +25722,7 @@
         </is>
       </c>
       <c r="G666" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H666" t="n">
         <v>117.062</v>
@@ -25760,10 +25760,10 @@
         </is>
       </c>
       <c r="G667" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H667" t="n">
-        <v>116.911</v>
+        <v>116.9109</v>
       </c>
     </row>
     <row r="668">
@@ -25877,7 +25877,7 @@
         <v>76.908394</v>
       </c>
       <c r="H670" t="n">
-        <v>118.0289</v>
+        <v>118.0288</v>
       </c>
     </row>
     <row r="671">
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="G672" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H672" t="n">
         <v>117.5454</v>
@@ -25988,7 +25988,7 @@
         </is>
       </c>
       <c r="G673" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H673" t="n">
         <v>116.8505</v>
@@ -26216,7 +26216,7 @@
         </is>
       </c>
       <c r="G679" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H679" t="n">
         <v>120.2495</v>
@@ -26333,7 +26333,7 @@
         <v>78.540863</v>
       </c>
       <c r="H682" t="n">
-        <v>120.5342</v>
+        <v>120.5341</v>
       </c>
     </row>
     <row r="683">
@@ -26371,7 +26371,7 @@
         <v>78.182869</v>
       </c>
       <c r="H683" t="n">
-        <v>119.9848</v>
+        <v>119.9847</v>
       </c>
     </row>
     <row r="684">
@@ -26789,7 +26789,7 @@
         <v>78.89885700000001</v>
       </c>
       <c r="H694" t="n">
-        <v>121.0836</v>
+        <v>121.0835</v>
       </c>
     </row>
     <row r="695">
@@ -27435,7 +27435,7 @@
         <v>80.112076</v>
       </c>
       <c r="H711" t="n">
-        <v>122.9455</v>
+        <v>122.9454</v>
       </c>
     </row>
     <row r="712">
@@ -27473,7 +27473,7 @@
         <v>80.291077</v>
       </c>
       <c r="H712" t="n">
-        <v>123.2202</v>
+        <v>123.2201</v>
       </c>
     </row>
     <row r="713">
@@ -27815,7 +27815,7 @@
         <v>81.295464</v>
       </c>
       <c r="H721" t="n">
-        <v>124.7616</v>
+        <v>124.7615</v>
       </c>
     </row>
     <row r="722">
@@ -28195,7 +28195,7 @@
         <v>81.21590399999999</v>
       </c>
       <c r="H731" t="n">
-        <v>124.6395</v>
+        <v>124.6394</v>
       </c>
     </row>
     <row r="732">
@@ -28385,7 +28385,7 @@
         <v>81.653458</v>
       </c>
       <c r="H736" t="n">
-        <v>125.311</v>
+        <v>125.3109</v>
       </c>
     </row>
     <row r="737">
@@ -28841,7 +28841,7 @@
         <v>80.900002</v>
       </c>
       <c r="H748" t="n">
-        <v>124.1547</v>
+        <v>124.1546</v>
       </c>
     </row>
     <row r="749">
@@ -29075,7 +29075,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.199997</v>
+        <v>79.699997</v>
       </c>
       <c r="H755" t="n">
-        <v>123.0804</v>
+        <v>122.313</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>130.039993</v>
+        <v>128.809998</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.952</v>
+        <v>118.8174</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>130.039993</v>
+        <v>128.809998</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.952</v>
+        <v>118.8174</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>130.039993</v>
+        <v>128.809998</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.952</v>
+        <v>118.8174</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>55.06221</v>
+        <v>55.062214</v>
       </c>
       <c r="H1510" t="n">
         <v>100.4799</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>55.042732</v>
+        <v>55.042728</v>
       </c>
       <c r="H1511" t="n">
         <v>100.4444</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.429092</v>
+        <v>54.429089</v>
       </c>
       <c r="H1515" t="n">
         <v>99.3246</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.740784</v>
+        <v>54.74078</v>
       </c>
       <c r="H1516" t="n">
         <v>99.8934</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.536236</v>
+        <v>54.536232</v>
       </c>
       <c r="H1517" t="n">
         <v>99.5201</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1519" t="n">
         <v>100.8354</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>54.682339</v>
+        <v>54.682335</v>
       </c>
       <c r="H1520" t="n">
         <v>99.7867</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1521" t="n">
         <v>100.8354</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1528" t="n">
         <v>101.3331</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1541" t="n">
         <v>99.16459999999999</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1542" t="n">
         <v>99.0757</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1547" t="n">
         <v>101.3331</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.987545</v>
+        <v>55.987549</v>
       </c>
       <c r="H1554" t="n">
         <v>102.1685</v>
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.549999</v>
+        <v>62.07</v>
       </c>
       <c r="H1760" t="n">
-        <v>114.144</v>
+        <v>113.268</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.910538</v>
+        <v>65.91052999999999</v>
       </c>
       <c r="H508" t="n">
         <v>100.3856</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>65.19961499999999</v>
+        <v>65.199623</v>
       </c>
       <c r="H510" t="n">
         <v>99.30289999999999</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.559944</v>
+        <v>65.559952</v>
       </c>
       <c r="H513" t="n">
         <v>99.85169999999999</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H519" t="n">
         <v>101.1421</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H522" t="n">
         <v>101.1421</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.98844099999999</v>
+        <v>65.988457</v>
       </c>
       <c r="H527" t="n">
         <v>100.5043</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H529" t="n">
         <v>101.0828</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H530" t="n">
         <v>101.9579</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H533" t="n">
         <v>101.7057</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.38771800000001</v>
+        <v>66.387726</v>
       </c>
       <c r="H540" t="n">
         <v>101.1124</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H541" t="n">
         <v>102.0469</v>
@@ -21124,10 +21124,10 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>66.874657</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H545" t="n">
-        <v>101.8541</v>
+        <v>101.854</v>
       </c>
     </row>
     <row r="546">
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H546" t="n">
         <v>101.9579</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H547" t="n">
         <v>102.6105</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.51739499999999</v>
+        <v>67.517403</v>
       </c>
       <c r="H548" t="n">
         <v>102.833</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.283661</v>
+        <v>67.283669</v>
       </c>
       <c r="H549" t="n">
         <v>102.477</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.22524300000001</v>
+        <v>67.22525</v>
       </c>
       <c r="H551" t="n">
         <v>102.388</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.478447</v>
+        <v>67.47843899999999</v>
       </c>
       <c r="H552" t="n">
         <v>102.7737</v>
@@ -21542,10 +21542,10 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.234978</v>
+        <v>67.23498499999999</v>
       </c>
       <c r="H556" t="n">
-        <v>102.4028</v>
+        <v>102.4029</v>
       </c>
     </row>
     <row r="557">
@@ -21580,10 +21580,10 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.619141</v>
+        <v>67.619148</v>
       </c>
       <c r="H557" t="n">
-        <v>102.9879</v>
+        <v>102.988</v>
       </c>
     </row>
     <row r="558">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H558" t="n">
         <v>103.4056</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>67.815033</v>
+        <v>67.81502500000001</v>
       </c>
       <c r="H559" t="n">
         <v>103.2863</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H563" t="n">
         <v>104.3603</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H565" t="n">
         <v>106.2697</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>69.48004899999999</v>
+        <v>69.480057</v>
       </c>
       <c r="H566" t="n">
         <v>105.8222</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H567" t="n">
         <v>106.1504</v>
@@ -22036,10 +22036,10 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H569" t="n">
-        <v>106.8962</v>
+        <v>106.8963</v>
       </c>
     </row>
     <row r="570">
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>70.273376</v>
+        <v>70.273369</v>
       </c>
       <c r="H570" t="n">
         <v>107.0305</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H573" t="n">
         <v>108.5819</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>70.723907</v>
+        <v>70.72391500000001</v>
       </c>
       <c r="H574" t="n">
         <v>107.7167</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H576" t="n">
         <v>107.1797</v>
@@ -22340,10 +22340,10 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H577" t="n">
-        <v>107.9404</v>
+        <v>107.9405</v>
       </c>
     </row>
     <row r="578">
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H587" t="n">
-        <v>110.1929</v>
+        <v>110.193</v>
       </c>
     </row>
     <row r="588">
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>73.201836</v>
+        <v>73.201843</v>
       </c>
       <c r="H588" t="n">
         <v>111.4907</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H589" t="n">
         <v>111.6548</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H591" t="n">
         <v>112.8929</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.828667</v>
+        <v>73.82867400000001</v>
       </c>
       <c r="H593" t="n">
         <v>112.4454</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H595" t="n">
         <v>112.5051</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H599" t="n">
         <v>113.5045</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H600" t="n">
         <v>113.8178</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>72.721931</v>
+        <v>72.72191599999999</v>
       </c>
       <c r="H610" t="n">
         <v>110.7598</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H611" t="n">
         <v>110.3272</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H612" t="n">
         <v>110.5062</v>
@@ -23784,10 +23784,10 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>72.64357800000001</v>
+        <v>72.643562</v>
       </c>
       <c r="H615" t="n">
-        <v>110.6405</v>
+        <v>110.6404</v>
       </c>
     </row>
     <row r="616">
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H616" t="n">
         <v>108.9202</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H617" t="n">
         <v>107.9157</v>
@@ -23936,10 +23936,10 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H619" t="n">
-        <v>108.7552</v>
+        <v>108.7553</v>
       </c>
     </row>
     <row r="620">
@@ -24050,10 +24050,10 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H622" t="n">
-        <v>108.7552</v>
+        <v>108.7553</v>
       </c>
     </row>
     <row r="623">
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H625" t="n">
         <v>110.7043</v>
@@ -24240,10 +24240,10 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H627" t="n">
-        <v>110.3445</v>
+        <v>110.3444</v>
       </c>
     </row>
     <row r="628">
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H629" t="n">
         <v>112.6233</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H630" t="n">
         <v>112.3684</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H632" t="n">
         <v>112.4434</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H634" t="n">
         <v>112.4134</v>
@@ -24658,7 +24658,7 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H638" t="n">
         <v>112.4434</v>
@@ -24772,7 +24772,7 @@
         </is>
       </c>
       <c r="G641" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H641" t="n">
         <v>111.9936</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H642" t="n">
         <v>112.3834</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H644" t="n">
         <v>113.3579</v>
@@ -25000,7 +25000,7 @@
         </is>
       </c>
       <c r="G647" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H647" t="n">
         <v>114.4374</v>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H648" t="n">
         <v>113.6728</v>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H650" t="n">
         <v>113.6728</v>
@@ -25304,7 +25304,7 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H655" t="n">
         <v>114.3774</v>
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H660" t="n">
         <v>117.4209</v>
@@ -25570,7 +25570,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H662" t="n">
         <v>116.6263</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H664" t="n">
         <v>116.1765</v>
@@ -25684,7 +25684,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H665" t="n">
         <v>116.0266</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H670" t="n">
         <v>116.6563</v>
@@ -25912,7 +25912,7 @@
         </is>
       </c>
       <c r="G671" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H671" t="n">
         <v>115.9666</v>
@@ -26140,7 +26140,7 @@
         </is>
       </c>
       <c r="G677" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H677" t="n">
         <v>119.3399</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1511" t="n">
         <v>100.6548</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>55.159622</v>
+        <v>55.159618</v>
       </c>
       <c r="H1512" t="n">
         <v>100.2124</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.429092</v>
+        <v>54.429089</v>
       </c>
       <c r="H1513" t="n">
         <v>98.8852</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.74078</v>
+        <v>54.740784</v>
       </c>
       <c r="H1514" t="n">
         <v>99.45140000000001</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.53624</v>
+        <v>54.536236</v>
       </c>
       <c r="H1515" t="n">
         <v>99.07980000000001</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1516" t="n">
         <v>99.593</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1517" t="n">
         <v>100.3893</v>
@@ -58098,10 +58098,10 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.682339</v>
+        <v>54.682343</v>
       </c>
       <c r="H1518" t="n">
-        <v>99.34520000000001</v>
+        <v>99.34529999999999</v>
       </c>
     </row>
     <row r="1519">
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1519" t="n">
         <v>100.3893</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1520" t="n">
         <v>100.6548</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1521" t="n">
         <v>100.4247</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.75378</v>
+        <v>55.753784</v>
       </c>
       <c r="H1523" t="n">
         <v>101.2918</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1526" t="n">
         <v>100.8848</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.295986</v>
+        <v>55.295982</v>
       </c>
       <c r="H1527" t="n">
         <v>100.4601</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.169353</v>
+        <v>55.169357</v>
       </c>
       <c r="H1529" t="n">
         <v>100.23</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1530" t="n">
         <v>100.4247</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.305717</v>
+        <v>55.305721</v>
       </c>
       <c r="H1538" t="n">
         <v>100.4778</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1539" t="n">
         <v>98.7259</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1545" t="n">
         <v>100.8848</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.75378</v>
+        <v>55.753784</v>
       </c>
       <c r="H1547" t="n">
         <v>101.2918</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.958324</v>
+        <v>55.958328</v>
       </c>
       <c r="H1551" t="n">
         <v>101.6634</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.841442</v>
+        <v>55.841446</v>
       </c>
       <c r="H1554" t="n">
         <v>101.4511</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.870659</v>
+        <v>55.870663</v>
       </c>
       <c r="H1555" t="n">
         <v>101.5042</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1557" t="n">
         <v>101.4688</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1559" t="n">
         <v>101.8487</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1560" t="n">
         <v>101.7244</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.558754</v>
+        <v>56.558758</v>
       </c>
       <c r="H1561" t="n">
         <v>102.7543</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1562" t="n">
         <v>103.1627</v>
@@ -59808,10 +59808,10 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.676044</v>
+        <v>56.676041</v>
       </c>
       <c r="H1563" t="n">
-        <v>102.9674</v>
+        <v>102.9673</v>
       </c>
     </row>
     <row r="1564">
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1565" t="n">
         <v>103.5</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>57.692471</v>
+        <v>57.692474</v>
       </c>
       <c r="H1567" t="n">
         <v>104.814</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1568" t="n">
         <v>105.755</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1570" t="n">
         <v>106.3055</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>58.39616</v>
+        <v>58.396156</v>
       </c>
       <c r="H1571" t="n">
         <v>106.0924</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>59.031437</v>
+        <v>59.031433</v>
       </c>
       <c r="H1572" t="n">
         <v>107.2466</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1573" t="n">
         <v>107.4241</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1575" t="n">
         <v>107.4596</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1576" t="n">
         <v>108.0811</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1577" t="n">
         <v>108.0988</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1579" t="n">
         <v>105.8793</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.91415</v>
+        <v>58.914154</v>
       </c>
       <c r="H1581" t="n">
         <v>107.0335</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.953247</v>
+        <v>58.953243</v>
       </c>
       <c r="H1583" t="n">
         <v>107.1045</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>58.835964</v>
+        <v>58.835968</v>
       </c>
       <c r="H1585" t="n">
         <v>106.8914</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>58.718685</v>
+        <v>58.718681</v>
       </c>
       <c r="H1586" t="n">
         <v>106.6784</v>
@@ -60720,7 +60720,7 @@
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.168262</v>
+        <v>59.168259</v>
       </c>
       <c r="H1587" t="n">
         <v>107.4951</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>59.246445</v>
+        <v>59.246449</v>
       </c>
       <c r="H1591" t="n">
         <v>107.6372</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1595" t="n">
         <v>109.3773</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.852402</v>
+        <v>59.852398</v>
       </c>
       <c r="H1597" t="n">
         <v>108.7381</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1598" t="n">
         <v>108.8979</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1599" t="n">
         <v>109.4838</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>61.406372</v>
+        <v>61.406376</v>
       </c>
       <c r="H1606" t="n">
         <v>111.5613</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>59.393051</v>
+        <v>59.393047</v>
       </c>
       <c r="H1610" t="n">
         <v>107.9035</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>58.581856</v>
+        <v>58.581852</v>
       </c>
       <c r="H1611" t="n">
         <v>106.4298</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1612" t="n">
         <v>105.4709</v>
@@ -61708,10 +61708,10 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1613" t="n">
-        <v>104.7429</v>
+        <v>104.743</v>
       </c>
     </row>
     <row r="1614">
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1614" t="n">
         <v>106.8027</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>58.4548</v>
+        <v>58.454803</v>
       </c>
       <c r="H1615" t="n">
         <v>106.1989</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H507" t="n">
         <v>98.79859999999999</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.19961499999999</v>
+        <v>65.199623</v>
       </c>
       <c r="H508" t="n">
         <v>99.30289999999999</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H509" t="n">
         <v>99.1694</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H512" t="n">
         <v>99.1842</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.842361</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H513" t="n">
         <v>100.2818</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H515" t="n">
         <v>100.4301</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H519" t="n">
         <v>100.8454</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H522" t="n">
         <v>100.6081</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H524" t="n">
         <v>100.9641</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368256</v>
       </c>
       <c r="H527" t="n">
         <v>101.0828</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H531" t="n">
         <v>101.7057</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H535" t="n">
         <v>100.5636</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H536" t="n">
         <v>100.356</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H539" t="n">
         <v>102.0469</v>
@@ -21048,10 +21048,10 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.874657</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H543" t="n">
-        <v>101.8541</v>
+        <v>101.854</v>
       </c>
     </row>
     <row r="544">
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.283661</v>
+        <v>67.283676</v>
       </c>
       <c r="H547" t="n">
         <v>102.477</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.29341100000001</v>
+        <v>67.293404</v>
       </c>
       <c r="H548" t="n">
         <v>102.4918</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.22524300000001</v>
+        <v>67.225235</v>
       </c>
       <c r="H549" t="n">
         <v>102.388</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H553" t="n">
         <v>102.299</v>
@@ -21466,10 +21466,10 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.234978</v>
+        <v>67.23498499999999</v>
       </c>
       <c r="H554" t="n">
-        <v>102.4028</v>
+        <v>102.4029</v>
       </c>
     </row>
     <row r="555">
@@ -21504,10 +21504,10 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.619141</v>
+        <v>67.619148</v>
       </c>
       <c r="H555" t="n">
-        <v>102.9879</v>
+        <v>102.988</v>
       </c>
     </row>
     <row r="556">
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H556" t="n">
         <v>103.4056</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H559" t="n">
         <v>103.9874</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H561" t="n">
         <v>104.3603</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H563" t="n">
         <v>106.2697</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H565" t="n">
         <v>106.1504</v>
@@ -21960,10 +21960,10 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H567" t="n">
-        <v>106.8962</v>
+        <v>106.8963</v>
       </c>
     </row>
     <row r="568">
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>70.273376</v>
+        <v>70.273369</v>
       </c>
       <c r="H568" t="n">
         <v>107.0305</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H571" t="n">
         <v>108.5819</v>
@@ -22188,10 +22188,10 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H573" t="n">
-        <v>106.7172</v>
+        <v>106.7173</v>
       </c>
     </row>
     <row r="574">
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H574" t="n">
         <v>107.1797</v>
@@ -22644,10 +22644,10 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H585" t="n">
-        <v>110.1929</v>
+        <v>110.193</v>
       </c>
     </row>
     <row r="586">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H587" t="n">
         <v>111.6548</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H588" t="n">
         <v>112.0427</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H589" t="n">
         <v>112.8929</v>
@@ -22834,10 +22834,10 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H590" t="n">
-        <v>112.4603</v>
+        <v>112.4604</v>
       </c>
     </row>
     <row r="591">
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>73.828667</v>
+        <v>73.82867400000001</v>
       </c>
       <c r="H591" t="n">
         <v>112.4454</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>73.88743599999999</v>
+        <v>73.887444</v>
       </c>
       <c r="H592" t="n">
         <v>112.5349</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H593" t="n">
         <v>112.5051</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H597" t="n">
         <v>113.5045</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H602" t="n">
         <v>114.2355</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>72.721931</v>
+        <v>72.721924</v>
       </c>
       <c r="H608" t="n">
         <v>110.7598</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H609" t="n">
         <v>110.3272</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H610" t="n">
         <v>110.5062</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>72.64357800000001</v>
+        <v>72.64357</v>
       </c>
       <c r="H613" t="n">
         <v>110.6405</v>
@@ -57604,7 +57604,7 @@
         </is>
       </c>
       <c r="G1505" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1505" t="n">
         <v>100.6548</v>
@@ -57642,7 +57642,7 @@
         </is>
       </c>
       <c r="G1506" t="n">
-        <v>55.159622</v>
+        <v>55.159618</v>
       </c>
       <c r="H1506" t="n">
         <v>100.2124</v>
@@ -57718,7 +57718,7 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>54.74078</v>
+        <v>54.740784</v>
       </c>
       <c r="H1508" t="n">
         <v>99.45140000000001</v>
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>54.53624</v>
+        <v>54.536236</v>
       </c>
       <c r="H1509" t="n">
         <v>99.07980000000001</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1510" t="n">
         <v>99.593</v>
@@ -57870,10 +57870,10 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.682339</v>
+        <v>54.682343</v>
       </c>
       <c r="H1512" t="n">
-        <v>99.34520000000001</v>
+        <v>99.34529999999999</v>
       </c>
     </row>
     <row r="1513">
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>55.403126</v>
+        <v>55.40313</v>
       </c>
       <c r="H1514" t="n">
         <v>100.6548</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1515" t="n">
         <v>100.4247</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.169353</v>
+        <v>55.169357</v>
       </c>
       <c r="H1523" t="n">
         <v>100.23</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1524" t="n">
         <v>100.4247</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>56.104431</v>
+        <v>56.104427</v>
       </c>
       <c r="H1528" t="n">
         <v>101.9289</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>56.143391</v>
+        <v>56.143387</v>
       </c>
       <c r="H1530" t="n">
         <v>101.9996</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.305717</v>
+        <v>55.305721</v>
       </c>
       <c r="H1532" t="n">
         <v>100.4778</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1533" t="n">
         <v>98.7259</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1535" t="n">
         <v>98.9913</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1537" t="n">
         <v>98.86750000000001</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>54.877148</v>
+        <v>54.877144</v>
       </c>
       <c r="H1538" t="n">
         <v>99.6992</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.958324</v>
+        <v>55.958328</v>
       </c>
       <c r="H1545" t="n">
         <v>101.6634</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.987545</v>
+        <v>55.987549</v>
       </c>
       <c r="H1546" t="n">
         <v>101.7165</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1551" t="n">
         <v>101.4688</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1552" t="n">
         <v>102.2749</v>
@@ -59466,7 +59466,7 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1554" t="n">
         <v>101.7244</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>56.558754</v>
+        <v>56.558758</v>
       </c>
       <c r="H1555" t="n">
         <v>102.7543</v>
@@ -59580,10 +59580,10 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>56.676044</v>
+        <v>56.676041</v>
       </c>
       <c r="H1557" t="n">
-        <v>102.9674</v>
+        <v>102.9673</v>
       </c>
     </row>
     <row r="1558">
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1559" t="n">
         <v>103.5</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>57.692471</v>
+        <v>57.692474</v>
       </c>
       <c r="H1561" t="n">
         <v>104.814</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1562" t="n">
         <v>105.755</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1563" t="n">
         <v>106.341</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1564" t="n">
         <v>106.3055</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1567" t="n">
         <v>107.4241</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1569" t="n">
         <v>107.4596</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1570" t="n">
         <v>108.0811</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1571" t="n">
         <v>108.0988</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1573" t="n">
         <v>105.8793</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1576" t="n">
         <v>106.9447</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>58.953247</v>
+        <v>58.953243</v>
       </c>
       <c r="H1577" t="n">
         <v>107.1045</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1578" t="n">
         <v>107.7437</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1589" t="n">
         <v>109.3773</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1592" t="n">
         <v>108.8979</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1593" t="n">
         <v>109.4838</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>60.956795</v>
+        <v>60.956799</v>
       </c>
       <c r="H1594" t="n">
         <v>110.7445</v>
@@ -61480,10 +61480,10 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1607" t="n">
-        <v>104.7429</v>
+        <v>104.743</v>
       </c>
     </row>
     <row r="1608">
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1608" t="n">
         <v>106.8027</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>37.419998</v>
+        <v>37.080002</v>
       </c>
       <c r="H253" t="n">
-        <v>125.9085</v>
+        <v>124.7645</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>49.990002</v>
+        <v>49.889999</v>
       </c>
       <c r="H504" t="n">
-        <v>132.494</v>
+        <v>132.229</v>
       </c>
     </row>
     <row r="505">
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.8685</v>
+        <v>64.868515</v>
       </c>
       <c r="H509" t="n">
         <v>98.79859999999999</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>65.199623</v>
+        <v>65.19961499999999</v>
       </c>
       <c r="H510" t="n">
         <v>99.30289999999999</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.540482</v>
+        <v>65.540474</v>
       </c>
       <c r="H512" t="n">
         <v>99.822</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.559952</v>
+        <v>65.559944</v>
       </c>
       <c r="H513" t="n">
         <v>99.85169999999999</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.842377</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H515" t="n">
         <v>100.2818</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.939751</v>
+        <v>65.939758</v>
       </c>
       <c r="H517" t="n">
         <v>100.4301</v>
@@ -20098,10 +20098,10 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>66.066345</v>
+        <v>66.06635300000001</v>
       </c>
       <c r="H518" t="n">
-        <v>100.6229</v>
+        <v>100.623</v>
       </c>
     </row>
     <row r="519">
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.339043</v>
+        <v>66.339035</v>
       </c>
       <c r="H520" t="n">
         <v>101.0383</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>66.212433</v>
+        <v>66.212425</v>
       </c>
       <c r="H521" t="n">
         <v>100.8454</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.09556600000001</v>
+        <v>66.095573</v>
       </c>
       <c r="H523" t="n">
         <v>100.6675</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H524" t="n">
         <v>100.6081</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.09556600000001</v>
+        <v>66.095573</v>
       </c>
       <c r="H525" t="n">
         <v>100.6675</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.988449</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H527" t="n">
         <v>100.5043</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368256</v>
       </c>
       <c r="H529" t="n">
         <v>101.0828</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H530" t="n">
         <v>101.9579</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H531" t="n">
-        <v>102.9072</v>
+        <v>102.9071</v>
       </c>
     </row>
     <row r="532">
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H532" t="n">
         <v>102.1359</v>
@@ -20820,10 +20820,10 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.027405</v>
+        <v>66.027412</v>
       </c>
       <c r="H537" t="n">
-        <v>100.5636</v>
+        <v>100.5637</v>
       </c>
     </row>
     <row r="538">
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.387726</v>
+        <v>66.38771800000001</v>
       </c>
       <c r="H540" t="n">
         <v>101.1124</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H541" t="n">
         <v>102.0469</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H544" t="n">
         <v>102.1359</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H546" t="n">
         <v>101.9579</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.371323</v>
+        <v>67.371315</v>
       </c>
       <c r="H547" t="n">
         <v>102.6105</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H548" t="n">
         <v>102.833</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.283669</v>
+        <v>67.283661</v>
       </c>
       <c r="H549" t="n">
         <v>102.477</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.3908</v>
+        <v>67.390793</v>
       </c>
       <c r="H553" t="n">
         <v>102.6402</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H555" t="n">
         <v>102.299</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H558" t="n">
         <v>103.4056</v>
@@ -21770,10 +21770,10 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>68.304733</v>
+        <v>68.30474100000001</v>
       </c>
       <c r="H562" t="n">
-        <v>104.0321</v>
+        <v>104.0322</v>
       </c>
     </row>
     <row r="563">
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H563" t="n">
         <v>104.3603</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>69.773865</v>
+        <v>69.773872</v>
       </c>
       <c r="H565" t="n">
         <v>106.2697</v>
@@ -22036,10 +22036,10 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>70.18523399999999</v>
+        <v>70.185226</v>
       </c>
       <c r="H569" t="n">
-        <v>106.8963</v>
+        <v>106.8962</v>
       </c>
     </row>
     <row r="570">
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>71.340935</v>
+        <v>71.340942</v>
       </c>
       <c r="H572" t="n">
         <v>108.6565</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H573" t="n">
         <v>108.5819</v>
@@ -22264,10 +22264,10 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H575" t="n">
-        <v>106.7173</v>
+        <v>106.7172</v>
       </c>
     </row>
     <row r="576">
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.371323</v>
+        <v>70.371315</v>
       </c>
       <c r="H576" t="n">
         <v>107.1797</v>
@@ -22340,10 +22340,10 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H577" t="n">
-        <v>107.9405</v>
+        <v>107.9404</v>
       </c>
     </row>
     <row r="578">
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.518227</v>
+        <v>70.51823400000001</v>
       </c>
       <c r="H578" t="n">
         <v>107.4034</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.410484</v>
+        <v>70.410492</v>
       </c>
       <c r="H580" t="n">
         <v>107.2393</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.68472300000001</v>
+        <v>70.684731</v>
       </c>
       <c r="H582" t="n">
         <v>107.657</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>72.87863900000001</v>
+        <v>72.878632</v>
       </c>
       <c r="H586" t="n">
         <v>110.9985</v>
@@ -22720,10 +22720,10 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H587" t="n">
-        <v>110.193</v>
+        <v>110.1929</v>
       </c>
     </row>
     <row r="588">
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H589" t="n">
         <v>111.6548</v>
@@ -22872,7 +22872,7 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H591" t="n">
         <v>112.8929</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.86784400000001</v>
+        <v>73.867851</v>
       </c>
       <c r="H595" t="n">
         <v>112.5051</v>
@@ -23062,7 +23062,7 @@
         </is>
       </c>
       <c r="G596" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H596" t="n">
         <v>113.4598</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H597" t="n">
         <v>113.4598</v>
@@ -23176,10 +23176,10 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>74.524063</v>
+        <v>74.52404799999999</v>
       </c>
       <c r="H599" t="n">
-        <v>113.5046</v>
+        <v>113.5045</v>
       </c>
     </row>
     <row r="600">
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H600" t="n">
         <v>113.8178</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>75.141098</v>
+        <v>75.14109000000001</v>
       </c>
       <c r="H601" t="n">
         <v>114.4443</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>75.278206</v>
+        <v>75.27821400000001</v>
       </c>
       <c r="H602" t="n">
         <v>114.6532</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>75.00398300000001</v>
+        <v>75.003975</v>
       </c>
       <c r="H604" t="n">
         <v>114.2355</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>72.721924</v>
+        <v>72.721931</v>
       </c>
       <c r="H610" t="n">
         <v>110.7598</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H611" t="n">
         <v>110.3272</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>72.55542800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H612" t="n">
         <v>110.5062</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>72.64357</v>
+        <v>72.64357800000001</v>
       </c>
       <c r="H615" t="n">
         <v>110.6405</v>
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H616" t="n">
         <v>108.9202</v>
@@ -23860,7 +23860,7 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H617" t="n">
         <v>107.9157</v>
@@ -23936,10 +23936,10 @@
         </is>
       </c>
       <c r="G619" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H619" t="n">
-        <v>108.7553</v>
+        <v>108.7552</v>
       </c>
     </row>
     <row r="620">
@@ -24050,10 +24050,10 @@
         </is>
       </c>
       <c r="G622" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H622" t="n">
-        <v>108.7553</v>
+        <v>108.7552</v>
       </c>
     </row>
     <row r="623">
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H625" t="n">
         <v>110.7043</v>
@@ -24240,10 +24240,10 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H627" t="n">
-        <v>110.3444</v>
+        <v>110.3445</v>
       </c>
     </row>
     <row r="628">
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H629" t="n">
         <v>112.6233</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H630" t="n">
         <v>112.3684</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H632" t="n">
         <v>112.4434</v>
@@ -24506,7 +24506,7 @@
         </is>
       </c>
       <c r="G634" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H634" t="n">
         <v>112.4134</v>
@@ -24658,7 +24658,7 @@
         </is>
       </c>
       <c r="G638" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H638" t="n">
         <v>112.4434</v>
@@ -24772,7 +24772,7 @@
         </is>
       </c>
       <c r="G641" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H641" t="n">
         <v>111.9936</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H642" t="n">
         <v>112.3834</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="G644" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H644" t="n">
         <v>113.3579</v>
@@ -25000,7 +25000,7 @@
         </is>
       </c>
       <c r="G647" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H647" t="n">
         <v>114.4374</v>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H648" t="n">
         <v>113.6728</v>
@@ -25114,7 +25114,7 @@
         </is>
       </c>
       <c r="G650" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H650" t="n">
         <v>113.6728</v>
@@ -25304,7 +25304,7 @@
         </is>
       </c>
       <c r="G655" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H655" t="n">
         <v>114.3774</v>
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H660" t="n">
         <v>117.4209</v>
@@ -25570,7 +25570,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H662" t="n">
         <v>116.6263</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H664" t="n">
         <v>116.1765</v>
@@ -25684,7 +25684,7 @@
         </is>
       </c>
       <c r="G665" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H665" t="n">
         <v>116.0266</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H670" t="n">
         <v>116.6563</v>
@@ -25912,7 +25912,7 @@
         </is>
       </c>
       <c r="G671" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H671" t="n">
         <v>115.9666</v>
@@ -26140,7 +26140,7 @@
         </is>
       </c>
       <c r="G677" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H677" t="n">
         <v>119.3399</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.959999</v>
+        <v>81</v>
       </c>
       <c r="H755" t="n">
-        <v>123.3069</v>
+        <v>123.3678</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>131.869995</v>
+        <v>131.850006</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.7159</v>
+        <v>120.6976</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>131.869995</v>
+        <v>131.850006</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.7159</v>
+        <v>120.6976</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>131.869995</v>
+        <v>131.850006</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.7159</v>
+        <v>120.6976</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>55.042732</v>
+        <v>55.042736</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57832,10 +57832,10 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>55.403122</v>
+        <v>55.40313</v>
       </c>
       <c r="H1511" t="n">
-        <v>100.6547</v>
+        <v>100.6548</v>
       </c>
     </row>
     <row r="1512">
@@ -57870,10 +57870,10 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>55.159622</v>
+        <v>55.159615</v>
       </c>
       <c r="H1512" t="n">
-        <v>100.2124</v>
+        <v>100.2123</v>
       </c>
     </row>
     <row r="1513">
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.74078</v>
+        <v>54.740788</v>
       </c>
       <c r="H1514" t="n">
         <v>99.45140000000001</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.536236</v>
+        <v>54.536232</v>
       </c>
       <c r="H1515" t="n">
         <v>99.07980000000001</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1518" t="n">
         <v>99.34520000000001</v>
@@ -58174,10 +58174,10 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.403122</v>
+        <v>55.40313</v>
       </c>
       <c r="H1520" t="n">
-        <v>100.6547</v>
+        <v>100.6548</v>
       </c>
     </row>
     <row r="1521">
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1521" t="n">
         <v>100.4247</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1523" t="n">
         <v>101.2918</v>
@@ -58329,7 +58329,7 @@
         <v>55.636894</v>
       </c>
       <c r="H1524" t="n">
-        <v>101.0795</v>
+        <v>101.0794</v>
       </c>
     </row>
     <row r="1525">
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.588188</v>
+        <v>55.588192</v>
       </c>
       <c r="H1525" t="n">
         <v>100.991</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1526" t="n">
         <v>100.8848</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1530" t="n">
         <v>100.4247</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.867405</v>
+        <v>54.867409</v>
       </c>
       <c r="H1531" t="n">
         <v>99.6815</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>54.584938</v>
+        <v>54.584934</v>
       </c>
       <c r="H1532" t="n">
         <v>99.1683</v>
@@ -58709,7 +58709,7 @@
         <v>56.104427</v>
       </c>
       <c r="H1534" t="n">
-        <v>101.9289</v>
+        <v>101.9288</v>
       </c>
     </row>
     <row r="1535">
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>56.523266</v>
+        <v>56.523262</v>
       </c>
       <c r="H1535" t="n">
         <v>102.6898</v>
@@ -58785,7 +58785,7 @@
         <v>56.143394</v>
       </c>
       <c r="H1536" t="n">
-        <v>101.9997</v>
+        <v>101.9996</v>
       </c>
     </row>
     <row r="1537">
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1541" t="n">
         <v>98.9913</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>54.351166</v>
+        <v>54.351162</v>
       </c>
       <c r="H1542" t="n">
         <v>98.7436</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.877151</v>
+        <v>54.877148</v>
       </c>
       <c r="H1544" t="n">
         <v>99.6992</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1545" t="n">
         <v>100.8848</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.75378</v>
+        <v>55.753777</v>
       </c>
       <c r="H1547" t="n">
         <v>101.2918</v>
@@ -59279,7 +59279,7 @@
         <v>55.636894</v>
       </c>
       <c r="H1549" t="n">
-        <v>101.0795</v>
+        <v>101.0794</v>
       </c>
     </row>
     <row r="1550">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.724556</v>
+        <v>55.72456</v>
       </c>
       <c r="H1550" t="n">
         <v>101.2387</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.958328</v>
+        <v>55.958332</v>
       </c>
       <c r="H1551" t="n">
         <v>101.6634</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1557" t="n">
         <v>101.4688</v>
@@ -59618,10 +59618,10 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1558" t="n">
-        <v>102.2749</v>
+        <v>102.2748</v>
       </c>
     </row>
     <row r="1559">
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1560" t="n">
         <v>101.7244</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.558754</v>
+        <v>56.558758</v>
       </c>
       <c r="H1561" t="n">
         <v>102.7543</v>
@@ -59773,7 +59773,7 @@
         <v>56.783543</v>
       </c>
       <c r="H1562" t="n">
-        <v>103.1627</v>
+        <v>103.1626</v>
       </c>
     </row>
     <row r="1563">
@@ -59808,10 +59808,10 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.676044</v>
+        <v>56.676041</v>
       </c>
       <c r="H1563" t="n">
-        <v>102.9674</v>
+        <v>102.9673</v>
       </c>
     </row>
     <row r="1564">
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1565" t="n">
         <v>103.5</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>57.692471</v>
+        <v>57.692474</v>
       </c>
       <c r="H1567" t="n">
         <v>104.814</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1568" t="n">
         <v>105.755</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1569" t="n">
         <v>106.341</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1570" t="n">
         <v>106.3055</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>59.129166</v>
+        <v>59.129169</v>
       </c>
       <c r="H1573" t="n">
         <v>107.4241</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1575" t="n">
         <v>107.4596</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1576" t="n">
         <v>108.0811</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1577" t="n">
         <v>108.0988</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1579" t="n">
         <v>105.8793</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1582" t="n">
         <v>106.9447</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>58.953247</v>
+        <v>58.953243</v>
       </c>
       <c r="H1583" t="n">
         <v>107.1045</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1584" t="n">
         <v>107.7437</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1595" t="n">
         <v>109.3773</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1598" t="n">
         <v>108.8979</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1599" t="n">
         <v>109.4838</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>60.956795</v>
+        <v>60.956799</v>
       </c>
       <c r="H1600" t="n">
         <v>110.7445</v>
@@ -61255,7 +61255,7 @@
         <v>60.65382</v>
       </c>
       <c r="H1601" t="n">
-        <v>110.1941</v>
+        <v>110.194</v>
       </c>
     </row>
     <row r="1602">
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1613" t="n">
         <v>104.7429</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1614" t="n">
         <v>106.8027</v>
@@ -62737,7 +62737,7 @@
         <v>61.085079</v>
       </c>
       <c r="H1640" t="n">
-        <v>110.9776</v>
+        <v>110.9775</v>
       </c>
     </row>
     <row r="1641">
@@ -62889,7 +62889,7 @@
         <v>59.948612</v>
       </c>
       <c r="H1644" t="n">
-        <v>108.9129</v>
+        <v>108.9128</v>
       </c>
     </row>
     <row r="1645">
@@ -63193,7 +63193,7 @@
         <v>61.055683</v>
       </c>
       <c r="H1652" t="n">
-        <v>110.9242</v>
+        <v>110.9241</v>
       </c>
     </row>
     <row r="1653">
@@ -64941,7 +64941,7 @@
         <v>63.321518</v>
       </c>
       <c r="H1698" t="n">
-        <v>115.0407</v>
+        <v>115.0406</v>
       </c>
     </row>
     <row r="1699">
@@ -65055,7 +65055,7 @@
         <v>63.371056</v>
       </c>
       <c r="H1701" t="n">
-        <v>115.1307</v>
+        <v>115.1306</v>
       </c>
     </row>
     <row r="1702">
@@ -65625,7 +65625,7 @@
         <v>64.95607</v>
       </c>
       <c r="H1716" t="n">
-        <v>118.0103</v>
+        <v>118.0102</v>
       </c>
     </row>
     <row r="1717">
@@ -66385,7 +66385,7 @@
         <v>64.17346999999999</v>
       </c>
       <c r="H1736" t="n">
-        <v>116.5885</v>
+        <v>116.5884</v>
       </c>
     </row>
     <row r="1737">
@@ -66955,7 +66955,7 @@
         <v>63.580002</v>
       </c>
       <c r="H1751" t="n">
-        <v>115.5103</v>
+        <v>115.5102</v>
       </c>
     </row>
     <row r="1752">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.040001</v>
+        <v>63.029999</v>
       </c>
       <c r="H1760" t="n">
-        <v>114.5292</v>
+        <v>114.511</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H509" t="n">
         <v>98.79859999999999</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>65.19961499999999</v>
+        <v>65.199623</v>
       </c>
       <c r="H510" t="n">
         <v>99.30289999999999</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.559944</v>
+        <v>65.559952</v>
       </c>
       <c r="H513" t="n">
         <v>99.85169999999999</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407211</v>
       </c>
       <c r="H519" t="n">
         <v>101.1421</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407211</v>
       </c>
       <c r="H522" t="n">
         <v>101.1421</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H524" t="n">
         <v>100.6081</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H526" t="n">
         <v>100.9641</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H529" t="n">
         <v>101.0828</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H531" t="n">
-        <v>102.9071</v>
+        <v>102.9072</v>
       </c>
     </row>
     <row r="532">
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.416939</v>
+        <v>66.41693100000001</v>
       </c>
       <c r="H534" t="n">
         <v>101.1569</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>65.754715</v>
+        <v>65.754723</v>
       </c>
       <c r="H535" t="n">
         <v>100.1483</v>
@@ -20820,10 +20820,10 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.027412</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H537" t="n">
-        <v>100.5637</v>
+        <v>100.5636</v>
       </c>
     </row>
     <row r="538">
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.124786</v>
+        <v>66.12479399999999</v>
       </c>
       <c r="H539" t="n">
         <v>100.712</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.38771800000001</v>
+        <v>66.387733</v>
       </c>
       <c r="H540" t="n">
         <v>101.1124</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H547" t="n">
         <v>102.6105</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.51739499999999</v>
+        <v>67.517403</v>
       </c>
       <c r="H548" t="n">
         <v>102.833</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.770599</v>
+        <v>67.77059199999999</v>
       </c>
       <c r="H554" t="n">
         <v>103.2186</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H555" t="n">
         <v>102.299</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H561" t="n">
         <v>103.9874</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H564" t="n">
         <v>105.4642</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H565" t="n">
         <v>106.2697</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H567" t="n">
         <v>106.1504</v>
@@ -22036,10 +22036,10 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H569" t="n">
-        <v>106.8962</v>
+        <v>106.8963</v>
       </c>
     </row>
     <row r="570">
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H576" t="n">
         <v>107.1797</v>
@@ -22454,10 +22454,10 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.410492</v>
+        <v>70.4105</v>
       </c>
       <c r="H580" t="n">
-        <v>107.2393</v>
+        <v>107.2394</v>
       </c>
     </row>
     <row r="581">
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H584" t="n">
         <v>109.1786</v>
@@ -22682,7 +22682,7 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H586" t="n">
         <v>110.9985</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H590" t="n">
         <v>112.0427</v>
@@ -22910,10 +22910,10 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H592" t="n">
-        <v>112.4603</v>
+        <v>112.4604</v>
       </c>
     </row>
     <row r="593">
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H595" t="n">
         <v>112.5051</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H599" t="n">
         <v>113.5045</v>
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H604" t="n">
         <v>114.2355</v>
@@ -23404,7 +23404,7 @@
         </is>
       </c>
       <c r="G605" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H605" t="n">
         <v>111.7294</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H612" t="n">
         <v>110.5062</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>72.64357800000001</v>
+        <v>72.64357</v>
       </c>
       <c r="H615" t="n">
         <v>110.6405</v>
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>55.042736</v>
+        <v>55.042728</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.974548</v>
+        <v>54.974545</v>
       </c>
       <c r="H1510" t="n">
         <v>99.87609999999999</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1511" t="n">
         <v>100.6548</v>
@@ -57870,10 +57870,10 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>55.159615</v>
+        <v>55.159618</v>
       </c>
       <c r="H1512" t="n">
-        <v>100.2123</v>
+        <v>100.2124</v>
       </c>
     </row>
     <row r="1513">
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.740788</v>
+        <v>54.74078</v>
       </c>
       <c r="H1514" t="n">
         <v>99.45140000000001</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.536232</v>
+        <v>54.536236</v>
       </c>
       <c r="H1515" t="n">
         <v>99.07980000000001</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.818707</v>
+        <v>54.818699</v>
       </c>
       <c r="H1516" t="n">
         <v>99.593</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1517" t="n">
         <v>100.3893</v>
@@ -58101,7 +58101,7 @@
         <v>54.682339</v>
       </c>
       <c r="H1518" t="n">
-        <v>99.34520000000001</v>
+        <v>99.34529999999999</v>
       </c>
     </row>
     <row r="1519">
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1519" t="n">
         <v>100.3893</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.40313</v>
+        <v>55.403126</v>
       </c>
       <c r="H1520" t="n">
         <v>100.6548</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1521" t="n">
         <v>100.4247</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1524" t="n">
-        <v>101.0794</v>
+        <v>101.0795</v>
       </c>
     </row>
     <row r="1525">
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.588192</v>
+        <v>55.588196</v>
       </c>
       <c r="H1525" t="n">
         <v>100.991</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1526" t="n">
         <v>100.8848</v>
@@ -58519,7 +58519,7 @@
         <v>55.169357</v>
       </c>
       <c r="H1529" t="n">
-        <v>100.23</v>
+        <v>100.2301</v>
       </c>
     </row>
     <row r="1530">
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1530" t="n">
         <v>100.4247</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.867409</v>
+        <v>54.867413</v>
       </c>
       <c r="H1531" t="n">
         <v>99.6815</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1533" t="n">
         <v>100.6194</v>
@@ -58706,10 +58706,10 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1534" t="n">
-        <v>101.9288</v>
+        <v>101.9289</v>
       </c>
     </row>
     <row r="1535">
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>56.523262</v>
+        <v>56.523266</v>
       </c>
       <c r="H1535" t="n">
         <v>102.6898</v>
@@ -58782,10 +58782,10 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1536" t="n">
-        <v>101.9996</v>
+        <v>101.9997</v>
       </c>
     </row>
     <row r="1537">
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.607674</v>
+        <v>55.60767</v>
       </c>
       <c r="H1537" t="n">
         <v>101.0264</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>55.305717</v>
+        <v>55.305721</v>
       </c>
       <c r="H1538" t="n">
         <v>100.4778</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1539" t="n">
         <v>98.7259</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1540" t="n">
         <v>98.6374</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.487534</v>
+        <v>54.48753</v>
       </c>
       <c r="H1541" t="n">
         <v>98.9913</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>54.351162</v>
+        <v>54.35117</v>
       </c>
       <c r="H1542" t="n">
         <v>98.7436</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1543" t="n">
         <v>98.86750000000001</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.877148</v>
+        <v>54.877144</v>
       </c>
       <c r="H1544" t="n">
         <v>99.6992</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1545" t="n">
         <v>100.8848</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1546" t="n">
         <v>100.9556</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1548" t="n">
         <v>100.9556</v>
@@ -59276,10 +59276,10 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1549" t="n">
-        <v>101.0794</v>
+        <v>101.0795</v>
       </c>
     </row>
     <row r="1550">
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.72456</v>
+        <v>55.724556</v>
       </c>
       <c r="H1550" t="n">
         <v>101.2387</v>
@@ -59428,10 +59428,10 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1553" t="n">
-        <v>101.5572</v>
+        <v>101.5573</v>
       </c>
     </row>
     <row r="1554">
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.870663</v>
+        <v>55.870667</v>
       </c>
       <c r="H1555" t="n">
         <v>101.5042</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>56.172611</v>
+        <v>56.172615</v>
       </c>
       <c r="H1556" t="n">
         <v>102.0527</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.851185</v>
+        <v>55.851181</v>
       </c>
       <c r="H1557" t="n">
         <v>101.4688</v>
@@ -59621,7 +59621,7 @@
         <v>56.294872</v>
       </c>
       <c r="H1558" t="n">
-        <v>102.2748</v>
+        <v>102.2749</v>
       </c>
     </row>
     <row r="1559">
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1559" t="n">
         <v>101.8487</v>
@@ -59770,10 +59770,10 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1562" t="n">
-        <v>103.1626</v>
+        <v>103.1627</v>
       </c>
     </row>
     <row r="1563">
@@ -59811,7 +59811,7 @@
         <v>56.676041</v>
       </c>
       <c r="H1563" t="n">
-        <v>102.9673</v>
+        <v>102.9674</v>
       </c>
     </row>
     <row r="1564">
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1565" t="n">
         <v>103.5</v>
@@ -60001,7 +60001,7 @@
         <v>58.210468</v>
       </c>
       <c r="H1568" t="n">
-        <v>105.755</v>
+        <v>105.7551</v>
       </c>
     </row>
     <row r="1569">
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>58.53299</v>
+        <v>58.532986</v>
       </c>
       <c r="H1569" t="n">
         <v>106.341</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>58.513443</v>
+        <v>58.513439</v>
       </c>
       <c r="H1570" t="n">
         <v>106.3055</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>59.129169</v>
+        <v>59.129162</v>
       </c>
       <c r="H1573" t="n">
         <v>107.4241</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1575" t="n">
         <v>107.4596</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1576" t="n">
         <v>108.0811</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1577" t="n">
         <v>108.0988</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1579" t="n">
         <v>105.8793</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.259331</v>
+        <v>58.259335</v>
       </c>
       <c r="H1580" t="n">
         <v>105.8438</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.86528</v>
+        <v>58.865284</v>
       </c>
       <c r="H1582" t="n">
         <v>106.9447</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.305092</v>
+        <v>59.305088</v>
       </c>
       <c r="H1584" t="n">
         <v>107.7437</v>
@@ -60913,7 +60913,7 @@
         <v>59.744892</v>
       </c>
       <c r="H1592" t="n">
-        <v>108.5427</v>
+        <v>108.5428</v>
       </c>
     </row>
     <row r="1593">
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>60.11628</v>
+        <v>60.116283</v>
       </c>
       <c r="H1594" t="n">
         <v>109.2175</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1595" t="n">
         <v>109.3773</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1596" t="n">
         <v>108.8801</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1598" t="n">
         <v>108.8979</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1599" t="n">
         <v>109.4838</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>60.956799</v>
+        <v>60.956791</v>
       </c>
       <c r="H1600" t="n">
         <v>110.7445</v>
@@ -61255,7 +61255,7 @@
         <v>60.65382</v>
       </c>
       <c r="H1601" t="n">
-        <v>110.194</v>
+        <v>110.1941</v>
       </c>
     </row>
     <row r="1602">
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1603" t="n">
         <v>110.5847</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>61.474785</v>
+        <v>61.474789</v>
       </c>
       <c r="H1605" t="n">
         <v>111.6856</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>61.445465</v>
+        <v>61.445469</v>
       </c>
       <c r="H1607" t="n">
         <v>111.6323</v>
@@ -61670,10 +61670,10 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1612" t="n">
-        <v>105.4709</v>
+        <v>105.471</v>
       </c>
     </row>
     <row r="1613">
@@ -61708,10 +61708,10 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>57.653385</v>
+        <v>57.653381</v>
       </c>
       <c r="H1613" t="n">
-        <v>104.7429</v>
+        <v>104.743</v>
       </c>
     </row>
     <row r="1614">
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1614" t="n">
         <v>106.8027</v>
@@ -61787,7 +61787,7 @@
         <v>58.4548</v>
       </c>
       <c r="H1615" t="n">
-        <v>106.1989</v>
+        <v>106.199</v>
       </c>
     </row>
     <row r="1616">
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1619" t="n">
         <v>106.154</v>
@@ -62053,7 +62053,7 @@
         <v>55.549702</v>
       </c>
       <c r="H1622" t="n">
-        <v>100.921</v>
+        <v>100.9211</v>
       </c>
     </row>
     <row r="1623">
@@ -62658,7 +62658,7 @@
         </is>
       </c>
       <c r="G1638" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1638" t="n">
         <v>109.2866</v>
@@ -62734,10 +62734,10 @@
         </is>
       </c>
       <c r="G1640" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1640" t="n">
-        <v>110.9775</v>
+        <v>110.9776</v>
       </c>
     </row>
     <row r="1641">
@@ -62810,10 +62810,10 @@
         </is>
       </c>
       <c r="G1642" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1642" t="n">
-        <v>109.1442</v>
+        <v>109.1443</v>
       </c>
     </row>
     <row r="1643">
@@ -62886,10 +62886,10 @@
         </is>
       </c>
       <c r="G1644" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1644" t="n">
-        <v>108.9128</v>
+        <v>108.9129</v>
       </c>
     </row>
     <row r="1645">
@@ -62924,7 +62924,7 @@
         </is>
       </c>
       <c r="G1645" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1645" t="n">
         <v>108.3255</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1648" t="n">
         <v>107.0973</v>
@@ -63152,7 +63152,7 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1651" t="n">
         <v>108.5213</v>
@@ -63190,10 +63190,10 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1652" t="n">
-        <v>110.9241</v>
+        <v>110.9242</v>
       </c>
     </row>
     <row r="1653">
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1654" t="n">
         <v>109.1086</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1656" t="n">
         <v>108.1119</v>
@@ -63383,7 +63383,7 @@
         <v>60.026989</v>
       </c>
       <c r="H1657" t="n">
-        <v>109.0552</v>
+        <v>109.0553</v>
       </c>
     </row>
     <row r="1658">
@@ -63497,7 +63497,7 @@
         <v>60.026989</v>
       </c>
       <c r="H1660" t="n">
-        <v>109.0552</v>
+        <v>109.0553</v>
       </c>
     </row>
     <row r="1661">
@@ -63535,7 +63535,7 @@
         <v>60.066177</v>
       </c>
       <c r="H1661" t="n">
-        <v>109.1264</v>
+        <v>109.1265</v>
       </c>
     </row>
     <row r="1662">
@@ -63722,7 +63722,7 @@
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1666" t="n">
         <v>112.4193</v>
@@ -63798,7 +63798,7 @@
         </is>
       </c>
       <c r="G1668" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1668" t="n">
         <v>111.9387</v>
@@ -63912,7 +63912,7 @@
         </is>
       </c>
       <c r="G1671" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1671" t="n">
         <v>112.0633</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1673" t="n">
         <v>111.9387</v>
@@ -64026,7 +64026,7 @@
         </is>
       </c>
       <c r="G1674" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1674" t="n">
         <v>111.4937</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1678" t="n">
         <v>111.3513</v>
@@ -64675,7 +64675,7 @@
         <v>63.341331</v>
       </c>
       <c r="H1691" t="n">
-        <v>115.0766</v>
+        <v>115.0767</v>
       </c>
     </row>
     <row r="1692">
@@ -64941,7 +64941,7 @@
         <v>63.321518</v>
       </c>
       <c r="H1698" t="n">
-        <v>115.0406</v>
+        <v>115.0407</v>
       </c>
     </row>
     <row r="1699">
@@ -64979,7 +64979,7 @@
         <v>63.390869</v>
       </c>
       <c r="H1699" t="n">
-        <v>115.1666</v>
+        <v>115.1667</v>
       </c>
     </row>
     <row r="1700">
@@ -65017,7 +65017,7 @@
         <v>63.390869</v>
       </c>
       <c r="H1700" t="n">
-        <v>115.1666</v>
+        <v>115.1667</v>
       </c>
     </row>
     <row r="1701">
@@ -65055,7 +65055,7 @@
         <v>63.371056</v>
       </c>
       <c r="H1701" t="n">
-        <v>115.1306</v>
+        <v>115.1307</v>
       </c>
     </row>
     <row r="1702">
@@ -65169,7 +65169,7 @@
         <v>63.361145</v>
       </c>
       <c r="H1704" t="n">
-        <v>115.1126</v>
+        <v>115.1127</v>
       </c>
     </row>
     <row r="1705">
@@ -65625,7 +65625,7 @@
         <v>64.95607</v>
       </c>
       <c r="H1716" t="n">
-        <v>118.0102</v>
+        <v>118.0103</v>
       </c>
     </row>
     <row r="1717">
@@ -65967,7 +65967,7 @@
         <v>65.015511</v>
       </c>
       <c r="H1725" t="n">
-        <v>118.1182</v>
+        <v>118.1183</v>
       </c>
     </row>
     <row r="1726">
@@ -66233,7 +66233,7 @@
         <v>65.015511</v>
       </c>
       <c r="H1732" t="n">
-        <v>118.1182</v>
+        <v>118.1183</v>
       </c>
     </row>
     <row r="1733">
@@ -66271,7 +66271,7 @@
         <v>64.599442</v>
       </c>
       <c r="H1733" t="n">
-        <v>117.3623</v>
+        <v>117.3624</v>
       </c>
     </row>
     <row r="1734">
@@ -66385,7 +66385,7 @@
         <v>64.17346999999999</v>
       </c>
       <c r="H1736" t="n">
-        <v>116.5884</v>
+        <v>116.5885</v>
       </c>
     </row>
     <row r="1737">
@@ -66727,7 +66727,7 @@
         <v>62.984707</v>
       </c>
       <c r="H1745" t="n">
-        <v>114.4287</v>
+        <v>114.4288</v>
       </c>
     </row>
     <row r="1746">
@@ -66879,7 +66879,7 @@
         <v>62.84</v>
       </c>
       <c r="H1749" t="n">
-        <v>114.1658</v>
+        <v>114.1659</v>
       </c>
     </row>
     <row r="1750">
@@ -66955,7 +66955,7 @@
         <v>63.580002</v>
       </c>
       <c r="H1751" t="n">
-        <v>115.5102</v>
+        <v>115.5103</v>
       </c>
     </row>
     <row r="1752">
@@ -67183,7 +67183,7 @@
         <v>62.869999</v>
       </c>
       <c r="H1757" t="n">
-        <v>114.2203</v>
+        <v>114.2204</v>
       </c>
     </row>
     <row r="1758">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H509" t="n">
         <v>98.79859999999999</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.111977</v>
+        <v>65.11198400000001</v>
       </c>
       <c r="H511" t="n">
         <v>99.1694</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.559952</v>
+        <v>65.559944</v>
       </c>
       <c r="H513" t="n">
         <v>99.85169999999999</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.84236900000001</v>
+        <v>65.842377</v>
       </c>
       <c r="H515" t="n">
         <v>100.2818</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368256</v>
       </c>
       <c r="H529" t="n">
         <v>101.0828</v>
@@ -20592,10 +20592,10 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H531" t="n">
-        <v>102.9072</v>
+        <v>102.9071</v>
       </c>
     </row>
     <row r="532">
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.77726699999999</v>
+        <v>66.77726</v>
       </c>
       <c r="H533" t="n">
         <v>101.7057</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>65.754723</v>
+        <v>65.754715</v>
       </c>
       <c r="H535" t="n">
         <v>100.1483</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027405</v>
       </c>
       <c r="H537" t="n">
         <v>100.5636</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>66.387733</v>
+        <v>66.387726</v>
       </c>
       <c r="H540" t="n">
         <v>101.1124</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.371323</v>
+        <v>67.371315</v>
       </c>
       <c r="H547" t="n">
         <v>102.6105</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H548" t="n">
         <v>102.833</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H555" t="n">
         <v>102.299</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>37.080002</v>
+        <v>36.73</v>
       </c>
       <c r="H253" t="n">
-        <v>124.7645</v>
+        <v>123.5868</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>49.889999</v>
+        <v>50.16</v>
       </c>
       <c r="H504" t="n">
-        <v>132.229</v>
+        <v>132.9446</v>
       </c>
     </row>
     <row r="505">
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.11198400000001</v>
+        <v>65.111969</v>
       </c>
       <c r="H511" t="n">
         <v>99.1694</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.559944</v>
+        <v>65.559952</v>
       </c>
       <c r="H513" t="n">
         <v>99.85169999999999</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H514" t="n">
         <v>99.1842</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.842377</v>
+        <v>65.842361</v>
       </c>
       <c r="H515" t="n">
         <v>100.2818</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H517" t="n">
         <v>100.4301</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>66.407211</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H519" t="n">
         <v>101.1421</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H521" t="n">
         <v>100.8454</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.407211</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H522" t="n">
         <v>101.1421</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H526" t="n">
         <v>100.9641</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H529" t="n">
         <v>101.0828</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H530" t="n">
         <v>101.9579</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H532" t="n">
         <v>102.1359</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.77726</v>
+        <v>66.777275</v>
       </c>
       <c r="H533" t="n">
         <v>101.7057</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.41693100000001</v>
+        <v>66.416939</v>
       </c>
       <c r="H534" t="n">
         <v>101.1569</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H537" t="n">
         <v>100.5636</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.12479399999999</v>
+        <v>66.124786</v>
       </c>
       <c r="H539" t="n">
         <v>100.712</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H541" t="n">
         <v>102.0469</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H544" t="n">
         <v>102.1359</v>
@@ -21124,10 +21124,10 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>66.874657</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H545" t="n">
-        <v>101.8541</v>
+        <v>101.854</v>
       </c>
     </row>
     <row r="546">
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H546" t="n">
         <v>101.9579</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H547" t="n">
         <v>102.6105</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.283661</v>
+        <v>67.283676</v>
       </c>
       <c r="H549" t="n">
         <v>102.477</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.22524300000001</v>
+        <v>67.22525</v>
       </c>
       <c r="H551" t="n">
         <v>102.388</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.478447</v>
+        <v>67.47843899999999</v>
       </c>
       <c r="H552" t="n">
         <v>102.7737</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H553" t="n">
         <v>102.6402</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H554" t="n">
         <v>103.2186</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.234978</v>
+        <v>67.23497</v>
       </c>
       <c r="H556" t="n">
         <v>102.4028</v>
@@ -29075,7 +29075,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>81</v>
+        <v>80.870003</v>
       </c>
       <c r="H755" t="n">
-        <v>123.3678</v>
+        <v>123.1698</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>131.850006</v>
+        <v>131.179993</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.6976</v>
+        <v>120.0842</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>131.850006</v>
+        <v>131.179993</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.6976</v>
+        <v>120.0842</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>131.850006</v>
+        <v>131.179993</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.6976</v>
+        <v>120.0842</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>55.042728</v>
+        <v>55.042732</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.974545</v>
+        <v>54.974548</v>
       </c>
       <c r="H1510" t="n">
         <v>99.87609999999999</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.74078</v>
+        <v>54.740784</v>
       </c>
       <c r="H1514" t="n">
         <v>99.45140000000001</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.536236</v>
+        <v>54.536232</v>
       </c>
       <c r="H1515" t="n">
         <v>99.07980000000001</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.818699</v>
+        <v>54.818703</v>
       </c>
       <c r="H1516" t="n">
         <v>99.593</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1517" t="n">
         <v>100.3893</v>
@@ -58101,7 +58101,7 @@
         <v>54.682339</v>
       </c>
       <c r="H1518" t="n">
-        <v>99.34529999999999</v>
+        <v>99.34520000000001</v>
       </c>
     </row>
     <row r="1519">
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1519" t="n">
         <v>100.3893</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1521" t="n">
         <v>100.4247</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1523" t="n">
         <v>101.2918</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1524" t="n">
         <v>101.0795</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.588196</v>
+        <v>55.588188</v>
       </c>
       <c r="H1525" t="n">
         <v>100.991</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.169357</v>
+        <v>55.169361</v>
       </c>
       <c r="H1529" t="n">
         <v>100.2301</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1530" t="n">
         <v>100.4247</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.867413</v>
+        <v>54.867405</v>
       </c>
       <c r="H1531" t="n">
         <v>99.6815</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>54.584934</v>
+        <v>54.584938</v>
       </c>
       <c r="H1532" t="n">
         <v>99.1683</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1533" t="n">
         <v>100.6194</v>
@@ -58706,10 +58706,10 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>56.104431</v>
+        <v>56.104424</v>
       </c>
       <c r="H1534" t="n">
-        <v>101.9289</v>
+        <v>101.9288</v>
       </c>
     </row>
     <row r="1535">
@@ -58785,7 +58785,7 @@
         <v>56.143391</v>
       </c>
       <c r="H1536" t="n">
-        <v>101.9997</v>
+        <v>101.9996</v>
       </c>
     </row>
     <row r="1537">
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.60767</v>
+        <v>55.607674</v>
       </c>
       <c r="H1537" t="n">
         <v>101.0264</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1540" t="n">
         <v>98.6374</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1541" t="n">
         <v>98.9913</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>54.35117</v>
+        <v>54.351166</v>
       </c>
       <c r="H1542" t="n">
         <v>98.7436</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>54.877144</v>
+        <v>54.877148</v>
       </c>
       <c r="H1544" t="n">
         <v>99.6992</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1546" t="n">
         <v>100.9556</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1547" t="n">
         <v>101.2918</v>
@@ -59238,7 +59238,7 @@
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1548" t="n">
         <v>100.9556</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1549" t="n">
         <v>101.0795</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.987545</v>
+        <v>55.987549</v>
       </c>
       <c r="H1552" t="n">
         <v>101.7165</v>
@@ -59428,10 +59428,10 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1553" t="n">
-        <v>101.5573</v>
+        <v>101.5572</v>
       </c>
     </row>
     <row r="1554">
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.870667</v>
+        <v>55.870663</v>
       </c>
       <c r="H1555" t="n">
         <v>101.5042</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>56.172615</v>
+        <v>56.172611</v>
       </c>
       <c r="H1556" t="n">
         <v>102.0527</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1557" t="n">
         <v>101.4688</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1559" t="n">
         <v>101.8487</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1562" t="n">
         <v>103.1627</v>
@@ -59811,7 +59811,7 @@
         <v>56.676041</v>
       </c>
       <c r="H1563" t="n">
-        <v>102.9674</v>
+        <v>102.9673</v>
       </c>
     </row>
     <row r="1564">
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1565" t="n">
         <v>103.5</v>
@@ -60001,7 +60001,7 @@
         <v>58.210468</v>
       </c>
       <c r="H1568" t="n">
-        <v>105.7551</v>
+        <v>105.755</v>
       </c>
     </row>
     <row r="1569">
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1569" t="n">
         <v>106.341</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1570" t="n">
         <v>106.3055</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>59.129162</v>
+        <v>59.129169</v>
       </c>
       <c r="H1573" t="n">
         <v>107.4241</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1575" t="n">
         <v>107.4596</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1576" t="n">
         <v>108.0811</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1577" t="n">
         <v>108.0988</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1579" t="n">
         <v>105.8793</v>
@@ -60454,7 +60454,7 @@
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.259335</v>
+        <v>58.259331</v>
       </c>
       <c r="H1580" t="n">
         <v>105.8438</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1582" t="n">
         <v>106.9447</v>
@@ -60606,7 +60606,7 @@
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1584" t="n">
         <v>107.7437</v>
@@ -60913,7 +60913,7 @@
         <v>59.744892</v>
       </c>
       <c r="H1592" t="n">
-        <v>108.5428</v>
+        <v>108.5427</v>
       </c>
     </row>
     <row r="1593">
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>60.116283</v>
+        <v>60.11628</v>
       </c>
       <c r="H1594" t="n">
         <v>109.2175</v>
@@ -61024,7 +61024,7 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1595" t="n">
         <v>109.3773</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1596" t="n">
         <v>108.8801</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1598" t="n">
         <v>108.8979</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1599" t="n">
         <v>109.4838</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>60.956791</v>
+        <v>60.956799</v>
       </c>
       <c r="H1600" t="n">
         <v>110.7445</v>
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1603" t="n">
         <v>110.5847</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>61.474789</v>
+        <v>61.474785</v>
       </c>
       <c r="H1605" t="n">
         <v>111.6856</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>61.445469</v>
+        <v>61.445465</v>
       </c>
       <c r="H1607" t="n">
         <v>111.6323</v>
@@ -61670,10 +61670,10 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1612" t="n">
-        <v>105.471</v>
+        <v>105.4709</v>
       </c>
     </row>
     <row r="1613">
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1613" t="n">
         <v>104.743</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1614" t="n">
         <v>106.8027</v>
@@ -61787,7 +61787,7 @@
         <v>58.4548</v>
       </c>
       <c r="H1615" t="n">
-        <v>106.199</v>
+        <v>106.1989</v>
       </c>
     </row>
     <row r="1616">
@@ -61936,7 +61936,7 @@
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1619" t="n">
         <v>106.154</v>
@@ -62053,7 +62053,7 @@
         <v>55.549702</v>
       </c>
       <c r="H1622" t="n">
-        <v>100.9211</v>
+        <v>100.921</v>
       </c>
     </row>
     <row r="1623">
@@ -62658,7 +62658,7 @@
         </is>
       </c>
       <c r="G1638" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1638" t="n">
         <v>109.2866</v>
@@ -62734,7 +62734,7 @@
         </is>
       </c>
       <c r="G1640" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1640" t="n">
         <v>110.9776</v>
@@ -62810,10 +62810,10 @@
         </is>
       </c>
       <c r="G1642" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1642" t="n">
-        <v>109.1443</v>
+        <v>109.1442</v>
       </c>
     </row>
     <row r="1643">
@@ -62886,7 +62886,7 @@
         </is>
       </c>
       <c r="G1644" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1644" t="n">
         <v>108.9129</v>
@@ -62924,7 +62924,7 @@
         </is>
       </c>
       <c r="G1645" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1645" t="n">
         <v>108.3255</v>
@@ -63038,7 +63038,7 @@
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1648" t="n">
         <v>107.0973</v>
@@ -63152,7 +63152,7 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1651" t="n">
         <v>108.5213</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1652" t="n">
         <v>110.9242</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1654" t="n">
         <v>109.1086</v>
@@ -63342,7 +63342,7 @@
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1656" t="n">
         <v>108.1119</v>
@@ -63383,7 +63383,7 @@
         <v>60.026989</v>
       </c>
       <c r="H1657" t="n">
-        <v>109.0553</v>
+        <v>109.0552</v>
       </c>
     </row>
     <row r="1658">
@@ -63497,7 +63497,7 @@
         <v>60.026989</v>
       </c>
       <c r="H1660" t="n">
-        <v>109.0553</v>
+        <v>109.0552</v>
       </c>
     </row>
     <row r="1661">
@@ -63535,7 +63535,7 @@
         <v>60.066177</v>
       </c>
       <c r="H1661" t="n">
-        <v>109.1265</v>
+        <v>109.1264</v>
       </c>
     </row>
     <row r="1662">
@@ -63722,7 +63722,7 @@
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1666" t="n">
         <v>112.4193</v>
@@ -63798,7 +63798,7 @@
         </is>
       </c>
       <c r="G1668" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1668" t="n">
         <v>111.9387</v>
@@ -63912,7 +63912,7 @@
         </is>
       </c>
       <c r="G1671" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1671" t="n">
         <v>112.0633</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1673" t="n">
         <v>111.9387</v>
@@ -64026,7 +64026,7 @@
         </is>
       </c>
       <c r="G1674" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1674" t="n">
         <v>111.4937</v>
@@ -64178,7 +64178,7 @@
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1678" t="n">
         <v>111.3513</v>
@@ -64675,7 +64675,7 @@
         <v>63.341331</v>
       </c>
       <c r="H1691" t="n">
-        <v>115.0767</v>
+        <v>115.0766</v>
       </c>
     </row>
     <row r="1692">
@@ -64979,7 +64979,7 @@
         <v>63.390869</v>
       </c>
       <c r="H1699" t="n">
-        <v>115.1667</v>
+        <v>115.1666</v>
       </c>
     </row>
     <row r="1700">
@@ -65017,7 +65017,7 @@
         <v>63.390869</v>
       </c>
       <c r="H1700" t="n">
-        <v>115.1667</v>
+        <v>115.1666</v>
       </c>
     </row>
     <row r="1701">
@@ -65169,7 +65169,7 @@
         <v>63.361145</v>
       </c>
       <c r="H1704" t="n">
-        <v>115.1127</v>
+        <v>115.1126</v>
       </c>
     </row>
     <row r="1705">
@@ -65967,7 +65967,7 @@
         <v>65.015511</v>
       </c>
       <c r="H1725" t="n">
-        <v>118.1183</v>
+        <v>118.1182</v>
       </c>
     </row>
     <row r="1726">
@@ -66233,7 +66233,7 @@
         <v>65.015511</v>
       </c>
       <c r="H1732" t="n">
-        <v>118.1183</v>
+        <v>118.1182</v>
       </c>
     </row>
     <row r="1733">
@@ -66271,7 +66271,7 @@
         <v>64.599442</v>
       </c>
       <c r="H1733" t="n">
-        <v>117.3624</v>
+        <v>117.3623</v>
       </c>
     </row>
     <row r="1734">
@@ -66727,7 +66727,7 @@
         <v>62.984707</v>
       </c>
       <c r="H1745" t="n">
-        <v>114.4288</v>
+        <v>114.4287</v>
       </c>
     </row>
     <row r="1746">
@@ -66879,7 +66879,7 @@
         <v>62.84</v>
       </c>
       <c r="H1749" t="n">
-        <v>114.1659</v>
+        <v>114.1658</v>
       </c>
     </row>
     <row r="1750">
@@ -67183,7 +67183,7 @@
         <v>62.869999</v>
       </c>
       <c r="H1757" t="n">
-        <v>114.2204</v>
+        <v>114.2203</v>
       </c>
     </row>
     <row r="1758">
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>63.029999</v>
+        <v>62.740002</v>
       </c>
       <c r="H1760" t="n">
-        <v>114.511</v>
+        <v>113.9842</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>36.724998</v>
+        <v>36.810001</v>
       </c>
       <c r="H253" t="n">
-        <v>126.5071</v>
+        <v>126.7999</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>49.255001</v>
+        <v>49.41</v>
       </c>
       <c r="H504" t="n">
-        <v>130.6325</v>
+        <v>131.0436</v>
       </c>
     </row>
     <row r="505">
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>65.19961499999999</v>
+        <v>65.199623</v>
       </c>
       <c r="H509" t="n">
         <v>99.30289999999999</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.559944</v>
+        <v>65.559952</v>
       </c>
       <c r="H512" t="n">
         <v>99.85169999999999</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H513" t="n">
         <v>99.1842</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H516" t="n">
         <v>100.4301</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H520" t="n">
         <v>100.8454</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H523" t="n">
         <v>100.6081</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H525" t="n">
         <v>100.9641</v>
@@ -20554,10 +20554,10 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H530" t="n">
-        <v>102.9071</v>
+        <v>102.9072</v>
       </c>
     </row>
     <row r="531">
@@ -20782,10 +20782,10 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.027412</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H536" t="n">
-        <v>100.5637</v>
+        <v>100.5636</v>
       </c>
     </row>
     <row r="537">
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H537" t="n">
         <v>100.356</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.38771800000001</v>
+        <v>66.387726</v>
       </c>
       <c r="H539" t="n">
         <v>101.1124</v>
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H540" t="n">
         <v>102.0469</v>
@@ -21086,10 +21086,10 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.874657</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H544" t="n">
-        <v>101.8541</v>
+        <v>101.854</v>
       </c>
     </row>
     <row r="545">
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.371315</v>
+        <v>67.371323</v>
       </c>
       <c r="H546" t="n">
         <v>102.6105</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.51739499999999</v>
+        <v>67.517403</v>
       </c>
       <c r="H547" t="n">
         <v>102.833</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.283661</v>
+        <v>67.283676</v>
       </c>
       <c r="H548" t="n">
         <v>102.477</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.29341100000001</v>
+        <v>67.293404</v>
       </c>
       <c r="H549" t="n">
         <v>102.4918</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.22524300000001</v>
+        <v>67.225235</v>
       </c>
       <c r="H550" t="n">
         <v>102.388</v>
@@ -21504,10 +21504,10 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.234978</v>
+        <v>67.23498499999999</v>
       </c>
       <c r="H555" t="n">
-        <v>102.4028</v>
+        <v>102.4029</v>
       </c>
     </row>
     <row r="556">
@@ -21542,10 +21542,10 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.619141</v>
+        <v>67.619148</v>
       </c>
       <c r="H556" t="n">
-        <v>102.9879</v>
+        <v>102.988</v>
       </c>
     </row>
     <row r="557">
@@ -21580,7 +21580,7 @@
         </is>
       </c>
       <c r="G557" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H557" t="n">
         <v>103.4056</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H560" t="n">
         <v>103.9874</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H562" t="n">
         <v>104.3603</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H564" t="n">
         <v>106.2697</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H566" t="n">
         <v>106.1504</v>
@@ -21998,10 +21998,10 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H568" t="n">
-        <v>106.8962</v>
+        <v>106.8963</v>
       </c>
     </row>
     <row r="569">
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>70.273376</v>
+        <v>70.273369</v>
       </c>
       <c r="H569" t="n">
         <v>107.0305</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H572" t="n">
         <v>108.5819</v>
@@ -22226,10 +22226,10 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H574" t="n">
-        <v>106.7172</v>
+        <v>106.7173</v>
       </c>
     </row>
     <row r="575">
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H575" t="n">
         <v>107.1797</v>
@@ -22682,10 +22682,10 @@
         </is>
       </c>
       <c r="G586" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H586" t="n">
-        <v>110.1929</v>
+        <v>110.193</v>
       </c>
     </row>
     <row r="587">
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H588" t="n">
         <v>111.6548</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H589" t="n">
         <v>112.0427</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H590" t="n">
         <v>112.8929</v>
@@ -22872,10 +22872,10 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H591" t="n">
-        <v>112.4603</v>
+        <v>112.4604</v>
       </c>
     </row>
     <row r="592">
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>73.828667</v>
+        <v>73.82867400000001</v>
       </c>
       <c r="H592" t="n">
         <v>112.4454</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.88743599999999</v>
+        <v>73.887444</v>
       </c>
       <c r="H593" t="n">
         <v>112.5349</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H594" t="n">
         <v>112.5051</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H598" t="n">
         <v>113.5045</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H603" t="n">
         <v>114.2355</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>72.721931</v>
+        <v>72.721924</v>
       </c>
       <c r="H609" t="n">
         <v>110.7598</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H610" t="n">
         <v>110.3272</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H611" t="n">
         <v>110.5062</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>72.64357800000001</v>
+        <v>72.64357</v>
       </c>
       <c r="H614" t="n">
         <v>110.6405</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.629997</v>
+        <v>80.650002</v>
       </c>
       <c r="H755" t="n">
-        <v>122.8043</v>
+        <v>122.8347</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>131.380005</v>
+        <v>131.470001</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.4548</v>
+        <v>120.5373</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>131.380005</v>
+        <v>131.470001</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.4548</v>
+        <v>120.5373</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>131.380005</v>
+        <v>131.470001</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.4548</v>
+        <v>120.5373</v>
       </c>
     </row>
     <row r="1509">
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>54.974548</v>
+        <v>54.974552</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>55.403122</v>
+        <v>55.403126</v>
       </c>
       <c r="H1510" t="n">
         <v>100.7796</v>
@@ -57835,7 +57835,7 @@
         <v>55.159622</v>
       </c>
       <c r="H1511" t="n">
-        <v>100.3367</v>
+        <v>100.3366</v>
       </c>
     </row>
     <row r="1512">
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.536236</v>
+        <v>54.53624</v>
       </c>
       <c r="H1514" t="n">
         <v>99.20269999999999</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1516" t="n">
         <v>100.5138</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1517" t="n">
         <v>99.46850000000001</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1518" t="n">
         <v>100.5138</v>
@@ -58136,7 +58136,7 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>55.403122</v>
+        <v>55.403126</v>
       </c>
       <c r="H1519" t="n">
         <v>100.7796</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1525" t="n">
         <v>101.0099</v>
@@ -58478,10 +58478,10 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.169357</v>
+        <v>55.169353</v>
       </c>
       <c r="H1528" t="n">
-        <v>100.3544</v>
+        <v>100.3543</v>
       </c>
     </row>
     <row r="1529">
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>54.867405</v>
+        <v>54.867409</v>
       </c>
       <c r="H1530" t="n">
         <v>99.8051</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.584938</v>
+        <v>54.584934</v>
       </c>
       <c r="H1531" t="n">
         <v>99.29130000000001</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1532" t="n">
         <v>100.7442</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1533" t="n">
         <v>102.0553</v>
@@ -58706,10 +58706,10 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>56.523266</v>
+        <v>56.523262</v>
       </c>
       <c r="H1534" t="n">
-        <v>102.8172</v>
+        <v>102.8171</v>
       </c>
     </row>
     <row r="1535">
@@ -58744,10 +58744,10 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1535" t="n">
-        <v>102.1262</v>
+        <v>102.1261</v>
       </c>
     </row>
     <row r="1536">
@@ -58899,7 +58899,7 @@
         <v>54.292728</v>
       </c>
       <c r="H1539" t="n">
-        <v>98.7598</v>
+        <v>98.7597</v>
       </c>
     </row>
     <row r="1540">
@@ -58975,7 +58975,7 @@
         <v>54.351166</v>
       </c>
       <c r="H1541" t="n">
-        <v>98.8661</v>
+        <v>98.866</v>
       </c>
     </row>
     <row r="1542">
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>54.877151</v>
+        <v>54.877148</v>
       </c>
       <c r="H1543" t="n">
         <v>99.8228</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1544" t="n">
         <v>101.0099</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1545" t="n">
         <v>101.0808</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1547" t="n">
         <v>101.0808</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.958328</v>
+        <v>55.958324</v>
       </c>
       <c r="H1550" t="n">
         <v>101.7895</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1552" t="n">
         <v>101.6832</v>
@@ -59466,10 +59466,10 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.870663</v>
+        <v>55.870659</v>
       </c>
       <c r="H1554" t="n">
-        <v>101.6301</v>
+        <v>101.63</v>
       </c>
     </row>
     <row r="1555">
@@ -60381,7 +60381,7 @@
         <v>58.278877</v>
       </c>
       <c r="H1578" t="n">
-        <v>106.0107</v>
+        <v>106.0106</v>
       </c>
     </row>
     <row r="1579">
@@ -60571,7 +60571,7 @@
         <v>59.305088</v>
       </c>
       <c r="H1583" t="n">
-        <v>107.8774</v>
+        <v>107.8773</v>
       </c>
     </row>
     <row r="1584">
@@ -60723,7 +60723,7 @@
         <v>59.793758</v>
       </c>
       <c r="H1587" t="n">
-        <v>108.7663</v>
+        <v>108.7662</v>
       </c>
     </row>
     <row r="1588">
@@ -61445,7 +61445,7 @@
         <v>61.445465</v>
       </c>
       <c r="H1606" t="n">
-        <v>111.7708</v>
+        <v>111.7707</v>
       </c>
     </row>
     <row r="1607">
@@ -61635,7 +61635,7 @@
         <v>58.054089</v>
       </c>
       <c r="H1611" t="n">
-        <v>105.6018</v>
+        <v>105.6017</v>
       </c>
     </row>
     <row r="1612">
@@ -61825,7 +61825,7 @@
         <v>57.790211</v>
       </c>
       <c r="H1616" t="n">
-        <v>105.1218</v>
+        <v>105.1217</v>
       </c>
     </row>
     <row r="1617">
@@ -62433,7 +62433,7 @@
         <v>59.772263</v>
       </c>
       <c r="H1632" t="n">
-        <v>108.7272</v>
+        <v>108.7271</v>
       </c>
     </row>
     <row r="1633">
@@ -63079,7 +63079,7 @@
         <v>59.125652</v>
       </c>
       <c r="H1649" t="n">
-        <v>107.551</v>
+        <v>107.5509</v>
       </c>
     </row>
     <row r="1650">
@@ -63725,7 +63725,7 @@
         <v>61.849255</v>
       </c>
       <c r="H1666" t="n">
-        <v>112.5053</v>
+        <v>112.5052</v>
       </c>
     </row>
     <row r="1667">
@@ -66347,7 +66347,7 @@
         <v>64.17346999999999</v>
       </c>
       <c r="H1735" t="n">
-        <v>116.7331</v>
+        <v>116.733</v>
       </c>
     </row>
     <row r="1736">
@@ -66385,7 +66385,7 @@
         <v>63.925808</v>
       </c>
       <c r="H1736" t="n">
-        <v>116.2826</v>
+        <v>116.2825</v>
       </c>
     </row>
     <row r="1737">
@@ -66423,7 +66423,7 @@
         <v>64.37159699999999</v>
       </c>
       <c r="H1737" t="n">
-        <v>117.0935</v>
+        <v>117.0934</v>
       </c>
     </row>
     <row r="1738">
@@ -66537,7 +66537,7 @@
         <v>64.322067</v>
       </c>
       <c r="H1740" t="n">
-        <v>117.0034</v>
+        <v>117.0033</v>
       </c>
     </row>
     <row r="1741">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.389999</v>
+        <v>62.439999</v>
       </c>
       <c r="H1760" t="n">
-        <v>113.4889</v>
+        <v>113.5798</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>65.910538</v>
+        <v>65.91052999999999</v>
       </c>
       <c r="H507" t="n">
         <v>100.3856</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.121712</v>
+        <v>65.121719</v>
       </c>
       <c r="H513" t="n">
         <v>99.1842</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.939751</v>
+        <v>65.939758</v>
       </c>
       <c r="H516" t="n">
         <v>100.4301</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H518" t="n">
         <v>101.1421</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.212433</v>
+        <v>66.212425</v>
       </c>
       <c r="H520" t="n">
         <v>100.8454</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407196</v>
       </c>
       <c r="H521" t="n">
         <v>101.1421</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H523" t="n">
         <v>100.6081</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H525" t="n">
         <v>100.9641</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.98844099999999</v>
+        <v>65.988457</v>
       </c>
       <c r="H526" t="n">
         <v>100.5043</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H528" t="n">
         <v>101.0828</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H529" t="n">
         <v>101.9579</v>
@@ -20554,10 +20554,10 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H530" t="n">
-        <v>102.9072</v>
+        <v>102.9071</v>
       </c>
     </row>
     <row r="531">
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H532" t="n">
         <v>101.7057</v>
@@ -20782,10 +20782,10 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027412</v>
       </c>
       <c r="H536" t="n">
-        <v>100.5636</v>
+        <v>100.5637</v>
       </c>
     </row>
     <row r="537">
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.89106</v>
+        <v>65.891068</v>
       </c>
       <c r="H537" t="n">
         <v>100.356</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>66.942818</v>
+        <v>66.942825</v>
       </c>
       <c r="H545" t="n">
         <v>101.9579</v>
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.283676</v>
+        <v>67.283669</v>
       </c>
       <c r="H548" t="n">
         <v>102.477</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.293404</v>
+        <v>67.29341100000001</v>
       </c>
       <c r="H549" t="n">
         <v>102.4918</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.225235</v>
+        <v>67.22525</v>
       </c>
       <c r="H550" t="n">
         <v>102.388</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.478447</v>
+        <v>67.47843899999999</v>
       </c>
       <c r="H551" t="n">
         <v>102.7737</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.815033</v>
+        <v>67.81502500000001</v>
       </c>
       <c r="H558" t="n">
         <v>103.2863</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H560" t="n">
         <v>103.9874</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>69.48004899999999</v>
+        <v>69.480057</v>
       </c>
       <c r="H565" t="n">
         <v>105.8222</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>70.723907</v>
+        <v>70.72391500000001</v>
       </c>
       <c r="H573" t="n">
         <v>107.7167</v>
@@ -22226,10 +22226,10 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H574" t="n">
-        <v>106.7173</v>
+        <v>106.7172</v>
       </c>
     </row>
     <row r="575">
@@ -22302,10 +22302,10 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H576" t="n">
-        <v>107.9404</v>
+        <v>107.9405</v>
       </c>
     </row>
     <row r="577">
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>73.201836</v>
+        <v>73.201843</v>
       </c>
       <c r="H587" t="n">
         <v>111.4907</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H589" t="n">
         <v>112.0427</v>
@@ -22872,10 +22872,10 @@
         </is>
       </c>
       <c r="G591" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H591" t="n">
-        <v>112.4604</v>
+        <v>112.4603</v>
       </c>
     </row>
     <row r="592">
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.887444</v>
+        <v>73.88743599999999</v>
       </c>
       <c r="H593" t="n">
         <v>112.5349</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H599" t="n">
         <v>113.8178</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>75.003967</v>
+        <v>75.003975</v>
       </c>
       <c r="H603" t="n">
         <v>114.2355</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>72.721924</v>
+        <v>72.72191599999999</v>
       </c>
       <c r="H609" t="n">
         <v>110.7598</v>
@@ -23746,10 +23746,10 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>72.64357</v>
+        <v>72.643562</v>
       </c>
       <c r="H614" t="n">
-        <v>110.6405</v>
+        <v>110.6404</v>
       </c>
     </row>
     <row r="615">
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H615" t="n">
         <v>108.9202</v>
@@ -23822,7 +23822,7 @@
         </is>
       </c>
       <c r="G616" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H616" t="n">
         <v>107.9157</v>
@@ -23898,10 +23898,10 @@
         </is>
       </c>
       <c r="G618" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H618" t="n">
-        <v>108.7552</v>
+        <v>108.7553</v>
       </c>
     </row>
     <row r="619">
@@ -24012,10 +24012,10 @@
         </is>
       </c>
       <c r="G621" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H621" t="n">
-        <v>108.7552</v>
+        <v>108.7553</v>
       </c>
     </row>
     <row r="622">
@@ -24126,7 +24126,7 @@
         </is>
       </c>
       <c r="G624" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H624" t="n">
         <v>110.7043</v>
@@ -24202,10 +24202,10 @@
         </is>
       </c>
       <c r="G626" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H626" t="n">
-        <v>110.3445</v>
+        <v>110.3444</v>
       </c>
     </row>
     <row r="627">
@@ -24278,7 +24278,7 @@
         </is>
       </c>
       <c r="G628" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H628" t="n">
         <v>112.6233</v>
@@ -24316,7 +24316,7 @@
         </is>
       </c>
       <c r="G629" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H629" t="n">
         <v>112.3684</v>
@@ -24392,7 +24392,7 @@
         </is>
       </c>
       <c r="G631" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H631" t="n">
         <v>112.4434</v>
@@ -24468,7 +24468,7 @@
         </is>
       </c>
       <c r="G633" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H633" t="n">
         <v>112.4134</v>
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="G637" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H637" t="n">
         <v>112.4434</v>
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H640" t="n">
         <v>111.9936</v>
@@ -24772,7 +24772,7 @@
         </is>
       </c>
       <c r="G641" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H641" t="n">
         <v>112.3834</v>
@@ -24848,7 +24848,7 @@
         </is>
       </c>
       <c r="G643" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H643" t="n">
         <v>113.3579</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H646" t="n">
         <v>114.4374</v>
@@ -25000,7 +25000,7 @@
         </is>
       </c>
       <c r="G647" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H647" t="n">
         <v>113.6728</v>
@@ -25076,7 +25076,7 @@
         </is>
       </c>
       <c r="G649" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H649" t="n">
         <v>113.6728</v>
@@ -25266,7 +25266,7 @@
         </is>
       </c>
       <c r="G654" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H654" t="n">
         <v>114.3774</v>
@@ -25456,7 +25456,7 @@
         </is>
       </c>
       <c r="G659" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H659" t="n">
         <v>117.4209</v>
@@ -25532,7 +25532,7 @@
         </is>
       </c>
       <c r="G661" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H661" t="n">
         <v>116.6263</v>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="G663" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H663" t="n">
         <v>116.1765</v>
@@ -25646,7 +25646,7 @@
         </is>
       </c>
       <c r="G664" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H664" t="n">
         <v>116.0266</v>
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H669" t="n">
         <v>116.6563</v>
@@ -25874,7 +25874,7 @@
         </is>
       </c>
       <c r="G670" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H670" t="n">
         <v>115.9666</v>
@@ -26102,7 +26102,7 @@
         </is>
       </c>
       <c r="G676" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H676" t="n">
         <v>119.3399</v>
@@ -57756,7 +57756,7 @@
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>54.974552</v>
+        <v>54.974548</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57835,7 +57835,7 @@
         <v>55.159622</v>
       </c>
       <c r="H1511" t="n">
-        <v>100.3366</v>
+        <v>100.3367</v>
       </c>
     </row>
     <row r="1512">
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.53624</v>
+        <v>54.536236</v>
       </c>
       <c r="H1514" t="n">
         <v>99.20269999999999</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.818707</v>
+        <v>54.818703</v>
       </c>
       <c r="H1515" t="n">
         <v>99.7165</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.257019</v>
+        <v>55.257015</v>
       </c>
       <c r="H1516" t="n">
         <v>100.5138</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.257019</v>
+        <v>55.257015</v>
       </c>
       <c r="H1518" t="n">
         <v>100.5138</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.588188</v>
+        <v>55.588192</v>
       </c>
       <c r="H1524" t="n">
         <v>101.1162</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1525" t="n">
         <v>101.0099</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.295986</v>
+        <v>55.295982</v>
       </c>
       <c r="H1526" t="n">
         <v>100.5847</v>
@@ -58481,7 +58481,7 @@
         <v>55.169353</v>
       </c>
       <c r="H1528" t="n">
-        <v>100.3543</v>
+        <v>100.3544</v>
       </c>
     </row>
     <row r="1529">
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.383648</v>
+        <v>55.383652</v>
       </c>
       <c r="H1532" t="n">
         <v>100.7442</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>56.104431</v>
+        <v>56.104427</v>
       </c>
       <c r="H1533" t="n">
         <v>102.0553</v>
@@ -58747,7 +58747,7 @@
         <v>56.143391</v>
       </c>
       <c r="H1535" t="n">
-        <v>102.1261</v>
+        <v>102.1262</v>
       </c>
     </row>
     <row r="1536">
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.607674</v>
+        <v>55.60767</v>
       </c>
       <c r="H1536" t="n">
         <v>101.1517</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.305717</v>
+        <v>55.305721</v>
       </c>
       <c r="H1537" t="n">
         <v>100.6024</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1539" t="n">
         <v>98.7597</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1540" t="n">
         <v>99.11409999999999</v>
@@ -58975,7 +58975,7 @@
         <v>54.351166</v>
       </c>
       <c r="H1541" t="n">
-        <v>98.866</v>
+        <v>98.8661</v>
       </c>
     </row>
     <row r="1542">
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1542" t="n">
         <v>98.9901</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.529747</v>
+        <v>55.529751</v>
       </c>
       <c r="H1544" t="n">
         <v>101.0099</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.958324</v>
+        <v>55.958328</v>
       </c>
       <c r="H1550" t="n">
         <v>101.7895</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1552" t="n">
         <v>101.6832</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.841442</v>
+        <v>55.841438</v>
       </c>
       <c r="H1553" t="n">
         <v>101.5769</v>
@@ -59466,10 +59466,10 @@
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.870659</v>
+        <v>55.870663</v>
       </c>
       <c r="H1554" t="n">
-        <v>101.63</v>
+        <v>101.6301</v>
       </c>
     </row>
     <row r="1555">
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>56.172611</v>
+        <v>56.172615</v>
       </c>
       <c r="H1555" t="n">
         <v>102.1793</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1557" t="n">
         <v>102.4017</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>56.06031</v>
+        <v>56.060314</v>
       </c>
       <c r="H1558" t="n">
         <v>101.975</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1559" t="n">
         <v>101.8506</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>56.558754</v>
+        <v>56.558758</v>
       </c>
       <c r="H1560" t="n">
         <v>102.8817</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.783543</v>
+        <v>56.783546</v>
       </c>
       <c r="H1561" t="n">
         <v>103.2906</v>
@@ -59770,7 +59770,7 @@
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.676044</v>
+        <v>56.676041</v>
       </c>
       <c r="H1562" t="n">
         <v>103.0951</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>57.692471</v>
+        <v>57.692474</v>
       </c>
       <c r="H1566" t="n">
         <v>104.944</v>
@@ -59960,7 +59960,7 @@
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1567" t="n">
         <v>105.8862</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>59.129166</v>
+        <v>59.129162</v>
       </c>
       <c r="H1572" t="n">
         <v>107.5573</v>
@@ -60381,7 +60381,7 @@
         <v>58.278877</v>
       </c>
       <c r="H1578" t="n">
-        <v>106.0106</v>
+        <v>106.0107</v>
       </c>
     </row>
     <row r="1579">
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.259331</v>
+        <v>58.259335</v>
       </c>
       <c r="H1579" t="n">
         <v>105.9751</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.953247</v>
+        <v>58.953243</v>
       </c>
       <c r="H1582" t="n">
         <v>107.2373</v>
@@ -60571,7 +60571,7 @@
         <v>59.305088</v>
       </c>
       <c r="H1583" t="n">
-        <v>107.8773</v>
+        <v>107.8774</v>
       </c>
     </row>
     <row r="1584">
@@ -60723,7 +60723,7 @@
         <v>59.793758</v>
       </c>
       <c r="H1587" t="n">
-        <v>108.7662</v>
+        <v>108.7663</v>
       </c>
     </row>
     <row r="1588">
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>60.11628</v>
+        <v>60.116283</v>
       </c>
       <c r="H1593" t="n">
         <v>109.3529</v>
@@ -61024,10 +61024,10 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.930584</v>
+        <v>59.930588</v>
       </c>
       <c r="H1595" t="n">
-        <v>109.0151</v>
+        <v>109.0152</v>
       </c>
     </row>
     <row r="1596">
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.956795</v>
+        <v>60.956791</v>
       </c>
       <c r="H1599" t="n">
         <v>110.8818</v>
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>60.868835</v>
+        <v>60.868832</v>
       </c>
       <c r="H1602" t="n">
         <v>110.7218</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>61.474785</v>
+        <v>61.474789</v>
       </c>
       <c r="H1604" t="n">
         <v>111.8241</v>
@@ -61442,10 +61442,10 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>61.445465</v>
+        <v>61.445469</v>
       </c>
       <c r="H1606" t="n">
-        <v>111.7707</v>
+        <v>111.7708</v>
       </c>
     </row>
     <row r="1607">
@@ -61632,10 +61632,10 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>58.054089</v>
+        <v>58.054092</v>
       </c>
       <c r="H1611" t="n">
-        <v>105.6017</v>
+        <v>105.6018</v>
       </c>
     </row>
     <row r="1612">
@@ -61825,7 +61825,7 @@
         <v>57.790211</v>
       </c>
       <c r="H1616" t="n">
-        <v>105.1217</v>
+        <v>105.1218</v>
       </c>
     </row>
     <row r="1617">
@@ -61898,10 +61898,10 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.430054</v>
+        <v>58.430058</v>
       </c>
       <c r="H1618" t="n">
-        <v>106.2856</v>
+        <v>106.2857</v>
       </c>
     </row>
     <row r="1619">
@@ -62433,7 +62433,7 @@
         <v>59.772263</v>
       </c>
       <c r="H1632" t="n">
-        <v>108.7271</v>
+        <v>108.7272</v>
       </c>
     </row>
     <row r="1633">
@@ -62620,7 +62620,7 @@
         </is>
       </c>
       <c r="G1637" t="n">
-        <v>60.154354</v>
+        <v>60.15435</v>
       </c>
       <c r="H1637" t="n">
         <v>109.4222</v>
@@ -62696,7 +62696,7 @@
         </is>
       </c>
       <c r="G1639" t="n">
-        <v>61.085079</v>
+        <v>61.085075</v>
       </c>
       <c r="H1639" t="n">
         <v>111.1152</v>
@@ -62772,7 +62772,7 @@
         </is>
       </c>
       <c r="G1641" t="n">
-        <v>60.075974</v>
+        <v>60.075977</v>
       </c>
       <c r="H1641" t="n">
         <v>109.2796</v>
@@ -62848,7 +62848,7 @@
         </is>
       </c>
       <c r="G1643" t="n">
-        <v>59.948612</v>
+        <v>59.948608</v>
       </c>
       <c r="H1643" t="n">
         <v>109.0479</v>
@@ -62886,7 +62886,7 @@
         </is>
       </c>
       <c r="G1644" t="n">
-        <v>59.625309</v>
+        <v>59.625305</v>
       </c>
       <c r="H1644" t="n">
         <v>108.4598</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>58.949306</v>
+        <v>58.949303</v>
       </c>
       <c r="H1647" t="n">
         <v>107.2302</v>
@@ -63079,7 +63079,7 @@
         <v>59.125652</v>
       </c>
       <c r="H1649" t="n">
-        <v>107.5509</v>
+        <v>107.551</v>
       </c>
     </row>
     <row r="1650">
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>59.733078</v>
+        <v>59.733074</v>
       </c>
       <c r="H1650" t="n">
         <v>108.6559</v>
@@ -63152,7 +63152,7 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>61.055683</v>
+        <v>61.055687</v>
       </c>
       <c r="H1651" t="n">
         <v>111.0617</v>
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>60.056381</v>
+        <v>60.056377</v>
       </c>
       <c r="H1653" t="n">
         <v>109.244</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>59.50774</v>
+        <v>59.507744</v>
       </c>
       <c r="H1655" t="n">
         <v>108.246</v>
@@ -63684,7 +63684,7 @@
         </is>
       </c>
       <c r="G1665" t="n">
-        <v>61.878647</v>
+        <v>61.878643</v>
       </c>
       <c r="H1665" t="n">
         <v>112.5587</v>
@@ -63725,7 +63725,7 @@
         <v>61.849255</v>
       </c>
       <c r="H1666" t="n">
-        <v>112.5052</v>
+        <v>112.5053</v>
       </c>
     </row>
     <row r="1667">
@@ -63760,7 +63760,7 @@
         </is>
       </c>
       <c r="G1667" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1667" t="n">
         <v>112.0775</v>
@@ -63874,7 +63874,7 @@
         </is>
       </c>
       <c r="G1670" t="n">
-        <v>61.682705</v>
+        <v>61.682701</v>
       </c>
       <c r="H1670" t="n">
         <v>112.2023</v>
@@ -63950,7 +63950,7 @@
         </is>
       </c>
       <c r="G1672" t="n">
-        <v>61.61412</v>
+        <v>61.614124</v>
       </c>
       <c r="H1672" t="n">
         <v>112.0775</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.369194</v>
+        <v>61.369198</v>
       </c>
       <c r="H1673" t="n">
         <v>111.632</v>
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.290817</v>
+        <v>61.290821</v>
       </c>
       <c r="H1677" t="n">
         <v>111.4894</v>
@@ -66347,7 +66347,7 @@
         <v>64.17346999999999</v>
       </c>
       <c r="H1735" t="n">
-        <v>116.733</v>
+        <v>116.7331</v>
       </c>
     </row>
     <row r="1736">
@@ -66385,7 +66385,7 @@
         <v>63.925808</v>
       </c>
       <c r="H1736" t="n">
-        <v>116.2825</v>
+        <v>116.2826</v>
       </c>
     </row>
     <row r="1737">
@@ -66423,7 +66423,7 @@
         <v>64.37159699999999</v>
       </c>
       <c r="H1737" t="n">
-        <v>117.0934</v>
+        <v>117.0935</v>
       </c>
     </row>
     <row r="1738">
@@ -66537,7 +66537,7 @@
         <v>64.322067</v>
       </c>
       <c r="H1740" t="n">
-        <v>117.0033</v>
+        <v>117.0034</v>
       </c>
     </row>
     <row r="1741">

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H507" t="n">
         <v>100.3856</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H508" t="n">
         <v>98.79859999999999</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>65.111977</v>
+        <v>65.111969</v>
       </c>
       <c r="H510" t="n">
         <v>99.1694</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H516" t="n">
         <v>100.4301</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H518" t="n">
         <v>101.1421</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H520" t="n">
         <v>100.8454</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H521" t="n">
         <v>101.1421</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H523" t="n">
         <v>100.6081</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H525" t="n">
         <v>100.9641</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.988457</v>
+        <v>65.988449</v>
       </c>
       <c r="H526" t="n">
         <v>100.5043</v>
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>65.57942199999999</v>
+        <v>65.579414</v>
       </c>
       <c r="H527" t="n">
         <v>99.8813</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368256</v>
       </c>
       <c r="H528" t="n">
         <v>101.0828</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H529" t="n">
         <v>101.9579</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H531" t="n">
         <v>102.1359</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H532" t="n">
         <v>101.7057</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.416939</v>
+        <v>66.416946</v>
       </c>
       <c r="H533" t="n">
         <v>101.1569</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>65.754715</v>
+        <v>65.754723</v>
       </c>
       <c r="H534" t="n">
         <v>100.1483</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>65.715767</v>
+        <v>65.71575900000001</v>
       </c>
       <c r="H535" t="n">
         <v>100.089</v>
@@ -20782,10 +20782,10 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.027412</v>
+        <v>66.027405</v>
       </c>
       <c r="H536" t="n">
-        <v>100.5637</v>
+        <v>100.5636</v>
       </c>
     </row>
     <row r="537">
@@ -20934,7 +20934,7 @@
         </is>
       </c>
       <c r="G540" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H540" t="n">
         <v>102.0469</v>
@@ -20972,10 +20972,10 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>66.96230300000001</v>
+        <v>66.962311</v>
       </c>
       <c r="H541" t="n">
-        <v>101.9875</v>
+        <v>101.9876</v>
       </c>
     </row>
     <row r="542">
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H543" t="n">
         <v>102.1359</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H545" t="n">
         <v>101.9579</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.371323</v>
+        <v>67.371315</v>
       </c>
       <c r="H546" t="n">
         <v>102.6105</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H547" t="n">
         <v>102.833</v>
@@ -21276,10 +21276,10 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.29341100000001</v>
+        <v>67.293419</v>
       </c>
       <c r="H549" t="n">
-        <v>102.4918</v>
+        <v>102.4919</v>
       </c>
     </row>
     <row r="550">
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.22525</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H550" t="n">
         <v>102.388</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H552" t="n">
         <v>102.6402</v>
@@ -21504,10 +21504,10 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.23498499999999</v>
+        <v>67.23497</v>
       </c>
       <c r="H555" t="n">
-        <v>102.4029</v>
+        <v>102.4028</v>
       </c>
     </row>
     <row r="556">
@@ -21542,10 +21542,10 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.619148</v>
+        <v>67.619141</v>
       </c>
       <c r="H556" t="n">
-        <v>102.988</v>
+        <v>102.9879</v>
       </c>
     </row>
     <row r="557">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>67.81502500000001</v>
+        <v>67.815033</v>
       </c>
       <c r="H558" t="n">
         <v>103.2863</v>
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275352</v>
       </c>
       <c r="H560" t="n">
         <v>103.9874</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>69.773865</v>
+        <v>69.773872</v>
       </c>
       <c r="H564" t="n">
         <v>106.2697</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>69.480057</v>
+        <v>69.48004899999999</v>
       </c>
       <c r="H565" t="n">
         <v>105.8222</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H566" t="n">
         <v>106.1504</v>
@@ -21998,10 +21998,10 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>70.18523399999999</v>
+        <v>70.185226</v>
       </c>
       <c r="H568" t="n">
-        <v>106.8963</v>
+        <v>106.8962</v>
       </c>
     </row>
     <row r="569">
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G569" t="n">
-        <v>70.273369</v>
+        <v>70.273376</v>
       </c>
       <c r="H569" t="n">
         <v>107.0305</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>70.645554</v>
+        <v>70.645561</v>
       </c>
       <c r="H570" t="n">
         <v>107.5974</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>70.72391500000001</v>
+        <v>70.723907</v>
       </c>
       <c r="H573" t="n">
         <v>107.7167</v>
@@ -22226,10 +22226,10 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H574" t="n">
-        <v>106.7172</v>
+        <v>106.7173</v>
       </c>
     </row>
     <row r="575">
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>70.371323</v>
+        <v>70.371315</v>
       </c>
       <c r="H575" t="n">
         <v>107.1797</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>70.51823400000001</v>
+        <v>70.518227</v>
       </c>
       <c r="H577" t="n">
         <v>107.4034</v>
@@ -22416,7 +22416,7 @@
         </is>
       </c>
       <c r="G579" t="n">
-        <v>70.410492</v>
+        <v>70.410484</v>
       </c>
       <c r="H579" t="n">
         <v>107.2393</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>70.890411</v>
+        <v>70.890404</v>
       </c>
       <c r="H582" t="n">
         <v>107.9703</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H583" t="n">
         <v>109.1786</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>72.37912799999999</v>
+        <v>72.37913500000001</v>
       </c>
       <c r="H584" t="n">
         <v>110.2377</v>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H585" t="n">
         <v>110.9985</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>73.201843</v>
+        <v>73.201836</v>
       </c>
       <c r="H587" t="n">
         <v>111.4907</v>
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>73.82867400000001</v>
+        <v>73.828667</v>
       </c>
       <c r="H592" t="n">
         <v>112.4454</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>73.86784400000001</v>
+        <v>73.867851</v>
       </c>
       <c r="H594" t="n">
         <v>112.5051</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>75.14109000000001</v>
+        <v>75.141098</v>
       </c>
       <c r="H600" t="n">
         <v>114.4443</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>75.27821400000001</v>
+        <v>75.278206</v>
       </c>
       <c r="H601" t="n">
         <v>114.6532</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>75.003975</v>
+        <v>75.00398300000001</v>
       </c>
       <c r="H603" t="n">
         <v>114.2355</v>
@@ -23442,7 +23442,7 @@
         </is>
       </c>
       <c r="G606" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H606" t="n">
         <v>111.3565</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>72.72191599999999</v>
+        <v>72.721931</v>
       </c>
       <c r="H609" t="n">
         <v>110.7598</v>
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H610" t="n">
         <v>110.3272</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>72.55542800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H611" t="n">
         <v>110.5062</v>
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H613" t="n">
         <v>111.3565</v>
@@ -23746,10 +23746,10 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>72.643562</v>
+        <v>72.64357</v>
       </c>
       <c r="H614" t="n">
-        <v>110.6404</v>
+        <v>110.6405</v>
       </c>
     </row>
     <row r="615">
@@ -57832,10 +57832,10 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>55.159622</v>
+        <v>55.159618</v>
       </c>
       <c r="H1511" t="n">
-        <v>100.3367</v>
+        <v>100.3366</v>
       </c>
     </row>
     <row r="1512">
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.74078</v>
+        <v>54.740784</v>
       </c>
       <c r="H1513" t="n">
         <v>99.5748</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.536236</v>
+        <v>54.536232</v>
       </c>
       <c r="H1514" t="n">
         <v>99.20269999999999</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.257015</v>
+        <v>55.257023</v>
       </c>
       <c r="H1516" t="n">
         <v>100.5138</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.257015</v>
+        <v>55.257023</v>
       </c>
       <c r="H1518" t="n">
         <v>100.5138</v>
@@ -58174,7 +58174,7 @@
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1520" t="n">
         <v>100.5493</v>
@@ -58326,7 +58326,7 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.588192</v>
+        <v>55.588188</v>
       </c>
       <c r="H1524" t="n">
         <v>101.1162</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1526" t="n">
         <v>100.5847</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.169353</v>
+        <v>55.169361</v>
       </c>
       <c r="H1528" t="n">
         <v>100.3544</v>
@@ -58516,7 +58516,7 @@
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1529" t="n">
         <v>100.5493</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>54.867409</v>
+        <v>54.867405</v>
       </c>
       <c r="H1530" t="n">
         <v>99.8051</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.584934</v>
+        <v>54.584938</v>
       </c>
       <c r="H1531" t="n">
         <v>99.29130000000001</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.383652</v>
+        <v>55.383644</v>
       </c>
       <c r="H1532" t="n">
         <v>100.7442</v>
@@ -58668,7 +58668,7 @@
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>56.104427</v>
+        <v>56.104424</v>
       </c>
       <c r="H1533" t="n">
         <v>102.0553</v>
@@ -58706,10 +58706,10 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>56.523262</v>
+        <v>56.523266</v>
       </c>
       <c r="H1534" t="n">
-        <v>102.8171</v>
+        <v>102.8172</v>
       </c>
     </row>
     <row r="1535">
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.60767</v>
+        <v>55.607674</v>
       </c>
       <c r="H1536" t="n">
         <v>101.1517</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1538" t="n">
         <v>98.84829999999999</v>
@@ -58896,10 +58896,10 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1539" t="n">
-        <v>98.7597</v>
+        <v>98.7598</v>
       </c>
     </row>
     <row r="1540">
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1545" t="n">
         <v>101.0808</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1547" t="n">
         <v>101.0808</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.958328</v>
+        <v>55.958332</v>
       </c>
       <c r="H1550" t="n">
         <v>101.7895</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.987545</v>
+        <v>55.987549</v>
       </c>
       <c r="H1551" t="n">
         <v>101.8427</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.841438</v>
+        <v>55.841442</v>
       </c>
       <c r="H1553" t="n">
         <v>101.5769</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>56.172615</v>
+        <v>56.172611</v>
       </c>
       <c r="H1555" t="n">
         <v>102.1793</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.851181</v>
+        <v>55.851185</v>
       </c>
       <c r="H1556" t="n">
         <v>101.5946</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1558" t="n">
         <v>101.975</v>
@@ -59732,7 +59732,7 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1561" t="n">
         <v>103.2906</v>
@@ -59846,7 +59846,7 @@
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.969242</v>
+        <v>56.969246</v>
       </c>
       <c r="H1564" t="n">
         <v>103.6284</v>
@@ -59998,7 +59998,7 @@
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>58.532986</v>
+        <v>58.53299</v>
       </c>
       <c r="H1568" t="n">
         <v>106.4729</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>58.513439</v>
+        <v>58.513443</v>
       </c>
       <c r="H1569" t="n">
         <v>106.4373</v>
@@ -60150,10 +60150,10 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>59.129162</v>
+        <v>59.129169</v>
       </c>
       <c r="H1572" t="n">
-        <v>107.5573</v>
+        <v>107.5574</v>
       </c>
     </row>
     <row r="1573">
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1574" t="n">
         <v>107.5929</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>59.490784</v>
+        <v>59.49078</v>
       </c>
       <c r="H1575" t="n">
         <v>108.2151</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>59.500553</v>
+        <v>59.500557</v>
       </c>
       <c r="H1576" t="n">
         <v>108.2329</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1578" t="n">
         <v>106.0107</v>
@@ -60416,7 +60416,7 @@
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.259335</v>
+        <v>58.259331</v>
       </c>
       <c r="H1579" t="n">
         <v>105.9751</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.865284</v>
+        <v>58.86528</v>
       </c>
       <c r="H1581" t="n">
         <v>107.0773</v>
@@ -60568,7 +60568,7 @@
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1583" t="n">
         <v>107.8774</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>60.116283</v>
+        <v>60.11628</v>
       </c>
       <c r="H1593" t="n">
         <v>109.3529</v>
@@ -60986,7 +60986,7 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>60.204243</v>
+        <v>60.204239</v>
       </c>
       <c r="H1594" t="n">
         <v>109.5129</v>
@@ -61024,10 +61024,10 @@
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1595" t="n">
-        <v>109.0152</v>
+        <v>109.0151</v>
       </c>
     </row>
     <row r="1596">
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.940365</v>
+        <v>59.940361</v>
       </c>
       <c r="H1597" t="n">
         <v>109.0329</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>60.262886</v>
+        <v>60.262882</v>
       </c>
       <c r="H1598" t="n">
         <v>109.6196</v>
@@ -61176,10 +61176,10 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.956791</v>
+        <v>60.956799</v>
       </c>
       <c r="H1599" t="n">
-        <v>110.8818</v>
+        <v>110.8819</v>
       </c>
     </row>
     <row r="1600">
@@ -61290,7 +61290,7 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1602" t="n">
         <v>110.7218</v>
@@ -61366,7 +61366,7 @@
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>61.474789</v>
+        <v>61.474785</v>
       </c>
       <c r="H1604" t="n">
         <v>111.8241</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>61.445469</v>
+        <v>61.445465</v>
       </c>
       <c r="H1606" t="n">
         <v>111.7708</v>
@@ -61632,7 +61632,7 @@
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1611" t="n">
         <v>105.6018</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>57.653381</v>
+        <v>57.653385</v>
       </c>
       <c r="H1612" t="n">
         <v>104.8729</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>58.787098</v>
+        <v>58.787102</v>
       </c>
       <c r="H1613" t="n">
         <v>106.9351</v>
@@ -61898,10 +61898,10 @@
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1618" t="n">
-        <v>106.2857</v>
+        <v>106.2856</v>
       </c>
     </row>
     <row r="1619">
@@ -62620,7 +62620,7 @@
         </is>
       </c>
       <c r="G1637" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1637" t="n">
         <v>109.4222</v>
@@ -62696,7 +62696,7 @@
         </is>
       </c>
       <c r="G1639" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1639" t="n">
         <v>111.1152</v>
@@ -62772,7 +62772,7 @@
         </is>
       </c>
       <c r="G1641" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1641" t="n">
         <v>109.2796</v>
@@ -62848,7 +62848,7 @@
         </is>
       </c>
       <c r="G1643" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1643" t="n">
         <v>109.0479</v>
@@ -62886,7 +62886,7 @@
         </is>
       </c>
       <c r="G1644" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1644" t="n">
         <v>108.4598</v>
@@ -63000,7 +63000,7 @@
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1647" t="n">
         <v>107.2302</v>
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1650" t="n">
         <v>108.6559</v>
@@ -63152,7 +63152,7 @@
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1651" t="n">
         <v>111.0617</v>
@@ -63228,7 +63228,7 @@
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1653" t="n">
         <v>109.244</v>
@@ -63304,7 +63304,7 @@
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1655" t="n">
         <v>108.246</v>
@@ -63684,7 +63684,7 @@
         </is>
       </c>
       <c r="G1665" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1665" t="n">
         <v>112.5587</v>
@@ -63760,7 +63760,7 @@
         </is>
       </c>
       <c r="G1667" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1667" t="n">
         <v>112.0775</v>
@@ -63874,7 +63874,7 @@
         </is>
       </c>
       <c r="G1670" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1670" t="n">
         <v>112.2023</v>
@@ -63950,7 +63950,7 @@
         </is>
       </c>
       <c r="G1672" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1672" t="n">
         <v>112.0775</v>
@@ -63988,7 +63988,7 @@
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1673" t="n">
         <v>111.632</v>
@@ -64140,7 +64140,7 @@
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1677" t="n">
         <v>111.4894</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1760"/>
+  <dimension ref="A1:H1763"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>36.810001</v>
+        <v>37.080002</v>
       </c>
       <c r="H253" t="n">
-        <v>126.7999</v>
+        <v>127.7299</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>49.41</v>
+        <v>49.889999</v>
       </c>
       <c r="H504" t="n">
-        <v>131.0436</v>
+        <v>132.3167</v>
       </c>
     </row>
     <row r="505">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H508" t="n">
         <v>98.79859999999999</v>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="G510" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H510" t="n">
         <v>99.1694</v>
@@ -19832,7 +19832,7 @@
         </is>
       </c>
       <c r="G511" t="n">
-        <v>65.540474</v>
+        <v>65.540482</v>
       </c>
       <c r="H511" t="n">
         <v>99.822</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>65.939751</v>
+        <v>65.939758</v>
       </c>
       <c r="H516" t="n">
         <v>100.4301</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H522" t="n">
         <v>100.6675</v>
@@ -20288,7 +20288,7 @@
         </is>
       </c>
       <c r="G523" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H523" t="n">
         <v>100.6081</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H524" t="n">
         <v>100.6675</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H525" t="n">
         <v>100.9641</v>
@@ -20402,7 +20402,7 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>65.988449</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H526" t="n">
         <v>100.5043</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.368256</v>
+        <v>66.36824799999999</v>
       </c>
       <c r="H528" t="n">
         <v>101.0828</v>
@@ -20554,10 +20554,10 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H530" t="n">
-        <v>102.9071</v>
+        <v>102.9072</v>
       </c>
     </row>
     <row r="531">
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>67.059692</v>
+        <v>67.05970000000001</v>
       </c>
       <c r="H531" t="n">
         <v>102.1359</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>66.416946</v>
+        <v>66.416939</v>
       </c>
       <c r="H533" t="n">
         <v>101.1569</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>65.754723</v>
+        <v>65.754715</v>
       </c>
       <c r="H534" t="n">
         <v>100.1483</v>
@@ -20744,7 +20744,7 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>65.71575900000001</v>
+        <v>65.715767</v>
       </c>
       <c r="H535" t="n">
         <v>100.089</v>
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H536" t="n">
         <v>100.5636</v>
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H537" t="n">
         <v>100.356</v>
@@ -20858,10 +20858,10 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.124786</v>
+        <v>66.124779</v>
       </c>
       <c r="H538" t="n">
-        <v>100.712</v>
+        <v>100.7119</v>
       </c>
     </row>
     <row r="539">
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.387726</v>
+        <v>66.387733</v>
       </c>
       <c r="H539" t="n">
         <v>101.1124</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>67.059692</v>
+        <v>67.05970000000001</v>
       </c>
       <c r="H543" t="n">
         <v>102.1359</v>
@@ -21276,10 +21276,10 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.293419</v>
+        <v>67.29341100000001</v>
       </c>
       <c r="H549" t="n">
-        <v>102.4919</v>
+        <v>102.4918</v>
       </c>
     </row>
     <row r="550">
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H551" t="n">
         <v>102.7737</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H554" t="n">
         <v>102.299</v>
@@ -21504,7 +21504,7 @@
         </is>
       </c>
       <c r="G555" t="n">
-        <v>67.23497</v>
+        <v>67.234978</v>
       </c>
       <c r="H555" t="n">
         <v>102.4028</v>
@@ -29075,7 +29075,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.650002</v>
+        <v>81</v>
       </c>
       <c r="H755" t="n">
-        <v>122.8347</v>
+        <v>123.3678</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>131.470001</v>
+        <v>131.850006</v>
       </c>
       <c r="H1006" t="n">
-        <v>120.5373</v>
+        <v>120.8857</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>131.470001</v>
+        <v>131.850006</v>
       </c>
       <c r="H1257" t="n">
-        <v>120.5373</v>
+        <v>120.8857</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>131.470001</v>
+        <v>131.850006</v>
       </c>
       <c r="H1508" t="n">
-        <v>120.5373</v>
+        <v>120.8857</v>
       </c>
     </row>
     <row r="1509">
@@ -57752,11 +57752,11 @@
       </c>
       <c r="F1509" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1509" t="n">
-        <v>54.974548</v>
+        <v>273.559998</v>
       </c>
       <c r="H1509" t="n">
         <v>100</v>
@@ -57790,14 +57790,14 @@
       </c>
       <c r="F1510" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>55.403126</v>
+        <v>275.559998</v>
       </c>
       <c r="H1510" t="n">
-        <v>100.7796</v>
+        <v>100.7311</v>
       </c>
     </row>
     <row r="1511">
@@ -57828,14 +57828,14 @@
       </c>
       <c r="F1511" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>55.159618</v>
+        <v>274.160004</v>
       </c>
       <c r="H1511" t="n">
-        <v>100.3366</v>
+        <v>100.2193</v>
       </c>
     </row>
     <row r="1512">
@@ -57866,14 +57866,14 @@
       </c>
       <c r="F1512" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.429092</v>
+        <v>270.899994</v>
       </c>
       <c r="H1512" t="n">
-        <v>99.0078</v>
+        <v>99.02760000000001</v>
       </c>
     </row>
     <row r="1513">
@@ -57904,14 +57904,14 @@
       </c>
       <c r="F1513" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.740784</v>
+        <v>272.25</v>
       </c>
       <c r="H1513" t="n">
-        <v>99.5748</v>
+        <v>99.5211</v>
       </c>
     </row>
     <row r="1514">
@@ -57942,14 +57942,14 @@
       </c>
       <c r="F1514" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.536232</v>
+        <v>271.160004</v>
       </c>
       <c r="H1514" t="n">
-        <v>99.20269999999999</v>
+        <v>99.12269999999999</v>
       </c>
     </row>
     <row r="1515">
@@ -57980,14 +57980,14 @@
       </c>
       <c r="F1515" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>54.818703</v>
+        <v>272.790009</v>
       </c>
       <c r="H1515" t="n">
-        <v>99.7165</v>
+        <v>99.71850000000001</v>
       </c>
     </row>
     <row r="1516">
@@ -58018,14 +58018,14 @@
       </c>
       <c r="F1516" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.257023</v>
+        <v>274.76001</v>
       </c>
       <c r="H1516" t="n">
-        <v>100.5138</v>
+        <v>100.4387</v>
       </c>
     </row>
     <row r="1517">
@@ -58056,14 +58056,14 @@
       </c>
       <c r="F1517" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>54.682339</v>
+        <v>272.170013</v>
       </c>
       <c r="H1517" t="n">
-        <v>99.46850000000001</v>
+        <v>99.4919</v>
       </c>
     </row>
     <row r="1518">
@@ -58094,14 +58094,14 @@
       </c>
       <c r="F1518" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.257023</v>
+        <v>274.829987</v>
       </c>
       <c r="H1518" t="n">
-        <v>100.5138</v>
+        <v>100.4642</v>
       </c>
     </row>
     <row r="1519">
@@ -58132,14 +58132,14 @@
       </c>
       <c r="F1519" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>55.403126</v>
+        <v>275.429993</v>
       </c>
       <c r="H1519" t="n">
-        <v>100.7796</v>
+        <v>100.6836</v>
       </c>
     </row>
     <row r="1520">
@@ -58170,14 +58170,14 @@
       </c>
       <c r="F1520" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1520" t="n">
-        <v>55.276505</v>
+        <v>275.059998</v>
       </c>
       <c r="H1520" t="n">
-        <v>100.5493</v>
+        <v>100.5483</v>
       </c>
     </row>
     <row r="1521">
@@ -58208,20 +58208,20 @@
       </c>
       <c r="F1521" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.47131</v>
+        <v>275.809998</v>
       </c>
       <c r="H1521" t="n">
-        <v>100.9036</v>
+        <v>100.8225</v>
       </c>
     </row>
     <row r="1522">
       <c r="A1522" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B1522" t="inlineStr">
@@ -58246,20 +58246,20 @@
       </c>
       <c r="F1522" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.75378</v>
+        <v>276.058685</v>
       </c>
       <c r="H1522" t="n">
-        <v>101.4174</v>
+        <v>100.9134</v>
       </c>
     </row>
     <row r="1523">
       <c r="A1523" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B1523" t="inlineStr">
@@ -58284,20 +58284,20 @@
       </c>
       <c r="F1523" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.636894</v>
+        <v>277.220001</v>
       </c>
       <c r="H1523" t="n">
-        <v>101.2048</v>
+        <v>101.3379</v>
       </c>
     </row>
     <row r="1524">
       <c r="A1524" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B1524" t="inlineStr">
@@ -58322,20 +58322,20 @@
       </c>
       <c r="F1524" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.588188</v>
+        <v>276.649994</v>
       </c>
       <c r="H1524" t="n">
-        <v>101.1162</v>
+        <v>101.1295</v>
       </c>
     </row>
     <row r="1525">
       <c r="A1525" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B1525" t="inlineStr">
@@ -58360,20 +58360,20 @@
       </c>
       <c r="F1525" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.529751</v>
+        <v>276.339996</v>
       </c>
       <c r="H1525" t="n">
-        <v>101.0099</v>
+        <v>101.0162</v>
       </c>
     </row>
     <row r="1526">
       <c r="A1526" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B1526" t="inlineStr">
@@ -58398,20 +58398,20 @@
       </c>
       <c r="F1526" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.295986</v>
+        <v>276.23999</v>
       </c>
       <c r="H1526" t="n">
-        <v>100.5847</v>
+        <v>100.9797</v>
       </c>
     </row>
     <row r="1527">
       <c r="A1527" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B1527" t="inlineStr">
@@ -58436,20 +58436,20 @@
       </c>
       <c r="F1527" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.325203</v>
+        <v>274.890015</v>
       </c>
       <c r="H1527" t="n">
-        <v>100.6378</v>
+        <v>100.4862</v>
       </c>
     </row>
     <row r="1528">
       <c r="A1528" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B1528" t="inlineStr">
@@ -58474,20 +58474,20 @@
       </c>
       <c r="F1528" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.169361</v>
+        <v>274.940002</v>
       </c>
       <c r="H1528" t="n">
-        <v>100.3544</v>
+        <v>100.5045</v>
       </c>
     </row>
     <row r="1529">
       <c r="A1529" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B1529" t="inlineStr">
@@ -58512,20 +58512,20 @@
       </c>
       <c r="F1529" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1529" t="n">
-        <v>55.276505</v>
+        <v>274.190002</v>
       </c>
       <c r="H1529" t="n">
-        <v>100.5493</v>
+        <v>100.2303</v>
       </c>
     </row>
     <row r="1530">
       <c r="A1530" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B1530" t="inlineStr">
@@ -58550,20 +58550,20 @@
       </c>
       <c r="F1530" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>54.867405</v>
+        <v>274.829987</v>
       </c>
       <c r="H1530" t="n">
-        <v>99.8051</v>
+        <v>100.4642</v>
       </c>
     </row>
     <row r="1531">
       <c r="A1531" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B1531" t="inlineStr">
@@ -58588,20 +58588,20 @@
       </c>
       <c r="F1531" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>54.584938</v>
+        <v>272.910004</v>
       </c>
       <c r="H1531" t="n">
-        <v>99.29130000000001</v>
+        <v>99.7624</v>
       </c>
     </row>
     <row r="1532">
       <c r="A1532" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B1532" t="inlineStr">
@@ -58626,20 +58626,20 @@
       </c>
       <c r="F1532" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>55.383644</v>
+        <v>271.450012</v>
       </c>
       <c r="H1532" t="n">
-        <v>100.7442</v>
+        <v>99.2287</v>
       </c>
     </row>
     <row r="1533">
       <c r="A1533" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B1533" t="inlineStr">
@@ -58664,20 +58664,20 @@
       </c>
       <c r="F1533" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1533" t="n">
-        <v>56.104424</v>
+        <v>275.26001</v>
       </c>
       <c r="H1533" t="n">
-        <v>102.0553</v>
+        <v>100.6214</v>
       </c>
     </row>
     <row r="1534">
       <c r="A1534" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B1534" t="inlineStr">
@@ -58702,20 +58702,20 @@
       </c>
       <c r="F1534" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>56.523266</v>
+        <v>278.899994</v>
       </c>
       <c r="H1534" t="n">
-        <v>102.8172</v>
+        <v>101.952</v>
       </c>
     </row>
     <row r="1535">
       <c r="A1535" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B1535" t="inlineStr">
@@ -58740,20 +58740,20 @@
       </c>
       <c r="F1535" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>56.143391</v>
+        <v>280.899994</v>
       </c>
       <c r="H1535" t="n">
-        <v>102.1262</v>
+        <v>102.6831</v>
       </c>
     </row>
     <row r="1536">
       <c r="A1536" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B1536" t="inlineStr">
@@ -58778,20 +58778,20 @@
       </c>
       <c r="F1536" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.607674</v>
+        <v>279.339996</v>
       </c>
       <c r="H1536" t="n">
-        <v>101.1517</v>
+        <v>102.1129</v>
       </c>
     </row>
     <row r="1537">
       <c r="A1537" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B1537" t="inlineStr">
@@ -58816,20 +58816,20 @@
       </c>
       <c r="F1537" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>55.305721</v>
+        <v>276.5</v>
       </c>
       <c r="H1537" t="n">
-        <v>100.6024</v>
+        <v>101.0747</v>
       </c>
     </row>
     <row r="1538">
       <c r="A1538" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B1538" t="inlineStr">
@@ -58854,20 +58854,20 @@
       </c>
       <c r="F1538" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>54.341431</v>
+        <v>274.980011</v>
       </c>
       <c r="H1538" t="n">
-        <v>98.84829999999999</v>
+        <v>100.5191</v>
       </c>
     </row>
     <row r="1539">
       <c r="A1539" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B1539" t="inlineStr">
@@ -58892,20 +58892,20 @@
       </c>
       <c r="F1539" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>54.292728</v>
+        <v>270.200012</v>
       </c>
       <c r="H1539" t="n">
-        <v>98.7598</v>
+        <v>98.7718</v>
       </c>
     </row>
     <row r="1540">
       <c r="A1540" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B1540" t="inlineStr">
@@ -58930,20 +58930,20 @@
       </c>
       <c r="F1540" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.487534</v>
+        <v>270.049988</v>
       </c>
       <c r="H1540" t="n">
-        <v>99.11409999999999</v>
+        <v>98.7169</v>
       </c>
     </row>
     <row r="1541">
       <c r="A1541" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B1541" t="inlineStr">
@@ -58968,20 +58968,20 @@
       </c>
       <c r="F1541" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.351166</v>
+        <v>271.130005</v>
       </c>
       <c r="H1541" t="n">
-        <v>98.8661</v>
+        <v>99.1117</v>
       </c>
     </row>
     <row r="1542">
       <c r="A1542" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B1542" t="inlineStr">
@@ -59006,20 +59006,20 @@
       </c>
       <c r="F1542" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>54.419353</v>
+        <v>270.429993</v>
       </c>
       <c r="H1542" t="n">
-        <v>98.9901</v>
+        <v>98.8558</v>
       </c>
     </row>
     <row r="1543">
       <c r="A1543" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B1543" t="inlineStr">
@@ -59044,20 +59044,20 @@
       </c>
       <c r="F1543" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>54.877148</v>
+        <v>270.859985</v>
       </c>
       <c r="H1543" t="n">
-        <v>99.8228</v>
+        <v>99.01300000000001</v>
       </c>
     </row>
     <row r="1544">
       <c r="A1544" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B1544" t="inlineStr">
@@ -59082,20 +59082,20 @@
       </c>
       <c r="F1544" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.529751</v>
+        <v>273.399994</v>
       </c>
       <c r="H1544" t="n">
-        <v>101.0099</v>
+        <v>99.9415</v>
       </c>
     </row>
     <row r="1545">
       <c r="A1545" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B1545" t="inlineStr">
@@ -59120,20 +59120,20 @@
       </c>
       <c r="F1545" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.568707</v>
+        <v>276.380005</v>
       </c>
       <c r="H1545" t="n">
-        <v>101.0808</v>
+        <v>101.0309</v>
       </c>
     </row>
     <row r="1546">
       <c r="A1546" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B1546" t="inlineStr">
@@ -59158,20 +59158,20 @@
       </c>
       <c r="F1546" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.75378</v>
+        <v>276.720001</v>
       </c>
       <c r="H1546" t="n">
-        <v>101.4174</v>
+        <v>101.1551</v>
       </c>
     </row>
     <row r="1547">
       <c r="A1547" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B1547" t="inlineStr">
@@ -59196,20 +59196,20 @@
       </c>
       <c r="F1547" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.568707</v>
+        <v>277.369995</v>
       </c>
       <c r="H1547" t="n">
-        <v>101.0808</v>
+        <v>101.3927</v>
       </c>
     </row>
     <row r="1548">
       <c r="A1548" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B1548" t="inlineStr">
@@ -59234,20 +59234,20 @@
       </c>
       <c r="F1548" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1548" t="n">
-        <v>55.636894</v>
+        <v>276.799988</v>
       </c>
       <c r="H1548" t="n">
-        <v>101.2048</v>
+        <v>101.1844</v>
       </c>
     </row>
     <row r="1549">
       <c r="A1549" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B1549" t="inlineStr">
@@ -59272,20 +59272,20 @@
       </c>
       <c r="F1549" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.724556</v>
+        <v>276.959991</v>
       </c>
       <c r="H1549" t="n">
-        <v>101.3643</v>
+        <v>101.2429</v>
       </c>
     </row>
     <row r="1550">
       <c r="A1550" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B1550" t="inlineStr">
@@ -59310,20 +59310,20 @@
       </c>
       <c r="F1550" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.958332</v>
+        <v>277.459991</v>
       </c>
       <c r="H1550" t="n">
-        <v>101.7895</v>
+        <v>101.4256</v>
       </c>
     </row>
     <row r="1551">
       <c r="A1551" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B1551" t="inlineStr">
@@ -59348,20 +59348,20 @@
       </c>
       <c r="F1551" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.987549</v>
+        <v>278.660004</v>
       </c>
       <c r="H1551" t="n">
-        <v>101.8427</v>
+        <v>101.8643</v>
       </c>
     </row>
     <row r="1552">
       <c r="A1552" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B1552" t="inlineStr">
@@ -59386,20 +59386,20 @@
       </c>
       <c r="F1552" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.899879</v>
+        <v>278.619995</v>
       </c>
       <c r="H1552" t="n">
-        <v>101.6832</v>
+        <v>101.8497</v>
       </c>
     </row>
     <row r="1553">
       <c r="A1553" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B1553" t="inlineStr">
@@ -59424,20 +59424,20 @@
       </c>
       <c r="F1553" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.841442</v>
+        <v>278.570007</v>
       </c>
       <c r="H1553" t="n">
-        <v>101.5769</v>
+        <v>101.8314</v>
       </c>
     </row>
     <row r="1554">
       <c r="A1554" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B1554" t="inlineStr">
@@ -59462,20 +59462,20 @@
       </c>
       <c r="F1554" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1554" t="n">
-        <v>55.870663</v>
+        <v>278.329987</v>
       </c>
       <c r="H1554" t="n">
-        <v>101.6301</v>
+        <v>101.7437</v>
       </c>
     </row>
     <row r="1555">
       <c r="A1555" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B1555" t="inlineStr">
@@ -59500,20 +59500,20 @@
       </c>
       <c r="F1555" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>56.172611</v>
+        <v>278.380005</v>
       </c>
       <c r="H1555" t="n">
-        <v>102.1793</v>
+        <v>101.762</v>
       </c>
     </row>
     <row r="1556">
       <c r="A1556" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B1556" t="inlineStr">
@@ -59538,20 +59538,20 @@
       </c>
       <c r="F1556" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>55.851185</v>
+        <v>280.059998</v>
       </c>
       <c r="H1556" t="n">
-        <v>101.5946</v>
+        <v>102.3761</v>
       </c>
     </row>
     <row r="1557">
       <c r="A1557" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B1557" t="inlineStr">
@@ -59576,20 +59576,20 @@
       </c>
       <c r="F1557" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>56.294872</v>
+        <v>278.369995</v>
       </c>
       <c r="H1557" t="n">
-        <v>102.4017</v>
+        <v>101.7583</v>
       </c>
     </row>
     <row r="1558">
       <c r="A1558" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B1558" t="inlineStr">
@@ -59614,20 +59614,20 @@
       </c>
       <c r="F1558" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>56.06031</v>
+        <v>280.51001</v>
       </c>
       <c r="H1558" t="n">
-        <v>101.975</v>
+        <v>102.5406</v>
       </c>
     </row>
     <row r="1559">
       <c r="A1559" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B1559" t="inlineStr">
@@ -59652,20 +59652,20 @@
       </c>
       <c r="F1559" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>55.991898</v>
+        <v>279.359985</v>
       </c>
       <c r="H1559" t="n">
-        <v>101.8506</v>
+        <v>102.1202</v>
       </c>
     </row>
     <row r="1560">
       <c r="A1560" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B1560" t="inlineStr">
@@ -59690,20 +59690,20 @@
       </c>
       <c r="F1560" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>56.558758</v>
+        <v>279.299988</v>
       </c>
       <c r="H1560" t="n">
-        <v>102.8817</v>
+        <v>102.0983</v>
       </c>
     </row>
     <row r="1561">
       <c r="A1561" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B1561" t="inlineStr">
@@ -59728,20 +59728,20 @@
       </c>
       <c r="F1561" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.783543</v>
+        <v>281.75</v>
       </c>
       <c r="H1561" t="n">
-        <v>103.2906</v>
+        <v>102.9939</v>
       </c>
     </row>
     <row r="1562">
       <c r="A1562" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B1562" t="inlineStr">
@@ -59766,20 +59766,20 @@
       </c>
       <c r="F1562" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1562" t="n">
-        <v>56.676041</v>
+        <v>282.890015</v>
       </c>
       <c r="H1562" t="n">
-        <v>103.0951</v>
+        <v>103.4106</v>
       </c>
     </row>
     <row r="1563">
       <c r="A1563" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B1563" t="inlineStr">
@@ -59804,20 +59804,20 @@
       </c>
       <c r="F1563" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.891052</v>
+        <v>282.709991</v>
       </c>
       <c r="H1563" t="n">
-        <v>103.4862</v>
+        <v>103.3448</v>
       </c>
     </row>
     <row r="1564">
       <c r="A1564" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B1564" t="inlineStr">
@@ -59842,20 +59842,20 @@
       </c>
       <c r="F1564" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1564" t="n">
-        <v>56.969246</v>
+        <v>283.630005</v>
       </c>
       <c r="H1564" t="n">
-        <v>103.6284</v>
+        <v>103.6811</v>
       </c>
     </row>
     <row r="1565">
       <c r="A1565" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B1565" t="inlineStr">
@@ -59880,20 +59880,20 @@
       </c>
       <c r="F1565" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>57.272217</v>
+        <v>285</v>
       </c>
       <c r="H1565" t="n">
-        <v>104.1795</v>
+        <v>104.1819</v>
       </c>
     </row>
     <row r="1566">
       <c r="A1566" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B1566" t="inlineStr">
@@ -59918,20 +59918,20 @@
       </c>
       <c r="F1566" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>57.692474</v>
+        <v>283.920013</v>
       </c>
       <c r="H1566" t="n">
-        <v>104.944</v>
+        <v>103.7871</v>
       </c>
     </row>
     <row r="1567">
       <c r="A1567" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B1567" t="inlineStr">
@@ -59956,20 +59956,20 @@
       </c>
       <c r="F1567" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1567" t="n">
-        <v>58.210468</v>
+        <v>285.769989</v>
       </c>
       <c r="H1567" t="n">
-        <v>105.8862</v>
+        <v>104.4634</v>
       </c>
     </row>
     <row r="1568">
       <c r="A1568" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B1568" t="inlineStr">
@@ -59994,20 +59994,20 @@
       </c>
       <c r="F1568" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1568" t="n">
-        <v>58.53299</v>
+        <v>285.059998</v>
       </c>
       <c r="H1568" t="n">
-        <v>106.4729</v>
+        <v>104.2038</v>
       </c>
     </row>
     <row r="1569">
       <c r="A1569" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B1569" t="inlineStr">
@@ -60032,20 +60032,20 @@
       </c>
       <c r="F1569" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>58.513443</v>
+        <v>287.329987</v>
       </c>
       <c r="H1569" t="n">
-        <v>106.4373</v>
+        <v>105.0336</v>
       </c>
     </row>
     <row r="1570">
       <c r="A1570" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B1570" t="inlineStr">
@@ -60070,20 +60070,20 @@
       </c>
       <c r="F1570" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>58.39616</v>
+        <v>290.100006</v>
       </c>
       <c r="H1570" t="n">
-        <v>106.224</v>
+        <v>106.0462</v>
       </c>
     </row>
     <row r="1571">
       <c r="A1571" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B1571" t="inlineStr">
@@ -60108,20 +60108,20 @@
       </c>
       <c r="F1571" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>59.031437</v>
+        <v>291.660004</v>
       </c>
       <c r="H1571" t="n">
-        <v>107.3796</v>
+        <v>106.6165</v>
       </c>
     </row>
     <row r="1572">
       <c r="A1572" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B1572" t="inlineStr">
@@ -60146,20 +60146,20 @@
       </c>
       <c r="F1572" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>59.129169</v>
+        <v>291.470001</v>
       </c>
       <c r="H1572" t="n">
-        <v>107.5574</v>
+        <v>106.547</v>
       </c>
     </row>
     <row r="1573">
       <c r="A1573" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B1573" t="inlineStr">
@@ -60184,20 +60184,20 @@
       </c>
       <c r="F1573" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>59.070522</v>
+        <v>290.910004</v>
       </c>
       <c r="H1573" t="n">
-        <v>107.4507</v>
+        <v>106.3423</v>
       </c>
     </row>
     <row r="1574">
       <c r="A1574" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B1574" t="inlineStr">
@@ -60222,20 +60222,20 @@
       </c>
       <c r="F1574" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>59.148712</v>
+        <v>293.779999</v>
       </c>
       <c r="H1574" t="n">
-        <v>107.5929</v>
+        <v>107.3914</v>
       </c>
     </row>
     <row r="1575">
       <c r="A1575" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B1575" t="inlineStr">
@@ -60260,20 +60260,20 @@
       </c>
       <c r="F1575" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>59.49078</v>
+        <v>294.450012</v>
       </c>
       <c r="H1575" t="n">
-        <v>108.2151</v>
+        <v>107.6364</v>
       </c>
     </row>
     <row r="1576">
       <c r="A1576" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B1576" t="inlineStr">
@@ -60298,20 +60298,20 @@
       </c>
       <c r="F1576" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>59.500557</v>
+        <v>294.089996</v>
       </c>
       <c r="H1576" t="n">
-        <v>108.2329</v>
+        <v>107.5048</v>
       </c>
     </row>
     <row r="1577">
       <c r="A1577" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B1577" t="inlineStr">
@@ -60336,20 +60336,20 @@
       </c>
       <c r="F1577" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>58.708908</v>
+        <v>294.579987</v>
       </c>
       <c r="H1577" t="n">
-        <v>106.7929</v>
+        <v>107.6839</v>
       </c>
     </row>
     <row r="1578">
       <c r="A1578" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B1578" t="inlineStr">
@@ -60374,20 +60374,20 @@
       </c>
       <c r="F1578" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>58.278881</v>
+        <v>296.079987</v>
       </c>
       <c r="H1578" t="n">
-        <v>106.0107</v>
+        <v>108.2322</v>
       </c>
     </row>
     <row r="1579">
       <c r="A1579" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B1579" t="inlineStr">
@@ -60412,20 +60412,20 @@
       </c>
       <c r="F1579" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1579" t="n">
-        <v>58.259331</v>
+        <v>296.109985</v>
       </c>
       <c r="H1579" t="n">
-        <v>105.9751</v>
+        <v>108.2432</v>
       </c>
     </row>
     <row r="1580">
       <c r="A1580" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B1580" t="inlineStr">
@@ -60450,20 +60450,20 @@
       </c>
       <c r="F1580" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1580" t="n">
-        <v>58.91415</v>
+        <v>292.609985</v>
       </c>
       <c r="H1580" t="n">
-        <v>107.1662</v>
+        <v>106.9637</v>
       </c>
     </row>
     <row r="1581">
       <c r="A1581" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B1581" t="inlineStr">
@@ -60488,20 +60488,20 @@
       </c>
       <c r="F1581" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.86528</v>
+        <v>290.529999</v>
       </c>
       <c r="H1581" t="n">
-        <v>107.0773</v>
+        <v>106.2034</v>
       </c>
     </row>
     <row r="1582">
       <c r="A1582" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B1582" t="inlineStr">
@@ -60526,20 +60526,20 @@
       </c>
       <c r="F1582" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>58.953243</v>
+        <v>290.339996</v>
       </c>
       <c r="H1582" t="n">
-        <v>107.2373</v>
+        <v>106.1339</v>
       </c>
     </row>
     <row r="1583">
       <c r="A1583" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B1583" t="inlineStr">
@@ -60564,20 +60564,20 @@
       </c>
       <c r="F1583" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1583" t="n">
-        <v>59.305092</v>
+        <v>293.299988</v>
       </c>
       <c r="H1583" t="n">
-        <v>107.8774</v>
+        <v>107.216</v>
       </c>
     </row>
     <row r="1584">
       <c r="A1584" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B1584" t="inlineStr">
@@ -60602,20 +60602,20 @@
       </c>
       <c r="F1584" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1584" t="n">
-        <v>58.835964</v>
+        <v>293.23999</v>
       </c>
       <c r="H1584" t="n">
-        <v>107.024</v>
+        <v>107.194</v>
       </c>
     </row>
     <row r="1585">
       <c r="A1585" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B1585" t="inlineStr">
@@ -60640,20 +60640,20 @@
       </c>
       <c r="F1585" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>58.718685</v>
+        <v>293.709991</v>
       </c>
       <c r="H1585" t="n">
-        <v>106.8107</v>
+        <v>107.3658</v>
       </c>
     </row>
     <row r="1586">
       <c r="A1586" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B1586" t="inlineStr">
@@ -60678,20 +60678,20 @@
       </c>
       <c r="F1586" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.168262</v>
+        <v>295.350006</v>
       </c>
       <c r="H1586" t="n">
-        <v>107.6285</v>
+        <v>107.9653</v>
       </c>
     </row>
     <row r="1587">
       <c r="A1587" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B1587" t="inlineStr">
@@ -60716,20 +60716,20 @@
       </c>
       <c r="F1587" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1587" t="n">
-        <v>59.793758</v>
+        <v>293.119995</v>
       </c>
       <c r="H1587" t="n">
-        <v>108.7663</v>
+        <v>107.1502</v>
       </c>
     </row>
     <row r="1588">
       <c r="A1588" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B1588" t="inlineStr">
@@ -60754,20 +60754,20 @@
       </c>
       <c r="F1588" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.774212</v>
+        <v>292.570007</v>
       </c>
       <c r="H1588" t="n">
-        <v>108.7307</v>
+        <v>106.9491</v>
       </c>
     </row>
     <row r="1589">
       <c r="A1589" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B1589" t="inlineStr">
@@ -60792,20 +60792,20 @@
       </c>
       <c r="F1589" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.803532</v>
+        <v>294.600006</v>
       </c>
       <c r="H1589" t="n">
-        <v>108.784</v>
+        <v>107.6912</v>
       </c>
     </row>
     <row r="1590">
       <c r="A1590" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B1590" t="inlineStr">
@@ -60830,20 +60830,20 @@
       </c>
       <c r="F1590" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.246445</v>
+        <v>297.76001</v>
       </c>
       <c r="H1590" t="n">
-        <v>107.7707</v>
+        <v>108.8463</v>
       </c>
     </row>
     <row r="1591">
       <c r="A1591" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B1591" t="inlineStr">
@@ -60868,20 +60868,20 @@
       </c>
       <c r="F1591" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>59.744892</v>
+        <v>297.779999</v>
       </c>
       <c r="H1591" t="n">
-        <v>108.6774</v>
+        <v>108.8536</v>
       </c>
     </row>
     <row r="1592">
       <c r="A1592" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B1592" t="inlineStr">
@@ -60906,20 +60906,20 @@
       </c>
       <c r="F1592" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>60.155373</v>
+        <v>297.820007</v>
       </c>
       <c r="H1592" t="n">
-        <v>109.424</v>
+        <v>108.8683</v>
       </c>
     </row>
     <row r="1593">
       <c r="A1593" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B1593" t="inlineStr">
@@ -60944,20 +60944,20 @@
       </c>
       <c r="F1593" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>60.11628</v>
+        <v>294.829987</v>
       </c>
       <c r="H1593" t="n">
-        <v>109.3529</v>
+        <v>107.7753</v>
       </c>
     </row>
     <row r="1594">
       <c r="A1594" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B1594" t="inlineStr">
@@ -60982,20 +60982,20 @@
       </c>
       <c r="F1594" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>60.204239</v>
+        <v>297.440002</v>
       </c>
       <c r="H1594" t="n">
-        <v>109.5129</v>
+        <v>108.7293</v>
       </c>
     </row>
     <row r="1595">
       <c r="A1595" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B1595" t="inlineStr">
@@ -61020,20 +61020,20 @@
       </c>
       <c r="F1595" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1595" t="n">
-        <v>59.930584</v>
+        <v>299.549988</v>
       </c>
       <c r="H1595" t="n">
-        <v>109.0151</v>
+        <v>109.5007</v>
       </c>
     </row>
     <row r="1596">
       <c r="A1596" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B1596" t="inlineStr">
@@ -61058,20 +61058,20 @@
       </c>
       <c r="F1596" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.852402</v>
+        <v>299.26001</v>
       </c>
       <c r="H1596" t="n">
-        <v>108.8729</v>
+        <v>109.3947</v>
       </c>
     </row>
     <row r="1597">
       <c r="A1597" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B1597" t="inlineStr">
@@ -61096,20 +61096,20 @@
       </c>
       <c r="F1597" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>59.940361</v>
+        <v>299.790009</v>
       </c>
       <c r="H1597" t="n">
-        <v>109.0329</v>
+        <v>109.5884</v>
       </c>
     </row>
     <row r="1598">
       <c r="A1598" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B1598" t="inlineStr">
@@ -61134,20 +61134,20 @@
       </c>
       <c r="F1598" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>60.262882</v>
+        <v>298.100006</v>
       </c>
       <c r="H1598" t="n">
-        <v>109.6196</v>
+        <v>108.9706</v>
       </c>
     </row>
     <row r="1599">
       <c r="A1599" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B1599" t="inlineStr">
@@ -61172,20 +61172,20 @@
       </c>
       <c r="F1599" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.956799</v>
+        <v>297.899994</v>
       </c>
       <c r="H1599" t="n">
-        <v>110.8819</v>
+        <v>108.8975</v>
       </c>
     </row>
     <row r="1600">
       <c r="A1600" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B1600" t="inlineStr">
@@ -61210,20 +61210,20 @@
       </c>
       <c r="F1600" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>60.65382</v>
+        <v>298.190002</v>
       </c>
       <c r="H1600" t="n">
-        <v>110.3307</v>
+        <v>109.0035</v>
       </c>
     </row>
     <row r="1601">
       <c r="A1601" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B1601" t="inlineStr">
@@ -61248,20 +61248,20 @@
       </c>
       <c r="F1601" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>61.201126</v>
+        <v>299.709991</v>
       </c>
       <c r="H1601" t="n">
-        <v>111.3263</v>
+        <v>109.5591</v>
       </c>
     </row>
     <row r="1602">
       <c r="A1602" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B1602" t="inlineStr">
@@ -61286,20 +61286,20 @@
       </c>
       <c r="F1602" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>60.868835</v>
+        <v>303.269989</v>
       </c>
       <c r="H1602" t="n">
-        <v>110.7218</v>
+        <v>110.8605</v>
       </c>
     </row>
     <row r="1603">
       <c r="A1603" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B1603" t="inlineStr">
@@ -61324,20 +61324,20 @@
       </c>
       <c r="F1603" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>61.015434</v>
+        <v>301.779999</v>
       </c>
       <c r="H1603" t="n">
-        <v>110.9885</v>
+        <v>110.3158</v>
       </c>
     </row>
     <row r="1604">
       <c r="A1604" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B1604" t="inlineStr">
@@ -61362,20 +61362,20 @@
       </c>
       <c r="F1604" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1604" t="n">
-        <v>61.474785</v>
+        <v>304.320007</v>
       </c>
       <c r="H1604" t="n">
-        <v>111.8241</v>
+        <v>111.2443</v>
       </c>
     </row>
     <row r="1605">
       <c r="A1605" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B1605" t="inlineStr">
@@ -61400,20 +61400,20 @@
       </c>
       <c r="F1605" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>61.406372</v>
+        <v>302.929993</v>
       </c>
       <c r="H1605" t="n">
-        <v>111.6996</v>
+        <v>110.7362</v>
       </c>
     </row>
     <row r="1606">
       <c r="A1606" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B1606" t="inlineStr">
@@ -61438,20 +61438,20 @@
       </c>
       <c r="F1606" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>61.445465</v>
+        <v>303.709991</v>
       </c>
       <c r="H1606" t="n">
-        <v>111.7708</v>
+        <v>111.0213</v>
       </c>
     </row>
     <row r="1607">
       <c r="A1607" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B1607" t="inlineStr">
@@ -61476,20 +61476,20 @@
       </c>
       <c r="F1607" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>60.448574</v>
+        <v>305.730011</v>
       </c>
       <c r="H1607" t="n">
-        <v>109.9574</v>
+        <v>111.7598</v>
       </c>
     </row>
     <row r="1608">
       <c r="A1608" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B1608" t="inlineStr">
@@ -61514,20 +61514,20 @@
       </c>
       <c r="F1608" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>58.640495</v>
+        <v>305.579987</v>
       </c>
       <c r="H1608" t="n">
-        <v>106.6684</v>
+        <v>111.7049</v>
       </c>
     </row>
     <row r="1609">
       <c r="A1609" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B1609" t="inlineStr">
@@ -61552,20 +61552,20 @@
       </c>
       <c r="F1609" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>59.393051</v>
+        <v>305.730011</v>
       </c>
       <c r="H1609" t="n">
-        <v>108.0374</v>
+        <v>111.7598</v>
       </c>
     </row>
     <row r="1610">
       <c r="A1610" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B1610" t="inlineStr">
@@ -61590,20 +61590,20 @@
       </c>
       <c r="F1610" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>58.581856</v>
+        <v>300.98999</v>
       </c>
       <c r="H1610" t="n">
-        <v>106.5618</v>
+        <v>110.027</v>
       </c>
     </row>
     <row r="1611">
       <c r="A1611" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B1611" t="inlineStr">
@@ -61628,20 +61628,20 @@
       </c>
       <c r="F1611" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1611" t="n">
-        <v>58.054089</v>
+        <v>291.589996</v>
       </c>
       <c r="H1611" t="n">
-        <v>105.6018</v>
+        <v>106.5909</v>
       </c>
     </row>
     <row r="1612">
       <c r="A1612" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B1612" t="inlineStr">
@@ -61666,20 +61666,20 @@
       </c>
       <c r="F1612" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>57.653385</v>
+        <v>295.579987</v>
       </c>
       <c r="H1612" t="n">
-        <v>104.8729</v>
+        <v>108.0494</v>
       </c>
     </row>
     <row r="1613">
       <c r="A1613" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B1613" t="inlineStr">
@@ -61704,20 +61704,20 @@
       </c>
       <c r="F1613" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>58.787102</v>
+        <v>291.769989</v>
       </c>
       <c r="H1613" t="n">
-        <v>106.9351</v>
+        <v>106.6567</v>
       </c>
     </row>
     <row r="1614">
       <c r="A1614" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B1614" t="inlineStr">
@@ -61742,20 +61742,20 @@
       </c>
       <c r="F1614" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>58.4548</v>
+        <v>289.100006</v>
       </c>
       <c r="H1614" t="n">
-        <v>106.3307</v>
+        <v>105.6807</v>
       </c>
     </row>
     <row r="1615">
       <c r="A1615" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B1615" t="inlineStr">
@@ -61780,20 +61780,20 @@
       </c>
       <c r="F1615" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>58.112728</v>
+        <v>287.440002</v>
       </c>
       <c r="H1615" t="n">
-        <v>105.7084</v>
+        <v>105.0738</v>
       </c>
     </row>
     <row r="1616">
       <c r="A1616" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B1616" t="inlineStr">
@@ -61818,20 +61818,20 @@
       </c>
       <c r="F1616" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1616" t="n">
-        <v>57.790211</v>
+        <v>292.799988</v>
       </c>
       <c r="H1616" t="n">
-        <v>105.1218</v>
+        <v>107.0332</v>
       </c>
     </row>
     <row r="1617">
       <c r="A1617" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B1617" t="inlineStr">
@@ -61856,20 +61856,20 @@
       </c>
       <c r="F1617" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>58.038174</v>
+        <v>291.149994</v>
       </c>
       <c r="H1617" t="n">
-        <v>105.5728</v>
+        <v>106.43</v>
       </c>
     </row>
     <row r="1618">
       <c r="A1618" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B1618" t="inlineStr">
@@ -61894,20 +61894,20 @@
       </c>
       <c r="F1618" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1618" t="n">
-        <v>58.430054</v>
+        <v>289.700012</v>
       </c>
       <c r="H1618" t="n">
-        <v>106.2856</v>
+        <v>105.9</v>
       </c>
     </row>
     <row r="1619">
       <c r="A1619" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B1619" t="inlineStr">
@@ -61932,20 +61932,20 @@
       </c>
       <c r="F1619" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1619" t="n">
-        <v>57.989185</v>
+        <v>288.130005</v>
       </c>
       <c r="H1619" t="n">
-        <v>105.4837</v>
+        <v>105.3261</v>
       </c>
     </row>
     <row r="1620">
       <c r="A1620" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B1620" t="inlineStr">
@@ -61970,20 +61970,20 @@
       </c>
       <c r="F1620" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1620" t="n">
-        <v>56.549011</v>
+        <v>289.320007</v>
       </c>
       <c r="H1620" t="n">
-        <v>102.864</v>
+        <v>105.7611</v>
       </c>
     </row>
     <row r="1621">
       <c r="A1621" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B1621" t="inlineStr">
@@ -62008,20 +62008,20 @@
       </c>
       <c r="F1621" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1621" t="n">
-        <v>55.549702</v>
+        <v>291.309998</v>
       </c>
       <c r="H1621" t="n">
-        <v>101.0462</v>
+        <v>106.4885</v>
       </c>
     </row>
     <row r="1622">
       <c r="A1622" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B1622" t="inlineStr">
@@ -62046,20 +62046,20 @@
       </c>
       <c r="F1622" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1622" t="n">
-        <v>55.980774</v>
+        <v>289.160004</v>
       </c>
       <c r="H1622" t="n">
-        <v>101.8303</v>
+        <v>105.7026</v>
       </c>
     </row>
     <row r="1623">
       <c r="A1623" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B1623" t="inlineStr">
@@ -62084,20 +62084,20 @@
       </c>
       <c r="F1623" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1623" t="n">
-        <v>56.157124</v>
+        <v>282.019989</v>
       </c>
       <c r="H1623" t="n">
-        <v>102.1511</v>
+        <v>103.0926</v>
       </c>
     </row>
     <row r="1624">
       <c r="A1624" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B1624" t="inlineStr">
@@ -62122,20 +62122,20 @@
       </c>
       <c r="F1624" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1624" t="n">
-        <v>57.107449</v>
+        <v>277.130005</v>
       </c>
       <c r="H1624" t="n">
-        <v>103.8798</v>
+        <v>101.305</v>
       </c>
     </row>
     <row r="1625">
       <c r="A1625" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B1625" t="inlineStr">
@@ -62160,20 +62160,20 @@
       </c>
       <c r="F1625" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1625" t="n">
-        <v>56.40205</v>
+        <v>279.190002</v>
       </c>
       <c r="H1625" t="n">
-        <v>102.5967</v>
+        <v>102.0581</v>
       </c>
     </row>
     <row r="1626">
       <c r="A1626" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B1626" t="inlineStr">
@@ -62198,20 +62198,20 @@
       </c>
       <c r="F1626" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1626" t="n">
-        <v>55.892601</v>
+        <v>280.200012</v>
       </c>
       <c r="H1626" t="n">
-        <v>101.67</v>
+        <v>102.4273</v>
       </c>
     </row>
     <row r="1627">
       <c r="A1627" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B1627" t="inlineStr">
@@ -62236,20 +62236,20 @@
       </c>
       <c r="F1627" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1627" t="n">
-        <v>56.470631</v>
+        <v>284.51001</v>
       </c>
       <c r="H1627" t="n">
-        <v>102.7214</v>
+        <v>104.0028</v>
       </c>
     </row>
     <row r="1628">
       <c r="A1628" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B1628" t="inlineStr">
@@ -62274,20 +62274,20 @@
       </c>
       <c r="F1628" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1628" t="n">
-        <v>56.744949</v>
+        <v>281.119995</v>
       </c>
       <c r="H1628" t="n">
-        <v>103.2204</v>
+        <v>102.7636</v>
       </c>
     </row>
     <row r="1629">
       <c r="A1629" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B1629" t="inlineStr">
@@ -62312,20 +62312,20 @@
       </c>
       <c r="F1629" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1629" t="n">
-        <v>58.155739</v>
+        <v>278.679993</v>
       </c>
       <c r="H1629" t="n">
-        <v>105.7867</v>
+        <v>101.8716</v>
       </c>
     </row>
     <row r="1630">
       <c r="A1630" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B1630" t="inlineStr">
@@ -62350,20 +62350,20 @@
       </c>
       <c r="F1630" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1630" t="n">
-        <v>58.038174</v>
+        <v>281.700012</v>
       </c>
       <c r="H1630" t="n">
-        <v>105.5728</v>
+        <v>102.9756</v>
       </c>
     </row>
     <row r="1631">
       <c r="A1631" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B1631" t="inlineStr">
@@ -62388,20 +62388,20 @@
       </c>
       <c r="F1631" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1631" t="n">
-        <v>57.450344</v>
+        <v>282.820007</v>
       </c>
       <c r="H1631" t="n">
-        <v>104.5035</v>
+        <v>103.385</v>
       </c>
     </row>
     <row r="1632">
       <c r="A1632" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B1632" t="inlineStr">
@@ -62426,20 +62426,20 @@
       </c>
       <c r="F1632" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1632" t="n">
-        <v>59.772263</v>
+        <v>289.859985</v>
       </c>
       <c r="H1632" t="n">
-        <v>108.7272</v>
+        <v>105.9585</v>
       </c>
     </row>
     <row r="1633">
       <c r="A1633" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B1633" t="inlineStr">
@@ -62464,20 +62464,20 @@
       </c>
       <c r="F1633" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1633" t="n">
-        <v>59.713482</v>
+        <v>289.619995</v>
       </c>
       <c r="H1633" t="n">
-        <v>108.6202</v>
+        <v>105.8707</v>
       </c>
     </row>
     <row r="1634">
       <c r="A1634" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B1634" t="inlineStr">
@@ -62502,20 +62502,20 @@
       </c>
       <c r="F1634" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1634" t="n">
-        <v>59.899628</v>
+        <v>286.329987</v>
       </c>
       <c r="H1634" t="n">
-        <v>108.9588</v>
+        <v>104.6681</v>
       </c>
     </row>
     <row r="1635">
       <c r="A1635" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B1635" t="inlineStr">
@@ -62540,20 +62540,20 @@
       </c>
       <c r="F1635" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1635" t="n">
-        <v>59.801655</v>
+        <v>297.929993</v>
       </c>
       <c r="H1635" t="n">
-        <v>108.7806</v>
+        <v>108.9085</v>
       </c>
     </row>
     <row r="1636">
       <c r="A1636" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B1636" t="inlineStr">
@@ -62578,20 +62578,20 @@
       </c>
       <c r="F1636" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1636" t="n">
-        <v>60.340496</v>
+        <v>297.420013</v>
       </c>
       <c r="H1636" t="n">
-        <v>109.7608</v>
+        <v>108.722</v>
       </c>
     </row>
     <row r="1637">
       <c r="A1637" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B1637" t="inlineStr">
@@ -62616,20 +62616,20 @@
       </c>
       <c r="F1637" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1637" t="n">
-        <v>60.154354</v>
+        <v>298.48999</v>
       </c>
       <c r="H1637" t="n">
-        <v>109.4222</v>
+        <v>109.1132</v>
       </c>
     </row>
     <row r="1638">
       <c r="A1638" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B1638" t="inlineStr">
@@ -62654,20 +62654,20 @@
       </c>
       <c r="F1638" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1638" t="n">
-        <v>60.124958</v>
+        <v>297.799988</v>
       </c>
       <c r="H1638" t="n">
-        <v>109.3687</v>
+        <v>108.8609</v>
       </c>
     </row>
     <row r="1639">
       <c r="A1639" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B1639" t="inlineStr">
@@ -62692,20 +62692,20 @@
       </c>
       <c r="F1639" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1639" t="n">
-        <v>61.085079</v>
+        <v>301.049988</v>
       </c>
       <c r="H1639" t="n">
-        <v>111.1152</v>
+        <v>110.049</v>
       </c>
     </row>
     <row r="1640">
       <c r="A1640" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B1640" t="inlineStr">
@@ -62730,20 +62730,20 @@
       </c>
       <c r="F1640" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1640" t="n">
-        <v>60.56583</v>
+        <v>299.649994</v>
       </c>
       <c r="H1640" t="n">
-        <v>110.1707</v>
+        <v>109.5372</v>
       </c>
     </row>
     <row r="1641">
       <c r="A1641" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B1641" t="inlineStr">
@@ -62768,20 +62768,20 @@
       </c>
       <c r="F1641" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1641" t="n">
-        <v>60.075974</v>
+        <v>299.450012</v>
       </c>
       <c r="H1641" t="n">
-        <v>109.2796</v>
+        <v>109.4641</v>
       </c>
     </row>
     <row r="1642">
       <c r="A1642" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B1642" t="inlineStr">
@@ -62806,20 +62806,20 @@
       </c>
       <c r="F1642" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1642" t="n">
-        <v>59.91922</v>
+        <v>304.200012</v>
       </c>
       <c r="H1642" t="n">
-        <v>108.9945</v>
+        <v>111.2005</v>
       </c>
     </row>
     <row r="1643">
       <c r="A1643" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B1643" t="inlineStr">
@@ -62844,20 +62844,20 @@
       </c>
       <c r="F1643" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1643" t="n">
-        <v>59.948612</v>
+        <v>301.850006</v>
       </c>
       <c r="H1643" t="n">
-        <v>109.0479</v>
+        <v>110.3414</v>
       </c>
     </row>
     <row r="1644">
       <c r="A1644" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B1644" t="inlineStr">
@@ -62882,20 +62882,20 @@
       </c>
       <c r="F1644" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1644" t="n">
-        <v>59.625309</v>
+        <v>299.399994</v>
       </c>
       <c r="H1644" t="n">
-        <v>108.4598</v>
+        <v>109.4458</v>
       </c>
     </row>
     <row r="1645">
       <c r="A1645" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B1645" t="inlineStr">
@@ -62920,20 +62920,20 @@
       </c>
       <c r="F1645" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1645" t="n">
-        <v>59.478348</v>
+        <v>298.450012</v>
       </c>
       <c r="H1645" t="n">
-        <v>108.1925</v>
+        <v>109.0986</v>
       </c>
     </row>
     <row r="1646">
       <c r="A1646" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B1646" t="inlineStr">
@@ -62958,20 +62958,20 @@
       </c>
       <c r="F1646" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1646" t="n">
-        <v>59.253017</v>
+        <v>298.649994</v>
       </c>
       <c r="H1646" t="n">
-        <v>107.7826</v>
+        <v>109.1717</v>
       </c>
     </row>
     <row r="1647">
       <c r="A1647" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B1647" t="inlineStr">
@@ -62996,20 +62996,20 @@
       </c>
       <c r="F1647" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1647" t="n">
-        <v>58.949306</v>
+        <v>297.299988</v>
       </c>
       <c r="H1647" t="n">
-        <v>107.2302</v>
+        <v>108.6782</v>
       </c>
     </row>
     <row r="1648">
       <c r="A1648" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B1648" t="inlineStr">
@@ -63034,20 +63034,20 @@
       </c>
       <c r="F1648" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1648" t="n">
-        <v>59.811451</v>
+        <v>296.399994</v>
       </c>
       <c r="H1648" t="n">
-        <v>108.7984</v>
+        <v>108.3492</v>
       </c>
     </row>
     <row r="1649">
       <c r="A1649" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B1649" t="inlineStr">
@@ -63072,20 +63072,20 @@
       </c>
       <c r="F1649" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>59.125652</v>
+        <v>295.450012</v>
       </c>
       <c r="H1649" t="n">
-        <v>107.551</v>
+        <v>108.0019</v>
       </c>
     </row>
     <row r="1650">
       <c r="A1650" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B1650" t="inlineStr">
@@ -63110,20 +63110,20 @@
       </c>
       <c r="F1650" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>59.733078</v>
+        <v>293.75</v>
       </c>
       <c r="H1650" t="n">
-        <v>108.6559</v>
+        <v>107.3805</v>
       </c>
     </row>
     <row r="1651">
       <c r="A1651" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B1651" t="inlineStr">
@@ -63148,20 +63148,20 @@
       </c>
       <c r="F1651" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1651" t="n">
-        <v>61.055683</v>
+        <v>298.100006</v>
       </c>
       <c r="H1651" t="n">
-        <v>111.0617</v>
+        <v>108.9706</v>
       </c>
     </row>
     <row r="1652">
       <c r="A1652" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B1652" t="inlineStr">
@@ -63186,20 +63186,20 @@
       </c>
       <c r="F1652" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>60.330704</v>
+        <v>294.25</v>
       </c>
       <c r="H1652" t="n">
-        <v>109.743</v>
+        <v>107.5632</v>
       </c>
     </row>
     <row r="1653">
       <c r="A1653" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B1653" t="inlineStr">
@@ -63224,20 +63224,20 @@
       </c>
       <c r="F1653" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1653" t="n">
-        <v>60.056381</v>
+        <v>297.649994</v>
       </c>
       <c r="H1653" t="n">
-        <v>109.244</v>
+        <v>108.8061</v>
       </c>
     </row>
     <row r="1654">
       <c r="A1654" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B1654" t="inlineStr">
@@ -63262,20 +63262,20 @@
       </c>
       <c r="F1654" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>60.134758</v>
+        <v>304.350006</v>
       </c>
       <c r="H1654" t="n">
-        <v>109.3865</v>
+        <v>111.2553</v>
       </c>
     </row>
     <row r="1655">
       <c r="A1655" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B1655" t="inlineStr">
@@ -63300,20 +63300,20 @@
       </c>
       <c r="F1655" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1655" t="n">
-        <v>59.50774</v>
+        <v>300.899994</v>
       </c>
       <c r="H1655" t="n">
-        <v>108.246</v>
+        <v>109.9941</v>
       </c>
     </row>
     <row r="1656">
       <c r="A1656" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B1656" t="inlineStr">
@@ -63338,20 +63338,20 @@
       </c>
       <c r="F1656" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1656" t="n">
-        <v>60.026989</v>
+        <v>299.200012</v>
       </c>
       <c r="H1656" t="n">
-        <v>109.1905</v>
+        <v>109.3727</v>
       </c>
     </row>
     <row r="1657">
       <c r="A1657" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B1657" t="inlineStr">
@@ -63376,20 +63376,20 @@
       </c>
       <c r="F1657" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1657" t="n">
-        <v>60.663799</v>
+        <v>299.549988</v>
       </c>
       <c r="H1657" t="n">
-        <v>110.3489</v>
+        <v>109.5007</v>
       </c>
     </row>
     <row r="1658">
       <c r="A1658" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B1658" t="inlineStr">
@@ -63414,20 +63414,20 @@
       </c>
       <c r="F1658" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1658" t="n">
-        <v>59.576324</v>
+        <v>296.600006</v>
       </c>
       <c r="H1658" t="n">
-        <v>108.3707</v>
+        <v>108.4223</v>
       </c>
     </row>
     <row r="1659">
       <c r="A1659" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B1659" t="inlineStr">
@@ -63452,20 +63452,20 @@
       </c>
       <c r="F1659" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1659" t="n">
-        <v>60.026989</v>
+        <v>299.100006</v>
       </c>
       <c r="H1659" t="n">
-        <v>109.1905</v>
+        <v>109.3362</v>
       </c>
     </row>
     <row r="1660">
       <c r="A1660" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B1660" t="inlineStr">
@@ -63490,20 +63490,20 @@
       </c>
       <c r="F1660" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1660" t="n">
-        <v>60.066177</v>
+        <v>302.25</v>
       </c>
       <c r="H1660" t="n">
-        <v>109.2618</v>
+        <v>110.4876</v>
       </c>
     </row>
     <row r="1661">
       <c r="A1661" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B1661" t="inlineStr">
@@ -63528,20 +63528,20 @@
       </c>
       <c r="F1661" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1661" t="n">
-        <v>61.065487</v>
+        <v>296.5</v>
       </c>
       <c r="H1661" t="n">
-        <v>111.0796</v>
+        <v>108.3857</v>
       </c>
     </row>
     <row r="1662">
       <c r="A1662" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B1662" t="inlineStr">
@@ -63566,20 +63566,20 @@
       </c>
       <c r="F1662" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1662" t="n">
-        <v>61.065487</v>
+        <v>299.149994</v>
       </c>
       <c r="H1662" t="n">
-        <v>111.0796</v>
+        <v>109.3544</v>
       </c>
     </row>
     <row r="1663">
       <c r="A1663" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B1663" t="inlineStr">
@@ -63604,20 +63604,20 @@
       </c>
       <c r="F1663" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1663" t="n">
-        <v>61.604328</v>
+        <v>299.600006</v>
       </c>
       <c r="H1663" t="n">
-        <v>112.0597</v>
+        <v>109.5189</v>
       </c>
     </row>
     <row r="1664">
       <c r="A1664" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B1664" t="inlineStr">
@@ -63642,20 +63642,20 @@
       </c>
       <c r="F1664" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1664" t="n">
-        <v>62.642818</v>
+        <v>304.299988</v>
       </c>
       <c r="H1664" t="n">
-        <v>113.9488</v>
+        <v>111.237</v>
       </c>
     </row>
     <row r="1665">
       <c r="A1665" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B1665" t="inlineStr">
@@ -63680,20 +63680,20 @@
       </c>
       <c r="F1665" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1665" t="n">
-        <v>61.878647</v>
+        <v>303.950012</v>
       </c>
       <c r="H1665" t="n">
-        <v>112.5587</v>
+        <v>111.1091</v>
       </c>
     </row>
     <row r="1666">
       <c r="A1666" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B1666" t="inlineStr">
@@ -63718,20 +63718,20 @@
       </c>
       <c r="F1666" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>61.849255</v>
+        <v>306.649994</v>
       </c>
       <c r="H1666" t="n">
-        <v>112.5053</v>
+        <v>112.0961</v>
       </c>
     </row>
     <row r="1667">
       <c r="A1667" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B1667" t="inlineStr">
@@ -63756,20 +63756,20 @@
       </c>
       <c r="F1667" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1667" t="n">
-        <v>61.61412</v>
+        <v>311.899994</v>
       </c>
       <c r="H1667" t="n">
-        <v>112.0775</v>
+        <v>114.0152</v>
       </c>
     </row>
     <row r="1668">
       <c r="A1668" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B1668" t="inlineStr">
@@ -63794,20 +63794,20 @@
       </c>
       <c r="F1668" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1668" t="n">
-        <v>61.633717</v>
+        <v>308.149994</v>
       </c>
       <c r="H1668" t="n">
-        <v>112.1132</v>
+        <v>112.6444</v>
       </c>
     </row>
     <row r="1669">
       <c r="A1669" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B1669" t="inlineStr">
@@ -63832,20 +63832,20 @@
       </c>
       <c r="F1669" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1669" t="n">
-        <v>61.32021</v>
+        <v>308.350006</v>
       </c>
       <c r="H1669" t="n">
-        <v>111.5429</v>
+        <v>112.7175</v>
       </c>
     </row>
     <row r="1670">
       <c r="A1670" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B1670" t="inlineStr">
@@ -63870,20 +63870,20 @@
       </c>
       <c r="F1670" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1670" t="n">
-        <v>61.682705</v>
+        <v>306.850006</v>
       </c>
       <c r="H1670" t="n">
-        <v>112.2023</v>
+        <v>112.1692</v>
       </c>
     </row>
     <row r="1671">
       <c r="A1671" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B1671" t="inlineStr">
@@ -63908,20 +63908,20 @@
       </c>
       <c r="F1671" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1671" t="n">
-        <v>61.241829</v>
+        <v>307.149994</v>
       </c>
       <c r="H1671" t="n">
-        <v>111.4003</v>
+        <v>112.2788</v>
       </c>
     </row>
     <row r="1672">
       <c r="A1672" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B1672" t="inlineStr">
@@ -63946,20 +63946,20 @@
       </c>
       <c r="F1672" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1672" t="n">
-        <v>61.61412</v>
+        <v>305.149994</v>
       </c>
       <c r="H1672" t="n">
-        <v>112.0775</v>
+        <v>111.5477</v>
       </c>
     </row>
     <row r="1673">
       <c r="A1673" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B1673" t="inlineStr">
@@ -63984,20 +63984,20 @@
       </c>
       <c r="F1673" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1673" t="n">
-        <v>61.369194</v>
+        <v>307.200012</v>
       </c>
       <c r="H1673" t="n">
-        <v>111.632</v>
+        <v>112.2971</v>
       </c>
     </row>
     <row r="1674">
       <c r="A1674" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B1674" t="inlineStr">
@@ -64022,20 +64022,20 @@
       </c>
       <c r="F1674" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1674" t="n">
-        <v>61.281021</v>
+        <v>305</v>
       </c>
       <c r="H1674" t="n">
-        <v>111.4716</v>
+        <v>111.4929</v>
       </c>
     </row>
     <row r="1675">
       <c r="A1675" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B1675" t="inlineStr">
@@ -64060,20 +64060,20 @@
       </c>
       <c r="F1675" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1675" t="n">
-        <v>60.957718</v>
+        <v>306.899994</v>
       </c>
       <c r="H1675" t="n">
-        <v>110.8835</v>
+        <v>112.1875</v>
       </c>
     </row>
     <row r="1676">
       <c r="A1676" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B1676" t="inlineStr">
@@ -64098,20 +64098,20 @@
       </c>
       <c r="F1676" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>60.898933</v>
+        <v>305.549988</v>
       </c>
       <c r="H1676" t="n">
-        <v>110.7766</v>
+        <v>111.694</v>
       </c>
     </row>
     <row r="1677">
       <c r="A1677" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B1677" t="inlineStr">
@@ -64136,20 +64136,20 @@
       </c>
       <c r="F1677" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1677" t="n">
-        <v>61.290817</v>
+        <v>305.350006</v>
       </c>
       <c r="H1677" t="n">
-        <v>111.4894</v>
+        <v>111.6209</v>
       </c>
     </row>
     <row r="1678">
       <c r="A1678" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B1678" t="inlineStr">
@@ -64174,20 +64174,20 @@
       </c>
       <c r="F1678" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1678" t="n">
-        <v>62.437084</v>
+        <v>303.450012</v>
       </c>
       <c r="H1678" t="n">
-        <v>113.5745</v>
+        <v>110.9263</v>
       </c>
     </row>
     <row r="1679">
       <c r="A1679" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B1679" t="inlineStr">
@@ -64212,20 +64212,20 @@
       </c>
       <c r="F1679" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1679" t="n">
-        <v>62.489388</v>
+        <v>303.100006</v>
       </c>
       <c r="H1679" t="n">
-        <v>113.6697</v>
+        <v>110.7984</v>
       </c>
     </row>
     <row r="1680">
       <c r="A1680" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B1680" t="inlineStr">
@@ -64250,20 +64250,20 @@
       </c>
       <c r="F1680" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1680" t="n">
-        <v>62.657795</v>
+        <v>305.299988</v>
       </c>
       <c r="H1680" t="n">
-        <v>113.976</v>
+        <v>111.6026</v>
       </c>
     </row>
     <row r="1681">
       <c r="A1681" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B1681" t="inlineStr">
@@ -64288,20 +64288,20 @@
       </c>
       <c r="F1681" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1681" t="n">
-        <v>63.034237</v>
+        <v>311</v>
       </c>
       <c r="H1681" t="n">
-        <v>114.6608</v>
+        <v>113.6862</v>
       </c>
     </row>
     <row r="1682">
       <c r="A1682" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B1682" t="inlineStr">
@@ -64326,20 +64326,20 @@
       </c>
       <c r="F1682" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1682" t="n">
-        <v>62.766766</v>
+        <v>311.75</v>
       </c>
       <c r="H1682" t="n">
-        <v>114.1742</v>
+        <v>113.9604</v>
       </c>
     </row>
     <row r="1683">
       <c r="A1683" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B1683" t="inlineStr">
@@ -64364,20 +64364,20 @@
       </c>
       <c r="F1683" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1683" t="n">
-        <v>62.628075</v>
+        <v>312.600006</v>
       </c>
       <c r="H1683" t="n">
-        <v>113.9219</v>
+        <v>114.2711</v>
       </c>
     </row>
     <row r="1684">
       <c r="A1684" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B1684" t="inlineStr">
@@ -64402,20 +64402,20 @@
       </c>
       <c r="F1684" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1684" t="n">
-        <v>63.034237</v>
+        <v>314.049988</v>
       </c>
       <c r="H1684" t="n">
-        <v>114.6608</v>
+        <v>114.8011</v>
       </c>
     </row>
     <row r="1685">
       <c r="A1685" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B1685" t="inlineStr">
@@ -64440,20 +64440,20 @@
       </c>
       <c r="F1685" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1685" t="n">
-        <v>62.588451</v>
+        <v>312.850006</v>
       </c>
       <c r="H1685" t="n">
-        <v>113.8499</v>
+        <v>114.3625</v>
       </c>
     </row>
     <row r="1686">
       <c r="A1686" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B1686" t="inlineStr">
@@ -64478,20 +64478,20 @@
       </c>
       <c r="F1686" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1686" t="n">
-        <v>62.707325</v>
+        <v>312.100006</v>
       </c>
       <c r="H1686" t="n">
-        <v>114.0661</v>
+        <v>114.0883</v>
       </c>
     </row>
     <row r="1687">
       <c r="A1687" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B1687" t="inlineStr">
@@ -64516,20 +64516,20 @@
       </c>
       <c r="F1687" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1687" t="n">
-        <v>63.192738</v>
+        <v>314</v>
       </c>
       <c r="H1687" t="n">
-        <v>114.9491</v>
+        <v>114.7829</v>
       </c>
     </row>
     <row r="1688">
       <c r="A1688" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B1688" t="inlineStr">
@@ -64554,20 +64554,20 @@
       </c>
       <c r="F1688" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1688" t="n">
-        <v>62.737045</v>
+        <v>311.649994</v>
       </c>
       <c r="H1688" t="n">
-        <v>114.1202</v>
+        <v>113.9238</v>
       </c>
     </row>
     <row r="1689">
       <c r="A1689" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B1689" t="inlineStr">
@@ -64592,20 +64592,20 @@
       </c>
       <c r="F1689" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1689" t="n">
-        <v>62.766766</v>
+        <v>311.899994</v>
       </c>
       <c r="H1689" t="n">
-        <v>114.1742</v>
+        <v>114.0152</v>
       </c>
     </row>
     <row r="1690">
       <c r="A1690" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B1690" t="inlineStr">
@@ -64630,20 +64630,20 @@
       </c>
       <c r="F1690" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1690" t="n">
-        <v>63.341331</v>
+        <v>314.450012</v>
       </c>
       <c r="H1690" t="n">
-        <v>115.2194</v>
+        <v>114.9474</v>
       </c>
     </row>
     <row r="1691">
       <c r="A1691" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B1691" t="inlineStr">
@@ -64668,20 +64668,20 @@
       </c>
       <c r="F1691" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1691" t="n">
-        <v>63.143208</v>
+        <v>312.350006</v>
       </c>
       <c r="H1691" t="n">
-        <v>114.859</v>
+        <v>114.1797</v>
       </c>
     </row>
     <row r="1692">
       <c r="A1692" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B1692" t="inlineStr">
@@ -64706,20 +64706,20 @@
       </c>
       <c r="F1692" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1692" t="n">
-        <v>64.054596</v>
+        <v>312.149994</v>
       </c>
       <c r="H1692" t="n">
-        <v>116.5168</v>
+        <v>114.1066</v>
       </c>
     </row>
     <row r="1693">
       <c r="A1693" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B1693" t="inlineStr">
@@ -64744,20 +64744,20 @@
       </c>
       <c r="F1693" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1693" t="n">
-        <v>64.450844</v>
+        <v>315.25</v>
       </c>
       <c r="H1693" t="n">
-        <v>117.2376</v>
+        <v>115.2398</v>
       </c>
     </row>
     <row r="1694">
       <c r="A1694" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B1694" t="inlineStr">
@@ -64782,20 +64782,20 @@
       </c>
       <c r="F1694" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1694" t="n">
-        <v>64.252724</v>
+        <v>314.200012</v>
       </c>
       <c r="H1694" t="n">
-        <v>116.8772</v>
+        <v>114.856</v>
       </c>
     </row>
     <row r="1695">
       <c r="A1695" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B1695" t="inlineStr">
@@ -64820,20 +64820,20 @@
       </c>
       <c r="F1695" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1695" t="n">
-        <v>63.846558</v>
+        <v>318.600006</v>
       </c>
       <c r="H1695" t="n">
-        <v>116.1384</v>
+        <v>116.4644</v>
       </c>
     </row>
     <row r="1696">
       <c r="A1696" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B1696" t="inlineStr">
@@ -64858,20 +64858,20 @@
       </c>
       <c r="F1696" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1696" t="n">
-        <v>62.855923</v>
+        <v>320.700012</v>
       </c>
       <c r="H1696" t="n">
-        <v>114.3364</v>
+        <v>117.2321</v>
       </c>
     </row>
     <row r="1697">
       <c r="A1697" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B1697" t="inlineStr">
@@ -64896,20 +64896,20 @@
       </c>
       <c r="F1697" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1697" t="n">
-        <v>63.321518</v>
+        <v>319.700012</v>
       </c>
       <c r="H1697" t="n">
-        <v>115.1833</v>
+        <v>116.8665</v>
       </c>
     </row>
     <row r="1698">
       <c r="A1698" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B1698" t="inlineStr">
@@ -64934,20 +64934,20 @@
       </c>
       <c r="F1698" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1698" t="n">
-        <v>63.390869</v>
+        <v>317.75</v>
       </c>
       <c r="H1698" t="n">
-        <v>115.3095</v>
+        <v>116.1537</v>
       </c>
     </row>
     <row r="1699">
       <c r="A1699" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B1699" t="inlineStr">
@@ -64972,20 +64972,20 @@
       </c>
       <c r="F1699" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1699" t="n">
-        <v>63.390869</v>
+        <v>312.5</v>
       </c>
       <c r="H1699" t="n">
-        <v>115.3095</v>
+        <v>114.2345</v>
       </c>
     </row>
     <row r="1700">
       <c r="A1700" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B1700" t="inlineStr">
@@ -65010,20 +65010,20 @@
       </c>
       <c r="F1700" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1700" t="n">
-        <v>63.371056</v>
+        <v>315.25</v>
       </c>
       <c r="H1700" t="n">
-        <v>115.2734</v>
+        <v>115.2398</v>
       </c>
     </row>
     <row r="1701">
       <c r="A1701" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B1701" t="inlineStr">
@@ -65048,20 +65048,20 @@
       </c>
       <c r="F1701" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1701" t="n">
-        <v>63.509743</v>
+        <v>315.450012</v>
       </c>
       <c r="H1701" t="n">
-        <v>115.5257</v>
+        <v>115.3129</v>
       </c>
     </row>
     <row r="1702">
       <c r="A1702" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B1702" t="inlineStr">
@@ -65086,20 +65086,20 @@
       </c>
       <c r="F1702" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1702" t="n">
-        <v>63.598896</v>
+        <v>315.350006</v>
       </c>
       <c r="H1702" t="n">
-        <v>115.6879</v>
+        <v>115.2764</v>
       </c>
     </row>
     <row r="1703">
       <c r="A1703" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B1703" t="inlineStr">
@@ -65124,20 +65124,20 @@
       </c>
       <c r="F1703" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1703" t="n">
-        <v>63.361145</v>
+        <v>315.549988</v>
       </c>
       <c r="H1703" t="n">
-        <v>115.2554</v>
+        <v>115.3495</v>
       </c>
     </row>
     <row r="1704">
       <c r="A1704" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B1704" t="inlineStr">
@@ -65162,20 +65162,20 @@
       </c>
       <c r="F1704" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1704" t="n">
-        <v>63.143208</v>
+        <v>316.149994</v>
       </c>
       <c r="H1704" t="n">
-        <v>114.859</v>
+        <v>115.5688</v>
       </c>
     </row>
     <row r="1705">
       <c r="A1705" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B1705" t="inlineStr">
@@ -65200,20 +65200,20 @@
       </c>
       <c r="F1705" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1705" t="n">
-        <v>63.509743</v>
+        <v>316.5</v>
       </c>
       <c r="H1705" t="n">
-        <v>115.5257</v>
+        <v>115.6967</v>
       </c>
     </row>
     <row r="1706">
       <c r="A1706" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B1706" t="inlineStr">
@@ -65238,20 +65238,20 @@
       </c>
       <c r="F1706" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1706" t="n">
-        <v>63.846558</v>
+        <v>315.450012</v>
       </c>
       <c r="H1706" t="n">
-        <v>116.1384</v>
+        <v>115.3129</v>
       </c>
     </row>
     <row r="1707">
       <c r="A1707" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B1707" t="inlineStr">
@@ -65276,20 +65276,20 @@
       </c>
       <c r="F1707" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1707" t="n">
-        <v>63.10358</v>
+        <v>314.399994</v>
       </c>
       <c r="H1707" t="n">
-        <v>114.7869</v>
+        <v>114.9291</v>
       </c>
     </row>
     <row r="1708">
       <c r="A1708" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B1708" t="inlineStr">
@@ -65314,20 +65314,20 @@
       </c>
       <c r="F1708" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1708" t="n">
-        <v>63.62862</v>
+        <v>316.299988</v>
       </c>
       <c r="H1708" t="n">
-        <v>115.742</v>
+        <v>115.6236</v>
       </c>
     </row>
     <row r="1709">
       <c r="A1709" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B1709" t="inlineStr">
@@ -65352,20 +65352,20 @@
       </c>
       <c r="F1709" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1709" t="n">
-        <v>63.588997</v>
+        <v>318.049988</v>
       </c>
       <c r="H1709" t="n">
-        <v>115.6699</v>
+        <v>116.2633</v>
       </c>
     </row>
     <row r="1710">
       <c r="A1710" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B1710" t="inlineStr">
@@ -65390,20 +65390,20 @@
       </c>
       <c r="F1710" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1710" t="n">
-        <v>63.886181</v>
+        <v>314.450012</v>
       </c>
       <c r="H1710" t="n">
-        <v>116.2105</v>
+        <v>114.9474</v>
       </c>
     </row>
     <row r="1711">
       <c r="A1711" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B1711" t="inlineStr">
@@ -65428,20 +65428,20 @@
       </c>
       <c r="F1711" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1711" t="n">
-        <v>63.707867</v>
+        <v>317.149994</v>
       </c>
       <c r="H1711" t="n">
-        <v>115.8861</v>
+        <v>115.9343</v>
       </c>
     </row>
     <row r="1712">
       <c r="A1712" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B1712" t="inlineStr">
@@ -65466,20 +65466,20 @@
       </c>
       <c r="F1712" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1712" t="n">
-        <v>64.203186</v>
+        <v>317.25</v>
       </c>
       <c r="H1712" t="n">
-        <v>116.7871</v>
+        <v>115.9709</v>
       </c>
     </row>
     <row r="1713">
       <c r="A1713" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B1713" t="inlineStr">
@@ -65504,20 +65504,20 @@
       </c>
       <c r="F1713" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1713" t="n">
-        <v>64.12394</v>
+        <v>318.350006</v>
       </c>
       <c r="H1713" t="n">
-        <v>116.643</v>
+        <v>116.373</v>
       </c>
     </row>
     <row r="1714">
       <c r="A1714" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B1714" t="inlineStr">
@@ -65542,20 +65542,20 @@
       </c>
       <c r="F1714" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1714" t="n">
-        <v>64.440941</v>
+        <v>317.299988</v>
       </c>
       <c r="H1714" t="n">
-        <v>117.2196</v>
+        <v>115.9892</v>
       </c>
     </row>
     <row r="1715">
       <c r="A1715" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B1715" t="inlineStr">
@@ -65580,20 +65580,20 @@
       </c>
       <c r="F1715" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1715" t="n">
-        <v>64.95607</v>
+        <v>319.950012</v>
       </c>
       <c r="H1715" t="n">
-        <v>118.1566</v>
+        <v>116.9579</v>
       </c>
     </row>
     <row r="1716">
       <c r="A1716" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B1716" t="inlineStr">
@@ -65618,20 +65618,20 @@
       </c>
       <c r="F1716" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1716" t="n">
-        <v>64.93626399999999</v>
+        <v>319.399994</v>
       </c>
       <c r="H1716" t="n">
-        <v>118.1206</v>
+        <v>116.7568</v>
       </c>
     </row>
     <row r="1717">
       <c r="A1717" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B1717" t="inlineStr">
@@ -65656,20 +65656,20 @@
       </c>
       <c r="F1717" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1717" t="n">
-        <v>65.08485400000001</v>
+        <v>320.899994</v>
       </c>
       <c r="H1717" t="n">
-        <v>118.3909</v>
+        <v>117.3052</v>
       </c>
     </row>
     <row r="1718">
       <c r="A1718" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B1718" t="inlineStr">
@@ -65694,20 +65694,20 @@
       </c>
       <c r="F1718" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1718" t="n">
-        <v>65.302795</v>
+        <v>323.25</v>
       </c>
       <c r="H1718" t="n">
-        <v>118.7873</v>
+        <v>118.1642</v>
       </c>
     </row>
     <row r="1719">
       <c r="A1719" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B1719" t="inlineStr">
@@ -65732,20 +65732,20 @@
       </c>
       <c r="F1719" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1719" t="n">
-        <v>65.282982</v>
+        <v>323.299988</v>
       </c>
       <c r="H1719" t="n">
-        <v>118.7513</v>
+        <v>118.1825</v>
       </c>
     </row>
     <row r="1720">
       <c r="A1720" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B1720" t="inlineStr">
@@ -65770,20 +65770,20 @@
       </c>
       <c r="F1720" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1720" t="n">
-        <v>65.33251199999999</v>
+        <v>324.149994</v>
       </c>
       <c r="H1720" t="n">
-        <v>118.8414</v>
+        <v>118.4932</v>
       </c>
     </row>
     <row r="1721">
       <c r="A1721" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B1721" t="inlineStr">
@@ -65808,20 +65808,20 @@
       </c>
       <c r="F1721" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1721" t="n">
-        <v>65.29289199999999</v>
+        <v>325.200012</v>
       </c>
       <c r="H1721" t="n">
-        <v>118.7693</v>
+        <v>118.877</v>
       </c>
     </row>
     <row r="1722">
       <c r="A1722" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B1722" t="inlineStr">
@@ -65846,20 +65846,20 @@
       </c>
       <c r="F1722" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1722" t="n">
-        <v>65.312698</v>
+        <v>325.200012</v>
       </c>
       <c r="H1722" t="n">
-        <v>118.8053</v>
+        <v>118.877</v>
       </c>
     </row>
     <row r="1723">
       <c r="A1723" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B1723" t="inlineStr">
@@ -65884,20 +65884,20 @@
       </c>
       <c r="F1723" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1723" t="n">
-        <v>65.144295</v>
+        <v>325.149994</v>
       </c>
       <c r="H1723" t="n">
-        <v>118.499</v>
+        <v>118.8588</v>
       </c>
     </row>
     <row r="1724">
       <c r="A1724" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B1724" t="inlineStr">
@@ -65922,20 +65922,20 @@
       </c>
       <c r="F1724" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1724" t="n">
-        <v>65.015511</v>
+        <v>324.75</v>
       </c>
       <c r="H1724" t="n">
-        <v>118.2647</v>
+        <v>118.7125</v>
       </c>
     </row>
     <row r="1725">
       <c r="A1725" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B1725" t="inlineStr">
@@ -65960,20 +65960,20 @@
       </c>
       <c r="F1725" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1725" t="n">
-        <v>64.54991099999999</v>
+        <v>324.850006</v>
       </c>
       <c r="H1725" t="n">
-        <v>117.4178</v>
+        <v>118.7491</v>
       </c>
     </row>
     <row r="1726">
       <c r="A1726" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B1726" t="inlineStr">
@@ -65998,20 +65998,20 @@
       </c>
       <c r="F1726" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1726" t="n">
-        <v>64.500381</v>
+        <v>324.299988</v>
       </c>
       <c r="H1726" t="n">
-        <v>117.3277</v>
+        <v>118.548</v>
       </c>
     </row>
     <row r="1727">
       <c r="A1727" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B1727" t="inlineStr">
@@ -66036,20 +66036,20 @@
       </c>
       <c r="F1727" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1727" t="n">
-        <v>64.3815</v>
+        <v>323.399994</v>
       </c>
       <c r="H1727" t="n">
-        <v>117.1115</v>
+        <v>118.219</v>
       </c>
     </row>
     <row r="1728">
       <c r="A1728" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B1728" t="inlineStr">
@@ -66074,20 +66074,20 @@
       </c>
       <c r="F1728" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1728" t="n">
-        <v>64.86691999999999</v>
+        <v>320.950012</v>
       </c>
       <c r="H1728" t="n">
-        <v>117.9945</v>
+        <v>117.3234</v>
       </c>
     </row>
     <row r="1729">
       <c r="A1729" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B1729" t="inlineStr">
@@ -66112,20 +66112,20 @@
       </c>
       <c r="F1729" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1729" t="n">
-        <v>64.81738300000001</v>
+        <v>320.600006</v>
       </c>
       <c r="H1729" t="n">
-        <v>117.9043</v>
+        <v>117.1955</v>
       </c>
     </row>
     <row r="1730">
       <c r="A1730" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B1730" t="inlineStr">
@@ -66150,20 +66150,20 @@
       </c>
       <c r="F1730" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1730" t="n">
-        <v>65.06504099999999</v>
+        <v>320.399994</v>
       </c>
       <c r="H1730" t="n">
-        <v>118.3548</v>
+        <v>117.1224</v>
       </c>
     </row>
     <row r="1731">
       <c r="A1731" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B1731" t="inlineStr">
@@ -66188,20 +66188,20 @@
       </c>
       <c r="F1731" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1731" t="n">
-        <v>65.015511</v>
+        <v>322.299988</v>
       </c>
       <c r="H1731" t="n">
-        <v>118.2647</v>
+        <v>117.8169</v>
       </c>
     </row>
     <row r="1732">
       <c r="A1732" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B1732" t="inlineStr">
@@ -66226,20 +66226,20 @@
       </c>
       <c r="F1732" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1732" t="n">
-        <v>64.599442</v>
+        <v>322.25</v>
       </c>
       <c r="H1732" t="n">
-        <v>117.5079</v>
+        <v>117.7987</v>
       </c>
     </row>
     <row r="1733">
       <c r="A1733" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B1733" t="inlineStr">
@@ -66264,20 +66264,20 @@
       </c>
       <c r="F1733" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1733" t="n">
-        <v>64.896637</v>
+        <v>323.399994</v>
       </c>
       <c r="H1733" t="n">
-        <v>118.0485</v>
+        <v>118.219</v>
       </c>
     </row>
     <row r="1734">
       <c r="A1734" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B1734" t="inlineStr">
@@ -66302,20 +66302,20 @@
       </c>
       <c r="F1734" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1734" t="n">
-        <v>64.361694</v>
+        <v>323.5</v>
       </c>
       <c r="H1734" t="n">
-        <v>117.0754</v>
+        <v>118.2556</v>
       </c>
     </row>
     <row r="1735">
       <c r="A1735" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B1735" t="inlineStr">
@@ -66340,20 +66340,20 @@
       </c>
       <c r="F1735" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1735" t="n">
-        <v>64.17346999999999</v>
+        <v>321.200012</v>
       </c>
       <c r="H1735" t="n">
-        <v>116.7331</v>
+        <v>117.4148</v>
       </c>
     </row>
     <row r="1736">
       <c r="A1736" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B1736" t="inlineStr">
@@ -66378,20 +66378,20 @@
       </c>
       <c r="F1736" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1736" t="n">
-        <v>63.925808</v>
+        <v>322.850006</v>
       </c>
       <c r="H1736" t="n">
-        <v>116.2826</v>
+        <v>118.018</v>
       </c>
     </row>
     <row r="1737">
       <c r="A1737" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B1737" t="inlineStr">
@@ -66416,20 +66416,20 @@
       </c>
       <c r="F1737" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1737" t="n">
-        <v>64.37159699999999</v>
+        <v>320.399994</v>
       </c>
       <c r="H1737" t="n">
-        <v>117.0935</v>
+        <v>117.1224</v>
       </c>
     </row>
     <row r="1738">
       <c r="A1738" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B1738" t="inlineStr">
@@ -66454,20 +66454,20 @@
       </c>
       <c r="F1738" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1738" t="n">
-        <v>64.39141100000001</v>
+        <v>319.149994</v>
       </c>
       <c r="H1738" t="n">
-        <v>117.1295</v>
+        <v>116.6654</v>
       </c>
     </row>
     <row r="1739">
       <c r="A1739" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B1739" t="inlineStr">
@@ -66492,20 +66492,20 @@
       </c>
       <c r="F1739" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1739" t="n">
-        <v>64.361694</v>
+        <v>318.149994</v>
       </c>
       <c r="H1739" t="n">
-        <v>117.0754</v>
+        <v>116.2999</v>
       </c>
     </row>
     <row r="1740">
       <c r="A1740" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B1740" t="inlineStr">
@@ -66530,20 +66530,20 @@
       </c>
       <c r="F1740" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1740" t="n">
-        <v>64.322067</v>
+        <v>320.100006</v>
       </c>
       <c r="H1740" t="n">
-        <v>117.0034</v>
+        <v>117.0127</v>
       </c>
     </row>
     <row r="1741">
       <c r="A1741" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B1741" t="inlineStr">
@@ -66568,20 +66568,20 @@
       </c>
       <c r="F1741" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1741" t="n">
-        <v>63.410679</v>
+        <v>320.450012</v>
       </c>
       <c r="H1741" t="n">
-        <v>115.3455</v>
+        <v>117.1407</v>
       </c>
     </row>
     <row r="1742">
       <c r="A1742" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B1742" t="inlineStr">
@@ -66606,20 +66606,20 @@
       </c>
       <c r="F1742" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1742" t="n">
-        <v>62.89555</v>
+        <v>320.450012</v>
       </c>
       <c r="H1742" t="n">
-        <v>114.4085</v>
+        <v>117.1407</v>
       </c>
     </row>
     <row r="1743">
       <c r="A1743" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B1743" t="inlineStr">
@@ -66644,20 +66644,20 @@
       </c>
       <c r="F1743" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1743" t="n">
-        <v>63.262085</v>
+        <v>320.25</v>
       </c>
       <c r="H1743" t="n">
-        <v>115.0752</v>
+        <v>117.0676</v>
       </c>
     </row>
     <row r="1744">
       <c r="A1744" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B1744" t="inlineStr">
@@ -66682,20 +66682,20 @@
       </c>
       <c r="F1744" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1744" t="n">
-        <v>62.984707</v>
+        <v>315.600006</v>
       </c>
       <c r="H1744" t="n">
-        <v>114.5707</v>
+        <v>115.3677</v>
       </c>
     </row>
     <row r="1745">
       <c r="A1745" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B1745" t="inlineStr">
@@ -66720,20 +66720,20 @@
       </c>
       <c r="F1745" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1745" t="n">
-        <v>62.740002</v>
+        <v>313.549988</v>
       </c>
       <c r="H1745" t="n">
-        <v>114.1255</v>
+        <v>114.6184</v>
       </c>
     </row>
     <row r="1746">
       <c r="A1746" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B1746" t="inlineStr">
@@ -66758,20 +66758,20 @@
       </c>
       <c r="F1746" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1746" t="n">
-        <v>63.040001</v>
+        <v>315.299988</v>
       </c>
       <c r="H1746" t="n">
-        <v>114.6712</v>
+        <v>115.2581</v>
       </c>
     </row>
     <row r="1747">
       <c r="A1747" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B1747" t="inlineStr">
@@ -66796,20 +66796,20 @@
       </c>
       <c r="F1747" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1747" t="n">
-        <v>63.59</v>
+        <v>313.649994</v>
       </c>
       <c r="H1747" t="n">
-        <v>115.6717</v>
+        <v>114.6549</v>
       </c>
     </row>
     <row r="1748">
       <c r="A1748" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B1748" t="inlineStr">
@@ -66834,20 +66834,20 @@
       </c>
       <c r="F1748" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1748" t="n">
-        <v>62.84</v>
+        <v>312.649994</v>
       </c>
       <c r="H1748" t="n">
-        <v>114.3074</v>
+        <v>114.2894</v>
       </c>
     </row>
     <row r="1749">
       <c r="A1749" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B1749" t="inlineStr">
@@ -66872,20 +66872,20 @@
       </c>
       <c r="F1749" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1749" t="n">
-        <v>63.509998</v>
+        <v>314.149994</v>
       </c>
       <c r="H1749" t="n">
-        <v>115.5262</v>
+        <v>114.8377</v>
       </c>
     </row>
     <row r="1750">
       <c r="A1750" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B1750" t="inlineStr">
@@ -66910,20 +66910,20 @@
       </c>
       <c r="F1750" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1750" t="n">
-        <v>63.580002</v>
+        <v>317.149994</v>
       </c>
       <c r="H1750" t="n">
-        <v>115.6535</v>
+        <v>115.9343</v>
       </c>
     </row>
     <row r="1751">
       <c r="A1751" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B1751" t="inlineStr">
@@ -66948,20 +66948,20 @@
       </c>
       <c r="F1751" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1751" t="n">
-        <v>63.360001</v>
+        <v>313.399994</v>
       </c>
       <c r="H1751" t="n">
-        <v>115.2533</v>
+        <v>114.5635</v>
       </c>
     </row>
     <row r="1752">
       <c r="A1752" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B1752" t="inlineStr">
@@ -66986,20 +66986,20 @@
       </c>
       <c r="F1752" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1752" t="n">
-        <v>62.98</v>
+        <v>316.600006</v>
       </c>
       <c r="H1752" t="n">
-        <v>114.5621</v>
+        <v>115.7333</v>
       </c>
     </row>
     <row r="1753">
       <c r="A1753" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B1753" t="inlineStr">
@@ -67024,20 +67024,20 @@
       </c>
       <c r="F1753" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1753" t="n">
-        <v>63.23</v>
+        <v>316.950012</v>
       </c>
       <c r="H1753" t="n">
-        <v>115.0169</v>
+        <v>115.8612</v>
       </c>
     </row>
     <row r="1754">
       <c r="A1754" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B1754" t="inlineStr">
@@ -67062,20 +67062,20 @@
       </c>
       <c r="F1754" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1754" t="n">
-        <v>63.200001</v>
+        <v>315.850006</v>
       </c>
       <c r="H1754" t="n">
-        <v>114.9623</v>
+        <v>115.4591</v>
       </c>
     </row>
     <row r="1755">
       <c r="A1755" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B1755" t="inlineStr">
@@ -67100,20 +67100,20 @@
       </c>
       <c r="F1755" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1755" t="n">
-        <v>63.139999</v>
+        <v>314.049988</v>
       </c>
       <c r="H1755" t="n">
-        <v>114.8531</v>
+        <v>114.8011</v>
       </c>
     </row>
     <row r="1756">
       <c r="A1756" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B1756" t="inlineStr">
@@ -67138,20 +67138,20 @@
       </c>
       <c r="F1756" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1756" t="n">
-        <v>62.869999</v>
+        <v>315.149994</v>
       </c>
       <c r="H1756" t="n">
-        <v>114.362</v>
+        <v>115.2032</v>
       </c>
     </row>
     <row r="1757">
       <c r="A1757" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B1757" t="inlineStr">
@@ -67176,20 +67176,20 @@
       </c>
       <c r="F1757" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1757" t="n">
-        <v>62.07</v>
+        <v>315.100006</v>
       </c>
       <c r="H1757" t="n">
-        <v>112.9068</v>
+        <v>115.185</v>
       </c>
     </row>
     <row r="1758">
       <c r="A1758" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B1758" t="inlineStr">
@@ -67214,20 +67214,20 @@
       </c>
       <c r="F1758" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1758" t="n">
-        <v>62.549999</v>
+        <v>314.850006</v>
       </c>
       <c r="H1758" t="n">
-        <v>113.7799</v>
+        <v>115.0936</v>
       </c>
     </row>
     <row r="1759">
       <c r="A1759" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B1759" t="inlineStr">
@@ -67252,20 +67252,20 @@
       </c>
       <c r="F1759" t="inlineStr">
         <is>
-          <t>EXSA.DE</t>
+          <t>MEUD.PA</t>
         </is>
       </c>
       <c r="G1759" t="n">
-        <v>62.740002</v>
+        <v>313.399994</v>
       </c>
       <c r="H1759" t="n">
-        <v>114.1255</v>
+        <v>114.5635</v>
       </c>
     </row>
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67290,14 +67290,128 @@
       </c>
       <c r="F1760" t="inlineStr">
         <is>
+          <t>MEUD.PA</t>
+        </is>
+      </c>
+      <c r="G1760" t="n">
+        <v>309.350006</v>
+      </c>
+      <c r="H1760" t="n">
+        <v>113.0831</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="E1761" t="inlineStr">
+        <is>
           <t>EXSA.DE</t>
         </is>
       </c>
-      <c r="G1760" t="n">
-        <v>62.439999</v>
-      </c>
-      <c r="H1760" t="n">
-        <v>113.5798</v>
+      <c r="F1761" t="inlineStr">
+        <is>
+          <t>MEUD.PA</t>
+        </is>
+      </c>
+      <c r="G1761" t="n">
+        <v>311.649994</v>
+      </c>
+      <c r="H1761" t="n">
+        <v>113.9238</v>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="E1762" t="inlineStr">
+        <is>
+          <t>EXSA.DE</t>
+        </is>
+      </c>
+      <c r="F1762" t="inlineStr">
+        <is>
+          <t>MEUD.PA</t>
+        </is>
+      </c>
+      <c r="G1762" t="n">
+        <v>312.649994</v>
+      </c>
+      <c r="H1762" t="n">
+        <v>114.2894</v>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>LU0261952682</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>Fidelity Euro 50 Index Fund</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>Europa</t>
+        </is>
+      </c>
+      <c r="E1763" t="inlineStr">
+        <is>
+          <t>EXSA.DE</t>
+        </is>
+      </c>
+      <c r="F1763" t="inlineStr">
+        <is>
+          <t>MEUD.PA</t>
+        </is>
+      </c>
+      <c r="G1763" t="n">
+        <v>314.200012</v>
+      </c>
+      <c r="H1763" t="n">
+        <v>114.856</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>37.060001</v>
+        <v>36.84</v>
       </c>
       <c r="H253" t="n">
-        <v>123.7396</v>
+        <v>123.005</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.785</v>
+        <v>48.59</v>
       </c>
       <c r="H504" t="n">
-        <v>128.4661</v>
+        <v>127.9526</v>
       </c>
     </row>
     <row r="505">
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="G508" t="n">
-        <v>65.19961499999999</v>
+        <v>65.199623</v>
       </c>
       <c r="H508" t="n">
         <v>98.76090000000001</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H509" t="n">
         <v>98.6281</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.842361</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H513" t="n">
         <v>99.7345</v>
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407211</v>
       </c>
       <c r="H517" t="n">
         <v>100.5901</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.40720399999999</v>
+        <v>66.407211</v>
       </c>
       <c r="H520" t="n">
         <v>100.5901</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H522" t="n">
         <v>100.059</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H524" t="n">
         <v>100.413</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H531" t="n">
         <v>101.1506</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.416939</v>
+        <v>66.41693100000001</v>
       </c>
       <c r="H532" t="n">
         <v>100.6048</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>65.754715</v>
+        <v>65.754723</v>
       </c>
       <c r="H533" t="n">
         <v>99.60169999999999</v>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.027405</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H535" t="n">
-        <v>100.0148</v>
+        <v>100.0147</v>
       </c>
     </row>
     <row r="536">
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.124786</v>
+        <v>66.12479399999999</v>
       </c>
       <c r="H537" t="n">
         <v>100.1623</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.387726</v>
+        <v>66.387733</v>
       </c>
       <c r="H538" t="n">
         <v>100.5606</v>
@@ -21390,10 +21390,10 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.770599</v>
+        <v>67.77059199999999</v>
       </c>
       <c r="H552" t="n">
-        <v>102.6553</v>
+        <v>102.6552</v>
       </c>
     </row>
     <row r="553">
@@ -21656,10 +21656,10 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H559" t="n">
-        <v>103.4198</v>
+        <v>103.4199</v>
       </c>
     </row>
     <row r="560">
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H562" t="n">
         <v>104.8886</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H563" t="n">
         <v>105.6897</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H565" t="n">
         <v>105.571</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>70.185226</v>
+        <v>70.18523399999999</v>
       </c>
       <c r="H567" t="n">
         <v>106.3128</v>
@@ -22226,7 +22226,7 @@
         </is>
       </c>
       <c r="G574" t="n">
-        <v>70.371315</v>
+        <v>70.371323</v>
       </c>
       <c r="H574" t="n">
         <v>106.5947</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.410492</v>
+        <v>70.4105</v>
       </c>
       <c r="H578" t="n">
         <v>106.654</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H582" t="n">
         <v>108.5827</v>
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="G584" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H584" t="n">
         <v>110.3926</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H588" t="n">
         <v>111.4311</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H590" t="n">
         <v>111.8465</v>
@@ -22948,7 +22948,7 @@
         </is>
       </c>
       <c r="G593" t="n">
-        <v>73.867851</v>
+        <v>73.86784400000001</v>
       </c>
       <c r="H593" t="n">
         <v>111.891</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>74.52404799999999</v>
+        <v>74.524055</v>
       </c>
       <c r="H597" t="n">
         <v>112.885</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>75.003975</v>
+        <v>75.003967</v>
       </c>
       <c r="H602" t="n">
         <v>113.612</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H603" t="n">
         <v>111.1196</v>
@@ -23594,10 +23594,10 @@
         </is>
       </c>
       <c r="G610" t="n">
-        <v>72.55542</v>
+        <v>72.55542800000001</v>
       </c>
       <c r="H610" t="n">
-        <v>109.903</v>
+        <v>109.9031</v>
       </c>
     </row>
     <row r="611">
@@ -23708,7 +23708,7 @@
         </is>
       </c>
       <c r="G613" t="n">
-        <v>72.64357800000001</v>
+        <v>72.64357</v>
       </c>
       <c r="H613" t="n">
         <v>110.0366</v>
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.41999800000001</v>
+        <v>80.239998</v>
       </c>
       <c r="H755" t="n">
-        <v>121.8159</v>
+        <v>121.5432</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>131.279999</v>
+        <v>130.979996</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.3346</v>
+        <v>119.0619</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>131.279999</v>
+        <v>130.979996</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.3346</v>
+        <v>119.0619</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>131.279999</v>
+        <v>130.979996</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.3346</v>
+        <v>119.0619</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>55.159618</v>
+        <v>55.159622</v>
       </c>
       <c r="H1510" t="n">
         <v>99.5605</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.429089</v>
+        <v>54.429092</v>
       </c>
       <c r="H1511" t="n">
         <v>98.2419</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.74078</v>
+        <v>54.740784</v>
       </c>
       <c r="H1512" t="n">
         <v>98.8045</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.536232</v>
+        <v>54.536236</v>
       </c>
       <c r="H1513" t="n">
         <v>98.4353</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1516" t="n">
         <v>98.699</v>
@@ -58136,10 +58136,10 @@
         </is>
       </c>
       <c r="G1519" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1519" t="n">
-        <v>99.7715</v>
+        <v>99.7714</v>
       </c>
     </row>
     <row r="1520">
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.75378</v>
+        <v>55.753784</v>
       </c>
       <c r="H1521" t="n">
         <v>100.6329</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.588196</v>
+        <v>55.588188</v>
       </c>
       <c r="H1523" t="n">
         <v>100.334</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1525" t="n">
         <v>99.8066</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.325203</v>
+        <v>55.325207</v>
       </c>
       <c r="H1526" t="n">
         <v>99.85939999999999</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.169357</v>
+        <v>55.169353</v>
       </c>
       <c r="H1527" t="n">
         <v>99.57810000000001</v>
@@ -58478,10 +58478,10 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>55.276505</v>
+        <v>55.276501</v>
       </c>
       <c r="H1528" t="n">
-        <v>99.7715</v>
+        <v>99.7714</v>
       </c>
     </row>
     <row r="1529">
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>56.104431</v>
+        <v>56.104427</v>
       </c>
       <c r="H1532" t="n">
         <v>101.2658</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1534" t="n">
         <v>101.3361</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.305721</v>
+        <v>55.305717</v>
       </c>
       <c r="H1536" t="n">
         <v>99.8242</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1537" t="n">
         <v>98.08369999999999</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>54.292728</v>
+        <v>54.292725</v>
       </c>
       <c r="H1538" t="n">
         <v>97.9958</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>54.48753</v>
+        <v>54.487534</v>
       </c>
       <c r="H1539" t="n">
         <v>98.34739999999999</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.35117</v>
+        <v>54.351166</v>
       </c>
       <c r="H1540" t="n">
         <v>98.10129999999999</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.41935</v>
+        <v>54.419353</v>
       </c>
       <c r="H1541" t="n">
         <v>98.2243</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.568707</v>
+        <v>55.568714</v>
       </c>
       <c r="H1544" t="n">
         <v>100.2989</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.75378</v>
+        <v>55.753784</v>
       </c>
       <c r="H1545" t="n">
         <v>100.6329</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.568707</v>
+        <v>55.568714</v>
       </c>
       <c r="H1546" t="n">
         <v>100.2989</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.958328</v>
+        <v>55.958324</v>
       </c>
       <c r="H1549" t="n">
         <v>101.0021</v>
@@ -59314,10 +59314,10 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.987549</v>
+        <v>55.987545</v>
       </c>
       <c r="H1550" t="n">
-        <v>101.0549</v>
+        <v>101.0548</v>
       </c>
     </row>
     <row r="1551">
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1551" t="n">
         <v>100.8966</v>
@@ -59390,7 +59390,7 @@
         </is>
       </c>
       <c r="G1552" t="n">
-        <v>55.841446</v>
+        <v>55.841442</v>
       </c>
       <c r="H1552" t="n">
         <v>100.7911</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.851181</v>
+        <v>55.851177</v>
       </c>
       <c r="H1555" t="n">
         <v>100.8087</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>56.294876</v>
+        <v>56.294872</v>
       </c>
       <c r="H1556" t="n">
         <v>101.6096</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.991901</v>
+        <v>55.991898</v>
       </c>
       <c r="H1558" t="n">
         <v>101.0627</v>
@@ -59808,7 +59808,7 @@
         </is>
       </c>
       <c r="G1563" t="n">
-        <v>56.969246</v>
+        <v>56.969242</v>
       </c>
       <c r="H1563" t="n">
         <v>102.8268</v>
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>58.210464</v>
+        <v>58.210468</v>
       </c>
       <c r="H1566" t="n">
         <v>105.0671</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1570" t="n">
         <v>106.5489</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>59.129166</v>
+        <v>59.129162</v>
       </c>
       <c r="H1571" t="n">
         <v>106.7253</v>
@@ -60226,7 +60226,7 @@
         </is>
       </c>
       <c r="G1574" t="n">
-        <v>59.49078</v>
+        <v>59.490784</v>
       </c>
       <c r="H1574" t="n">
         <v>107.378</v>
@@ -60264,7 +60264,7 @@
         </is>
       </c>
       <c r="G1575" t="n">
-        <v>59.500557</v>
+        <v>59.500553</v>
       </c>
       <c r="H1575" t="n">
         <v>107.3957</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1577" t="n">
         <v>105.1906</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>58.259331</v>
+        <v>58.259335</v>
       </c>
       <c r="H1578" t="n">
         <v>105.1553</v>
@@ -60644,7 +60644,7 @@
         </is>
       </c>
       <c r="G1585" t="n">
-        <v>59.168259</v>
+        <v>59.168262</v>
       </c>
       <c r="H1585" t="n">
         <v>106.7959</v>
@@ -60682,7 +60682,7 @@
         </is>
       </c>
       <c r="G1586" t="n">
-        <v>59.793755</v>
+        <v>59.793758</v>
       </c>
       <c r="H1586" t="n">
         <v>107.9249</v>
@@ -60758,7 +60758,7 @@
         </is>
       </c>
       <c r="G1588" t="n">
-        <v>59.803528</v>
+        <v>59.803532</v>
       </c>
       <c r="H1588" t="n">
         <v>107.9425</v>
@@ -60796,7 +60796,7 @@
         </is>
       </c>
       <c r="G1589" t="n">
-        <v>59.246449</v>
+        <v>59.246445</v>
       </c>
       <c r="H1589" t="n">
         <v>106.937</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>59.744896</v>
+        <v>59.744892</v>
       </c>
       <c r="H1590" t="n">
         <v>107.8367</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>60.116276</v>
+        <v>60.116283</v>
       </c>
       <c r="H1592" t="n">
         <v>108.507</v>
@@ -60948,7 +60948,7 @@
         </is>
       </c>
       <c r="G1593" t="n">
-        <v>60.204239</v>
+        <v>60.204243</v>
       </c>
       <c r="H1593" t="n">
         <v>108.6658</v>
@@ -61062,7 +61062,7 @@
         </is>
       </c>
       <c r="G1596" t="n">
-        <v>59.940361</v>
+        <v>59.940365</v>
       </c>
       <c r="H1596" t="n">
         <v>108.1895</v>
@@ -61100,7 +61100,7 @@
         </is>
       </c>
       <c r="G1597" t="n">
-        <v>60.262882</v>
+        <v>60.262886</v>
       </c>
       <c r="H1597" t="n">
         <v>108.7716</v>
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>60.956795</v>
+        <v>60.956791</v>
       </c>
       <c r="H1598" t="n">
         <v>110.0241</v>
@@ -61176,10 +61176,10 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>60.653816</v>
+        <v>60.65382</v>
       </c>
       <c r="H1599" t="n">
-        <v>109.4772</v>
+        <v>109.4773</v>
       </c>
     </row>
     <row r="1600">
@@ -61290,10 +61290,10 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1602" t="n">
-        <v>110.13</v>
+        <v>110.1299</v>
       </c>
     </row>
     <row r="1603">
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>61.474785</v>
+        <v>61.474789</v>
       </c>
       <c r="H1603" t="n">
         <v>110.9591</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>61.445465</v>
+        <v>61.445469</v>
       </c>
       <c r="H1605" t="n">
         <v>110.9061</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1608" t="n">
         <v>107.2016</v>
@@ -61556,10 +61556,10 @@
         </is>
       </c>
       <c r="G1609" t="n">
-        <v>58.581852</v>
+        <v>58.581856</v>
       </c>
       <c r="H1609" t="n">
-        <v>105.7374</v>
+        <v>105.7375</v>
       </c>
     </row>
     <row r="1610">
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>58.787102</v>
+        <v>58.787098</v>
       </c>
       <c r="H1612" t="n">
         <v>106.1079</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1613" t="n">
         <v>105.5081</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1614" t="n">
         <v>104.8907</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.209999</v>
+        <v>61.93</v>
       </c>
       <c r="H1760" t="n">
-        <v>112.2861</v>
+        <v>111.7807</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="G515" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H515" t="n">
         <v>99.88200000000001</v>
@@ -20022,10 +20022,10 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>66.06635300000001</v>
+        <v>66.066345</v>
       </c>
       <c r="H516" t="n">
-        <v>100.0738</v>
+        <v>100.0737</v>
       </c>
     </row>
     <row r="517">
@@ -20060,7 +20060,7 @@
         </is>
       </c>
       <c r="G517" t="n">
-        <v>66.407211</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H517" t="n">
         <v>100.5901</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.407211</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H520" t="n">
         <v>100.5901</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.056618</v>
+        <v>66.05661000000001</v>
       </c>
       <c r="H522" t="n">
         <v>100.059</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.29033699999999</v>
+        <v>66.290344</v>
       </c>
       <c r="H524" t="n">
         <v>100.413</v>
@@ -20364,10 +20364,10 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.98844099999999</v>
+        <v>65.988457</v>
       </c>
       <c r="H525" t="n">
-        <v>99.95569999999999</v>
+        <v>99.9558</v>
       </c>
     </row>
     <row r="526">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.942818</v>
+        <v>66.94283299999999</v>
       </c>
       <c r="H528" t="n">
         <v>101.4014</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H529" t="n">
         <v>102.3455</v>
@@ -20630,7 +20630,7 @@
         </is>
       </c>
       <c r="G532" t="n">
-        <v>66.41693100000001</v>
+        <v>66.416939</v>
       </c>
       <c r="H532" t="n">
         <v>100.6048</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>65.754723</v>
+        <v>65.754715</v>
       </c>
       <c r="H533" t="n">
         <v>99.60169999999999</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>65.715767</v>
+        <v>65.71577499999999</v>
       </c>
       <c r="H534" t="n">
         <v>99.5427</v>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.02739699999999</v>
+        <v>66.027412</v>
       </c>
       <c r="H535" t="n">
-        <v>100.0147</v>
+        <v>100.0148</v>
       </c>
     </row>
     <row r="536">
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.12479399999999</v>
+        <v>66.124779</v>
       </c>
       <c r="H537" t="n">
         <v>100.1623</v>
@@ -20858,7 +20858,7 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>66.387733</v>
+        <v>66.387726</v>
       </c>
       <c r="H538" t="n">
         <v>100.5606</v>
@@ -20896,7 +20896,7 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H539" t="n">
         <v>101.4899</v>
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.874657</v>
+        <v>66.87464900000001</v>
       </c>
       <c r="H543" t="n">
         <v>101.2981</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.942818</v>
+        <v>66.94283299999999</v>
       </c>
       <c r="H544" t="n">
         <v>101.4014</v>
@@ -21162,7 +21162,7 @@
         </is>
       </c>
       <c r="G546" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H546" t="n">
         <v>102.2717</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.283661</v>
+        <v>67.283669</v>
       </c>
       <c r="H547" t="n">
         <v>101.9177</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.22524300000001</v>
+        <v>67.22525</v>
       </c>
       <c r="H549" t="n">
         <v>101.8292</v>
@@ -21390,10 +21390,10 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.77059199999999</v>
+        <v>67.770599</v>
       </c>
       <c r="H552" t="n">
-        <v>102.6552</v>
+        <v>102.6553</v>
       </c>
     </row>
     <row r="553">
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.166809</v>
+        <v>67.16681699999999</v>
       </c>
       <c r="H553" t="n">
         <v>101.7407</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.893387</v>
+        <v>67.893379</v>
       </c>
       <c r="H556" t="n">
         <v>102.8412</v>
@@ -21656,10 +21656,10 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>68.275368</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H559" t="n">
-        <v>103.4199</v>
+        <v>103.4198</v>
       </c>
     </row>
     <row r="560">
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>68.30474100000001</v>
+        <v>68.304733</v>
       </c>
       <c r="H560" t="n">
         <v>103.4643</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>68.520218</v>
+        <v>68.52021000000001</v>
       </c>
       <c r="H561" t="n">
         <v>103.7907</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>69.24498</v>
+        <v>69.24498699999999</v>
       </c>
       <c r="H562" t="n">
         <v>104.8886</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H565" t="n">
         <v>105.571</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>71.340942</v>
+        <v>71.340935</v>
       </c>
       <c r="H570" t="n">
         <v>108.0634</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>71.29196899999999</v>
+        <v>71.291977</v>
       </c>
       <c r="H571" t="n">
         <v>107.9892</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H573" t="n">
         <v>106.1348</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>70.870819</v>
+        <v>70.87082700000001</v>
       </c>
       <c r="H575" t="n">
         <v>107.3513</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.51823400000001</v>
+        <v>70.518227</v>
       </c>
       <c r="H576" t="n">
         <v>106.8172</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.4105</v>
+        <v>70.410484</v>
       </c>
       <c r="H578" t="n">
         <v>106.654</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.684731</v>
+        <v>70.68472300000001</v>
       </c>
       <c r="H580" t="n">
         <v>107.0694</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>71.683746</v>
+        <v>71.683739</v>
       </c>
       <c r="H582" t="n">
         <v>108.5827</v>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>72.34974699999999</v>
+        <v>72.349754</v>
       </c>
       <c r="H585" t="n">
         <v>109.5915</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>73.309578</v>
+        <v>73.30956999999999</v>
       </c>
       <c r="H587" t="n">
         <v>111.0454</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>73.564232</v>
+        <v>73.564224</v>
       </c>
       <c r="H588" t="n">
         <v>111.4311</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>74.12249799999999</v>
+        <v>74.12249</v>
       </c>
       <c r="H589" t="n">
         <v>112.2768</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>73.83847</v>
+        <v>73.838463</v>
       </c>
       <c r="H590" t="n">
         <v>111.8465</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H594" t="n">
         <v>112.8405</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>74.494675</v>
+        <v>74.49466700000001</v>
       </c>
       <c r="H595" t="n">
         <v>112.8405</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>74.524055</v>
+        <v>74.524063</v>
       </c>
       <c r="H597" t="n">
         <v>112.885</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>74.729736</v>
+        <v>74.729744</v>
       </c>
       <c r="H598" t="n">
         <v>113.1966</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>75.14109000000001</v>
+        <v>75.141098</v>
       </c>
       <c r="H599" t="n">
         <v>113.8197</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>75.27821400000001</v>
+        <v>75.278206</v>
       </c>
       <c r="H600" t="n">
         <v>114.0274</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>75.003967</v>
+        <v>75.00398300000001</v>
       </c>
       <c r="H602" t="n">
         <v>113.612</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>73.358543</v>
+        <v>73.35855100000001</v>
       </c>
       <c r="H603" t="n">
         <v>111.1196</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>72.721931</v>
+        <v>72.721924</v>
       </c>
       <c r="H608" t="n">
         <v>110.1553</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>72.43789700000001</v>
+        <v>72.437889</v>
       </c>
       <c r="H609" t="n">
         <v>109.725</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>71.514076</v>
+        <v>71.514084</v>
       </c>
       <c r="H614" t="n">
         <v>108.3257</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>70.854553</v>
+        <v>70.854561</v>
       </c>
       <c r="H615" t="n">
         <v>107.3267</v>
@@ -23860,10 +23860,10 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H617" t="n">
-        <v>108.1616</v>
+        <v>108.1617</v>
       </c>
     </row>
     <row r="618">
@@ -23974,10 +23974,10 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>71.40579200000001</v>
+        <v>71.4058</v>
       </c>
       <c r="H620" t="n">
-        <v>108.1616</v>
+        <v>108.1617</v>
       </c>
     </row>
     <row r="621">
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>72.68547100000001</v>
+        <v>72.685463</v>
       </c>
       <c r="H623" t="n">
         <v>110.1</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>72.449226</v>
+        <v>72.449219</v>
       </c>
       <c r="H625" t="n">
         <v>109.7422</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>73.945457</v>
+        <v>73.945465</v>
       </c>
       <c r="H627" t="n">
         <v>112.0086</v>
@@ -24278,7 +24278,7 @@
         </is>
       </c>
       <c r="G628" t="n">
-        <v>73.778114</v>
+        <v>73.77810700000001</v>
       </c>
       <c r="H628" t="n">
         <v>111.7551</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H630" t="n">
         <v>111.8297</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>73.807648</v>
+        <v>73.807655</v>
       </c>
       <c r="H632" t="n">
         <v>111.7999</v>
@@ -24582,7 +24582,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>73.82733899999999</v>
+        <v>73.827332</v>
       </c>
       <c r="H636" t="n">
         <v>111.8297</v>
@@ -24696,10 +24696,10 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.532021</v>
+        <v>73.532028</v>
       </c>
       <c r="H639" t="n">
-        <v>111.3823</v>
+        <v>111.3824</v>
       </c>
     </row>
     <row r="640">
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.787964</v>
+        <v>73.78795599999999</v>
       </c>
       <c r="H640" t="n">
         <v>111.77</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>74.427803</v>
+        <v>74.427795</v>
       </c>
       <c r="H642" t="n">
         <v>112.7392</v>
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G645" t="n">
-        <v>75.13653600000001</v>
+        <v>75.136543</v>
       </c>
       <c r="H645" t="n">
         <v>113.8128</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H646" t="n">
         <v>113.0523</v>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>74.634514</v>
+        <v>74.634506</v>
       </c>
       <c r="H648" t="n">
         <v>113.0523</v>
@@ -25228,7 +25228,7 @@
         </is>
       </c>
       <c r="G653" t="n">
-        <v>75.09716</v>
+        <v>75.097168</v>
       </c>
       <c r="H653" t="n">
         <v>113.7531</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>77.095428</v>
+        <v>77.095421</v>
       </c>
       <c r="H658" t="n">
         <v>116.78</v>
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>76.573708</v>
+        <v>76.57371500000001</v>
       </c>
       <c r="H660" t="n">
         <v>115.9897</v>
@@ -25570,7 +25570,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>76.27840399999999</v>
+        <v>76.278397</v>
       </c>
       <c r="H662" t="n">
         <v>115.5424</v>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="G663" t="n">
-        <v>76.17997</v>
+        <v>76.179962</v>
       </c>
       <c r="H663" t="n">
         <v>115.3933</v>
@@ -25798,10 +25798,10 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>76.59339900000001</v>
+        <v>76.593391</v>
       </c>
       <c r="H668" t="n">
-        <v>116.0196</v>
+        <v>116.0195</v>
       </c>
     </row>
     <row r="669">
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.14059399999999</v>
+        <v>76.140587</v>
       </c>
       <c r="H669" t="n">
         <v>115.3337</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>78.355408</v>
+        <v>78.35541499999999</v>
       </c>
       <c r="H675" t="n">
         <v>118.6886</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.818703</v>
+        <v>54.818699</v>
       </c>
       <c r="H1514" t="n">
         <v>98.9451</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.753784</v>
+        <v>55.753777</v>
       </c>
       <c r="H1521" t="n">
         <v>100.6329</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1522" t="n">
         <v>100.4219</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.588188</v>
+        <v>55.588196</v>
       </c>
       <c r="H1523" t="n">
         <v>100.334</v>
@@ -58326,10 +58326,10 @@
         </is>
       </c>
       <c r="G1524" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1524" t="n">
-        <v>100.2286</v>
+        <v>100.2285</v>
       </c>
     </row>
     <row r="1525">
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.295986</v>
+        <v>55.295982</v>
       </c>
       <c r="H1525" t="n">
         <v>99.8066</v>
@@ -58402,10 +58402,10 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.325207</v>
+        <v>55.325199</v>
       </c>
       <c r="H1526" t="n">
-        <v>99.85939999999999</v>
+        <v>99.8593</v>
       </c>
     </row>
     <row r="1527">
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1532" t="n">
         <v>101.2658</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.607674</v>
+        <v>55.60767</v>
       </c>
       <c r="H1535" t="n">
         <v>100.3692</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.305717</v>
+        <v>55.305725</v>
       </c>
       <c r="H1536" t="n">
         <v>99.8242</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>54.341427</v>
+        <v>54.341431</v>
       </c>
       <c r="H1537" t="n">
         <v>98.08369999999999</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.351166</v>
+        <v>54.35117</v>
       </c>
       <c r="H1540" t="n">
         <v>98.10129999999999</v>
@@ -59048,10 +59048,10 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1543" t="n">
-        <v>100.2286</v>
+        <v>100.2285</v>
       </c>
     </row>
     <row r="1544">
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.568714</v>
+        <v>55.568707</v>
       </c>
       <c r="H1544" t="n">
         <v>100.2989</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.753784</v>
+        <v>55.753777</v>
       </c>
       <c r="H1545" t="n">
         <v>100.6329</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.568714</v>
+        <v>55.568707</v>
       </c>
       <c r="H1546" t="n">
         <v>100.2989</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.636894</v>
+        <v>55.63689</v>
       </c>
       <c r="H1547" t="n">
         <v>100.4219</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.958324</v>
+        <v>55.958328</v>
       </c>
       <c r="H1549" t="n">
         <v>101.0021</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.987545</v>
+        <v>55.987541</v>
       </c>
       <c r="H1550" t="n">
         <v>101.0548</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1551" t="n">
         <v>100.8966</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>55.851177</v>
+        <v>55.851181</v>
       </c>
       <c r="H1555" t="n">
         <v>100.8087</v>
@@ -59542,7 +59542,7 @@
         </is>
       </c>
       <c r="G1556" t="n">
-        <v>56.294872</v>
+        <v>56.294876</v>
       </c>
       <c r="H1556" t="n">
         <v>101.6096</v>
@@ -59618,7 +59618,7 @@
         </is>
       </c>
       <c r="G1558" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1558" t="n">
         <v>101.0627</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1560" t="n">
         <v>102.4916</v>
@@ -59732,10 +59732,10 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.676041</v>
+        <v>56.676037</v>
       </c>
       <c r="H1561" t="n">
-        <v>102.2976</v>
+        <v>102.2975</v>
       </c>
     </row>
     <row r="1562">
@@ -59922,7 +59922,7 @@
         </is>
       </c>
       <c r="G1566" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1566" t="n">
         <v>105.0671</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>59.031437</v>
+        <v>59.031433</v>
       </c>
       <c r="H1570" t="n">
         <v>106.5489</v>
@@ -60112,7 +60112,7 @@
         </is>
       </c>
       <c r="G1571" t="n">
-        <v>59.129162</v>
+        <v>59.129166</v>
       </c>
       <c r="H1571" t="n">
         <v>106.7253</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1573" t="n">
         <v>106.7606</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1577" t="n">
         <v>105.1906</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1582" t="n">
         <v>107.0429</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>60.155373</v>
+        <v>60.155376</v>
       </c>
       <c r="H1591" t="n">
         <v>108.5776</v>
@@ -60910,7 +60910,7 @@
         </is>
       </c>
       <c r="G1592" t="n">
-        <v>60.116283</v>
+        <v>60.11628</v>
       </c>
       <c r="H1592" t="n">
         <v>108.507</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>61.201126</v>
+        <v>61.20113</v>
       </c>
       <c r="H1600" t="n">
         <v>110.4651</v>
@@ -61290,10 +61290,10 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>61.015434</v>
+        <v>61.015438</v>
       </c>
       <c r="H1602" t="n">
-        <v>110.1299</v>
+        <v>110.13</v>
       </c>
     </row>
     <row r="1603">
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>58.640495</v>
+        <v>58.640491</v>
       </c>
       <c r="H1607" t="n">
         <v>105.8433</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>59.393051</v>
+        <v>59.393047</v>
       </c>
       <c r="H1608" t="n">
         <v>107.2016</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>58.4548</v>
+        <v>58.454803</v>
       </c>
       <c r="H1613" t="n">
         <v>105.5081</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>58.112728</v>
+        <v>58.112732</v>
       </c>
       <c r="H1614" t="n">
         <v>104.8907</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>57.790211</v>
+        <v>57.790207</v>
       </c>
       <c r="H1615" t="n">
         <v>104.3086</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.86850699999999</v>
+        <v>64.868515</v>
       </c>
       <c r="H507" t="n">
         <v>98.2593</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>65.111977</v>
+        <v>65.111969</v>
       </c>
       <c r="H509" t="n">
         <v>98.6281</v>
@@ -19870,7 +19870,7 @@
         </is>
       </c>
       <c r="G512" t="n">
-        <v>65.121719</v>
+        <v>65.121712</v>
       </c>
       <c r="H512" t="n">
         <v>98.6429</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.84236900000001</v>
+        <v>65.842361</v>
       </c>
       <c r="H513" t="n">
         <v>99.7345</v>
@@ -20022,10 +20022,10 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>66.066345</v>
+        <v>66.06635300000001</v>
       </c>
       <c r="H516" t="n">
-        <v>100.0737</v>
+        <v>100.0738</v>
       </c>
     </row>
     <row r="517">
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H519" t="n">
         <v>100.295</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H522" t="n">
         <v>100.059</v>
@@ -20364,10 +20364,10 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.988457</v>
+        <v>65.98844099999999</v>
       </c>
       <c r="H525" t="n">
-        <v>99.9558</v>
+        <v>99.95569999999999</v>
       </c>
     </row>
     <row r="526">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>66.94283299999999</v>
+        <v>66.942825</v>
       </c>
       <c r="H528" t="n">
         <v>101.4014</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H530" t="n">
         <v>101.5784</v>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="G531" t="n">
-        <v>66.77726699999999</v>
+        <v>66.777275</v>
       </c>
       <c r="H531" t="n">
         <v>101.1506</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>65.71577499999999</v>
+        <v>65.715767</v>
       </c>
       <c r="H534" t="n">
         <v>99.5427</v>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>66.027412</v>
+        <v>66.02739699999999</v>
       </c>
       <c r="H535" t="n">
-        <v>100.0148</v>
+        <v>100.0147</v>
       </c>
     </row>
     <row r="536">
@@ -20820,7 +20820,7 @@
         </is>
       </c>
       <c r="G537" t="n">
-        <v>66.124779</v>
+        <v>66.124786</v>
       </c>
       <c r="H537" t="n">
         <v>100.1623</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H542" t="n">
         <v>101.5784</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>66.94283299999999</v>
+        <v>66.942825</v>
       </c>
       <c r="H544" t="n">
         <v>101.4014</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.283669</v>
+        <v>67.283676</v>
       </c>
       <c r="H547" t="n">
         <v>101.9177</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.478447</v>
+        <v>67.47843899999999</v>
       </c>
       <c r="H550" t="n">
         <v>102.2127</v>
@@ -21352,10 +21352,10 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H551" t="n">
-        <v>102.0799</v>
+        <v>102.08</v>
       </c>
     </row>
     <row r="552">
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.234978</v>
+        <v>67.23497</v>
       </c>
       <c r="H554" t="n">
         <v>101.8439</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.893379</v>
+        <v>67.893387</v>
       </c>
       <c r="H556" t="n">
         <v>102.8412</v>
@@ -21656,10 +21656,10 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275368</v>
       </c>
       <c r="H559" t="n">
-        <v>103.4198</v>
+        <v>103.4199</v>
       </c>
     </row>
     <row r="560">
@@ -21694,7 +21694,7 @@
         </is>
       </c>
       <c r="G560" t="n">
-        <v>68.304733</v>
+        <v>68.30474100000001</v>
       </c>
       <c r="H560" t="n">
         <v>103.4643</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="G561" t="n">
-        <v>68.52021000000001</v>
+        <v>68.520218</v>
       </c>
       <c r="H561" t="n">
         <v>103.7907</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>69.24498699999999</v>
+        <v>69.24498</v>
       </c>
       <c r="H562" t="n">
         <v>104.8886</v>
@@ -21884,7 +21884,7 @@
         </is>
       </c>
       <c r="G565" t="n">
-        <v>69.69551800000001</v>
+        <v>69.695526</v>
       </c>
       <c r="H565" t="n">
         <v>105.571</v>
@@ -22074,7 +22074,7 @@
         </is>
       </c>
       <c r="G570" t="n">
-        <v>71.340935</v>
+        <v>71.340942</v>
       </c>
       <c r="H570" t="n">
         <v>108.0634</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>71.291977</v>
+        <v>71.29196899999999</v>
       </c>
       <c r="H571" t="n">
         <v>107.9892</v>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>70.06770299999999</v>
+        <v>70.067696</v>
       </c>
       <c r="H573" t="n">
         <v>106.1348</v>
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>70.87082700000001</v>
+        <v>70.870819</v>
       </c>
       <c r="H575" t="n">
         <v>107.3513</v>
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="G576" t="n">
-        <v>70.518227</v>
+        <v>70.51823400000001</v>
       </c>
       <c r="H576" t="n">
         <v>106.8172</v>
@@ -22378,7 +22378,7 @@
         </is>
       </c>
       <c r="G578" t="n">
-        <v>70.410484</v>
+        <v>70.4105</v>
       </c>
       <c r="H578" t="n">
         <v>106.654</v>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.68472300000001</v>
+        <v>70.684731</v>
       </c>
       <c r="H580" t="n">
         <v>107.0694</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H582" t="n">
         <v>108.5827</v>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>72.349754</v>
+        <v>72.34974699999999</v>
       </c>
       <c r="H585" t="n">
         <v>109.5915</v>
@@ -22720,7 +22720,7 @@
         </is>
       </c>
       <c r="G587" t="n">
-        <v>73.30956999999999</v>
+        <v>73.309578</v>
       </c>
       <c r="H587" t="n">
         <v>111.0454</v>
@@ -22758,7 +22758,7 @@
         </is>
       </c>
       <c r="G588" t="n">
-        <v>73.564224</v>
+        <v>73.564232</v>
       </c>
       <c r="H588" t="n">
         <v>111.4311</v>
@@ -22796,7 +22796,7 @@
         </is>
       </c>
       <c r="G589" t="n">
-        <v>74.12249</v>
+        <v>74.12249799999999</v>
       </c>
       <c r="H589" t="n">
         <v>112.2768</v>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>73.838463</v>
+        <v>73.83847</v>
       </c>
       <c r="H590" t="n">
         <v>111.8465</v>
@@ -22986,7 +22986,7 @@
         </is>
       </c>
       <c r="G594" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H594" t="n">
         <v>112.8405</v>
@@ -23024,7 +23024,7 @@
         </is>
       </c>
       <c r="G595" t="n">
-        <v>74.49466700000001</v>
+        <v>74.494675</v>
       </c>
       <c r="H595" t="n">
         <v>112.8405</v>
@@ -23100,7 +23100,7 @@
         </is>
       </c>
       <c r="G597" t="n">
-        <v>74.524063</v>
+        <v>74.524055</v>
       </c>
       <c r="H597" t="n">
         <v>112.885</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>74.729744</v>
+        <v>74.729736</v>
       </c>
       <c r="H598" t="n">
         <v>113.1966</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>75.141098</v>
+        <v>75.14109000000001</v>
       </c>
       <c r="H599" t="n">
         <v>113.8197</v>
@@ -23214,7 +23214,7 @@
         </is>
       </c>
       <c r="G600" t="n">
-        <v>75.278206</v>
+        <v>75.27821400000001</v>
       </c>
       <c r="H600" t="n">
         <v>114.0274</v>
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G602" t="n">
-        <v>75.00398300000001</v>
+        <v>75.003967</v>
       </c>
       <c r="H602" t="n">
         <v>113.612</v>
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="G603" t="n">
-        <v>73.35855100000001</v>
+        <v>73.358543</v>
       </c>
       <c r="H603" t="n">
         <v>111.1196</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>72.721924</v>
+        <v>72.721931</v>
       </c>
       <c r="H608" t="n">
         <v>110.1553</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H609" t="n">
         <v>109.725</v>
@@ -23746,7 +23746,7 @@
         </is>
       </c>
       <c r="G614" t="n">
-        <v>71.514084</v>
+        <v>71.514076</v>
       </c>
       <c r="H614" t="n">
         <v>108.3257</v>
@@ -23784,7 +23784,7 @@
         </is>
       </c>
       <c r="G615" t="n">
-        <v>70.854561</v>
+        <v>70.854553</v>
       </c>
       <c r="H615" t="n">
         <v>107.3267</v>
@@ -23860,10 +23860,10 @@
         </is>
       </c>
       <c r="G617" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H617" t="n">
-        <v>108.1617</v>
+        <v>108.1616</v>
       </c>
     </row>
     <row r="618">
@@ -23974,10 +23974,10 @@
         </is>
       </c>
       <c r="G620" t="n">
-        <v>71.4058</v>
+        <v>71.40579200000001</v>
       </c>
       <c r="H620" t="n">
-        <v>108.1617</v>
+        <v>108.1616</v>
       </c>
     </row>
     <row r="621">
@@ -24088,7 +24088,7 @@
         </is>
       </c>
       <c r="G623" t="n">
-        <v>72.685463</v>
+        <v>72.68547100000001</v>
       </c>
       <c r="H623" t="n">
         <v>110.1</v>
@@ -24164,7 +24164,7 @@
         </is>
       </c>
       <c r="G625" t="n">
-        <v>72.449219</v>
+        <v>72.449226</v>
       </c>
       <c r="H625" t="n">
         <v>109.7422</v>
@@ -24240,7 +24240,7 @@
         </is>
       </c>
       <c r="G627" t="n">
-        <v>73.945465</v>
+        <v>73.945457</v>
       </c>
       <c r="H627" t="n">
         <v>112.0086</v>
@@ -24278,7 +24278,7 @@
         </is>
       </c>
       <c r="G628" t="n">
-        <v>73.77810700000001</v>
+        <v>73.778114</v>
       </c>
       <c r="H628" t="n">
         <v>111.7551</v>
@@ -24354,7 +24354,7 @@
         </is>
       </c>
       <c r="G630" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H630" t="n">
         <v>111.8297</v>
@@ -24430,7 +24430,7 @@
         </is>
       </c>
       <c r="G632" t="n">
-        <v>73.807655</v>
+        <v>73.807648</v>
       </c>
       <c r="H632" t="n">
         <v>111.7999</v>
@@ -24582,7 +24582,7 @@
         </is>
       </c>
       <c r="G636" t="n">
-        <v>73.827332</v>
+        <v>73.82733899999999</v>
       </c>
       <c r="H636" t="n">
         <v>111.8297</v>
@@ -24696,10 +24696,10 @@
         </is>
       </c>
       <c r="G639" t="n">
-        <v>73.532028</v>
+        <v>73.532021</v>
       </c>
       <c r="H639" t="n">
-        <v>111.3824</v>
+        <v>111.3823</v>
       </c>
     </row>
     <row r="640">
@@ -24734,7 +24734,7 @@
         </is>
       </c>
       <c r="G640" t="n">
-        <v>73.78795599999999</v>
+        <v>73.787964</v>
       </c>
       <c r="H640" t="n">
         <v>111.77</v>
@@ -24810,7 +24810,7 @@
         </is>
       </c>
       <c r="G642" t="n">
-        <v>74.427795</v>
+        <v>74.427803</v>
       </c>
       <c r="H642" t="n">
         <v>112.7392</v>
@@ -24924,7 +24924,7 @@
         </is>
       </c>
       <c r="G645" t="n">
-        <v>75.136543</v>
+        <v>75.13653600000001</v>
       </c>
       <c r="H645" t="n">
         <v>113.8128</v>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="G646" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H646" t="n">
         <v>113.0523</v>
@@ -25038,7 +25038,7 @@
         </is>
       </c>
       <c r="G648" t="n">
-        <v>74.634506</v>
+        <v>74.634514</v>
       </c>
       <c r="H648" t="n">
         <v>113.0523</v>
@@ -25228,7 +25228,7 @@
         </is>
       </c>
       <c r="G653" t="n">
-        <v>75.097168</v>
+        <v>75.09716</v>
       </c>
       <c r="H653" t="n">
         <v>113.7531</v>
@@ -25418,7 +25418,7 @@
         </is>
       </c>
       <c r="G658" t="n">
-        <v>77.095421</v>
+        <v>77.095428</v>
       </c>
       <c r="H658" t="n">
         <v>116.78</v>
@@ -25494,7 +25494,7 @@
         </is>
       </c>
       <c r="G660" t="n">
-        <v>76.57371500000001</v>
+        <v>76.573708</v>
       </c>
       <c r="H660" t="n">
         <v>115.9897</v>
@@ -25570,7 +25570,7 @@
         </is>
       </c>
       <c r="G662" t="n">
-        <v>76.278397</v>
+        <v>76.27840399999999</v>
       </c>
       <c r="H662" t="n">
         <v>115.5424</v>
@@ -25608,7 +25608,7 @@
         </is>
       </c>
       <c r="G663" t="n">
-        <v>76.179962</v>
+        <v>76.17997</v>
       </c>
       <c r="H663" t="n">
         <v>115.3933</v>
@@ -25798,10 +25798,10 @@
         </is>
       </c>
       <c r="G668" t="n">
-        <v>76.593391</v>
+        <v>76.59339900000001</v>
       </c>
       <c r="H668" t="n">
-        <v>116.0195</v>
+        <v>116.0196</v>
       </c>
     </row>
     <row r="669">
@@ -25836,7 +25836,7 @@
         </is>
       </c>
       <c r="G669" t="n">
-        <v>76.140587</v>
+        <v>76.14059399999999</v>
       </c>
       <c r="H669" t="n">
         <v>115.3337</v>
@@ -26064,7 +26064,7 @@
         </is>
       </c>
       <c r="G675" t="n">
-        <v>78.35541499999999</v>
+        <v>78.355408</v>
       </c>
       <c r="H675" t="n">
         <v>118.6886</v>
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>55.159622</v>
+        <v>55.159618</v>
       </c>
       <c r="H1510" t="n">
         <v>99.5605</v>
@@ -57946,10 +57946,10 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>54.818699</v>
+        <v>54.818707</v>
       </c>
       <c r="H1514" t="n">
-        <v>98.9451</v>
+        <v>98.9452</v>
       </c>
     </row>
     <row r="1515">
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1515" t="n">
         <v>99.7363</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.682339</v>
+        <v>54.682335</v>
       </c>
       <c r="H1516" t="n">
         <v>98.699</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.257019</v>
+        <v>55.257023</v>
       </c>
       <c r="H1517" t="n">
         <v>99.7363</v>
@@ -58212,7 +58212,7 @@
         </is>
       </c>
       <c r="G1521" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1521" t="n">
         <v>100.6329</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1522" t="n">
         <v>100.4219</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.588196</v>
+        <v>55.588188</v>
       </c>
       <c r="H1523" t="n">
         <v>100.334</v>
@@ -58364,7 +58364,7 @@
         </is>
       </c>
       <c r="G1525" t="n">
-        <v>55.295982</v>
+        <v>55.295986</v>
       </c>
       <c r="H1525" t="n">
         <v>99.8066</v>
@@ -58402,10 +58402,10 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.325199</v>
+        <v>55.325203</v>
       </c>
       <c r="H1526" t="n">
-        <v>99.8593</v>
+        <v>99.85939999999999</v>
       </c>
     </row>
     <row r="1527">
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.169353</v>
+        <v>55.169357</v>
       </c>
       <c r="H1527" t="n">
         <v>99.57810000000001</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.383648</v>
+        <v>55.383644</v>
       </c>
       <c r="H1531" t="n">
         <v>99.9648</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>56.104431</v>
+        <v>56.104427</v>
       </c>
       <c r="H1532" t="n">
         <v>101.2658</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>56.143391</v>
+        <v>56.143394</v>
       </c>
       <c r="H1534" t="n">
         <v>101.3361</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.60767</v>
+        <v>55.607677</v>
       </c>
       <c r="H1535" t="n">
         <v>100.3692</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.305725</v>
+        <v>55.305721</v>
       </c>
       <c r="H1536" t="n">
         <v>99.8242</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>54.341431</v>
+        <v>54.341427</v>
       </c>
       <c r="H1537" t="n">
         <v>98.08369999999999</v>
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>54.487534</v>
+        <v>54.48753</v>
       </c>
       <c r="H1539" t="n">
         <v>98.34739999999999</v>
@@ -58934,7 +58934,7 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.35117</v>
+        <v>54.351166</v>
       </c>
       <c r="H1540" t="n">
         <v>98.10129999999999</v>
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1541" t="n">
         <v>98.2243</v>
@@ -59086,7 +59086,7 @@
         </is>
       </c>
       <c r="G1544" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1544" t="n">
         <v>100.2989</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.753777</v>
+        <v>55.75378</v>
       </c>
       <c r="H1545" t="n">
         <v>100.6329</v>
@@ -59162,7 +59162,7 @@
         </is>
       </c>
       <c r="G1546" t="n">
-        <v>55.568707</v>
+        <v>55.56871</v>
       </c>
       <c r="H1546" t="n">
         <v>100.2989</v>
@@ -59200,7 +59200,7 @@
         </is>
       </c>
       <c r="G1547" t="n">
-        <v>55.63689</v>
+        <v>55.636894</v>
       </c>
       <c r="H1547" t="n">
         <v>100.4219</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.899883</v>
+        <v>55.899879</v>
       </c>
       <c r="H1551" t="n">
         <v>100.8966</v>
@@ -59580,7 +59580,7 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>56.060314</v>
+        <v>56.06031</v>
       </c>
       <c r="H1557" t="n">
         <v>101.1862</v>
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>56.558758</v>
+        <v>56.558754</v>
       </c>
       <c r="H1559" t="n">
         <v>102.0859</v>
@@ -59732,10 +59732,10 @@
         </is>
       </c>
       <c r="G1561" t="n">
-        <v>56.676037</v>
+        <v>56.676044</v>
       </c>
       <c r="H1561" t="n">
-        <v>102.2975</v>
+        <v>102.2976</v>
       </c>
     </row>
     <row r="1562">
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>57.692474</v>
+        <v>57.692471</v>
       </c>
       <c r="H1565" t="n">
         <v>104.1322</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>59.031433</v>
+        <v>59.031437</v>
       </c>
       <c r="H1570" t="n">
         <v>106.5489</v>
@@ -60188,7 +60188,7 @@
         </is>
       </c>
       <c r="G1573" t="n">
-        <v>59.148712</v>
+        <v>59.148716</v>
       </c>
       <c r="H1573" t="n">
         <v>106.7606</v>
@@ -60340,7 +60340,7 @@
         </is>
       </c>
       <c r="G1577" t="n">
-        <v>58.278881</v>
+        <v>58.278877</v>
       </c>
       <c r="H1577" t="n">
         <v>105.1906</v>
@@ -60378,7 +60378,7 @@
         </is>
       </c>
       <c r="G1578" t="n">
-        <v>58.259335</v>
+        <v>58.259331</v>
       </c>
       <c r="H1578" t="n">
         <v>105.1553</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>58.953243</v>
+        <v>58.953247</v>
       </c>
       <c r="H1581" t="n">
         <v>106.4078</v>
@@ -60530,7 +60530,7 @@
         </is>
       </c>
       <c r="G1582" t="n">
-        <v>59.305092</v>
+        <v>59.305088</v>
       </c>
       <c r="H1582" t="n">
         <v>107.0429</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>60.155376</v>
+        <v>60.155373</v>
       </c>
       <c r="H1591" t="n">
         <v>108.5776</v>
@@ -60986,10 +60986,10 @@
         </is>
       </c>
       <c r="G1594" t="n">
-        <v>59.930588</v>
+        <v>59.930584</v>
       </c>
       <c r="H1594" t="n">
-        <v>108.1719</v>
+        <v>108.1718</v>
       </c>
     </row>
     <row r="1595">
@@ -61138,7 +61138,7 @@
         </is>
       </c>
       <c r="G1598" t="n">
-        <v>60.956791</v>
+        <v>60.956795</v>
       </c>
       <c r="H1598" t="n">
         <v>110.0241</v>
@@ -61214,7 +61214,7 @@
         </is>
       </c>
       <c r="G1600" t="n">
-        <v>61.20113</v>
+        <v>61.201126</v>
       </c>
       <c r="H1600" t="n">
         <v>110.4651</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>60.868832</v>
+        <v>60.868835</v>
       </c>
       <c r="H1601" t="n">
         <v>109.8653</v>
@@ -61290,10 +61290,10 @@
         </is>
       </c>
       <c r="G1602" t="n">
-        <v>61.015438</v>
+        <v>61.015434</v>
       </c>
       <c r="H1602" t="n">
-        <v>110.13</v>
+        <v>110.1299</v>
       </c>
     </row>
     <row r="1603">
@@ -61328,7 +61328,7 @@
         </is>
       </c>
       <c r="G1603" t="n">
-        <v>61.474789</v>
+        <v>61.474785</v>
       </c>
       <c r="H1603" t="n">
         <v>110.9591</v>
@@ -61404,7 +61404,7 @@
         </is>
       </c>
       <c r="G1605" t="n">
-        <v>61.445469</v>
+        <v>61.445465</v>
       </c>
       <c r="H1605" t="n">
         <v>110.9061</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>58.640491</v>
+        <v>58.640495</v>
       </c>
       <c r="H1607" t="n">
         <v>105.8433</v>
@@ -61518,7 +61518,7 @@
         </is>
       </c>
       <c r="G1608" t="n">
-        <v>59.393047</v>
+        <v>59.393051</v>
       </c>
       <c r="H1608" t="n">
         <v>107.2016</v>
@@ -61594,7 +61594,7 @@
         </is>
       </c>
       <c r="G1610" t="n">
-        <v>58.054092</v>
+        <v>58.054089</v>
       </c>
       <c r="H1610" t="n">
         <v>104.7849</v>
@@ -61708,7 +61708,7 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>58.454803</v>
+        <v>58.4548</v>
       </c>
       <c r="H1613" t="n">
         <v>105.5081</v>
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>58.112732</v>
+        <v>58.112728</v>
       </c>
       <c r="H1614" t="n">
         <v>104.8907</v>
@@ -61784,7 +61784,7 @@
         </is>
       </c>
       <c r="G1615" t="n">
-        <v>57.790207</v>
+        <v>57.790211</v>
       </c>
       <c r="H1615" t="n">
         <v>104.3086</v>
@@ -61860,7 +61860,7 @@
         </is>
       </c>
       <c r="G1617" t="n">
-        <v>58.430058</v>
+        <v>58.430054</v>
       </c>
       <c r="H1617" t="n">
         <v>105.4635</v>
@@ -62582,7 +62582,7 @@
         </is>
       </c>
       <c r="G1636" t="n">
-        <v>60.15435</v>
+        <v>60.154354</v>
       </c>
       <c r="H1636" t="n">
         <v>108.5757</v>
@@ -62658,10 +62658,10 @@
         </is>
       </c>
       <c r="G1638" t="n">
-        <v>61.085075</v>
+        <v>61.085079</v>
       </c>
       <c r="H1638" t="n">
-        <v>110.2556</v>
+        <v>110.2557</v>
       </c>
     </row>
     <row r="1639">
@@ -62734,7 +62734,7 @@
         </is>
       </c>
       <c r="G1640" t="n">
-        <v>60.075977</v>
+        <v>60.075974</v>
       </c>
       <c r="H1640" t="n">
         <v>108.4343</v>
@@ -62810,7 +62810,7 @@
         </is>
       </c>
       <c r="G1642" t="n">
-        <v>59.948608</v>
+        <v>59.948612</v>
       </c>
       <c r="H1642" t="n">
         <v>108.2044</v>
@@ -62848,7 +62848,7 @@
         </is>
       </c>
       <c r="G1643" t="n">
-        <v>59.625305</v>
+        <v>59.625309</v>
       </c>
       <c r="H1643" t="n">
         <v>107.6208</v>
@@ -62962,7 +62962,7 @@
         </is>
       </c>
       <c r="G1646" t="n">
-        <v>58.949303</v>
+        <v>58.949306</v>
       </c>
       <c r="H1646" t="n">
         <v>106.4007</v>
@@ -63076,7 +63076,7 @@
         </is>
       </c>
       <c r="G1649" t="n">
-        <v>59.733074</v>
+        <v>59.733078</v>
       </c>
       <c r="H1649" t="n">
         <v>107.8154</v>
@@ -63114,7 +63114,7 @@
         </is>
       </c>
       <c r="G1650" t="n">
-        <v>61.055687</v>
+        <v>61.055683</v>
       </c>
       <c r="H1650" t="n">
         <v>110.2026</v>
@@ -63190,7 +63190,7 @@
         </is>
       </c>
       <c r="G1652" t="n">
-        <v>60.056377</v>
+        <v>60.056381</v>
       </c>
       <c r="H1652" t="n">
         <v>108.3989</v>
@@ -63266,7 +63266,7 @@
         </is>
       </c>
       <c r="G1654" t="n">
-        <v>59.507744</v>
+        <v>59.50774</v>
       </c>
       <c r="H1654" t="n">
         <v>107.4086</v>
@@ -63646,7 +63646,7 @@
         </is>
       </c>
       <c r="G1664" t="n">
-        <v>61.878643</v>
+        <v>61.878647</v>
       </c>
       <c r="H1664" t="n">
         <v>111.688</v>
@@ -63722,10 +63722,10 @@
         </is>
       </c>
       <c r="G1666" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1666" t="n">
-        <v>111.2106</v>
+        <v>111.2105</v>
       </c>
     </row>
     <row r="1667">
@@ -63836,7 +63836,7 @@
         </is>
       </c>
       <c r="G1669" t="n">
-        <v>61.682701</v>
+        <v>61.682705</v>
       </c>
       <c r="H1669" t="n">
         <v>111.3343</v>
@@ -63912,10 +63912,10 @@
         </is>
       </c>
       <c r="G1671" t="n">
-        <v>61.614124</v>
+        <v>61.61412</v>
       </c>
       <c r="H1671" t="n">
-        <v>111.2106</v>
+        <v>111.2105</v>
       </c>
     </row>
     <row r="1672">
@@ -63950,7 +63950,7 @@
         </is>
       </c>
       <c r="G1672" t="n">
-        <v>61.369198</v>
+        <v>61.369194</v>
       </c>
       <c r="H1672" t="n">
         <v>110.7685</v>
@@ -64102,7 +64102,7 @@
         </is>
       </c>
       <c r="G1676" t="n">
-        <v>61.290821</v>
+        <v>61.290817</v>
       </c>
       <c r="H1676" t="n">
         <v>110.627</v>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -9999,7 +9999,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>36.84</v>
+        <v>36.810001</v>
       </c>
       <c r="H253" t="n">
-        <v>123.005</v>
+        <v>122.9048</v>
       </c>
     </row>
     <row r="254">
@@ -19537,7 +19537,7 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.59</v>
+        <v>49.41</v>
       </c>
       <c r="H504" t="n">
-        <v>127.9526</v>
+        <v>130.1119</v>
       </c>
     </row>
     <row r="505">
@@ -19680,7 +19680,7 @@
         </is>
       </c>
       <c r="G507" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H507" t="n">
         <v>98.2593</v>
@@ -19756,7 +19756,7 @@
         </is>
       </c>
       <c r="G509" t="n">
-        <v>65.111969</v>
+        <v>65.111977</v>
       </c>
       <c r="H509" t="n">
         <v>98.6281</v>
@@ -19908,7 +19908,7 @@
         </is>
       </c>
       <c r="G513" t="n">
-        <v>65.842361</v>
+        <v>65.84236900000001</v>
       </c>
       <c r="H513" t="n">
         <v>99.7345</v>
@@ -20022,10 +20022,10 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>66.06635300000001</v>
+        <v>66.066345</v>
       </c>
       <c r="H516" t="n">
-        <v>100.0738</v>
+        <v>100.0737</v>
       </c>
     </row>
     <row r="517">
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>66.339035</v>
+        <v>66.339043</v>
       </c>
       <c r="H518" t="n">
         <v>100.4868</v>
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>66.290344</v>
+        <v>66.29033699999999</v>
       </c>
       <c r="H524" t="n">
         <v>100.413</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H529" t="n">
         <v>102.3455</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H530" t="n">
         <v>101.5784</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>65.754715</v>
+        <v>65.754723</v>
       </c>
       <c r="H533" t="n">
         <v>99.60169999999999</v>
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.24472</v>
+        <v>67.24472799999999</v>
       </c>
       <c r="H541" t="n">
         <v>101.8587</v>
@@ -21010,7 +21010,7 @@
         </is>
       </c>
       <c r="G542" t="n">
-        <v>67.059692</v>
+        <v>67.059685</v>
       </c>
       <c r="H542" t="n">
         <v>101.5784</v>
@@ -21200,7 +21200,7 @@
         </is>
       </c>
       <c r="G547" t="n">
-        <v>67.283676</v>
+        <v>67.283669</v>
       </c>
       <c r="H547" t="n">
         <v>101.9177</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.22525</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H549" t="n">
         <v>101.8292</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H550" t="n">
         <v>102.2127</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H553" t="n">
         <v>101.7407</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.23497</v>
+        <v>67.234978</v>
       </c>
       <c r="H554" t="n">
         <v>101.8439</v>
@@ -29075,7 +29075,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.239998</v>
+        <v>80.650002</v>
       </c>
       <c r="H755" t="n">
-        <v>121.5432</v>
+        <v>122.1643</v>
       </c>
     </row>
     <row r="756">
@@ -38613,7 +38613,7 @@
     <row r="1006">
       <c r="A1006" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B1006" t="inlineStr">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>130.979996</v>
+        <v>131.470001</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.0619</v>
+        <v>119.5073</v>
       </c>
     </row>
     <row r="1007">
@@ -48151,7 +48151,7 @@
     <row r="1257">
       <c r="A1257" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B1257" t="inlineStr">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>130.979996</v>
+        <v>131.470001</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.0619</v>
+        <v>119.5073</v>
       </c>
     </row>
     <row r="1258">
@@ -57689,7 +57689,7 @@
     <row r="1508">
       <c r="A1508" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B1508" t="inlineStr">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>130.979996</v>
+        <v>131.470001</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.0619</v>
+        <v>119.5073</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>55.159618</v>
+        <v>55.159622</v>
       </c>
       <c r="H1510" t="n">
         <v>99.5605</v>
@@ -57870,7 +57870,7 @@
         </is>
       </c>
       <c r="G1512" t="n">
-        <v>54.740784</v>
+        <v>54.74078</v>
       </c>
       <c r="H1512" t="n">
         <v>98.8045</v>
@@ -57908,7 +57908,7 @@
         </is>
       </c>
       <c r="G1513" t="n">
-        <v>54.536236</v>
+        <v>54.53624</v>
       </c>
       <c r="H1513" t="n">
         <v>98.4353</v>
@@ -57984,7 +57984,7 @@
         </is>
       </c>
       <c r="G1515" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1515" t="n">
         <v>99.7363</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>54.682335</v>
+        <v>54.682339</v>
       </c>
       <c r="H1516" t="n">
         <v>98.699</v>
@@ -58060,7 +58060,7 @@
         </is>
       </c>
       <c r="G1517" t="n">
-        <v>55.257023</v>
+        <v>55.257019</v>
       </c>
       <c r="H1517" t="n">
         <v>99.7363</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.169357</v>
+        <v>55.169353</v>
       </c>
       <c r="H1527" t="n">
         <v>99.57810000000001</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>55.383644</v>
+        <v>55.383648</v>
       </c>
       <c r="H1531" t="n">
         <v>99.9648</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1532" t="n">
         <v>101.2658</v>
@@ -58706,7 +58706,7 @@
         </is>
       </c>
       <c r="G1534" t="n">
-        <v>56.143394</v>
+        <v>56.143391</v>
       </c>
       <c r="H1534" t="n">
         <v>101.3361</v>
@@ -58744,7 +58744,7 @@
         </is>
       </c>
       <c r="G1535" t="n">
-        <v>55.607677</v>
+        <v>55.607674</v>
       </c>
       <c r="H1535" t="n">
         <v>100.3692</v>
@@ -58782,7 +58782,7 @@
         </is>
       </c>
       <c r="G1536" t="n">
-        <v>55.305721</v>
+        <v>55.305717</v>
       </c>
       <c r="H1536" t="n">
         <v>99.8242</v>
@@ -58858,7 +58858,7 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>54.292725</v>
+        <v>54.292728</v>
       </c>
       <c r="H1538" t="n">
         <v>97.9958</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.958328</v>
+        <v>55.958324</v>
       </c>
       <c r="H1549" t="n">
         <v>101.0021</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.987541</v>
+        <v>55.987545</v>
       </c>
       <c r="H1550" t="n">
         <v>101.0548</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1551" t="n">
         <v>100.8966</v>
@@ -59428,7 +59428,7 @@
         </is>
       </c>
       <c r="G1553" t="n">
-        <v>55.870663</v>
+        <v>55.870659</v>
       </c>
       <c r="H1553" t="n">
         <v>100.8439</v>
@@ -67265,7 +67265,7 @@
     <row r="1760">
       <c r="A1760" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B1760" t="inlineStr">
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>61.93</v>
+        <v>62.439999</v>
       </c>
       <c r="H1760" t="n">
-        <v>111.7807</v>
+        <v>112.7012</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -10028,10 +10028,10 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>37.884998</v>
+        <v>38.060001</v>
       </c>
       <c r="H253" t="n">
-        <v>125.4262</v>
+        <v>126.0056</v>
       </c>
     </row>
     <row r="254">
@@ -19566,10 +19566,10 @@
         </is>
       </c>
       <c r="G504" t="n">
-        <v>48.965</v>
+        <v>48.904999</v>
       </c>
       <c r="H504" t="n">
-        <v>129.076</v>
+        <v>128.9179</v>
       </c>
     </row>
     <row r="505">
@@ -19604,7 +19604,7 @@
         </is>
       </c>
       <c r="G505" t="n">
-        <v>65.91052999999999</v>
+        <v>65.910538</v>
       </c>
       <c r="H505" t="n">
         <v>100</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H520" t="n">
         <v>100.2807</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.095573</v>
+        <v>66.095581</v>
       </c>
       <c r="H522" t="n">
         <v>100.2807</v>
@@ -20291,7 +20291,7 @@
         <v>66.290344</v>
       </c>
       <c r="H523" t="n">
-        <v>100.5763</v>
+        <v>100.5762</v>
       </c>
     </row>
     <row r="524">
@@ -20326,7 +20326,7 @@
         </is>
       </c>
       <c r="G524" t="n">
-        <v>65.988457</v>
+        <v>65.988449</v>
       </c>
       <c r="H524" t="n">
         <v>100.1182</v>
@@ -20364,7 +20364,7 @@
         </is>
       </c>
       <c r="G525" t="n">
-        <v>65.57942199999999</v>
+        <v>65.579414</v>
       </c>
       <c r="H525" t="n">
         <v>99.49760000000001</v>
@@ -20405,7 +20405,7 @@
         <v>66.36824799999999</v>
       </c>
       <c r="H526" t="n">
-        <v>100.6945</v>
+        <v>100.6944</v>
       </c>
     </row>
     <row r="527">
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>67.566086</v>
+        <v>67.566093</v>
       </c>
       <c r="H528" t="n">
         <v>102.5118</v>
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="G529" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H529" t="n">
         <v>101.7435</v>
@@ -20554,7 +20554,7 @@
         </is>
       </c>
       <c r="G530" t="n">
-        <v>66.777275</v>
+        <v>66.77726699999999</v>
       </c>
       <c r="H530" t="n">
         <v>101.315</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>65.715767</v>
+        <v>65.71577499999999</v>
       </c>
       <c r="H533" t="n">
         <v>99.7045</v>
@@ -20706,7 +20706,7 @@
         </is>
       </c>
       <c r="G534" t="n">
-        <v>66.027412</v>
+        <v>66.027405</v>
       </c>
       <c r="H534" t="n">
         <v>100.1773</v>
@@ -20744,10 +20744,10 @@
         </is>
       </c>
       <c r="G535" t="n">
-        <v>65.891068</v>
+        <v>65.89106</v>
       </c>
       <c r="H535" t="n">
-        <v>99.9705</v>
+        <v>99.9704</v>
       </c>
     </row>
     <row r="536">
@@ -20782,10 +20782,10 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.124786</v>
+        <v>66.124779</v>
       </c>
       <c r="H536" t="n">
-        <v>100.3251</v>
+        <v>100.325</v>
       </c>
     </row>
     <row r="537">
@@ -20858,10 +20858,10 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>67.001259</v>
+        <v>67.001251</v>
       </c>
       <c r="H538" t="n">
-        <v>101.6549</v>
+        <v>101.6548</v>
       </c>
     </row>
     <row r="539">
@@ -20899,7 +20899,7 @@
         <v>66.96230300000001</v>
       </c>
       <c r="H539" t="n">
-        <v>101.5958</v>
+        <v>101.5957</v>
       </c>
     </row>
     <row r="540">
@@ -20972,7 +20972,7 @@
         </is>
       </c>
       <c r="G541" t="n">
-        <v>67.059685</v>
+        <v>67.059692</v>
       </c>
       <c r="H541" t="n">
         <v>101.7435</v>
@@ -21086,7 +21086,7 @@
         </is>
       </c>
       <c r="G544" t="n">
-        <v>67.371323</v>
+        <v>67.371315</v>
       </c>
       <c r="H544" t="n">
         <v>102.2163</v>
@@ -21124,10 +21124,10 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>67.517403</v>
+        <v>67.51739499999999</v>
       </c>
       <c r="H545" t="n">
-        <v>102.438</v>
+        <v>102.4379</v>
       </c>
     </row>
     <row r="546">
@@ -21238,7 +21238,7 @@
         </is>
       </c>
       <c r="G548" t="n">
-        <v>67.22525</v>
+        <v>67.22524300000001</v>
       </c>
       <c r="H548" t="n">
         <v>101.9947</v>
@@ -21276,7 +21276,7 @@
         </is>
       </c>
       <c r="G549" t="n">
-        <v>67.47843899999999</v>
+        <v>67.478447</v>
       </c>
       <c r="H549" t="n">
         <v>102.3788</v>
@@ -21428,7 +21428,7 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.23498499999999</v>
+        <v>67.234978</v>
       </c>
       <c r="H553" t="n">
         <v>102.0095</v>
@@ -21466,7 +21466,7 @@
         </is>
       </c>
       <c r="G554" t="n">
-        <v>67.619148</v>
+        <v>67.619141</v>
       </c>
       <c r="H554" t="n">
         <v>102.5923</v>
@@ -21542,7 +21542,7 @@
         </is>
       </c>
       <c r="G556" t="n">
-        <v>67.81502500000001</v>
+        <v>67.815033</v>
       </c>
       <c r="H556" t="n">
         <v>102.8895</v>
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>68.27536000000001</v>
+        <v>68.275352</v>
       </c>
       <c r="H558" t="n">
         <v>103.5879</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>69.773865</v>
+        <v>69.773872</v>
       </c>
       <c r="H562" t="n">
         <v>105.8615</v>
@@ -21808,7 +21808,7 @@
         </is>
       </c>
       <c r="G563" t="n">
-        <v>69.480057</v>
+        <v>69.48004899999999</v>
       </c>
       <c r="H563" t="n">
         <v>105.4157</v>
@@ -21846,7 +21846,7 @@
         </is>
       </c>
       <c r="G564" t="n">
-        <v>69.695526</v>
+        <v>69.69551800000001</v>
       </c>
       <c r="H564" t="n">
         <v>105.7426</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>70.18523399999999</v>
+        <v>70.185226</v>
       </c>
       <c r="H566" t="n">
         <v>106.4856</v>
@@ -21960,7 +21960,7 @@
         </is>
       </c>
       <c r="G567" t="n">
-        <v>70.273369</v>
+        <v>70.273376</v>
       </c>
       <c r="H567" t="n">
         <v>106.6193</v>
@@ -21998,7 +21998,7 @@
         </is>
       </c>
       <c r="G568" t="n">
-        <v>70.645554</v>
+        <v>70.645561</v>
       </c>
       <c r="H568" t="n">
         <v>107.184</v>
@@ -22112,7 +22112,7 @@
         </is>
       </c>
       <c r="G571" t="n">
-        <v>70.72391500000001</v>
+        <v>70.723907</v>
       </c>
       <c r="H571" t="n">
         <v>107.3029</v>
@@ -22150,7 +22150,7 @@
         </is>
       </c>
       <c r="G572" t="n">
-        <v>70.067696</v>
+        <v>70.06770299999999</v>
       </c>
       <c r="H572" t="n">
         <v>106.3073</v>
@@ -22188,10 +22188,10 @@
         </is>
       </c>
       <c r="G573" t="n">
-        <v>70.371323</v>
+        <v>70.371315</v>
       </c>
       <c r="H573" t="n">
-        <v>106.768</v>
+        <v>106.7679</v>
       </c>
     </row>
     <row r="574">
@@ -22264,7 +22264,7 @@
         </is>
       </c>
       <c r="G575" t="n">
-        <v>70.51823400000001</v>
+        <v>70.518227</v>
       </c>
       <c r="H575" t="n">
         <v>106.9908</v>
@@ -22340,7 +22340,7 @@
         </is>
       </c>
       <c r="G577" t="n">
-        <v>70.410492</v>
+        <v>70.410484</v>
       </c>
       <c r="H577" t="n">
         <v>106.8274</v>
@@ -22419,7 +22419,7 @@
         <v>70.684731</v>
       </c>
       <c r="H579" t="n">
-        <v>107.2435</v>
+        <v>107.2434</v>
       </c>
     </row>
     <row r="580">
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="G580" t="n">
-        <v>70.890411</v>
+        <v>70.890404</v>
       </c>
       <c r="H580" t="n">
         <v>107.5555</v>
@@ -22492,7 +22492,7 @@
         </is>
       </c>
       <c r="G581" t="n">
-        <v>71.683739</v>
+        <v>71.683746</v>
       </c>
       <c r="H581" t="n">
         <v>108.7592</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="G582" t="n">
-        <v>72.37912799999999</v>
+        <v>72.37913500000001</v>
       </c>
       <c r="H582" t="n">
         <v>109.8142</v>
@@ -22568,7 +22568,7 @@
         </is>
       </c>
       <c r="G583" t="n">
-        <v>72.878632</v>
+        <v>72.87863900000001</v>
       </c>
       <c r="H583" t="n">
         <v>110.5721</v>
@@ -22644,7 +22644,7 @@
         </is>
       </c>
       <c r="G585" t="n">
-        <v>73.201843</v>
+        <v>73.201836</v>
       </c>
       <c r="H585" t="n">
         <v>111.0624</v>
@@ -22761,7 +22761,7 @@
         <v>74.12249</v>
       </c>
       <c r="H588" t="n">
-        <v>112.4593</v>
+        <v>112.4592</v>
       </c>
     </row>
     <row r="589">
@@ -22834,10 +22834,10 @@
         </is>
       </c>
       <c r="G590" t="n">
-        <v>73.82867400000001</v>
+        <v>73.828667</v>
       </c>
       <c r="H590" t="n">
-        <v>112.0135</v>
+        <v>112.0134</v>
       </c>
     </row>
     <row r="591">
@@ -22910,7 +22910,7 @@
         </is>
       </c>
       <c r="G592" t="n">
-        <v>73.86784400000001</v>
+        <v>73.867851</v>
       </c>
       <c r="H592" t="n">
         <v>112.0729</v>
@@ -23138,7 +23138,7 @@
         </is>
       </c>
       <c r="G598" t="n">
-        <v>75.14109000000001</v>
+        <v>75.141098</v>
       </c>
       <c r="H598" t="n">
         <v>114.0047</v>
@@ -23176,7 +23176,7 @@
         </is>
       </c>
       <c r="G599" t="n">
-        <v>75.27821400000001</v>
+        <v>75.278206</v>
       </c>
       <c r="H599" t="n">
         <v>114.2127</v>
@@ -23252,7 +23252,7 @@
         </is>
       </c>
       <c r="G601" t="n">
-        <v>75.003975</v>
+        <v>75.00398300000001</v>
       </c>
       <c r="H601" t="n">
         <v>113.7966</v>
@@ -23331,7 +23331,7 @@
         <v>73.85805499999999</v>
       </c>
       <c r="H603" t="n">
-        <v>112.0581</v>
+        <v>112.058</v>
       </c>
     </row>
     <row r="604">
@@ -23366,7 +23366,7 @@
         </is>
       </c>
       <c r="G604" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H604" t="n">
         <v>110.9287</v>
@@ -23407,7 +23407,7 @@
         <v>72.026535</v>
       </c>
       <c r="H605" t="n">
-        <v>109.2793</v>
+        <v>109.2792</v>
       </c>
     </row>
     <row r="606">
@@ -23480,7 +23480,7 @@
         </is>
       </c>
       <c r="G607" t="n">
-        <v>72.72191599999999</v>
+        <v>72.721931</v>
       </c>
       <c r="H607" t="n">
         <v>110.3343</v>
@@ -23518,7 +23518,7 @@
         </is>
       </c>
       <c r="G608" t="n">
-        <v>72.437889</v>
+        <v>72.43789700000001</v>
       </c>
       <c r="H608" t="n">
         <v>109.9034</v>
@@ -23556,7 +23556,7 @@
         </is>
       </c>
       <c r="G609" t="n">
-        <v>72.55542800000001</v>
+        <v>72.55542</v>
       </c>
       <c r="H609" t="n">
         <v>110.0817</v>
@@ -23632,7 +23632,7 @@
         </is>
       </c>
       <c r="G611" t="n">
-        <v>73.113693</v>
+        <v>73.11370100000001</v>
       </c>
       <c r="H611" t="n">
         <v>110.9287</v>
@@ -23670,7 +23670,7 @@
         </is>
       </c>
       <c r="G612" t="n">
-        <v>72.643562</v>
+        <v>72.64357</v>
       </c>
       <c r="H612" t="n">
         <v>110.2154</v>
@@ -23711,7 +23711,7 @@
         <v>71.514084</v>
       </c>
       <c r="H613" t="n">
-        <v>108.5018</v>
+        <v>108.5017</v>
       </c>
     </row>
     <row r="614">
@@ -23787,7 +23787,7 @@
         <v>71.031746</v>
       </c>
       <c r="H615" t="n">
-        <v>107.77</v>
+        <v>107.7699</v>
       </c>
     </row>
     <row r="616">
@@ -23977,7 +23977,7 @@
         <v>72.05547300000001</v>
       </c>
       <c r="H620" t="n">
-        <v>109.3232</v>
+        <v>109.3231</v>
       </c>
     </row>
     <row r="621">
@@ -24129,7 +24129,7 @@
         <v>72.449219</v>
       </c>
       <c r="H624" t="n">
-        <v>109.9206</v>
+        <v>109.9205</v>
       </c>
     </row>
     <row r="625">
@@ -24243,7 +24243,7 @@
         <v>73.77810700000001</v>
       </c>
       <c r="H627" t="n">
-        <v>111.9368</v>
+        <v>111.9367</v>
       </c>
     </row>
     <row r="628">
@@ -24281,7 +24281,7 @@
         <v>73.492653</v>
       </c>
       <c r="H628" t="n">
-        <v>111.5037</v>
+        <v>111.5036</v>
       </c>
     </row>
     <row r="629">
@@ -25155,7 +25155,7 @@
         <v>75.047943</v>
       </c>
       <c r="H651" t="n">
-        <v>113.8634</v>
+        <v>113.8633</v>
       </c>
     </row>
     <row r="652">
@@ -25421,7 +25421,7 @@
         <v>76.741051</v>
       </c>
       <c r="H658" t="n">
-        <v>116.4322</v>
+        <v>116.4321</v>
       </c>
     </row>
     <row r="659">
@@ -25497,7 +25497,7 @@
         <v>76.34730500000001</v>
       </c>
       <c r="H660" t="n">
-        <v>115.8348</v>
+        <v>115.8347</v>
       </c>
     </row>
     <row r="661">
@@ -25649,7 +25649,7 @@
         <v>76.741051</v>
       </c>
       <c r="H664" t="n">
-        <v>116.4322</v>
+        <v>116.4321</v>
       </c>
     </row>
     <row r="665">
@@ -26409,7 +26409,7 @@
         <v>78.451363</v>
       </c>
       <c r="H684" t="n">
-        <v>119.0271</v>
+        <v>119.027</v>
       </c>
     </row>
     <row r="685">
@@ -26447,7 +26447,7 @@
         <v>78.938637</v>
       </c>
       <c r="H685" t="n">
-        <v>119.7664</v>
+        <v>119.7663</v>
       </c>
     </row>
     <row r="686">
@@ -26485,7 +26485,7 @@
         <v>79.42591899999999</v>
       </c>
       <c r="H686" t="n">
-        <v>120.5057</v>
+        <v>120.5056</v>
       </c>
     </row>
     <row r="687">
@@ -26751,7 +26751,7 @@
         <v>79.50547</v>
       </c>
       <c r="H693" t="n">
-        <v>120.6264</v>
+        <v>120.6263</v>
       </c>
     </row>
     <row r="694">
@@ -27929,7 +27929,7 @@
         <v>81.205963</v>
       </c>
       <c r="H724" t="n">
-        <v>123.2064</v>
+        <v>123.2063</v>
       </c>
     </row>
     <row r="725">
@@ -27967,7 +27967,7 @@
         <v>80.798241</v>
       </c>
       <c r="H725" t="n">
-        <v>122.5878</v>
+        <v>122.5877</v>
       </c>
     </row>
     <row r="726">
@@ -28233,7 +28233,7 @@
         <v>81.36507400000001</v>
       </c>
       <c r="H732" t="n">
-        <v>123.4478</v>
+        <v>123.4477</v>
       </c>
     </row>
     <row r="733">
@@ -28575,7 +28575,7 @@
         <v>80.5</v>
       </c>
       <c r="H741" t="n">
-        <v>122.1353</v>
+        <v>122.1352</v>
       </c>
     </row>
     <row r="742">
@@ -28765,7 +28765,7 @@
         <v>80.540001</v>
       </c>
       <c r="H746" t="n">
-        <v>122.196</v>
+        <v>122.1959</v>
       </c>
     </row>
     <row r="747">
@@ -29104,10 +29104,10 @@
         </is>
       </c>
       <c r="G755" t="n">
-        <v>80.989998</v>
+        <v>81.05999799999999</v>
       </c>
       <c r="H755" t="n">
-        <v>122.8787</v>
+        <v>122.9849</v>
       </c>
     </row>
     <row r="756">
@@ -38642,10 +38642,10 @@
         </is>
       </c>
       <c r="G1006" t="n">
-        <v>131.550003</v>
+        <v>131.669998</v>
       </c>
       <c r="H1006" t="n">
-        <v>119.5149</v>
+        <v>119.6239</v>
       </c>
     </row>
     <row r="1007">
@@ -48180,10 +48180,10 @@
         </is>
       </c>
       <c r="G1257" t="n">
-        <v>131.550003</v>
+        <v>131.669998</v>
       </c>
       <c r="H1257" t="n">
-        <v>119.5149</v>
+        <v>119.6239</v>
       </c>
     </row>
     <row r="1258">
@@ -57718,10 +57718,10 @@
         </is>
       </c>
       <c r="G1508" t="n">
-        <v>131.550003</v>
+        <v>131.669998</v>
       </c>
       <c r="H1508" t="n">
-        <v>119.5149</v>
+        <v>119.6239</v>
       </c>
     </row>
     <row r="1509">
@@ -57794,7 +57794,7 @@
         </is>
       </c>
       <c r="G1510" t="n">
-        <v>54.429092</v>
+        <v>54.429096</v>
       </c>
       <c r="H1510" t="n">
         <v>98.6756</v>
@@ -57832,7 +57832,7 @@
         </is>
       </c>
       <c r="G1511" t="n">
-        <v>54.74078</v>
+        <v>54.740784</v>
       </c>
       <c r="H1511" t="n">
         <v>99.2407</v>
@@ -57946,7 +57946,7 @@
         </is>
       </c>
       <c r="G1514" t="n">
-        <v>55.257015</v>
+        <v>55.257019</v>
       </c>
       <c r="H1514" t="n">
         <v>100.1766</v>
@@ -58022,7 +58022,7 @@
         </is>
       </c>
       <c r="G1516" t="n">
-        <v>55.257015</v>
+        <v>55.257019</v>
       </c>
       <c r="H1516" t="n">
         <v>100.1766</v>
@@ -58098,7 +58098,7 @@
         </is>
       </c>
       <c r="G1518" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1518" t="n">
         <v>100.2119</v>
@@ -58250,7 +58250,7 @@
         </is>
       </c>
       <c r="G1522" t="n">
-        <v>55.588192</v>
+        <v>55.588196</v>
       </c>
       <c r="H1522" t="n">
         <v>100.777</v>
@@ -58288,7 +58288,7 @@
         </is>
       </c>
       <c r="G1523" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1523" t="n">
         <v>100.671</v>
@@ -58402,7 +58402,7 @@
         </is>
       </c>
       <c r="G1526" t="n">
-        <v>55.169353</v>
+        <v>55.169357</v>
       </c>
       <c r="H1526" t="n">
         <v>100.0176</v>
@@ -58440,7 +58440,7 @@
         </is>
       </c>
       <c r="G1527" t="n">
-        <v>55.276501</v>
+        <v>55.276505</v>
       </c>
       <c r="H1527" t="n">
         <v>100.2119</v>
@@ -58478,7 +58478,7 @@
         </is>
       </c>
       <c r="G1528" t="n">
-        <v>54.867409</v>
+        <v>54.867413</v>
       </c>
       <c r="H1528" t="n">
         <v>99.47020000000001</v>
@@ -58554,7 +58554,7 @@
         </is>
       </c>
       <c r="G1530" t="n">
-        <v>55.383652</v>
+        <v>55.383648</v>
       </c>
       <c r="H1530" t="n">
         <v>100.4061</v>
@@ -58592,7 +58592,7 @@
         </is>
       </c>
       <c r="G1531" t="n">
-        <v>56.104427</v>
+        <v>56.104431</v>
       </c>
       <c r="H1531" t="n">
         <v>101.7129</v>
@@ -58630,7 +58630,7 @@
         </is>
       </c>
       <c r="G1532" t="n">
-        <v>56.523262</v>
+        <v>56.523266</v>
       </c>
       <c r="H1532" t="n">
         <v>102.4722</v>
@@ -58820,7 +58820,7 @@
         </is>
       </c>
       <c r="G1537" t="n">
-        <v>54.292725</v>
+        <v>54.292721</v>
       </c>
       <c r="H1537" t="n">
         <v>98.4284</v>
@@ -58858,10 +58858,10 @@
         </is>
       </c>
       <c r="G1538" t="n">
-        <v>54.487534</v>
+        <v>54.48753</v>
       </c>
       <c r="H1538" t="n">
-        <v>98.7816</v>
+        <v>98.78149999999999</v>
       </c>
     </row>
     <row r="1539">
@@ -58896,7 +58896,7 @@
         </is>
       </c>
       <c r="G1539" t="n">
-        <v>54.351166</v>
+        <v>54.35117</v>
       </c>
       <c r="H1539" t="n">
         <v>98.5343</v>
@@ -58934,10 +58934,10 @@
         </is>
       </c>
       <c r="G1540" t="n">
-        <v>54.419353</v>
+        <v>54.41935</v>
       </c>
       <c r="H1540" t="n">
-        <v>98.658</v>
+        <v>98.6579</v>
       </c>
     </row>
     <row r="1541">
@@ -58972,7 +58972,7 @@
         </is>
       </c>
       <c r="G1541" t="n">
-        <v>54.877148</v>
+        <v>54.877144</v>
       </c>
       <c r="H1541" t="n">
         <v>99.4879</v>
@@ -59010,7 +59010,7 @@
         </is>
       </c>
       <c r="G1542" t="n">
-        <v>55.529751</v>
+        <v>55.529747</v>
       </c>
       <c r="H1542" t="n">
         <v>100.671</v>
@@ -59048,7 +59048,7 @@
         </is>
       </c>
       <c r="G1543" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1543" t="n">
         <v>100.7416</v>
@@ -59124,7 +59124,7 @@
         </is>
       </c>
       <c r="G1545" t="n">
-        <v>55.56871</v>
+        <v>55.568707</v>
       </c>
       <c r="H1545" t="n">
         <v>100.7416</v>
@@ -59276,7 +59276,7 @@
         </is>
       </c>
       <c r="G1549" t="n">
-        <v>55.987545</v>
+        <v>55.987541</v>
       </c>
       <c r="H1549" t="n">
         <v>101.501</v>
@@ -59314,7 +59314,7 @@
         </is>
       </c>
       <c r="G1550" t="n">
-        <v>55.899879</v>
+        <v>55.899883</v>
       </c>
       <c r="H1550" t="n">
         <v>101.342</v>
@@ -59352,7 +59352,7 @@
         </is>
       </c>
       <c r="G1551" t="n">
-        <v>55.841438</v>
+        <v>55.841442</v>
       </c>
       <c r="H1551" t="n">
         <v>101.2361</v>
@@ -59504,7 +59504,7 @@
         </is>
       </c>
       <c r="G1555" t="n">
-        <v>56.294872</v>
+        <v>56.294876</v>
       </c>
       <c r="H1555" t="n">
         <v>102.0581</v>
@@ -59580,10 +59580,10 @@
         </is>
       </c>
       <c r="G1557" t="n">
-        <v>55.991898</v>
+        <v>55.991901</v>
       </c>
       <c r="H1557" t="n">
-        <v>101.5088</v>
+        <v>101.5089</v>
       </c>
     </row>
     <row r="1558">
@@ -59656,7 +59656,7 @@
         </is>
       </c>
       <c r="G1559" t="n">
-        <v>56.783546</v>
+        <v>56.783543</v>
       </c>
       <c r="H1559" t="n">
         <v>102.944</v>
@@ -59694,7 +59694,7 @@
         </is>
       </c>
       <c r="G1560" t="n">
-        <v>56.676041</v>
+        <v>56.676037</v>
       </c>
       <c r="H1560" t="n">
         <v>102.7491</v>
@@ -59884,7 +59884,7 @@
         </is>
       </c>
       <c r="G1565" t="n">
-        <v>58.210468</v>
+        <v>58.210464</v>
       </c>
       <c r="H1565" t="n">
         <v>105.5309</v>
@@ -60036,7 +60036,7 @@
         </is>
       </c>
       <c r="G1569" t="n">
-        <v>59.031437</v>
+        <v>59.031433</v>
       </c>
       <c r="H1569" t="n">
         <v>107.0193</v>
@@ -60074,7 +60074,7 @@
         </is>
       </c>
       <c r="G1570" t="n">
-        <v>59.129162</v>
+        <v>59.129166</v>
       </c>
       <c r="H1570" t="n">
         <v>107.1965</v>
@@ -60150,7 +60150,7 @@
         </is>
       </c>
       <c r="G1572" t="n">
-        <v>59.148716</v>
+        <v>59.148712</v>
       </c>
       <c r="H1572" t="n">
         <v>107.2319</v>
@@ -60302,7 +60302,7 @@
         </is>
       </c>
       <c r="G1576" t="n">
-        <v>58.278877</v>
+        <v>58.278881</v>
       </c>
       <c r="H1576" t="n">
         <v>105.655</v>
@@ -60492,7 +60492,7 @@
         </is>
       </c>
       <c r="G1581" t="n">
-        <v>59.305088</v>
+        <v>59.305092</v>
       </c>
       <c r="H1581" t="n">
         <v>107.5154</v>
@@ -60834,7 +60834,7 @@
         </is>
       </c>
       <c r="G1590" t="n">
-        <v>60.155373</v>
+        <v>60.155376</v>
       </c>
       <c r="H1590" t="n">
         <v>109.0569</v>
@@ -60872,7 +60872,7 @@
         </is>
       </c>
       <c r="G1591" t="n">
-        <v>60.116283</v>
+        <v>60.11628</v>
       </c>
       <c r="H1591" t="n">
         <v>108.986</v>
@@ -61176,7 +61176,7 @@
         </is>
       </c>
       <c r="G1599" t="n">
-        <v>61.201126</v>
+        <v>61.20113</v>
       </c>
       <c r="H1599" t="n">
         <v>110.9528</v>
@@ -61252,7 +61252,7 @@
         </is>
       </c>
       <c r="G1601" t="n">
-        <v>61.015434</v>
+        <v>61.015438</v>
       </c>
       <c r="H1601" t="n">
         <v>110.6161</v>
@@ -61442,7 +61442,7 @@
         </is>
       </c>
       <c r="G1606" t="n">
-        <v>58.640495</v>
+        <v>58.640491</v>
       </c>
       <c r="H1606" t="n">
         <v>106.3105</v>
@@ -61480,7 +61480,7 @@
         </is>
       </c>
       <c r="G1607" t="n">
-        <v>59.393051</v>
+        <v>59.393047</v>
       </c>
       <c r="H1607" t="n">
         <v>107.6749</v>
@@ -61670,7 +61670,7 @@
         </is>
       </c>
       <c r="G1612" t="n">
-        <v>58.4548</v>
+        <v>58.454803</v>
       </c>
       <c r="H1612" t="n">
         <v>105.9739</v>
@@ -61708,10 +61708,10 @@
         </is>
       </c>
       <c r="G1613" t="n">
-        <v>58.112728</v>
+        <v>58.112732</v>
       </c>
       <c r="H1613" t="n">
-        <v>105.3537</v>
+        <v>105.3538</v>
       </c>
     </row>
     <row r="1614">
@@ -61746,7 +61746,7 @@
         </is>
       </c>
       <c r="G1614" t="n">
-        <v>57.790211</v>
+        <v>57.790207</v>
       </c>
       <c r="H1614" t="n">
         <v>104.769</v>
@@ -67294,10 +67294,10 @@
         </is>
       </c>
       <c r="G1760" t="n">
-        <v>62.599998</v>
+        <v>62.59</v>
       </c>
       <c r="H1760" t="n">
-        <v>113.4888</v>
+        <v>113.4707</v>
       </c>
     </row>
   </sheetData>

--- a/AlphaForge_Fund_Price_History.xlsx
+++ b/AlphaForge_Fund_Price_History.xlsx
@@ -19642,7 +19642,7 @@
         </is>
       </c>
       <c r="G506" t="n">
-        <v>64.868515</v>
+        <v>64.86850699999999</v>
       </c>
       <c r="H506" t="n">
         <v>98.419</v>
@@ -19946,7 +19946,7 @@
         </is>
       </c>
       <c r="G514" t="n">
-        <v>65.939758</v>
+        <v>65.939751</v>
       </c>
       <c r="H514" t="n">
         <v>100.0443</v>
@@ -20022,7 +20022,7 @@
         </is>
       </c>
       <c r="G516" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H516" t="n">
         <v>100.7535</v>
@@ -20098,7 +20098,7 @@
         </is>
       </c>
       <c r="G518" t="n">
-        <v>66.212425</v>
+        <v>66.212433</v>
       </c>
       <c r="H518" t="n">
         <v>100.458</v>
@@ -20136,7 +20136,7 @@
         </is>
       </c>
       <c r="G519" t="n">
-        <v>66.407196</v>
+        <v>66.40720399999999</v>
       </c>
       <c r="H519" t="n">
         <v>100.7535</v>
@@ -20174,7 +20174,7 @@
         </is>
       </c>
       <c r="G520" t="n">
-        <v>66.095581</v>
+        <v>66.095573</v>
       </c>
       <c r="H520" t="n">
         <v>100.2807</v>
@@ -20212,7 +20212,7 @@
         </is>
       </c>
       <c r="G521" t="n">
-        <v>66.05661000000001</v>
+        <v>66.056618</v>
       </c>
       <c r="H521" t="n">
         <v>100.2216</v>
@@ -20250,7 +20250,7 @@
         </is>
       </c>
       <c r="G522" t="n">
-        <v>66.095581</v>
+        <v>66.095573</v>
       </c>
       <c r="H522" t="n">
         <v>100.2807</v>
@@ -20402,10 +20402,10 @@
         </is>
       </c>
       <c r="G526" t="n">
-        <v>66.36824799999999</v>
+        <v>66.368256</v>
       </c>
       <c r="H526" t="n">
-        <v>100.6944</v>
+        <v>100.6945</v>
       </c>
     </row>
     <row r="527">
@@ -20440,7 +20440,7 @@
         </is>
       </c>
       <c r="G527" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H527" t="n">
         <v>101.5662</v>
@@ -20478,7 +20478,7 @@
         </is>
       </c>
       <c r="G528" t="n">
-        <v>67.566093</v>
+        <v>67.566086</v>
       </c>
       <c r="H528" t="n">
         <v>102.5118</v>
@@ -20668,7 +20668,7 @@
         </is>
       </c>
       <c r="G533" t="n">
-        <v>65.71577499999999</v>
+        <v>65.715767</v>
       </c>
       <c r="H533" t="n">
         <v>99.7045</v>
@@ -20782,10 +20782,10 @@
         </is>
       </c>
       <c r="G536" t="n">
-        <v>66.124779</v>
+        <v>66.124786</v>
       </c>
       <c r="H536" t="n">
-        <v>100.325</v>
+        <v>100.3251</v>
       </c>
     </row>
     <row r="537">
@@ -20858,10 +20858,10 @@
         </is>
       </c>
       <c r="G538" t="n">
-        <v>67.001251</v>
+        <v>67.001259</v>
       </c>
       <c r="H538" t="n">
-        <v>101.6548</v>
+        <v>101.6549</v>
       </c>
     </row>
     <row r="539">
@@ -20896,10 +20896,10 @@
         </is>
       </c>
       <c r="G539" t="n">
-        <v>66.96230300000001</v>
+        <v>66.962311</v>
       </c>
       <c r="H539" t="n">
-        <v>101.5957</v>
+        <v>101.5958</v>
       </c>
     </row>
     <row r="540">
@@ -21048,7 +21048,7 @@
         </is>
       </c>
       <c r="G543" t="n">
-        <v>66.942825</v>
+        <v>66.942818</v>
       </c>
       <c r="H543" t="n">
         <v>101.5662</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="G545" t="n">
-        <v>67.51739499999999</v>
+        <v>67.517403</v>
       </c>
       <c r="H545" t="n">
         <v>102.4379</v>
@@ -21314,7 +21314,7 @@
         </is>
       </c>
       <c r="G550" t="n">
-        <v>67.390793</v>
+        <v>67.3908</v>
       </c>
       <c r="H550" t="n">
         <v>102.2459</v>
@@ -21352,7 +21352,7 @@
         </is>
       </c>
       <c r="G551" t="n">
-        <v>67.770599</v>
+        <v>67.77059199999999</v>
       </c>
       <c r="H551" t="n">
         <v>102.8221</v>
@@ -21390,7 +21390,7 @@
         </is>
       </c>
       <c r="G552" t="n">
-        <v>67.16681699999999</v>
+        <v>67.166809</v>
       </c>
       <c r="H552" t="n">
         <v>101.906</v>
@@ -21428,10 +21428,10 @@
         </is>
       </c>
       <c r="G553" t="n">
-        <v>67.234978</v>
+        <v>67.23497</v>
       </c>
       <c r="H553" t="n">
-        <v>102.0095</v>
+        <v>102.0094</v>
       </c>
     </row>
     <row r="554">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="G558" t="n">
-        <v>68.275352</v>
+        <v>68.27536000000001</v>
       </c>
       <c r="H558" t="n">
         <v>103.5879</v>
@@ -21656,7 +21656,7 @@
         </is>
       </c>
       <c r="G559" t="n">
-        <v>68.30474100000001</v>
+        <v>68.304733</v>
       </c>
       <c r="H559" t="n">
         <v>103.6325</v>
@@ -21770,7 +21770,7 @@
         </is>
       </c>
       <c r="G562" t="n">
-        <v>69.773872</v>
+        <v>69.773865</v>
       </c>
       <c r="H562" t="n">
         <v>105.8615</v>
@@ -21922,7 +21922,7 @@
         </is>
       </c>
       <c r="G566" t="n">
-        <v>70.185226</v